--- a/api/1/clv3/xlsx/fr/HumanitarianPlan.xlsx
+++ b/api/1/clv3/xlsx/fr/HumanitarianPlan.xlsx
@@ -25,15 +25,15 @@
     <t>codeforiati:plan-type</t>
   </si>
   <si>
+    <t>codeforiati:plan-end-date</t>
+  </si>
+  <si>
+    <t>codeforiati:plan-year</t>
+  </si>
+  <si>
     <t>codeforiati:plan-start-date</t>
   </si>
   <si>
-    <t>codeforiati:plan-year</t>
-  </si>
-  <si>
-    <t>codeforiati:plan-end-date</t>
-  </si>
-  <si>
     <t>HAFG25</t>
   </si>
   <si>
@@ -43,15 +43,15 @@
     <t>Humanitarian needs and response plan</t>
   </si>
   <si>
+    <t>2025-12-31</t>
+  </si>
+  <si>
+    <t>2025</t>
+  </si>
+  <si>
     <t>2025-01-01</t>
   </si>
   <si>
-    <t>2025</t>
-  </si>
-  <si>
-    <t>2025-12-31</t>
-  </si>
-  <si>
     <t>RIRNPAK25</t>
   </si>
   <si>
@@ -217,15 +217,15 @@
     <t>HAFG24</t>
   </si>
   <si>
+    <t>2024-12-31</t>
+  </si>
+  <si>
+    <t>2024</t>
+  </si>
+  <si>
     <t>2024-01-01</t>
   </si>
   <si>
-    <t>2024</t>
-  </si>
-  <si>
-    <t>2024-12-31</t>
-  </si>
-  <si>
     <t>RAFG_RRP24</t>
   </si>
   <si>
@@ -421,15 +421,15 @@
     <t>HAFG23</t>
   </si>
   <si>
+    <t>2023-12-31</t>
+  </si>
+  <si>
+    <t>2023</t>
+  </si>
+  <si>
     <t>2023-01-01</t>
   </si>
   <si>
-    <t>2023</t>
-  </si>
-  <si>
-    <t>2023-12-31</t>
-  </si>
-  <si>
     <t>RAFG23</t>
   </si>
   <si>
@@ -493,21 +493,21 @@
     <t>OMNG2223</t>
   </si>
   <si>
+    <t>2023-05-31</t>
+  </si>
+  <si>
     <t>2022-12-01</t>
   </si>
   <si>
-    <t>2023-05-31</t>
-  </si>
-  <si>
     <t>OMOZ23</t>
   </si>
   <si>
+    <t>2023-09-30</t>
+  </si>
+  <si>
     <t>2023-03-01</t>
   </si>
   <si>
-    <t>2023-09-30</t>
-  </si>
-  <si>
     <t>HMOZ23</t>
   </si>
   <si>
@@ -553,12 +553,12 @@
     <t>RRSDN23</t>
   </si>
   <si>
+    <t>2023-10-31</t>
+  </si>
+  <si>
     <t>2023-05-01</t>
   </si>
   <si>
-    <t>2023-10-31</t>
-  </si>
-  <si>
     <t>HSDN23</t>
   </si>
   <si>
@@ -601,15 +601,15 @@
     <t>HAFG22</t>
   </si>
   <si>
+    <t>2022-12-31</t>
+  </si>
+  <si>
+    <t>2022</t>
+  </si>
+  <si>
     <t>2022-01-01</t>
   </si>
   <si>
-    <t>2022</t>
-  </si>
-  <si>
-    <t>2022-12-31</t>
-  </si>
-  <si>
     <t>RAFG22</t>
   </si>
   <si>
@@ -631,12 +631,12 @@
     <t>OCUB2223</t>
   </si>
   <si>
+    <t>2023-03-31</t>
+  </si>
+  <si>
     <t>2022-10-20</t>
   </si>
   <si>
-    <t>2023-03-31</t>
-  </si>
-  <si>
     <t>RDRCRRP22</t>
   </si>
   <si>
@@ -652,12 +652,12 @@
     <t>FHTI2223</t>
   </si>
   <si>
+    <t>2023-04-15</t>
+  </si>
+  <si>
     <t>2022-10-16</t>
   </si>
   <si>
-    <t>2023-04-15</t>
-  </si>
-  <si>
     <t>FHTI22</t>
   </si>
   <si>
@@ -688,24 +688,24 @@
     <t>FMWI22</t>
   </si>
   <si>
+    <t>2022-05-31</t>
+  </si>
+  <si>
     <t>2022-02-26</t>
   </si>
   <si>
-    <t>2022-05-31</t>
-  </si>
-  <si>
     <t>HMLI22</t>
   </si>
   <si>
     <t>FMOZ22</t>
   </si>
   <si>
+    <t>2022-09-30</t>
+  </si>
+  <si>
     <t>2022-04-01</t>
   </si>
   <si>
-    <t>2022-09-30</t>
-  </si>
-  <si>
     <t>HMOZ22</t>
   </si>
   <si>
@@ -736,12 +736,12 @@
     <t>OPHL2122</t>
   </si>
   <si>
+    <t>2022-06-30</t>
+  </si>
+  <si>
     <t>2021-12-24</t>
   </si>
   <si>
-    <t>2022-06-30</t>
-  </si>
-  <si>
     <t>RREG22</t>
   </si>
   <si>
@@ -805,15 +805,15 @@
     <t>FAFG21</t>
   </si>
   <si>
+    <t>2021-12-31</t>
+  </si>
+  <si>
+    <t>2021</t>
+  </si>
+  <si>
     <t>2021-09-01</t>
   </si>
   <si>
-    <t>2021</t>
-  </si>
-  <si>
-    <t>2021-12-31</t>
-  </si>
-  <si>
     <t>HAFG21</t>
   </si>
   <si>
@@ -862,12 +862,12 @@
     <t>FPSE21</t>
   </si>
   <si>
+    <t>2021-08-27</t>
+  </si>
+  <si>
     <t>2021-05-27</t>
   </si>
   <si>
-    <t>2021-08-27</t>
-  </si>
-  <si>
     <t>HETH21</t>
   </si>
   <si>
@@ -880,24 +880,24 @@
     <t>FHTI2122</t>
   </si>
   <si>
+    <t>2022-02-15</t>
+  </si>
+  <si>
     <t>2021-08-16</t>
   </si>
   <si>
-    <t>2022-02-15</t>
-  </si>
-  <si>
     <t>HHTI21</t>
   </si>
   <si>
     <t>FHND2021</t>
   </si>
   <si>
+    <t>2021-06-30</t>
+  </si>
+  <si>
     <t>2020-11-15</t>
   </si>
   <si>
-    <t>2021-06-30</t>
-  </si>
-  <si>
     <t>HHND21</t>
   </si>
   <si>
@@ -916,12 +916,12 @@
     <t>OLBN2122</t>
   </si>
   <si>
+    <t>2022-07-31</t>
+  </si>
+  <si>
     <t>2021-08-03</t>
   </si>
   <si>
-    <t>2022-07-31</t>
-  </si>
-  <si>
     <t>HLBY21</t>
   </si>
   <si>
@@ -1009,15 +1009,15 @@
     <t>HAFG20</t>
   </si>
   <si>
+    <t>2020-12-31</t>
+  </si>
+  <si>
+    <t>2020</t>
+  </si>
+  <si>
     <t>2020-01-01</t>
   </si>
   <si>
-    <t>2020</t>
-  </si>
-  <si>
-    <t>2020-12-31</t>
-  </si>
-  <si>
     <t>OBGD20</t>
   </si>
   <si>
@@ -1081,12 +1081,12 @@
     <t>FDJI1920</t>
   </si>
   <si>
+    <t>2020-03-31</t>
+  </si>
+  <si>
     <t>2019-12-17</t>
   </si>
   <si>
-    <t>2020-03-31</t>
-  </si>
-  <si>
     <t>ODJI20</t>
   </si>
   <si>
@@ -1135,24 +1135,24 @@
     <t>FLBN20</t>
   </si>
   <si>
+    <t>2020-11-13</t>
+  </si>
+  <si>
     <t>2020-08-05</t>
   </si>
   <si>
-    <t>2020-11-13</t>
-  </si>
-  <si>
     <t>OLBN20</t>
   </si>
   <si>
     <t>FLSO1920</t>
   </si>
   <si>
+    <t>2020-04-30</t>
+  </si>
+  <si>
     <t>2019-11-01</t>
   </si>
   <si>
-    <t>2020-04-30</t>
-  </si>
-  <si>
     <t>OLBR20</t>
   </si>
   <si>
@@ -1249,15 +1249,15 @@
     <t>HAFG19</t>
   </si>
   <si>
+    <t>2019-12-31</t>
+  </si>
+  <si>
+    <t>2019</t>
+  </si>
+  <si>
     <t>2019-01-01</t>
   </si>
   <si>
-    <t>2019</t>
-  </si>
-  <si>
-    <t>2019-12-31</t>
-  </si>
-  <si>
     <t>RBGD19</t>
   </si>
   <si>
@@ -1366,12 +1366,12 @@
     <t>FZWE1920</t>
   </si>
   <si>
+    <t>2020-04-29</t>
+  </si>
+  <si>
     <t>2019-02-01</t>
   </si>
   <si>
-    <t>2020-04-29</t>
-  </si>
-  <si>
     <t>FZWE1820</t>
   </si>
   <si>
@@ -1381,15 +1381,15 @@
     <t>HAFG18</t>
   </si>
   <si>
+    <t>2018-12-31</t>
+  </si>
+  <si>
+    <t>2018</t>
+  </si>
+  <si>
     <t>2018-01-01</t>
   </si>
   <si>
-    <t>2018</t>
-  </si>
-  <si>
-    <t>2018-12-31</t>
-  </si>
-  <si>
     <t>OBGD18</t>
   </si>
   <si>
@@ -1483,12 +1483,12 @@
     <t>HSYR18</t>
   </si>
   <si>
+    <t>2018-12-30</t>
+  </si>
+  <si>
     <t>2018-11-30</t>
   </si>
   <si>
-    <t>2018-12-30</t>
-  </si>
-  <si>
     <t>RSYR18</t>
   </si>
   <si>
@@ -1507,15 +1507,15 @@
     <t>OEUR17</t>
   </si>
   <si>
+    <t>2017-12-31</t>
+  </si>
+  <si>
+    <t>2017</t>
+  </si>
+  <si>
     <t>2017-01-01</t>
   </si>
   <si>
-    <t>2017</t>
-  </si>
-  <si>
-    <t>2017-12-31</t>
-  </si>
-  <si>
     <t>HAFG17</t>
   </si>
   <si>
@@ -1558,12 +1558,12 @@
     <t>FDMA17</t>
   </si>
   <si>
+    <t>2017-12-29</t>
+  </si>
+  <si>
     <t>2017-09-28</t>
   </si>
   <si>
-    <t>2017-12-29</t>
-  </si>
-  <si>
     <t>OPRK17</t>
   </si>
   <si>
@@ -1585,24 +1585,24 @@
     <t>FKEN17</t>
   </si>
   <si>
+    <t>2017-11-30</t>
+  </si>
+  <si>
     <t>2017-02-10</t>
   </si>
   <si>
-    <t>2017-11-30</t>
-  </si>
-  <si>
     <t>HLBY17</t>
   </si>
   <si>
     <t>FMDG17</t>
   </si>
   <si>
+    <t>2017-06-20</t>
+  </si>
+  <si>
     <t>2017-03-20</t>
   </si>
   <si>
-    <t>2017-06-20</t>
-  </si>
-  <si>
     <t>HMLI17</t>
   </si>
   <si>
@@ -1612,12 +1612,12 @@
     <t>FMOZ17</t>
   </si>
   <si>
+    <t>2017-05-31</t>
+  </si>
+  <si>
     <t>2017-02-28</t>
   </si>
   <si>
-    <t>2017-05-31</t>
-  </si>
-  <si>
     <t>HMMR17</t>
   </si>
   <si>
@@ -1636,12 +1636,12 @@
     <t>FPER17</t>
   </si>
   <si>
+    <t>2017-10-31</t>
+  </si>
+  <si>
     <t>2017-04-01</t>
   </si>
   <si>
-    <t>2017-10-31</t>
-  </si>
-  <si>
     <t>HCOG17</t>
   </si>
   <si>
@@ -1678,15 +1678,15 @@
     <t>OEUR16</t>
   </si>
   <si>
+    <t>2016-12-31</t>
+  </si>
+  <si>
+    <t>2016</t>
+  </si>
+  <si>
     <t>2016-01-01</t>
   </si>
   <si>
-    <t>2016</t>
-  </si>
-  <si>
-    <t>2016-12-31</t>
-  </si>
-  <si>
     <t>HAFG16</t>
   </si>
   <si>
@@ -1726,21 +1726,21 @@
     <t>FECU16</t>
   </si>
   <si>
+    <t>2016-10-31</t>
+  </si>
+  <si>
     <t>2016-04-16</t>
   </si>
   <si>
-    <t>2016-10-31</t>
-  </si>
-  <si>
     <t>FFJI16</t>
   </si>
   <si>
+    <t>2016-05-30</t>
+  </si>
+  <si>
     <t>2016-02-20</t>
   </si>
   <si>
-    <t>2016-05-30</t>
-  </si>
-  <si>
     <t>HGMB16</t>
   </si>
   <si>
@@ -1783,12 +1783,12 @@
     <t>FIRQ16</t>
   </si>
   <si>
+    <t>2016-10-01</t>
+  </si>
+  <si>
     <t>2016-07-20</t>
   </si>
   <si>
-    <t>2016-10-01</t>
-  </si>
-  <si>
     <t>HMMR16</t>
   </si>
   <si>
@@ -1831,27 +1831,27 @@
     <t>HZWE1617</t>
   </si>
   <si>
+    <t>2017-03-31</t>
+  </si>
+  <si>
     <t>2016-04-01</t>
   </si>
   <si>
-    <t>2017-03-31</t>
-  </si>
-  <si>
     <t>HAFG15</t>
   </si>
   <si>
     <t>Strategic response plan</t>
   </si>
   <si>
+    <t>2015-12-31</t>
+  </si>
+  <si>
+    <t>2015</t>
+  </si>
+  <si>
     <t>2015-01-01</t>
   </si>
   <si>
-    <t>2015</t>
-  </si>
-  <si>
-    <t>2015-12-31</t>
-  </si>
-  <si>
     <t>HBFA15</t>
   </si>
   <si>
@@ -1879,12 +1879,12 @@
     <t>FGTM1415</t>
   </si>
   <si>
+    <t>2015-09-30</t>
+  </si>
+  <si>
     <t>2014-11-03</t>
   </si>
   <si>
-    <t>2015-09-30</t>
-  </si>
-  <si>
     <t>FHTI15</t>
   </si>
   <si>
@@ -1900,24 +1900,24 @@
     <t>FVUT15</t>
   </si>
   <si>
+    <t>2015-10-31</t>
+  </si>
+  <si>
     <t>2015-03-24</t>
   </si>
   <si>
-    <t>2015-10-31</t>
-  </si>
-  <si>
     <t>HIRQ15</t>
   </si>
   <si>
     <t>HLBY1415</t>
   </si>
   <si>
+    <t>2015-05-31</t>
+  </si>
+  <si>
     <t>2014-10-01</t>
   </si>
   <si>
-    <t>2015-05-31</t>
-  </si>
-  <si>
     <t>HMLI15</t>
   </si>
   <si>
@@ -1975,15 +1975,15 @@
     <t>HAFG14</t>
   </si>
   <si>
+    <t>2014-12-31</t>
+  </si>
+  <si>
+    <t>2014</t>
+  </si>
+  <si>
     <t>2014-01-01</t>
   </si>
   <si>
-    <t>2014</t>
-  </si>
-  <si>
-    <t>2014-12-31</t>
-  </si>
-  <si>
     <t>HBFA1314</t>
   </si>
   <si>
@@ -2059,21 +2059,21 @@
     <t>FPHL1314</t>
   </si>
   <si>
+    <t>2014-04-22</t>
+  </si>
+  <si>
     <t>2013-10-22</t>
   </si>
   <si>
-    <t>2014-04-22</t>
-  </si>
-  <si>
     <t>SPHL1314</t>
   </si>
   <si>
+    <t>2014-11-07</t>
+  </si>
+  <si>
     <t>2013-11-08</t>
   </si>
   <si>
-    <t>2014-11-07</t>
-  </si>
-  <si>
     <t>HPHL1314</t>
   </si>
   <si>
@@ -2083,12 +2083,12 @@
     <t>HPHL1314a</t>
   </si>
   <si>
+    <t>2014-08-31</t>
+  </si>
+  <si>
     <t>2013-10-01</t>
   </si>
   <si>
-    <t>2014-08-31</t>
-  </si>
-  <si>
     <t>SCOD14</t>
   </si>
   <si>
@@ -2152,12 +2152,12 @@
     <t>Consolidated appeals process</t>
   </si>
   <si>
+    <t>2013-12-31</t>
+  </si>
+  <si>
     <t>2013</t>
   </si>
   <si>
-    <t>2013-12-31</t>
-  </si>
-  <si>
     <t>CBFA13</t>
   </si>
   <si>
@@ -2242,15 +2242,15 @@
     <t>CKEN12</t>
   </si>
   <si>
+    <t>2012-12-31</t>
+  </si>
+  <si>
+    <t>2012</t>
+  </si>
+  <si>
     <t>2012-01-01</t>
   </si>
   <si>
-    <t>2012</t>
-  </si>
-  <si>
-    <t>2012-12-31</t>
-  </si>
-  <si>
     <t>CAFG1112</t>
   </si>
   <si>
@@ -2290,12 +2290,12 @@
     <t>FLSO1213</t>
   </si>
   <si>
+    <t>2013-03-25</t>
+  </si>
+  <si>
     <t>2012-09-18</t>
   </si>
   <si>
-    <t>2013-03-25</t>
-  </si>
-  <si>
     <t>CLBR12</t>
   </si>
   <si>
@@ -2335,12 +2335,12 @@
     <t>CSYR12</t>
   </si>
   <si>
+    <t>2012-12-05</t>
+  </si>
+  <si>
     <t>2012-06-05</t>
   </si>
   <si>
-    <t>2012-12-05</t>
-  </si>
-  <si>
     <t>CYEM12</t>
   </si>
   <si>
@@ -2353,12 +2353,12 @@
     <t>CKEN1113</t>
   </si>
   <si>
+    <t>2011</t>
+  </si>
+  <si>
     <t>2011-01-01</t>
   </si>
   <si>
-    <t>2011</t>
-  </si>
-  <si>
     <t>CAFG11</t>
   </si>
   <si>
@@ -2383,12 +2383,12 @@
     <t>FSLV1112</t>
   </si>
   <si>
+    <t>2012-04-25</t>
+  </si>
+  <si>
     <t>2011-10-25</t>
   </si>
   <si>
-    <t>2012-04-25</t>
-  </si>
-  <si>
     <t>CHTI1011</t>
   </si>
   <si>
@@ -2407,33 +2407,33 @@
     <t>FNAM11</t>
   </si>
   <si>
+    <t>2011-10-11</t>
+  </si>
+  <si>
     <t>2011-04-11</t>
   </si>
   <si>
-    <t>2011-10-11</t>
-  </si>
-  <si>
     <t>FNIC1112</t>
   </si>
   <si>
+    <t>2012-04-26</t>
+  </si>
+  <si>
     <t>2011-10-27</t>
   </si>
   <si>
-    <t>2012-04-26</t>
-  </si>
-  <si>
     <t>CNER11</t>
   </si>
   <si>
     <t>FPAK1112</t>
   </si>
   <si>
+    <t>2012-06-30</t>
+  </si>
+  <si>
     <t>2011-09-15</t>
   </si>
   <si>
-    <t>2012-06-30</t>
-  </si>
-  <si>
     <t>FXLBYREG11</t>
   </si>
   <si>
@@ -2476,24 +2476,24 @@
     <t>CAFG10</t>
   </si>
   <si>
+    <t>2010-12-31</t>
+  </si>
+  <si>
+    <t>2010</t>
+  </si>
+  <si>
     <t>2010-01-01</t>
   </si>
   <si>
-    <t>2010</t>
-  </si>
-  <si>
-    <t>2010-12-31</t>
-  </si>
-  <si>
     <t>OBFA1011</t>
   </si>
   <si>
+    <t>2011-01-31</t>
+  </si>
+  <si>
     <t>2010-08-01</t>
   </si>
   <si>
-    <t>2011-01-31</t>
-  </si>
-  <si>
     <t>CCAF10</t>
   </si>
   <si>
@@ -2506,30 +2506,30 @@
     <t>FSLV0910</t>
   </si>
   <si>
+    <t>2010-05-31</t>
+  </si>
+  <si>
     <t>2009-11-01</t>
   </si>
   <si>
-    <t>2010-05-31</t>
-  </si>
-  <si>
     <t>FGTM10</t>
   </si>
   <si>
+    <t>2010-12-09</t>
+  </si>
+  <si>
     <t>2010-06-10</t>
   </si>
   <si>
-    <t>2010-12-09</t>
-  </si>
-  <si>
     <t>CGTM10</t>
   </si>
   <si>
+    <t>2010-08-11</t>
+  </si>
+  <si>
     <t>2010-02-12</t>
   </si>
   <si>
-    <t>2010-08-11</t>
-  </si>
-  <si>
     <t>FHTI10</t>
   </si>
   <si>
@@ -2545,12 +2545,12 @@
     <t>FKGZ1011</t>
   </si>
   <si>
+    <t>2011-06-30</t>
+  </si>
+  <si>
     <t>2010-06-01</t>
   </si>
   <si>
-    <t>2011-06-30</t>
-  </si>
-  <si>
     <t>CMNG1011</t>
   </si>
   <si>
@@ -2608,24 +2608,24 @@
     <t>CAFG09</t>
   </si>
   <si>
+    <t>2009-12-31</t>
+  </si>
+  <si>
+    <t>2009</t>
+  </si>
+  <si>
     <t>2009-01-01</t>
   </si>
   <si>
-    <t>2009</t>
-  </si>
-  <si>
-    <t>2009-12-31</t>
-  </si>
-  <si>
     <t>FBFA0910</t>
   </si>
   <si>
+    <t>2010-03-09</t>
+  </si>
+  <si>
     <t>2009-09-10</t>
   </si>
   <si>
-    <t>2010-03-09</t>
-  </si>
-  <si>
     <t>CCAF09</t>
   </si>
   <si>
@@ -2662,21 +2662,21 @@
     <t>FMDG09</t>
   </si>
   <si>
+    <t>2009-10-31</t>
+  </si>
+  <si>
     <t>2009-04-01</t>
   </si>
   <si>
-    <t>2009-10-31</t>
-  </si>
-  <si>
     <t>FNAM09</t>
   </si>
   <si>
+    <t>2009-09-30</t>
+  </si>
+  <si>
     <t>2009-03-20</t>
   </si>
   <si>
-    <t>2009-09-30</t>
-  </si>
-  <si>
     <t>ONPL09</t>
   </si>
   <si>
@@ -2689,12 +2689,12 @@
     <t>FPHL0910</t>
   </si>
   <si>
+    <t>2010-03-31</t>
+  </si>
+  <si>
     <t>2009-10-03</t>
   </si>
   <si>
-    <t>2010-03-31</t>
-  </si>
-  <si>
     <t>CSOM09</t>
   </si>
   <si>
@@ -2707,12 +2707,12 @@
     <t>OSYR0910</t>
   </si>
   <si>
+    <t>2010-06-14</t>
+  </si>
+  <si>
     <t>2009-07-15</t>
   </si>
   <si>
-    <t>2010-06-14</t>
-  </si>
-  <si>
     <t>OTJK09</t>
   </si>
   <si>
@@ -2746,24 +2746,24 @@
     <t>OAFG08</t>
   </si>
   <si>
+    <t>2008-06-30</t>
+  </si>
+  <si>
+    <t>2008</t>
+  </si>
+  <si>
     <t>2008-02-01</t>
   </si>
   <si>
-    <t>2008</t>
-  </si>
-  <si>
-    <t>2008-06-30</t>
-  </si>
-  <si>
     <t>OAFG0809</t>
   </si>
   <si>
+    <t>2009-06-30</t>
+  </si>
+  <si>
     <t>2008-07-01</t>
   </si>
   <si>
-    <t>2009-06-30</t>
-  </si>
-  <si>
     <t>FBOL08</t>
   </si>
   <si>
@@ -2773,12 +2773,12 @@
     <t>CCAF08</t>
   </si>
   <si>
+    <t>2008-12-31</t>
+  </si>
+  <si>
     <t>2008-01-01</t>
   </si>
   <si>
-    <t>2008-12-31</t>
-  </si>
-  <si>
     <t>CTCD08</t>
   </si>
   <si>
@@ -2794,21 +2794,21 @@
     <t>ODJI0809</t>
   </si>
   <si>
+    <t>2009-02-28</t>
+  </si>
+  <si>
     <t>2008-08-01</t>
   </si>
   <si>
-    <t>2009-02-28</t>
-  </si>
-  <si>
     <t>FGEO0809</t>
   </si>
   <si>
+    <t>2009-02-09</t>
+  </si>
+  <si>
     <t>2008-08-09</t>
   </si>
   <si>
-    <t>2009-02-09</t>
-  </si>
-  <si>
     <t>FHTI0809</t>
   </si>
   <si>
@@ -2818,12 +2818,12 @@
     <t>FHND0809</t>
   </si>
   <si>
+    <t>2009-04-30</t>
+  </si>
+  <si>
     <t>2008-11-01</t>
   </si>
   <si>
-    <t>2009-04-30</t>
-  </si>
-  <si>
     <t>CIRQ08</t>
   </si>
   <si>
@@ -2833,12 +2833,12 @@
     <t>FKGZ0809</t>
   </si>
   <si>
+    <t>2009-05-31</t>
+  </si>
+  <si>
     <t>2008-12-01</t>
   </si>
   <si>
-    <t>2009-05-31</t>
-  </si>
-  <si>
     <t>OLAO0809</t>
   </si>
   <si>
@@ -2857,12 +2857,12 @@
     <t>FMMR08</t>
   </si>
   <si>
+    <t>2008-11-30</t>
+  </si>
+  <si>
     <t>2008-05-01</t>
   </si>
   <si>
-    <t>2008-11-30</t>
-  </si>
-  <si>
     <t>ONPL08</t>
   </si>
   <si>
@@ -2914,33 +2914,33 @@
     <t>FBOL07</t>
   </si>
   <si>
+    <t>2007-08-21</t>
+  </si>
+  <si>
+    <t>2007</t>
+  </si>
+  <si>
     <t>2007-02-22</t>
   </si>
   <si>
-    <t>2007</t>
-  </si>
-  <si>
-    <t>2007-08-21</t>
-  </si>
-  <si>
     <t>FBFA0708</t>
   </si>
   <si>
+    <t>2008-01-31</t>
+  </si>
+  <si>
     <t>2007-11-01</t>
   </si>
   <si>
-    <t>2008-01-31</t>
-  </si>
-  <si>
     <t>CBDI07</t>
   </si>
   <si>
+    <t>2007-12-31</t>
+  </si>
+  <si>
     <t>2007-01-01</t>
   </si>
   <si>
-    <t>2007-12-31</t>
-  </si>
-  <si>
     <t>CCAF07</t>
   </si>
   <si>
@@ -2962,12 +2962,12 @@
     <t>FGHA0708</t>
   </si>
   <si>
+    <t>2008-03-31</t>
+  </si>
+  <si>
     <t>2007-09-01</t>
   </si>
   <si>
-    <t>2008-03-31</t>
-  </si>
-  <si>
     <t>CXGLR07</t>
   </si>
   <si>
@@ -2980,75 +2980,75 @@
     <t>FPRK07</t>
   </si>
   <si>
+    <t>2007-11-30</t>
+  </si>
+  <si>
     <t>2007-08-28</t>
   </si>
   <si>
-    <t>2007-11-30</t>
-  </si>
-  <si>
     <t>OLBN07</t>
   </si>
   <si>
+    <t>2007-09-03</t>
+  </si>
+  <si>
     <t>2007-06-04</t>
   </si>
   <si>
-    <t>2007-09-03</t>
-  </si>
-  <si>
     <t>FLSO0708</t>
   </si>
   <si>
+    <t>2008-01-28</t>
+  </si>
+  <si>
     <t>2007-07-28</t>
   </si>
   <si>
-    <t>2008-01-28</t>
-  </si>
-  <si>
     <t>CLBR07</t>
   </si>
   <si>
     <t>FMDG07</t>
   </si>
   <si>
+    <t>2007-09-15</t>
+  </si>
+  <si>
     <t>2007-03-15</t>
   </si>
   <si>
-    <t>2007-09-15</t>
-  </si>
-  <si>
     <t>FMOZ07</t>
   </si>
   <si>
+    <t>2007-06-30</t>
+  </si>
+  <si>
     <t>2007-03-01</t>
   </si>
   <si>
-    <t>2007-06-30</t>
-  </si>
-  <si>
     <t>ONPL07</t>
   </si>
   <si>
     <t>FNIC0708</t>
   </si>
   <si>
+    <t>2008-02-28</t>
+  </si>
+  <si>
     <t>2007-09-07</t>
   </si>
   <si>
-    <t>2008-02-28</t>
-  </si>
-  <si>
     <t>ORUS07</t>
   </si>
   <si>
     <t>FPAK07</t>
   </si>
   <si>
+    <t>2007-10-31</t>
+  </si>
+  <si>
     <t>2007-07-15</t>
   </si>
   <si>
-    <t>2007-10-31</t>
-  </si>
-  <si>
     <t>FPER0708</t>
   </si>
   <si>
@@ -3082,12 +3082,12 @@
     <t>FSWZ0708</t>
   </si>
   <si>
+    <t>2008-01-20</t>
+  </si>
+  <si>
     <t>2007-07-20</t>
   </si>
   <si>
-    <t>2008-01-20</t>
-  </si>
-  <si>
     <t>CTLS07</t>
   </si>
   <si>
@@ -3112,15 +3112,15 @@
     <t>OAFG06</t>
   </si>
   <si>
+    <t>2006-12-31</t>
+  </si>
+  <si>
+    <t>2006</t>
+  </si>
+  <si>
     <t>2006-07-01</t>
   </si>
   <si>
-    <t>2006</t>
-  </si>
-  <si>
-    <t>2006-12-31</t>
-  </si>
-  <si>
     <t>CBDI06</t>
   </si>
   <si>
@@ -3145,21 +3145,21 @@
     <t>OETH06a</t>
   </si>
   <si>
+    <t>2006-11-25</t>
+  </si>
+  <si>
     <t>2006-08-25</t>
   </si>
   <si>
-    <t>2006-11-25</t>
-  </si>
-  <si>
     <t>OETH0607</t>
   </si>
   <si>
+    <t>2007-01-22</t>
+  </si>
+  <si>
     <t>2006-11-23</t>
   </si>
   <si>
-    <t>2007-01-22</t>
-  </si>
-  <si>
     <t>CXGLR06</t>
   </si>
   <si>
@@ -3169,12 +3169,12 @@
     <t>FGNB06</t>
   </si>
   <si>
+    <t>2006-11-30</t>
+  </si>
+  <si>
     <t>2006-05-01</t>
   </si>
   <si>
-    <t>2006-11-30</t>
-  </si>
-  <si>
     <t>CXHAF06</t>
   </si>
   <si>
@@ -3184,12 +3184,12 @@
     <t>FKEN0607</t>
   </si>
   <si>
+    <t>2007-04-15</t>
+  </si>
+  <si>
     <t>2006-10-16</t>
   </si>
   <si>
-    <t>2007-04-15</t>
-  </si>
-  <si>
     <t>FKEN06</t>
   </si>
   <si>
@@ -3199,12 +3199,12 @@
     <t>FLBN06</t>
   </si>
   <si>
+    <t>2006-10-23</t>
+  </si>
+  <si>
     <t>2006-07-24</t>
   </si>
   <si>
-    <t>2006-10-23</t>
-  </si>
-  <si>
     <t>CLBR06</t>
   </si>
   <si>
@@ -3232,12 +3232,12 @@
     <t>FSOM0607</t>
   </si>
   <si>
+    <t>2007-03-05</t>
+  </si>
+  <si>
     <t>2006-12-05</t>
   </si>
   <si>
-    <t>2007-03-05</t>
-  </si>
-  <si>
     <t>OLKA06</t>
   </si>
   <si>
@@ -3271,33 +3271,33 @@
     <t>FAGO05</t>
   </si>
   <si>
+    <t>2005-06-30</t>
+  </si>
+  <si>
+    <t>2005</t>
+  </si>
+  <si>
     <t>2005-04-01</t>
   </si>
   <si>
-    <t>2005</t>
-  </si>
-  <si>
-    <t>2005-06-30</t>
-  </si>
-  <si>
     <t>FBEN05</t>
   </si>
   <si>
+    <t>2005-10-31</t>
+  </si>
+  <si>
     <t>2005-05-01</t>
   </si>
   <si>
-    <t>2005-10-31</t>
-  </si>
-  <si>
     <t>CBDI05</t>
   </si>
   <si>
+    <t>2005-12-31</t>
+  </si>
+  <si>
     <t>2005-01-01</t>
   </si>
   <si>
-    <t>2005-12-31</t>
-  </si>
-  <si>
     <t>CCAF05</t>
   </si>
   <si>
@@ -3337,12 +3337,12 @@
     <t>FGUY05</t>
   </si>
   <si>
+    <t>2005-08-01</t>
+  </si>
+  <si>
     <t>2005-02-01</t>
   </si>
   <si>
-    <t>2005-08-01</t>
-  </si>
-  <si>
     <t>FXINDTSU05</t>
   </si>
   <si>
@@ -3355,12 +3355,12 @@
     <t>FNER05</t>
   </si>
   <si>
+    <t>2005-09-30</t>
+  </si>
+  <si>
     <t>2005-06-01</t>
   </si>
   <si>
-    <t>2005-09-30</t>
-  </si>
-  <si>
     <t>CCOG05</t>
   </si>
   <si>
@@ -3370,12 +3370,12 @@
     <t>FXSASIA0506</t>
   </si>
   <si>
+    <t>2006-04-10</t>
+  </si>
+  <si>
     <t>2005-10-11</t>
   </si>
   <si>
-    <t>2006-04-10</t>
-  </si>
-  <si>
     <t>CSDN05</t>
   </si>
   <si>
@@ -3388,27 +3388,27 @@
     <t>FXWAF0506</t>
   </si>
   <si>
+    <t>2006-05-31</t>
+  </si>
+  <si>
     <t>2005-11-01</t>
   </si>
   <si>
-    <t>2006-05-31</t>
-  </si>
-  <si>
     <t>CPSE05</t>
   </si>
   <si>
     <t>OAFG04</t>
   </si>
   <si>
+    <t>2004-12-31</t>
+  </si>
+  <si>
+    <t>2004</t>
+  </si>
+  <si>
     <t>2004-09-01</t>
   </si>
   <si>
-    <t>2004</t>
-  </si>
-  <si>
-    <t>2004-12-31</t>
-  </si>
-  <si>
     <t>CAGO04</t>
   </si>
   <si>
@@ -3418,21 +3418,21 @@
     <t>FBGD0405</t>
   </si>
   <si>
+    <t>2005-01-31</t>
+  </si>
+  <si>
     <t>2004-08-01</t>
   </si>
   <si>
-    <t>2005-01-31</t>
-  </si>
-  <si>
     <t>FBOL0405</t>
   </si>
   <si>
+    <t>2005-05-31</t>
+  </si>
+  <si>
     <t>2004-11-01</t>
   </si>
   <si>
-    <t>2005-05-31</t>
-  </si>
-  <si>
     <t>CBDI04</t>
   </si>
   <si>
@@ -3505,21 +3505,21 @@
     <t>FMDG04</t>
   </si>
   <si>
+    <t>2004-06-19</t>
+  </si>
+  <si>
     <t>2004-03-19</t>
   </si>
   <si>
-    <t>2004-06-19</t>
-  </si>
-  <si>
     <t>FPHL0405</t>
   </si>
   <si>
+    <t>2005-03-15</t>
+  </si>
+  <si>
     <t>2004-12-15</t>
   </si>
   <si>
-    <t>2005-03-15</t>
-  </si>
-  <si>
     <t>CSLE04</t>
   </si>
   <si>
@@ -3550,15 +3550,15 @@
     <t>OAFG03</t>
   </si>
   <si>
+    <t>2003-12-31</t>
+  </si>
+  <si>
+    <t>2003</t>
+  </si>
+  <si>
     <t>2003-01-01</t>
   </si>
   <si>
-    <t>2003</t>
-  </si>
-  <si>
-    <t>2003-12-31</t>
-  </si>
-  <si>
     <t>CAGO03</t>
   </si>
   <si>
@@ -3568,12 +3568,12 @@
     <t>FCAF03</t>
   </si>
   <si>
+    <t>2003-06-30</t>
+  </si>
+  <si>
     <t>2003-04-01</t>
   </si>
   <si>
-    <t>2003-06-30</t>
-  </si>
-  <si>
     <t>CRUS03</t>
   </si>
   <si>
@@ -3586,12 +3586,12 @@
     <t>FCIV0203</t>
   </si>
   <si>
+    <t>2003-01-31</t>
+  </si>
+  <si>
     <t>2002-11-01</t>
   </si>
   <si>
-    <t>2003-01-31</t>
-  </si>
-  <si>
     <t>CPRK03</t>
   </si>
   <si>
@@ -3610,21 +3610,21 @@
     <t>OHTI03</t>
   </si>
   <si>
+    <t>2003-08-31</t>
+  </si>
+  <si>
     <t>2003-03-01</t>
   </si>
   <si>
-    <t>2003-08-31</t>
-  </si>
-  <si>
     <t>CLSO0304</t>
   </si>
   <si>
+    <t>2004-06-30</t>
+  </si>
+  <si>
     <t>2003-07-01</t>
   </si>
   <si>
-    <t>2004-06-30</t>
-  </si>
-  <si>
     <t>CMWI03</t>
   </si>
   <si>
@@ -3676,15 +3676,15 @@
     <t>CAFG0102</t>
   </si>
   <si>
+    <t>2002-12-31</t>
+  </si>
+  <si>
+    <t>2002</t>
+  </si>
+  <si>
     <t>2001-10-01</t>
   </si>
   <si>
-    <t>2002</t>
-  </si>
-  <si>
-    <t>2002-12-31</t>
-  </si>
-  <si>
     <t>CAGO02</t>
   </si>
   <si>
@@ -3778,15 +3778,15 @@
     <t>CAFG01</t>
   </si>
   <si>
+    <t>2001-09-30</t>
+  </si>
+  <si>
+    <t>2001</t>
+  </si>
+  <si>
     <t>2001-01-01</t>
   </si>
   <si>
-    <t>2001</t>
-  </si>
-  <si>
-    <t>2001-09-30</t>
-  </si>
-  <si>
     <t>CAGO01</t>
   </si>
   <si>
@@ -3859,15 +3859,15 @@
     <t>CAGO00</t>
   </si>
   <si>
+    <t>2000-12-31</t>
+  </si>
+  <si>
+    <t>2000</t>
+  </si>
+  <si>
     <t>2000-01-01</t>
   </si>
   <si>
-    <t>2000</t>
-  </si>
-  <si>
-    <t>2000-12-31</t>
-  </si>
-  <si>
     <t>CBDI00</t>
   </si>
   <si>
@@ -3913,10 +3913,10 @@
     <t>CTLS9900</t>
   </si>
   <si>
+    <t>1999</t>
+  </si>
+  <si>
     <t>1999-10-01</t>
-  </si>
-  <si>
-    <t>1999</t>
   </si>
   <si>
     <t>CRUS9900</t>
@@ -4331,13 +4331,13 @@
         <v>15</v>
       </c>
       <c r="D4" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E4" t="s">
         <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -4531,13 +4531,13 @@
         <v>24</v>
       </c>
       <c r="D14" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E14" t="s">
         <v>10</v>
       </c>
       <c r="F14" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -4551,13 +4551,13 @@
         <v>24</v>
       </c>
       <c r="D15" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="E15" t="s">
         <v>10</v>
       </c>
       <c r="F15" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -4591,13 +4591,13 @@
         <v>24</v>
       </c>
       <c r="D17" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="E17" t="s">
         <v>10</v>
       </c>
       <c r="F17" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -4631,13 +4631,13 @@
         <v>24</v>
       </c>
       <c r="D19" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="E19" t="s">
         <v>10</v>
       </c>
       <c r="F19" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -4651,13 +4651,13 @@
         <v>8</v>
       </c>
       <c r="D20" t="s">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="E20" t="s">
         <v>10</v>
       </c>
       <c r="F20" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -4731,13 +4731,13 @@
         <v>15</v>
       </c>
       <c r="D24" t="s">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="E24" t="s">
         <v>10</v>
       </c>
       <c r="F24" t="s">
-        <v>43</v>
+        <v>11</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -4931,13 +4931,13 @@
         <v>24</v>
       </c>
       <c r="D34" t="s">
-        <v>54</v>
+        <v>9</v>
       </c>
       <c r="E34" t="s">
         <v>10</v>
       </c>
       <c r="F34" t="s">
-        <v>11</v>
+        <v>54</v>
       </c>
     </row>
     <row r="35" spans="1:6">
@@ -5091,13 +5091,13 @@
         <v>15</v>
       </c>
       <c r="D42" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="E42" t="s">
         <v>10</v>
       </c>
       <c r="F42" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
     </row>
     <row r="43" spans="1:6">
@@ -5131,13 +5131,13 @@
         <v>24</v>
       </c>
       <c r="D44" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="E44" t="s">
         <v>10</v>
       </c>
       <c r="F44" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
     </row>
     <row r="45" spans="1:6">
@@ -5151,13 +5151,13 @@
         <v>24</v>
       </c>
       <c r="D45" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="E45" t="s">
         <v>10</v>
       </c>
       <c r="F45" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
     </row>
     <row r="46" spans="1:6">
@@ -5211,13 +5211,13 @@
         <v>15</v>
       </c>
       <c r="D48" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="E48" t="s">
         <v>68</v>
       </c>
       <c r="F48" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="49" spans="1:6">
@@ -5251,13 +5251,13 @@
         <v>15</v>
       </c>
       <c r="D50" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="E50" t="s">
         <v>68</v>
       </c>
       <c r="F50" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
     </row>
     <row r="51" spans="1:6">
@@ -5391,13 +5391,13 @@
         <v>24</v>
       </c>
       <c r="D57" t="s">
-        <v>83</v>
+        <v>67</v>
       </c>
       <c r="E57" t="s">
         <v>68</v>
       </c>
       <c r="F57" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
     </row>
     <row r="58" spans="1:6">
@@ -5471,13 +5471,13 @@
         <v>15</v>
       </c>
       <c r="D61" t="s">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="E61" t="s">
         <v>68</v>
       </c>
       <c r="F61" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
     </row>
     <row r="62" spans="1:6">
@@ -5491,13 +5491,13 @@
         <v>24</v>
       </c>
       <c r="D62" t="s">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="E62" t="s">
         <v>68</v>
       </c>
       <c r="F62" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
     </row>
     <row r="63" spans="1:6">
@@ -5511,13 +5511,13 @@
         <v>24</v>
       </c>
       <c r="D63" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="E63" t="s">
         <v>68</v>
       </c>
       <c r="F63" t="s">
-        <v>91</v>
+        <v>69</v>
       </c>
     </row>
     <row r="64" spans="1:6">
@@ -5531,13 +5531,13 @@
         <v>24</v>
       </c>
       <c r="D64" t="s">
-        <v>67</v>
+        <v>93</v>
       </c>
       <c r="E64" t="s">
         <v>68</v>
       </c>
       <c r="F64" t="s">
-        <v>93</v>
+        <v>69</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -5551,13 +5551,13 @@
         <v>24</v>
       </c>
       <c r="D65" t="s">
-        <v>95</v>
+        <v>67</v>
       </c>
       <c r="E65" t="s">
         <v>68</v>
       </c>
       <c r="F65" t="s">
-        <v>69</v>
+        <v>95</v>
       </c>
     </row>
     <row r="66" spans="1:6">
@@ -5591,13 +5591,13 @@
         <v>15</v>
       </c>
       <c r="D67" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="E67" t="s">
         <v>68</v>
       </c>
       <c r="F67" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -5611,13 +5611,13 @@
         <v>24</v>
       </c>
       <c r="D68" t="s">
-        <v>100</v>
+        <v>67</v>
       </c>
       <c r="E68" t="s">
         <v>68</v>
       </c>
       <c r="F68" t="s">
-        <v>69</v>
+        <v>100</v>
       </c>
     </row>
     <row r="69" spans="1:6">
@@ -5671,13 +5671,13 @@
         <v>15</v>
       </c>
       <c r="D71" t="s">
-        <v>104</v>
+        <v>67</v>
       </c>
       <c r="E71" t="s">
         <v>68</v>
       </c>
       <c r="F71" t="s">
-        <v>69</v>
+        <v>104</v>
       </c>
     </row>
     <row r="72" spans="1:6">
@@ -5731,13 +5731,13 @@
         <v>15</v>
       </c>
       <c r="D74" t="s">
-        <v>108</v>
+        <v>67</v>
       </c>
       <c r="E74" t="s">
         <v>68</v>
       </c>
       <c r="F74" t="s">
-        <v>69</v>
+        <v>108</v>
       </c>
     </row>
     <row r="75" spans="1:6">
@@ -5851,13 +5851,13 @@
         <v>24</v>
       </c>
       <c r="D80" t="s">
-        <v>83</v>
+        <v>67</v>
       </c>
       <c r="E80" t="s">
         <v>68</v>
       </c>
       <c r="F80" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
     </row>
     <row r="81" spans="1:6">
@@ -6111,13 +6111,13 @@
         <v>15</v>
       </c>
       <c r="D93" t="s">
-        <v>129</v>
+        <v>67</v>
       </c>
       <c r="E93" t="s">
         <v>68</v>
       </c>
       <c r="F93" t="s">
-        <v>69</v>
+        <v>129</v>
       </c>
     </row>
     <row r="94" spans="1:6">
@@ -6151,13 +6151,13 @@
         <v>24</v>
       </c>
       <c r="D95" t="s">
-        <v>132</v>
+        <v>67</v>
       </c>
       <c r="E95" t="s">
         <v>68</v>
       </c>
       <c r="F95" t="s">
-        <v>69</v>
+        <v>132</v>
       </c>
     </row>
     <row r="96" spans="1:6">
@@ -6171,13 +6171,13 @@
         <v>24</v>
       </c>
       <c r="D96" t="s">
-        <v>132</v>
+        <v>67</v>
       </c>
       <c r="E96" t="s">
         <v>68</v>
       </c>
       <c r="F96" t="s">
-        <v>69</v>
+        <v>132</v>
       </c>
     </row>
     <row r="97" spans="1:6">
@@ -6351,13 +6351,13 @@
         <v>24</v>
       </c>
       <c r="D105" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="E105" t="s">
         <v>136</v>
       </c>
       <c r="F105" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
     </row>
     <row r="106" spans="1:6">
@@ -6511,13 +6511,13 @@
         <v>24</v>
       </c>
       <c r="D113" t="s">
-        <v>155</v>
+        <v>135</v>
       </c>
       <c r="E113" t="s">
         <v>136</v>
       </c>
       <c r="F113" t="s">
-        <v>137</v>
+        <v>155</v>
       </c>
     </row>
     <row r="114" spans="1:6">
@@ -6691,13 +6691,13 @@
         <v>19</v>
       </c>
       <c r="D122" t="s">
-        <v>135</v>
+        <v>162</v>
       </c>
       <c r="E122" t="s">
         <v>136</v>
       </c>
       <c r="F122" t="s">
-        <v>163</v>
+        <v>137</v>
       </c>
     </row>
     <row r="123" spans="1:6">
@@ -6711,13 +6711,13 @@
         <v>15</v>
       </c>
       <c r="D123" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="E123" t="s">
         <v>136</v>
       </c>
       <c r="F123" t="s">
-        <v>160</v>
+        <v>137</v>
       </c>
     </row>
     <row r="124" spans="1:6">
@@ -6931,13 +6931,13 @@
         <v>24</v>
       </c>
       <c r="D134" t="s">
-        <v>183</v>
+        <v>159</v>
       </c>
       <c r="E134" t="s">
         <v>136</v>
       </c>
       <c r="F134" t="s">
-        <v>160</v>
+        <v>183</v>
       </c>
     </row>
     <row r="135" spans="1:6">
@@ -6971,13 +6971,13 @@
         <v>24</v>
       </c>
       <c r="D136" t="s">
-        <v>186</v>
+        <v>159</v>
       </c>
       <c r="E136" t="s">
         <v>136</v>
       </c>
       <c r="F136" t="s">
-        <v>160</v>
+        <v>186</v>
       </c>
     </row>
     <row r="137" spans="1:6">
@@ -7391,13 +7391,13 @@
         <v>24</v>
       </c>
       <c r="D157" t="s">
-        <v>212</v>
+        <v>195</v>
       </c>
       <c r="E157" t="s">
         <v>196</v>
       </c>
       <c r="F157" t="s">
-        <v>197</v>
+        <v>213</v>
       </c>
     </row>
     <row r="158" spans="1:6">
@@ -7471,13 +7471,13 @@
         <v>24</v>
       </c>
       <c r="D161" t="s">
-        <v>195</v>
+        <v>219</v>
       </c>
       <c r="E161" t="s">
         <v>196</v>
       </c>
       <c r="F161" t="s">
-        <v>219</v>
+        <v>197</v>
       </c>
     </row>
     <row r="162" spans="1:6">
@@ -7711,13 +7711,13 @@
         <v>15</v>
       </c>
       <c r="D173" t="s">
-        <v>236</v>
+        <v>195</v>
       </c>
       <c r="E173" t="s">
         <v>196</v>
       </c>
       <c r="F173" t="s">
-        <v>197</v>
+        <v>236</v>
       </c>
     </row>
     <row r="174" spans="1:6">
@@ -7731,13 +7731,13 @@
         <v>15</v>
       </c>
       <c r="D174" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="E174" t="s">
         <v>196</v>
       </c>
       <c r="F174" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="175" spans="1:6">
@@ -7911,13 +7911,13 @@
         <v>15</v>
       </c>
       <c r="D183" t="s">
-        <v>250</v>
+        <v>195</v>
       </c>
       <c r="E183" t="s">
         <v>196</v>
       </c>
       <c r="F183" t="s">
-        <v>197</v>
+        <v>250</v>
       </c>
     </row>
     <row r="184" spans="1:6">
@@ -8011,13 +8011,13 @@
         <v>24</v>
       </c>
       <c r="D188" t="s">
-        <v>256</v>
+        <v>195</v>
       </c>
       <c r="E188" t="s">
         <v>196</v>
       </c>
       <c r="F188" t="s">
-        <v>197</v>
+        <v>256</v>
       </c>
     </row>
     <row r="189" spans="1:6">
@@ -8051,13 +8051,13 @@
         <v>13</v>
       </c>
       <c r="D190" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="E190" t="s">
         <v>196</v>
       </c>
       <c r="F190" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
     </row>
     <row r="191" spans="1:6">
@@ -8131,13 +8131,13 @@
         <v>19</v>
       </c>
       <c r="D194" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="E194" t="s">
         <v>264</v>
       </c>
       <c r="F194" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="195" spans="1:6">
@@ -8151,13 +8151,13 @@
         <v>13</v>
       </c>
       <c r="D195" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="E195" t="s">
         <v>264</v>
       </c>
       <c r="F195" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="196" spans="1:6">
@@ -8171,13 +8171,13 @@
         <v>19</v>
       </c>
       <c r="D196" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="E196" t="s">
         <v>264</v>
       </c>
       <c r="F196" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="197" spans="1:6">
@@ -8191,13 +8191,13 @@
         <v>19</v>
       </c>
       <c r="D197" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="E197" t="s">
         <v>264</v>
       </c>
       <c r="F197" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="198" spans="1:6">
@@ -8211,13 +8211,13 @@
         <v>13</v>
       </c>
       <c r="D198" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="E198" t="s">
         <v>264</v>
       </c>
       <c r="F198" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="199" spans="1:6">
@@ -8231,13 +8231,13 @@
         <v>19</v>
       </c>
       <c r="D199" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="E199" t="s">
         <v>264</v>
       </c>
       <c r="F199" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="200" spans="1:6">
@@ -8251,13 +8251,13 @@
         <v>19</v>
       </c>
       <c r="D200" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="E200" t="s">
         <v>264</v>
       </c>
       <c r="F200" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="201" spans="1:6">
@@ -8271,13 +8271,13 @@
         <v>19</v>
       </c>
       <c r="D201" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="E201" t="s">
         <v>264</v>
       </c>
       <c r="F201" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="202" spans="1:6">
@@ -8291,13 +8291,13 @@
         <v>19</v>
       </c>
       <c r="D202" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="E202" t="s">
         <v>264</v>
       </c>
       <c r="F202" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="203" spans="1:6">
@@ -8311,13 +8311,13 @@
         <v>19</v>
       </c>
       <c r="D203" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="E203" t="s">
         <v>264</v>
       </c>
       <c r="F203" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="204" spans="1:6">
@@ -8331,13 +8331,13 @@
         <v>13</v>
       </c>
       <c r="D204" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="E204" t="s">
         <v>264</v>
       </c>
       <c r="F204" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="205" spans="1:6">
@@ -8351,13 +8351,13 @@
         <v>19</v>
       </c>
       <c r="D205" t="s">
-        <v>279</v>
+        <v>263</v>
       </c>
       <c r="E205" t="s">
         <v>264</v>
       </c>
       <c r="F205" t="s">
-        <v>265</v>
+        <v>279</v>
       </c>
     </row>
     <row r="206" spans="1:6">
@@ -8371,13 +8371,13 @@
         <v>19</v>
       </c>
       <c r="D206" t="s">
-        <v>279</v>
+        <v>195</v>
       </c>
       <c r="E206" t="s">
         <v>264</v>
       </c>
       <c r="F206" t="s">
-        <v>197</v>
+        <v>279</v>
       </c>
     </row>
     <row r="207" spans="1:6">
@@ -8411,13 +8411,13 @@
         <v>19</v>
       </c>
       <c r="D208" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="E208" t="s">
         <v>264</v>
       </c>
       <c r="F208" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="209" spans="1:6">
@@ -8431,13 +8431,13 @@
         <v>19</v>
       </c>
       <c r="D209" t="s">
-        <v>279</v>
+        <v>263</v>
       </c>
       <c r="E209" t="s">
         <v>264</v>
       </c>
       <c r="F209" t="s">
-        <v>265</v>
+        <v>279</v>
       </c>
     </row>
     <row r="210" spans="1:6">
@@ -8451,13 +8451,13 @@
         <v>19</v>
       </c>
       <c r="D210" t="s">
-        <v>279</v>
+        <v>195</v>
       </c>
       <c r="E210" t="s">
         <v>264</v>
       </c>
       <c r="F210" t="s">
-        <v>197</v>
+        <v>279</v>
       </c>
     </row>
     <row r="211" spans="1:6">
@@ -8491,13 +8491,13 @@
         <v>19</v>
       </c>
       <c r="D212" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="E212" t="s">
         <v>264</v>
       </c>
       <c r="F212" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="213" spans="1:6">
@@ -8531,13 +8531,13 @@
         <v>19</v>
       </c>
       <c r="D214" t="s">
-        <v>279</v>
+        <v>263</v>
       </c>
       <c r="E214" t="s">
         <v>264</v>
       </c>
       <c r="F214" t="s">
-        <v>265</v>
+        <v>279</v>
       </c>
     </row>
     <row r="215" spans="1:6">
@@ -8551,13 +8551,13 @@
         <v>19</v>
       </c>
       <c r="D215" t="s">
-        <v>279</v>
+        <v>195</v>
       </c>
       <c r="E215" t="s">
         <v>264</v>
       </c>
       <c r="F215" t="s">
-        <v>197</v>
+        <v>279</v>
       </c>
     </row>
     <row r="216" spans="1:6">
@@ -8571,13 +8571,13 @@
         <v>19</v>
       </c>
       <c r="D216" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="E216" t="s">
         <v>264</v>
       </c>
       <c r="F216" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="217" spans="1:6">
@@ -8591,13 +8591,13 @@
         <v>24</v>
       </c>
       <c r="D217" t="s">
-        <v>298</v>
+        <v>263</v>
       </c>
       <c r="E217" t="s">
         <v>264</v>
       </c>
       <c r="F217" t="s">
-        <v>265</v>
+        <v>298</v>
       </c>
     </row>
     <row r="218" spans="1:6">
@@ -8631,13 +8631,13 @@
         <v>19</v>
       </c>
       <c r="D219" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="E219" t="s">
         <v>264</v>
       </c>
       <c r="F219" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="220" spans="1:6">
@@ -8651,13 +8651,13 @@
         <v>24</v>
       </c>
       <c r="D220" t="s">
-        <v>267</v>
+        <v>224</v>
       </c>
       <c r="E220" t="s">
         <v>264</v>
       </c>
       <c r="F220" t="s">
-        <v>225</v>
+        <v>267</v>
       </c>
     </row>
     <row r="221" spans="1:6">
@@ -8671,13 +8671,13 @@
         <v>24</v>
       </c>
       <c r="D221" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="E221" t="s">
         <v>264</v>
       </c>
       <c r="F221" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="222" spans="1:6">
@@ -8691,13 +8691,13 @@
         <v>19</v>
       </c>
       <c r="D222" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="E222" t="s">
         <v>264</v>
       </c>
       <c r="F222" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="223" spans="1:6">
@@ -8711,13 +8711,13 @@
         <v>19</v>
       </c>
       <c r="D223" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="E223" t="s">
         <v>264</v>
       </c>
       <c r="F223" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="224" spans="1:6">
@@ -8731,13 +8731,13 @@
         <v>19</v>
       </c>
       <c r="D224" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="E224" t="s">
         <v>264</v>
       </c>
       <c r="F224" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="225" spans="1:6">
@@ -8751,13 +8751,13 @@
         <v>15</v>
       </c>
       <c r="D225" t="s">
-        <v>309</v>
+        <v>263</v>
       </c>
       <c r="E225" t="s">
         <v>264</v>
       </c>
       <c r="F225" t="s">
-        <v>265</v>
+        <v>309</v>
       </c>
     </row>
     <row r="226" spans="1:6">
@@ -8771,13 +8771,13 @@
         <v>15</v>
       </c>
       <c r="D226" t="s">
-        <v>311</v>
+        <v>263</v>
       </c>
       <c r="E226" t="s">
         <v>264</v>
       </c>
       <c r="F226" t="s">
-        <v>265</v>
+        <v>311</v>
       </c>
     </row>
     <row r="227" spans="1:6">
@@ -8791,13 +8791,13 @@
         <v>19</v>
       </c>
       <c r="D227" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="E227" t="s">
         <v>264</v>
       </c>
       <c r="F227" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="228" spans="1:6">
@@ -8811,13 +8811,13 @@
         <v>19</v>
       </c>
       <c r="D228" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="E228" t="s">
         <v>264</v>
       </c>
       <c r="F228" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="229" spans="1:6">
@@ -8831,13 +8831,13 @@
         <v>24</v>
       </c>
       <c r="D229" t="s">
-        <v>311</v>
+        <v>263</v>
       </c>
       <c r="E229" t="s">
         <v>264</v>
       </c>
       <c r="F229" t="s">
-        <v>265</v>
+        <v>311</v>
       </c>
     </row>
     <row r="230" spans="1:6">
@@ -8851,13 +8851,13 @@
         <v>15</v>
       </c>
       <c r="D230" t="s">
-        <v>311</v>
+        <v>263</v>
       </c>
       <c r="E230" t="s">
         <v>264</v>
       </c>
       <c r="F230" t="s">
-        <v>265</v>
+        <v>311</v>
       </c>
     </row>
     <row r="231" spans="1:6">
@@ -8871,13 +8871,13 @@
         <v>19</v>
       </c>
       <c r="D231" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="E231" t="s">
         <v>264</v>
       </c>
       <c r="F231" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="232" spans="1:6">
@@ -8891,13 +8891,13 @@
         <v>19</v>
       </c>
       <c r="D232" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="E232" t="s">
         <v>264</v>
       </c>
       <c r="F232" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="233" spans="1:6">
@@ -8911,13 +8911,13 @@
         <v>13</v>
       </c>
       <c r="D233" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="E233" t="s">
         <v>264</v>
       </c>
       <c r="F233" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="234" spans="1:6">
@@ -8931,13 +8931,13 @@
         <v>13</v>
       </c>
       <c r="D234" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="E234" t="s">
         <v>264</v>
       </c>
       <c r="F234" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="235" spans="1:6">
@@ -8951,13 +8951,13 @@
         <v>19</v>
       </c>
       <c r="D235" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="E235" t="s">
         <v>264</v>
       </c>
       <c r="F235" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="236" spans="1:6">
@@ -8971,13 +8971,13 @@
         <v>19</v>
       </c>
       <c r="D236" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="E236" t="s">
         <v>264</v>
       </c>
       <c r="F236" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="237" spans="1:6">
@@ -8991,13 +8991,13 @@
         <v>13</v>
       </c>
       <c r="D237" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="E237" t="s">
         <v>264</v>
       </c>
       <c r="F237" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="238" spans="1:6">
@@ -9011,13 +9011,13 @@
         <v>19</v>
       </c>
       <c r="D238" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="E238" t="s">
         <v>264</v>
       </c>
       <c r="F238" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="239" spans="1:6">
@@ -9031,13 +9031,13 @@
         <v>19</v>
       </c>
       <c r="D239" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="E239" t="s">
         <v>264</v>
       </c>
       <c r="F239" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="240" spans="1:6">
@@ -9051,13 +9051,13 @@
         <v>13</v>
       </c>
       <c r="D240" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="E240" t="s">
         <v>264</v>
       </c>
       <c r="F240" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="241" spans="1:6">
@@ -9071,13 +9071,13 @@
         <v>19</v>
       </c>
       <c r="D241" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="E241" t="s">
         <v>264</v>
       </c>
       <c r="F241" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="242" spans="1:6">
@@ -9091,13 +9091,13 @@
         <v>19</v>
       </c>
       <c r="D242" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="E242" t="s">
         <v>264</v>
       </c>
       <c r="F242" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="243" spans="1:6">
@@ -9111,13 +9111,13 @@
         <v>19</v>
       </c>
       <c r="D243" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="E243" t="s">
         <v>264</v>
       </c>
       <c r="F243" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="244" spans="1:6">
@@ -9131,13 +9131,13 @@
         <v>19</v>
       </c>
       <c r="D244" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="E244" t="s">
         <v>264</v>
       </c>
       <c r="F244" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="245" spans="1:6">
@@ -9171,13 +9171,13 @@
         <v>15</v>
       </c>
       <c r="D246" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="E246" t="s">
         <v>332</v>
       </c>
       <c r="F246" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="247" spans="1:6">
@@ -9211,13 +9211,13 @@
         <v>15</v>
       </c>
       <c r="D248" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="E248" t="s">
         <v>332</v>
       </c>
       <c r="F248" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="249" spans="1:6">
@@ -9291,13 +9291,13 @@
         <v>15</v>
       </c>
       <c r="D252" t="s">
-        <v>342</v>
+        <v>331</v>
       </c>
       <c r="E252" t="s">
         <v>332</v>
       </c>
       <c r="F252" t="s">
-        <v>333</v>
+        <v>342</v>
       </c>
     </row>
     <row r="253" spans="1:6">
@@ -9331,13 +9331,13 @@
         <v>19</v>
       </c>
       <c r="D254" t="s">
-        <v>345</v>
+        <v>267</v>
       </c>
       <c r="E254" t="s">
         <v>332</v>
       </c>
       <c r="F254" t="s">
-        <v>267</v>
+        <v>345</v>
       </c>
     </row>
     <row r="255" spans="1:6">
@@ -9391,13 +9391,13 @@
         <v>15</v>
       </c>
       <c r="D257" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="E257" t="s">
         <v>332</v>
       </c>
       <c r="F257" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="258" spans="1:6">
@@ -9411,13 +9411,13 @@
         <v>15</v>
       </c>
       <c r="D258" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="E258" t="s">
         <v>332</v>
       </c>
       <c r="F258" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="259" spans="1:6">
@@ -9431,13 +9431,13 @@
         <v>19</v>
       </c>
       <c r="D259" t="s">
-        <v>351</v>
+        <v>331</v>
       </c>
       <c r="E259" t="s">
         <v>332</v>
       </c>
       <c r="F259" t="s">
-        <v>333</v>
+        <v>351</v>
       </c>
     </row>
     <row r="260" spans="1:6">
@@ -9511,13 +9511,13 @@
         <v>15</v>
       </c>
       <c r="D263" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="E263" t="s">
         <v>332</v>
       </c>
       <c r="F263" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="264" spans="1:6">
@@ -9531,13 +9531,13 @@
         <v>15</v>
       </c>
       <c r="D264" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="E264" t="s">
         <v>332</v>
       </c>
       <c r="F264" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="265" spans="1:6">
@@ -9571,13 +9571,13 @@
         <v>15</v>
       </c>
       <c r="D266" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="E266" t="s">
         <v>332</v>
       </c>
       <c r="F266" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="267" spans="1:6">
@@ -9611,13 +9611,13 @@
         <v>15</v>
       </c>
       <c r="D268" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="E268" t="s">
         <v>332</v>
       </c>
       <c r="F268" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="269" spans="1:6">
@@ -9631,13 +9631,13 @@
         <v>15</v>
       </c>
       <c r="D269" t="s">
-        <v>351</v>
+        <v>331</v>
       </c>
       <c r="E269" t="s">
         <v>332</v>
       </c>
       <c r="F269" t="s">
-        <v>333</v>
+        <v>351</v>
       </c>
     </row>
     <row r="270" spans="1:6">
@@ -9651,13 +9651,13 @@
         <v>15</v>
       </c>
       <c r="D270" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="E270" t="s">
         <v>332</v>
       </c>
       <c r="F270" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="271" spans="1:6">
@@ -9671,13 +9671,13 @@
         <v>15</v>
       </c>
       <c r="D271" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="E271" t="s">
         <v>332</v>
       </c>
       <c r="F271" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="272" spans="1:6">
@@ -9711,13 +9711,13 @@
         <v>15</v>
       </c>
       <c r="D273" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="E273" t="s">
         <v>332</v>
       </c>
       <c r="F273" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="274" spans="1:6">
@@ -9751,13 +9751,13 @@
         <v>15</v>
       </c>
       <c r="D275" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="E275" t="s">
         <v>332</v>
       </c>
       <c r="F275" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="276" spans="1:6">
@@ -9771,13 +9771,13 @@
         <v>15</v>
       </c>
       <c r="D276" t="s">
-        <v>371</v>
+        <v>331</v>
       </c>
       <c r="E276" t="s">
         <v>332</v>
       </c>
       <c r="F276" t="s">
-        <v>333</v>
+        <v>371</v>
       </c>
     </row>
     <row r="277" spans="1:6">
@@ -9811,13 +9811,13 @@
         <v>15</v>
       </c>
       <c r="D278" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="E278" t="s">
         <v>332</v>
       </c>
       <c r="F278" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="279" spans="1:6">
@@ -9851,13 +9851,13 @@
         <v>15</v>
       </c>
       <c r="D280" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="E280" t="s">
         <v>332</v>
       </c>
       <c r="F280" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="281" spans="1:6">
@@ -9911,13 +9911,13 @@
         <v>15</v>
       </c>
       <c r="D283" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="E283" t="s">
         <v>332</v>
       </c>
       <c r="F283" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="284" spans="1:6">
@@ -10011,13 +10011,13 @@
         <v>15</v>
       </c>
       <c r="D288" t="s">
-        <v>371</v>
+        <v>331</v>
       </c>
       <c r="E288" t="s">
         <v>332</v>
       </c>
       <c r="F288" t="s">
-        <v>333</v>
+        <v>371</v>
       </c>
     </row>
     <row r="289" spans="1:6">
@@ -10031,13 +10031,13 @@
         <v>15</v>
       </c>
       <c r="D289" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="E289" t="s">
         <v>332</v>
       </c>
       <c r="F289" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="290" spans="1:6">
@@ -10091,13 +10091,13 @@
         <v>15</v>
       </c>
       <c r="D292" t="s">
-        <v>371</v>
+        <v>331</v>
       </c>
       <c r="E292" t="s">
         <v>332</v>
       </c>
       <c r="F292" t="s">
-        <v>333</v>
+        <v>371</v>
       </c>
     </row>
     <row r="293" spans="1:6">
@@ -10111,13 +10111,13 @@
         <v>15</v>
       </c>
       <c r="D293" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="E293" t="s">
         <v>332</v>
       </c>
       <c r="F293" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="294" spans="1:6">
@@ -10251,13 +10251,13 @@
         <v>15</v>
       </c>
       <c r="D300" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="E300" t="s">
         <v>332</v>
       </c>
       <c r="F300" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="301" spans="1:6">
@@ -10271,13 +10271,13 @@
         <v>15</v>
       </c>
       <c r="D301" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="E301" t="s">
         <v>332</v>
       </c>
       <c r="F301" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="302" spans="1:6">
@@ -10291,13 +10291,13 @@
         <v>15</v>
       </c>
       <c r="D302" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="E302" t="s">
         <v>332</v>
       </c>
       <c r="F302" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="303" spans="1:6">
@@ -10331,13 +10331,13 @@
         <v>15</v>
       </c>
       <c r="D304" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="E304" t="s">
         <v>332</v>
       </c>
       <c r="F304" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="305" spans="1:6">
@@ -10391,13 +10391,13 @@
         <v>15</v>
       </c>
       <c r="D307" t="s">
-        <v>407</v>
+        <v>355</v>
       </c>
       <c r="E307" t="s">
         <v>332</v>
       </c>
       <c r="F307" t="s">
-        <v>356</v>
+        <v>407</v>
       </c>
     </row>
     <row r="308" spans="1:6">
@@ -10411,13 +10411,13 @@
         <v>15</v>
       </c>
       <c r="D308" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="E308" t="s">
         <v>332</v>
       </c>
       <c r="F308" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="309" spans="1:6">
@@ -10711,13 +10711,13 @@
         <v>15</v>
       </c>
       <c r="D323" t="s">
-        <v>427</v>
+        <v>411</v>
       </c>
       <c r="E323" t="s">
         <v>412</v>
       </c>
       <c r="F323" t="s">
-        <v>413</v>
+        <v>427</v>
       </c>
     </row>
     <row r="324" spans="1:6">
@@ -10751,13 +10751,13 @@
         <v>24</v>
       </c>
       <c r="D325" t="s">
-        <v>411</v>
+        <v>430</v>
       </c>
       <c r="E325" t="s">
         <v>412</v>
       </c>
       <c r="F325" t="s">
-        <v>430</v>
+        <v>413</v>
       </c>
     </row>
     <row r="326" spans="1:6">
@@ -10871,13 +10871,13 @@
         <v>19</v>
       </c>
       <c r="D331" t="s">
-        <v>411</v>
+        <v>437</v>
       </c>
       <c r="E331" t="s">
         <v>412</v>
       </c>
       <c r="F331" t="s">
-        <v>437</v>
+        <v>413</v>
       </c>
     </row>
     <row r="332" spans="1:6">
@@ -11131,13 +11131,13 @@
         <v>24</v>
       </c>
       <c r="D344" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="E344" t="s">
         <v>412</v>
       </c>
       <c r="F344" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="345" spans="1:6">
@@ -11171,13 +11171,13 @@
         <v>15</v>
       </c>
       <c r="D346" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="E346" t="s">
         <v>456</v>
       </c>
       <c r="F346" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="347" spans="1:6">
@@ -11371,13 +11371,13 @@
         <v>15</v>
       </c>
       <c r="D356" t="s">
-        <v>470</v>
+        <v>455</v>
       </c>
       <c r="E356" t="s">
         <v>456</v>
       </c>
       <c r="F356" t="s">
-        <v>457</v>
+        <v>470</v>
       </c>
     </row>
     <row r="357" spans="1:6">
@@ -11571,13 +11571,13 @@
         <v>15</v>
       </c>
       <c r="D366" t="s">
-        <v>481</v>
+        <v>455</v>
       </c>
       <c r="E366" t="s">
         <v>456</v>
       </c>
       <c r="F366" t="s">
-        <v>457</v>
+        <v>481</v>
       </c>
     </row>
     <row r="367" spans="1:6">
@@ -11591,13 +11591,13 @@
         <v>13</v>
       </c>
       <c r="D367" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="E367" t="s">
         <v>456</v>
       </c>
       <c r="F367" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="368" spans="1:6">
@@ -11671,13 +11671,13 @@
         <v>19</v>
       </c>
       <c r="D371" t="s">
-        <v>455</v>
+        <v>487</v>
       </c>
       <c r="E371" t="s">
         <v>456</v>
       </c>
       <c r="F371" t="s">
-        <v>487</v>
+        <v>457</v>
       </c>
     </row>
     <row r="372" spans="1:6">
@@ -11851,13 +11851,13 @@
         <v>13</v>
       </c>
       <c r="D380" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
       <c r="E380" t="s">
         <v>498</v>
       </c>
       <c r="F380" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
     <row r="381" spans="1:6">
@@ -11971,13 +11971,13 @@
         <v>15</v>
       </c>
       <c r="D386" t="s">
-        <v>509</v>
+        <v>497</v>
       </c>
       <c r="E386" t="s">
         <v>498</v>
       </c>
       <c r="F386" t="s">
-        <v>499</v>
+        <v>509</v>
       </c>
     </row>
     <row r="387" spans="1:6">
@@ -11991,13 +11991,13 @@
         <v>19</v>
       </c>
       <c r="D387" t="s">
-        <v>511</v>
+        <v>497</v>
       </c>
       <c r="E387" t="s">
         <v>498</v>
       </c>
       <c r="F387" t="s">
-        <v>499</v>
+        <v>511</v>
       </c>
     </row>
     <row r="388" spans="1:6">
@@ -12111,13 +12111,13 @@
         <v>15</v>
       </c>
       <c r="D393" t="s">
-        <v>520</v>
+        <v>497</v>
       </c>
       <c r="E393" t="s">
         <v>498</v>
       </c>
       <c r="F393" t="s">
-        <v>499</v>
+        <v>520</v>
       </c>
     </row>
     <row r="394" spans="1:6">
@@ -12391,13 +12391,13 @@
         <v>19</v>
       </c>
       <c r="D407" t="s">
-        <v>543</v>
+        <v>497</v>
       </c>
       <c r="E407" t="s">
         <v>498</v>
       </c>
       <c r="F407" t="s">
-        <v>499</v>
+        <v>543</v>
       </c>
     </row>
     <row r="408" spans="1:6">
@@ -12631,13 +12631,13 @@
         <v>24</v>
       </c>
       <c r="D419" t="s">
-        <v>559</v>
+        <v>554</v>
       </c>
       <c r="E419" t="s">
         <v>555</v>
       </c>
       <c r="F419" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
     </row>
     <row r="420" spans="1:6">
@@ -12671,13 +12671,13 @@
         <v>19</v>
       </c>
       <c r="D421" t="s">
-        <v>562</v>
+        <v>554</v>
       </c>
       <c r="E421" t="s">
         <v>555</v>
       </c>
       <c r="F421" t="s">
-        <v>556</v>
+        <v>562</v>
       </c>
     </row>
     <row r="422" spans="1:6">
@@ -12911,13 +12911,13 @@
         <v>24</v>
       </c>
       <c r="D433" t="s">
-        <v>579</v>
+        <v>554</v>
       </c>
       <c r="E433" t="s">
         <v>555</v>
       </c>
       <c r="F433" t="s">
-        <v>556</v>
+        <v>579</v>
       </c>
     </row>
     <row r="434" spans="1:6">
@@ -12971,13 +12971,13 @@
         <v>24</v>
       </c>
       <c r="D436" t="s">
-        <v>583</v>
+        <v>554</v>
       </c>
       <c r="E436" t="s">
         <v>555</v>
       </c>
       <c r="F436" t="s">
-        <v>556</v>
+        <v>583</v>
       </c>
     </row>
     <row r="437" spans="1:6">
@@ -12991,13 +12991,13 @@
         <v>19</v>
       </c>
       <c r="D437" t="s">
-        <v>585</v>
+        <v>554</v>
       </c>
       <c r="E437" t="s">
         <v>555</v>
       </c>
       <c r="F437" t="s">
-        <v>556</v>
+        <v>585</v>
       </c>
     </row>
     <row r="438" spans="1:6">
@@ -13551,13 +13551,13 @@
         <v>24</v>
       </c>
       <c r="D465" t="s">
-        <v>624</v>
+        <v>609</v>
       </c>
       <c r="E465" t="s">
         <v>610</v>
       </c>
       <c r="F465" t="s">
-        <v>611</v>
+        <v>624</v>
       </c>
     </row>
     <row r="466" spans="1:6">
@@ -13571,13 +13571,13 @@
         <v>24</v>
       </c>
       <c r="D466" t="s">
-        <v>626</v>
+        <v>621</v>
       </c>
       <c r="E466" t="s">
         <v>610</v>
       </c>
       <c r="F466" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
     </row>
     <row r="467" spans="1:6">
@@ -13711,13 +13711,13 @@
         <v>24</v>
       </c>
       <c r="D473" t="s">
-        <v>638</v>
+        <v>621</v>
       </c>
       <c r="E473" t="s">
         <v>610</v>
       </c>
       <c r="F473" t="s">
-        <v>622</v>
+        <v>638</v>
       </c>
     </row>
     <row r="474" spans="1:6">
@@ -14011,13 +14011,13 @@
         <v>608</v>
       </c>
       <c r="D488" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="E488" t="s">
         <v>654</v>
       </c>
       <c r="F488" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
     </row>
     <row r="489" spans="1:6">
@@ -14091,13 +14091,13 @@
         <v>19</v>
       </c>
       <c r="D492" t="s">
-        <v>653</v>
+        <v>662</v>
       </c>
       <c r="E492" t="s">
         <v>654</v>
       </c>
       <c r="F492" t="s">
-        <v>662</v>
+        <v>655</v>
       </c>
     </row>
     <row r="493" spans="1:6">
@@ -14131,13 +14131,13 @@
         <v>13</v>
       </c>
       <c r="D494" t="s">
-        <v>632</v>
+        <v>665</v>
       </c>
       <c r="E494" t="s">
         <v>654</v>
       </c>
       <c r="F494" t="s">
-        <v>665</v>
+        <v>633</v>
       </c>
     </row>
     <row r="495" spans="1:6">
@@ -14151,13 +14151,13 @@
         <v>15</v>
       </c>
       <c r="D495" t="s">
-        <v>632</v>
+        <v>665</v>
       </c>
       <c r="E495" t="s">
         <v>654</v>
       </c>
       <c r="F495" t="s">
-        <v>665</v>
+        <v>633</v>
       </c>
     </row>
     <row r="496" spans="1:6">
@@ -14211,13 +14211,13 @@
         <v>608</v>
       </c>
       <c r="D498" t="s">
-        <v>670</v>
+        <v>653</v>
       </c>
       <c r="E498" t="s">
         <v>654</v>
       </c>
       <c r="F498" t="s">
-        <v>655</v>
+        <v>670</v>
       </c>
     </row>
     <row r="499" spans="1:6">
@@ -14291,13 +14291,13 @@
         <v>19</v>
       </c>
       <c r="D502" t="s">
-        <v>675</v>
+        <v>653</v>
       </c>
       <c r="E502" t="s">
         <v>654</v>
       </c>
       <c r="F502" t="s">
-        <v>655</v>
+        <v>675</v>
       </c>
     </row>
     <row r="503" spans="1:6">
@@ -14431,13 +14431,13 @@
         <v>19</v>
       </c>
       <c r="D509" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="E509" t="s">
         <v>654</v>
       </c>
       <c r="F509" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
     </row>
     <row r="510" spans="1:6">
@@ -14491,13 +14491,13 @@
         <v>15</v>
       </c>
       <c r="D512" t="s">
-        <v>693</v>
+        <v>653</v>
       </c>
       <c r="E512" t="s">
         <v>654</v>
       </c>
       <c r="F512" t="s">
-        <v>655</v>
+        <v>693</v>
       </c>
     </row>
     <row r="513" spans="1:6">
@@ -14511,13 +14511,13 @@
         <v>19</v>
       </c>
       <c r="D513" t="s">
-        <v>653</v>
+        <v>695</v>
       </c>
       <c r="E513" t="s">
         <v>654</v>
       </c>
       <c r="F513" t="s">
-        <v>695</v>
+        <v>655</v>
       </c>
     </row>
     <row r="514" spans="1:6">
@@ -14671,13 +14671,13 @@
         <v>19</v>
       </c>
       <c r="D521" t="s">
-        <v>704</v>
+        <v>653</v>
       </c>
       <c r="E521" t="s">
         <v>654</v>
       </c>
       <c r="F521" t="s">
-        <v>655</v>
+        <v>704</v>
       </c>
     </row>
     <row r="522" spans="1:6">
@@ -14691,13 +14691,13 @@
         <v>13</v>
       </c>
       <c r="D522" t="s">
-        <v>706</v>
+        <v>653</v>
       </c>
       <c r="E522" t="s">
         <v>654</v>
       </c>
       <c r="F522" t="s">
-        <v>655</v>
+        <v>706</v>
       </c>
     </row>
     <row r="523" spans="1:6">
@@ -14711,13 +14711,13 @@
         <v>24</v>
       </c>
       <c r="D523" t="s">
-        <v>708</v>
+        <v>653</v>
       </c>
       <c r="E523" t="s">
         <v>654</v>
       </c>
       <c r="F523" t="s">
-        <v>655</v>
+        <v>708</v>
       </c>
     </row>
     <row r="524" spans="1:6">
@@ -14751,13 +14751,13 @@
         <v>711</v>
       </c>
       <c r="D525" t="s">
+        <v>712</v>
+      </c>
+      <c r="E525" t="s">
+        <v>713</v>
+      </c>
+      <c r="F525" t="s">
         <v>657</v>
-      </c>
-      <c r="E525" t="s">
-        <v>712</v>
-      </c>
-      <c r="F525" t="s">
-        <v>713</v>
       </c>
     </row>
     <row r="526" spans="1:6">
@@ -14771,13 +14771,13 @@
         <v>711</v>
       </c>
       <c r="D526" t="s">
+        <v>712</v>
+      </c>
+      <c r="E526" t="s">
+        <v>713</v>
+      </c>
+      <c r="F526" t="s">
         <v>657</v>
-      </c>
-      <c r="E526" t="s">
-        <v>712</v>
-      </c>
-      <c r="F526" t="s">
-        <v>713</v>
       </c>
     </row>
     <row r="527" spans="1:6">
@@ -14791,13 +14791,13 @@
         <v>711</v>
       </c>
       <c r="D527" t="s">
+        <v>712</v>
+      </c>
+      <c r="E527" t="s">
+        <v>713</v>
+      </c>
+      <c r="F527" t="s">
         <v>657</v>
-      </c>
-      <c r="E527" t="s">
-        <v>712</v>
-      </c>
-      <c r="F527" t="s">
-        <v>713</v>
       </c>
     </row>
     <row r="528" spans="1:6">
@@ -14811,13 +14811,13 @@
         <v>711</v>
       </c>
       <c r="D528" t="s">
+        <v>712</v>
+      </c>
+      <c r="E528" t="s">
+        <v>713</v>
+      </c>
+      <c r="F528" t="s">
         <v>657</v>
-      </c>
-      <c r="E528" t="s">
-        <v>712</v>
-      </c>
-      <c r="F528" t="s">
-        <v>713</v>
       </c>
     </row>
     <row r="529" spans="1:6">
@@ -14831,13 +14831,13 @@
         <v>15</v>
       </c>
       <c r="D529" t="s">
+        <v>712</v>
+      </c>
+      <c r="E529" t="s">
+        <v>713</v>
+      </c>
+      <c r="F529" t="s">
         <v>718</v>
-      </c>
-      <c r="E529" t="s">
-        <v>712</v>
-      </c>
-      <c r="F529" t="s">
-        <v>713</v>
       </c>
     </row>
     <row r="530" spans="1:6">
@@ -14851,13 +14851,13 @@
         <v>711</v>
       </c>
       <c r="D530" t="s">
+        <v>720</v>
+      </c>
+      <c r="E530" t="s">
+        <v>713</v>
+      </c>
+      <c r="F530" t="s">
         <v>657</v>
-      </c>
-      <c r="E530" t="s">
-        <v>712</v>
-      </c>
-      <c r="F530" t="s">
-        <v>720</v>
       </c>
     </row>
     <row r="531" spans="1:6">
@@ -14871,13 +14871,13 @@
         <v>711</v>
       </c>
       <c r="D531" t="s">
+        <v>712</v>
+      </c>
+      <c r="E531" t="s">
+        <v>713</v>
+      </c>
+      <c r="F531" t="s">
         <v>657</v>
-      </c>
-      <c r="E531" t="s">
-        <v>712</v>
-      </c>
-      <c r="F531" t="s">
-        <v>713</v>
       </c>
     </row>
     <row r="532" spans="1:6">
@@ -14891,13 +14891,13 @@
         <v>711</v>
       </c>
       <c r="D532" t="s">
+        <v>712</v>
+      </c>
+      <c r="E532" t="s">
+        <v>713</v>
+      </c>
+      <c r="F532" t="s">
         <v>657</v>
-      </c>
-      <c r="E532" t="s">
-        <v>712</v>
-      </c>
-      <c r="F532" t="s">
-        <v>713</v>
       </c>
     </row>
     <row r="533" spans="1:6">
@@ -14911,13 +14911,13 @@
         <v>711</v>
       </c>
       <c r="D533" t="s">
+        <v>712</v>
+      </c>
+      <c r="E533" t="s">
+        <v>713</v>
+      </c>
+      <c r="F533" t="s">
         <v>657</v>
-      </c>
-      <c r="E533" t="s">
-        <v>712</v>
-      </c>
-      <c r="F533" t="s">
-        <v>713</v>
       </c>
     </row>
     <row r="534" spans="1:6">
@@ -14931,13 +14931,13 @@
         <v>711</v>
       </c>
       <c r="D534" t="s">
+        <v>712</v>
+      </c>
+      <c r="E534" t="s">
+        <v>713</v>
+      </c>
+      <c r="F534" t="s">
         <v>657</v>
-      </c>
-      <c r="E534" t="s">
-        <v>712</v>
-      </c>
-      <c r="F534" t="s">
-        <v>713</v>
       </c>
     </row>
     <row r="535" spans="1:6">
@@ -14951,13 +14951,13 @@
         <v>711</v>
       </c>
       <c r="D535" t="s">
+        <v>712</v>
+      </c>
+      <c r="E535" t="s">
+        <v>713</v>
+      </c>
+      <c r="F535" t="s">
         <v>657</v>
-      </c>
-      <c r="E535" t="s">
-        <v>712</v>
-      </c>
-      <c r="F535" t="s">
-        <v>713</v>
       </c>
     </row>
     <row r="536" spans="1:6">
@@ -14971,13 +14971,13 @@
         <v>15</v>
       </c>
       <c r="D536" t="s">
+        <v>712</v>
+      </c>
+      <c r="E536" t="s">
+        <v>713</v>
+      </c>
+      <c r="F536" t="s">
         <v>727</v>
-      </c>
-      <c r="E536" t="s">
-        <v>712</v>
-      </c>
-      <c r="F536" t="s">
-        <v>713</v>
       </c>
     </row>
     <row r="537" spans="1:6">
@@ -14991,13 +14991,13 @@
         <v>15</v>
       </c>
       <c r="D537" t="s">
+        <v>712</v>
+      </c>
+      <c r="E537" t="s">
+        <v>713</v>
+      </c>
+      <c r="F537" t="s">
         <v>729</v>
-      </c>
-      <c r="E537" t="s">
-        <v>712</v>
-      </c>
-      <c r="F537" t="s">
-        <v>713</v>
       </c>
     </row>
     <row r="538" spans="1:6">
@@ -15011,13 +15011,13 @@
         <v>711</v>
       </c>
       <c r="D538" t="s">
+        <v>712</v>
+      </c>
+      <c r="E538" t="s">
+        <v>713</v>
+      </c>
+      <c r="F538" t="s">
         <v>657</v>
-      </c>
-      <c r="E538" t="s">
-        <v>712</v>
-      </c>
-      <c r="F538" t="s">
-        <v>713</v>
       </c>
     </row>
     <row r="539" spans="1:6">
@@ -15031,13 +15031,13 @@
         <v>711</v>
       </c>
       <c r="D539" t="s">
+        <v>712</v>
+      </c>
+      <c r="E539" t="s">
+        <v>713</v>
+      </c>
+      <c r="F539" t="s">
         <v>657</v>
-      </c>
-      <c r="E539" t="s">
-        <v>712</v>
-      </c>
-      <c r="F539" t="s">
-        <v>713</v>
       </c>
     </row>
     <row r="540" spans="1:6">
@@ -15051,13 +15051,13 @@
         <v>711</v>
       </c>
       <c r="D540" t="s">
+        <v>689</v>
+      </c>
+      <c r="E540" t="s">
+        <v>713</v>
+      </c>
+      <c r="F540" t="s">
         <v>657</v>
-      </c>
-      <c r="E540" t="s">
-        <v>712</v>
-      </c>
-      <c r="F540" t="s">
-        <v>690</v>
       </c>
     </row>
     <row r="541" spans="1:6">
@@ -15071,13 +15071,13 @@
         <v>711</v>
       </c>
       <c r="D541" t="s">
+        <v>712</v>
+      </c>
+      <c r="E541" t="s">
+        <v>713</v>
+      </c>
+      <c r="F541" t="s">
         <v>657</v>
-      </c>
-      <c r="E541" t="s">
-        <v>712</v>
-      </c>
-      <c r="F541" t="s">
-        <v>713</v>
       </c>
     </row>
     <row r="542" spans="1:6">
@@ -15091,13 +15091,13 @@
         <v>711</v>
       </c>
       <c r="D542" t="s">
+        <v>712</v>
+      </c>
+      <c r="E542" t="s">
+        <v>713</v>
+      </c>
+      <c r="F542" t="s">
         <v>657</v>
-      </c>
-      <c r="E542" t="s">
-        <v>712</v>
-      </c>
-      <c r="F542" t="s">
-        <v>713</v>
       </c>
     </row>
     <row r="543" spans="1:6">
@@ -15111,13 +15111,13 @@
         <v>711</v>
       </c>
       <c r="D543" t="s">
+        <v>712</v>
+      </c>
+      <c r="E543" t="s">
+        <v>713</v>
+      </c>
+      <c r="F543" t="s">
         <v>657</v>
-      </c>
-      <c r="E543" t="s">
-        <v>712</v>
-      </c>
-      <c r="F543" t="s">
-        <v>713</v>
       </c>
     </row>
     <row r="544" spans="1:6">
@@ -15131,13 +15131,13 @@
         <v>711</v>
       </c>
       <c r="D544" t="s">
+        <v>712</v>
+      </c>
+      <c r="E544" t="s">
+        <v>713</v>
+      </c>
+      <c r="F544" t="s">
         <v>657</v>
-      </c>
-      <c r="E544" t="s">
-        <v>712</v>
-      </c>
-      <c r="F544" t="s">
-        <v>713</v>
       </c>
     </row>
     <row r="545" spans="1:6">
@@ -15151,13 +15151,13 @@
         <v>13</v>
       </c>
       <c r="D545" t="s">
+        <v>738</v>
+      </c>
+      <c r="E545" t="s">
+        <v>713</v>
+      </c>
+      <c r="F545" t="s">
         <v>657</v>
-      </c>
-      <c r="E545" t="s">
-        <v>712</v>
-      </c>
-      <c r="F545" t="s">
-        <v>738</v>
       </c>
     </row>
     <row r="546" spans="1:6">
@@ -15171,13 +15171,13 @@
         <v>711</v>
       </c>
       <c r="D546" t="s">
+        <v>712</v>
+      </c>
+      <c r="E546" t="s">
+        <v>713</v>
+      </c>
+      <c r="F546" t="s">
         <v>657</v>
-      </c>
-      <c r="E546" t="s">
-        <v>712</v>
-      </c>
-      <c r="F546" t="s">
-        <v>713</v>
       </c>
     </row>
     <row r="547" spans="1:6">
@@ -15191,13 +15191,13 @@
         <v>15</v>
       </c>
       <c r="D547" t="s">
+        <v>712</v>
+      </c>
+      <c r="E547" t="s">
+        <v>713</v>
+      </c>
+      <c r="F547" t="s">
         <v>657</v>
-      </c>
-      <c r="E547" t="s">
-        <v>712</v>
-      </c>
-      <c r="F547" t="s">
-        <v>713</v>
       </c>
     </row>
     <row r="548" spans="1:6">
@@ -15231,13 +15231,13 @@
         <v>711</v>
       </c>
       <c r="D549" t="s">
-        <v>746</v>
+        <v>742</v>
       </c>
       <c r="E549" t="s">
         <v>743</v>
       </c>
       <c r="F549" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
     </row>
     <row r="550" spans="1:6">
@@ -15251,13 +15251,13 @@
         <v>711</v>
       </c>
       <c r="D550" t="s">
-        <v>748</v>
+        <v>742</v>
       </c>
       <c r="E550" t="s">
         <v>743</v>
       </c>
       <c r="F550" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="551" spans="1:6">
@@ -15331,13 +15331,13 @@
         <v>711</v>
       </c>
       <c r="D554" t="s">
-        <v>742</v>
+        <v>753</v>
       </c>
       <c r="E554" t="s">
         <v>743</v>
       </c>
       <c r="F554" t="s">
-        <v>753</v>
+        <v>744</v>
       </c>
     </row>
     <row r="555" spans="1:6">
@@ -15451,13 +15451,13 @@
         <v>711</v>
       </c>
       <c r="D560" t="s">
-        <v>762</v>
+        <v>742</v>
       </c>
       <c r="E560" t="s">
         <v>743</v>
       </c>
       <c r="F560" t="s">
-        <v>744</v>
+        <v>762</v>
       </c>
     </row>
     <row r="561" spans="1:6">
@@ -15471,13 +15471,13 @@
         <v>711</v>
       </c>
       <c r="D561" t="s">
-        <v>762</v>
+        <v>742</v>
       </c>
       <c r="E561" t="s">
         <v>743</v>
       </c>
       <c r="F561" t="s">
-        <v>744</v>
+        <v>762</v>
       </c>
     </row>
     <row r="562" spans="1:6">
@@ -15511,13 +15511,13 @@
         <v>15</v>
       </c>
       <c r="D563" t="s">
-        <v>742</v>
+        <v>766</v>
       </c>
       <c r="E563" t="s">
         <v>743</v>
       </c>
       <c r="F563" t="s">
-        <v>766</v>
+        <v>744</v>
       </c>
     </row>
     <row r="564" spans="1:6">
@@ -15711,13 +15711,13 @@
         <v>711</v>
       </c>
       <c r="D573" t="s">
+        <v>712</v>
+      </c>
+      <c r="E573" t="s">
         <v>779</v>
       </c>
-      <c r="E573" t="s">
+      <c r="F573" t="s">
         <v>780</v>
-      </c>
-      <c r="F573" t="s">
-        <v>713</v>
       </c>
     </row>
     <row r="574" spans="1:6">
@@ -15731,13 +15731,13 @@
         <v>711</v>
       </c>
       <c r="D574" t="s">
+        <v>782</v>
+      </c>
+      <c r="E574" t="s">
         <v>779</v>
       </c>
-      <c r="E574" t="s">
+      <c r="F574" t="s">
         <v>780</v>
-      </c>
-      <c r="F574" t="s">
-        <v>782</v>
       </c>
     </row>
     <row r="575" spans="1:6">
@@ -15751,13 +15751,13 @@
         <v>711</v>
       </c>
       <c r="D575" t="s">
+        <v>782</v>
+      </c>
+      <c r="E575" t="s">
         <v>779</v>
       </c>
-      <c r="E575" t="s">
+      <c r="F575" t="s">
         <v>780</v>
-      </c>
-      <c r="F575" t="s">
-        <v>782</v>
       </c>
     </row>
     <row r="576" spans="1:6">
@@ -15771,13 +15771,13 @@
         <v>711</v>
       </c>
       <c r="D576" t="s">
+        <v>782</v>
+      </c>
+      <c r="E576" t="s">
         <v>779</v>
       </c>
-      <c r="E576" t="s">
+      <c r="F576" t="s">
         <v>780</v>
-      </c>
-      <c r="F576" t="s">
-        <v>782</v>
       </c>
     </row>
     <row r="577" spans="1:6">
@@ -15791,13 +15791,13 @@
         <v>711</v>
       </c>
       <c r="D577" t="s">
+        <v>742</v>
+      </c>
+      <c r="E577" t="s">
         <v>779</v>
       </c>
-      <c r="E577" t="s">
+      <c r="F577" t="s">
         <v>780</v>
-      </c>
-      <c r="F577" t="s">
-        <v>744</v>
       </c>
     </row>
     <row r="578" spans="1:6">
@@ -15811,13 +15811,13 @@
         <v>711</v>
       </c>
       <c r="D578" t="s">
+        <v>782</v>
+      </c>
+      <c r="E578" t="s">
+        <v>779</v>
+      </c>
+      <c r="F578" t="s">
         <v>787</v>
-      </c>
-      <c r="E578" t="s">
-        <v>780</v>
-      </c>
-      <c r="F578" t="s">
-        <v>782</v>
       </c>
     </row>
     <row r="579" spans="1:6">
@@ -15834,7 +15834,7 @@
         <v>789</v>
       </c>
       <c r="E579" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="F579" t="s">
         <v>790</v>
@@ -15851,13 +15851,13 @@
         <v>711</v>
       </c>
       <c r="D580" t="s">
+        <v>782</v>
+      </c>
+      <c r="E580" t="s">
+        <v>779</v>
+      </c>
+      <c r="F580" t="s">
         <v>792</v>
-      </c>
-      <c r="E580" t="s">
-        <v>780</v>
-      </c>
-      <c r="F580" t="s">
-        <v>782</v>
       </c>
     </row>
     <row r="581" spans="1:6">
@@ -15871,13 +15871,13 @@
         <v>15</v>
       </c>
       <c r="D581" t="s">
+        <v>782</v>
+      </c>
+      <c r="E581" t="s">
+        <v>779</v>
+      </c>
+      <c r="F581" t="s">
         <v>794</v>
-      </c>
-      <c r="E581" t="s">
-        <v>780</v>
-      </c>
-      <c r="F581" t="s">
-        <v>782</v>
       </c>
     </row>
     <row r="582" spans="1:6">
@@ -15891,13 +15891,13 @@
         <v>15</v>
       </c>
       <c r="D582" t="s">
+        <v>782</v>
+      </c>
+      <c r="E582" t="s">
         <v>779</v>
       </c>
-      <c r="E582" t="s">
+      <c r="F582" t="s">
         <v>780</v>
-      </c>
-      <c r="F582" t="s">
-        <v>782</v>
       </c>
     </row>
     <row r="583" spans="1:6">
@@ -15914,7 +15914,7 @@
         <v>797</v>
       </c>
       <c r="E583" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="F583" t="s">
         <v>798</v>
@@ -15934,7 +15934,7 @@
         <v>800</v>
       </c>
       <c r="E584" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="F584" t="s">
         <v>801</v>
@@ -15951,13 +15951,13 @@
         <v>711</v>
       </c>
       <c r="D585" t="s">
+        <v>782</v>
+      </c>
+      <c r="E585" t="s">
         <v>779</v>
       </c>
-      <c r="E585" t="s">
+      <c r="F585" t="s">
         <v>780</v>
-      </c>
-      <c r="F585" t="s">
-        <v>782</v>
       </c>
     </row>
     <row r="586" spans="1:6">
@@ -15974,7 +15974,7 @@
         <v>804</v>
       </c>
       <c r="E586" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="F586" t="s">
         <v>805</v>
@@ -15991,13 +15991,13 @@
         <v>13</v>
       </c>
       <c r="D587" t="s">
+        <v>782</v>
+      </c>
+      <c r="E587" t="s">
+        <v>779</v>
+      </c>
+      <c r="F587" t="s">
         <v>807</v>
-      </c>
-      <c r="E587" t="s">
-        <v>780</v>
-      </c>
-      <c r="F587" t="s">
-        <v>782</v>
       </c>
     </row>
     <row r="588" spans="1:6">
@@ -16011,13 +16011,13 @@
         <v>711</v>
       </c>
       <c r="D588" t="s">
+        <v>782</v>
+      </c>
+      <c r="E588" t="s">
+        <v>779</v>
+      </c>
+      <c r="F588" t="s">
         <v>809</v>
-      </c>
-      <c r="E588" t="s">
-        <v>780</v>
-      </c>
-      <c r="F588" t="s">
-        <v>782</v>
       </c>
     </row>
     <row r="589" spans="1:6">
@@ -16031,13 +16031,13 @@
         <v>711</v>
       </c>
       <c r="D589" t="s">
+        <v>782</v>
+      </c>
+      <c r="E589" t="s">
         <v>779</v>
       </c>
-      <c r="E589" t="s">
+      <c r="F589" t="s">
         <v>780</v>
-      </c>
-      <c r="F589" t="s">
-        <v>782</v>
       </c>
     </row>
     <row r="590" spans="1:6">
@@ -16051,13 +16051,13 @@
         <v>24</v>
       </c>
       <c r="D590" t="s">
+        <v>782</v>
+      </c>
+      <c r="E590" t="s">
         <v>779</v>
       </c>
-      <c r="E590" t="s">
+      <c r="F590" t="s">
         <v>780</v>
-      </c>
-      <c r="F590" t="s">
-        <v>782</v>
       </c>
     </row>
     <row r="591" spans="1:6">
@@ -16071,13 +16071,13 @@
         <v>15</v>
       </c>
       <c r="D591" t="s">
+        <v>782</v>
+      </c>
+      <c r="E591" t="s">
         <v>779</v>
       </c>
-      <c r="E591" t="s">
+      <c r="F591" t="s">
         <v>780</v>
-      </c>
-      <c r="F591" t="s">
-        <v>782</v>
       </c>
     </row>
     <row r="592" spans="1:6">
@@ -16091,13 +16091,13 @@
         <v>711</v>
       </c>
       <c r="D592" t="s">
+        <v>814</v>
+      </c>
+      <c r="E592" t="s">
         <v>779</v>
       </c>
-      <c r="E592" t="s">
+      <c r="F592" t="s">
         <v>780</v>
-      </c>
-      <c r="F592" t="s">
-        <v>814</v>
       </c>
     </row>
     <row r="593" spans="1:6">
@@ -16111,13 +16111,13 @@
         <v>13</v>
       </c>
       <c r="D593" t="s">
+        <v>782</v>
+      </c>
+      <c r="E593" t="s">
         <v>779</v>
       </c>
-      <c r="E593" t="s">
+      <c r="F593" t="s">
         <v>780</v>
-      </c>
-      <c r="F593" t="s">
-        <v>782</v>
       </c>
     </row>
     <row r="594" spans="1:6">
@@ -16131,13 +16131,13 @@
         <v>711</v>
       </c>
       <c r="D594" t="s">
+        <v>782</v>
+      </c>
+      <c r="E594" t="s">
         <v>779</v>
       </c>
-      <c r="E594" t="s">
+      <c r="F594" t="s">
         <v>780</v>
-      </c>
-      <c r="F594" t="s">
-        <v>782</v>
       </c>
     </row>
     <row r="595" spans="1:6">
@@ -16151,13 +16151,13 @@
         <v>711</v>
       </c>
       <c r="D595" t="s">
+        <v>782</v>
+      </c>
+      <c r="E595" t="s">
         <v>779</v>
       </c>
-      <c r="E595" t="s">
+      <c r="F595" t="s">
         <v>780</v>
-      </c>
-      <c r="F595" t="s">
-        <v>782</v>
       </c>
     </row>
     <row r="596" spans="1:6">
@@ -16171,13 +16171,13 @@
         <v>711</v>
       </c>
       <c r="D596" t="s">
+        <v>782</v>
+      </c>
+      <c r="E596" t="s">
         <v>779</v>
       </c>
-      <c r="E596" t="s">
+      <c r="F596" t="s">
         <v>780</v>
-      </c>
-      <c r="F596" t="s">
-        <v>782</v>
       </c>
     </row>
     <row r="597" spans="1:6">
@@ -16351,13 +16351,13 @@
         <v>24</v>
       </c>
       <c r="D605" t="s">
-        <v>839</v>
+        <v>820</v>
       </c>
       <c r="E605" t="s">
         <v>821</v>
       </c>
       <c r="F605" t="s">
-        <v>822</v>
+        <v>839</v>
       </c>
     </row>
     <row r="606" spans="1:6">
@@ -16431,13 +16431,13 @@
         <v>711</v>
       </c>
       <c r="D609" t="s">
-        <v>846</v>
+        <v>807</v>
       </c>
       <c r="E609" t="s">
         <v>821</v>
       </c>
       <c r="F609" t="s">
-        <v>807</v>
+        <v>846</v>
       </c>
     </row>
     <row r="610" spans="1:6">
@@ -16471,13 +16471,13 @@
         <v>24</v>
       </c>
       <c r="D611" t="s">
-        <v>824</v>
+        <v>849</v>
       </c>
       <c r="E611" t="s">
         <v>821</v>
       </c>
       <c r="F611" t="s">
-        <v>849</v>
+        <v>825</v>
       </c>
     </row>
     <row r="612" spans="1:6">
@@ -16491,13 +16491,13 @@
         <v>15</v>
       </c>
       <c r="D612" t="s">
-        <v>851</v>
+        <v>820</v>
       </c>
       <c r="E612" t="s">
         <v>821</v>
       </c>
       <c r="F612" t="s">
-        <v>822</v>
+        <v>851</v>
       </c>
     </row>
     <row r="613" spans="1:6">
@@ -16531,13 +16531,13 @@
         <v>711</v>
       </c>
       <c r="D614" t="s">
-        <v>854</v>
+        <v>820</v>
       </c>
       <c r="E614" t="s">
         <v>821</v>
       </c>
       <c r="F614" t="s">
-        <v>822</v>
+        <v>854</v>
       </c>
     </row>
     <row r="615" spans="1:6">
@@ -16811,13 +16811,13 @@
         <v>711</v>
       </c>
       <c r="D628" t="s">
-        <v>864</v>
+        <v>874</v>
       </c>
       <c r="E628" t="s">
         <v>865</v>
       </c>
       <c r="F628" t="s">
-        <v>874</v>
+        <v>866</v>
       </c>
     </row>
     <row r="629" spans="1:6">
@@ -16831,13 +16831,13 @@
         <v>24</v>
       </c>
       <c r="D629" t="s">
-        <v>876</v>
+        <v>864</v>
       </c>
       <c r="E629" t="s">
         <v>865</v>
       </c>
       <c r="F629" t="s">
-        <v>866</v>
+        <v>876</v>
       </c>
     </row>
     <row r="630" spans="1:6">
@@ -16891,13 +16891,13 @@
         <v>24</v>
       </c>
       <c r="D632" t="s">
-        <v>876</v>
+        <v>880</v>
       </c>
       <c r="E632" t="s">
         <v>865</v>
       </c>
       <c r="F632" t="s">
-        <v>880</v>
+        <v>876</v>
       </c>
     </row>
     <row r="633" spans="1:6">
@@ -16971,13 +16971,13 @@
         <v>711</v>
       </c>
       <c r="D636" t="s">
-        <v>889</v>
+        <v>864</v>
       </c>
       <c r="E636" t="s">
         <v>865</v>
       </c>
       <c r="F636" t="s">
-        <v>866</v>
+        <v>889</v>
       </c>
     </row>
     <row r="637" spans="1:6">
@@ -17091,13 +17091,13 @@
         <v>15</v>
       </c>
       <c r="D642" t="s">
-        <v>900</v>
+        <v>864</v>
       </c>
       <c r="E642" t="s">
         <v>865</v>
       </c>
       <c r="F642" t="s">
-        <v>866</v>
+        <v>900</v>
       </c>
     </row>
     <row r="643" spans="1:6">
@@ -17111,13 +17111,13 @@
         <v>15</v>
       </c>
       <c r="D643" t="s">
-        <v>902</v>
+        <v>864</v>
       </c>
       <c r="E643" t="s">
         <v>865</v>
       </c>
       <c r="F643" t="s">
-        <v>866</v>
+        <v>902</v>
       </c>
     </row>
     <row r="644" spans="1:6">
@@ -17171,13 +17171,13 @@
         <v>24</v>
       </c>
       <c r="D646" t="s">
-        <v>906</v>
+        <v>864</v>
       </c>
       <c r="E646" t="s">
         <v>865</v>
       </c>
       <c r="F646" t="s">
-        <v>866</v>
+        <v>906</v>
       </c>
     </row>
     <row r="647" spans="1:6">
@@ -17271,13 +17271,13 @@
         <v>24</v>
       </c>
       <c r="D651" t="s">
-        <v>910</v>
+        <v>917</v>
       </c>
       <c r="E651" t="s">
         <v>911</v>
       </c>
       <c r="F651" t="s">
-        <v>917</v>
+        <v>912</v>
       </c>
     </row>
     <row r="652" spans="1:6">
@@ -17331,13 +17331,13 @@
         <v>15</v>
       </c>
       <c r="D654" t="s">
-        <v>902</v>
+        <v>864</v>
       </c>
       <c r="E654" t="s">
         <v>911</v>
       </c>
       <c r="F654" t="s">
-        <v>866</v>
+        <v>902</v>
       </c>
     </row>
     <row r="655" spans="1:6">
@@ -17431,13 +17431,13 @@
         <v>24</v>
       </c>
       <c r="D659" t="s">
-        <v>889</v>
+        <v>932</v>
       </c>
       <c r="E659" t="s">
         <v>911</v>
       </c>
       <c r="F659" t="s">
-        <v>932</v>
+        <v>889</v>
       </c>
     </row>
     <row r="660" spans="1:6">
@@ -17491,13 +17491,13 @@
         <v>24</v>
       </c>
       <c r="D662" t="s">
-        <v>919</v>
+        <v>915</v>
       </c>
       <c r="E662" t="s">
         <v>911</v>
       </c>
       <c r="F662" t="s">
-        <v>914</v>
+        <v>920</v>
       </c>
     </row>
     <row r="663" spans="1:6">
@@ -17531,13 +17531,13 @@
         <v>15</v>
       </c>
       <c r="D664" t="s">
-        <v>902</v>
+        <v>942</v>
       </c>
       <c r="E664" t="s">
         <v>911</v>
       </c>
       <c r="F664" t="s">
-        <v>942</v>
+        <v>902</v>
       </c>
     </row>
     <row r="665" spans="1:6">
@@ -17551,13 +17551,13 @@
         <v>711</v>
       </c>
       <c r="D665" t="s">
-        <v>944</v>
+        <v>919</v>
       </c>
       <c r="E665" t="s">
         <v>911</v>
       </c>
       <c r="F665" t="s">
-        <v>920</v>
+        <v>944</v>
       </c>
     </row>
     <row r="666" spans="1:6">
@@ -17571,13 +17571,13 @@
         <v>24</v>
       </c>
       <c r="D666" t="s">
-        <v>944</v>
+        <v>910</v>
       </c>
       <c r="E666" t="s">
         <v>911</v>
       </c>
       <c r="F666" t="s">
-        <v>912</v>
+        <v>944</v>
       </c>
     </row>
     <row r="667" spans="1:6">
@@ -17631,13 +17631,13 @@
         <v>15</v>
       </c>
       <c r="D669" t="s">
-        <v>902</v>
+        <v>932</v>
       </c>
       <c r="E669" t="s">
         <v>911</v>
       </c>
       <c r="F669" t="s">
-        <v>932</v>
+        <v>902</v>
       </c>
     </row>
     <row r="670" spans="1:6">
@@ -17671,13 +17671,13 @@
         <v>24</v>
       </c>
       <c r="D671" t="s">
-        <v>910</v>
+        <v>953</v>
       </c>
       <c r="E671" t="s">
         <v>911</v>
       </c>
       <c r="F671" t="s">
-        <v>953</v>
+        <v>912</v>
       </c>
     </row>
     <row r="672" spans="1:6">
@@ -17731,13 +17731,13 @@
         <v>15</v>
       </c>
       <c r="D674" t="s">
-        <v>902</v>
+        <v>934</v>
       </c>
       <c r="E674" t="s">
         <v>911</v>
       </c>
       <c r="F674" t="s">
-        <v>935</v>
+        <v>902</v>
       </c>
     </row>
     <row r="675" spans="1:6">
@@ -17751,13 +17751,13 @@
         <v>24</v>
       </c>
       <c r="D675" t="s">
-        <v>910</v>
+        <v>917</v>
       </c>
       <c r="E675" t="s">
         <v>911</v>
       </c>
       <c r="F675" t="s">
-        <v>917</v>
+        <v>912</v>
       </c>
     </row>
     <row r="676" spans="1:6">
@@ -17771,13 +17771,13 @@
         <v>15</v>
       </c>
       <c r="D676" t="s">
-        <v>959</v>
+        <v>919</v>
       </c>
       <c r="E676" t="s">
         <v>911</v>
       </c>
       <c r="F676" t="s">
-        <v>920</v>
+        <v>959</v>
       </c>
     </row>
     <row r="677" spans="1:6">
@@ -18031,13 +18031,13 @@
         <v>24</v>
       </c>
       <c r="D689" t="s">
-        <v>970</v>
+        <v>980</v>
       </c>
       <c r="E689" t="s">
         <v>967</v>
       </c>
       <c r="F689" t="s">
-        <v>980</v>
+        <v>971</v>
       </c>
     </row>
     <row r="690" spans="1:6">
@@ -18091,13 +18091,13 @@
         <v>15</v>
       </c>
       <c r="D692" t="s">
-        <v>986</v>
+        <v>919</v>
       </c>
       <c r="E692" t="s">
         <v>967</v>
       </c>
       <c r="F692" t="s">
-        <v>920</v>
+        <v>986</v>
       </c>
     </row>
     <row r="693" spans="1:6">
@@ -18311,13 +18311,13 @@
         <v>24</v>
       </c>
       <c r="D703" t="s">
-        <v>1012</v>
+        <v>1005</v>
       </c>
       <c r="E703" t="s">
         <v>967</v>
       </c>
       <c r="F703" t="s">
-        <v>1006</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="704" spans="1:6">
@@ -18351,13 +18351,13 @@
         <v>15</v>
       </c>
       <c r="D705" t="s">
-        <v>1015</v>
+        <v>1001</v>
       </c>
       <c r="E705" t="s">
         <v>967</v>
       </c>
       <c r="F705" t="s">
-        <v>1002</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="706" spans="1:6">
@@ -18391,13 +18391,13 @@
         <v>15</v>
       </c>
       <c r="D707" t="s">
-        <v>973</v>
+        <v>1001</v>
       </c>
       <c r="E707" t="s">
         <v>967</v>
       </c>
       <c r="F707" t="s">
-        <v>1002</v>
+        <v>974</v>
       </c>
     </row>
     <row r="708" spans="1:6">
@@ -18411,13 +18411,13 @@
         <v>24</v>
       </c>
       <c r="D708" t="s">
-        <v>1019</v>
+        <v>970</v>
       </c>
       <c r="E708" t="s">
         <v>967</v>
       </c>
       <c r="F708" t="s">
-        <v>971</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="709" spans="1:6">
@@ -18471,13 +18471,13 @@
         <v>711</v>
       </c>
       <c r="D711" t="s">
-        <v>973</v>
+        <v>1001</v>
       </c>
       <c r="E711" t="s">
         <v>967</v>
       </c>
       <c r="F711" t="s">
-        <v>1002</v>
+        <v>974</v>
       </c>
     </row>
     <row r="712" spans="1:6">
@@ -18551,13 +18551,13 @@
         <v>24</v>
       </c>
       <c r="D715" t="s">
-        <v>998</v>
+        <v>1001</v>
       </c>
       <c r="E715" t="s">
         <v>967</v>
       </c>
       <c r="F715" t="s">
-        <v>1002</v>
+        <v>999</v>
       </c>
     </row>
     <row r="716" spans="1:6">
@@ -18631,13 +18631,13 @@
         <v>711</v>
       </c>
       <c r="D719" t="s">
-        <v>1036</v>
+        <v>1032</v>
       </c>
       <c r="E719" t="s">
         <v>1033</v>
       </c>
       <c r="F719" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="720" spans="1:6">
@@ -18651,13 +18651,13 @@
         <v>711</v>
       </c>
       <c r="D720" t="s">
-        <v>1036</v>
+        <v>1032</v>
       </c>
       <c r="E720" t="s">
         <v>1033</v>
       </c>
       <c r="F720" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="721" spans="1:6">
@@ -18671,13 +18671,13 @@
         <v>711</v>
       </c>
       <c r="D721" t="s">
-        <v>1036</v>
+        <v>1032</v>
       </c>
       <c r="E721" t="s">
         <v>1033</v>
       </c>
       <c r="F721" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="722" spans="1:6">
@@ -18691,13 +18691,13 @@
         <v>711</v>
       </c>
       <c r="D722" t="s">
-        <v>1036</v>
+        <v>1032</v>
       </c>
       <c r="E722" t="s">
         <v>1033</v>
       </c>
       <c r="F722" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="723" spans="1:6">
@@ -18711,13 +18711,13 @@
         <v>711</v>
       </c>
       <c r="D723" t="s">
-        <v>1036</v>
+        <v>1032</v>
       </c>
       <c r="E723" t="s">
         <v>1033</v>
       </c>
       <c r="F723" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="724" spans="1:6">
@@ -18731,13 +18731,13 @@
         <v>15</v>
       </c>
       <c r="D724" t="s">
-        <v>1036</v>
+        <v>1032</v>
       </c>
       <c r="E724" t="s">
         <v>1033</v>
       </c>
       <c r="F724" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="725" spans="1:6">
@@ -18791,13 +18791,13 @@
         <v>711</v>
       </c>
       <c r="D727" t="s">
-        <v>1036</v>
+        <v>1032</v>
       </c>
       <c r="E727" t="s">
         <v>1033</v>
       </c>
       <c r="F727" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="728" spans="1:6">
@@ -18811,13 +18811,13 @@
         <v>711</v>
       </c>
       <c r="D728" t="s">
-        <v>1036</v>
+        <v>1032</v>
       </c>
       <c r="E728" t="s">
         <v>1033</v>
       </c>
       <c r="F728" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="729" spans="1:6">
@@ -18851,13 +18851,13 @@
         <v>13</v>
       </c>
       <c r="D730" t="s">
-        <v>1036</v>
+        <v>1032</v>
       </c>
       <c r="E730" t="s">
         <v>1033</v>
       </c>
       <c r="F730" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="731" spans="1:6">
@@ -18911,13 +18911,13 @@
         <v>24</v>
       </c>
       <c r="D733" t="s">
-        <v>1059</v>
+        <v>1032</v>
       </c>
       <c r="E733" t="s">
         <v>1033</v>
       </c>
       <c r="F733" t="s">
-        <v>1034</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="734" spans="1:6">
@@ -18951,13 +18951,13 @@
         <v>711</v>
       </c>
       <c r="D735" t="s">
-        <v>1036</v>
+        <v>1032</v>
       </c>
       <c r="E735" t="s">
         <v>1033</v>
       </c>
       <c r="F735" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="736" spans="1:6">
@@ -18971,13 +18971,13 @@
         <v>711</v>
       </c>
       <c r="D736" t="s">
-        <v>1065</v>
+        <v>1032</v>
       </c>
       <c r="E736" t="s">
         <v>1033</v>
       </c>
       <c r="F736" t="s">
-        <v>1034</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="737" spans="1:6">
@@ -18991,13 +18991,13 @@
         <v>15</v>
       </c>
       <c r="D737" t="s">
-        <v>1036</v>
+        <v>1032</v>
       </c>
       <c r="E737" t="s">
         <v>1033</v>
       </c>
       <c r="F737" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="738" spans="1:6">
@@ -19011,13 +19011,13 @@
         <v>15</v>
       </c>
       <c r="D738" t="s">
-        <v>1068</v>
+        <v>973</v>
       </c>
       <c r="E738" t="s">
         <v>1033</v>
       </c>
       <c r="F738" t="s">
-        <v>974</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="739" spans="1:6">
@@ -19031,13 +19031,13 @@
         <v>711</v>
       </c>
       <c r="D739" t="s">
-        <v>1036</v>
+        <v>1032</v>
       </c>
       <c r="E739" t="s">
         <v>1033</v>
       </c>
       <c r="F739" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="740" spans="1:6">
@@ -19051,13 +19051,13 @@
         <v>711</v>
       </c>
       <c r="D740" t="s">
-        <v>1036</v>
+        <v>1032</v>
       </c>
       <c r="E740" t="s">
         <v>1033</v>
       </c>
       <c r="F740" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="741" spans="1:6">
@@ -19091,13 +19091,13 @@
         <v>15</v>
       </c>
       <c r="D742" t="s">
-        <v>1075</v>
+        <v>1032</v>
       </c>
       <c r="E742" t="s">
         <v>1033</v>
       </c>
       <c r="F742" t="s">
-        <v>1034</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="743" spans="1:6">
@@ -19111,13 +19111,13 @@
         <v>711</v>
       </c>
       <c r="D743" t="s">
-        <v>1036</v>
+        <v>1032</v>
       </c>
       <c r="E743" t="s">
         <v>1033</v>
       </c>
       <c r="F743" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="744" spans="1:6">
@@ -19151,13 +19151,13 @@
         <v>24</v>
       </c>
       <c r="D745" t="s">
-        <v>1079</v>
+        <v>1032</v>
       </c>
       <c r="E745" t="s">
         <v>1033</v>
       </c>
       <c r="F745" t="s">
-        <v>1034</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="746" spans="1:6">
@@ -19171,13 +19171,13 @@
         <v>711</v>
       </c>
       <c r="D746" t="s">
-        <v>1036</v>
+        <v>1032</v>
       </c>
       <c r="E746" t="s">
         <v>1033</v>
       </c>
       <c r="F746" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="747" spans="1:6">
@@ -19191,13 +19191,13 @@
         <v>711</v>
       </c>
       <c r="D747" t="s">
-        <v>1036</v>
+        <v>1032</v>
       </c>
       <c r="E747" t="s">
         <v>1033</v>
       </c>
       <c r="F747" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="748" spans="1:6">
@@ -19211,13 +19211,13 @@
         <v>711</v>
       </c>
       <c r="D748" t="s">
-        <v>1036</v>
+        <v>1032</v>
       </c>
       <c r="E748" t="s">
         <v>1033</v>
       </c>
       <c r="F748" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="749" spans="1:6">
@@ -19231,13 +19231,13 @@
         <v>711</v>
       </c>
       <c r="D749" t="s">
-        <v>1036</v>
+        <v>1032</v>
       </c>
       <c r="E749" t="s">
         <v>1033</v>
       </c>
       <c r="F749" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="750" spans="1:6">
@@ -19411,13 +19411,13 @@
         <v>24</v>
       </c>
       <c r="D758" t="s">
-        <v>1085</v>
+        <v>1089</v>
       </c>
       <c r="E758" t="s">
         <v>1086</v>
       </c>
       <c r="F758" t="s">
-        <v>1090</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="759" spans="1:6">
@@ -19431,13 +19431,13 @@
         <v>15</v>
       </c>
       <c r="D759" t="s">
-        <v>1065</v>
+        <v>1092</v>
       </c>
       <c r="E759" t="s">
         <v>1086</v>
       </c>
       <c r="F759" t="s">
-        <v>1093</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="760" spans="1:6">
@@ -19491,13 +19491,13 @@
         <v>24</v>
       </c>
       <c r="D762" t="s">
-        <v>1065</v>
+        <v>1104</v>
       </c>
       <c r="E762" t="s">
         <v>1086</v>
       </c>
       <c r="F762" t="s">
-        <v>1104</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="763" spans="1:6">
@@ -19551,13 +19551,13 @@
         <v>24</v>
       </c>
       <c r="D765" t="s">
-        <v>1092</v>
+        <v>1085</v>
       </c>
       <c r="E765" t="s">
         <v>1086</v>
       </c>
       <c r="F765" t="s">
-        <v>1087</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="766" spans="1:6">
@@ -19571,13 +19571,13 @@
         <v>24</v>
       </c>
       <c r="D766" t="s">
-        <v>1111</v>
+        <v>1104</v>
       </c>
       <c r="E766" t="s">
         <v>1086</v>
       </c>
       <c r="F766" t="s">
-        <v>1104</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="767" spans="1:6">
@@ -19791,13 +19791,13 @@
         <v>711</v>
       </c>
       <c r="D777" t="s">
-        <v>1132</v>
+        <v>1128</v>
       </c>
       <c r="E777" t="s">
         <v>1129</v>
       </c>
       <c r="F777" t="s">
-        <v>1130</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="778" spans="1:6">
@@ -19851,13 +19851,13 @@
         <v>711</v>
       </c>
       <c r="D780" t="s">
-        <v>1132</v>
+        <v>1128</v>
       </c>
       <c r="E780" t="s">
         <v>1129</v>
       </c>
       <c r="F780" t="s">
-        <v>1130</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="781" spans="1:6">
@@ -19871,13 +19871,13 @@
         <v>711</v>
       </c>
       <c r="D781" t="s">
-        <v>1132</v>
+        <v>1128</v>
       </c>
       <c r="E781" t="s">
         <v>1129</v>
       </c>
       <c r="F781" t="s">
-        <v>1130</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="782" spans="1:6">
@@ -19891,13 +19891,13 @@
         <v>711</v>
       </c>
       <c r="D782" t="s">
-        <v>1142</v>
+        <v>1128</v>
       </c>
       <c r="E782" t="s">
         <v>1129</v>
       </c>
       <c r="F782" t="s">
-        <v>1130</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="783" spans="1:6">
@@ -19911,13 +19911,13 @@
         <v>711</v>
       </c>
       <c r="D783" t="s">
-        <v>1132</v>
+        <v>1128</v>
       </c>
       <c r="E783" t="s">
         <v>1129</v>
       </c>
       <c r="F783" t="s">
-        <v>1130</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="784" spans="1:6">
@@ -19931,13 +19931,13 @@
         <v>711</v>
       </c>
       <c r="D784" t="s">
-        <v>1132</v>
+        <v>1128</v>
       </c>
       <c r="E784" t="s">
         <v>1129</v>
       </c>
       <c r="F784" t="s">
-        <v>1130</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="785" spans="1:6">
@@ -19951,13 +19951,13 @@
         <v>711</v>
       </c>
       <c r="D785" t="s">
-        <v>1132</v>
+        <v>1128</v>
       </c>
       <c r="E785" t="s">
         <v>1129</v>
       </c>
       <c r="F785" t="s">
-        <v>1130</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="786" spans="1:6">
@@ -19971,13 +19971,13 @@
         <v>711</v>
       </c>
       <c r="D786" t="s">
-        <v>1132</v>
+        <v>1128</v>
       </c>
       <c r="E786" t="s">
         <v>1129</v>
       </c>
       <c r="F786" t="s">
-        <v>1130</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="787" spans="1:6">
@@ -19991,13 +19991,13 @@
         <v>711</v>
       </c>
       <c r="D787" t="s">
-        <v>1132</v>
+        <v>1128</v>
       </c>
       <c r="E787" t="s">
         <v>1129</v>
       </c>
       <c r="F787" t="s">
-        <v>1130</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="788" spans="1:6">
@@ -20011,13 +20011,13 @@
         <v>711</v>
       </c>
       <c r="D788" t="s">
-        <v>1132</v>
+        <v>1128</v>
       </c>
       <c r="E788" t="s">
         <v>1129</v>
       </c>
       <c r="F788" t="s">
-        <v>1130</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="789" spans="1:6">
@@ -20031,13 +20031,13 @@
         <v>24</v>
       </c>
       <c r="D789" t="s">
-        <v>1128</v>
+        <v>1150</v>
       </c>
       <c r="E789" t="s">
         <v>1129</v>
       </c>
       <c r="F789" t="s">
-        <v>1150</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="790" spans="1:6">
@@ -20051,13 +20051,13 @@
         <v>711</v>
       </c>
       <c r="D790" t="s">
-        <v>1132</v>
+        <v>1128</v>
       </c>
       <c r="E790" t="s">
         <v>1129</v>
       </c>
       <c r="F790" t="s">
-        <v>1130</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="791" spans="1:6">
@@ -20071,13 +20071,13 @@
         <v>24</v>
       </c>
       <c r="D791" t="s">
-        <v>1142</v>
+        <v>1153</v>
       </c>
       <c r="E791" t="s">
         <v>1129</v>
       </c>
       <c r="F791" t="s">
-        <v>1153</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="792" spans="1:6">
@@ -20091,13 +20091,13 @@
         <v>24</v>
       </c>
       <c r="D792" t="s">
-        <v>1155</v>
+        <v>1150</v>
       </c>
       <c r="E792" t="s">
         <v>1129</v>
       </c>
       <c r="F792" t="s">
-        <v>1150</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="793" spans="1:6">
@@ -20111,13 +20111,13 @@
         <v>711</v>
       </c>
       <c r="D793" t="s">
-        <v>1132</v>
+        <v>1128</v>
       </c>
       <c r="E793" t="s">
         <v>1129</v>
       </c>
       <c r="F793" t="s">
-        <v>1130</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="794" spans="1:6">
@@ -20131,13 +20131,13 @@
         <v>24</v>
       </c>
       <c r="D794" t="s">
-        <v>1132</v>
+        <v>1158</v>
       </c>
       <c r="E794" t="s">
         <v>1129</v>
       </c>
       <c r="F794" t="s">
-        <v>1158</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="795" spans="1:6">
@@ -20151,13 +20151,13 @@
         <v>24</v>
       </c>
       <c r="D795" t="s">
-        <v>1160</v>
+        <v>1128</v>
       </c>
       <c r="E795" t="s">
         <v>1129</v>
       </c>
       <c r="F795" t="s">
-        <v>1130</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="796" spans="1:6">
@@ -20171,13 +20171,13 @@
         <v>711</v>
       </c>
       <c r="D796" t="s">
-        <v>1132</v>
+        <v>1128</v>
       </c>
       <c r="E796" t="s">
         <v>1129</v>
       </c>
       <c r="F796" t="s">
-        <v>1130</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="797" spans="1:6">
@@ -20231,13 +20231,13 @@
         <v>711</v>
       </c>
       <c r="D799" t="s">
-        <v>1132</v>
+        <v>1128</v>
       </c>
       <c r="E799" t="s">
         <v>1129</v>
       </c>
       <c r="F799" t="s">
-        <v>1130</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="800" spans="1:6">
@@ -20251,13 +20251,13 @@
         <v>711</v>
       </c>
       <c r="D800" t="s">
-        <v>1132</v>
+        <v>1128</v>
       </c>
       <c r="E800" t="s">
         <v>1129</v>
       </c>
       <c r="F800" t="s">
-        <v>1130</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="801" spans="1:6">
@@ -20271,13 +20271,13 @@
         <v>711</v>
       </c>
       <c r="D801" t="s">
-        <v>1132</v>
+        <v>1128</v>
       </c>
       <c r="E801" t="s">
         <v>1129</v>
       </c>
       <c r="F801" t="s">
-        <v>1130</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="802" spans="1:6">
@@ -20291,13 +20291,13 @@
         <v>711</v>
       </c>
       <c r="D802" t="s">
-        <v>1132</v>
+        <v>1128</v>
       </c>
       <c r="E802" t="s">
         <v>1129</v>
       </c>
       <c r="F802" t="s">
-        <v>1130</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="803" spans="1:6">
@@ -20311,13 +20311,13 @@
         <v>711</v>
       </c>
       <c r="D803" t="s">
-        <v>1132</v>
+        <v>1128</v>
       </c>
       <c r="E803" t="s">
         <v>1129</v>
       </c>
       <c r="F803" t="s">
-        <v>1130</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="804" spans="1:6">
@@ -20331,13 +20331,13 @@
         <v>711</v>
       </c>
       <c r="D804" t="s">
-        <v>1132</v>
+        <v>1128</v>
       </c>
       <c r="E804" t="s">
         <v>1129</v>
       </c>
       <c r="F804" t="s">
-        <v>1130</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="805" spans="1:6">
@@ -20351,13 +20351,13 @@
         <v>711</v>
       </c>
       <c r="D805" t="s">
-        <v>1132</v>
+        <v>1128</v>
       </c>
       <c r="E805" t="s">
         <v>1129</v>
       </c>
       <c r="F805" t="s">
-        <v>1130</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="806" spans="1:6">
@@ -20371,13 +20371,13 @@
         <v>711</v>
       </c>
       <c r="D806" t="s">
-        <v>1132</v>
+        <v>1128</v>
       </c>
       <c r="E806" t="s">
         <v>1129</v>
       </c>
       <c r="F806" t="s">
-        <v>1130</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="807" spans="1:6">
@@ -20391,13 +20391,13 @@
         <v>711</v>
       </c>
       <c r="D807" t="s">
-        <v>1132</v>
+        <v>1128</v>
       </c>
       <c r="E807" t="s">
         <v>1129</v>
       </c>
       <c r="F807" t="s">
-        <v>1130</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="808" spans="1:6">
@@ -20531,13 +20531,13 @@
         <v>711</v>
       </c>
       <c r="D814" t="s">
-        <v>1184</v>
+        <v>1178</v>
       </c>
       <c r="E814" t="s">
         <v>1179</v>
       </c>
       <c r="F814" t="s">
-        <v>1180</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="815" spans="1:6">
@@ -20711,13 +20711,13 @@
         <v>711</v>
       </c>
       <c r="D823" t="s">
-        <v>1201</v>
+        <v>1178</v>
       </c>
       <c r="E823" t="s">
         <v>1179</v>
       </c>
       <c r="F823" t="s">
-        <v>1180</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="824" spans="1:6">
@@ -20811,13 +20811,13 @@
         <v>711</v>
       </c>
       <c r="D828" t="s">
-        <v>1201</v>
+        <v>1178</v>
       </c>
       <c r="E828" t="s">
         <v>1179</v>
       </c>
       <c r="F828" t="s">
-        <v>1180</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="829" spans="1:6">
@@ -20851,13 +20851,13 @@
         <v>711</v>
       </c>
       <c r="D830" t="s">
-        <v>1184</v>
+        <v>1178</v>
       </c>
       <c r="E830" t="s">
         <v>1179</v>
       </c>
       <c r="F830" t="s">
-        <v>1180</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="831" spans="1:6">
@@ -21051,13 +21051,13 @@
         <v>711</v>
       </c>
       <c r="D840" t="s">
-        <v>1224</v>
+        <v>1220</v>
       </c>
       <c r="E840" t="s">
         <v>1221</v>
       </c>
       <c r="F840" t="s">
-        <v>1222</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="841" spans="1:6">
@@ -21071,13 +21071,13 @@
         <v>711</v>
       </c>
       <c r="D841" t="s">
-        <v>1224</v>
+        <v>1220</v>
       </c>
       <c r="E841" t="s">
         <v>1221</v>
       </c>
       <c r="F841" t="s">
-        <v>1222</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="842" spans="1:6">
@@ -21091,13 +21091,13 @@
         <v>711</v>
       </c>
       <c r="D842" t="s">
-        <v>1224</v>
+        <v>1220</v>
       </c>
       <c r="E842" t="s">
         <v>1221</v>
       </c>
       <c r="F842" t="s">
-        <v>1222</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="843" spans="1:6">
@@ -21111,13 +21111,13 @@
         <v>711</v>
       </c>
       <c r="D843" t="s">
-        <v>1224</v>
+        <v>1220</v>
       </c>
       <c r="E843" t="s">
         <v>1221</v>
       </c>
       <c r="F843" t="s">
-        <v>1222</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="844" spans="1:6">
@@ -21131,13 +21131,13 @@
         <v>711</v>
       </c>
       <c r="D844" t="s">
-        <v>1224</v>
+        <v>1220</v>
       </c>
       <c r="E844" t="s">
         <v>1221</v>
       </c>
       <c r="F844" t="s">
-        <v>1222</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="845" spans="1:6">
@@ -21151,13 +21151,13 @@
         <v>711</v>
       </c>
       <c r="D845" t="s">
-        <v>1224</v>
+        <v>1220</v>
       </c>
       <c r="E845" t="s">
         <v>1221</v>
       </c>
       <c r="F845" t="s">
-        <v>1222</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="846" spans="1:6">
@@ -21171,13 +21171,13 @@
         <v>711</v>
       </c>
       <c r="D846" t="s">
-        <v>1224</v>
+        <v>1220</v>
       </c>
       <c r="E846" t="s">
         <v>1221</v>
       </c>
       <c r="F846" t="s">
-        <v>1222</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="847" spans="1:6">
@@ -21191,13 +21191,13 @@
         <v>711</v>
       </c>
       <c r="D847" t="s">
-        <v>1232</v>
+        <v>1184</v>
       </c>
       <c r="E847" t="s">
         <v>1221</v>
       </c>
       <c r="F847" t="s">
-        <v>1185</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="848" spans="1:6">
@@ -21211,13 +21211,13 @@
         <v>711</v>
       </c>
       <c r="D848" t="s">
-        <v>1232</v>
+        <v>1184</v>
       </c>
       <c r="E848" t="s">
         <v>1221</v>
       </c>
       <c r="F848" t="s">
-        <v>1185</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="849" spans="1:6">
@@ -21231,13 +21231,13 @@
         <v>711</v>
       </c>
       <c r="D849" t="s">
-        <v>1232</v>
+        <v>1184</v>
       </c>
       <c r="E849" t="s">
         <v>1221</v>
       </c>
       <c r="F849" t="s">
-        <v>1185</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="850" spans="1:6">
@@ -21251,13 +21251,13 @@
         <v>711</v>
       </c>
       <c r="D850" t="s">
-        <v>1232</v>
+        <v>1236</v>
       </c>
       <c r="E850" t="s">
         <v>1221</v>
       </c>
       <c r="F850" t="s">
-        <v>1236</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="851" spans="1:6">
@@ -21271,13 +21271,13 @@
         <v>711</v>
       </c>
       <c r="D851" t="s">
-        <v>1232</v>
+        <v>1184</v>
       </c>
       <c r="E851" t="s">
         <v>1221</v>
       </c>
       <c r="F851" t="s">
-        <v>1185</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="852" spans="1:6">
@@ -21291,13 +21291,13 @@
         <v>711</v>
       </c>
       <c r="D852" t="s">
-        <v>1232</v>
+        <v>1184</v>
       </c>
       <c r="E852" t="s">
         <v>1221</v>
       </c>
       <c r="F852" t="s">
-        <v>1185</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="853" spans="1:6">
@@ -21311,13 +21311,13 @@
         <v>711</v>
       </c>
       <c r="D853" t="s">
-        <v>1224</v>
+        <v>1220</v>
       </c>
       <c r="E853" t="s">
         <v>1221</v>
       </c>
       <c r="F853" t="s">
-        <v>1222</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="854" spans="1:6">
@@ -21331,13 +21331,13 @@
         <v>15</v>
       </c>
       <c r="D854" t="s">
-        <v>1224</v>
+        <v>1220</v>
       </c>
       <c r="E854" t="s">
         <v>1221</v>
       </c>
       <c r="F854" t="s">
-        <v>1222</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="855" spans="1:6">
@@ -21351,13 +21351,13 @@
         <v>15</v>
       </c>
       <c r="D855" t="s">
-        <v>1224</v>
+        <v>1220</v>
       </c>
       <c r="E855" t="s">
         <v>1221</v>
       </c>
       <c r="F855" t="s">
-        <v>1222</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="856" spans="1:6">
@@ -21371,13 +21371,13 @@
         <v>15</v>
       </c>
       <c r="D856" t="s">
-        <v>1224</v>
+        <v>1220</v>
       </c>
       <c r="E856" t="s">
         <v>1221</v>
       </c>
       <c r="F856" t="s">
-        <v>1222</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="857" spans="1:6">
@@ -21391,13 +21391,13 @@
         <v>711</v>
       </c>
       <c r="D857" t="s">
-        <v>1224</v>
+        <v>1220</v>
       </c>
       <c r="E857" t="s">
         <v>1221</v>
       </c>
       <c r="F857" t="s">
-        <v>1222</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="858" spans="1:6">
@@ -21411,13 +21411,13 @@
         <v>711</v>
       </c>
       <c r="D858" t="s">
-        <v>1224</v>
+        <v>1220</v>
       </c>
       <c r="E858" t="s">
         <v>1221</v>
       </c>
       <c r="F858" t="s">
-        <v>1222</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="859" spans="1:6">
@@ -21431,13 +21431,13 @@
         <v>15</v>
       </c>
       <c r="D859" t="s">
-        <v>1224</v>
+        <v>1220</v>
       </c>
       <c r="E859" t="s">
         <v>1221</v>
       </c>
       <c r="F859" t="s">
-        <v>1222</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="860" spans="1:6">
@@ -21451,13 +21451,13 @@
         <v>711</v>
       </c>
       <c r="D860" t="s">
-        <v>1224</v>
+        <v>1220</v>
       </c>
       <c r="E860" t="s">
         <v>1221</v>
       </c>
       <c r="F860" t="s">
-        <v>1222</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="861" spans="1:6">
@@ -21471,13 +21471,13 @@
         <v>711</v>
       </c>
       <c r="D861" t="s">
-        <v>1224</v>
+        <v>1220</v>
       </c>
       <c r="E861" t="s">
         <v>1221</v>
       </c>
       <c r="F861" t="s">
-        <v>1222</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="862" spans="1:6">
@@ -21491,13 +21491,13 @@
         <v>711</v>
       </c>
       <c r="D862" t="s">
-        <v>1224</v>
+        <v>1220</v>
       </c>
       <c r="E862" t="s">
         <v>1221</v>
       </c>
       <c r="F862" t="s">
-        <v>1222</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="863" spans="1:6">
@@ -21511,13 +21511,13 @@
         <v>711</v>
       </c>
       <c r="D863" t="s">
-        <v>1224</v>
+        <v>1220</v>
       </c>
       <c r="E863" t="s">
         <v>1221</v>
       </c>
       <c r="F863" t="s">
-        <v>1222</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="864" spans="1:6">
@@ -21531,13 +21531,13 @@
         <v>711</v>
       </c>
       <c r="D864" t="s">
-        <v>1224</v>
+        <v>1220</v>
       </c>
       <c r="E864" t="s">
         <v>1221</v>
       </c>
       <c r="F864" t="s">
-        <v>1222</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="865" spans="1:6">
@@ -21551,13 +21551,13 @@
         <v>711</v>
       </c>
       <c r="D865" t="s">
-        <v>1224</v>
+        <v>1220</v>
       </c>
       <c r="E865" t="s">
         <v>1221</v>
       </c>
       <c r="F865" t="s">
-        <v>1222</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="866" spans="1:6">
@@ -21571,13 +21571,13 @@
         <v>711</v>
       </c>
       <c r="D866" t="s">
-        <v>1224</v>
+        <v>1220</v>
       </c>
       <c r="E866" t="s">
         <v>1221</v>
       </c>
       <c r="F866" t="s">
-        <v>1222</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="867" spans="1:6">
@@ -21611,13 +21611,13 @@
         <v>711</v>
       </c>
       <c r="D868" t="s">
-        <v>1254</v>
+        <v>1258</v>
       </c>
       <c r="E868" t="s">
         <v>1255</v>
       </c>
       <c r="F868" t="s">
-        <v>1258</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="869" spans="1:6">
@@ -21631,13 +21631,13 @@
         <v>711</v>
       </c>
       <c r="D869" t="s">
-        <v>1254</v>
+        <v>1258</v>
       </c>
       <c r="E869" t="s">
         <v>1255</v>
       </c>
       <c r="F869" t="s">
-        <v>1258</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="870" spans="1:6">
@@ -21651,13 +21651,13 @@
         <v>711</v>
       </c>
       <c r="D870" t="s">
-        <v>1254</v>
+        <v>1258</v>
       </c>
       <c r="E870" t="s">
         <v>1255</v>
       </c>
       <c r="F870" t="s">
-        <v>1258</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="871" spans="1:6">
@@ -21671,13 +21671,13 @@
         <v>711</v>
       </c>
       <c r="D871" t="s">
-        <v>1254</v>
+        <v>1258</v>
       </c>
       <c r="E871" t="s">
         <v>1255</v>
       </c>
       <c r="F871" t="s">
-        <v>1258</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="872" spans="1:6">
@@ -21691,13 +21691,13 @@
         <v>15</v>
       </c>
       <c r="D872" t="s">
-        <v>1254</v>
+        <v>1258</v>
       </c>
       <c r="E872" t="s">
         <v>1255</v>
       </c>
       <c r="F872" t="s">
-        <v>1258</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="873" spans="1:6">
@@ -21711,13 +21711,13 @@
         <v>15</v>
       </c>
       <c r="D873" t="s">
-        <v>1254</v>
+        <v>1258</v>
       </c>
       <c r="E873" t="s">
         <v>1255</v>
       </c>
       <c r="F873" t="s">
-        <v>1258</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="874" spans="1:6">
@@ -21731,13 +21731,13 @@
         <v>711</v>
       </c>
       <c r="D874" t="s">
-        <v>1254</v>
+        <v>1258</v>
       </c>
       <c r="E874" t="s">
         <v>1255</v>
       </c>
       <c r="F874" t="s">
-        <v>1258</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="875" spans="1:6">
@@ -21751,13 +21751,13 @@
         <v>711</v>
       </c>
       <c r="D875" t="s">
-        <v>1254</v>
+        <v>1258</v>
       </c>
       <c r="E875" t="s">
         <v>1255</v>
       </c>
       <c r="F875" t="s">
-        <v>1258</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="876" spans="1:6">
@@ -21771,13 +21771,13 @@
         <v>711</v>
       </c>
       <c r="D876" t="s">
-        <v>1254</v>
+        <v>1258</v>
       </c>
       <c r="E876" t="s">
         <v>1255</v>
       </c>
       <c r="F876" t="s">
-        <v>1258</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="877" spans="1:6">
@@ -21791,13 +21791,13 @@
         <v>15</v>
       </c>
       <c r="D877" t="s">
-        <v>1254</v>
+        <v>1258</v>
       </c>
       <c r="E877" t="s">
         <v>1255</v>
       </c>
       <c r="F877" t="s">
-        <v>1258</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="878" spans="1:6">
@@ -21811,13 +21811,13 @@
         <v>711</v>
       </c>
       <c r="D878" t="s">
-        <v>1254</v>
+        <v>1258</v>
       </c>
       <c r="E878" t="s">
         <v>1255</v>
       </c>
       <c r="F878" t="s">
-        <v>1258</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="879" spans="1:6">
@@ -21831,13 +21831,13 @@
         <v>711</v>
       </c>
       <c r="D879" t="s">
-        <v>1254</v>
+        <v>1258</v>
       </c>
       <c r="E879" t="s">
         <v>1255</v>
       </c>
       <c r="F879" t="s">
-        <v>1258</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="880" spans="1:6">
@@ -21851,13 +21851,13 @@
         <v>711</v>
       </c>
       <c r="D880" t="s">
-        <v>1254</v>
+        <v>1258</v>
       </c>
       <c r="E880" t="s">
         <v>1255</v>
       </c>
       <c r="F880" t="s">
-        <v>1258</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="881" spans="1:6">
@@ -21871,13 +21871,13 @@
         <v>711</v>
       </c>
       <c r="D881" t="s">
-        <v>1254</v>
+        <v>1258</v>
       </c>
       <c r="E881" t="s">
         <v>1255</v>
       </c>
       <c r="F881" t="s">
-        <v>1258</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="882" spans="1:6">
@@ -21891,13 +21891,13 @@
         <v>711</v>
       </c>
       <c r="D882" t="s">
-        <v>1254</v>
+        <v>1258</v>
       </c>
       <c r="E882" t="s">
         <v>1255</v>
       </c>
       <c r="F882" t="s">
-        <v>1258</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="883" spans="1:6">
@@ -21911,13 +21911,13 @@
         <v>711</v>
       </c>
       <c r="D883" t="s">
-        <v>1254</v>
+        <v>1258</v>
       </c>
       <c r="E883" t="s">
         <v>1255</v>
       </c>
       <c r="F883" t="s">
-        <v>1258</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="884" spans="1:6">
@@ -21931,13 +21931,13 @@
         <v>711</v>
       </c>
       <c r="D884" t="s">
-        <v>1254</v>
+        <v>1258</v>
       </c>
       <c r="E884" t="s">
         <v>1255</v>
       </c>
       <c r="F884" t="s">
-        <v>1258</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="885" spans="1:6">
@@ -21951,13 +21951,13 @@
         <v>711</v>
       </c>
       <c r="D885" t="s">
-        <v>1254</v>
+        <v>1258</v>
       </c>
       <c r="E885" t="s">
         <v>1255</v>
       </c>
       <c r="F885" t="s">
-        <v>1258</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="886" spans="1:6">
@@ -21971,13 +21971,13 @@
         <v>711</v>
       </c>
       <c r="D886" t="s">
-        <v>1254</v>
+        <v>1258</v>
       </c>
       <c r="E886" t="s">
         <v>1255</v>
       </c>
       <c r="F886" t="s">
-        <v>1258</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="887" spans="1:6">
@@ -21991,13 +21991,13 @@
         <v>15</v>
       </c>
       <c r="D887" t="s">
-        <v>1254</v>
+        <v>1258</v>
       </c>
       <c r="E887" t="s">
         <v>1255</v>
       </c>
       <c r="F887" t="s">
-        <v>1258</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="888" spans="1:6">
@@ -22011,13 +22011,13 @@
         <v>711</v>
       </c>
       <c r="D888" t="s">
-        <v>1254</v>
+        <v>1258</v>
       </c>
       <c r="E888" t="s">
         <v>1255</v>
       </c>
       <c r="F888" t="s">
-        <v>1258</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="889" spans="1:6">
@@ -22031,13 +22031,13 @@
         <v>711</v>
       </c>
       <c r="D889" t="s">
-        <v>1254</v>
+        <v>1258</v>
       </c>
       <c r="E889" t="s">
         <v>1255</v>
       </c>
       <c r="F889" t="s">
-        <v>1258</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="890" spans="1:6">
@@ -22151,13 +22151,13 @@
         <v>711</v>
       </c>
       <c r="D895" t="s">
-        <v>1289</v>
+        <v>1281</v>
       </c>
       <c r="E895" t="s">
         <v>1282</v>
       </c>
       <c r="F895" t="s">
-        <v>1283</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="896" spans="1:6">
@@ -22331,13 +22331,13 @@
         <v>711</v>
       </c>
       <c r="D904" t="s">
+        <v>1281</v>
+      </c>
+      <c r="E904" t="s">
         <v>1299</v>
       </c>
-      <c r="E904" t="s">
+      <c r="F904" t="s">
         <v>1300</v>
-      </c>
-      <c r="F904" t="s">
-        <v>1283</v>
       </c>
     </row>
     <row r="905" spans="1:6">
@@ -22351,13 +22351,13 @@
         <v>711</v>
       </c>
       <c r="D905" t="s">
+        <v>1281</v>
+      </c>
+      <c r="E905" t="s">
+        <v>1299</v>
+      </c>
+      <c r="F905" t="s">
         <v>1302</v>
-      </c>
-      <c r="E905" t="s">
-        <v>1300</v>
-      </c>
-      <c r="F905" t="s">
-        <v>1283</v>
       </c>
     </row>
     <row r="906" spans="1:6">
@@ -22371,13 +22371,13 @@
         <v>711</v>
       </c>
       <c r="D906" t="s">
+        <v>1281</v>
+      </c>
+      <c r="E906" t="s">
         <v>1299</v>
       </c>
-      <c r="E906" t="s">
+      <c r="F906" t="s">
         <v>1300</v>
-      </c>
-      <c r="F906" t="s">
-        <v>1283</v>
       </c>
     </row>
   </sheetData>

--- a/api/1/clv3/xlsx/fr/HumanitarianPlan.xlsx
+++ b/api/1/clv3/xlsx/fr/HumanitarianPlan.xlsx
@@ -25,12 +25,12 @@
     <t>codeforiati:plan-start-date</t>
   </si>
   <si>
+    <t>codeforiati:plan-end-date</t>
+  </si>
+  <si>
     <t>codeforiati:plan-year</t>
   </si>
   <si>
-    <t>codeforiati:plan-end-date</t>
-  </si>
-  <si>
     <t>codeforiati:plan-type</t>
   </si>
   <si>
@@ -43,12 +43,12 @@
     <t>2025-01-01</t>
   </si>
   <si>
+    <t>2025-12-31</t>
+  </si>
+  <si>
     <t>2025</t>
   </si>
   <si>
-    <t>2025-12-31</t>
-  </si>
-  <si>
     <t>Humanitarian needs and response plan</t>
   </si>
   <si>
@@ -220,12 +220,12 @@
     <t>2024-01-01</t>
   </si>
   <si>
+    <t>2024-12-31</t>
+  </si>
+  <si>
     <t>2024</t>
   </si>
   <si>
-    <t>2024-12-31</t>
-  </si>
-  <si>
     <t>RAFG_RRP24</t>
   </si>
   <si>
@@ -424,12 +424,12 @@
     <t>2023-01-01</t>
   </si>
   <si>
+    <t>2023-12-31</t>
+  </si>
+  <si>
     <t>2023</t>
   </si>
   <si>
-    <t>2023-12-31</t>
-  </si>
-  <si>
     <t>RAFG23</t>
   </si>
   <si>
@@ -604,12 +604,12 @@
     <t>2022-01-01</t>
   </si>
   <si>
+    <t>2022-12-31</t>
+  </si>
+  <si>
     <t>2022</t>
   </si>
   <si>
-    <t>2022-12-31</t>
-  </si>
-  <si>
     <t>RAFG22</t>
   </si>
   <si>
@@ -808,12 +808,12 @@
     <t>2021-09-01</t>
   </si>
   <si>
+    <t>2021-12-31</t>
+  </si>
+  <si>
     <t>2021</t>
   </si>
   <si>
-    <t>2021-12-31</t>
-  </si>
-  <si>
     <t>HAFG21</t>
   </si>
   <si>
@@ -1012,12 +1012,12 @@
     <t>2020-01-01</t>
   </si>
   <si>
+    <t>2020-12-31</t>
+  </si>
+  <si>
     <t>2020</t>
   </si>
   <si>
-    <t>2020-12-31</t>
-  </si>
-  <si>
     <t>OBGD20</t>
   </si>
   <si>
@@ -1252,12 +1252,12 @@
     <t>2019-01-01</t>
   </si>
   <si>
+    <t>2019-12-31</t>
+  </si>
+  <si>
     <t>2019</t>
   </si>
   <si>
-    <t>2019-12-31</t>
-  </si>
-  <si>
     <t>RBGD19</t>
   </si>
   <si>
@@ -1384,12 +1384,12 @@
     <t>2018-01-01</t>
   </si>
   <si>
+    <t>2018-12-31</t>
+  </si>
+  <si>
     <t>2018</t>
   </si>
   <si>
-    <t>2018-12-31</t>
-  </si>
-  <si>
     <t>OBGD18</t>
   </si>
   <si>
@@ -1510,12 +1510,12 @@
     <t>2017-01-01</t>
   </si>
   <si>
+    <t>2017-12-31</t>
+  </si>
+  <si>
     <t>2017</t>
   </si>
   <si>
-    <t>2017-12-31</t>
-  </si>
-  <si>
     <t>HAFG17</t>
   </si>
   <si>
@@ -1681,12 +1681,12 @@
     <t>2016-01-01</t>
   </si>
   <si>
+    <t>2016-12-31</t>
+  </si>
+  <si>
     <t>2016</t>
   </si>
   <si>
-    <t>2016-12-31</t>
-  </si>
-  <si>
     <t>HAFG16</t>
   </si>
   <si>
@@ -1843,12 +1843,12 @@
     <t>2015-01-01</t>
   </si>
   <si>
+    <t>2015-12-31</t>
+  </si>
+  <si>
     <t>2015</t>
   </si>
   <si>
-    <t>2015-12-31</t>
-  </si>
-  <si>
     <t>Strategic response plan</t>
   </si>
   <si>
@@ -1978,12 +1978,12 @@
     <t>2014-01-01</t>
   </si>
   <si>
+    <t>2014-12-31</t>
+  </si>
+  <si>
     <t>2014</t>
   </si>
   <si>
-    <t>2014-12-31</t>
-  </si>
-  <si>
     <t>HBFA1314</t>
   </si>
   <si>
@@ -2149,12 +2149,12 @@
     <t>CAFG13</t>
   </si>
   <si>
+    <t>2013-12-31</t>
+  </si>
+  <si>
     <t>2013</t>
   </si>
   <si>
-    <t>2013-12-31</t>
-  </si>
-  <si>
     <t>Consolidated appeals process</t>
   </si>
   <si>
@@ -2245,12 +2245,12 @@
     <t>2012-01-01</t>
   </si>
   <si>
+    <t>2012-12-31</t>
+  </si>
+  <si>
     <t>2012</t>
   </si>
   <si>
-    <t>2012-12-31</t>
-  </si>
-  <si>
     <t>CAFG1112</t>
   </si>
   <si>
@@ -2479,12 +2479,12 @@
     <t>2010-01-01</t>
   </si>
   <si>
+    <t>2010-12-31</t>
+  </si>
+  <si>
     <t>2010</t>
   </si>
   <si>
-    <t>2010-12-31</t>
-  </si>
-  <si>
     <t>OBFA1011</t>
   </si>
   <si>
@@ -2611,12 +2611,12 @@
     <t>2009-01-01</t>
   </si>
   <si>
+    <t>2009-12-31</t>
+  </si>
+  <si>
     <t>2009</t>
   </si>
   <si>
-    <t>2009-12-31</t>
-  </si>
-  <si>
     <t>FBFA0910</t>
   </si>
   <si>
@@ -2749,12 +2749,12 @@
     <t>2008-02-01</t>
   </si>
   <si>
+    <t>2008-06-30</t>
+  </si>
+  <si>
     <t>2008</t>
   </si>
   <si>
-    <t>2008-06-30</t>
-  </si>
-  <si>
     <t>OAFG0809</t>
   </si>
   <si>
@@ -2917,12 +2917,12 @@
     <t>2007-02-22</t>
   </si>
   <si>
+    <t>2007-08-21</t>
+  </si>
+  <si>
     <t>2007</t>
   </si>
   <si>
-    <t>2007-08-21</t>
-  </si>
-  <si>
     <t>FBFA0708</t>
   </si>
   <si>
@@ -3115,12 +3115,12 @@
     <t>2006-07-01</t>
   </si>
   <si>
+    <t>2006-12-31</t>
+  </si>
+  <si>
     <t>2006</t>
   </si>
   <si>
-    <t>2006-12-31</t>
-  </si>
-  <si>
     <t>CBDI06</t>
   </si>
   <si>
@@ -3274,12 +3274,12 @@
     <t>2005-04-01</t>
   </si>
   <si>
+    <t>2005-06-30</t>
+  </si>
+  <si>
     <t>2005</t>
   </si>
   <si>
-    <t>2005-06-30</t>
-  </si>
-  <si>
     <t>FBEN05</t>
   </si>
   <si>
@@ -3403,12 +3403,12 @@
     <t>2004-09-01</t>
   </si>
   <si>
+    <t>2004-12-31</t>
+  </si>
+  <si>
     <t>2004</t>
   </si>
   <si>
-    <t>2004-12-31</t>
-  </si>
-  <si>
     <t>CAGO04</t>
   </si>
   <si>
@@ -3553,12 +3553,12 @@
     <t>2003-01-01</t>
   </si>
   <si>
+    <t>2003-12-31</t>
+  </si>
+  <si>
     <t>2003</t>
   </si>
   <si>
-    <t>2003-12-31</t>
-  </si>
-  <si>
     <t>CAGO03</t>
   </si>
   <si>
@@ -3682,12 +3682,12 @@
     <t>2001-10-01</t>
   </si>
   <si>
+    <t>2002-12-31</t>
+  </si>
+  <si>
     <t>2002</t>
   </si>
   <si>
-    <t>2002-12-31</t>
-  </si>
-  <si>
     <t>CAGO02</t>
   </si>
   <si>
@@ -3784,12 +3784,12 @@
     <t>2001-01-01</t>
   </si>
   <si>
+    <t>2001-09-30</t>
+  </si>
+  <si>
     <t>2001</t>
   </si>
   <si>
-    <t>2001-09-30</t>
-  </si>
-  <si>
     <t>CAGO01</t>
   </si>
   <si>
@@ -3865,10 +3865,10 @@
     <t>2000-01-01</t>
   </si>
   <si>
+    <t>2000-12-31</t>
+  </si>
+  <si>
     <t>2000</t>
-  </si>
-  <si>
-    <t>2000-12-31</t>
   </si>
   <si>
     <t>CBDI00</t>
@@ -4337,10 +4337,10 @@
         <v>8</v>
       </c>
       <c r="D4" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E4" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F4" t="s">
         <v>16</v>
@@ -4537,10 +4537,10 @@
         <v>8</v>
       </c>
       <c r="D14" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E14" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F14" t="s">
         <v>24</v>
@@ -4557,10 +4557,10 @@
         <v>8</v>
       </c>
       <c r="D15" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="E15" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F15" t="s">
         <v>24</v>
@@ -4597,10 +4597,10 @@
         <v>8</v>
       </c>
       <c r="D17" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="E17" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="F17" t="s">
         <v>24</v>
@@ -4637,10 +4637,10 @@
         <v>8</v>
       </c>
       <c r="D19" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="E19" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="F19" t="s">
         <v>24</v>
@@ -4737,10 +4737,10 @@
         <v>8</v>
       </c>
       <c r="D24" t="s">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="E24" t="s">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="F24" t="s">
         <v>16</v>
@@ -5097,10 +5097,10 @@
         <v>8</v>
       </c>
       <c r="D42" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="E42" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="F42" t="s">
         <v>16</v>
@@ -5137,10 +5137,10 @@
         <v>8</v>
       </c>
       <c r="D44" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="E44" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="F44" t="s">
         <v>24</v>
@@ -5157,10 +5157,10 @@
         <v>8</v>
       </c>
       <c r="D45" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="E45" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F45" t="s">
         <v>24</v>
@@ -5517,10 +5517,10 @@
         <v>67</v>
       </c>
       <c r="D63" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="E63" t="s">
-        <v>91</v>
+        <v>69</v>
       </c>
       <c r="F63" t="s">
         <v>24</v>
@@ -5537,10 +5537,10 @@
         <v>67</v>
       </c>
       <c r="D64" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="E64" t="s">
-        <v>93</v>
+        <v>69</v>
       </c>
       <c r="F64" t="s">
         <v>24</v>
@@ -5597,10 +5597,10 @@
         <v>98</v>
       </c>
       <c r="D67" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="E67" t="s">
-        <v>93</v>
+        <v>69</v>
       </c>
       <c r="F67" t="s">
         <v>16</v>
@@ -6577,10 +6577,10 @@
         <v>159</v>
       </c>
       <c r="D116" t="s">
-        <v>136</v>
+        <v>160</v>
       </c>
       <c r="E116" t="s">
-        <v>160</v>
+        <v>137</v>
       </c>
       <c r="F116" t="s">
         <v>16</v>
@@ -6597,10 +6597,10 @@
         <v>162</v>
       </c>
       <c r="D117" t="s">
-        <v>136</v>
+        <v>163</v>
       </c>
       <c r="E117" t="s">
-        <v>163</v>
+        <v>137</v>
       </c>
       <c r="F117" t="s">
         <v>16</v>
@@ -6697,10 +6697,10 @@
         <v>135</v>
       </c>
       <c r="D122" t="s">
-        <v>136</v>
+        <v>163</v>
       </c>
       <c r="E122" t="s">
-        <v>163</v>
+        <v>137</v>
       </c>
       <c r="F122" t="s">
         <v>19</v>
@@ -6717,10 +6717,10 @@
         <v>135</v>
       </c>
       <c r="D123" t="s">
-        <v>136</v>
+        <v>160</v>
       </c>
       <c r="E123" t="s">
-        <v>160</v>
+        <v>137</v>
       </c>
       <c r="F123" t="s">
         <v>16</v>
@@ -6897,10 +6897,10 @@
         <v>179</v>
       </c>
       <c r="D132" t="s">
-        <v>136</v>
+        <v>180</v>
       </c>
       <c r="E132" t="s">
-        <v>180</v>
+        <v>137</v>
       </c>
       <c r="F132" t="s">
         <v>13</v>
@@ -6937,10 +6937,10 @@
         <v>183</v>
       </c>
       <c r="D134" t="s">
-        <v>136</v>
+        <v>160</v>
       </c>
       <c r="E134" t="s">
-        <v>160</v>
+        <v>137</v>
       </c>
       <c r="F134" t="s">
         <v>24</v>
@@ -6977,10 +6977,10 @@
         <v>186</v>
       </c>
       <c r="D136" t="s">
-        <v>136</v>
+        <v>160</v>
       </c>
       <c r="E136" t="s">
-        <v>160</v>
+        <v>137</v>
       </c>
       <c r="F136" t="s">
         <v>24</v>
@@ -7277,10 +7277,10 @@
         <v>205</v>
       </c>
       <c r="D151" t="s">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="E151" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="F151" t="s">
         <v>16</v>
@@ -7377,10 +7377,10 @@
         <v>212</v>
       </c>
       <c r="D156" t="s">
-        <v>196</v>
+        <v>213</v>
       </c>
       <c r="E156" t="s">
-        <v>213</v>
+        <v>197</v>
       </c>
       <c r="F156" t="s">
         <v>24</v>
@@ -7477,10 +7477,10 @@
         <v>195</v>
       </c>
       <c r="D161" t="s">
-        <v>196</v>
+        <v>219</v>
       </c>
       <c r="E161" t="s">
-        <v>219</v>
+        <v>197</v>
       </c>
       <c r="F161" t="s">
         <v>24</v>
@@ -7557,10 +7557,10 @@
         <v>224</v>
       </c>
       <c r="D165" t="s">
-        <v>196</v>
+        <v>225</v>
       </c>
       <c r="E165" t="s">
-        <v>225</v>
+        <v>197</v>
       </c>
       <c r="F165" t="s">
         <v>24</v>
@@ -7597,10 +7597,10 @@
         <v>228</v>
       </c>
       <c r="D167" t="s">
-        <v>196</v>
+        <v>229</v>
       </c>
       <c r="E167" t="s">
-        <v>229</v>
+        <v>197</v>
       </c>
       <c r="F167" t="s">
         <v>24</v>
@@ -7737,10 +7737,10 @@
         <v>236</v>
       </c>
       <c r="D174" t="s">
-        <v>196</v>
+        <v>238</v>
       </c>
       <c r="E174" t="s">
-        <v>238</v>
+        <v>197</v>
       </c>
       <c r="F174" t="s">
         <v>16</v>
@@ -7757,10 +7757,10 @@
         <v>240</v>
       </c>
       <c r="D175" t="s">
-        <v>196</v>
+        <v>241</v>
       </c>
       <c r="E175" t="s">
-        <v>241</v>
+        <v>197</v>
       </c>
       <c r="F175" t="s">
         <v>16</v>
@@ -8057,10 +8057,10 @@
         <v>256</v>
       </c>
       <c r="D190" t="s">
-        <v>196</v>
+        <v>259</v>
       </c>
       <c r="E190" t="s">
-        <v>259</v>
+        <v>197</v>
       </c>
       <c r="F190" t="s">
         <v>13</v>
@@ -8377,10 +8377,10 @@
         <v>279</v>
       </c>
       <c r="D206" t="s">
-        <v>264</v>
+        <v>196</v>
       </c>
       <c r="E206" t="s">
-        <v>197</v>
+        <v>265</v>
       </c>
       <c r="F206" t="s">
         <v>19</v>
@@ -8397,10 +8397,10 @@
         <v>282</v>
       </c>
       <c r="D207" t="s">
-        <v>264</v>
+        <v>283</v>
       </c>
       <c r="E207" t="s">
-        <v>283</v>
+        <v>265</v>
       </c>
       <c r="F207" t="s">
         <v>24</v>
@@ -8457,10 +8457,10 @@
         <v>279</v>
       </c>
       <c r="D210" t="s">
-        <v>264</v>
+        <v>196</v>
       </c>
       <c r="E210" t="s">
-        <v>197</v>
+        <v>265</v>
       </c>
       <c r="F210" t="s">
         <v>19</v>
@@ -8477,10 +8477,10 @@
         <v>288</v>
       </c>
       <c r="D211" t="s">
-        <v>264</v>
+        <v>289</v>
       </c>
       <c r="E211" t="s">
-        <v>289</v>
+        <v>265</v>
       </c>
       <c r="F211" t="s">
         <v>24</v>
@@ -8517,10 +8517,10 @@
         <v>292</v>
       </c>
       <c r="D213" t="s">
-        <v>264</v>
+        <v>293</v>
       </c>
       <c r="E213" t="s">
-        <v>293</v>
+        <v>265</v>
       </c>
       <c r="F213" t="s">
         <v>24</v>
@@ -8557,10 +8557,10 @@
         <v>279</v>
       </c>
       <c r="D215" t="s">
-        <v>264</v>
+        <v>196</v>
       </c>
       <c r="E215" t="s">
-        <v>197</v>
+        <v>265</v>
       </c>
       <c r="F215" t="s">
         <v>19</v>
@@ -8617,10 +8617,10 @@
         <v>300</v>
       </c>
       <c r="D218" t="s">
-        <v>264</v>
+        <v>301</v>
       </c>
       <c r="E218" t="s">
-        <v>301</v>
+        <v>265</v>
       </c>
       <c r="F218" t="s">
         <v>16</v>
@@ -8657,10 +8657,10 @@
         <v>267</v>
       </c>
       <c r="D220" t="s">
-        <v>264</v>
+        <v>225</v>
       </c>
       <c r="E220" t="s">
-        <v>225</v>
+        <v>265</v>
       </c>
       <c r="F220" t="s">
         <v>24</v>
@@ -9337,10 +9337,10 @@
         <v>345</v>
       </c>
       <c r="D254" t="s">
-        <v>332</v>
+        <v>267</v>
       </c>
       <c r="E254" t="s">
-        <v>267</v>
+        <v>333</v>
       </c>
       <c r="F254" t="s">
         <v>19</v>
@@ -9497,10 +9497,10 @@
         <v>355</v>
       </c>
       <c r="D262" t="s">
-        <v>332</v>
+        <v>356</v>
       </c>
       <c r="E262" t="s">
-        <v>356</v>
+        <v>333</v>
       </c>
       <c r="F262" t="s">
         <v>24</v>
@@ -9797,10 +9797,10 @@
         <v>373</v>
       </c>
       <c r="D277" t="s">
-        <v>332</v>
+        <v>374</v>
       </c>
       <c r="E277" t="s">
-        <v>374</v>
+        <v>333</v>
       </c>
       <c r="F277" t="s">
         <v>24</v>
@@ -9837,10 +9837,10 @@
         <v>377</v>
       </c>
       <c r="D279" t="s">
-        <v>332</v>
+        <v>378</v>
       </c>
       <c r="E279" t="s">
-        <v>378</v>
+        <v>333</v>
       </c>
       <c r="F279" t="s">
         <v>24</v>
@@ -10397,10 +10397,10 @@
         <v>407</v>
       </c>
       <c r="D307" t="s">
-        <v>332</v>
+        <v>356</v>
       </c>
       <c r="E307" t="s">
-        <v>356</v>
+        <v>333</v>
       </c>
       <c r="F307" t="s">
         <v>16</v>
@@ -10757,10 +10757,10 @@
         <v>411</v>
       </c>
       <c r="D325" t="s">
-        <v>412</v>
+        <v>430</v>
       </c>
       <c r="E325" t="s">
-        <v>430</v>
+        <v>413</v>
       </c>
       <c r="F325" t="s">
         <v>24</v>
@@ -10877,10 +10877,10 @@
         <v>411</v>
       </c>
       <c r="D331" t="s">
-        <v>412</v>
+        <v>437</v>
       </c>
       <c r="E331" t="s">
-        <v>437</v>
+        <v>413</v>
       </c>
       <c r="F331" t="s">
         <v>19</v>
@@ -11117,10 +11117,10 @@
         <v>450</v>
       </c>
       <c r="D343" t="s">
-        <v>412</v>
+        <v>451</v>
       </c>
       <c r="E343" t="s">
-        <v>451</v>
+        <v>413</v>
       </c>
       <c r="F343" t="s">
         <v>24</v>
@@ -11137,10 +11137,10 @@
         <v>453</v>
       </c>
       <c r="D344" t="s">
-        <v>412</v>
+        <v>451</v>
       </c>
       <c r="E344" t="s">
-        <v>451</v>
+        <v>413</v>
       </c>
       <c r="F344" t="s">
         <v>24</v>
@@ -11677,10 +11677,10 @@
         <v>455</v>
       </c>
       <c r="D371" t="s">
-        <v>456</v>
+        <v>487</v>
       </c>
       <c r="E371" t="s">
-        <v>487</v>
+        <v>457</v>
       </c>
       <c r="F371" t="s">
         <v>19</v>
@@ -11697,10 +11697,10 @@
         <v>489</v>
       </c>
       <c r="D372" t="s">
-        <v>456</v>
+        <v>490</v>
       </c>
       <c r="E372" t="s">
-        <v>490</v>
+        <v>457</v>
       </c>
       <c r="F372" t="s">
         <v>19</v>
@@ -11737,10 +11737,10 @@
         <v>489</v>
       </c>
       <c r="D374" t="s">
-        <v>456</v>
+        <v>490</v>
       </c>
       <c r="E374" t="s">
-        <v>490</v>
+        <v>457</v>
       </c>
       <c r="F374" t="s">
         <v>19</v>
@@ -12037,10 +12037,10 @@
         <v>514</v>
       </c>
       <c r="D389" t="s">
-        <v>498</v>
+        <v>515</v>
       </c>
       <c r="E389" t="s">
-        <v>515</v>
+        <v>499</v>
       </c>
       <c r="F389" t="s">
         <v>24</v>
@@ -12157,10 +12157,10 @@
         <v>523</v>
       </c>
       <c r="D395" t="s">
-        <v>498</v>
+        <v>524</v>
       </c>
       <c r="E395" t="s">
-        <v>524</v>
+        <v>499</v>
       </c>
       <c r="F395" t="s">
         <v>24</v>
@@ -12197,10 +12197,10 @@
         <v>527</v>
       </c>
       <c r="D397" t="s">
-        <v>498</v>
+        <v>528</v>
       </c>
       <c r="E397" t="s">
-        <v>528</v>
+        <v>499</v>
       </c>
       <c r="F397" t="s">
         <v>24</v>
@@ -12257,10 +12257,10 @@
         <v>532</v>
       </c>
       <c r="D400" t="s">
-        <v>498</v>
+        <v>533</v>
       </c>
       <c r="E400" t="s">
-        <v>533</v>
+        <v>499</v>
       </c>
       <c r="F400" t="s">
         <v>24</v>
@@ -12377,10 +12377,10 @@
         <v>540</v>
       </c>
       <c r="D406" t="s">
-        <v>498</v>
+        <v>541</v>
       </c>
       <c r="E406" t="s">
-        <v>541</v>
+        <v>499</v>
       </c>
       <c r="F406" t="s">
         <v>24</v>
@@ -12817,10 +12817,10 @@
         <v>570</v>
       </c>
       <c r="D428" t="s">
-        <v>555</v>
+        <v>571</v>
       </c>
       <c r="E428" t="s">
-        <v>571</v>
+        <v>556</v>
       </c>
       <c r="F428" t="s">
         <v>24</v>
@@ -12837,10 +12837,10 @@
         <v>573</v>
       </c>
       <c r="D429" t="s">
-        <v>555</v>
+        <v>574</v>
       </c>
       <c r="E429" t="s">
-        <v>574</v>
+        <v>556</v>
       </c>
       <c r="F429" t="s">
         <v>24</v>
@@ -13057,10 +13057,10 @@
         <v>589</v>
       </c>
       <c r="D440" t="s">
-        <v>555</v>
+        <v>590</v>
       </c>
       <c r="E440" t="s">
-        <v>590</v>
+        <v>556</v>
       </c>
       <c r="F440" t="s">
         <v>24</v>
@@ -13337,10 +13337,10 @@
         <v>605</v>
       </c>
       <c r="D454" t="s">
-        <v>555</v>
+        <v>606</v>
       </c>
       <c r="E454" t="s">
-        <v>606</v>
+        <v>556</v>
       </c>
       <c r="F454" t="s">
         <v>19</v>
@@ -13537,10 +13537,10 @@
         <v>621</v>
       </c>
       <c r="D464" t="s">
-        <v>609</v>
+        <v>622</v>
       </c>
       <c r="E464" t="s">
-        <v>622</v>
+        <v>610</v>
       </c>
       <c r="F464" t="s">
         <v>24</v>
@@ -13577,10 +13577,10 @@
         <v>626</v>
       </c>
       <c r="D466" t="s">
-        <v>609</v>
+        <v>622</v>
       </c>
       <c r="E466" t="s">
-        <v>622</v>
+        <v>610</v>
       </c>
       <c r="F466" t="s">
         <v>24</v>
@@ -13597,10 +13597,10 @@
         <v>628</v>
       </c>
       <c r="D467" t="s">
-        <v>609</v>
+        <v>629</v>
       </c>
       <c r="E467" t="s">
-        <v>629</v>
+        <v>610</v>
       </c>
       <c r="F467" t="s">
         <v>24</v>
@@ -13637,10 +13637,10 @@
         <v>632</v>
       </c>
       <c r="D469" t="s">
-        <v>609</v>
+        <v>633</v>
       </c>
       <c r="E469" t="s">
-        <v>633</v>
+        <v>610</v>
       </c>
       <c r="F469" t="s">
         <v>24</v>
@@ -13717,10 +13717,10 @@
         <v>638</v>
       </c>
       <c r="D473" t="s">
-        <v>609</v>
+        <v>622</v>
       </c>
       <c r="E473" t="s">
-        <v>622</v>
+        <v>610</v>
       </c>
       <c r="F473" t="s">
         <v>24</v>
@@ -14097,10 +14097,10 @@
         <v>653</v>
       </c>
       <c r="D492" t="s">
-        <v>654</v>
+        <v>662</v>
       </c>
       <c r="E492" t="s">
-        <v>662</v>
+        <v>655</v>
       </c>
       <c r="F492" t="s">
         <v>19</v>
@@ -14137,10 +14137,10 @@
         <v>632</v>
       </c>
       <c r="D494" t="s">
-        <v>654</v>
+        <v>665</v>
       </c>
       <c r="E494" t="s">
-        <v>665</v>
+        <v>655</v>
       </c>
       <c r="F494" t="s">
         <v>13</v>
@@ -14157,10 +14157,10 @@
         <v>632</v>
       </c>
       <c r="D495" t="s">
-        <v>654</v>
+        <v>665</v>
       </c>
       <c r="E495" t="s">
-        <v>665</v>
+        <v>655</v>
       </c>
       <c r="F495" t="s">
         <v>16</v>
@@ -14397,10 +14397,10 @@
         <v>681</v>
       </c>
       <c r="D507" t="s">
-        <v>654</v>
+        <v>682</v>
       </c>
       <c r="E507" t="s">
-        <v>682</v>
+        <v>655</v>
       </c>
       <c r="F507" t="s">
         <v>24</v>
@@ -14417,10 +14417,10 @@
         <v>684</v>
       </c>
       <c r="D508" t="s">
-        <v>654</v>
+        <v>685</v>
       </c>
       <c r="E508" t="s">
-        <v>685</v>
+        <v>655</v>
       </c>
       <c r="F508" t="s">
         <v>611</v>
@@ -14437,10 +14437,10 @@
         <v>684</v>
       </c>
       <c r="D509" t="s">
-        <v>654</v>
+        <v>687</v>
       </c>
       <c r="E509" t="s">
-        <v>687</v>
+        <v>655</v>
       </c>
       <c r="F509" t="s">
         <v>19</v>
@@ -14457,10 +14457,10 @@
         <v>689</v>
       </c>
       <c r="D510" t="s">
-        <v>654</v>
+        <v>690</v>
       </c>
       <c r="E510" t="s">
-        <v>690</v>
+        <v>655</v>
       </c>
       <c r="F510" t="s">
         <v>24</v>
@@ -14517,10 +14517,10 @@
         <v>653</v>
       </c>
       <c r="D513" t="s">
-        <v>654</v>
+        <v>695</v>
       </c>
       <c r="E513" t="s">
-        <v>695</v>
+        <v>655</v>
       </c>
       <c r="F513" t="s">
         <v>19</v>
@@ -14857,10 +14857,10 @@
         <v>657</v>
       </c>
       <c r="D530" t="s">
-        <v>711</v>
+        <v>720</v>
       </c>
       <c r="E530" t="s">
-        <v>720</v>
+        <v>712</v>
       </c>
       <c r="F530" t="s">
         <v>713</v>
@@ -15057,10 +15057,10 @@
         <v>657</v>
       </c>
       <c r="D540" t="s">
-        <v>711</v>
+        <v>690</v>
       </c>
       <c r="E540" t="s">
-        <v>690</v>
+        <v>712</v>
       </c>
       <c r="F540" t="s">
         <v>713</v>
@@ -15157,10 +15157,10 @@
         <v>657</v>
       </c>
       <c r="D545" t="s">
-        <v>711</v>
+        <v>738</v>
       </c>
       <c r="E545" t="s">
-        <v>738</v>
+        <v>712</v>
       </c>
       <c r="F545" t="s">
         <v>13</v>
@@ -15337,10 +15337,10 @@
         <v>742</v>
       </c>
       <c r="D554" t="s">
-        <v>743</v>
+        <v>753</v>
       </c>
       <c r="E554" t="s">
-        <v>753</v>
+        <v>744</v>
       </c>
       <c r="F554" t="s">
         <v>713</v>
@@ -15417,10 +15417,10 @@
         <v>758</v>
       </c>
       <c r="D558" t="s">
-        <v>743</v>
+        <v>759</v>
       </c>
       <c r="E558" t="s">
-        <v>759</v>
+        <v>744</v>
       </c>
       <c r="F558" t="s">
         <v>24</v>
@@ -15517,10 +15517,10 @@
         <v>742</v>
       </c>
       <c r="D563" t="s">
-        <v>743</v>
+        <v>766</v>
       </c>
       <c r="E563" t="s">
-        <v>766</v>
+        <v>744</v>
       </c>
       <c r="F563" t="s">
         <v>16</v>
@@ -15637,10 +15637,10 @@
         <v>773</v>
       </c>
       <c r="D569" t="s">
-        <v>743</v>
+        <v>774</v>
       </c>
       <c r="E569" t="s">
-        <v>774</v>
+        <v>744</v>
       </c>
       <c r="F569" t="s">
         <v>713</v>
@@ -15717,10 +15717,10 @@
         <v>779</v>
       </c>
       <c r="D573" t="s">
+        <v>711</v>
+      </c>
+      <c r="E573" t="s">
         <v>780</v>
-      </c>
-      <c r="E573" t="s">
-        <v>712</v>
       </c>
       <c r="F573" t="s">
         <v>713</v>
@@ -15737,10 +15737,10 @@
         <v>779</v>
       </c>
       <c r="D574" t="s">
+        <v>782</v>
+      </c>
+      <c r="E574" t="s">
         <v>780</v>
-      </c>
-      <c r="E574" t="s">
-        <v>782</v>
       </c>
       <c r="F574" t="s">
         <v>713</v>
@@ -15757,10 +15757,10 @@
         <v>779</v>
       </c>
       <c r="D575" t="s">
+        <v>782</v>
+      </c>
+      <c r="E575" t="s">
         <v>780</v>
-      </c>
-      <c r="E575" t="s">
-        <v>782</v>
       </c>
       <c r="F575" t="s">
         <v>713</v>
@@ -15777,10 +15777,10 @@
         <v>779</v>
       </c>
       <c r="D576" t="s">
+        <v>782</v>
+      </c>
+      <c r="E576" t="s">
         <v>780</v>
-      </c>
-      <c r="E576" t="s">
-        <v>782</v>
       </c>
       <c r="F576" t="s">
         <v>713</v>
@@ -15797,10 +15797,10 @@
         <v>779</v>
       </c>
       <c r="D577" t="s">
+        <v>743</v>
+      </c>
+      <c r="E577" t="s">
         <v>780</v>
-      </c>
-      <c r="E577" t="s">
-        <v>744</v>
       </c>
       <c r="F577" t="s">
         <v>713</v>
@@ -15817,10 +15817,10 @@
         <v>787</v>
       </c>
       <c r="D578" t="s">
+        <v>782</v>
+      </c>
+      <c r="E578" t="s">
         <v>780</v>
-      </c>
-      <c r="E578" t="s">
-        <v>782</v>
       </c>
       <c r="F578" t="s">
         <v>713</v>
@@ -15837,10 +15837,10 @@
         <v>789</v>
       </c>
       <c r="D579" t="s">
+        <v>790</v>
+      </c>
+      <c r="E579" t="s">
         <v>780</v>
-      </c>
-      <c r="E579" t="s">
-        <v>790</v>
       </c>
       <c r="F579" t="s">
         <v>24</v>
@@ -15857,10 +15857,10 @@
         <v>792</v>
       </c>
       <c r="D580" t="s">
+        <v>782</v>
+      </c>
+      <c r="E580" t="s">
         <v>780</v>
-      </c>
-      <c r="E580" t="s">
-        <v>782</v>
       </c>
       <c r="F580" t="s">
         <v>713</v>
@@ -15877,10 +15877,10 @@
         <v>794</v>
       </c>
       <c r="D581" t="s">
+        <v>782</v>
+      </c>
+      <c r="E581" t="s">
         <v>780</v>
-      </c>
-      <c r="E581" t="s">
-        <v>782</v>
       </c>
       <c r="F581" t="s">
         <v>16</v>
@@ -15897,10 +15897,10 @@
         <v>779</v>
       </c>
       <c r="D582" t="s">
+        <v>782</v>
+      </c>
+      <c r="E582" t="s">
         <v>780</v>
-      </c>
-      <c r="E582" t="s">
-        <v>782</v>
       </c>
       <c r="F582" t="s">
         <v>16</v>
@@ -15917,10 +15917,10 @@
         <v>797</v>
       </c>
       <c r="D583" t="s">
+        <v>798</v>
+      </c>
+      <c r="E583" t="s">
         <v>780</v>
-      </c>
-      <c r="E583" t="s">
-        <v>798</v>
       </c>
       <c r="F583" t="s">
         <v>24</v>
@@ -15937,10 +15937,10 @@
         <v>800</v>
       </c>
       <c r="D584" t="s">
+        <v>801</v>
+      </c>
+      <c r="E584" t="s">
         <v>780</v>
-      </c>
-      <c r="E584" t="s">
-        <v>801</v>
       </c>
       <c r="F584" t="s">
         <v>24</v>
@@ -15957,10 +15957,10 @@
         <v>779</v>
       </c>
       <c r="D585" t="s">
+        <v>782</v>
+      </c>
+      <c r="E585" t="s">
         <v>780</v>
-      </c>
-      <c r="E585" t="s">
-        <v>782</v>
       </c>
       <c r="F585" t="s">
         <v>713</v>
@@ -15977,10 +15977,10 @@
         <v>804</v>
       </c>
       <c r="D586" t="s">
+        <v>805</v>
+      </c>
+      <c r="E586" t="s">
         <v>780</v>
-      </c>
-      <c r="E586" t="s">
-        <v>805</v>
       </c>
       <c r="F586" t="s">
         <v>24</v>
@@ -15997,10 +15997,10 @@
         <v>807</v>
       </c>
       <c r="D587" t="s">
+        <v>782</v>
+      </c>
+      <c r="E587" t="s">
         <v>780</v>
-      </c>
-      <c r="E587" t="s">
-        <v>782</v>
       </c>
       <c r="F587" t="s">
         <v>13</v>
@@ -16017,10 +16017,10 @@
         <v>809</v>
       </c>
       <c r="D588" t="s">
+        <v>782</v>
+      </c>
+      <c r="E588" t="s">
         <v>780</v>
-      </c>
-      <c r="E588" t="s">
-        <v>782</v>
       </c>
       <c r="F588" t="s">
         <v>713</v>
@@ -16037,10 +16037,10 @@
         <v>779</v>
       </c>
       <c r="D589" t="s">
+        <v>782</v>
+      </c>
+      <c r="E589" t="s">
         <v>780</v>
-      </c>
-      <c r="E589" t="s">
-        <v>782</v>
       </c>
       <c r="F589" t="s">
         <v>713</v>
@@ -16057,10 +16057,10 @@
         <v>779</v>
       </c>
       <c r="D590" t="s">
+        <v>782</v>
+      </c>
+      <c r="E590" t="s">
         <v>780</v>
-      </c>
-      <c r="E590" t="s">
-        <v>782</v>
       </c>
       <c r="F590" t="s">
         <v>24</v>
@@ -16077,10 +16077,10 @@
         <v>779</v>
       </c>
       <c r="D591" t="s">
+        <v>782</v>
+      </c>
+      <c r="E591" t="s">
         <v>780</v>
-      </c>
-      <c r="E591" t="s">
-        <v>782</v>
       </c>
       <c r="F591" t="s">
         <v>16</v>
@@ -16097,10 +16097,10 @@
         <v>779</v>
       </c>
       <c r="D592" t="s">
+        <v>814</v>
+      </c>
+      <c r="E592" t="s">
         <v>780</v>
-      </c>
-      <c r="E592" t="s">
-        <v>814</v>
       </c>
       <c r="F592" t="s">
         <v>713</v>
@@ -16117,10 +16117,10 @@
         <v>779</v>
       </c>
       <c r="D593" t="s">
+        <v>782</v>
+      </c>
+      <c r="E593" t="s">
         <v>780</v>
-      </c>
-      <c r="E593" t="s">
-        <v>782</v>
       </c>
       <c r="F593" t="s">
         <v>13</v>
@@ -16137,10 +16137,10 @@
         <v>779</v>
       </c>
       <c r="D594" t="s">
+        <v>782</v>
+      </c>
+      <c r="E594" t="s">
         <v>780</v>
-      </c>
-      <c r="E594" t="s">
-        <v>782</v>
       </c>
       <c r="F594" t="s">
         <v>713</v>
@@ -16157,10 +16157,10 @@
         <v>779</v>
       </c>
       <c r="D595" t="s">
+        <v>782</v>
+      </c>
+      <c r="E595" t="s">
         <v>780</v>
-      </c>
-      <c r="E595" t="s">
-        <v>782</v>
       </c>
       <c r="F595" t="s">
         <v>713</v>
@@ -16177,10 +16177,10 @@
         <v>779</v>
       </c>
       <c r="D596" t="s">
+        <v>782</v>
+      </c>
+      <c r="E596" t="s">
         <v>780</v>
-      </c>
-      <c r="E596" t="s">
-        <v>782</v>
       </c>
       <c r="F596" t="s">
         <v>713</v>
@@ -16217,10 +16217,10 @@
         <v>824</v>
       </c>
       <c r="D598" t="s">
-        <v>821</v>
+        <v>825</v>
       </c>
       <c r="E598" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="F598" t="s">
         <v>16</v>
@@ -16297,10 +16297,10 @@
         <v>830</v>
       </c>
       <c r="D602" t="s">
-        <v>821</v>
+        <v>831</v>
       </c>
       <c r="E602" t="s">
-        <v>831</v>
+        <v>822</v>
       </c>
       <c r="F602" t="s">
         <v>24</v>
@@ -16317,10 +16317,10 @@
         <v>833</v>
       </c>
       <c r="D603" t="s">
-        <v>821</v>
+        <v>834</v>
       </c>
       <c r="E603" t="s">
-        <v>834</v>
+        <v>822</v>
       </c>
       <c r="F603" t="s">
         <v>24</v>
@@ -16337,10 +16337,10 @@
         <v>836</v>
       </c>
       <c r="D604" t="s">
-        <v>821</v>
+        <v>837</v>
       </c>
       <c r="E604" t="s">
-        <v>837</v>
+        <v>822</v>
       </c>
       <c r="F604" t="s">
         <v>713</v>
@@ -16417,10 +16417,10 @@
         <v>843</v>
       </c>
       <c r="D608" t="s">
-        <v>821</v>
+        <v>844</v>
       </c>
       <c r="E608" t="s">
-        <v>844</v>
+        <v>822</v>
       </c>
       <c r="F608" t="s">
         <v>24</v>
@@ -16437,10 +16437,10 @@
         <v>846</v>
       </c>
       <c r="D609" t="s">
-        <v>821</v>
+        <v>807</v>
       </c>
       <c r="E609" t="s">
-        <v>807</v>
+        <v>822</v>
       </c>
       <c r="F609" t="s">
         <v>713</v>
@@ -16477,10 +16477,10 @@
         <v>824</v>
       </c>
       <c r="D611" t="s">
-        <v>821</v>
+        <v>849</v>
       </c>
       <c r="E611" t="s">
-        <v>849</v>
+        <v>822</v>
       </c>
       <c r="F611" t="s">
         <v>24</v>
@@ -16737,10 +16737,10 @@
         <v>868</v>
       </c>
       <c r="D624" t="s">
-        <v>865</v>
+        <v>869</v>
       </c>
       <c r="E624" t="s">
-        <v>869</v>
+        <v>866</v>
       </c>
       <c r="F624" t="s">
         <v>24</v>
@@ -16817,10 +16817,10 @@
         <v>864</v>
       </c>
       <c r="D628" t="s">
-        <v>865</v>
+        <v>874</v>
       </c>
       <c r="E628" t="s">
-        <v>874</v>
+        <v>866</v>
       </c>
       <c r="F628" t="s">
         <v>713</v>
@@ -16897,10 +16897,10 @@
         <v>876</v>
       </c>
       <c r="D632" t="s">
-        <v>865</v>
+        <v>880</v>
       </c>
       <c r="E632" t="s">
-        <v>880</v>
+        <v>866</v>
       </c>
       <c r="F632" t="s">
         <v>24</v>
@@ -16917,10 +16917,10 @@
         <v>882</v>
       </c>
       <c r="D633" t="s">
-        <v>865</v>
+        <v>883</v>
       </c>
       <c r="E633" t="s">
-        <v>883</v>
+        <v>866</v>
       </c>
       <c r="F633" t="s">
         <v>24</v>
@@ -16937,10 +16937,10 @@
         <v>885</v>
       </c>
       <c r="D634" t="s">
-        <v>865</v>
+        <v>886</v>
       </c>
       <c r="E634" t="s">
-        <v>886</v>
+        <v>866</v>
       </c>
       <c r="F634" t="s">
         <v>24</v>
@@ -16997,10 +16997,10 @@
         <v>891</v>
       </c>
       <c r="D637" t="s">
-        <v>865</v>
+        <v>892</v>
       </c>
       <c r="E637" t="s">
-        <v>892</v>
+        <v>866</v>
       </c>
       <c r="F637" t="s">
         <v>24</v>
@@ -17077,10 +17077,10 @@
         <v>897</v>
       </c>
       <c r="D641" t="s">
-        <v>865</v>
+        <v>898</v>
       </c>
       <c r="E641" t="s">
-        <v>898</v>
+        <v>866</v>
       </c>
       <c r="F641" t="s">
         <v>16</v>
@@ -17257,10 +17257,10 @@
         <v>914</v>
       </c>
       <c r="D650" t="s">
-        <v>911</v>
+        <v>915</v>
       </c>
       <c r="E650" t="s">
-        <v>915</v>
+        <v>912</v>
       </c>
       <c r="F650" t="s">
         <v>16</v>
@@ -17277,10 +17277,10 @@
         <v>910</v>
       </c>
       <c r="D651" t="s">
-        <v>911</v>
+        <v>917</v>
       </c>
       <c r="E651" t="s">
-        <v>917</v>
+        <v>912</v>
       </c>
       <c r="F651" t="s">
         <v>24</v>
@@ -17297,10 +17297,10 @@
         <v>919</v>
       </c>
       <c r="D652" t="s">
-        <v>911</v>
+        <v>920</v>
       </c>
       <c r="E652" t="s">
-        <v>920</v>
+        <v>912</v>
       </c>
       <c r="F652" t="s">
         <v>713</v>
@@ -17317,10 +17317,10 @@
         <v>919</v>
       </c>
       <c r="D653" t="s">
-        <v>911</v>
+        <v>920</v>
       </c>
       <c r="E653" t="s">
-        <v>920</v>
+        <v>912</v>
       </c>
       <c r="F653" t="s">
         <v>713</v>
@@ -17337,10 +17337,10 @@
         <v>902</v>
       </c>
       <c r="D654" t="s">
-        <v>911</v>
+        <v>865</v>
       </c>
       <c r="E654" t="s">
-        <v>866</v>
+        <v>912</v>
       </c>
       <c r="F654" t="s">
         <v>16</v>
@@ -17357,10 +17357,10 @@
         <v>919</v>
       </c>
       <c r="D655" t="s">
-        <v>911</v>
+        <v>920</v>
       </c>
       <c r="E655" t="s">
-        <v>920</v>
+        <v>912</v>
       </c>
       <c r="F655" t="s">
         <v>713</v>
@@ -17377,10 +17377,10 @@
         <v>919</v>
       </c>
       <c r="D656" t="s">
-        <v>911</v>
+        <v>920</v>
       </c>
       <c r="E656" t="s">
-        <v>920</v>
+        <v>912</v>
       </c>
       <c r="F656" t="s">
         <v>713</v>
@@ -17397,10 +17397,10 @@
         <v>926</v>
       </c>
       <c r="D657" t="s">
-        <v>911</v>
+        <v>927</v>
       </c>
       <c r="E657" t="s">
-        <v>927</v>
+        <v>912</v>
       </c>
       <c r="F657" t="s">
         <v>16</v>
@@ -17417,10 +17417,10 @@
         <v>929</v>
       </c>
       <c r="D658" t="s">
-        <v>911</v>
+        <v>930</v>
       </c>
       <c r="E658" t="s">
-        <v>930</v>
+        <v>912</v>
       </c>
       <c r="F658" t="s">
         <v>24</v>
@@ -17437,10 +17437,10 @@
         <v>889</v>
       </c>
       <c r="D659" t="s">
-        <v>911</v>
+        <v>932</v>
       </c>
       <c r="E659" t="s">
-        <v>932</v>
+        <v>912</v>
       </c>
       <c r="F659" t="s">
         <v>24</v>
@@ -17457,10 +17457,10 @@
         <v>934</v>
       </c>
       <c r="D660" t="s">
-        <v>911</v>
+        <v>935</v>
       </c>
       <c r="E660" t="s">
-        <v>935</v>
+        <v>912</v>
       </c>
       <c r="F660" t="s">
         <v>24</v>
@@ -17477,10 +17477,10 @@
         <v>919</v>
       </c>
       <c r="D661" t="s">
-        <v>911</v>
+        <v>920</v>
       </c>
       <c r="E661" t="s">
-        <v>920</v>
+        <v>912</v>
       </c>
       <c r="F661" t="s">
         <v>713</v>
@@ -17497,10 +17497,10 @@
         <v>919</v>
       </c>
       <c r="D662" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E662" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
       <c r="F662" t="s">
         <v>24</v>
@@ -17517,10 +17517,10 @@
         <v>939</v>
       </c>
       <c r="D663" t="s">
-        <v>911</v>
+        <v>940</v>
       </c>
       <c r="E663" t="s">
-        <v>940</v>
+        <v>912</v>
       </c>
       <c r="F663" t="s">
         <v>24</v>
@@ -17537,10 +17537,10 @@
         <v>902</v>
       </c>
       <c r="D664" t="s">
-        <v>911</v>
+        <v>942</v>
       </c>
       <c r="E664" t="s">
-        <v>942</v>
+        <v>912</v>
       </c>
       <c r="F664" t="s">
         <v>16</v>
@@ -17557,10 +17557,10 @@
         <v>944</v>
       </c>
       <c r="D665" t="s">
-        <v>911</v>
+        <v>920</v>
       </c>
       <c r="E665" t="s">
-        <v>920</v>
+        <v>912</v>
       </c>
       <c r="F665" t="s">
         <v>713</v>
@@ -17597,10 +17597,10 @@
         <v>947</v>
       </c>
       <c r="D667" t="s">
-        <v>911</v>
+        <v>948</v>
       </c>
       <c r="E667" t="s">
-        <v>948</v>
+        <v>912</v>
       </c>
       <c r="F667" t="s">
         <v>24</v>
@@ -17617,10 +17617,10 @@
         <v>919</v>
       </c>
       <c r="D668" t="s">
-        <v>911</v>
+        <v>920</v>
       </c>
       <c r="E668" t="s">
-        <v>920</v>
+        <v>912</v>
       </c>
       <c r="F668" t="s">
         <v>16</v>
@@ -17637,10 +17637,10 @@
         <v>902</v>
       </c>
       <c r="D669" t="s">
-        <v>911</v>
+        <v>932</v>
       </c>
       <c r="E669" t="s">
-        <v>932</v>
+        <v>912</v>
       </c>
       <c r="F669" t="s">
         <v>16</v>
@@ -17657,10 +17657,10 @@
         <v>919</v>
       </c>
       <c r="D670" t="s">
-        <v>911</v>
+        <v>920</v>
       </c>
       <c r="E670" t="s">
-        <v>920</v>
+        <v>912</v>
       </c>
       <c r="F670" t="s">
         <v>713</v>
@@ -17677,10 +17677,10 @@
         <v>910</v>
       </c>
       <c r="D671" t="s">
-        <v>911</v>
+        <v>953</v>
       </c>
       <c r="E671" t="s">
-        <v>953</v>
+        <v>912</v>
       </c>
       <c r="F671" t="s">
         <v>24</v>
@@ -17697,10 +17697,10 @@
         <v>919</v>
       </c>
       <c r="D672" t="s">
-        <v>911</v>
+        <v>920</v>
       </c>
       <c r="E672" t="s">
-        <v>920</v>
+        <v>912</v>
       </c>
       <c r="F672" t="s">
         <v>16</v>
@@ -17717,10 +17717,10 @@
         <v>919</v>
       </c>
       <c r="D673" t="s">
-        <v>911</v>
+        <v>920</v>
       </c>
       <c r="E673" t="s">
-        <v>920</v>
+        <v>912</v>
       </c>
       <c r="F673" t="s">
         <v>713</v>
@@ -17737,10 +17737,10 @@
         <v>902</v>
       </c>
       <c r="D674" t="s">
-        <v>911</v>
+        <v>935</v>
       </c>
       <c r="E674" t="s">
-        <v>935</v>
+        <v>912</v>
       </c>
       <c r="F674" t="s">
         <v>16</v>
@@ -17757,10 +17757,10 @@
         <v>910</v>
       </c>
       <c r="D675" t="s">
-        <v>911</v>
+        <v>917</v>
       </c>
       <c r="E675" t="s">
-        <v>917</v>
+        <v>912</v>
       </c>
       <c r="F675" t="s">
         <v>24</v>
@@ -17777,10 +17777,10 @@
         <v>959</v>
       </c>
       <c r="D676" t="s">
-        <v>911</v>
+        <v>920</v>
       </c>
       <c r="E676" t="s">
-        <v>920</v>
+        <v>912</v>
       </c>
       <c r="F676" t="s">
         <v>16</v>
@@ -17797,10 +17797,10 @@
         <v>919</v>
       </c>
       <c r="D677" t="s">
-        <v>911</v>
+        <v>920</v>
       </c>
       <c r="E677" t="s">
-        <v>920</v>
+        <v>912</v>
       </c>
       <c r="F677" t="s">
         <v>713</v>
@@ -17817,10 +17817,10 @@
         <v>919</v>
       </c>
       <c r="D678" t="s">
-        <v>911</v>
+        <v>920</v>
       </c>
       <c r="E678" t="s">
-        <v>920</v>
+        <v>912</v>
       </c>
       <c r="F678" t="s">
         <v>713</v>
@@ -17837,10 +17837,10 @@
         <v>934</v>
       </c>
       <c r="D679" t="s">
-        <v>911</v>
+        <v>935</v>
       </c>
       <c r="E679" t="s">
-        <v>935</v>
+        <v>912</v>
       </c>
       <c r="F679" t="s">
         <v>24</v>
@@ -17857,10 +17857,10 @@
         <v>919</v>
       </c>
       <c r="D680" t="s">
-        <v>911</v>
+        <v>920</v>
       </c>
       <c r="E680" t="s">
-        <v>920</v>
+        <v>912</v>
       </c>
       <c r="F680" t="s">
         <v>713</v>
@@ -17877,10 +17877,10 @@
         <v>919</v>
       </c>
       <c r="D681" t="s">
-        <v>911</v>
+        <v>920</v>
       </c>
       <c r="E681" t="s">
-        <v>920</v>
+        <v>912</v>
       </c>
       <c r="F681" t="s">
         <v>713</v>
@@ -17917,10 +17917,10 @@
         <v>970</v>
       </c>
       <c r="D683" t="s">
-        <v>967</v>
+        <v>971</v>
       </c>
       <c r="E683" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="F683" t="s">
         <v>24</v>
@@ -17937,10 +17937,10 @@
         <v>973</v>
       </c>
       <c r="D684" t="s">
-        <v>967</v>
+        <v>974</v>
       </c>
       <c r="E684" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
       <c r="F684" t="s">
         <v>713</v>
@@ -17957,10 +17957,10 @@
         <v>973</v>
       </c>
       <c r="D685" t="s">
-        <v>967</v>
+        <v>974</v>
       </c>
       <c r="E685" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
       <c r="F685" t="s">
         <v>713</v>
@@ -17977,10 +17977,10 @@
         <v>973</v>
       </c>
       <c r="D686" t="s">
-        <v>967</v>
+        <v>974</v>
       </c>
       <c r="E686" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
       <c r="F686" t="s">
         <v>713</v>
@@ -17997,10 +17997,10 @@
         <v>973</v>
       </c>
       <c r="D687" t="s">
-        <v>967</v>
+        <v>974</v>
       </c>
       <c r="E687" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
       <c r="F687" t="s">
         <v>713</v>
@@ -18017,10 +18017,10 @@
         <v>973</v>
       </c>
       <c r="D688" t="s">
-        <v>967</v>
+        <v>974</v>
       </c>
       <c r="E688" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
       <c r="F688" t="s">
         <v>713</v>
@@ -18037,10 +18037,10 @@
         <v>970</v>
       </c>
       <c r="D689" t="s">
-        <v>967</v>
+        <v>980</v>
       </c>
       <c r="E689" t="s">
-        <v>980</v>
+        <v>968</v>
       </c>
       <c r="F689" t="s">
         <v>24</v>
@@ -18057,10 +18057,10 @@
         <v>982</v>
       </c>
       <c r="D690" t="s">
-        <v>967</v>
+        <v>983</v>
       </c>
       <c r="E690" t="s">
-        <v>983</v>
+        <v>968</v>
       </c>
       <c r="F690" t="s">
         <v>24</v>
@@ -18077,10 +18077,10 @@
         <v>973</v>
       </c>
       <c r="D691" t="s">
-        <v>967</v>
+        <v>974</v>
       </c>
       <c r="E691" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
       <c r="F691" t="s">
         <v>13</v>
@@ -18097,10 +18097,10 @@
         <v>986</v>
       </c>
       <c r="D692" t="s">
-        <v>967</v>
+        <v>920</v>
       </c>
       <c r="E692" t="s">
-        <v>920</v>
+        <v>968</v>
       </c>
       <c r="F692" t="s">
         <v>16</v>
@@ -18117,10 +18117,10 @@
         <v>988</v>
       </c>
       <c r="D693" t="s">
-        <v>967</v>
+        <v>989</v>
       </c>
       <c r="E693" t="s">
-        <v>989</v>
+        <v>968</v>
       </c>
       <c r="F693" t="s">
         <v>24</v>
@@ -18137,10 +18137,10 @@
         <v>991</v>
       </c>
       <c r="D694" t="s">
-        <v>967</v>
+        <v>992</v>
       </c>
       <c r="E694" t="s">
-        <v>992</v>
+        <v>968</v>
       </c>
       <c r="F694" t="s">
         <v>16</v>
@@ -18157,10 +18157,10 @@
         <v>994</v>
       </c>
       <c r="D695" t="s">
-        <v>967</v>
+        <v>995</v>
       </c>
       <c r="E695" t="s">
-        <v>995</v>
+        <v>968</v>
       </c>
       <c r="F695" t="s">
         <v>24</v>
@@ -18177,10 +18177,10 @@
         <v>973</v>
       </c>
       <c r="D696" t="s">
-        <v>967</v>
+        <v>974</v>
       </c>
       <c r="E696" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
       <c r="F696" t="s">
         <v>713</v>
@@ -18197,10 +18197,10 @@
         <v>998</v>
       </c>
       <c r="D697" t="s">
-        <v>967</v>
+        <v>999</v>
       </c>
       <c r="E697" t="s">
-        <v>999</v>
+        <v>968</v>
       </c>
       <c r="F697" t="s">
         <v>24</v>
@@ -18217,10 +18217,10 @@
         <v>1001</v>
       </c>
       <c r="D698" t="s">
-        <v>967</v>
+        <v>1002</v>
       </c>
       <c r="E698" t="s">
-        <v>1002</v>
+        <v>968</v>
       </c>
       <c r="F698" t="s">
         <v>24</v>
@@ -18237,10 +18237,10 @@
         <v>973</v>
       </c>
       <c r="D699" t="s">
-        <v>967</v>
+        <v>974</v>
       </c>
       <c r="E699" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
       <c r="F699" t="s">
         <v>16</v>
@@ -18257,10 +18257,10 @@
         <v>1005</v>
       </c>
       <c r="D700" t="s">
-        <v>967</v>
+        <v>1006</v>
       </c>
       <c r="E700" t="s">
-        <v>1006</v>
+        <v>968</v>
       </c>
       <c r="F700" t="s">
         <v>24</v>
@@ -18277,10 +18277,10 @@
         <v>973</v>
       </c>
       <c r="D701" t="s">
-        <v>967</v>
+        <v>974</v>
       </c>
       <c r="E701" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
       <c r="F701" t="s">
         <v>16</v>
@@ -18297,10 +18297,10 @@
         <v>1009</v>
       </c>
       <c r="D702" t="s">
-        <v>967</v>
+        <v>1010</v>
       </c>
       <c r="E702" t="s">
-        <v>1010</v>
+        <v>968</v>
       </c>
       <c r="F702" t="s">
         <v>24</v>
@@ -18317,10 +18317,10 @@
         <v>1012</v>
       </c>
       <c r="D703" t="s">
-        <v>967</v>
+        <v>1006</v>
       </c>
       <c r="E703" t="s">
-        <v>1006</v>
+        <v>968</v>
       </c>
       <c r="F703" t="s">
         <v>24</v>
@@ -18337,10 +18337,10 @@
         <v>973</v>
       </c>
       <c r="D704" t="s">
-        <v>967</v>
+        <v>974</v>
       </c>
       <c r="E704" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
       <c r="F704" t="s">
         <v>713</v>
@@ -18357,10 +18357,10 @@
         <v>1015</v>
       </c>
       <c r="D705" t="s">
-        <v>967</v>
+        <v>1002</v>
       </c>
       <c r="E705" t="s">
-        <v>1002</v>
+        <v>968</v>
       </c>
       <c r="F705" t="s">
         <v>16</v>
@@ -18377,10 +18377,10 @@
         <v>973</v>
       </c>
       <c r="D706" t="s">
-        <v>967</v>
+        <v>974</v>
       </c>
       <c r="E706" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
       <c r="F706" t="s">
         <v>713</v>
@@ -18397,10 +18397,10 @@
         <v>973</v>
       </c>
       <c r="D707" t="s">
-        <v>967</v>
+        <v>1002</v>
       </c>
       <c r="E707" t="s">
-        <v>1002</v>
+        <v>968</v>
       </c>
       <c r="F707" t="s">
         <v>16</v>
@@ -18417,10 +18417,10 @@
         <v>1019</v>
       </c>
       <c r="D708" t="s">
-        <v>967</v>
+        <v>971</v>
       </c>
       <c r="E708" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="F708" t="s">
         <v>24</v>
@@ -18437,10 +18437,10 @@
         <v>973</v>
       </c>
       <c r="D709" t="s">
-        <v>967</v>
+        <v>974</v>
       </c>
       <c r="E709" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
       <c r="F709" t="s">
         <v>713</v>
@@ -18457,10 +18457,10 @@
         <v>1022</v>
       </c>
       <c r="D710" t="s">
-        <v>967</v>
+        <v>1023</v>
       </c>
       <c r="E710" t="s">
-        <v>1023</v>
+        <v>968</v>
       </c>
       <c r="F710" t="s">
         <v>24</v>
@@ -18477,10 +18477,10 @@
         <v>973</v>
       </c>
       <c r="D711" t="s">
-        <v>967</v>
+        <v>1002</v>
       </c>
       <c r="E711" t="s">
-        <v>1002</v>
+        <v>968</v>
       </c>
       <c r="F711" t="s">
         <v>713</v>
@@ -18497,10 +18497,10 @@
         <v>973</v>
       </c>
       <c r="D712" t="s">
-        <v>967</v>
+        <v>974</v>
       </c>
       <c r="E712" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
       <c r="F712" t="s">
         <v>713</v>
@@ -18517,10 +18517,10 @@
         <v>982</v>
       </c>
       <c r="D713" t="s">
-        <v>967</v>
+        <v>983</v>
       </c>
       <c r="E713" t="s">
-        <v>983</v>
+        <v>968</v>
       </c>
       <c r="F713" t="s">
         <v>24</v>
@@ -18537,10 +18537,10 @@
         <v>973</v>
       </c>
       <c r="D714" t="s">
-        <v>967</v>
+        <v>974</v>
       </c>
       <c r="E714" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
       <c r="F714" t="s">
         <v>713</v>
@@ -18557,10 +18557,10 @@
         <v>998</v>
       </c>
       <c r="D715" t="s">
-        <v>967</v>
+        <v>1002</v>
       </c>
       <c r="E715" t="s">
-        <v>1002</v>
+        <v>968</v>
       </c>
       <c r="F715" t="s">
         <v>24</v>
@@ -18577,10 +18577,10 @@
         <v>973</v>
       </c>
       <c r="D716" t="s">
-        <v>967</v>
+        <v>974</v>
       </c>
       <c r="E716" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
       <c r="F716" t="s">
         <v>713</v>
@@ -18597,10 +18597,10 @@
         <v>973</v>
       </c>
       <c r="D717" t="s">
-        <v>967</v>
+        <v>974</v>
       </c>
       <c r="E717" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
       <c r="F717" t="s">
         <v>713</v>
@@ -18757,10 +18757,10 @@
         <v>1043</v>
       </c>
       <c r="D725" t="s">
-        <v>1033</v>
+        <v>1044</v>
       </c>
       <c r="E725" t="s">
-        <v>1044</v>
+        <v>1034</v>
       </c>
       <c r="F725" t="s">
         <v>16</v>
@@ -18777,10 +18777,10 @@
         <v>1046</v>
       </c>
       <c r="D726" t="s">
-        <v>1033</v>
+        <v>1047</v>
       </c>
       <c r="E726" t="s">
-        <v>1047</v>
+        <v>1034</v>
       </c>
       <c r="F726" t="s">
         <v>16</v>
@@ -18837,10 +18837,10 @@
         <v>1051</v>
       </c>
       <c r="D729" t="s">
-        <v>1033</v>
+        <v>1052</v>
       </c>
       <c r="E729" t="s">
-        <v>1052</v>
+        <v>1034</v>
       </c>
       <c r="F729" t="s">
         <v>24</v>
@@ -18877,10 +18877,10 @@
         <v>1051</v>
       </c>
       <c r="D731" t="s">
-        <v>1033</v>
+        <v>1052</v>
       </c>
       <c r="E731" t="s">
-        <v>1052</v>
+        <v>1034</v>
       </c>
       <c r="F731" t="s">
         <v>24</v>
@@ -18897,10 +18897,10 @@
         <v>1056</v>
       </c>
       <c r="D732" t="s">
-        <v>1033</v>
+        <v>1057</v>
       </c>
       <c r="E732" t="s">
-        <v>1057</v>
+        <v>1034</v>
       </c>
       <c r="F732" t="s">
         <v>24</v>
@@ -18937,10 +18937,10 @@
         <v>1061</v>
       </c>
       <c r="D734" t="s">
-        <v>1033</v>
+        <v>1062</v>
       </c>
       <c r="E734" t="s">
-        <v>1062</v>
+        <v>1034</v>
       </c>
       <c r="F734" t="s">
         <v>24</v>
@@ -19017,10 +19017,10 @@
         <v>1068</v>
       </c>
       <c r="D738" t="s">
-        <v>1033</v>
+        <v>974</v>
       </c>
       <c r="E738" t="s">
-        <v>974</v>
+        <v>1034</v>
       </c>
       <c r="F738" t="s">
         <v>16</v>
@@ -19077,10 +19077,10 @@
         <v>1072</v>
       </c>
       <c r="D741" t="s">
-        <v>1033</v>
+        <v>1073</v>
       </c>
       <c r="E741" t="s">
-        <v>1073</v>
+        <v>1034</v>
       </c>
       <c r="F741" t="s">
         <v>24</v>
@@ -19277,10 +19277,10 @@
         <v>1089</v>
       </c>
       <c r="D751" t="s">
-        <v>1086</v>
+        <v>1090</v>
       </c>
       <c r="E751" t="s">
-        <v>1090</v>
+        <v>1087</v>
       </c>
       <c r="F751" t="s">
         <v>24</v>
@@ -19297,10 +19297,10 @@
         <v>1092</v>
       </c>
       <c r="D752" t="s">
-        <v>1086</v>
+        <v>1093</v>
       </c>
       <c r="E752" t="s">
-        <v>1093</v>
+        <v>1087</v>
       </c>
       <c r="F752" t="s">
         <v>713</v>
@@ -19317,10 +19317,10 @@
         <v>1092</v>
       </c>
       <c r="D753" t="s">
-        <v>1086</v>
+        <v>1093</v>
       </c>
       <c r="E753" t="s">
-        <v>1093</v>
+        <v>1087</v>
       </c>
       <c r="F753" t="s">
         <v>713</v>
@@ -19337,10 +19337,10 @@
         <v>1092</v>
       </c>
       <c r="D754" t="s">
-        <v>1086</v>
+        <v>1093</v>
       </c>
       <c r="E754" t="s">
-        <v>1093</v>
+        <v>1087</v>
       </c>
       <c r="F754" t="s">
         <v>713</v>
@@ -19357,10 +19357,10 @@
         <v>1092</v>
       </c>
       <c r="D755" t="s">
-        <v>1086</v>
+        <v>1093</v>
       </c>
       <c r="E755" t="s">
-        <v>1093</v>
+        <v>1087</v>
       </c>
       <c r="F755" t="s">
         <v>713</v>
@@ -19377,10 +19377,10 @@
         <v>1092</v>
       </c>
       <c r="D756" t="s">
-        <v>1086</v>
+        <v>1093</v>
       </c>
       <c r="E756" t="s">
-        <v>1093</v>
+        <v>1087</v>
       </c>
       <c r="F756" t="s">
         <v>713</v>
@@ -19397,10 +19397,10 @@
         <v>1092</v>
       </c>
       <c r="D757" t="s">
-        <v>1086</v>
+        <v>1093</v>
       </c>
       <c r="E757" t="s">
-        <v>1093</v>
+        <v>1087</v>
       </c>
       <c r="F757" t="s">
         <v>713</v>
@@ -19417,10 +19417,10 @@
         <v>1085</v>
       </c>
       <c r="D758" t="s">
-        <v>1086</v>
+        <v>1090</v>
       </c>
       <c r="E758" t="s">
-        <v>1090</v>
+        <v>1087</v>
       </c>
       <c r="F758" t="s">
         <v>24</v>
@@ -19437,10 +19437,10 @@
         <v>1065</v>
       </c>
       <c r="D759" t="s">
-        <v>1086</v>
+        <v>1093</v>
       </c>
       <c r="E759" t="s">
-        <v>1093</v>
+        <v>1087</v>
       </c>
       <c r="F759" t="s">
         <v>16</v>
@@ -19457,10 +19457,10 @@
         <v>1092</v>
       </c>
       <c r="D760" t="s">
-        <v>1086</v>
+        <v>1093</v>
       </c>
       <c r="E760" t="s">
-        <v>1093</v>
+        <v>1087</v>
       </c>
       <c r="F760" t="s">
         <v>713</v>
@@ -19477,10 +19477,10 @@
         <v>1092</v>
       </c>
       <c r="D761" t="s">
-        <v>1086</v>
+        <v>1093</v>
       </c>
       <c r="E761" t="s">
-        <v>1093</v>
+        <v>1087</v>
       </c>
       <c r="F761" t="s">
         <v>713</v>
@@ -19497,10 +19497,10 @@
         <v>1065</v>
       </c>
       <c r="D762" t="s">
-        <v>1086</v>
+        <v>1104</v>
       </c>
       <c r="E762" t="s">
-        <v>1104</v>
+        <v>1087</v>
       </c>
       <c r="F762" t="s">
         <v>24</v>
@@ -19517,10 +19517,10 @@
         <v>1092</v>
       </c>
       <c r="D763" t="s">
-        <v>1086</v>
+        <v>1093</v>
       </c>
       <c r="E763" t="s">
-        <v>1093</v>
+        <v>1087</v>
       </c>
       <c r="F763" t="s">
         <v>713</v>
@@ -19537,10 +19537,10 @@
         <v>1107</v>
       </c>
       <c r="D764" t="s">
-        <v>1086</v>
+        <v>1108</v>
       </c>
       <c r="E764" t="s">
-        <v>1108</v>
+        <v>1087</v>
       </c>
       <c r="F764" t="s">
         <v>24</v>
@@ -19577,10 +19577,10 @@
         <v>1111</v>
       </c>
       <c r="D766" t="s">
-        <v>1086</v>
+        <v>1104</v>
       </c>
       <c r="E766" t="s">
-        <v>1104</v>
+        <v>1087</v>
       </c>
       <c r="F766" t="s">
         <v>24</v>
@@ -19597,10 +19597,10 @@
         <v>1113</v>
       </c>
       <c r="D767" t="s">
-        <v>1086</v>
+        <v>1114</v>
       </c>
       <c r="E767" t="s">
-        <v>1114</v>
+        <v>1087</v>
       </c>
       <c r="F767" t="s">
         <v>24</v>
@@ -19617,10 +19617,10 @@
         <v>1092</v>
       </c>
       <c r="D768" t="s">
-        <v>1086</v>
+        <v>1093</v>
       </c>
       <c r="E768" t="s">
-        <v>1093</v>
+        <v>1087</v>
       </c>
       <c r="F768" t="s">
         <v>713</v>
@@ -19637,10 +19637,10 @@
         <v>1092</v>
       </c>
       <c r="D769" t="s">
-        <v>1086</v>
+        <v>1093</v>
       </c>
       <c r="E769" t="s">
-        <v>1093</v>
+        <v>1087</v>
       </c>
       <c r="F769" t="s">
         <v>713</v>
@@ -19657,10 +19657,10 @@
         <v>1118</v>
       </c>
       <c r="D770" t="s">
-        <v>1086</v>
+        <v>1119</v>
       </c>
       <c r="E770" t="s">
-        <v>1119</v>
+        <v>1087</v>
       </c>
       <c r="F770" t="s">
         <v>24</v>
@@ -19677,10 +19677,10 @@
         <v>1092</v>
       </c>
       <c r="D771" t="s">
-        <v>1086</v>
+        <v>1093</v>
       </c>
       <c r="E771" t="s">
-        <v>1093</v>
+        <v>1087</v>
       </c>
       <c r="F771" t="s">
         <v>713</v>
@@ -19697,10 +19697,10 @@
         <v>1092</v>
       </c>
       <c r="D772" t="s">
-        <v>1086</v>
+        <v>1093</v>
       </c>
       <c r="E772" t="s">
-        <v>1093</v>
+        <v>1087</v>
       </c>
       <c r="F772" t="s">
         <v>713</v>
@@ -19717,10 +19717,10 @@
         <v>1092</v>
       </c>
       <c r="D773" t="s">
-        <v>1086</v>
+        <v>1093</v>
       </c>
       <c r="E773" t="s">
-        <v>1093</v>
+        <v>1087</v>
       </c>
       <c r="F773" t="s">
         <v>713</v>
@@ -19737,10 +19737,10 @@
         <v>1124</v>
       </c>
       <c r="D774" t="s">
-        <v>1086</v>
+        <v>1125</v>
       </c>
       <c r="E774" t="s">
-        <v>1125</v>
+        <v>1087</v>
       </c>
       <c r="F774" t="s">
         <v>24</v>
@@ -19757,10 +19757,10 @@
         <v>1092</v>
       </c>
       <c r="D775" t="s">
-        <v>1086</v>
+        <v>1093</v>
       </c>
       <c r="E775" t="s">
-        <v>1093</v>
+        <v>1087</v>
       </c>
       <c r="F775" t="s">
         <v>713</v>
@@ -19817,10 +19817,10 @@
         <v>1134</v>
       </c>
       <c r="D778" t="s">
-        <v>1129</v>
+        <v>1135</v>
       </c>
       <c r="E778" t="s">
-        <v>1135</v>
+        <v>1130</v>
       </c>
       <c r="F778" t="s">
         <v>24</v>
@@ -19837,10 +19837,10 @@
         <v>1137</v>
       </c>
       <c r="D779" t="s">
-        <v>1129</v>
+        <v>1138</v>
       </c>
       <c r="E779" t="s">
-        <v>1138</v>
+        <v>1130</v>
       </c>
       <c r="F779" t="s">
         <v>24</v>
@@ -20037,10 +20037,10 @@
         <v>1128</v>
       </c>
       <c r="D789" t="s">
-        <v>1129</v>
+        <v>1150</v>
       </c>
       <c r="E789" t="s">
-        <v>1150</v>
+        <v>1130</v>
       </c>
       <c r="F789" t="s">
         <v>24</v>
@@ -20077,10 +20077,10 @@
         <v>1142</v>
       </c>
       <c r="D791" t="s">
-        <v>1129</v>
+        <v>1153</v>
       </c>
       <c r="E791" t="s">
-        <v>1153</v>
+        <v>1130</v>
       </c>
       <c r="F791" t="s">
         <v>24</v>
@@ -20097,10 +20097,10 @@
         <v>1155</v>
       </c>
       <c r="D792" t="s">
-        <v>1129</v>
+        <v>1150</v>
       </c>
       <c r="E792" t="s">
-        <v>1150</v>
+        <v>1130</v>
       </c>
       <c r="F792" t="s">
         <v>24</v>
@@ -20137,10 +20137,10 @@
         <v>1132</v>
       </c>
       <c r="D794" t="s">
-        <v>1129</v>
+        <v>1158</v>
       </c>
       <c r="E794" t="s">
-        <v>1158</v>
+        <v>1130</v>
       </c>
       <c r="F794" t="s">
         <v>24</v>
@@ -20197,10 +20197,10 @@
         <v>1163</v>
       </c>
       <c r="D797" t="s">
-        <v>1129</v>
+        <v>1164</v>
       </c>
       <c r="E797" t="s">
-        <v>1164</v>
+        <v>1130</v>
       </c>
       <c r="F797" t="s">
         <v>24</v>
@@ -20217,10 +20217,10 @@
         <v>1166</v>
       </c>
       <c r="D798" t="s">
-        <v>1129</v>
+        <v>1167</v>
       </c>
       <c r="E798" t="s">
-        <v>1167</v>
+        <v>1130</v>
       </c>
       <c r="F798" t="s">
         <v>24</v>
@@ -20477,10 +20477,10 @@
         <v>1185</v>
       </c>
       <c r="D811" t="s">
-        <v>1179</v>
+        <v>1186</v>
       </c>
       <c r="E811" t="s">
-        <v>1186</v>
+        <v>1180</v>
       </c>
       <c r="F811" t="s">
         <v>24</v>
@@ -20557,10 +20557,10 @@
         <v>1191</v>
       </c>
       <c r="D815" t="s">
-        <v>1179</v>
+        <v>1192</v>
       </c>
       <c r="E815" t="s">
-        <v>1192</v>
+        <v>1180</v>
       </c>
       <c r="F815" t="s">
         <v>24</v>
@@ -20677,10 +20677,10 @@
         <v>1199</v>
       </c>
       <c r="D821" t="s">
-        <v>1179</v>
+        <v>1200</v>
       </c>
       <c r="E821" t="s">
-        <v>1200</v>
+        <v>1180</v>
       </c>
       <c r="F821" t="s">
         <v>16</v>
@@ -20697,10 +20697,10 @@
         <v>1202</v>
       </c>
       <c r="D822" t="s">
-        <v>1179</v>
+        <v>1203</v>
       </c>
       <c r="E822" t="s">
-        <v>1203</v>
+        <v>1180</v>
       </c>
       <c r="F822" t="s">
         <v>1182</v>
@@ -20737,10 +20737,10 @@
         <v>1202</v>
       </c>
       <c r="D824" t="s">
-        <v>1179</v>
+        <v>1203</v>
       </c>
       <c r="E824" t="s">
-        <v>1203</v>
+        <v>1180</v>
       </c>
       <c r="F824" t="s">
         <v>1182</v>
@@ -20757,10 +20757,10 @@
         <v>1202</v>
       </c>
       <c r="D825" t="s">
-        <v>1179</v>
+        <v>1203</v>
       </c>
       <c r="E825" t="s">
-        <v>1203</v>
+        <v>1180</v>
       </c>
       <c r="F825" t="s">
         <v>713</v>
@@ -20777,10 +20777,10 @@
         <v>1202</v>
       </c>
       <c r="D826" t="s">
-        <v>1179</v>
+        <v>1203</v>
       </c>
       <c r="E826" t="s">
-        <v>1203</v>
+        <v>1180</v>
       </c>
       <c r="F826" t="s">
         <v>1182</v>
@@ -20797,10 +20797,10 @@
         <v>1202</v>
       </c>
       <c r="D827" t="s">
-        <v>1179</v>
+        <v>1203</v>
       </c>
       <c r="E827" t="s">
-        <v>1203</v>
+        <v>1180</v>
       </c>
       <c r="F827" t="s">
         <v>1182</v>
@@ -21197,10 +21197,10 @@
         <v>1233</v>
       </c>
       <c r="D847" t="s">
-        <v>1222</v>
+        <v>1186</v>
       </c>
       <c r="E847" t="s">
-        <v>1186</v>
+        <v>1223</v>
       </c>
       <c r="F847" t="s">
         <v>1182</v>
@@ -21217,10 +21217,10 @@
         <v>1233</v>
       </c>
       <c r="D848" t="s">
-        <v>1222</v>
+        <v>1186</v>
       </c>
       <c r="E848" t="s">
-        <v>1186</v>
+        <v>1223</v>
       </c>
       <c r="F848" t="s">
         <v>1182</v>
@@ -21237,10 +21237,10 @@
         <v>1233</v>
       </c>
       <c r="D849" t="s">
-        <v>1222</v>
+        <v>1186</v>
       </c>
       <c r="E849" t="s">
-        <v>1186</v>
+        <v>1223</v>
       </c>
       <c r="F849" t="s">
         <v>713</v>
@@ -21257,10 +21257,10 @@
         <v>1233</v>
       </c>
       <c r="D850" t="s">
-        <v>1222</v>
+        <v>1237</v>
       </c>
       <c r="E850" t="s">
-        <v>1237</v>
+        <v>1223</v>
       </c>
       <c r="F850" t="s">
         <v>1182</v>
@@ -21277,10 +21277,10 @@
         <v>1233</v>
       </c>
       <c r="D851" t="s">
-        <v>1222</v>
+        <v>1186</v>
       </c>
       <c r="E851" t="s">
-        <v>1186</v>
+        <v>1223</v>
       </c>
       <c r="F851" t="s">
         <v>1182</v>
@@ -21297,10 +21297,10 @@
         <v>1233</v>
       </c>
       <c r="D852" t="s">
-        <v>1222</v>
+        <v>1186</v>
       </c>
       <c r="E852" t="s">
-        <v>1186</v>
+        <v>1223</v>
       </c>
       <c r="F852" t="s">
         <v>1182</v>
@@ -21617,10 +21617,10 @@
         <v>1255</v>
       </c>
       <c r="D868" t="s">
-        <v>1256</v>
+        <v>1259</v>
       </c>
       <c r="E868" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
       <c r="F868" t="s">
         <v>1182</v>
@@ -21637,10 +21637,10 @@
         <v>1255</v>
       </c>
       <c r="D869" t="s">
-        <v>1256</v>
+        <v>1259</v>
       </c>
       <c r="E869" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
       <c r="F869" t="s">
         <v>1182</v>
@@ -21657,10 +21657,10 @@
         <v>1255</v>
       </c>
       <c r="D870" t="s">
-        <v>1256</v>
+        <v>1259</v>
       </c>
       <c r="E870" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
       <c r="F870" t="s">
         <v>1182</v>
@@ -21677,10 +21677,10 @@
         <v>1255</v>
       </c>
       <c r="D871" t="s">
-        <v>1256</v>
+        <v>1259</v>
       </c>
       <c r="E871" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
       <c r="F871" t="s">
         <v>1182</v>
@@ -21697,10 +21697,10 @@
         <v>1255</v>
       </c>
       <c r="D872" t="s">
-        <v>1256</v>
+        <v>1259</v>
       </c>
       <c r="E872" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
       <c r="F872" t="s">
         <v>16</v>
@@ -21717,10 +21717,10 @@
         <v>1255</v>
       </c>
       <c r="D873" t="s">
-        <v>1256</v>
+        <v>1259</v>
       </c>
       <c r="E873" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
       <c r="F873" t="s">
         <v>16</v>
@@ -21737,10 +21737,10 @@
         <v>1255</v>
       </c>
       <c r="D874" t="s">
-        <v>1256</v>
+        <v>1259</v>
       </c>
       <c r="E874" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
       <c r="F874" t="s">
         <v>1182</v>
@@ -21757,10 +21757,10 @@
         <v>1255</v>
       </c>
       <c r="D875" t="s">
-        <v>1256</v>
+        <v>1259</v>
       </c>
       <c r="E875" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
       <c r="F875" t="s">
         <v>1182</v>
@@ -21777,10 +21777,10 @@
         <v>1255</v>
       </c>
       <c r="D876" t="s">
-        <v>1256</v>
+        <v>1259</v>
       </c>
       <c r="E876" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
       <c r="F876" t="s">
         <v>713</v>
@@ -21797,10 +21797,10 @@
         <v>1255</v>
       </c>
       <c r="D877" t="s">
-        <v>1256</v>
+        <v>1259</v>
       </c>
       <c r="E877" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
       <c r="F877" t="s">
         <v>16</v>
@@ -21817,10 +21817,10 @@
         <v>1255</v>
       </c>
       <c r="D878" t="s">
-        <v>1256</v>
+        <v>1259</v>
       </c>
       <c r="E878" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
       <c r="F878" t="s">
         <v>1182</v>
@@ -21837,10 +21837,10 @@
         <v>1255</v>
       </c>
       <c r="D879" t="s">
-        <v>1256</v>
+        <v>1259</v>
       </c>
       <c r="E879" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
       <c r="F879" t="s">
         <v>1182</v>
@@ -21857,10 +21857,10 @@
         <v>1255</v>
       </c>
       <c r="D880" t="s">
-        <v>1256</v>
+        <v>1259</v>
       </c>
       <c r="E880" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
       <c r="F880" t="s">
         <v>1182</v>
@@ -21877,10 +21877,10 @@
         <v>1255</v>
       </c>
       <c r="D881" t="s">
-        <v>1256</v>
+        <v>1259</v>
       </c>
       <c r="E881" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
       <c r="F881" t="s">
         <v>1182</v>
@@ -21897,10 +21897,10 @@
         <v>1255</v>
       </c>
       <c r="D882" t="s">
-        <v>1256</v>
+        <v>1259</v>
       </c>
       <c r="E882" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
       <c r="F882" t="s">
         <v>1182</v>
@@ -21917,10 +21917,10 @@
         <v>1255</v>
       </c>
       <c r="D883" t="s">
-        <v>1256</v>
+        <v>1259</v>
       </c>
       <c r="E883" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
       <c r="F883" t="s">
         <v>713</v>
@@ -21937,10 +21937,10 @@
         <v>1255</v>
       </c>
       <c r="D884" t="s">
-        <v>1256</v>
+        <v>1259</v>
       </c>
       <c r="E884" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
       <c r="F884" t="s">
         <v>1182</v>
@@ -21957,10 +21957,10 @@
         <v>1255</v>
       </c>
       <c r="D885" t="s">
-        <v>1256</v>
+        <v>1259</v>
       </c>
       <c r="E885" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
       <c r="F885" t="s">
         <v>1182</v>
@@ -21977,10 +21977,10 @@
         <v>1255</v>
       </c>
       <c r="D886" t="s">
-        <v>1256</v>
+        <v>1259</v>
       </c>
       <c r="E886" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
       <c r="F886" t="s">
         <v>1182</v>
@@ -21997,10 +21997,10 @@
         <v>1255</v>
       </c>
       <c r="D887" t="s">
-        <v>1256</v>
+        <v>1259</v>
       </c>
       <c r="E887" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
       <c r="F887" t="s">
         <v>16</v>
@@ -22017,10 +22017,10 @@
         <v>1255</v>
       </c>
       <c r="D888" t="s">
-        <v>1256</v>
+        <v>1259</v>
       </c>
       <c r="E888" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
       <c r="F888" t="s">
         <v>1182</v>
@@ -22037,10 +22037,10 @@
         <v>1255</v>
       </c>
       <c r="D889" t="s">
-        <v>1256</v>
+        <v>1259</v>
       </c>
       <c r="E889" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
       <c r="F889" t="s">
         <v>713</v>
@@ -22357,10 +22357,10 @@
         <v>1301</v>
       </c>
       <c r="D905" t="s">
+        <v>1283</v>
+      </c>
+      <c r="E905" t="s">
         <v>1302</v>
-      </c>
-      <c r="E905" t="s">
-        <v>1284</v>
       </c>
       <c r="F905" t="s">
         <v>1182</v>
@@ -22377,10 +22377,10 @@
         <v>1304</v>
       </c>
       <c r="D906" t="s">
+        <v>1283</v>
+      </c>
+      <c r="E906" t="s">
         <v>1302</v>
-      </c>
-      <c r="E906" t="s">
-        <v>1284</v>
       </c>
       <c r="F906" t="s">
         <v>1182</v>
@@ -22397,10 +22397,10 @@
         <v>1301</v>
       </c>
       <c r="D907" t="s">
+        <v>1283</v>
+      </c>
+      <c r="E907" t="s">
         <v>1302</v>
-      </c>
-      <c r="E907" t="s">
-        <v>1284</v>
       </c>
       <c r="F907" t="s">
         <v>1182</v>

--- a/api/1/clv3/xlsx/fr/HumanitarianPlan.xlsx
+++ b/api/1/clv3/xlsx/fr/HumanitarianPlan.xlsx
@@ -22,15 +22,15 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:plan-year</t>
+  </si>
+  <si>
+    <t>codeforiati:plan-end-date</t>
+  </si>
+  <si>
     <t>codeforiati:plan-start-date</t>
   </si>
   <si>
-    <t>codeforiati:plan-end-date</t>
-  </si>
-  <si>
-    <t>codeforiati:plan-year</t>
-  </si>
-  <si>
     <t>codeforiati:plan-type</t>
   </si>
   <si>
@@ -40,15 +40,15 @@
     <t>active</t>
   </si>
   <si>
+    <t>2025</t>
+  </si>
+  <si>
+    <t>2025-12-31</t>
+  </si>
+  <si>
     <t>2025-01-01</t>
   </si>
   <si>
-    <t>2025-12-31</t>
-  </si>
-  <si>
-    <t>2025</t>
-  </si>
-  <si>
     <t>Humanitarian needs and response plan</t>
   </si>
   <si>
@@ -217,15 +217,15 @@
     <t>HAFG24</t>
   </si>
   <si>
+    <t>2024</t>
+  </si>
+  <si>
+    <t>2024-12-31</t>
+  </si>
+  <si>
     <t>2024-01-01</t>
   </si>
   <si>
-    <t>2024-12-31</t>
-  </si>
-  <si>
-    <t>2024</t>
-  </si>
-  <si>
     <t>RAFG_RRP24</t>
   </si>
   <si>
@@ -421,15 +421,15 @@
     <t>HAFG23</t>
   </si>
   <si>
+    <t>2023</t>
+  </si>
+  <si>
+    <t>2023-12-31</t>
+  </si>
+  <si>
     <t>2023-01-01</t>
   </si>
   <si>
-    <t>2023-12-31</t>
-  </si>
-  <si>
-    <t>2023</t>
-  </si>
-  <si>
     <t>RAFG23</t>
   </si>
   <si>
@@ -493,21 +493,21 @@
     <t>OMNG2223</t>
   </si>
   <si>
+    <t>2023-05-31</t>
+  </si>
+  <si>
     <t>2022-12-01</t>
   </si>
   <si>
-    <t>2023-05-31</t>
-  </si>
-  <si>
     <t>OMOZ23</t>
   </si>
   <si>
+    <t>2023-09-30</t>
+  </si>
+  <si>
     <t>2023-03-01</t>
   </si>
   <si>
-    <t>2023-09-30</t>
-  </si>
-  <si>
     <t>HMOZ23</t>
   </si>
   <si>
@@ -553,12 +553,12 @@
     <t>RRSDN23</t>
   </si>
   <si>
+    <t>2023-10-31</t>
+  </si>
+  <si>
     <t>2023-05-01</t>
   </si>
   <si>
-    <t>2023-10-31</t>
-  </si>
-  <si>
     <t>HSDN23</t>
   </si>
   <si>
@@ -601,15 +601,15 @@
     <t>HAFG22</t>
   </si>
   <si>
+    <t>2022</t>
+  </si>
+  <si>
+    <t>2022-12-31</t>
+  </si>
+  <si>
     <t>2022-01-01</t>
   </si>
   <si>
-    <t>2022-12-31</t>
-  </si>
-  <si>
-    <t>2022</t>
-  </si>
-  <si>
     <t>RAFG22</t>
   </si>
   <si>
@@ -631,12 +631,12 @@
     <t>OCUB2223</t>
   </si>
   <si>
+    <t>2023-03-31</t>
+  </si>
+  <si>
     <t>2022-10-20</t>
   </si>
   <si>
-    <t>2023-03-31</t>
-  </si>
-  <si>
     <t>RDRCRRP22</t>
   </si>
   <si>
@@ -652,12 +652,12 @@
     <t>FHTI2223</t>
   </si>
   <si>
+    <t>2023-04-15</t>
+  </si>
+  <si>
     <t>2022-10-16</t>
   </si>
   <si>
-    <t>2023-04-15</t>
-  </si>
-  <si>
     <t>FHTI22</t>
   </si>
   <si>
@@ -688,24 +688,24 @@
     <t>FMWI22</t>
   </si>
   <si>
+    <t>2022-05-31</t>
+  </si>
+  <si>
     <t>2022-02-26</t>
   </si>
   <si>
-    <t>2022-05-31</t>
-  </si>
-  <si>
     <t>HMLI22</t>
   </si>
   <si>
     <t>FMOZ22</t>
   </si>
   <si>
+    <t>2022-09-30</t>
+  </si>
+  <si>
     <t>2022-04-01</t>
   </si>
   <si>
-    <t>2022-09-30</t>
-  </si>
-  <si>
     <t>HMOZ22</t>
   </si>
   <si>
@@ -736,12 +736,12 @@
     <t>OPHL2122</t>
   </si>
   <si>
+    <t>2022-06-30</t>
+  </si>
+  <si>
     <t>2021-12-24</t>
   </si>
   <si>
-    <t>2022-06-30</t>
-  </si>
-  <si>
     <t>RREG22</t>
   </si>
   <si>
@@ -805,15 +805,15 @@
     <t>FAFG21</t>
   </si>
   <si>
+    <t>2021</t>
+  </si>
+  <si>
+    <t>2021-12-31</t>
+  </si>
+  <si>
     <t>2021-09-01</t>
   </si>
   <si>
-    <t>2021-12-31</t>
-  </si>
-  <si>
-    <t>2021</t>
-  </si>
-  <si>
     <t>HAFG21</t>
   </si>
   <si>
@@ -862,12 +862,12 @@
     <t>FPSE21</t>
   </si>
   <si>
+    <t>2021-08-27</t>
+  </si>
+  <si>
     <t>2021-05-27</t>
   </si>
   <si>
-    <t>2021-08-27</t>
-  </si>
-  <si>
     <t>HETH21</t>
   </si>
   <si>
@@ -880,24 +880,24 @@
     <t>FHTI2122</t>
   </si>
   <si>
+    <t>2022-02-15</t>
+  </si>
+  <si>
     <t>2021-08-16</t>
   </si>
   <si>
-    <t>2022-02-15</t>
-  </si>
-  <si>
     <t>HHTI21</t>
   </si>
   <si>
     <t>FHND2021</t>
   </si>
   <si>
+    <t>2021-06-30</t>
+  </si>
+  <si>
     <t>2020-11-15</t>
   </si>
   <si>
-    <t>2021-06-30</t>
-  </si>
-  <si>
     <t>HHND21</t>
   </si>
   <si>
@@ -916,12 +916,12 @@
     <t>OLBN2122</t>
   </si>
   <si>
+    <t>2022-07-31</t>
+  </si>
+  <si>
     <t>2021-08-03</t>
   </si>
   <si>
-    <t>2022-07-31</t>
-  </si>
-  <si>
     <t>HLBY21</t>
   </si>
   <si>
@@ -1009,15 +1009,15 @@
     <t>HAFG20</t>
   </si>
   <si>
+    <t>2020</t>
+  </si>
+  <si>
+    <t>2020-12-31</t>
+  </si>
+  <si>
     <t>2020-01-01</t>
   </si>
   <si>
-    <t>2020-12-31</t>
-  </si>
-  <si>
-    <t>2020</t>
-  </si>
-  <si>
     <t>OBGD20</t>
   </si>
   <si>
@@ -1081,12 +1081,12 @@
     <t>FDJI1920</t>
   </si>
   <si>
+    <t>2020-03-31</t>
+  </si>
+  <si>
     <t>2019-12-17</t>
   </si>
   <si>
-    <t>2020-03-31</t>
-  </si>
-  <si>
     <t>ODJI20</t>
   </si>
   <si>
@@ -1135,24 +1135,24 @@
     <t>FLBN20</t>
   </si>
   <si>
+    <t>2020-11-13</t>
+  </si>
+  <si>
     <t>2020-08-05</t>
   </si>
   <si>
-    <t>2020-11-13</t>
-  </si>
-  <si>
     <t>OLBN20</t>
   </si>
   <si>
     <t>FLSO1920</t>
   </si>
   <si>
+    <t>2020-04-30</t>
+  </si>
+  <si>
     <t>2019-11-01</t>
   </si>
   <si>
-    <t>2020-04-30</t>
-  </si>
-  <si>
     <t>OLBR20</t>
   </si>
   <si>
@@ -1249,15 +1249,15 @@
     <t>HAFG19</t>
   </si>
   <si>
+    <t>2019</t>
+  </si>
+  <si>
+    <t>2019-12-31</t>
+  </si>
+  <si>
     <t>2019-01-01</t>
   </si>
   <si>
-    <t>2019-12-31</t>
-  </si>
-  <si>
-    <t>2019</t>
-  </si>
-  <si>
     <t>RBGD19</t>
   </si>
   <si>
@@ -1366,12 +1366,12 @@
     <t>FZWE1920</t>
   </si>
   <si>
+    <t>2020-04-29</t>
+  </si>
+  <si>
     <t>2019-02-01</t>
   </si>
   <si>
-    <t>2020-04-29</t>
-  </si>
-  <si>
     <t>FZWE1820</t>
   </si>
   <si>
@@ -1381,15 +1381,15 @@
     <t>HAFG18</t>
   </si>
   <si>
+    <t>2018</t>
+  </si>
+  <si>
+    <t>2018-12-31</t>
+  </si>
+  <si>
     <t>2018-01-01</t>
   </si>
   <si>
-    <t>2018-12-31</t>
-  </si>
-  <si>
-    <t>2018</t>
-  </si>
-  <si>
     <t>OBGD18</t>
   </si>
   <si>
@@ -1483,12 +1483,12 @@
     <t>HSYR18</t>
   </si>
   <si>
+    <t>2018-12-30</t>
+  </si>
+  <si>
     <t>2018-11-30</t>
   </si>
   <si>
-    <t>2018-12-30</t>
-  </si>
-  <si>
     <t>RSYR18</t>
   </si>
   <si>
@@ -1507,15 +1507,15 @@
     <t>OEUR17</t>
   </si>
   <si>
+    <t>2017</t>
+  </si>
+  <si>
+    <t>2017-12-31</t>
+  </si>
+  <si>
     <t>2017-01-01</t>
   </si>
   <si>
-    <t>2017-12-31</t>
-  </si>
-  <si>
-    <t>2017</t>
-  </si>
-  <si>
     <t>HAFG17</t>
   </si>
   <si>
@@ -1558,12 +1558,12 @@
     <t>FDMA17</t>
   </si>
   <si>
+    <t>2017-12-29</t>
+  </si>
+  <si>
     <t>2017-09-28</t>
   </si>
   <si>
-    <t>2017-12-29</t>
-  </si>
-  <si>
     <t>OPRK17</t>
   </si>
   <si>
@@ -1585,24 +1585,24 @@
     <t>FKEN17</t>
   </si>
   <si>
+    <t>2017-11-30</t>
+  </si>
+  <si>
     <t>2017-02-10</t>
   </si>
   <si>
-    <t>2017-11-30</t>
-  </si>
-  <si>
     <t>HLBY17</t>
   </si>
   <si>
     <t>FMDG17</t>
   </si>
   <si>
+    <t>2017-06-20</t>
+  </si>
+  <si>
     <t>2017-03-20</t>
   </si>
   <si>
-    <t>2017-06-20</t>
-  </si>
-  <si>
     <t>HMLI17</t>
   </si>
   <si>
@@ -1612,12 +1612,12 @@
     <t>FMOZ17</t>
   </si>
   <si>
+    <t>2017-05-31</t>
+  </si>
+  <si>
     <t>2017-02-28</t>
   </si>
   <si>
-    <t>2017-05-31</t>
-  </si>
-  <si>
     <t>HMMR17</t>
   </si>
   <si>
@@ -1636,12 +1636,12 @@
     <t>FPER17</t>
   </si>
   <si>
+    <t>2017-10-31</t>
+  </si>
+  <si>
     <t>2017-04-01</t>
   </si>
   <si>
-    <t>2017-10-31</t>
-  </si>
-  <si>
     <t>HCOG17</t>
   </si>
   <si>
@@ -1678,15 +1678,15 @@
     <t>OEUR16</t>
   </si>
   <si>
+    <t>2016</t>
+  </si>
+  <si>
+    <t>2016-12-31</t>
+  </si>
+  <si>
     <t>2016-01-01</t>
   </si>
   <si>
-    <t>2016-12-31</t>
-  </si>
-  <si>
-    <t>2016</t>
-  </si>
-  <si>
     <t>HAFG16</t>
   </si>
   <si>
@@ -1726,21 +1726,21 @@
     <t>FECU16</t>
   </si>
   <si>
+    <t>2016-10-31</t>
+  </si>
+  <si>
     <t>2016-04-16</t>
   </si>
   <si>
-    <t>2016-10-31</t>
-  </si>
-  <si>
     <t>FFJI16</t>
   </si>
   <si>
+    <t>2016-05-30</t>
+  </si>
+  <si>
     <t>2016-02-20</t>
   </si>
   <si>
-    <t>2016-05-30</t>
-  </si>
-  <si>
     <t>HGMB16</t>
   </si>
   <si>
@@ -1783,12 +1783,12 @@
     <t>FIRQ16</t>
   </si>
   <si>
+    <t>2016-10-01</t>
+  </si>
+  <si>
     <t>2016-07-20</t>
   </si>
   <si>
-    <t>2016-10-01</t>
-  </si>
-  <si>
     <t>HMMR16</t>
   </si>
   <si>
@@ -1831,24 +1831,24 @@
     <t>HZWE1617</t>
   </si>
   <si>
+    <t>2017-03-31</t>
+  </si>
+  <si>
     <t>2016-04-01</t>
   </si>
   <si>
-    <t>2017-03-31</t>
-  </si>
-  <si>
     <t>HAFG15</t>
   </si>
   <si>
+    <t>2015</t>
+  </si>
+  <si>
+    <t>2015-12-31</t>
+  </si>
+  <si>
     <t>2015-01-01</t>
   </si>
   <si>
-    <t>2015-12-31</t>
-  </si>
-  <si>
-    <t>2015</t>
-  </si>
-  <si>
     <t>Strategic response plan</t>
   </si>
   <si>
@@ -1879,12 +1879,12 @@
     <t>FGTM1415</t>
   </si>
   <si>
+    <t>2015-09-30</t>
+  </si>
+  <si>
     <t>2014-11-03</t>
   </si>
   <si>
-    <t>2015-09-30</t>
-  </si>
-  <si>
     <t>FHTI15</t>
   </si>
   <si>
@@ -1900,24 +1900,24 @@
     <t>FVUT15</t>
   </si>
   <si>
+    <t>2015-10-31</t>
+  </si>
+  <si>
     <t>2015-03-24</t>
   </si>
   <si>
-    <t>2015-10-31</t>
-  </si>
-  <si>
     <t>HIRQ15</t>
   </si>
   <si>
     <t>HLBY1415</t>
   </si>
   <si>
+    <t>2015-05-31</t>
+  </si>
+  <si>
     <t>2014-10-01</t>
   </si>
   <si>
-    <t>2015-05-31</t>
-  </si>
-  <si>
     <t>HMLI15</t>
   </si>
   <si>
@@ -1975,15 +1975,15 @@
     <t>HAFG14</t>
   </si>
   <si>
+    <t>2014</t>
+  </si>
+  <si>
+    <t>2014-12-31</t>
+  </si>
+  <si>
     <t>2014-01-01</t>
   </si>
   <si>
-    <t>2014-12-31</t>
-  </si>
-  <si>
-    <t>2014</t>
-  </si>
-  <si>
     <t>HBFA1314</t>
   </si>
   <si>
@@ -2059,21 +2059,21 @@
     <t>FPHL1314</t>
   </si>
   <si>
+    <t>2014-04-22</t>
+  </si>
+  <si>
     <t>2013-10-22</t>
   </si>
   <si>
-    <t>2014-04-22</t>
-  </si>
-  <si>
     <t>SPHL1314</t>
   </si>
   <si>
+    <t>2014-11-07</t>
+  </si>
+  <si>
     <t>2013-11-08</t>
   </si>
   <si>
-    <t>2014-11-07</t>
-  </si>
-  <si>
     <t>HPHL1314</t>
   </si>
   <si>
@@ -2083,12 +2083,12 @@
     <t>HPHL1314a</t>
   </si>
   <si>
+    <t>2014-08-31</t>
+  </si>
+  <si>
     <t>2013-10-01</t>
   </si>
   <si>
-    <t>2014-08-31</t>
-  </si>
-  <si>
     <t>SCOD14</t>
   </si>
   <si>
@@ -2149,12 +2149,12 @@
     <t>CAFG13</t>
   </si>
   <si>
+    <t>2013</t>
+  </si>
+  <si>
     <t>2013-12-31</t>
   </si>
   <si>
-    <t>2013</t>
-  </si>
-  <si>
     <t>Consolidated appeals process</t>
   </si>
   <si>
@@ -2242,15 +2242,15 @@
     <t>CKEN12</t>
   </si>
   <si>
+    <t>2012</t>
+  </si>
+  <si>
+    <t>2012-12-31</t>
+  </si>
+  <si>
     <t>2012-01-01</t>
   </si>
   <si>
-    <t>2012-12-31</t>
-  </si>
-  <si>
-    <t>2012</t>
-  </si>
-  <si>
     <t>CAFG1112</t>
   </si>
   <si>
@@ -2290,12 +2290,12 @@
     <t>FLSO1213</t>
   </si>
   <si>
+    <t>2013-03-25</t>
+  </si>
+  <si>
     <t>2012-09-18</t>
   </si>
   <si>
-    <t>2013-03-25</t>
-  </si>
-  <si>
     <t>CLBR12</t>
   </si>
   <si>
@@ -2335,12 +2335,12 @@
     <t>CSYR12</t>
   </si>
   <si>
+    <t>2012-12-05</t>
+  </si>
+  <si>
     <t>2012-06-05</t>
   </si>
   <si>
-    <t>2012-12-05</t>
-  </si>
-  <si>
     <t>CYEM12</t>
   </si>
   <si>
@@ -2353,12 +2353,12 @@
     <t>CKEN1113</t>
   </si>
   <si>
+    <t>2011</t>
+  </si>
+  <si>
     <t>2011-01-01</t>
   </si>
   <si>
-    <t>2011</t>
-  </si>
-  <si>
     <t>CAFG11</t>
   </si>
   <si>
@@ -2383,12 +2383,12 @@
     <t>FSLV1112</t>
   </si>
   <si>
+    <t>2012-04-25</t>
+  </si>
+  <si>
     <t>2011-10-25</t>
   </si>
   <si>
-    <t>2012-04-25</t>
-  </si>
-  <si>
     <t>CHTI1011</t>
   </si>
   <si>
@@ -2407,33 +2407,33 @@
     <t>FNAM11</t>
   </si>
   <si>
+    <t>2011-10-11</t>
+  </si>
+  <si>
     <t>2011-04-11</t>
   </si>
   <si>
-    <t>2011-10-11</t>
-  </si>
-  <si>
     <t>FNIC1112</t>
   </si>
   <si>
+    <t>2012-04-26</t>
+  </si>
+  <si>
     <t>2011-10-27</t>
   </si>
   <si>
-    <t>2012-04-26</t>
-  </si>
-  <si>
     <t>CNER11</t>
   </si>
   <si>
     <t>FPAK1112</t>
   </si>
   <si>
+    <t>2012-06-30</t>
+  </si>
+  <si>
     <t>2011-09-15</t>
   </si>
   <si>
-    <t>2012-06-30</t>
-  </si>
-  <si>
     <t>FXLBYREG11</t>
   </si>
   <si>
@@ -2476,24 +2476,24 @@
     <t>CAFG10</t>
   </si>
   <si>
+    <t>2010</t>
+  </si>
+  <si>
+    <t>2010-12-31</t>
+  </si>
+  <si>
     <t>2010-01-01</t>
   </si>
   <si>
-    <t>2010-12-31</t>
-  </si>
-  <si>
-    <t>2010</t>
-  </si>
-  <si>
     <t>OBFA1011</t>
   </si>
   <si>
+    <t>2011-01-31</t>
+  </si>
+  <si>
     <t>2010-08-01</t>
   </si>
   <si>
-    <t>2011-01-31</t>
-  </si>
-  <si>
     <t>CCAF10</t>
   </si>
   <si>
@@ -2506,30 +2506,30 @@
     <t>FSLV0910</t>
   </si>
   <si>
+    <t>2010-05-31</t>
+  </si>
+  <si>
     <t>2009-11-01</t>
   </si>
   <si>
-    <t>2010-05-31</t>
-  </si>
-  <si>
     <t>FGTM10</t>
   </si>
   <si>
+    <t>2010-12-09</t>
+  </si>
+  <si>
     <t>2010-06-10</t>
   </si>
   <si>
-    <t>2010-12-09</t>
-  </si>
-  <si>
     <t>CGTM10</t>
   </si>
   <si>
+    <t>2010-08-11</t>
+  </si>
+  <si>
     <t>2010-02-12</t>
   </si>
   <si>
-    <t>2010-08-11</t>
-  </si>
-  <si>
     <t>FHTI10</t>
   </si>
   <si>
@@ -2545,12 +2545,12 @@
     <t>FKGZ1011</t>
   </si>
   <si>
+    <t>2011-06-30</t>
+  </si>
+  <si>
     <t>2010-06-01</t>
   </si>
   <si>
-    <t>2011-06-30</t>
-  </si>
-  <si>
     <t>CMNG1011</t>
   </si>
   <si>
@@ -2608,24 +2608,24 @@
     <t>CAFG09</t>
   </si>
   <si>
+    <t>2009</t>
+  </si>
+  <si>
+    <t>2009-12-31</t>
+  </si>
+  <si>
     <t>2009-01-01</t>
   </si>
   <si>
-    <t>2009-12-31</t>
-  </si>
-  <si>
-    <t>2009</t>
-  </si>
-  <si>
     <t>FBFA0910</t>
   </si>
   <si>
+    <t>2010-03-09</t>
+  </si>
+  <si>
     <t>2009-09-10</t>
   </si>
   <si>
-    <t>2010-03-09</t>
-  </si>
-  <si>
     <t>CCAF09</t>
   </si>
   <si>
@@ -2662,21 +2662,21 @@
     <t>FMDG09</t>
   </si>
   <si>
+    <t>2009-10-31</t>
+  </si>
+  <si>
     <t>2009-04-01</t>
   </si>
   <si>
-    <t>2009-10-31</t>
-  </si>
-  <si>
     <t>FNAM09</t>
   </si>
   <si>
+    <t>2009-09-30</t>
+  </si>
+  <si>
     <t>2009-03-20</t>
   </si>
   <si>
-    <t>2009-09-30</t>
-  </si>
-  <si>
     <t>ONPL09</t>
   </si>
   <si>
@@ -2689,12 +2689,12 @@
     <t>FPHL0910</t>
   </si>
   <si>
+    <t>2010-03-31</t>
+  </si>
+  <si>
     <t>2009-10-03</t>
   </si>
   <si>
-    <t>2010-03-31</t>
-  </si>
-  <si>
     <t>CSOM09</t>
   </si>
   <si>
@@ -2707,12 +2707,12 @@
     <t>OSYR0910</t>
   </si>
   <si>
+    <t>2010-06-14</t>
+  </si>
+  <si>
     <t>2009-07-15</t>
   </si>
   <si>
-    <t>2010-06-14</t>
-  </si>
-  <si>
     <t>OTJK09</t>
   </si>
   <si>
@@ -2746,24 +2746,24 @@
     <t>OAFG08</t>
   </si>
   <si>
+    <t>2008</t>
+  </si>
+  <si>
+    <t>2008-06-30</t>
+  </si>
+  <si>
     <t>2008-02-01</t>
   </si>
   <si>
-    <t>2008-06-30</t>
-  </si>
-  <si>
-    <t>2008</t>
-  </si>
-  <si>
     <t>OAFG0809</t>
   </si>
   <si>
+    <t>2009-06-30</t>
+  </si>
+  <si>
     <t>2008-07-01</t>
   </si>
   <si>
-    <t>2009-06-30</t>
-  </si>
-  <si>
     <t>FBOL08</t>
   </si>
   <si>
@@ -2773,12 +2773,12 @@
     <t>CCAF08</t>
   </si>
   <si>
+    <t>2008-12-31</t>
+  </si>
+  <si>
     <t>2008-01-01</t>
   </si>
   <si>
-    <t>2008-12-31</t>
-  </si>
-  <si>
     <t>CTCD08</t>
   </si>
   <si>
@@ -2794,21 +2794,21 @@
     <t>ODJI0809</t>
   </si>
   <si>
+    <t>2009-02-28</t>
+  </si>
+  <si>
     <t>2008-08-01</t>
   </si>
   <si>
-    <t>2009-02-28</t>
-  </si>
-  <si>
     <t>FGEO0809</t>
   </si>
   <si>
+    <t>2009-02-09</t>
+  </si>
+  <si>
     <t>2008-08-09</t>
   </si>
   <si>
-    <t>2009-02-09</t>
-  </si>
-  <si>
     <t>FHTI0809</t>
   </si>
   <si>
@@ -2818,12 +2818,12 @@
     <t>FHND0809</t>
   </si>
   <si>
+    <t>2009-04-30</t>
+  </si>
+  <si>
     <t>2008-11-01</t>
   </si>
   <si>
-    <t>2009-04-30</t>
-  </si>
-  <si>
     <t>CIRQ08</t>
   </si>
   <si>
@@ -2833,12 +2833,12 @@
     <t>FKGZ0809</t>
   </si>
   <si>
+    <t>2009-05-31</t>
+  </si>
+  <si>
     <t>2008-12-01</t>
   </si>
   <si>
-    <t>2009-05-31</t>
-  </si>
-  <si>
     <t>OLAO0809</t>
   </si>
   <si>
@@ -2857,12 +2857,12 @@
     <t>FMMR08</t>
   </si>
   <si>
+    <t>2008-11-30</t>
+  </si>
+  <si>
     <t>2008-05-01</t>
   </si>
   <si>
-    <t>2008-11-30</t>
-  </si>
-  <si>
     <t>ONPL08</t>
   </si>
   <si>
@@ -2914,33 +2914,33 @@
     <t>FBOL07</t>
   </si>
   <si>
+    <t>2007</t>
+  </si>
+  <si>
+    <t>2007-08-21</t>
+  </si>
+  <si>
     <t>2007-02-22</t>
   </si>
   <si>
-    <t>2007-08-21</t>
-  </si>
-  <si>
-    <t>2007</t>
-  </si>
-  <si>
     <t>FBFA0708</t>
   </si>
   <si>
+    <t>2008-01-31</t>
+  </si>
+  <si>
     <t>2007-11-01</t>
   </si>
   <si>
-    <t>2008-01-31</t>
-  </si>
-  <si>
     <t>CBDI07</t>
   </si>
   <si>
+    <t>2007-12-31</t>
+  </si>
+  <si>
     <t>2007-01-01</t>
   </si>
   <si>
-    <t>2007-12-31</t>
-  </si>
-  <si>
     <t>CCAF07</t>
   </si>
   <si>
@@ -2962,12 +2962,12 @@
     <t>FGHA0708</t>
   </si>
   <si>
+    <t>2008-03-31</t>
+  </si>
+  <si>
     <t>2007-09-01</t>
   </si>
   <si>
-    <t>2008-03-31</t>
-  </si>
-  <si>
     <t>CXGLR07</t>
   </si>
   <si>
@@ -2980,75 +2980,75 @@
     <t>FPRK07</t>
   </si>
   <si>
+    <t>2007-11-30</t>
+  </si>
+  <si>
     <t>2007-08-28</t>
   </si>
   <si>
-    <t>2007-11-30</t>
-  </si>
-  <si>
     <t>OLBN07</t>
   </si>
   <si>
+    <t>2007-09-03</t>
+  </si>
+  <si>
     <t>2007-06-04</t>
   </si>
   <si>
-    <t>2007-09-03</t>
-  </si>
-  <si>
     <t>FLSO0708</t>
   </si>
   <si>
+    <t>2008-01-28</t>
+  </si>
+  <si>
     <t>2007-07-28</t>
   </si>
   <si>
-    <t>2008-01-28</t>
-  </si>
-  <si>
     <t>CLBR07</t>
   </si>
   <si>
     <t>FMDG07</t>
   </si>
   <si>
+    <t>2007-09-15</t>
+  </si>
+  <si>
     <t>2007-03-15</t>
   </si>
   <si>
-    <t>2007-09-15</t>
-  </si>
-  <si>
     <t>FMOZ07</t>
   </si>
   <si>
+    <t>2007-06-30</t>
+  </si>
+  <si>
     <t>2007-03-01</t>
   </si>
   <si>
-    <t>2007-06-30</t>
-  </si>
-  <si>
     <t>ONPL07</t>
   </si>
   <si>
     <t>FNIC0708</t>
   </si>
   <si>
+    <t>2008-02-28</t>
+  </si>
+  <si>
     <t>2007-09-07</t>
   </si>
   <si>
-    <t>2008-02-28</t>
-  </si>
-  <si>
     <t>ORUS07</t>
   </si>
   <si>
     <t>FPAK07</t>
   </si>
   <si>
+    <t>2007-10-31</t>
+  </si>
+  <si>
     <t>2007-07-15</t>
   </si>
   <si>
-    <t>2007-10-31</t>
-  </si>
-  <si>
     <t>FPER0708</t>
   </si>
   <si>
@@ -3082,12 +3082,12 @@
     <t>FSWZ0708</t>
   </si>
   <si>
+    <t>2008-01-20</t>
+  </si>
+  <si>
     <t>2007-07-20</t>
   </si>
   <si>
-    <t>2008-01-20</t>
-  </si>
-  <si>
     <t>CTLS07</t>
   </si>
   <si>
@@ -3112,15 +3112,15 @@
     <t>OAFG06</t>
   </si>
   <si>
+    <t>2006</t>
+  </si>
+  <si>
+    <t>2006-12-31</t>
+  </si>
+  <si>
     <t>2006-07-01</t>
   </si>
   <si>
-    <t>2006-12-31</t>
-  </si>
-  <si>
-    <t>2006</t>
-  </si>
-  <si>
     <t>CBDI06</t>
   </si>
   <si>
@@ -3145,21 +3145,21 @@
     <t>OETH06a</t>
   </si>
   <si>
+    <t>2006-11-25</t>
+  </si>
+  <si>
     <t>2006-08-25</t>
   </si>
   <si>
-    <t>2006-11-25</t>
-  </si>
-  <si>
     <t>OETH0607</t>
   </si>
   <si>
+    <t>2007-01-22</t>
+  </si>
+  <si>
     <t>2006-11-23</t>
   </si>
   <si>
-    <t>2007-01-22</t>
-  </si>
-  <si>
     <t>CXGLR06</t>
   </si>
   <si>
@@ -3169,12 +3169,12 @@
     <t>FGNB06</t>
   </si>
   <si>
+    <t>2006-11-30</t>
+  </si>
+  <si>
     <t>2006-05-01</t>
   </si>
   <si>
-    <t>2006-11-30</t>
-  </si>
-  <si>
     <t>CXHAF06</t>
   </si>
   <si>
@@ -3184,12 +3184,12 @@
     <t>FKEN0607</t>
   </si>
   <si>
+    <t>2007-04-15</t>
+  </si>
+  <si>
     <t>2006-10-16</t>
   </si>
   <si>
-    <t>2007-04-15</t>
-  </si>
-  <si>
     <t>FKEN06</t>
   </si>
   <si>
@@ -3199,12 +3199,12 @@
     <t>FLBN06</t>
   </si>
   <si>
+    <t>2006-10-23</t>
+  </si>
+  <si>
     <t>2006-07-24</t>
   </si>
   <si>
-    <t>2006-10-23</t>
-  </si>
-  <si>
     <t>CLBR06</t>
   </si>
   <si>
@@ -3232,12 +3232,12 @@
     <t>FSOM0607</t>
   </si>
   <si>
+    <t>2007-03-05</t>
+  </si>
+  <si>
     <t>2006-12-05</t>
   </si>
   <si>
-    <t>2007-03-05</t>
-  </si>
-  <si>
     <t>OLKA06</t>
   </si>
   <si>
@@ -3271,33 +3271,33 @@
     <t>FAGO05</t>
   </si>
   <si>
+    <t>2005</t>
+  </si>
+  <si>
+    <t>2005-06-30</t>
+  </si>
+  <si>
     <t>2005-04-01</t>
   </si>
   <si>
-    <t>2005-06-30</t>
-  </si>
-  <si>
-    <t>2005</t>
-  </si>
-  <si>
     <t>FBEN05</t>
   </si>
   <si>
+    <t>2005-10-31</t>
+  </si>
+  <si>
     <t>2005-05-01</t>
   </si>
   <si>
-    <t>2005-10-31</t>
-  </si>
-  <si>
     <t>CBDI05</t>
   </si>
   <si>
+    <t>2005-12-31</t>
+  </si>
+  <si>
     <t>2005-01-01</t>
   </si>
   <si>
-    <t>2005-12-31</t>
-  </si>
-  <si>
     <t>CCAF05</t>
   </si>
   <si>
@@ -3337,12 +3337,12 @@
     <t>FGUY05</t>
   </si>
   <si>
+    <t>2005-08-01</t>
+  </si>
+  <si>
     <t>2005-02-01</t>
   </si>
   <si>
-    <t>2005-08-01</t>
-  </si>
-  <si>
     <t>FXINDTSU05</t>
   </si>
   <si>
@@ -3355,12 +3355,12 @@
     <t>FNER05</t>
   </si>
   <si>
+    <t>2005-09-30</t>
+  </si>
+  <si>
     <t>2005-06-01</t>
   </si>
   <si>
-    <t>2005-09-30</t>
-  </si>
-  <si>
     <t>CCOG05</t>
   </si>
   <si>
@@ -3370,12 +3370,12 @@
     <t>FXSASIA0506</t>
   </si>
   <si>
+    <t>2006-04-10</t>
+  </si>
+  <si>
     <t>2005-10-11</t>
   </si>
   <si>
-    <t>2006-04-10</t>
-  </si>
-  <si>
     <t>CSDN05</t>
   </si>
   <si>
@@ -3388,27 +3388,27 @@
     <t>FXWAF0506</t>
   </si>
   <si>
+    <t>2006-05-31</t>
+  </si>
+  <si>
     <t>2005-11-01</t>
   </si>
   <si>
-    <t>2006-05-31</t>
-  </si>
-  <si>
     <t>CPSE05</t>
   </si>
   <si>
     <t>OAFG04</t>
   </si>
   <si>
+    <t>2004</t>
+  </si>
+  <si>
+    <t>2004-12-31</t>
+  </si>
+  <si>
     <t>2004-09-01</t>
   </si>
   <si>
-    <t>2004-12-31</t>
-  </si>
-  <si>
-    <t>2004</t>
-  </si>
-  <si>
     <t>CAGO04</t>
   </si>
   <si>
@@ -3418,21 +3418,21 @@
     <t>FBGD0405</t>
   </si>
   <si>
+    <t>2005-01-31</t>
+  </si>
+  <si>
     <t>2004-08-01</t>
   </si>
   <si>
-    <t>2005-01-31</t>
-  </si>
-  <si>
     <t>FBOL0405</t>
   </si>
   <si>
+    <t>2005-05-31</t>
+  </si>
+  <si>
     <t>2004-11-01</t>
   </si>
   <si>
-    <t>2005-05-31</t>
-  </si>
-  <si>
     <t>CBDI04</t>
   </si>
   <si>
@@ -3505,21 +3505,21 @@
     <t>FMDG04</t>
   </si>
   <si>
+    <t>2004-06-19</t>
+  </si>
+  <si>
     <t>2004-03-19</t>
   </si>
   <si>
-    <t>2004-06-19</t>
-  </si>
-  <si>
     <t>FPHL0405</t>
   </si>
   <si>
+    <t>2005-03-15</t>
+  </si>
+  <si>
     <t>2004-12-15</t>
   </si>
   <si>
-    <t>2005-03-15</t>
-  </si>
-  <si>
     <t>CSLE04</t>
   </si>
   <si>
@@ -3550,15 +3550,15 @@
     <t>OAFG03</t>
   </si>
   <si>
+    <t>2003</t>
+  </si>
+  <si>
+    <t>2003-12-31</t>
+  </si>
+  <si>
     <t>2003-01-01</t>
   </si>
   <si>
-    <t>2003-12-31</t>
-  </si>
-  <si>
-    <t>2003</t>
-  </si>
-  <si>
     <t>CAGO03</t>
   </si>
   <si>
@@ -3571,12 +3571,12 @@
     <t>FCAF03</t>
   </si>
   <si>
+    <t>2003-06-30</t>
+  </si>
+  <si>
     <t>2003-04-01</t>
   </si>
   <si>
-    <t>2003-06-30</t>
-  </si>
-  <si>
     <t>CRUS03</t>
   </si>
   <si>
@@ -3589,12 +3589,12 @@
     <t>FCIV0203</t>
   </si>
   <si>
+    <t>2003-01-31</t>
+  </si>
+  <si>
     <t>2002-11-01</t>
   </si>
   <si>
-    <t>2003-01-31</t>
-  </si>
-  <si>
     <t>CPRK03</t>
   </si>
   <si>
@@ -3613,21 +3613,21 @@
     <t>OHTI03</t>
   </si>
   <si>
+    <t>2003-08-31</t>
+  </si>
+  <si>
     <t>2003-03-01</t>
   </si>
   <si>
-    <t>2003-08-31</t>
-  </si>
-  <si>
     <t>CLSO0304</t>
   </si>
   <si>
+    <t>2004-06-30</t>
+  </si>
+  <si>
     <t>2003-07-01</t>
   </si>
   <si>
-    <t>2004-06-30</t>
-  </si>
-  <si>
     <t>CMWI03</t>
   </si>
   <si>
@@ -3679,15 +3679,15 @@
     <t>CAFG0102</t>
   </si>
   <si>
+    <t>2002</t>
+  </si>
+  <si>
+    <t>2002-12-31</t>
+  </si>
+  <si>
     <t>2001-10-01</t>
   </si>
   <si>
-    <t>2002-12-31</t>
-  </si>
-  <si>
-    <t>2002</t>
-  </si>
-  <si>
     <t>CAGO02</t>
   </si>
   <si>
@@ -3781,15 +3781,15 @@
     <t>CAFG01</t>
   </si>
   <si>
+    <t>2001</t>
+  </si>
+  <si>
+    <t>2001-09-30</t>
+  </si>
+  <si>
     <t>2001-01-01</t>
   </si>
   <si>
-    <t>2001-09-30</t>
-  </si>
-  <si>
-    <t>2001</t>
-  </si>
-  <si>
     <t>CAGO01</t>
   </si>
   <si>
@@ -3862,15 +3862,15 @@
     <t>CAGO00</t>
   </si>
   <si>
+    <t>2000</t>
+  </si>
+  <si>
+    <t>2000-12-31</t>
+  </si>
+  <si>
     <t>2000-01-01</t>
   </si>
   <si>
-    <t>2000-12-31</t>
-  </si>
-  <si>
-    <t>2000</t>
-  </si>
-  <si>
     <t>CBDI00</t>
   </si>
   <si>
@@ -3919,10 +3919,10 @@
     <t>CTLS9900</t>
   </si>
   <si>
+    <t>1999</t>
+  </si>
+  <si>
     <t>1999-10-01</t>
-  </si>
-  <si>
-    <t>1999</t>
   </si>
   <si>
     <t>CRUS9900</t>
@@ -4654,13 +4654,13 @@
         <v>7</v>
       </c>
       <c r="C20" t="s">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="D20" t="s">
         <v>9</v>
       </c>
       <c r="E20" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="F20" t="s">
         <v>11</v>
@@ -4934,13 +4934,13 @@
         <v>7</v>
       </c>
       <c r="C34" t="s">
-        <v>54</v>
+        <v>8</v>
       </c>
       <c r="D34" t="s">
         <v>9</v>
       </c>
       <c r="E34" t="s">
-        <v>10</v>
+        <v>54</v>
       </c>
       <c r="F34" t="s">
         <v>24</v>
@@ -5214,13 +5214,13 @@
         <v>7</v>
       </c>
       <c r="C48" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="D48" t="s">
         <v>68</v>
       </c>
       <c r="E48" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F48" t="s">
         <v>16</v>
@@ -5254,13 +5254,13 @@
         <v>7</v>
       </c>
       <c r="C50" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="D50" t="s">
         <v>68</v>
       </c>
       <c r="E50" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="F50" t="s">
         <v>16</v>
@@ -5394,13 +5394,13 @@
         <v>7</v>
       </c>
       <c r="C57" t="s">
-        <v>83</v>
+        <v>67</v>
       </c>
       <c r="D57" t="s">
         <v>68</v>
       </c>
       <c r="E57" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="F57" t="s">
         <v>24</v>
@@ -5474,13 +5474,13 @@
         <v>7</v>
       </c>
       <c r="C61" t="s">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="D61" t="s">
         <v>68</v>
       </c>
       <c r="E61" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="F61" t="s">
         <v>16</v>
@@ -5494,13 +5494,13 @@
         <v>7</v>
       </c>
       <c r="C62" t="s">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="D62" t="s">
         <v>68</v>
       </c>
       <c r="E62" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="F62" t="s">
         <v>24</v>
@@ -5554,13 +5554,13 @@
         <v>7</v>
       </c>
       <c r="C65" t="s">
-        <v>95</v>
+        <v>67</v>
       </c>
       <c r="D65" t="s">
         <v>68</v>
       </c>
       <c r="E65" t="s">
-        <v>69</v>
+        <v>95</v>
       </c>
       <c r="F65" t="s">
         <v>24</v>
@@ -5594,13 +5594,13 @@
         <v>7</v>
       </c>
       <c r="C67" t="s">
-        <v>98</v>
+        <v>67</v>
       </c>
       <c r="D67" t="s">
         <v>93</v>
       </c>
       <c r="E67" t="s">
-        <v>69</v>
+        <v>98</v>
       </c>
       <c r="F67" t="s">
         <v>16</v>
@@ -5614,13 +5614,13 @@
         <v>7</v>
       </c>
       <c r="C68" t="s">
-        <v>100</v>
+        <v>67</v>
       </c>
       <c r="D68" t="s">
         <v>68</v>
       </c>
       <c r="E68" t="s">
-        <v>69</v>
+        <v>100</v>
       </c>
       <c r="F68" t="s">
         <v>24</v>
@@ -5674,13 +5674,13 @@
         <v>7</v>
       </c>
       <c r="C71" t="s">
-        <v>104</v>
+        <v>67</v>
       </c>
       <c r="D71" t="s">
         <v>68</v>
       </c>
       <c r="E71" t="s">
-        <v>69</v>
+        <v>104</v>
       </c>
       <c r="F71" t="s">
         <v>16</v>
@@ -5734,13 +5734,13 @@
         <v>7</v>
       </c>
       <c r="C74" t="s">
-        <v>108</v>
+        <v>67</v>
       </c>
       <c r="D74" t="s">
         <v>68</v>
       </c>
       <c r="E74" t="s">
-        <v>69</v>
+        <v>108</v>
       </c>
       <c r="F74" t="s">
         <v>16</v>
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="C80" t="s">
-        <v>83</v>
+        <v>67</v>
       </c>
       <c r="D80" t="s">
         <v>68</v>
       </c>
       <c r="E80" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="F80" t="s">
         <v>24</v>
@@ -6114,13 +6114,13 @@
         <v>7</v>
       </c>
       <c r="C93" t="s">
-        <v>129</v>
+        <v>67</v>
       </c>
       <c r="D93" t="s">
         <v>68</v>
       </c>
       <c r="E93" t="s">
-        <v>69</v>
+        <v>129</v>
       </c>
       <c r="F93" t="s">
         <v>16</v>
@@ -6154,13 +6154,13 @@
         <v>7</v>
       </c>
       <c r="C95" t="s">
-        <v>132</v>
+        <v>67</v>
       </c>
       <c r="D95" t="s">
         <v>68</v>
       </c>
       <c r="E95" t="s">
-        <v>69</v>
+        <v>132</v>
       </c>
       <c r="F95" t="s">
         <v>24</v>
@@ -6174,13 +6174,13 @@
         <v>7</v>
       </c>
       <c r="C96" t="s">
-        <v>132</v>
+        <v>67</v>
       </c>
       <c r="D96" t="s">
         <v>68</v>
       </c>
       <c r="E96" t="s">
-        <v>69</v>
+        <v>132</v>
       </c>
       <c r="F96" t="s">
         <v>24</v>
@@ -6354,13 +6354,13 @@
         <v>7</v>
       </c>
       <c r="C105" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="D105" t="s">
         <v>136</v>
       </c>
       <c r="E105" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="F105" t="s">
         <v>24</v>
@@ -6514,13 +6514,13 @@
         <v>7</v>
       </c>
       <c r="C113" t="s">
-        <v>155</v>
+        <v>135</v>
       </c>
       <c r="D113" t="s">
         <v>136</v>
       </c>
       <c r="E113" t="s">
-        <v>137</v>
+        <v>155</v>
       </c>
       <c r="F113" t="s">
         <v>24</v>
@@ -6574,13 +6574,13 @@
         <v>7</v>
       </c>
       <c r="C116" t="s">
+        <v>135</v>
+      </c>
+      <c r="D116" t="s">
         <v>159</v>
       </c>
-      <c r="D116" t="s">
+      <c r="E116" t="s">
         <v>160</v>
-      </c>
-      <c r="E116" t="s">
-        <v>137</v>
       </c>
       <c r="F116" t="s">
         <v>16</v>
@@ -6594,13 +6594,13 @@
         <v>7</v>
       </c>
       <c r="C117" t="s">
+        <v>135</v>
+      </c>
+      <c r="D117" t="s">
         <v>162</v>
       </c>
-      <c r="D117" t="s">
+      <c r="E117" t="s">
         <v>163</v>
-      </c>
-      <c r="E117" t="s">
-        <v>137</v>
       </c>
       <c r="F117" t="s">
         <v>16</v>
@@ -6697,7 +6697,7 @@
         <v>135</v>
       </c>
       <c r="D122" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E122" t="s">
         <v>137</v>
@@ -6717,7 +6717,7 @@
         <v>135</v>
       </c>
       <c r="D123" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E123" t="s">
         <v>137</v>
@@ -6894,13 +6894,13 @@
         <v>7</v>
       </c>
       <c r="C132" t="s">
+        <v>135</v>
+      </c>
+      <c r="D132" t="s">
         <v>179</v>
       </c>
-      <c r="D132" t="s">
+      <c r="E132" t="s">
         <v>180</v>
-      </c>
-      <c r="E132" t="s">
-        <v>137</v>
       </c>
       <c r="F132" t="s">
         <v>13</v>
@@ -6934,13 +6934,13 @@
         <v>7</v>
       </c>
       <c r="C134" t="s">
+        <v>135</v>
+      </c>
+      <c r="D134" t="s">
+        <v>159</v>
+      </c>
+      <c r="E134" t="s">
         <v>183</v>
-      </c>
-      <c r="D134" t="s">
-        <v>160</v>
-      </c>
-      <c r="E134" t="s">
-        <v>137</v>
       </c>
       <c r="F134" t="s">
         <v>24</v>
@@ -6974,13 +6974,13 @@
         <v>7</v>
       </c>
       <c r="C136" t="s">
+        <v>135</v>
+      </c>
+      <c r="D136" t="s">
+        <v>159</v>
+      </c>
+      <c r="E136" t="s">
         <v>186</v>
-      </c>
-      <c r="D136" t="s">
-        <v>160</v>
-      </c>
-      <c r="E136" t="s">
-        <v>137</v>
       </c>
       <c r="F136" t="s">
         <v>24</v>
@@ -7274,13 +7274,13 @@
         <v>7</v>
       </c>
       <c r="C151" t="s">
+        <v>195</v>
+      </c>
+      <c r="D151" t="s">
         <v>205</v>
       </c>
-      <c r="D151" t="s">
+      <c r="E151" t="s">
         <v>206</v>
-      </c>
-      <c r="E151" t="s">
-        <v>197</v>
       </c>
       <c r="F151" t="s">
         <v>16</v>
@@ -7374,13 +7374,13 @@
         <v>7</v>
       </c>
       <c r="C156" t="s">
+        <v>195</v>
+      </c>
+      <c r="D156" t="s">
         <v>212</v>
       </c>
-      <c r="D156" t="s">
+      <c r="E156" t="s">
         <v>213</v>
-      </c>
-      <c r="E156" t="s">
-        <v>197</v>
       </c>
       <c r="F156" t="s">
         <v>24</v>
@@ -7394,13 +7394,13 @@
         <v>110</v>
       </c>
       <c r="C157" t="s">
-        <v>212</v>
+        <v>195</v>
       </c>
       <c r="D157" t="s">
         <v>196</v>
       </c>
       <c r="E157" t="s">
-        <v>197</v>
+        <v>213</v>
       </c>
       <c r="F157" t="s">
         <v>24</v>
@@ -7554,13 +7554,13 @@
         <v>7</v>
       </c>
       <c r="C165" t="s">
+        <v>195</v>
+      </c>
+      <c r="D165" t="s">
         <v>224</v>
       </c>
-      <c r="D165" t="s">
+      <c r="E165" t="s">
         <v>225</v>
-      </c>
-      <c r="E165" t="s">
-        <v>197</v>
       </c>
       <c r="F165" t="s">
         <v>24</v>
@@ -7594,13 +7594,13 @@
         <v>7</v>
       </c>
       <c r="C167" t="s">
+        <v>195</v>
+      </c>
+      <c r="D167" t="s">
         <v>228</v>
       </c>
-      <c r="D167" t="s">
+      <c r="E167" t="s">
         <v>229</v>
-      </c>
-      <c r="E167" t="s">
-        <v>197</v>
       </c>
       <c r="F167" t="s">
         <v>24</v>
@@ -7714,13 +7714,13 @@
         <v>7</v>
       </c>
       <c r="C173" t="s">
-        <v>236</v>
+        <v>195</v>
       </c>
       <c r="D173" t="s">
         <v>196</v>
       </c>
       <c r="E173" t="s">
-        <v>197</v>
+        <v>236</v>
       </c>
       <c r="F173" t="s">
         <v>16</v>
@@ -7734,13 +7734,13 @@
         <v>110</v>
       </c>
       <c r="C174" t="s">
-        <v>236</v>
+        <v>195</v>
       </c>
       <c r="D174" t="s">
         <v>238</v>
       </c>
       <c r="E174" t="s">
-        <v>197</v>
+        <v>236</v>
       </c>
       <c r="F174" t="s">
         <v>16</v>
@@ -7754,13 +7754,13 @@
         <v>7</v>
       </c>
       <c r="C175" t="s">
+        <v>195</v>
+      </c>
+      <c r="D175" t="s">
         <v>240</v>
       </c>
-      <c r="D175" t="s">
+      <c r="E175" t="s">
         <v>241</v>
-      </c>
-      <c r="E175" t="s">
-        <v>197</v>
       </c>
       <c r="F175" t="s">
         <v>16</v>
@@ -7914,13 +7914,13 @@
         <v>7</v>
       </c>
       <c r="C183" t="s">
-        <v>250</v>
+        <v>195</v>
       </c>
       <c r="D183" t="s">
         <v>196</v>
       </c>
       <c r="E183" t="s">
-        <v>197</v>
+        <v>250</v>
       </c>
       <c r="F183" t="s">
         <v>16</v>
@@ -8014,13 +8014,13 @@
         <v>7</v>
       </c>
       <c r="C188" t="s">
-        <v>256</v>
+        <v>195</v>
       </c>
       <c r="D188" t="s">
         <v>196</v>
       </c>
       <c r="E188" t="s">
-        <v>197</v>
+        <v>256</v>
       </c>
       <c r="F188" t="s">
         <v>24</v>
@@ -8054,13 +8054,13 @@
         <v>7</v>
       </c>
       <c r="C190" t="s">
-        <v>256</v>
+        <v>195</v>
       </c>
       <c r="D190" t="s">
         <v>259</v>
       </c>
       <c r="E190" t="s">
-        <v>197</v>
+        <v>256</v>
       </c>
       <c r="F190" t="s">
         <v>13</v>
@@ -8134,13 +8134,13 @@
         <v>7</v>
       </c>
       <c r="C194" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="D194" t="s">
         <v>264</v>
       </c>
       <c r="E194" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F194" t="s">
         <v>19</v>
@@ -8154,13 +8154,13 @@
         <v>7</v>
       </c>
       <c r="C195" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="D195" t="s">
         <v>264</v>
       </c>
       <c r="E195" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F195" t="s">
         <v>13</v>
@@ -8174,13 +8174,13 @@
         <v>7</v>
       </c>
       <c r="C196" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="D196" t="s">
         <v>264</v>
       </c>
       <c r="E196" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F196" t="s">
         <v>19</v>
@@ -8194,13 +8194,13 @@
         <v>7</v>
       </c>
       <c r="C197" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="D197" t="s">
         <v>264</v>
       </c>
       <c r="E197" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F197" t="s">
         <v>19</v>
@@ -8214,13 +8214,13 @@
         <v>7</v>
       </c>
       <c r="C198" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="D198" t="s">
         <v>264</v>
       </c>
       <c r="E198" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F198" t="s">
         <v>13</v>
@@ -8234,13 +8234,13 @@
         <v>7</v>
       </c>
       <c r="C199" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="D199" t="s">
         <v>264</v>
       </c>
       <c r="E199" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F199" t="s">
         <v>19</v>
@@ -8254,13 +8254,13 @@
         <v>7</v>
       </c>
       <c r="C200" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="D200" t="s">
         <v>264</v>
       </c>
       <c r="E200" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F200" t="s">
         <v>19</v>
@@ -8274,13 +8274,13 @@
         <v>7</v>
       </c>
       <c r="C201" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="D201" t="s">
         <v>264</v>
       </c>
       <c r="E201" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F201" t="s">
         <v>19</v>
@@ -8294,13 +8294,13 @@
         <v>7</v>
       </c>
       <c r="C202" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="D202" t="s">
         <v>264</v>
       </c>
       <c r="E202" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F202" t="s">
         <v>19</v>
@@ -8314,13 +8314,13 @@
         <v>7</v>
       </c>
       <c r="C203" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="D203" t="s">
         <v>264</v>
       </c>
       <c r="E203" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F203" t="s">
         <v>19</v>
@@ -8334,13 +8334,13 @@
         <v>7</v>
       </c>
       <c r="C204" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="D204" t="s">
         <v>264</v>
       </c>
       <c r="E204" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F204" t="s">
         <v>13</v>
@@ -8354,13 +8354,13 @@
         <v>7</v>
       </c>
       <c r="C205" t="s">
-        <v>279</v>
+        <v>263</v>
       </c>
       <c r="D205" t="s">
         <v>264</v>
       </c>
       <c r="E205" t="s">
-        <v>265</v>
+        <v>279</v>
       </c>
       <c r="F205" t="s">
         <v>19</v>
@@ -8374,13 +8374,13 @@
         <v>110</v>
       </c>
       <c r="C206" t="s">
-        <v>279</v>
+        <v>263</v>
       </c>
       <c r="D206" t="s">
         <v>196</v>
       </c>
       <c r="E206" t="s">
-        <v>265</v>
+        <v>279</v>
       </c>
       <c r="F206" t="s">
         <v>19</v>
@@ -8394,13 +8394,13 @@
         <v>7</v>
       </c>
       <c r="C207" t="s">
+        <v>263</v>
+      </c>
+      <c r="D207" t="s">
         <v>282</v>
       </c>
-      <c r="D207" t="s">
+      <c r="E207" t="s">
         <v>283</v>
-      </c>
-      <c r="E207" t="s">
-        <v>265</v>
       </c>
       <c r="F207" t="s">
         <v>24</v>
@@ -8414,13 +8414,13 @@
         <v>7</v>
       </c>
       <c r="C208" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="D208" t="s">
         <v>264</v>
       </c>
       <c r="E208" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F208" t="s">
         <v>19</v>
@@ -8434,13 +8434,13 @@
         <v>7</v>
       </c>
       <c r="C209" t="s">
-        <v>279</v>
+        <v>263</v>
       </c>
       <c r="D209" t="s">
         <v>264</v>
       </c>
       <c r="E209" t="s">
-        <v>265</v>
+        <v>279</v>
       </c>
       <c r="F209" t="s">
         <v>19</v>
@@ -8454,13 +8454,13 @@
         <v>110</v>
       </c>
       <c r="C210" t="s">
-        <v>279</v>
+        <v>263</v>
       </c>
       <c r="D210" t="s">
         <v>196</v>
       </c>
       <c r="E210" t="s">
-        <v>265</v>
+        <v>279</v>
       </c>
       <c r="F210" t="s">
         <v>19</v>
@@ -8474,13 +8474,13 @@
         <v>7</v>
       </c>
       <c r="C211" t="s">
+        <v>263</v>
+      </c>
+      <c r="D211" t="s">
         <v>288</v>
       </c>
-      <c r="D211" t="s">
+      <c r="E211" t="s">
         <v>289</v>
-      </c>
-      <c r="E211" t="s">
-        <v>265</v>
       </c>
       <c r="F211" t="s">
         <v>24</v>
@@ -8494,13 +8494,13 @@
         <v>7</v>
       </c>
       <c r="C212" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="D212" t="s">
         <v>264</v>
       </c>
       <c r="E212" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F212" t="s">
         <v>19</v>
@@ -8514,13 +8514,13 @@
         <v>7</v>
       </c>
       <c r="C213" t="s">
+        <v>263</v>
+      </c>
+      <c r="D213" t="s">
         <v>292</v>
       </c>
-      <c r="D213" t="s">
+      <c r="E213" t="s">
         <v>293</v>
-      </c>
-      <c r="E213" t="s">
-        <v>265</v>
       </c>
       <c r="F213" t="s">
         <v>24</v>
@@ -8534,13 +8534,13 @@
         <v>7</v>
       </c>
       <c r="C214" t="s">
-        <v>279</v>
+        <v>263</v>
       </c>
       <c r="D214" t="s">
         <v>264</v>
       </c>
       <c r="E214" t="s">
-        <v>265</v>
+        <v>279</v>
       </c>
       <c r="F214" t="s">
         <v>19</v>
@@ -8554,13 +8554,13 @@
         <v>110</v>
       </c>
       <c r="C215" t="s">
-        <v>279</v>
+        <v>263</v>
       </c>
       <c r="D215" t="s">
         <v>196</v>
       </c>
       <c r="E215" t="s">
-        <v>265</v>
+        <v>279</v>
       </c>
       <c r="F215" t="s">
         <v>19</v>
@@ -8574,13 +8574,13 @@
         <v>7</v>
       </c>
       <c r="C216" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="D216" t="s">
         <v>264</v>
       </c>
       <c r="E216" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F216" t="s">
         <v>19</v>
@@ -8594,13 +8594,13 @@
         <v>7</v>
       </c>
       <c r="C217" t="s">
-        <v>298</v>
+        <v>263</v>
       </c>
       <c r="D217" t="s">
         <v>264</v>
       </c>
       <c r="E217" t="s">
-        <v>265</v>
+        <v>298</v>
       </c>
       <c r="F217" t="s">
         <v>24</v>
@@ -8614,13 +8614,13 @@
         <v>7</v>
       </c>
       <c r="C218" t="s">
+        <v>263</v>
+      </c>
+      <c r="D218" t="s">
         <v>300</v>
       </c>
-      <c r="D218" t="s">
+      <c r="E218" t="s">
         <v>301</v>
-      </c>
-      <c r="E218" t="s">
-        <v>265</v>
       </c>
       <c r="F218" t="s">
         <v>16</v>
@@ -8634,13 +8634,13 @@
         <v>7</v>
       </c>
       <c r="C219" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="D219" t="s">
         <v>264</v>
       </c>
       <c r="E219" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F219" t="s">
         <v>19</v>
@@ -8654,13 +8654,13 @@
         <v>110</v>
       </c>
       <c r="C220" t="s">
+        <v>263</v>
+      </c>
+      <c r="D220" t="s">
+        <v>224</v>
+      </c>
+      <c r="E220" t="s">
         <v>267</v>
-      </c>
-      <c r="D220" t="s">
-        <v>225</v>
-      </c>
-      <c r="E220" t="s">
-        <v>265</v>
       </c>
       <c r="F220" t="s">
         <v>24</v>
@@ -8674,13 +8674,13 @@
         <v>7</v>
       </c>
       <c r="C221" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="D221" t="s">
         <v>264</v>
       </c>
       <c r="E221" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F221" t="s">
         <v>24</v>
@@ -8694,13 +8694,13 @@
         <v>7</v>
       </c>
       <c r="C222" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="D222" t="s">
         <v>264</v>
       </c>
       <c r="E222" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F222" t="s">
         <v>19</v>
@@ -8714,13 +8714,13 @@
         <v>7</v>
       </c>
       <c r="C223" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="D223" t="s">
         <v>264</v>
       </c>
       <c r="E223" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F223" t="s">
         <v>19</v>
@@ -8734,13 +8734,13 @@
         <v>7</v>
       </c>
       <c r="C224" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="D224" t="s">
         <v>264</v>
       </c>
       <c r="E224" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F224" t="s">
         <v>19</v>
@@ -8754,13 +8754,13 @@
         <v>7</v>
       </c>
       <c r="C225" t="s">
-        <v>309</v>
+        <v>263</v>
       </c>
       <c r="D225" t="s">
         <v>264</v>
       </c>
       <c r="E225" t="s">
-        <v>265</v>
+        <v>309</v>
       </c>
       <c r="F225" t="s">
         <v>16</v>
@@ -8774,13 +8774,13 @@
         <v>7</v>
       </c>
       <c r="C226" t="s">
-        <v>311</v>
+        <v>263</v>
       </c>
       <c r="D226" t="s">
         <v>264</v>
       </c>
       <c r="E226" t="s">
-        <v>265</v>
+        <v>311</v>
       </c>
       <c r="F226" t="s">
         <v>16</v>
@@ -8794,13 +8794,13 @@
         <v>7</v>
       </c>
       <c r="C227" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="D227" t="s">
         <v>264</v>
       </c>
       <c r="E227" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F227" t="s">
         <v>19</v>
@@ -8814,13 +8814,13 @@
         <v>7</v>
       </c>
       <c r="C228" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="D228" t="s">
         <v>264</v>
       </c>
       <c r="E228" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F228" t="s">
         <v>19</v>
@@ -8834,13 +8834,13 @@
         <v>7</v>
       </c>
       <c r="C229" t="s">
-        <v>311</v>
+        <v>263</v>
       </c>
       <c r="D229" t="s">
         <v>264</v>
       </c>
       <c r="E229" t="s">
-        <v>265</v>
+        <v>311</v>
       </c>
       <c r="F229" t="s">
         <v>24</v>
@@ -8854,13 +8854,13 @@
         <v>110</v>
       </c>
       <c r="C230" t="s">
-        <v>311</v>
+        <v>263</v>
       </c>
       <c r="D230" t="s">
         <v>264</v>
       </c>
       <c r="E230" t="s">
-        <v>265</v>
+        <v>311</v>
       </c>
       <c r="F230" t="s">
         <v>16</v>
@@ -8874,13 +8874,13 @@
         <v>7</v>
       </c>
       <c r="C231" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="D231" t="s">
         <v>264</v>
       </c>
       <c r="E231" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F231" t="s">
         <v>19</v>
@@ -8894,13 +8894,13 @@
         <v>7</v>
       </c>
       <c r="C232" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="D232" t="s">
         <v>264</v>
       </c>
       <c r="E232" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F232" t="s">
         <v>19</v>
@@ -8914,13 +8914,13 @@
         <v>7</v>
       </c>
       <c r="C233" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="D233" t="s">
         <v>264</v>
       </c>
       <c r="E233" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F233" t="s">
         <v>13</v>
@@ -8934,13 +8934,13 @@
         <v>7</v>
       </c>
       <c r="C234" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="D234" t="s">
         <v>264</v>
       </c>
       <c r="E234" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F234" t="s">
         <v>13</v>
@@ -8954,13 +8954,13 @@
         <v>7</v>
       </c>
       <c r="C235" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="D235" t="s">
         <v>264</v>
       </c>
       <c r="E235" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F235" t="s">
         <v>19</v>
@@ -8974,13 +8974,13 @@
         <v>7</v>
       </c>
       <c r="C236" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="D236" t="s">
         <v>264</v>
       </c>
       <c r="E236" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F236" t="s">
         <v>19</v>
@@ -8994,13 +8994,13 @@
         <v>7</v>
       </c>
       <c r="C237" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="D237" t="s">
         <v>264</v>
       </c>
       <c r="E237" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F237" t="s">
         <v>13</v>
@@ -9014,13 +9014,13 @@
         <v>7</v>
       </c>
       <c r="C238" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="D238" t="s">
         <v>264</v>
       </c>
       <c r="E238" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F238" t="s">
         <v>19</v>
@@ -9034,13 +9034,13 @@
         <v>7</v>
       </c>
       <c r="C239" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="D239" t="s">
         <v>264</v>
       </c>
       <c r="E239" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F239" t="s">
         <v>19</v>
@@ -9054,13 +9054,13 @@
         <v>7</v>
       </c>
       <c r="C240" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="D240" t="s">
         <v>264</v>
       </c>
       <c r="E240" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F240" t="s">
         <v>13</v>
@@ -9074,13 +9074,13 @@
         <v>7</v>
       </c>
       <c r="C241" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="D241" t="s">
         <v>264</v>
       </c>
       <c r="E241" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F241" t="s">
         <v>19</v>
@@ -9094,13 +9094,13 @@
         <v>7</v>
       </c>
       <c r="C242" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="D242" t="s">
         <v>264</v>
       </c>
       <c r="E242" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F242" t="s">
         <v>19</v>
@@ -9114,13 +9114,13 @@
         <v>7</v>
       </c>
       <c r="C243" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="D243" t="s">
         <v>264</v>
       </c>
       <c r="E243" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F243" t="s">
         <v>19</v>
@@ -9134,13 +9134,13 @@
         <v>7</v>
       </c>
       <c r="C244" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="D244" t="s">
         <v>264</v>
       </c>
       <c r="E244" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F244" t="s">
         <v>19</v>
@@ -9174,13 +9174,13 @@
         <v>7</v>
       </c>
       <c r="C246" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="D246" t="s">
         <v>332</v>
       </c>
       <c r="E246" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="F246" t="s">
         <v>16</v>
@@ -9214,13 +9214,13 @@
         <v>7</v>
       </c>
       <c r="C248" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="D248" t="s">
         <v>332</v>
       </c>
       <c r="E248" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="F248" t="s">
         <v>16</v>
@@ -9294,13 +9294,13 @@
         <v>7</v>
       </c>
       <c r="C252" t="s">
-        <v>342</v>
+        <v>331</v>
       </c>
       <c r="D252" t="s">
         <v>332</v>
       </c>
       <c r="E252" t="s">
-        <v>333</v>
+        <v>342</v>
       </c>
       <c r="F252" t="s">
         <v>16</v>
@@ -9334,13 +9334,13 @@
         <v>7</v>
       </c>
       <c r="C254" t="s">
-        <v>345</v>
+        <v>331</v>
       </c>
       <c r="D254" t="s">
         <v>267</v>
       </c>
       <c r="E254" t="s">
-        <v>333</v>
+        <v>345</v>
       </c>
       <c r="F254" t="s">
         <v>19</v>
@@ -9394,13 +9394,13 @@
         <v>7</v>
       </c>
       <c r="C257" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="D257" t="s">
         <v>332</v>
       </c>
       <c r="E257" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="F257" t="s">
         <v>16</v>
@@ -9414,13 +9414,13 @@
         <v>7</v>
       </c>
       <c r="C258" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="D258" t="s">
         <v>332</v>
       </c>
       <c r="E258" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="F258" t="s">
         <v>16</v>
@@ -9434,13 +9434,13 @@
         <v>110</v>
       </c>
       <c r="C259" t="s">
-        <v>351</v>
+        <v>331</v>
       </c>
       <c r="D259" t="s">
         <v>332</v>
       </c>
       <c r="E259" t="s">
-        <v>333</v>
+        <v>351</v>
       </c>
       <c r="F259" t="s">
         <v>19</v>
@@ -9494,13 +9494,13 @@
         <v>7</v>
       </c>
       <c r="C262" t="s">
+        <v>331</v>
+      </c>
+      <c r="D262" t="s">
         <v>355</v>
       </c>
-      <c r="D262" t="s">
+      <c r="E262" t="s">
         <v>356</v>
-      </c>
-      <c r="E262" t="s">
-        <v>333</v>
       </c>
       <c r="F262" t="s">
         <v>24</v>
@@ -9514,13 +9514,13 @@
         <v>7</v>
       </c>
       <c r="C263" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="D263" t="s">
         <v>332</v>
       </c>
       <c r="E263" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="F263" t="s">
         <v>16</v>
@@ -9534,13 +9534,13 @@
         <v>110</v>
       </c>
       <c r="C264" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="D264" t="s">
         <v>332</v>
       </c>
       <c r="E264" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="F264" t="s">
         <v>16</v>
@@ -9574,13 +9574,13 @@
         <v>7</v>
       </c>
       <c r="C266" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="D266" t="s">
         <v>332</v>
       </c>
       <c r="E266" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="F266" t="s">
         <v>16</v>
@@ -9614,13 +9614,13 @@
         <v>7</v>
       </c>
       <c r="C268" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="D268" t="s">
         <v>332</v>
       </c>
       <c r="E268" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="F268" t="s">
         <v>16</v>
@@ -9634,13 +9634,13 @@
         <v>7</v>
       </c>
       <c r="C269" t="s">
-        <v>351</v>
+        <v>331</v>
       </c>
       <c r="D269" t="s">
         <v>332</v>
       </c>
       <c r="E269" t="s">
-        <v>333</v>
+        <v>351</v>
       </c>
       <c r="F269" t="s">
         <v>16</v>
@@ -9654,13 +9654,13 @@
         <v>110</v>
       </c>
       <c r="C270" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="D270" t="s">
         <v>332</v>
       </c>
       <c r="E270" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="F270" t="s">
         <v>16</v>
@@ -9674,13 +9674,13 @@
         <v>7</v>
       </c>
       <c r="C271" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="D271" t="s">
         <v>332</v>
       </c>
       <c r="E271" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="F271" t="s">
         <v>16</v>
@@ -9714,13 +9714,13 @@
         <v>7</v>
       </c>
       <c r="C273" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="D273" t="s">
         <v>332</v>
       </c>
       <c r="E273" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="F273" t="s">
         <v>16</v>
@@ -9754,13 +9754,13 @@
         <v>7</v>
       </c>
       <c r="C275" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="D275" t="s">
         <v>332</v>
       </c>
       <c r="E275" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="F275" t="s">
         <v>16</v>
@@ -9774,13 +9774,13 @@
         <v>7</v>
       </c>
       <c r="C276" t="s">
-        <v>371</v>
+        <v>331</v>
       </c>
       <c r="D276" t="s">
         <v>332</v>
       </c>
       <c r="E276" t="s">
-        <v>333</v>
+        <v>371</v>
       </c>
       <c r="F276" t="s">
         <v>16</v>
@@ -9794,13 +9794,13 @@
         <v>7</v>
       </c>
       <c r="C277" t="s">
+        <v>331</v>
+      </c>
+      <c r="D277" t="s">
         <v>373</v>
       </c>
-      <c r="D277" t="s">
+      <c r="E277" t="s">
         <v>374</v>
-      </c>
-      <c r="E277" t="s">
-        <v>333</v>
       </c>
       <c r="F277" t="s">
         <v>24</v>
@@ -9814,13 +9814,13 @@
         <v>7</v>
       </c>
       <c r="C278" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="D278" t="s">
         <v>332</v>
       </c>
       <c r="E278" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="F278" t="s">
         <v>16</v>
@@ -9834,13 +9834,13 @@
         <v>7</v>
       </c>
       <c r="C279" t="s">
+        <v>331</v>
+      </c>
+      <c r="D279" t="s">
         <v>377</v>
       </c>
-      <c r="D279" t="s">
+      <c r="E279" t="s">
         <v>378</v>
-      </c>
-      <c r="E279" t="s">
-        <v>333</v>
       </c>
       <c r="F279" t="s">
         <v>24</v>
@@ -9854,13 +9854,13 @@
         <v>7</v>
       </c>
       <c r="C280" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="D280" t="s">
         <v>332</v>
       </c>
       <c r="E280" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="F280" t="s">
         <v>16</v>
@@ -9914,13 +9914,13 @@
         <v>7</v>
       </c>
       <c r="C283" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="D283" t="s">
         <v>332</v>
       </c>
       <c r="E283" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="F283" t="s">
         <v>16</v>
@@ -10014,13 +10014,13 @@
         <v>7</v>
       </c>
       <c r="C288" t="s">
-        <v>371</v>
+        <v>331</v>
       </c>
       <c r="D288" t="s">
         <v>332</v>
       </c>
       <c r="E288" t="s">
-        <v>333</v>
+        <v>371</v>
       </c>
       <c r="F288" t="s">
         <v>16</v>
@@ -10034,13 +10034,13 @@
         <v>7</v>
       </c>
       <c r="C289" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="D289" t="s">
         <v>332</v>
       </c>
       <c r="E289" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="F289" t="s">
         <v>16</v>
@@ -10094,13 +10094,13 @@
         <v>7</v>
       </c>
       <c r="C292" t="s">
-        <v>371</v>
+        <v>331</v>
       </c>
       <c r="D292" t="s">
         <v>332</v>
       </c>
       <c r="E292" t="s">
-        <v>333</v>
+        <v>371</v>
       </c>
       <c r="F292" t="s">
         <v>16</v>
@@ -10114,13 +10114,13 @@
         <v>7</v>
       </c>
       <c r="C293" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="D293" t="s">
         <v>332</v>
       </c>
       <c r="E293" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="F293" t="s">
         <v>16</v>
@@ -10254,13 +10254,13 @@
         <v>7</v>
       </c>
       <c r="C300" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="D300" t="s">
         <v>332</v>
       </c>
       <c r="E300" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="F300" t="s">
         <v>16</v>
@@ -10274,13 +10274,13 @@
         <v>7</v>
       </c>
       <c r="C301" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="D301" t="s">
         <v>332</v>
       </c>
       <c r="E301" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="F301" t="s">
         <v>16</v>
@@ -10294,13 +10294,13 @@
         <v>7</v>
       </c>
       <c r="C302" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="D302" t="s">
         <v>332</v>
       </c>
       <c r="E302" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="F302" t="s">
         <v>16</v>
@@ -10334,13 +10334,13 @@
         <v>7</v>
       </c>
       <c r="C304" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="D304" t="s">
         <v>332</v>
       </c>
       <c r="E304" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="F304" t="s">
         <v>16</v>
@@ -10394,13 +10394,13 @@
         <v>7</v>
       </c>
       <c r="C307" t="s">
+        <v>331</v>
+      </c>
+      <c r="D307" t="s">
+        <v>355</v>
+      </c>
+      <c r="E307" t="s">
         <v>407</v>
-      </c>
-      <c r="D307" t="s">
-        <v>356</v>
-      </c>
-      <c r="E307" t="s">
-        <v>333</v>
       </c>
       <c r="F307" t="s">
         <v>16</v>
@@ -10414,13 +10414,13 @@
         <v>7</v>
       </c>
       <c r="C308" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="D308" t="s">
         <v>332</v>
       </c>
       <c r="E308" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="F308" t="s">
         <v>16</v>
@@ -10714,13 +10714,13 @@
         <v>7</v>
       </c>
       <c r="C323" t="s">
-        <v>427</v>
+        <v>411</v>
       </c>
       <c r="D323" t="s">
         <v>412</v>
       </c>
       <c r="E323" t="s">
-        <v>413</v>
+        <v>427</v>
       </c>
       <c r="F323" t="s">
         <v>16</v>
@@ -11114,13 +11114,13 @@
         <v>7</v>
       </c>
       <c r="C343" t="s">
+        <v>411</v>
+      </c>
+      <c r="D343" t="s">
         <v>450</v>
       </c>
-      <c r="D343" t="s">
+      <c r="E343" t="s">
         <v>451</v>
-      </c>
-      <c r="E343" t="s">
-        <v>413</v>
       </c>
       <c r="F343" t="s">
         <v>24</v>
@@ -11134,13 +11134,13 @@
         <v>110</v>
       </c>
       <c r="C344" t="s">
+        <v>411</v>
+      </c>
+      <c r="D344" t="s">
+        <v>450</v>
+      </c>
+      <c r="E344" t="s">
         <v>453</v>
-      </c>
-      <c r="D344" t="s">
-        <v>451</v>
-      </c>
-      <c r="E344" t="s">
-        <v>413</v>
       </c>
       <c r="F344" t="s">
         <v>24</v>
@@ -11174,13 +11174,13 @@
         <v>110</v>
       </c>
       <c r="C346" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="D346" t="s">
         <v>456</v>
       </c>
       <c r="E346" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="F346" t="s">
         <v>16</v>
@@ -11374,13 +11374,13 @@
         <v>7</v>
       </c>
       <c r="C356" t="s">
-        <v>470</v>
+        <v>455</v>
       </c>
       <c r="D356" t="s">
         <v>456</v>
       </c>
       <c r="E356" t="s">
-        <v>457</v>
+        <v>470</v>
       </c>
       <c r="F356" t="s">
         <v>16</v>
@@ -11574,13 +11574,13 @@
         <v>7</v>
       </c>
       <c r="C366" t="s">
-        <v>481</v>
+        <v>455</v>
       </c>
       <c r="D366" t="s">
         <v>456</v>
       </c>
       <c r="E366" t="s">
-        <v>457</v>
+        <v>481</v>
       </c>
       <c r="F366" t="s">
         <v>16</v>
@@ -11594,13 +11594,13 @@
         <v>7</v>
       </c>
       <c r="C367" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="D367" t="s">
         <v>456</v>
       </c>
       <c r="E367" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="F367" t="s">
         <v>13</v>
@@ -11694,13 +11694,13 @@
         <v>7</v>
       </c>
       <c r="C372" t="s">
+        <v>455</v>
+      </c>
+      <c r="D372" t="s">
         <v>489</v>
       </c>
-      <c r="D372" t="s">
+      <c r="E372" t="s">
         <v>490</v>
-      </c>
-      <c r="E372" t="s">
-        <v>457</v>
       </c>
       <c r="F372" t="s">
         <v>19</v>
@@ -11734,13 +11734,13 @@
         <v>110</v>
       </c>
       <c r="C374" t="s">
+        <v>455</v>
+      </c>
+      <c r="D374" t="s">
         <v>489</v>
       </c>
-      <c r="D374" t="s">
+      <c r="E374" t="s">
         <v>490</v>
-      </c>
-      <c r="E374" t="s">
-        <v>457</v>
       </c>
       <c r="F374" t="s">
         <v>19</v>
@@ -11854,13 +11854,13 @@
         <v>7</v>
       </c>
       <c r="C380" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
       <c r="D380" t="s">
         <v>498</v>
       </c>
       <c r="E380" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="F380" t="s">
         <v>13</v>
@@ -11974,13 +11974,13 @@
         <v>7</v>
       </c>
       <c r="C386" t="s">
-        <v>509</v>
+        <v>497</v>
       </c>
       <c r="D386" t="s">
         <v>498</v>
       </c>
       <c r="E386" t="s">
-        <v>499</v>
+        <v>509</v>
       </c>
       <c r="F386" t="s">
         <v>16</v>
@@ -11994,13 +11994,13 @@
         <v>7</v>
       </c>
       <c r="C387" t="s">
-        <v>511</v>
+        <v>497</v>
       </c>
       <c r="D387" t="s">
         <v>498</v>
       </c>
       <c r="E387" t="s">
-        <v>499</v>
+        <v>511</v>
       </c>
       <c r="F387" t="s">
         <v>19</v>
@@ -12034,13 +12034,13 @@
         <v>7</v>
       </c>
       <c r="C389" t="s">
+        <v>497</v>
+      </c>
+      <c r="D389" t="s">
         <v>514</v>
       </c>
-      <c r="D389" t="s">
+      <c r="E389" t="s">
         <v>515</v>
-      </c>
-      <c r="E389" t="s">
-        <v>499</v>
       </c>
       <c r="F389" t="s">
         <v>24</v>
@@ -12114,13 +12114,13 @@
         <v>7</v>
       </c>
       <c r="C393" t="s">
-        <v>520</v>
+        <v>497</v>
       </c>
       <c r="D393" t="s">
         <v>498</v>
       </c>
       <c r="E393" t="s">
-        <v>499</v>
+        <v>520</v>
       </c>
       <c r="F393" t="s">
         <v>16</v>
@@ -12154,13 +12154,13 @@
         <v>7</v>
       </c>
       <c r="C395" t="s">
+        <v>497</v>
+      </c>
+      <c r="D395" t="s">
         <v>523</v>
       </c>
-      <c r="D395" t="s">
+      <c r="E395" t="s">
         <v>524</v>
-      </c>
-      <c r="E395" t="s">
-        <v>499</v>
       </c>
       <c r="F395" t="s">
         <v>24</v>
@@ -12194,13 +12194,13 @@
         <v>7</v>
       </c>
       <c r="C397" t="s">
+        <v>497</v>
+      </c>
+      <c r="D397" t="s">
         <v>527</v>
       </c>
-      <c r="D397" t="s">
+      <c r="E397" t="s">
         <v>528</v>
-      </c>
-      <c r="E397" t="s">
-        <v>499</v>
       </c>
       <c r="F397" t="s">
         <v>24</v>
@@ -12254,13 +12254,13 @@
         <v>7</v>
       </c>
       <c r="C400" t="s">
+        <v>497</v>
+      </c>
+      <c r="D400" t="s">
         <v>532</v>
       </c>
-      <c r="D400" t="s">
+      <c r="E400" t="s">
         <v>533</v>
-      </c>
-      <c r="E400" t="s">
-        <v>499</v>
       </c>
       <c r="F400" t="s">
         <v>24</v>
@@ -12374,13 +12374,13 @@
         <v>7</v>
       </c>
       <c r="C406" t="s">
+        <v>497</v>
+      </c>
+      <c r="D406" t="s">
         <v>540</v>
       </c>
-      <c r="D406" t="s">
+      <c r="E406" t="s">
         <v>541</v>
-      </c>
-      <c r="E406" t="s">
-        <v>499</v>
       </c>
       <c r="F406" t="s">
         <v>24</v>
@@ -12394,13 +12394,13 @@
         <v>7</v>
       </c>
       <c r="C407" t="s">
-        <v>543</v>
+        <v>497</v>
       </c>
       <c r="D407" t="s">
         <v>498</v>
       </c>
       <c r="E407" t="s">
-        <v>499</v>
+        <v>543</v>
       </c>
       <c r="F407" t="s">
         <v>19</v>
@@ -12634,13 +12634,13 @@
         <v>7</v>
       </c>
       <c r="C419" t="s">
-        <v>559</v>
+        <v>554</v>
       </c>
       <c r="D419" t="s">
         <v>555</v>
       </c>
       <c r="E419" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="F419" t="s">
         <v>24</v>
@@ -12674,13 +12674,13 @@
         <v>7</v>
       </c>
       <c r="C421" t="s">
-        <v>562</v>
+        <v>554</v>
       </c>
       <c r="D421" t="s">
         <v>555</v>
       </c>
       <c r="E421" t="s">
-        <v>556</v>
+        <v>562</v>
       </c>
       <c r="F421" t="s">
         <v>19</v>
@@ -12814,13 +12814,13 @@
         <v>7</v>
       </c>
       <c r="C428" t="s">
+        <v>554</v>
+      </c>
+      <c r="D428" t="s">
         <v>570</v>
       </c>
-      <c r="D428" t="s">
+      <c r="E428" t="s">
         <v>571</v>
-      </c>
-      <c r="E428" t="s">
-        <v>556</v>
       </c>
       <c r="F428" t="s">
         <v>24</v>
@@ -12834,13 +12834,13 @@
         <v>7</v>
       </c>
       <c r="C429" t="s">
+        <v>554</v>
+      </c>
+      <c r="D429" t="s">
         <v>573</v>
       </c>
-      <c r="D429" t="s">
+      <c r="E429" t="s">
         <v>574</v>
-      </c>
-      <c r="E429" t="s">
-        <v>556</v>
       </c>
       <c r="F429" t="s">
         <v>24</v>
@@ -12914,13 +12914,13 @@
         <v>7</v>
       </c>
       <c r="C433" t="s">
-        <v>579</v>
+        <v>554</v>
       </c>
       <c r="D433" t="s">
         <v>555</v>
       </c>
       <c r="E433" t="s">
-        <v>556</v>
+        <v>579</v>
       </c>
       <c r="F433" t="s">
         <v>24</v>
@@ -12974,13 +12974,13 @@
         <v>7</v>
       </c>
       <c r="C436" t="s">
-        <v>583</v>
+        <v>554</v>
       </c>
       <c r="D436" t="s">
         <v>555</v>
       </c>
       <c r="E436" t="s">
-        <v>556</v>
+        <v>583</v>
       </c>
       <c r="F436" t="s">
         <v>24</v>
@@ -12994,13 +12994,13 @@
         <v>7</v>
       </c>
       <c r="C437" t="s">
-        <v>585</v>
+        <v>554</v>
       </c>
       <c r="D437" t="s">
         <v>555</v>
       </c>
       <c r="E437" t="s">
-        <v>556</v>
+        <v>585</v>
       </c>
       <c r="F437" t="s">
         <v>19</v>
@@ -13054,13 +13054,13 @@
         <v>7</v>
       </c>
       <c r="C440" t="s">
+        <v>554</v>
+      </c>
+      <c r="D440" t="s">
         <v>589</v>
       </c>
-      <c r="D440" t="s">
+      <c r="E440" t="s">
         <v>590</v>
-      </c>
-      <c r="E440" t="s">
-        <v>556</v>
       </c>
       <c r="F440" t="s">
         <v>24</v>
@@ -13334,13 +13334,13 @@
         <v>7</v>
       </c>
       <c r="C454" t="s">
+        <v>554</v>
+      </c>
+      <c r="D454" t="s">
         <v>605</v>
       </c>
-      <c r="D454" t="s">
+      <c r="E454" t="s">
         <v>606</v>
-      </c>
-      <c r="E454" t="s">
-        <v>556</v>
       </c>
       <c r="F454" t="s">
         <v>19</v>
@@ -13534,13 +13534,13 @@
         <v>7</v>
       </c>
       <c r="C464" t="s">
+        <v>608</v>
+      </c>
+      <c r="D464" t="s">
         <v>621</v>
       </c>
-      <c r="D464" t="s">
+      <c r="E464" t="s">
         <v>622</v>
-      </c>
-      <c r="E464" t="s">
-        <v>610</v>
       </c>
       <c r="F464" t="s">
         <v>24</v>
@@ -13554,13 +13554,13 @@
         <v>7</v>
       </c>
       <c r="C465" t="s">
-        <v>624</v>
+        <v>608</v>
       </c>
       <c r="D465" t="s">
         <v>609</v>
       </c>
       <c r="E465" t="s">
-        <v>610</v>
+        <v>624</v>
       </c>
       <c r="F465" t="s">
         <v>24</v>
@@ -13574,13 +13574,13 @@
         <v>7</v>
       </c>
       <c r="C466" t="s">
+        <v>608</v>
+      </c>
+      <c r="D466" t="s">
+        <v>621</v>
+      </c>
+      <c r="E466" t="s">
         <v>626</v>
-      </c>
-      <c r="D466" t="s">
-        <v>622</v>
-      </c>
-      <c r="E466" t="s">
-        <v>610</v>
       </c>
       <c r="F466" t="s">
         <v>24</v>
@@ -13594,13 +13594,13 @@
         <v>7</v>
       </c>
       <c r="C467" t="s">
+        <v>608</v>
+      </c>
+      <c r="D467" t="s">
         <v>628</v>
       </c>
-      <c r="D467" t="s">
+      <c r="E467" t="s">
         <v>629</v>
-      </c>
-      <c r="E467" t="s">
-        <v>610</v>
       </c>
       <c r="F467" t="s">
         <v>24</v>
@@ -13634,13 +13634,13 @@
         <v>7</v>
       </c>
       <c r="C469" t="s">
+        <v>608</v>
+      </c>
+      <c r="D469" t="s">
         <v>632</v>
       </c>
-      <c r="D469" t="s">
+      <c r="E469" t="s">
         <v>633</v>
-      </c>
-      <c r="E469" t="s">
-        <v>610</v>
       </c>
       <c r="F469" t="s">
         <v>24</v>
@@ -13714,13 +13714,13 @@
         <v>7</v>
       </c>
       <c r="C473" t="s">
+        <v>608</v>
+      </c>
+      <c r="D473" t="s">
+        <v>621</v>
+      </c>
+      <c r="E473" t="s">
         <v>638</v>
-      </c>
-      <c r="D473" t="s">
-        <v>622</v>
-      </c>
-      <c r="E473" t="s">
-        <v>610</v>
       </c>
       <c r="F473" t="s">
         <v>24</v>
@@ -14014,13 +14014,13 @@
         <v>7</v>
       </c>
       <c r="C488" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="D488" t="s">
         <v>654</v>
       </c>
       <c r="E488" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="F488" t="s">
         <v>611</v>
@@ -14134,13 +14134,13 @@
         <v>7</v>
       </c>
       <c r="C494" t="s">
-        <v>632</v>
+        <v>653</v>
       </c>
       <c r="D494" t="s">
         <v>665</v>
       </c>
       <c r="E494" t="s">
-        <v>655</v>
+        <v>633</v>
       </c>
       <c r="F494" t="s">
         <v>13</v>
@@ -14154,13 +14154,13 @@
         <v>110</v>
       </c>
       <c r="C495" t="s">
-        <v>632</v>
+        <v>653</v>
       </c>
       <c r="D495" t="s">
         <v>665</v>
       </c>
       <c r="E495" t="s">
-        <v>655</v>
+        <v>633</v>
       </c>
       <c r="F495" t="s">
         <v>16</v>
@@ -14214,13 +14214,13 @@
         <v>7</v>
       </c>
       <c r="C498" t="s">
-        <v>670</v>
+        <v>653</v>
       </c>
       <c r="D498" t="s">
         <v>654</v>
       </c>
       <c r="E498" t="s">
-        <v>655</v>
+        <v>670</v>
       </c>
       <c r="F498" t="s">
         <v>611</v>
@@ -14294,13 +14294,13 @@
         <v>110</v>
       </c>
       <c r="C502" t="s">
-        <v>675</v>
+        <v>653</v>
       </c>
       <c r="D502" t="s">
         <v>654</v>
       </c>
       <c r="E502" t="s">
-        <v>655</v>
+        <v>675</v>
       </c>
       <c r="F502" t="s">
         <v>19</v>
@@ -14394,13 +14394,13 @@
         <v>7</v>
       </c>
       <c r="C507" t="s">
+        <v>653</v>
+      </c>
+      <c r="D507" t="s">
         <v>681</v>
       </c>
-      <c r="D507" t="s">
+      <c r="E507" t="s">
         <v>682</v>
-      </c>
-      <c r="E507" t="s">
-        <v>655</v>
       </c>
       <c r="F507" t="s">
         <v>24</v>
@@ -14414,13 +14414,13 @@
         <v>7</v>
       </c>
       <c r="C508" t="s">
+        <v>653</v>
+      </c>
+      <c r="D508" t="s">
         <v>684</v>
       </c>
-      <c r="D508" t="s">
+      <c r="E508" t="s">
         <v>685</v>
-      </c>
-      <c r="E508" t="s">
-        <v>655</v>
       </c>
       <c r="F508" t="s">
         <v>611</v>
@@ -14434,13 +14434,13 @@
         <v>110</v>
       </c>
       <c r="C509" t="s">
-        <v>684</v>
+        <v>653</v>
       </c>
       <c r="D509" t="s">
         <v>687</v>
       </c>
       <c r="E509" t="s">
-        <v>655</v>
+        <v>685</v>
       </c>
       <c r="F509" t="s">
         <v>19</v>
@@ -14454,13 +14454,13 @@
         <v>7</v>
       </c>
       <c r="C510" t="s">
+        <v>653</v>
+      </c>
+      <c r="D510" t="s">
         <v>689</v>
       </c>
-      <c r="D510" t="s">
+      <c r="E510" t="s">
         <v>690</v>
-      </c>
-      <c r="E510" t="s">
-        <v>655</v>
       </c>
       <c r="F510" t="s">
         <v>24</v>
@@ -14494,13 +14494,13 @@
         <v>7</v>
       </c>
       <c r="C512" t="s">
-        <v>693</v>
+        <v>653</v>
       </c>
       <c r="D512" t="s">
         <v>654</v>
       </c>
       <c r="E512" t="s">
-        <v>655</v>
+        <v>693</v>
       </c>
       <c r="F512" t="s">
         <v>16</v>
@@ -14674,13 +14674,13 @@
         <v>110</v>
       </c>
       <c r="C521" t="s">
-        <v>704</v>
+        <v>653</v>
       </c>
       <c r="D521" t="s">
         <v>654</v>
       </c>
       <c r="E521" t="s">
-        <v>655</v>
+        <v>704</v>
       </c>
       <c r="F521" t="s">
         <v>19</v>
@@ -14694,13 +14694,13 @@
         <v>110</v>
       </c>
       <c r="C522" t="s">
-        <v>706</v>
+        <v>653</v>
       </c>
       <c r="D522" t="s">
         <v>654</v>
       </c>
       <c r="E522" t="s">
-        <v>655</v>
+        <v>706</v>
       </c>
       <c r="F522" t="s">
         <v>13</v>
@@ -14714,13 +14714,13 @@
         <v>7</v>
       </c>
       <c r="C523" t="s">
-        <v>708</v>
+        <v>653</v>
       </c>
       <c r="D523" t="s">
         <v>654</v>
       </c>
       <c r="E523" t="s">
-        <v>655</v>
+        <v>708</v>
       </c>
       <c r="F523" t="s">
         <v>24</v>
@@ -14754,13 +14754,13 @@
         <v>7</v>
       </c>
       <c r="C525" t="s">
+        <v>711</v>
+      </c>
+      <c r="D525" t="s">
+        <v>712</v>
+      </c>
+      <c r="E525" t="s">
         <v>657</v>
-      </c>
-      <c r="D525" t="s">
-        <v>711</v>
-      </c>
-      <c r="E525" t="s">
-        <v>712</v>
       </c>
       <c r="F525" t="s">
         <v>713</v>
@@ -14774,13 +14774,13 @@
         <v>7</v>
       </c>
       <c r="C526" t="s">
+        <v>711</v>
+      </c>
+      <c r="D526" t="s">
+        <v>712</v>
+      </c>
+      <c r="E526" t="s">
         <v>657</v>
-      </c>
-      <c r="D526" t="s">
-        <v>711</v>
-      </c>
-      <c r="E526" t="s">
-        <v>712</v>
       </c>
       <c r="F526" t="s">
         <v>713</v>
@@ -14794,13 +14794,13 @@
         <v>7</v>
       </c>
       <c r="C527" t="s">
+        <v>711</v>
+      </c>
+      <c r="D527" t="s">
+        <v>712</v>
+      </c>
+      <c r="E527" t="s">
         <v>657</v>
-      </c>
-      <c r="D527" t="s">
-        <v>711</v>
-      </c>
-      <c r="E527" t="s">
-        <v>712</v>
       </c>
       <c r="F527" t="s">
         <v>713</v>
@@ -14814,13 +14814,13 @@
         <v>7</v>
       </c>
       <c r="C528" t="s">
+        <v>711</v>
+      </c>
+      <c r="D528" t="s">
+        <v>712</v>
+      </c>
+      <c r="E528" t="s">
         <v>657</v>
-      </c>
-      <c r="D528" t="s">
-        <v>711</v>
-      </c>
-      <c r="E528" t="s">
-        <v>712</v>
       </c>
       <c r="F528" t="s">
         <v>713</v>
@@ -14834,13 +14834,13 @@
         <v>7</v>
       </c>
       <c r="C529" t="s">
+        <v>711</v>
+      </c>
+      <c r="D529" t="s">
+        <v>712</v>
+      </c>
+      <c r="E529" t="s">
         <v>718</v>
-      </c>
-      <c r="D529" t="s">
-        <v>711</v>
-      </c>
-      <c r="E529" t="s">
-        <v>712</v>
       </c>
       <c r="F529" t="s">
         <v>16</v>
@@ -14854,13 +14854,13 @@
         <v>7</v>
       </c>
       <c r="C530" t="s">
-        <v>657</v>
+        <v>711</v>
       </c>
       <c r="D530" t="s">
         <v>720</v>
       </c>
       <c r="E530" t="s">
-        <v>712</v>
+        <v>657</v>
       </c>
       <c r="F530" t="s">
         <v>713</v>
@@ -14874,13 +14874,13 @@
         <v>7</v>
       </c>
       <c r="C531" t="s">
+        <v>711</v>
+      </c>
+      <c r="D531" t="s">
+        <v>712</v>
+      </c>
+      <c r="E531" t="s">
         <v>657</v>
-      </c>
-      <c r="D531" t="s">
-        <v>711</v>
-      </c>
-      <c r="E531" t="s">
-        <v>712</v>
       </c>
       <c r="F531" t="s">
         <v>713</v>
@@ -14894,13 +14894,13 @@
         <v>7</v>
       </c>
       <c r="C532" t="s">
+        <v>711</v>
+      </c>
+      <c r="D532" t="s">
+        <v>712</v>
+      </c>
+      <c r="E532" t="s">
         <v>657</v>
-      </c>
-      <c r="D532" t="s">
-        <v>711</v>
-      </c>
-      <c r="E532" t="s">
-        <v>712</v>
       </c>
       <c r="F532" t="s">
         <v>713</v>
@@ -14914,13 +14914,13 @@
         <v>7</v>
       </c>
       <c r="C533" t="s">
+        <v>711</v>
+      </c>
+      <c r="D533" t="s">
+        <v>712</v>
+      </c>
+      <c r="E533" t="s">
         <v>657</v>
-      </c>
-      <c r="D533" t="s">
-        <v>711</v>
-      </c>
-      <c r="E533" t="s">
-        <v>712</v>
       </c>
       <c r="F533" t="s">
         <v>713</v>
@@ -14934,13 +14934,13 @@
         <v>7</v>
       </c>
       <c r="C534" t="s">
+        <v>711</v>
+      </c>
+      <c r="D534" t="s">
+        <v>712</v>
+      </c>
+      <c r="E534" t="s">
         <v>657</v>
-      </c>
-      <c r="D534" t="s">
-        <v>711</v>
-      </c>
-      <c r="E534" t="s">
-        <v>712</v>
       </c>
       <c r="F534" t="s">
         <v>713</v>
@@ -14954,13 +14954,13 @@
         <v>7</v>
       </c>
       <c r="C535" t="s">
+        <v>711</v>
+      </c>
+      <c r="D535" t="s">
+        <v>712</v>
+      </c>
+      <c r="E535" t="s">
         <v>657</v>
-      </c>
-      <c r="D535" t="s">
-        <v>711</v>
-      </c>
-      <c r="E535" t="s">
-        <v>712</v>
       </c>
       <c r="F535" t="s">
         <v>713</v>
@@ -14974,13 +14974,13 @@
         <v>7</v>
       </c>
       <c r="C536" t="s">
+        <v>711</v>
+      </c>
+      <c r="D536" t="s">
+        <v>712</v>
+      </c>
+      <c r="E536" t="s">
         <v>727</v>
-      </c>
-      <c r="D536" t="s">
-        <v>711</v>
-      </c>
-      <c r="E536" t="s">
-        <v>712</v>
       </c>
       <c r="F536" t="s">
         <v>16</v>
@@ -14994,13 +14994,13 @@
         <v>7</v>
       </c>
       <c r="C537" t="s">
+        <v>711</v>
+      </c>
+      <c r="D537" t="s">
+        <v>712</v>
+      </c>
+      <c r="E537" t="s">
         <v>729</v>
-      </c>
-      <c r="D537" t="s">
-        <v>711</v>
-      </c>
-      <c r="E537" t="s">
-        <v>712</v>
       </c>
       <c r="F537" t="s">
         <v>16</v>
@@ -15014,13 +15014,13 @@
         <v>7</v>
       </c>
       <c r="C538" t="s">
+        <v>711</v>
+      </c>
+      <c r="D538" t="s">
+        <v>712</v>
+      </c>
+      <c r="E538" t="s">
         <v>657</v>
-      </c>
-      <c r="D538" t="s">
-        <v>711</v>
-      </c>
-      <c r="E538" t="s">
-        <v>712</v>
       </c>
       <c r="F538" t="s">
         <v>713</v>
@@ -15034,13 +15034,13 @@
         <v>7</v>
       </c>
       <c r="C539" t="s">
+        <v>711</v>
+      </c>
+      <c r="D539" t="s">
+        <v>712</v>
+      </c>
+      <c r="E539" t="s">
         <v>657</v>
-      </c>
-      <c r="D539" t="s">
-        <v>711</v>
-      </c>
-      <c r="E539" t="s">
-        <v>712</v>
       </c>
       <c r="F539" t="s">
         <v>713</v>
@@ -15054,13 +15054,13 @@
         <v>7</v>
       </c>
       <c r="C540" t="s">
+        <v>711</v>
+      </c>
+      <c r="D540" t="s">
+        <v>689</v>
+      </c>
+      <c r="E540" t="s">
         <v>657</v>
-      </c>
-      <c r="D540" t="s">
-        <v>690</v>
-      </c>
-      <c r="E540" t="s">
-        <v>712</v>
       </c>
       <c r="F540" t="s">
         <v>713</v>
@@ -15074,13 +15074,13 @@
         <v>7</v>
       </c>
       <c r="C541" t="s">
+        <v>711</v>
+      </c>
+      <c r="D541" t="s">
+        <v>712</v>
+      </c>
+      <c r="E541" t="s">
         <v>657</v>
-      </c>
-      <c r="D541" t="s">
-        <v>711</v>
-      </c>
-      <c r="E541" t="s">
-        <v>712</v>
       </c>
       <c r="F541" t="s">
         <v>713</v>
@@ -15094,13 +15094,13 @@
         <v>7</v>
       </c>
       <c r="C542" t="s">
+        <v>711</v>
+      </c>
+      <c r="D542" t="s">
+        <v>712</v>
+      </c>
+      <c r="E542" t="s">
         <v>657</v>
-      </c>
-      <c r="D542" t="s">
-        <v>711</v>
-      </c>
-      <c r="E542" t="s">
-        <v>712</v>
       </c>
       <c r="F542" t="s">
         <v>713</v>
@@ -15114,13 +15114,13 @@
         <v>7</v>
       </c>
       <c r="C543" t="s">
+        <v>711</v>
+      </c>
+      <c r="D543" t="s">
+        <v>712</v>
+      </c>
+      <c r="E543" t="s">
         <v>657</v>
-      </c>
-      <c r="D543" t="s">
-        <v>711</v>
-      </c>
-      <c r="E543" t="s">
-        <v>712</v>
       </c>
       <c r="F543" t="s">
         <v>713</v>
@@ -15134,13 +15134,13 @@
         <v>7</v>
       </c>
       <c r="C544" t="s">
+        <v>711</v>
+      </c>
+      <c r="D544" t="s">
+        <v>712</v>
+      </c>
+      <c r="E544" t="s">
         <v>657</v>
-      </c>
-      <c r="D544" t="s">
-        <v>711</v>
-      </c>
-      <c r="E544" t="s">
-        <v>712</v>
       </c>
       <c r="F544" t="s">
         <v>713</v>
@@ -15154,13 +15154,13 @@
         <v>7</v>
       </c>
       <c r="C545" t="s">
-        <v>657</v>
+        <v>711</v>
       </c>
       <c r="D545" t="s">
         <v>738</v>
       </c>
       <c r="E545" t="s">
-        <v>712</v>
+        <v>657</v>
       </c>
       <c r="F545" t="s">
         <v>13</v>
@@ -15174,13 +15174,13 @@
         <v>7</v>
       </c>
       <c r="C546" t="s">
+        <v>711</v>
+      </c>
+      <c r="D546" t="s">
+        <v>712</v>
+      </c>
+      <c r="E546" t="s">
         <v>657</v>
-      </c>
-      <c r="D546" t="s">
-        <v>711</v>
-      </c>
-      <c r="E546" t="s">
-        <v>712</v>
       </c>
       <c r="F546" t="s">
         <v>713</v>
@@ -15194,13 +15194,13 @@
         <v>7</v>
       </c>
       <c r="C547" t="s">
+        <v>711</v>
+      </c>
+      <c r="D547" t="s">
+        <v>712</v>
+      </c>
+      <c r="E547" t="s">
         <v>657</v>
-      </c>
-      <c r="D547" t="s">
-        <v>711</v>
-      </c>
-      <c r="E547" t="s">
-        <v>712</v>
       </c>
       <c r="F547" t="s">
         <v>16</v>
@@ -15234,13 +15234,13 @@
         <v>7</v>
       </c>
       <c r="C549" t="s">
-        <v>746</v>
+        <v>742</v>
       </c>
       <c r="D549" t="s">
         <v>743</v>
       </c>
       <c r="E549" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="F549" t="s">
         <v>713</v>
@@ -15254,13 +15254,13 @@
         <v>7</v>
       </c>
       <c r="C550" t="s">
-        <v>748</v>
+        <v>742</v>
       </c>
       <c r="D550" t="s">
         <v>743</v>
       </c>
       <c r="E550" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
       <c r="F550" t="s">
         <v>713</v>
@@ -15414,13 +15414,13 @@
         <v>7</v>
       </c>
       <c r="C558" t="s">
+        <v>742</v>
+      </c>
+      <c r="D558" t="s">
         <v>758</v>
       </c>
-      <c r="D558" t="s">
+      <c r="E558" t="s">
         <v>759</v>
-      </c>
-      <c r="E558" t="s">
-        <v>744</v>
       </c>
       <c r="F558" t="s">
         <v>24</v>
@@ -15454,13 +15454,13 @@
         <v>7</v>
       </c>
       <c r="C560" t="s">
-        <v>762</v>
+        <v>742</v>
       </c>
       <c r="D560" t="s">
         <v>743</v>
       </c>
       <c r="E560" t="s">
-        <v>744</v>
+        <v>762</v>
       </c>
       <c r="F560" t="s">
         <v>713</v>
@@ -15474,13 +15474,13 @@
         <v>7</v>
       </c>
       <c r="C561" t="s">
-        <v>762</v>
+        <v>742</v>
       </c>
       <c r="D561" t="s">
         <v>743</v>
       </c>
       <c r="E561" t="s">
-        <v>744</v>
+        <v>762</v>
       </c>
       <c r="F561" t="s">
         <v>713</v>
@@ -15634,13 +15634,13 @@
         <v>7</v>
       </c>
       <c r="C569" t="s">
+        <v>742</v>
+      </c>
+      <c r="D569" t="s">
         <v>773</v>
       </c>
-      <c r="D569" t="s">
+      <c r="E569" t="s">
         <v>774</v>
-      </c>
-      <c r="E569" t="s">
-        <v>744</v>
       </c>
       <c r="F569" t="s">
         <v>713</v>
@@ -15717,7 +15717,7 @@
         <v>779</v>
       </c>
       <c r="D573" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="E573" t="s">
         <v>780</v>
@@ -15814,13 +15814,13 @@
         <v>7</v>
       </c>
       <c r="C578" t="s">
-        <v>787</v>
+        <v>779</v>
       </c>
       <c r="D578" t="s">
         <v>782</v>
       </c>
       <c r="E578" t="s">
-        <v>780</v>
+        <v>787</v>
       </c>
       <c r="F578" t="s">
         <v>713</v>
@@ -15834,13 +15834,13 @@
         <v>7</v>
       </c>
       <c r="C579" t="s">
+        <v>779</v>
+      </c>
+      <c r="D579" t="s">
         <v>789</v>
       </c>
-      <c r="D579" t="s">
+      <c r="E579" t="s">
         <v>790</v>
-      </c>
-      <c r="E579" t="s">
-        <v>780</v>
       </c>
       <c r="F579" t="s">
         <v>24</v>
@@ -15854,13 +15854,13 @@
         <v>7</v>
       </c>
       <c r="C580" t="s">
-        <v>792</v>
+        <v>779</v>
       </c>
       <c r="D580" t="s">
         <v>782</v>
       </c>
       <c r="E580" t="s">
-        <v>780</v>
+        <v>792</v>
       </c>
       <c r="F580" t="s">
         <v>713</v>
@@ -15874,13 +15874,13 @@
         <v>7</v>
       </c>
       <c r="C581" t="s">
-        <v>794</v>
+        <v>779</v>
       </c>
       <c r="D581" t="s">
         <v>782</v>
       </c>
       <c r="E581" t="s">
-        <v>780</v>
+        <v>794</v>
       </c>
       <c r="F581" t="s">
         <v>16</v>
@@ -15914,13 +15914,13 @@
         <v>7</v>
       </c>
       <c r="C583" t="s">
+        <v>779</v>
+      </c>
+      <c r="D583" t="s">
         <v>797</v>
       </c>
-      <c r="D583" t="s">
+      <c r="E583" t="s">
         <v>798</v>
-      </c>
-      <c r="E583" t="s">
-        <v>780</v>
       </c>
       <c r="F583" t="s">
         <v>24</v>
@@ -15934,13 +15934,13 @@
         <v>7</v>
       </c>
       <c r="C584" t="s">
+        <v>779</v>
+      </c>
+      <c r="D584" t="s">
         <v>800</v>
       </c>
-      <c r="D584" t="s">
+      <c r="E584" t="s">
         <v>801</v>
-      </c>
-      <c r="E584" t="s">
-        <v>780</v>
       </c>
       <c r="F584" t="s">
         <v>24</v>
@@ -15974,13 +15974,13 @@
         <v>7</v>
       </c>
       <c r="C586" t="s">
+        <v>779</v>
+      </c>
+      <c r="D586" t="s">
         <v>804</v>
       </c>
-      <c r="D586" t="s">
+      <c r="E586" t="s">
         <v>805</v>
-      </c>
-      <c r="E586" t="s">
-        <v>780</v>
       </c>
       <c r="F586" t="s">
         <v>24</v>
@@ -15994,13 +15994,13 @@
         <v>7</v>
       </c>
       <c r="C587" t="s">
-        <v>807</v>
+        <v>779</v>
       </c>
       <c r="D587" t="s">
         <v>782</v>
       </c>
       <c r="E587" t="s">
-        <v>780</v>
+        <v>807</v>
       </c>
       <c r="F587" t="s">
         <v>13</v>
@@ -16014,13 +16014,13 @@
         <v>7</v>
       </c>
       <c r="C588" t="s">
-        <v>809</v>
+        <v>779</v>
       </c>
       <c r="D588" t="s">
         <v>782</v>
       </c>
       <c r="E588" t="s">
-        <v>780</v>
+        <v>809</v>
       </c>
       <c r="F588" t="s">
         <v>713</v>
@@ -16214,13 +16214,13 @@
         <v>7</v>
       </c>
       <c r="C598" t="s">
+        <v>820</v>
+      </c>
+      <c r="D598" t="s">
         <v>824</v>
       </c>
-      <c r="D598" t="s">
+      <c r="E598" t="s">
         <v>825</v>
-      </c>
-      <c r="E598" t="s">
-        <v>822</v>
       </c>
       <c r="F598" t="s">
         <v>16</v>
@@ -16294,13 +16294,13 @@
         <v>7</v>
       </c>
       <c r="C602" t="s">
+        <v>820</v>
+      </c>
+      <c r="D602" t="s">
         <v>830</v>
       </c>
-      <c r="D602" t="s">
+      <c r="E602" t="s">
         <v>831</v>
-      </c>
-      <c r="E602" t="s">
-        <v>822</v>
       </c>
       <c r="F602" t="s">
         <v>24</v>
@@ -16314,13 +16314,13 @@
         <v>7</v>
       </c>
       <c r="C603" t="s">
+        <v>820</v>
+      </c>
+      <c r="D603" t="s">
         <v>833</v>
       </c>
-      <c r="D603" t="s">
+      <c r="E603" t="s">
         <v>834</v>
-      </c>
-      <c r="E603" t="s">
-        <v>822</v>
       </c>
       <c r="F603" t="s">
         <v>24</v>
@@ -16334,13 +16334,13 @@
         <v>7</v>
       </c>
       <c r="C604" t="s">
+        <v>820</v>
+      </c>
+      <c r="D604" t="s">
         <v>836</v>
       </c>
-      <c r="D604" t="s">
+      <c r="E604" t="s">
         <v>837</v>
-      </c>
-      <c r="E604" t="s">
-        <v>822</v>
       </c>
       <c r="F604" t="s">
         <v>713</v>
@@ -16354,13 +16354,13 @@
         <v>7</v>
       </c>
       <c r="C605" t="s">
-        <v>839</v>
+        <v>820</v>
       </c>
       <c r="D605" t="s">
         <v>821</v>
       </c>
       <c r="E605" t="s">
-        <v>822</v>
+        <v>839</v>
       </c>
       <c r="F605" t="s">
         <v>24</v>
@@ -16414,13 +16414,13 @@
         <v>7</v>
       </c>
       <c r="C608" t="s">
+        <v>820</v>
+      </c>
+      <c r="D608" t="s">
         <v>843</v>
       </c>
-      <c r="D608" t="s">
+      <c r="E608" t="s">
         <v>844</v>
-      </c>
-      <c r="E608" t="s">
-        <v>822</v>
       </c>
       <c r="F608" t="s">
         <v>24</v>
@@ -16434,13 +16434,13 @@
         <v>7</v>
       </c>
       <c r="C609" t="s">
-        <v>846</v>
+        <v>820</v>
       </c>
       <c r="D609" t="s">
         <v>807</v>
       </c>
       <c r="E609" t="s">
-        <v>822</v>
+        <v>846</v>
       </c>
       <c r="F609" t="s">
         <v>713</v>
@@ -16474,13 +16474,13 @@
         <v>7</v>
       </c>
       <c r="C611" t="s">
-        <v>824</v>
+        <v>820</v>
       </c>
       <c r="D611" t="s">
         <v>849</v>
       </c>
       <c r="E611" t="s">
-        <v>822</v>
+        <v>825</v>
       </c>
       <c r="F611" t="s">
         <v>24</v>
@@ -16494,13 +16494,13 @@
         <v>7</v>
       </c>
       <c r="C612" t="s">
-        <v>851</v>
+        <v>820</v>
       </c>
       <c r="D612" t="s">
         <v>821</v>
       </c>
       <c r="E612" t="s">
-        <v>822</v>
+        <v>851</v>
       </c>
       <c r="F612" t="s">
         <v>16</v>
@@ -16534,13 +16534,13 @@
         <v>7</v>
       </c>
       <c r="C614" t="s">
-        <v>854</v>
+        <v>820</v>
       </c>
       <c r="D614" t="s">
         <v>821</v>
       </c>
       <c r="E614" t="s">
-        <v>822</v>
+        <v>854</v>
       </c>
       <c r="F614" t="s">
         <v>713</v>
@@ -16734,13 +16734,13 @@
         <v>7</v>
       </c>
       <c r="C624" t="s">
+        <v>864</v>
+      </c>
+      <c r="D624" t="s">
         <v>868</v>
       </c>
-      <c r="D624" t="s">
+      <c r="E624" t="s">
         <v>869</v>
-      </c>
-      <c r="E624" t="s">
-        <v>866</v>
       </c>
       <c r="F624" t="s">
         <v>24</v>
@@ -16834,13 +16834,13 @@
         <v>7</v>
       </c>
       <c r="C629" t="s">
-        <v>876</v>
+        <v>864</v>
       </c>
       <c r="D629" t="s">
         <v>865</v>
       </c>
       <c r="E629" t="s">
-        <v>866</v>
+        <v>876</v>
       </c>
       <c r="F629" t="s">
         <v>24</v>
@@ -16894,13 +16894,13 @@
         <v>7</v>
       </c>
       <c r="C632" t="s">
-        <v>876</v>
+        <v>864</v>
       </c>
       <c r="D632" t="s">
         <v>880</v>
       </c>
       <c r="E632" t="s">
-        <v>866</v>
+        <v>876</v>
       </c>
       <c r="F632" t="s">
         <v>24</v>
@@ -16914,13 +16914,13 @@
         <v>7</v>
       </c>
       <c r="C633" t="s">
+        <v>864</v>
+      </c>
+      <c r="D633" t="s">
         <v>882</v>
       </c>
-      <c r="D633" t="s">
+      <c r="E633" t="s">
         <v>883</v>
-      </c>
-      <c r="E633" t="s">
-        <v>866</v>
       </c>
       <c r="F633" t="s">
         <v>24</v>
@@ -16934,13 +16934,13 @@
         <v>7</v>
       </c>
       <c r="C634" t="s">
+        <v>864</v>
+      </c>
+      <c r="D634" t="s">
         <v>885</v>
       </c>
-      <c r="D634" t="s">
+      <c r="E634" t="s">
         <v>886</v>
-      </c>
-      <c r="E634" t="s">
-        <v>866</v>
       </c>
       <c r="F634" t="s">
         <v>24</v>
@@ -16974,13 +16974,13 @@
         <v>7</v>
       </c>
       <c r="C636" t="s">
-        <v>889</v>
+        <v>864</v>
       </c>
       <c r="D636" t="s">
         <v>865</v>
       </c>
       <c r="E636" t="s">
-        <v>866</v>
+        <v>889</v>
       </c>
       <c r="F636" t="s">
         <v>713</v>
@@ -16994,13 +16994,13 @@
         <v>7</v>
       </c>
       <c r="C637" t="s">
+        <v>864</v>
+      </c>
+      <c r="D637" t="s">
         <v>891</v>
       </c>
-      <c r="D637" t="s">
+      <c r="E637" t="s">
         <v>892</v>
-      </c>
-      <c r="E637" t="s">
-        <v>866</v>
       </c>
       <c r="F637" t="s">
         <v>24</v>
@@ -17074,13 +17074,13 @@
         <v>7</v>
       </c>
       <c r="C641" t="s">
+        <v>864</v>
+      </c>
+      <c r="D641" t="s">
         <v>897</v>
       </c>
-      <c r="D641" t="s">
+      <c r="E641" t="s">
         <v>898</v>
-      </c>
-      <c r="E641" t="s">
-        <v>866</v>
       </c>
       <c r="F641" t="s">
         <v>16</v>
@@ -17094,13 +17094,13 @@
         <v>7</v>
       </c>
       <c r="C642" t="s">
-        <v>900</v>
+        <v>864</v>
       </c>
       <c r="D642" t="s">
         <v>865</v>
       </c>
       <c r="E642" t="s">
-        <v>866</v>
+        <v>900</v>
       </c>
       <c r="F642" t="s">
         <v>16</v>
@@ -17114,13 +17114,13 @@
         <v>7</v>
       </c>
       <c r="C643" t="s">
-        <v>902</v>
+        <v>864</v>
       </c>
       <c r="D643" t="s">
         <v>865</v>
       </c>
       <c r="E643" t="s">
-        <v>866</v>
+        <v>902</v>
       </c>
       <c r="F643" t="s">
         <v>16</v>
@@ -17174,13 +17174,13 @@
         <v>7</v>
       </c>
       <c r="C646" t="s">
-        <v>906</v>
+        <v>864</v>
       </c>
       <c r="D646" t="s">
         <v>865</v>
       </c>
       <c r="E646" t="s">
-        <v>866</v>
+        <v>906</v>
       </c>
       <c r="F646" t="s">
         <v>24</v>
@@ -17254,13 +17254,13 @@
         <v>7</v>
       </c>
       <c r="C650" t="s">
+        <v>910</v>
+      </c>
+      <c r="D650" t="s">
         <v>914</v>
       </c>
-      <c r="D650" t="s">
+      <c r="E650" t="s">
         <v>915</v>
-      </c>
-      <c r="E650" t="s">
-        <v>912</v>
       </c>
       <c r="F650" t="s">
         <v>16</v>
@@ -17294,13 +17294,13 @@
         <v>7</v>
       </c>
       <c r="C652" t="s">
+        <v>910</v>
+      </c>
+      <c r="D652" t="s">
         <v>919</v>
       </c>
-      <c r="D652" t="s">
+      <c r="E652" t="s">
         <v>920</v>
-      </c>
-      <c r="E652" t="s">
-        <v>912</v>
       </c>
       <c r="F652" t="s">
         <v>713</v>
@@ -17314,13 +17314,13 @@
         <v>7</v>
       </c>
       <c r="C653" t="s">
+        <v>910</v>
+      </c>
+      <c r="D653" t="s">
         <v>919</v>
       </c>
-      <c r="D653" t="s">
+      <c r="E653" t="s">
         <v>920</v>
-      </c>
-      <c r="E653" t="s">
-        <v>912</v>
       </c>
       <c r="F653" t="s">
         <v>713</v>
@@ -17334,13 +17334,13 @@
         <v>7</v>
       </c>
       <c r="C654" t="s">
-        <v>902</v>
+        <v>910</v>
       </c>
       <c r="D654" t="s">
         <v>865</v>
       </c>
       <c r="E654" t="s">
-        <v>912</v>
+        <v>902</v>
       </c>
       <c r="F654" t="s">
         <v>16</v>
@@ -17354,13 +17354,13 @@
         <v>7</v>
       </c>
       <c r="C655" t="s">
+        <v>910</v>
+      </c>
+      <c r="D655" t="s">
         <v>919</v>
       </c>
-      <c r="D655" t="s">
+      <c r="E655" t="s">
         <v>920</v>
-      </c>
-      <c r="E655" t="s">
-        <v>912</v>
       </c>
       <c r="F655" t="s">
         <v>713</v>
@@ -17374,13 +17374,13 @@
         <v>7</v>
       </c>
       <c r="C656" t="s">
+        <v>910</v>
+      </c>
+      <c r="D656" t="s">
         <v>919</v>
       </c>
-      <c r="D656" t="s">
+      <c r="E656" t="s">
         <v>920</v>
-      </c>
-      <c r="E656" t="s">
-        <v>912</v>
       </c>
       <c r="F656" t="s">
         <v>713</v>
@@ -17394,13 +17394,13 @@
         <v>7</v>
       </c>
       <c r="C657" t="s">
+        <v>910</v>
+      </c>
+      <c r="D657" t="s">
         <v>926</v>
       </c>
-      <c r="D657" t="s">
+      <c r="E657" t="s">
         <v>927</v>
-      </c>
-      <c r="E657" t="s">
-        <v>912</v>
       </c>
       <c r="F657" t="s">
         <v>16</v>
@@ -17414,13 +17414,13 @@
         <v>7</v>
       </c>
       <c r="C658" t="s">
+        <v>910</v>
+      </c>
+      <c r="D658" t="s">
         <v>929</v>
       </c>
-      <c r="D658" t="s">
+      <c r="E658" t="s">
         <v>930</v>
-      </c>
-      <c r="E658" t="s">
-        <v>912</v>
       </c>
       <c r="F658" t="s">
         <v>24</v>
@@ -17434,13 +17434,13 @@
         <v>7</v>
       </c>
       <c r="C659" t="s">
-        <v>889</v>
+        <v>910</v>
       </c>
       <c r="D659" t="s">
         <v>932</v>
       </c>
       <c r="E659" t="s">
-        <v>912</v>
+        <v>889</v>
       </c>
       <c r="F659" t="s">
         <v>24</v>
@@ -17454,13 +17454,13 @@
         <v>7</v>
       </c>
       <c r="C660" t="s">
+        <v>910</v>
+      </c>
+      <c r="D660" t="s">
         <v>934</v>
       </c>
-      <c r="D660" t="s">
+      <c r="E660" t="s">
         <v>935</v>
-      </c>
-      <c r="E660" t="s">
-        <v>912</v>
       </c>
       <c r="F660" t="s">
         <v>24</v>
@@ -17474,13 +17474,13 @@
         <v>7</v>
       </c>
       <c r="C661" t="s">
+        <v>910</v>
+      </c>
+      <c r="D661" t="s">
         <v>919</v>
       </c>
-      <c r="D661" t="s">
+      <c r="E661" t="s">
         <v>920</v>
-      </c>
-      <c r="E661" t="s">
-        <v>912</v>
       </c>
       <c r="F661" t="s">
         <v>713</v>
@@ -17494,13 +17494,13 @@
         <v>7</v>
       </c>
       <c r="C662" t="s">
-        <v>919</v>
+        <v>910</v>
       </c>
       <c r="D662" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="E662" t="s">
-        <v>912</v>
+        <v>920</v>
       </c>
       <c r="F662" t="s">
         <v>24</v>
@@ -17514,13 +17514,13 @@
         <v>7</v>
       </c>
       <c r="C663" t="s">
+        <v>910</v>
+      </c>
+      <c r="D663" t="s">
         <v>939</v>
       </c>
-      <c r="D663" t="s">
+      <c r="E663" t="s">
         <v>940</v>
-      </c>
-      <c r="E663" t="s">
-        <v>912</v>
       </c>
       <c r="F663" t="s">
         <v>24</v>
@@ -17534,13 +17534,13 @@
         <v>7</v>
       </c>
       <c r="C664" t="s">
-        <v>902</v>
+        <v>910</v>
       </c>
       <c r="D664" t="s">
         <v>942</v>
       </c>
       <c r="E664" t="s">
-        <v>912</v>
+        <v>902</v>
       </c>
       <c r="F664" t="s">
         <v>16</v>
@@ -17554,13 +17554,13 @@
         <v>7</v>
       </c>
       <c r="C665" t="s">
+        <v>910</v>
+      </c>
+      <c r="D665" t="s">
+        <v>919</v>
+      </c>
+      <c r="E665" t="s">
         <v>944</v>
-      </c>
-      <c r="D665" t="s">
-        <v>920</v>
-      </c>
-      <c r="E665" t="s">
-        <v>912</v>
       </c>
       <c r="F665" t="s">
         <v>713</v>
@@ -17574,13 +17574,13 @@
         <v>7</v>
       </c>
       <c r="C666" t="s">
-        <v>944</v>
+        <v>910</v>
       </c>
       <c r="D666" t="s">
         <v>911</v>
       </c>
       <c r="E666" t="s">
-        <v>912</v>
+        <v>944</v>
       </c>
       <c r="F666" t="s">
         <v>24</v>
@@ -17594,13 +17594,13 @@
         <v>7</v>
       </c>
       <c r="C667" t="s">
+        <v>910</v>
+      </c>
+      <c r="D667" t="s">
         <v>947</v>
       </c>
-      <c r="D667" t="s">
+      <c r="E667" t="s">
         <v>948</v>
-      </c>
-      <c r="E667" t="s">
-        <v>912</v>
       </c>
       <c r="F667" t="s">
         <v>24</v>
@@ -17614,13 +17614,13 @@
         <v>7</v>
       </c>
       <c r="C668" t="s">
+        <v>910</v>
+      </c>
+      <c r="D668" t="s">
         <v>919</v>
       </c>
-      <c r="D668" t="s">
+      <c r="E668" t="s">
         <v>920</v>
-      </c>
-      <c r="E668" t="s">
-        <v>912</v>
       </c>
       <c r="F668" t="s">
         <v>16</v>
@@ -17634,13 +17634,13 @@
         <v>7</v>
       </c>
       <c r="C669" t="s">
-        <v>902</v>
+        <v>910</v>
       </c>
       <c r="D669" t="s">
         <v>932</v>
       </c>
       <c r="E669" t="s">
-        <v>912</v>
+        <v>902</v>
       </c>
       <c r="F669" t="s">
         <v>16</v>
@@ -17654,13 +17654,13 @@
         <v>7</v>
       </c>
       <c r="C670" t="s">
+        <v>910</v>
+      </c>
+      <c r="D670" t="s">
         <v>919</v>
       </c>
-      <c r="D670" t="s">
+      <c r="E670" t="s">
         <v>920</v>
-      </c>
-      <c r="E670" t="s">
-        <v>912</v>
       </c>
       <c r="F670" t="s">
         <v>713</v>
@@ -17694,13 +17694,13 @@
         <v>7</v>
       </c>
       <c r="C672" t="s">
+        <v>910</v>
+      </c>
+      <c r="D672" t="s">
         <v>919</v>
       </c>
-      <c r="D672" t="s">
+      <c r="E672" t="s">
         <v>920</v>
-      </c>
-      <c r="E672" t="s">
-        <v>912</v>
       </c>
       <c r="F672" t="s">
         <v>16</v>
@@ -17714,13 +17714,13 @@
         <v>7</v>
       </c>
       <c r="C673" t="s">
+        <v>910</v>
+      </c>
+      <c r="D673" t="s">
         <v>919</v>
       </c>
-      <c r="D673" t="s">
+      <c r="E673" t="s">
         <v>920</v>
-      </c>
-      <c r="E673" t="s">
-        <v>912</v>
       </c>
       <c r="F673" t="s">
         <v>713</v>
@@ -17734,13 +17734,13 @@
         <v>7</v>
       </c>
       <c r="C674" t="s">
+        <v>910</v>
+      </c>
+      <c r="D674" t="s">
+        <v>934</v>
+      </c>
+      <c r="E674" t="s">
         <v>902</v>
-      </c>
-      <c r="D674" t="s">
-        <v>935</v>
-      </c>
-      <c r="E674" t="s">
-        <v>912</v>
       </c>
       <c r="F674" t="s">
         <v>16</v>
@@ -17774,13 +17774,13 @@
         <v>7</v>
       </c>
       <c r="C676" t="s">
+        <v>910</v>
+      </c>
+      <c r="D676" t="s">
+        <v>919</v>
+      </c>
+      <c r="E676" t="s">
         <v>959</v>
-      </c>
-      <c r="D676" t="s">
-        <v>920</v>
-      </c>
-      <c r="E676" t="s">
-        <v>912</v>
       </c>
       <c r="F676" t="s">
         <v>16</v>
@@ -17794,13 +17794,13 @@
         <v>7</v>
       </c>
       <c r="C677" t="s">
+        <v>910</v>
+      </c>
+      <c r="D677" t="s">
         <v>919</v>
       </c>
-      <c r="D677" t="s">
+      <c r="E677" t="s">
         <v>920</v>
-      </c>
-      <c r="E677" t="s">
-        <v>912</v>
       </c>
       <c r="F677" t="s">
         <v>713</v>
@@ -17814,13 +17814,13 @@
         <v>7</v>
       </c>
       <c r="C678" t="s">
+        <v>910</v>
+      </c>
+      <c r="D678" t="s">
         <v>919</v>
       </c>
-      <c r="D678" t="s">
+      <c r="E678" t="s">
         <v>920</v>
-      </c>
-      <c r="E678" t="s">
-        <v>912</v>
       </c>
       <c r="F678" t="s">
         <v>713</v>
@@ -17834,13 +17834,13 @@
         <v>7</v>
       </c>
       <c r="C679" t="s">
+        <v>910</v>
+      </c>
+      <c r="D679" t="s">
         <v>934</v>
       </c>
-      <c r="D679" t="s">
+      <c r="E679" t="s">
         <v>935</v>
-      </c>
-      <c r="E679" t="s">
-        <v>912</v>
       </c>
       <c r="F679" t="s">
         <v>24</v>
@@ -17854,13 +17854,13 @@
         <v>7</v>
       </c>
       <c r="C680" t="s">
+        <v>910</v>
+      </c>
+      <c r="D680" t="s">
         <v>919</v>
       </c>
-      <c r="D680" t="s">
+      <c r="E680" t="s">
         <v>920</v>
-      </c>
-      <c r="E680" t="s">
-        <v>912</v>
       </c>
       <c r="F680" t="s">
         <v>713</v>
@@ -17874,13 +17874,13 @@
         <v>7</v>
       </c>
       <c r="C681" t="s">
+        <v>910</v>
+      </c>
+      <c r="D681" t="s">
         <v>919</v>
       </c>
-      <c r="D681" t="s">
+      <c r="E681" t="s">
         <v>920</v>
-      </c>
-      <c r="E681" t="s">
-        <v>912</v>
       </c>
       <c r="F681" t="s">
         <v>713</v>
@@ -17914,13 +17914,13 @@
         <v>7</v>
       </c>
       <c r="C683" t="s">
+        <v>966</v>
+      </c>
+      <c r="D683" t="s">
         <v>970</v>
       </c>
-      <c r="D683" t="s">
+      <c r="E683" t="s">
         <v>971</v>
-      </c>
-      <c r="E683" t="s">
-        <v>968</v>
       </c>
       <c r="F683" t="s">
         <v>24</v>
@@ -17934,13 +17934,13 @@
         <v>7</v>
       </c>
       <c r="C684" t="s">
+        <v>966</v>
+      </c>
+      <c r="D684" t="s">
         <v>973</v>
       </c>
-      <c r="D684" t="s">
+      <c r="E684" t="s">
         <v>974</v>
-      </c>
-      <c r="E684" t="s">
-        <v>968</v>
       </c>
       <c r="F684" t="s">
         <v>713</v>
@@ -17954,13 +17954,13 @@
         <v>7</v>
       </c>
       <c r="C685" t="s">
+        <v>966</v>
+      </c>
+      <c r="D685" t="s">
         <v>973</v>
       </c>
-      <c r="D685" t="s">
+      <c r="E685" t="s">
         <v>974</v>
-      </c>
-      <c r="E685" t="s">
-        <v>968</v>
       </c>
       <c r="F685" t="s">
         <v>713</v>
@@ -17974,13 +17974,13 @@
         <v>7</v>
       </c>
       <c r="C686" t="s">
+        <v>966</v>
+      </c>
+      <c r="D686" t="s">
         <v>973</v>
       </c>
-      <c r="D686" t="s">
+      <c r="E686" t="s">
         <v>974</v>
-      </c>
-      <c r="E686" t="s">
-        <v>968</v>
       </c>
       <c r="F686" t="s">
         <v>713</v>
@@ -17994,13 +17994,13 @@
         <v>7</v>
       </c>
       <c r="C687" t="s">
+        <v>966</v>
+      </c>
+      <c r="D687" t="s">
         <v>973</v>
       </c>
-      <c r="D687" t="s">
+      <c r="E687" t="s">
         <v>974</v>
-      </c>
-      <c r="E687" t="s">
-        <v>968</v>
       </c>
       <c r="F687" t="s">
         <v>713</v>
@@ -18014,13 +18014,13 @@
         <v>7</v>
       </c>
       <c r="C688" t="s">
+        <v>966</v>
+      </c>
+      <c r="D688" t="s">
         <v>973</v>
       </c>
-      <c r="D688" t="s">
+      <c r="E688" t="s">
         <v>974</v>
-      </c>
-      <c r="E688" t="s">
-        <v>968</v>
       </c>
       <c r="F688" t="s">
         <v>713</v>
@@ -18034,13 +18034,13 @@
         <v>7</v>
       </c>
       <c r="C689" t="s">
-        <v>970</v>
+        <v>966</v>
       </c>
       <c r="D689" t="s">
         <v>980</v>
       </c>
       <c r="E689" t="s">
-        <v>968</v>
+        <v>971</v>
       </c>
       <c r="F689" t="s">
         <v>24</v>
@@ -18054,13 +18054,13 @@
         <v>7</v>
       </c>
       <c r="C690" t="s">
+        <v>966</v>
+      </c>
+      <c r="D690" t="s">
         <v>982</v>
       </c>
-      <c r="D690" t="s">
+      <c r="E690" t="s">
         <v>983</v>
-      </c>
-      <c r="E690" t="s">
-        <v>968</v>
       </c>
       <c r="F690" t="s">
         <v>24</v>
@@ -18074,13 +18074,13 @@
         <v>7</v>
       </c>
       <c r="C691" t="s">
+        <v>966</v>
+      </c>
+      <c r="D691" t="s">
         <v>973</v>
       </c>
-      <c r="D691" t="s">
+      <c r="E691" t="s">
         <v>974</v>
-      </c>
-      <c r="E691" t="s">
-        <v>968</v>
       </c>
       <c r="F691" t="s">
         <v>13</v>
@@ -18094,13 +18094,13 @@
         <v>7</v>
       </c>
       <c r="C692" t="s">
+        <v>966</v>
+      </c>
+      <c r="D692" t="s">
+        <v>919</v>
+      </c>
+      <c r="E692" t="s">
         <v>986</v>
-      </c>
-      <c r="D692" t="s">
-        <v>920</v>
-      </c>
-      <c r="E692" t="s">
-        <v>968</v>
       </c>
       <c r="F692" t="s">
         <v>16</v>
@@ -18114,13 +18114,13 @@
         <v>7</v>
       </c>
       <c r="C693" t="s">
+        <v>966</v>
+      </c>
+      <c r="D693" t="s">
         <v>988</v>
       </c>
-      <c r="D693" t="s">
+      <c r="E693" t="s">
         <v>989</v>
-      </c>
-      <c r="E693" t="s">
-        <v>968</v>
       </c>
       <c r="F693" t="s">
         <v>24</v>
@@ -18134,13 +18134,13 @@
         <v>7</v>
       </c>
       <c r="C694" t="s">
+        <v>966</v>
+      </c>
+      <c r="D694" t="s">
         <v>991</v>
       </c>
-      <c r="D694" t="s">
+      <c r="E694" t="s">
         <v>992</v>
-      </c>
-      <c r="E694" t="s">
-        <v>968</v>
       </c>
       <c r="F694" t="s">
         <v>16</v>
@@ -18154,13 +18154,13 @@
         <v>7</v>
       </c>
       <c r="C695" t="s">
+        <v>966</v>
+      </c>
+      <c r="D695" t="s">
         <v>994</v>
       </c>
-      <c r="D695" t="s">
+      <c r="E695" t="s">
         <v>995</v>
-      </c>
-      <c r="E695" t="s">
-        <v>968</v>
       </c>
       <c r="F695" t="s">
         <v>24</v>
@@ -18174,13 +18174,13 @@
         <v>7</v>
       </c>
       <c r="C696" t="s">
+        <v>966</v>
+      </c>
+      <c r="D696" t="s">
         <v>973</v>
       </c>
-      <c r="D696" t="s">
+      <c r="E696" t="s">
         <v>974</v>
-      </c>
-      <c r="E696" t="s">
-        <v>968</v>
       </c>
       <c r="F696" t="s">
         <v>713</v>
@@ -18194,13 +18194,13 @@
         <v>7</v>
       </c>
       <c r="C697" t="s">
+        <v>966</v>
+      </c>
+      <c r="D697" t="s">
         <v>998</v>
       </c>
-      <c r="D697" t="s">
+      <c r="E697" t="s">
         <v>999</v>
-      </c>
-      <c r="E697" t="s">
-        <v>968</v>
       </c>
       <c r="F697" t="s">
         <v>24</v>
@@ -18214,13 +18214,13 @@
         <v>7</v>
       </c>
       <c r="C698" t="s">
+        <v>966</v>
+      </c>
+      <c r="D698" t="s">
         <v>1001</v>
       </c>
-      <c r="D698" t="s">
+      <c r="E698" t="s">
         <v>1002</v>
-      </c>
-      <c r="E698" t="s">
-        <v>968</v>
       </c>
       <c r="F698" t="s">
         <v>24</v>
@@ -18234,13 +18234,13 @@
         <v>7</v>
       </c>
       <c r="C699" t="s">
+        <v>966</v>
+      </c>
+      <c r="D699" t="s">
         <v>973</v>
       </c>
-      <c r="D699" t="s">
+      <c r="E699" t="s">
         <v>974</v>
-      </c>
-      <c r="E699" t="s">
-        <v>968</v>
       </c>
       <c r="F699" t="s">
         <v>16</v>
@@ -18254,13 +18254,13 @@
         <v>7</v>
       </c>
       <c r="C700" t="s">
+        <v>966</v>
+      </c>
+      <c r="D700" t="s">
         <v>1005</v>
       </c>
-      <c r="D700" t="s">
+      <c r="E700" t="s">
         <v>1006</v>
-      </c>
-      <c r="E700" t="s">
-        <v>968</v>
       </c>
       <c r="F700" t="s">
         <v>24</v>
@@ -18274,13 +18274,13 @@
         <v>7</v>
       </c>
       <c r="C701" t="s">
+        <v>966</v>
+      </c>
+      <c r="D701" t="s">
         <v>973</v>
       </c>
-      <c r="D701" t="s">
+      <c r="E701" t="s">
         <v>974</v>
-      </c>
-      <c r="E701" t="s">
-        <v>968</v>
       </c>
       <c r="F701" t="s">
         <v>16</v>
@@ -18294,13 +18294,13 @@
         <v>7</v>
       </c>
       <c r="C702" t="s">
+        <v>966</v>
+      </c>
+      <c r="D702" t="s">
         <v>1009</v>
       </c>
-      <c r="D702" t="s">
+      <c r="E702" t="s">
         <v>1010</v>
-      </c>
-      <c r="E702" t="s">
-        <v>968</v>
       </c>
       <c r="F702" t="s">
         <v>24</v>
@@ -18314,13 +18314,13 @@
         <v>7</v>
       </c>
       <c r="C703" t="s">
+        <v>966</v>
+      </c>
+      <c r="D703" t="s">
+        <v>1005</v>
+      </c>
+      <c r="E703" t="s">
         <v>1012</v>
-      </c>
-      <c r="D703" t="s">
-        <v>1006</v>
-      </c>
-      <c r="E703" t="s">
-        <v>968</v>
       </c>
       <c r="F703" t="s">
         <v>24</v>
@@ -18334,13 +18334,13 @@
         <v>7</v>
       </c>
       <c r="C704" t="s">
+        <v>966</v>
+      </c>
+      <c r="D704" t="s">
         <v>973</v>
       </c>
-      <c r="D704" t="s">
+      <c r="E704" t="s">
         <v>974</v>
-      </c>
-      <c r="E704" t="s">
-        <v>968</v>
       </c>
       <c r="F704" t="s">
         <v>713</v>
@@ -18354,13 +18354,13 @@
         <v>7</v>
       </c>
       <c r="C705" t="s">
+        <v>966</v>
+      </c>
+      <c r="D705" t="s">
+        <v>1001</v>
+      </c>
+      <c r="E705" t="s">
         <v>1015</v>
-      </c>
-      <c r="D705" t="s">
-        <v>1002</v>
-      </c>
-      <c r="E705" t="s">
-        <v>968</v>
       </c>
       <c r="F705" t="s">
         <v>16</v>
@@ -18374,13 +18374,13 @@
         <v>7</v>
       </c>
       <c r="C706" t="s">
+        <v>966</v>
+      </c>
+      <c r="D706" t="s">
         <v>973</v>
       </c>
-      <c r="D706" t="s">
+      <c r="E706" t="s">
         <v>974</v>
-      </c>
-      <c r="E706" t="s">
-        <v>968</v>
       </c>
       <c r="F706" t="s">
         <v>713</v>
@@ -18394,13 +18394,13 @@
         <v>7</v>
       </c>
       <c r="C707" t="s">
-        <v>973</v>
+        <v>966</v>
       </c>
       <c r="D707" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="E707" t="s">
-        <v>968</v>
+        <v>974</v>
       </c>
       <c r="F707" t="s">
         <v>16</v>
@@ -18414,13 +18414,13 @@
         <v>7</v>
       </c>
       <c r="C708" t="s">
+        <v>966</v>
+      </c>
+      <c r="D708" t="s">
+        <v>970</v>
+      </c>
+      <c r="E708" t="s">
         <v>1019</v>
-      </c>
-      <c r="D708" t="s">
-        <v>971</v>
-      </c>
-      <c r="E708" t="s">
-        <v>968</v>
       </c>
       <c r="F708" t="s">
         <v>24</v>
@@ -18434,13 +18434,13 @@
         <v>7</v>
       </c>
       <c r="C709" t="s">
+        <v>966</v>
+      </c>
+      <c r="D709" t="s">
         <v>973</v>
       </c>
-      <c r="D709" t="s">
+      <c r="E709" t="s">
         <v>974</v>
-      </c>
-      <c r="E709" t="s">
-        <v>968</v>
       </c>
       <c r="F709" t="s">
         <v>713</v>
@@ -18454,13 +18454,13 @@
         <v>7</v>
       </c>
       <c r="C710" t="s">
+        <v>966</v>
+      </c>
+      <c r="D710" t="s">
         <v>1022</v>
       </c>
-      <c r="D710" t="s">
+      <c r="E710" t="s">
         <v>1023</v>
-      </c>
-      <c r="E710" t="s">
-        <v>968</v>
       </c>
       <c r="F710" t="s">
         <v>24</v>
@@ -18474,13 +18474,13 @@
         <v>7</v>
       </c>
       <c r="C711" t="s">
-        <v>973</v>
+        <v>966</v>
       </c>
       <c r="D711" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="E711" t="s">
-        <v>968</v>
+        <v>974</v>
       </c>
       <c r="F711" t="s">
         <v>713</v>
@@ -18494,13 +18494,13 @@
         <v>7</v>
       </c>
       <c r="C712" t="s">
+        <v>966</v>
+      </c>
+      <c r="D712" t="s">
         <v>973</v>
       </c>
-      <c r="D712" t="s">
+      <c r="E712" t="s">
         <v>974</v>
-      </c>
-      <c r="E712" t="s">
-        <v>968</v>
       </c>
       <c r="F712" t="s">
         <v>713</v>
@@ -18514,13 +18514,13 @@
         <v>7</v>
       </c>
       <c r="C713" t="s">
+        <v>966</v>
+      </c>
+      <c r="D713" t="s">
         <v>982</v>
       </c>
-      <c r="D713" t="s">
+      <c r="E713" t="s">
         <v>983</v>
-      </c>
-      <c r="E713" t="s">
-        <v>968</v>
       </c>
       <c r="F713" t="s">
         <v>24</v>
@@ -18534,13 +18534,13 @@
         <v>7</v>
       </c>
       <c r="C714" t="s">
+        <v>966</v>
+      </c>
+      <c r="D714" t="s">
         <v>973</v>
       </c>
-      <c r="D714" t="s">
+      <c r="E714" t="s">
         <v>974</v>
-      </c>
-      <c r="E714" t="s">
-        <v>968</v>
       </c>
       <c r="F714" t="s">
         <v>713</v>
@@ -18554,13 +18554,13 @@
         <v>7</v>
       </c>
       <c r="C715" t="s">
-        <v>998</v>
+        <v>966</v>
       </c>
       <c r="D715" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="E715" t="s">
-        <v>968</v>
+        <v>999</v>
       </c>
       <c r="F715" t="s">
         <v>24</v>
@@ -18574,13 +18574,13 @@
         <v>7</v>
       </c>
       <c r="C716" t="s">
+        <v>966</v>
+      </c>
+      <c r="D716" t="s">
         <v>973</v>
       </c>
-      <c r="D716" t="s">
+      <c r="E716" t="s">
         <v>974</v>
-      </c>
-      <c r="E716" t="s">
-        <v>968</v>
       </c>
       <c r="F716" t="s">
         <v>713</v>
@@ -18594,13 +18594,13 @@
         <v>7</v>
       </c>
       <c r="C717" t="s">
+        <v>966</v>
+      </c>
+      <c r="D717" t="s">
         <v>973</v>
       </c>
-      <c r="D717" t="s">
+      <c r="E717" t="s">
         <v>974</v>
-      </c>
-      <c r="E717" t="s">
-        <v>968</v>
       </c>
       <c r="F717" t="s">
         <v>713</v>
@@ -18634,13 +18634,13 @@
         <v>7</v>
       </c>
       <c r="C719" t="s">
-        <v>1036</v>
+        <v>1032</v>
       </c>
       <c r="D719" t="s">
         <v>1033</v>
       </c>
       <c r="E719" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
       <c r="F719" t="s">
         <v>713</v>
@@ -18654,13 +18654,13 @@
         <v>7</v>
       </c>
       <c r="C720" t="s">
-        <v>1036</v>
+        <v>1032</v>
       </c>
       <c r="D720" t="s">
         <v>1033</v>
       </c>
       <c r="E720" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
       <c r="F720" t="s">
         <v>713</v>
@@ -18674,13 +18674,13 @@
         <v>7</v>
       </c>
       <c r="C721" t="s">
-        <v>1036</v>
+        <v>1032</v>
       </c>
       <c r="D721" t="s">
         <v>1033</v>
       </c>
       <c r="E721" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
       <c r="F721" t="s">
         <v>713</v>
@@ -18694,13 +18694,13 @@
         <v>7</v>
       </c>
       <c r="C722" t="s">
-        <v>1036</v>
+        <v>1032</v>
       </c>
       <c r="D722" t="s">
         <v>1033</v>
       </c>
       <c r="E722" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
       <c r="F722" t="s">
         <v>713</v>
@@ -18714,13 +18714,13 @@
         <v>7</v>
       </c>
       <c r="C723" t="s">
-        <v>1036</v>
+        <v>1032</v>
       </c>
       <c r="D723" t="s">
         <v>1033</v>
       </c>
       <c r="E723" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
       <c r="F723" t="s">
         <v>713</v>
@@ -18734,13 +18734,13 @@
         <v>7</v>
       </c>
       <c r="C724" t="s">
-        <v>1036</v>
+        <v>1032</v>
       </c>
       <c r="D724" t="s">
         <v>1033</v>
       </c>
       <c r="E724" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
       <c r="F724" t="s">
         <v>16</v>
@@ -18754,13 +18754,13 @@
         <v>7</v>
       </c>
       <c r="C725" t="s">
+        <v>1032</v>
+      </c>
+      <c r="D725" t="s">
         <v>1043</v>
       </c>
-      <c r="D725" t="s">
+      <c r="E725" t="s">
         <v>1044</v>
-      </c>
-      <c r="E725" t="s">
-        <v>1034</v>
       </c>
       <c r="F725" t="s">
         <v>16</v>
@@ -18774,13 +18774,13 @@
         <v>7</v>
       </c>
       <c r="C726" t="s">
+        <v>1032</v>
+      </c>
+      <c r="D726" t="s">
         <v>1046</v>
       </c>
-      <c r="D726" t="s">
+      <c r="E726" t="s">
         <v>1047</v>
-      </c>
-      <c r="E726" t="s">
-        <v>1034</v>
       </c>
       <c r="F726" t="s">
         <v>16</v>
@@ -18794,13 +18794,13 @@
         <v>7</v>
       </c>
       <c r="C727" t="s">
-        <v>1036</v>
+        <v>1032</v>
       </c>
       <c r="D727" t="s">
         <v>1033</v>
       </c>
       <c r="E727" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
       <c r="F727" t="s">
         <v>713</v>
@@ -18814,13 +18814,13 @@
         <v>7</v>
       </c>
       <c r="C728" t="s">
-        <v>1036</v>
+        <v>1032</v>
       </c>
       <c r="D728" t="s">
         <v>1033</v>
       </c>
       <c r="E728" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
       <c r="F728" t="s">
         <v>713</v>
@@ -18834,13 +18834,13 @@
         <v>7</v>
       </c>
       <c r="C729" t="s">
+        <v>1032</v>
+      </c>
+      <c r="D729" t="s">
         <v>1051</v>
       </c>
-      <c r="D729" t="s">
+      <c r="E729" t="s">
         <v>1052</v>
-      </c>
-      <c r="E729" t="s">
-        <v>1034</v>
       </c>
       <c r="F729" t="s">
         <v>24</v>
@@ -18854,13 +18854,13 @@
         <v>7</v>
       </c>
       <c r="C730" t="s">
-        <v>1036</v>
+        <v>1032</v>
       </c>
       <c r="D730" t="s">
         <v>1033</v>
       </c>
       <c r="E730" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
       <c r="F730" t="s">
         <v>13</v>
@@ -18874,13 +18874,13 @@
         <v>7</v>
       </c>
       <c r="C731" t="s">
+        <v>1032</v>
+      </c>
+      <c r="D731" t="s">
         <v>1051</v>
       </c>
-      <c r="D731" t="s">
+      <c r="E731" t="s">
         <v>1052</v>
-      </c>
-      <c r="E731" t="s">
-        <v>1034</v>
       </c>
       <c r="F731" t="s">
         <v>24</v>
@@ -18894,13 +18894,13 @@
         <v>7</v>
       </c>
       <c r="C732" t="s">
+        <v>1032</v>
+      </c>
+      <c r="D732" t="s">
         <v>1056</v>
       </c>
-      <c r="D732" t="s">
+      <c r="E732" t="s">
         <v>1057</v>
-      </c>
-      <c r="E732" t="s">
-        <v>1034</v>
       </c>
       <c r="F732" t="s">
         <v>24</v>
@@ -18914,13 +18914,13 @@
         <v>7</v>
       </c>
       <c r="C733" t="s">
-        <v>1059</v>
+        <v>1032</v>
       </c>
       <c r="D733" t="s">
         <v>1033</v>
       </c>
       <c r="E733" t="s">
-        <v>1034</v>
+        <v>1059</v>
       </c>
       <c r="F733" t="s">
         <v>24</v>
@@ -18934,13 +18934,13 @@
         <v>7</v>
       </c>
       <c r="C734" t="s">
+        <v>1032</v>
+      </c>
+      <c r="D734" t="s">
         <v>1061</v>
       </c>
-      <c r="D734" t="s">
+      <c r="E734" t="s">
         <v>1062</v>
-      </c>
-      <c r="E734" t="s">
-        <v>1034</v>
       </c>
       <c r="F734" t="s">
         <v>24</v>
@@ -18954,13 +18954,13 @@
         <v>7</v>
       </c>
       <c r="C735" t="s">
-        <v>1036</v>
+        <v>1032</v>
       </c>
       <c r="D735" t="s">
         <v>1033</v>
       </c>
       <c r="E735" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
       <c r="F735" t="s">
         <v>713</v>
@@ -18974,13 +18974,13 @@
         <v>7</v>
       </c>
       <c r="C736" t="s">
-        <v>1065</v>
+        <v>1032</v>
       </c>
       <c r="D736" t="s">
         <v>1033</v>
       </c>
       <c r="E736" t="s">
-        <v>1034</v>
+        <v>1065</v>
       </c>
       <c r="F736" t="s">
         <v>713</v>
@@ -18994,13 +18994,13 @@
         <v>7</v>
       </c>
       <c r="C737" t="s">
-        <v>1036</v>
+        <v>1032</v>
       </c>
       <c r="D737" t="s">
         <v>1033</v>
       </c>
       <c r="E737" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
       <c r="F737" t="s">
         <v>16</v>
@@ -19014,13 +19014,13 @@
         <v>7</v>
       </c>
       <c r="C738" t="s">
+        <v>1032</v>
+      </c>
+      <c r="D738" t="s">
+        <v>973</v>
+      </c>
+      <c r="E738" t="s">
         <v>1068</v>
-      </c>
-      <c r="D738" t="s">
-        <v>974</v>
-      </c>
-      <c r="E738" t="s">
-        <v>1034</v>
       </c>
       <c r="F738" t="s">
         <v>16</v>
@@ -19034,13 +19034,13 @@
         <v>7</v>
       </c>
       <c r="C739" t="s">
-        <v>1036</v>
+        <v>1032</v>
       </c>
       <c r="D739" t="s">
         <v>1033</v>
       </c>
       <c r="E739" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
       <c r="F739" t="s">
         <v>713</v>
@@ -19054,13 +19054,13 @@
         <v>7</v>
       </c>
       <c r="C740" t="s">
-        <v>1036</v>
+        <v>1032</v>
       </c>
       <c r="D740" t="s">
         <v>1033</v>
       </c>
       <c r="E740" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
       <c r="F740" t="s">
         <v>713</v>
@@ -19074,13 +19074,13 @@
         <v>7</v>
       </c>
       <c r="C741" t="s">
+        <v>1032</v>
+      </c>
+      <c r="D741" t="s">
         <v>1072</v>
       </c>
-      <c r="D741" t="s">
+      <c r="E741" t="s">
         <v>1073</v>
-      </c>
-      <c r="E741" t="s">
-        <v>1034</v>
       </c>
       <c r="F741" t="s">
         <v>24</v>
@@ -19094,13 +19094,13 @@
         <v>7</v>
       </c>
       <c r="C742" t="s">
-        <v>1075</v>
+        <v>1032</v>
       </c>
       <c r="D742" t="s">
         <v>1033</v>
       </c>
       <c r="E742" t="s">
-        <v>1034</v>
+        <v>1075</v>
       </c>
       <c r="F742" t="s">
         <v>16</v>
@@ -19114,13 +19114,13 @@
         <v>7</v>
       </c>
       <c r="C743" t="s">
-        <v>1036</v>
+        <v>1032</v>
       </c>
       <c r="D743" t="s">
         <v>1033</v>
       </c>
       <c r="E743" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
       <c r="F743" t="s">
         <v>713</v>
@@ -19154,13 +19154,13 @@
         <v>7</v>
       </c>
       <c r="C745" t="s">
-        <v>1079</v>
+        <v>1032</v>
       </c>
       <c r="D745" t="s">
         <v>1033</v>
       </c>
       <c r="E745" t="s">
-        <v>1034</v>
+        <v>1079</v>
       </c>
       <c r="F745" t="s">
         <v>24</v>
@@ -19174,13 +19174,13 @@
         <v>7</v>
       </c>
       <c r="C746" t="s">
-        <v>1036</v>
+        <v>1032</v>
       </c>
       <c r="D746" t="s">
         <v>1033</v>
       </c>
       <c r="E746" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
       <c r="F746" t="s">
         <v>713</v>
@@ -19194,13 +19194,13 @@
         <v>7</v>
       </c>
       <c r="C747" t="s">
-        <v>1036</v>
+        <v>1032</v>
       </c>
       <c r="D747" t="s">
         <v>1033</v>
       </c>
       <c r="E747" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
       <c r="F747" t="s">
         <v>713</v>
@@ -19214,13 +19214,13 @@
         <v>7</v>
       </c>
       <c r="C748" t="s">
-        <v>1036</v>
+        <v>1032</v>
       </c>
       <c r="D748" t="s">
         <v>1033</v>
       </c>
       <c r="E748" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
       <c r="F748" t="s">
         <v>713</v>
@@ -19234,13 +19234,13 @@
         <v>7</v>
       </c>
       <c r="C749" t="s">
-        <v>1036</v>
+        <v>1032</v>
       </c>
       <c r="D749" t="s">
         <v>1033</v>
       </c>
       <c r="E749" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
       <c r="F749" t="s">
         <v>713</v>
@@ -19274,13 +19274,13 @@
         <v>7</v>
       </c>
       <c r="C751" t="s">
+        <v>1085</v>
+      </c>
+      <c r="D751" t="s">
         <v>1089</v>
       </c>
-      <c r="D751" t="s">
+      <c r="E751" t="s">
         <v>1090</v>
-      </c>
-      <c r="E751" t="s">
-        <v>1087</v>
       </c>
       <c r="F751" t="s">
         <v>24</v>
@@ -19294,13 +19294,13 @@
         <v>7</v>
       </c>
       <c r="C752" t="s">
+        <v>1085</v>
+      </c>
+      <c r="D752" t="s">
         <v>1092</v>
       </c>
-      <c r="D752" t="s">
+      <c r="E752" t="s">
         <v>1093</v>
-      </c>
-      <c r="E752" t="s">
-        <v>1087</v>
       </c>
       <c r="F752" t="s">
         <v>713</v>
@@ -19314,13 +19314,13 @@
         <v>7</v>
       </c>
       <c r="C753" t="s">
+        <v>1085</v>
+      </c>
+      <c r="D753" t="s">
         <v>1092</v>
       </c>
-      <c r="D753" t="s">
+      <c r="E753" t="s">
         <v>1093</v>
-      </c>
-      <c r="E753" t="s">
-        <v>1087</v>
       </c>
       <c r="F753" t="s">
         <v>713</v>
@@ -19334,13 +19334,13 @@
         <v>7</v>
       </c>
       <c r="C754" t="s">
+        <v>1085</v>
+      </c>
+      <c r="D754" t="s">
         <v>1092</v>
       </c>
-      <c r="D754" t="s">
+      <c r="E754" t="s">
         <v>1093</v>
-      </c>
-      <c r="E754" t="s">
-        <v>1087</v>
       </c>
       <c r="F754" t="s">
         <v>713</v>
@@ -19354,13 +19354,13 @@
         <v>7</v>
       </c>
       <c r="C755" t="s">
+        <v>1085</v>
+      </c>
+      <c r="D755" t="s">
         <v>1092</v>
       </c>
-      <c r="D755" t="s">
+      <c r="E755" t="s">
         <v>1093</v>
-      </c>
-      <c r="E755" t="s">
-        <v>1087</v>
       </c>
       <c r="F755" t="s">
         <v>713</v>
@@ -19374,13 +19374,13 @@
         <v>7</v>
       </c>
       <c r="C756" t="s">
+        <v>1085</v>
+      </c>
+      <c r="D756" t="s">
         <v>1092</v>
       </c>
-      <c r="D756" t="s">
+      <c r="E756" t="s">
         <v>1093</v>
-      </c>
-      <c r="E756" t="s">
-        <v>1087</v>
       </c>
       <c r="F756" t="s">
         <v>713</v>
@@ -19394,13 +19394,13 @@
         <v>7</v>
       </c>
       <c r="C757" t="s">
+        <v>1085</v>
+      </c>
+      <c r="D757" t="s">
         <v>1092</v>
       </c>
-      <c r="D757" t="s">
+      <c r="E757" t="s">
         <v>1093</v>
-      </c>
-      <c r="E757" t="s">
-        <v>1087</v>
       </c>
       <c r="F757" t="s">
         <v>713</v>
@@ -19417,7 +19417,7 @@
         <v>1085</v>
       </c>
       <c r="D758" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="E758" t="s">
         <v>1087</v>
@@ -19434,13 +19434,13 @@
         <v>7</v>
       </c>
       <c r="C759" t="s">
+        <v>1085</v>
+      </c>
+      <c r="D759" t="s">
+        <v>1092</v>
+      </c>
+      <c r="E759" t="s">
         <v>1065</v>
-      </c>
-      <c r="D759" t="s">
-        <v>1093</v>
-      </c>
-      <c r="E759" t="s">
-        <v>1087</v>
       </c>
       <c r="F759" t="s">
         <v>16</v>
@@ -19454,13 +19454,13 @@
         <v>7</v>
       </c>
       <c r="C760" t="s">
+        <v>1085</v>
+      </c>
+      <c r="D760" t="s">
         <v>1092</v>
       </c>
-      <c r="D760" t="s">
+      <c r="E760" t="s">
         <v>1093</v>
-      </c>
-      <c r="E760" t="s">
-        <v>1087</v>
       </c>
       <c r="F760" t="s">
         <v>713</v>
@@ -19474,13 +19474,13 @@
         <v>7</v>
       </c>
       <c r="C761" t="s">
+        <v>1085</v>
+      </c>
+      <c r="D761" t="s">
         <v>1092</v>
       </c>
-      <c r="D761" t="s">
+      <c r="E761" t="s">
         <v>1093</v>
-      </c>
-      <c r="E761" t="s">
-        <v>1087</v>
       </c>
       <c r="F761" t="s">
         <v>713</v>
@@ -19494,13 +19494,13 @@
         <v>7</v>
       </c>
       <c r="C762" t="s">
-        <v>1065</v>
+        <v>1085</v>
       </c>
       <c r="D762" t="s">
         <v>1104</v>
       </c>
       <c r="E762" t="s">
-        <v>1087</v>
+        <v>1065</v>
       </c>
       <c r="F762" t="s">
         <v>24</v>
@@ -19514,13 +19514,13 @@
         <v>7</v>
       </c>
       <c r="C763" t="s">
+        <v>1085</v>
+      </c>
+      <c r="D763" t="s">
         <v>1092</v>
       </c>
-      <c r="D763" t="s">
+      <c r="E763" t="s">
         <v>1093</v>
-      </c>
-      <c r="E763" t="s">
-        <v>1087</v>
       </c>
       <c r="F763" t="s">
         <v>713</v>
@@ -19534,13 +19534,13 @@
         <v>7</v>
       </c>
       <c r="C764" t="s">
+        <v>1085</v>
+      </c>
+      <c r="D764" t="s">
         <v>1107</v>
       </c>
-      <c r="D764" t="s">
+      <c r="E764" t="s">
         <v>1108</v>
-      </c>
-      <c r="E764" t="s">
-        <v>1087</v>
       </c>
       <c r="F764" t="s">
         <v>24</v>
@@ -19554,13 +19554,13 @@
         <v>7</v>
       </c>
       <c r="C765" t="s">
-        <v>1092</v>
+        <v>1085</v>
       </c>
       <c r="D765" t="s">
         <v>1086</v>
       </c>
       <c r="E765" t="s">
-        <v>1087</v>
+        <v>1093</v>
       </c>
       <c r="F765" t="s">
         <v>24</v>
@@ -19574,13 +19574,13 @@
         <v>7</v>
       </c>
       <c r="C766" t="s">
-        <v>1111</v>
+        <v>1085</v>
       </c>
       <c r="D766" t="s">
         <v>1104</v>
       </c>
       <c r="E766" t="s">
-        <v>1087</v>
+        <v>1111</v>
       </c>
       <c r="F766" t="s">
         <v>24</v>
@@ -19594,13 +19594,13 @@
         <v>7</v>
       </c>
       <c r="C767" t="s">
+        <v>1085</v>
+      </c>
+      <c r="D767" t="s">
         <v>1113</v>
       </c>
-      <c r="D767" t="s">
+      <c r="E767" t="s">
         <v>1114</v>
-      </c>
-      <c r="E767" t="s">
-        <v>1087</v>
       </c>
       <c r="F767" t="s">
         <v>24</v>
@@ -19614,13 +19614,13 @@
         <v>7</v>
       </c>
       <c r="C768" t="s">
+        <v>1085</v>
+      </c>
+      <c r="D768" t="s">
         <v>1092</v>
       </c>
-      <c r="D768" t="s">
+      <c r="E768" t="s">
         <v>1093</v>
-      </c>
-      <c r="E768" t="s">
-        <v>1087</v>
       </c>
       <c r="F768" t="s">
         <v>713</v>
@@ -19634,13 +19634,13 @@
         <v>7</v>
       </c>
       <c r="C769" t="s">
+        <v>1085</v>
+      </c>
+      <c r="D769" t="s">
         <v>1092</v>
       </c>
-      <c r="D769" t="s">
+      <c r="E769" t="s">
         <v>1093</v>
-      </c>
-      <c r="E769" t="s">
-        <v>1087</v>
       </c>
       <c r="F769" t="s">
         <v>713</v>
@@ -19654,13 +19654,13 @@
         <v>7</v>
       </c>
       <c r="C770" t="s">
+        <v>1085</v>
+      </c>
+      <c r="D770" t="s">
         <v>1118</v>
       </c>
-      <c r="D770" t="s">
+      <c r="E770" t="s">
         <v>1119</v>
-      </c>
-      <c r="E770" t="s">
-        <v>1087</v>
       </c>
       <c r="F770" t="s">
         <v>24</v>
@@ -19674,13 +19674,13 @@
         <v>7</v>
       </c>
       <c r="C771" t="s">
+        <v>1085</v>
+      </c>
+      <c r="D771" t="s">
         <v>1092</v>
       </c>
-      <c r="D771" t="s">
+      <c r="E771" t="s">
         <v>1093</v>
-      </c>
-      <c r="E771" t="s">
-        <v>1087</v>
       </c>
       <c r="F771" t="s">
         <v>713</v>
@@ -19694,13 +19694,13 @@
         <v>7</v>
       </c>
       <c r="C772" t="s">
+        <v>1085</v>
+      </c>
+      <c r="D772" t="s">
         <v>1092</v>
       </c>
-      <c r="D772" t="s">
+      <c r="E772" t="s">
         <v>1093</v>
-      </c>
-      <c r="E772" t="s">
-        <v>1087</v>
       </c>
       <c r="F772" t="s">
         <v>713</v>
@@ -19714,13 +19714,13 @@
         <v>7</v>
       </c>
       <c r="C773" t="s">
+        <v>1085</v>
+      </c>
+      <c r="D773" t="s">
         <v>1092</v>
       </c>
-      <c r="D773" t="s">
+      <c r="E773" t="s">
         <v>1093</v>
-      </c>
-      <c r="E773" t="s">
-        <v>1087</v>
       </c>
       <c r="F773" t="s">
         <v>713</v>
@@ -19734,13 +19734,13 @@
         <v>7</v>
       </c>
       <c r="C774" t="s">
+        <v>1085</v>
+      </c>
+      <c r="D774" t="s">
         <v>1124</v>
       </c>
-      <c r="D774" t="s">
+      <c r="E774" t="s">
         <v>1125</v>
-      </c>
-      <c r="E774" t="s">
-        <v>1087</v>
       </c>
       <c r="F774" t="s">
         <v>24</v>
@@ -19754,13 +19754,13 @@
         <v>7</v>
       </c>
       <c r="C775" t="s">
+        <v>1085</v>
+      </c>
+      <c r="D775" t="s">
         <v>1092</v>
       </c>
-      <c r="D775" t="s">
+      <c r="E775" t="s">
         <v>1093</v>
-      </c>
-      <c r="E775" t="s">
-        <v>1087</v>
       </c>
       <c r="F775" t="s">
         <v>713</v>
@@ -19794,13 +19794,13 @@
         <v>7</v>
       </c>
       <c r="C777" t="s">
-        <v>1132</v>
+        <v>1128</v>
       </c>
       <c r="D777" t="s">
         <v>1129</v>
       </c>
       <c r="E777" t="s">
-        <v>1130</v>
+        <v>1132</v>
       </c>
       <c r="F777" t="s">
         <v>713</v>
@@ -19814,13 +19814,13 @@
         <v>7</v>
       </c>
       <c r="C778" t="s">
+        <v>1128</v>
+      </c>
+      <c r="D778" t="s">
         <v>1134</v>
       </c>
-      <c r="D778" t="s">
+      <c r="E778" t="s">
         <v>1135</v>
-      </c>
-      <c r="E778" t="s">
-        <v>1130</v>
       </c>
       <c r="F778" t="s">
         <v>24</v>
@@ -19834,13 +19834,13 @@
         <v>7</v>
       </c>
       <c r="C779" t="s">
+        <v>1128</v>
+      </c>
+      <c r="D779" t="s">
         <v>1137</v>
       </c>
-      <c r="D779" t="s">
+      <c r="E779" t="s">
         <v>1138</v>
-      </c>
-      <c r="E779" t="s">
-        <v>1130</v>
       </c>
       <c r="F779" t="s">
         <v>24</v>
@@ -19854,13 +19854,13 @@
         <v>7</v>
       </c>
       <c r="C780" t="s">
-        <v>1132</v>
+        <v>1128</v>
       </c>
       <c r="D780" t="s">
         <v>1129</v>
       </c>
       <c r="E780" t="s">
-        <v>1130</v>
+        <v>1132</v>
       </c>
       <c r="F780" t="s">
         <v>713</v>
@@ -19874,13 +19874,13 @@
         <v>7</v>
       </c>
       <c r="C781" t="s">
-        <v>1132</v>
+        <v>1128</v>
       </c>
       <c r="D781" t="s">
         <v>1129</v>
       </c>
       <c r="E781" t="s">
-        <v>1130</v>
+        <v>1132</v>
       </c>
       <c r="F781" t="s">
         <v>713</v>
@@ -19894,13 +19894,13 @@
         <v>7</v>
       </c>
       <c r="C782" t="s">
-        <v>1142</v>
+        <v>1128</v>
       </c>
       <c r="D782" t="s">
         <v>1129</v>
       </c>
       <c r="E782" t="s">
-        <v>1130</v>
+        <v>1142</v>
       </c>
       <c r="F782" t="s">
         <v>713</v>
@@ -19914,13 +19914,13 @@
         <v>7</v>
       </c>
       <c r="C783" t="s">
-        <v>1132</v>
+        <v>1128</v>
       </c>
       <c r="D783" t="s">
         <v>1129</v>
       </c>
       <c r="E783" t="s">
-        <v>1130</v>
+        <v>1132</v>
       </c>
       <c r="F783" t="s">
         <v>713</v>
@@ -19934,13 +19934,13 @@
         <v>7</v>
       </c>
       <c r="C784" t="s">
-        <v>1132</v>
+        <v>1128</v>
       </c>
       <c r="D784" t="s">
         <v>1129</v>
       </c>
       <c r="E784" t="s">
-        <v>1130</v>
+        <v>1132</v>
       </c>
       <c r="F784" t="s">
         <v>713</v>
@@ -19954,13 +19954,13 @@
         <v>7</v>
       </c>
       <c r="C785" t="s">
-        <v>1132</v>
+        <v>1128</v>
       </c>
       <c r="D785" t="s">
         <v>1129</v>
       </c>
       <c r="E785" t="s">
-        <v>1130</v>
+        <v>1132</v>
       </c>
       <c r="F785" t="s">
         <v>713</v>
@@ -19974,13 +19974,13 @@
         <v>7</v>
       </c>
       <c r="C786" t="s">
-        <v>1132</v>
+        <v>1128</v>
       </c>
       <c r="D786" t="s">
         <v>1129</v>
       </c>
       <c r="E786" t="s">
-        <v>1130</v>
+        <v>1132</v>
       </c>
       <c r="F786" t="s">
         <v>713</v>
@@ -19994,13 +19994,13 @@
         <v>7</v>
       </c>
       <c r="C787" t="s">
-        <v>1132</v>
+        <v>1128</v>
       </c>
       <c r="D787" t="s">
         <v>1129</v>
       </c>
       <c r="E787" t="s">
-        <v>1130</v>
+        <v>1132</v>
       </c>
       <c r="F787" t="s">
         <v>713</v>
@@ -20014,13 +20014,13 @@
         <v>7</v>
       </c>
       <c r="C788" t="s">
-        <v>1132</v>
+        <v>1128</v>
       </c>
       <c r="D788" t="s">
         <v>1129</v>
       </c>
       <c r="E788" t="s">
-        <v>1130</v>
+        <v>1132</v>
       </c>
       <c r="F788" t="s">
         <v>713</v>
@@ -20054,13 +20054,13 @@
         <v>7</v>
       </c>
       <c r="C790" t="s">
-        <v>1132</v>
+        <v>1128</v>
       </c>
       <c r="D790" t="s">
         <v>1129</v>
       </c>
       <c r="E790" t="s">
-        <v>1130</v>
+        <v>1132</v>
       </c>
       <c r="F790" t="s">
         <v>713</v>
@@ -20074,13 +20074,13 @@
         <v>7</v>
       </c>
       <c r="C791" t="s">
-        <v>1142</v>
+        <v>1128</v>
       </c>
       <c r="D791" t="s">
         <v>1153</v>
       </c>
       <c r="E791" t="s">
-        <v>1130</v>
+        <v>1142</v>
       </c>
       <c r="F791" t="s">
         <v>24</v>
@@ -20094,13 +20094,13 @@
         <v>7</v>
       </c>
       <c r="C792" t="s">
-        <v>1155</v>
+        <v>1128</v>
       </c>
       <c r="D792" t="s">
         <v>1150</v>
       </c>
       <c r="E792" t="s">
-        <v>1130</v>
+        <v>1155</v>
       </c>
       <c r="F792" t="s">
         <v>24</v>
@@ -20114,13 +20114,13 @@
         <v>7</v>
       </c>
       <c r="C793" t="s">
-        <v>1132</v>
+        <v>1128</v>
       </c>
       <c r="D793" t="s">
         <v>1129</v>
       </c>
       <c r="E793" t="s">
-        <v>1130</v>
+        <v>1132</v>
       </c>
       <c r="F793" t="s">
         <v>713</v>
@@ -20134,13 +20134,13 @@
         <v>7</v>
       </c>
       <c r="C794" t="s">
-        <v>1132</v>
+        <v>1128</v>
       </c>
       <c r="D794" t="s">
         <v>1158</v>
       </c>
       <c r="E794" t="s">
-        <v>1130</v>
+        <v>1132</v>
       </c>
       <c r="F794" t="s">
         <v>24</v>
@@ -20154,13 +20154,13 @@
         <v>7</v>
       </c>
       <c r="C795" t="s">
-        <v>1160</v>
+        <v>1128</v>
       </c>
       <c r="D795" t="s">
         <v>1129</v>
       </c>
       <c r="E795" t="s">
-        <v>1130</v>
+        <v>1160</v>
       </c>
       <c r="F795" t="s">
         <v>24</v>
@@ -20174,13 +20174,13 @@
         <v>7</v>
       </c>
       <c r="C796" t="s">
-        <v>1132</v>
+        <v>1128</v>
       </c>
       <c r="D796" t="s">
         <v>1129</v>
       </c>
       <c r="E796" t="s">
-        <v>1130</v>
+        <v>1132</v>
       </c>
       <c r="F796" t="s">
         <v>713</v>
@@ -20194,13 +20194,13 @@
         <v>7</v>
       </c>
       <c r="C797" t="s">
+        <v>1128</v>
+      </c>
+      <c r="D797" t="s">
         <v>1163</v>
       </c>
-      <c r="D797" t="s">
+      <c r="E797" t="s">
         <v>1164</v>
-      </c>
-      <c r="E797" t="s">
-        <v>1130</v>
       </c>
       <c r="F797" t="s">
         <v>24</v>
@@ -20214,13 +20214,13 @@
         <v>7</v>
       </c>
       <c r="C798" t="s">
+        <v>1128</v>
+      </c>
+      <c r="D798" t="s">
         <v>1166</v>
       </c>
-      <c r="D798" t="s">
+      <c r="E798" t="s">
         <v>1167</v>
-      </c>
-      <c r="E798" t="s">
-        <v>1130</v>
       </c>
       <c r="F798" t="s">
         <v>24</v>
@@ -20234,13 +20234,13 @@
         <v>7</v>
       </c>
       <c r="C799" t="s">
-        <v>1132</v>
+        <v>1128</v>
       </c>
       <c r="D799" t="s">
         <v>1129</v>
       </c>
       <c r="E799" t="s">
-        <v>1130</v>
+        <v>1132</v>
       </c>
       <c r="F799" t="s">
         <v>713</v>
@@ -20254,13 +20254,13 @@
         <v>7</v>
       </c>
       <c r="C800" t="s">
-        <v>1132</v>
+        <v>1128</v>
       </c>
       <c r="D800" t="s">
         <v>1129</v>
       </c>
       <c r="E800" t="s">
-        <v>1130</v>
+        <v>1132</v>
       </c>
       <c r="F800" t="s">
         <v>713</v>
@@ -20274,13 +20274,13 @@
         <v>7</v>
       </c>
       <c r="C801" t="s">
-        <v>1132</v>
+        <v>1128</v>
       </c>
       <c r="D801" t="s">
         <v>1129</v>
       </c>
       <c r="E801" t="s">
-        <v>1130</v>
+        <v>1132</v>
       </c>
       <c r="F801" t="s">
         <v>713</v>
@@ -20294,13 +20294,13 @@
         <v>7</v>
       </c>
       <c r="C802" t="s">
-        <v>1132</v>
+        <v>1128</v>
       </c>
       <c r="D802" t="s">
         <v>1129</v>
       </c>
       <c r="E802" t="s">
-        <v>1130</v>
+        <v>1132</v>
       </c>
       <c r="F802" t="s">
         <v>713</v>
@@ -20314,13 +20314,13 @@
         <v>7</v>
       </c>
       <c r="C803" t="s">
-        <v>1132</v>
+        <v>1128</v>
       </c>
       <c r="D803" t="s">
         <v>1129</v>
       </c>
       <c r="E803" t="s">
-        <v>1130</v>
+        <v>1132</v>
       </c>
       <c r="F803" t="s">
         <v>713</v>
@@ -20334,13 +20334,13 @@
         <v>7</v>
       </c>
       <c r="C804" t="s">
-        <v>1132</v>
+        <v>1128</v>
       </c>
       <c r="D804" t="s">
         <v>1129</v>
       </c>
       <c r="E804" t="s">
-        <v>1130</v>
+        <v>1132</v>
       </c>
       <c r="F804" t="s">
         <v>713</v>
@@ -20354,13 +20354,13 @@
         <v>7</v>
       </c>
       <c r="C805" t="s">
-        <v>1132</v>
+        <v>1128</v>
       </c>
       <c r="D805" t="s">
         <v>1129</v>
       </c>
       <c r="E805" t="s">
-        <v>1130</v>
+        <v>1132</v>
       </c>
       <c r="F805" t="s">
         <v>713</v>
@@ -20374,13 +20374,13 @@
         <v>7</v>
       </c>
       <c r="C806" t="s">
-        <v>1132</v>
+        <v>1128</v>
       </c>
       <c r="D806" t="s">
         <v>1129</v>
       </c>
       <c r="E806" t="s">
-        <v>1130</v>
+        <v>1132</v>
       </c>
       <c r="F806" t="s">
         <v>713</v>
@@ -20394,13 +20394,13 @@
         <v>7</v>
       </c>
       <c r="C807" t="s">
-        <v>1132</v>
+        <v>1128</v>
       </c>
       <c r="D807" t="s">
         <v>1129</v>
       </c>
       <c r="E807" t="s">
-        <v>1130</v>
+        <v>1132</v>
       </c>
       <c r="F807" t="s">
         <v>713</v>
@@ -20474,13 +20474,13 @@
         <v>7</v>
       </c>
       <c r="C811" t="s">
+        <v>1178</v>
+      </c>
+      <c r="D811" t="s">
         <v>1185</v>
       </c>
-      <c r="D811" t="s">
+      <c r="E811" t="s">
         <v>1186</v>
-      </c>
-      <c r="E811" t="s">
-        <v>1180</v>
       </c>
       <c r="F811" t="s">
         <v>24</v>
@@ -20534,13 +20534,13 @@
         <v>7</v>
       </c>
       <c r="C814" t="s">
-        <v>1185</v>
+        <v>1178</v>
       </c>
       <c r="D814" t="s">
         <v>1179</v>
       </c>
       <c r="E814" t="s">
-        <v>1180</v>
+        <v>1186</v>
       </c>
       <c r="F814" t="s">
         <v>713</v>
@@ -20554,13 +20554,13 @@
         <v>7</v>
       </c>
       <c r="C815" t="s">
+        <v>1178</v>
+      </c>
+      <c r="D815" t="s">
         <v>1191</v>
       </c>
-      <c r="D815" t="s">
+      <c r="E815" t="s">
         <v>1192</v>
-      </c>
-      <c r="E815" t="s">
-        <v>1180</v>
       </c>
       <c r="F815" t="s">
         <v>24</v>
@@ -20674,13 +20674,13 @@
         <v>7</v>
       </c>
       <c r="C821" t="s">
+        <v>1178</v>
+      </c>
+      <c r="D821" t="s">
         <v>1199</v>
       </c>
-      <c r="D821" t="s">
+      <c r="E821" t="s">
         <v>1200</v>
-      </c>
-      <c r="E821" t="s">
-        <v>1180</v>
       </c>
       <c r="F821" t="s">
         <v>16</v>
@@ -20694,13 +20694,13 @@
         <v>7</v>
       </c>
       <c r="C822" t="s">
+        <v>1178</v>
+      </c>
+      <c r="D822" t="s">
         <v>1202</v>
       </c>
-      <c r="D822" t="s">
+      <c r="E822" t="s">
         <v>1203</v>
-      </c>
-      <c r="E822" t="s">
-        <v>1180</v>
       </c>
       <c r="F822" t="s">
         <v>1182</v>
@@ -20714,13 +20714,13 @@
         <v>7</v>
       </c>
       <c r="C823" t="s">
-        <v>1202</v>
+        <v>1178</v>
       </c>
       <c r="D823" t="s">
         <v>1179</v>
       </c>
       <c r="E823" t="s">
-        <v>1180</v>
+        <v>1203</v>
       </c>
       <c r="F823" t="s">
         <v>1182</v>
@@ -20734,13 +20734,13 @@
         <v>7</v>
       </c>
       <c r="C824" t="s">
+        <v>1178</v>
+      </c>
+      <c r="D824" t="s">
         <v>1202</v>
       </c>
-      <c r="D824" t="s">
+      <c r="E824" t="s">
         <v>1203</v>
-      </c>
-      <c r="E824" t="s">
-        <v>1180</v>
       </c>
       <c r="F824" t="s">
         <v>1182</v>
@@ -20754,13 +20754,13 @@
         <v>7</v>
       </c>
       <c r="C825" t="s">
+        <v>1178</v>
+      </c>
+      <c r="D825" t="s">
         <v>1202</v>
       </c>
-      <c r="D825" t="s">
+      <c r="E825" t="s">
         <v>1203</v>
-      </c>
-      <c r="E825" t="s">
-        <v>1180</v>
       </c>
       <c r="F825" t="s">
         <v>713</v>
@@ -20774,13 +20774,13 @@
         <v>7</v>
       </c>
       <c r="C826" t="s">
+        <v>1178</v>
+      </c>
+      <c r="D826" t="s">
         <v>1202</v>
       </c>
-      <c r="D826" t="s">
+      <c r="E826" t="s">
         <v>1203</v>
-      </c>
-      <c r="E826" t="s">
-        <v>1180</v>
       </c>
       <c r="F826" t="s">
         <v>1182</v>
@@ -20794,13 +20794,13 @@
         <v>7</v>
       </c>
       <c r="C827" t="s">
+        <v>1178</v>
+      </c>
+      <c r="D827" t="s">
         <v>1202</v>
       </c>
-      <c r="D827" t="s">
+      <c r="E827" t="s">
         <v>1203</v>
-      </c>
-      <c r="E827" t="s">
-        <v>1180</v>
       </c>
       <c r="F827" t="s">
         <v>1182</v>
@@ -20814,13 +20814,13 @@
         <v>7</v>
       </c>
       <c r="C828" t="s">
-        <v>1202</v>
+        <v>1178</v>
       </c>
       <c r="D828" t="s">
         <v>1179</v>
       </c>
       <c r="E828" t="s">
-        <v>1180</v>
+        <v>1203</v>
       </c>
       <c r="F828" t="s">
         <v>1182</v>
@@ -20854,13 +20854,13 @@
         <v>7</v>
       </c>
       <c r="C830" t="s">
-        <v>1185</v>
+        <v>1178</v>
       </c>
       <c r="D830" t="s">
         <v>1179</v>
       </c>
       <c r="E830" t="s">
-        <v>1180</v>
+        <v>1186</v>
       </c>
       <c r="F830" t="s">
         <v>1182</v>
@@ -21054,13 +21054,13 @@
         <v>7</v>
       </c>
       <c r="C840" t="s">
-        <v>1225</v>
+        <v>1221</v>
       </c>
       <c r="D840" t="s">
         <v>1222</v>
       </c>
       <c r="E840" t="s">
-        <v>1223</v>
+        <v>1225</v>
       </c>
       <c r="F840" t="s">
         <v>1182</v>
@@ -21074,13 +21074,13 @@
         <v>7</v>
       </c>
       <c r="C841" t="s">
-        <v>1225</v>
+        <v>1221</v>
       </c>
       <c r="D841" t="s">
         <v>1222</v>
       </c>
       <c r="E841" t="s">
-        <v>1223</v>
+        <v>1225</v>
       </c>
       <c r="F841" t="s">
         <v>1182</v>
@@ -21094,13 +21094,13 @@
         <v>7</v>
       </c>
       <c r="C842" t="s">
-        <v>1225</v>
+        <v>1221</v>
       </c>
       <c r="D842" t="s">
         <v>1222</v>
       </c>
       <c r="E842" t="s">
-        <v>1223</v>
+        <v>1225</v>
       </c>
       <c r="F842" t="s">
         <v>1182</v>
@@ -21114,13 +21114,13 @@
         <v>7</v>
       </c>
       <c r="C843" t="s">
-        <v>1225</v>
+        <v>1221</v>
       </c>
       <c r="D843" t="s">
         <v>1222</v>
       </c>
       <c r="E843" t="s">
-        <v>1223</v>
+        <v>1225</v>
       </c>
       <c r="F843" t="s">
         <v>1182</v>
@@ -21134,13 +21134,13 @@
         <v>7</v>
       </c>
       <c r="C844" t="s">
-        <v>1225</v>
+        <v>1221</v>
       </c>
       <c r="D844" t="s">
         <v>1222</v>
       </c>
       <c r="E844" t="s">
-        <v>1223</v>
+        <v>1225</v>
       </c>
       <c r="F844" t="s">
         <v>1182</v>
@@ -21154,13 +21154,13 @@
         <v>7</v>
       </c>
       <c r="C845" t="s">
-        <v>1225</v>
+        <v>1221</v>
       </c>
       <c r="D845" t="s">
         <v>1222</v>
       </c>
       <c r="E845" t="s">
-        <v>1223</v>
+        <v>1225</v>
       </c>
       <c r="F845" t="s">
         <v>713</v>
@@ -21174,13 +21174,13 @@
         <v>7</v>
       </c>
       <c r="C846" t="s">
-        <v>1225</v>
+        <v>1221</v>
       </c>
       <c r="D846" t="s">
         <v>1222</v>
       </c>
       <c r="E846" t="s">
-        <v>1223</v>
+        <v>1225</v>
       </c>
       <c r="F846" t="s">
         <v>1182</v>
@@ -21194,13 +21194,13 @@
         <v>7</v>
       </c>
       <c r="C847" t="s">
+        <v>1221</v>
+      </c>
+      <c r="D847" t="s">
+        <v>1185</v>
+      </c>
+      <c r="E847" t="s">
         <v>1233</v>
-      </c>
-      <c r="D847" t="s">
-        <v>1186</v>
-      </c>
-      <c r="E847" t="s">
-        <v>1223</v>
       </c>
       <c r="F847" t="s">
         <v>1182</v>
@@ -21214,13 +21214,13 @@
         <v>7</v>
       </c>
       <c r="C848" t="s">
+        <v>1221</v>
+      </c>
+      <c r="D848" t="s">
+        <v>1185</v>
+      </c>
+      <c r="E848" t="s">
         <v>1233</v>
-      </c>
-      <c r="D848" t="s">
-        <v>1186</v>
-      </c>
-      <c r="E848" t="s">
-        <v>1223</v>
       </c>
       <c r="F848" t="s">
         <v>1182</v>
@@ -21234,13 +21234,13 @@
         <v>7</v>
       </c>
       <c r="C849" t="s">
+        <v>1221</v>
+      </c>
+      <c r="D849" t="s">
+        <v>1185</v>
+      </c>
+      <c r="E849" t="s">
         <v>1233</v>
-      </c>
-      <c r="D849" t="s">
-        <v>1186</v>
-      </c>
-      <c r="E849" t="s">
-        <v>1223</v>
       </c>
       <c r="F849" t="s">
         <v>713</v>
@@ -21254,13 +21254,13 @@
         <v>7</v>
       </c>
       <c r="C850" t="s">
-        <v>1233</v>
+        <v>1221</v>
       </c>
       <c r="D850" t="s">
         <v>1237</v>
       </c>
       <c r="E850" t="s">
-        <v>1223</v>
+        <v>1233</v>
       </c>
       <c r="F850" t="s">
         <v>1182</v>
@@ -21274,13 +21274,13 @@
         <v>7</v>
       </c>
       <c r="C851" t="s">
+        <v>1221</v>
+      </c>
+      <c r="D851" t="s">
+        <v>1185</v>
+      </c>
+      <c r="E851" t="s">
         <v>1233</v>
-      </c>
-      <c r="D851" t="s">
-        <v>1186</v>
-      </c>
-      <c r="E851" t="s">
-        <v>1223</v>
       </c>
       <c r="F851" t="s">
         <v>1182</v>
@@ -21294,13 +21294,13 @@
         <v>7</v>
       </c>
       <c r="C852" t="s">
+        <v>1221</v>
+      </c>
+      <c r="D852" t="s">
+        <v>1185</v>
+      </c>
+      <c r="E852" t="s">
         <v>1233</v>
-      </c>
-      <c r="D852" t="s">
-        <v>1186</v>
-      </c>
-      <c r="E852" t="s">
-        <v>1223</v>
       </c>
       <c r="F852" t="s">
         <v>1182</v>
@@ -21314,13 +21314,13 @@
         <v>7</v>
       </c>
       <c r="C853" t="s">
-        <v>1225</v>
+        <v>1221</v>
       </c>
       <c r="D853" t="s">
         <v>1222</v>
       </c>
       <c r="E853" t="s">
-        <v>1223</v>
+        <v>1225</v>
       </c>
       <c r="F853" t="s">
         <v>1182</v>
@@ -21334,13 +21334,13 @@
         <v>7</v>
       </c>
       <c r="C854" t="s">
-        <v>1225</v>
+        <v>1221</v>
       </c>
       <c r="D854" t="s">
         <v>1222</v>
       </c>
       <c r="E854" t="s">
-        <v>1223</v>
+        <v>1225</v>
       </c>
       <c r="F854" t="s">
         <v>16</v>
@@ -21354,13 +21354,13 @@
         <v>7</v>
       </c>
       <c r="C855" t="s">
-        <v>1225</v>
+        <v>1221</v>
       </c>
       <c r="D855" t="s">
         <v>1222</v>
       </c>
       <c r="E855" t="s">
-        <v>1223</v>
+        <v>1225</v>
       </c>
       <c r="F855" t="s">
         <v>16</v>
@@ -21374,13 +21374,13 @@
         <v>7</v>
       </c>
       <c r="C856" t="s">
-        <v>1225</v>
+        <v>1221</v>
       </c>
       <c r="D856" t="s">
         <v>1222</v>
       </c>
       <c r="E856" t="s">
-        <v>1223</v>
+        <v>1225</v>
       </c>
       <c r="F856" t="s">
         <v>16</v>
@@ -21394,13 +21394,13 @@
         <v>7</v>
       </c>
       <c r="C857" t="s">
-        <v>1225</v>
+        <v>1221</v>
       </c>
       <c r="D857" t="s">
         <v>1222</v>
       </c>
       <c r="E857" t="s">
-        <v>1223</v>
+        <v>1225</v>
       </c>
       <c r="F857" t="s">
         <v>1182</v>
@@ -21414,13 +21414,13 @@
         <v>7</v>
       </c>
       <c r="C858" t="s">
-        <v>1225</v>
+        <v>1221</v>
       </c>
       <c r="D858" t="s">
         <v>1222</v>
       </c>
       <c r="E858" t="s">
-        <v>1223</v>
+        <v>1225</v>
       </c>
       <c r="F858" t="s">
         <v>1182</v>
@@ -21434,13 +21434,13 @@
         <v>7</v>
       </c>
       <c r="C859" t="s">
-        <v>1225</v>
+        <v>1221</v>
       </c>
       <c r="D859" t="s">
         <v>1222</v>
       </c>
       <c r="E859" t="s">
-        <v>1223</v>
+        <v>1225</v>
       </c>
       <c r="F859" t="s">
         <v>16</v>
@@ -21454,13 +21454,13 @@
         <v>7</v>
       </c>
       <c r="C860" t="s">
-        <v>1225</v>
+        <v>1221</v>
       </c>
       <c r="D860" t="s">
         <v>1222</v>
       </c>
       <c r="E860" t="s">
-        <v>1223</v>
+        <v>1225</v>
       </c>
       <c r="F860" t="s">
         <v>1182</v>
@@ -21474,13 +21474,13 @@
         <v>7</v>
       </c>
       <c r="C861" t="s">
-        <v>1225</v>
+        <v>1221</v>
       </c>
       <c r="D861" t="s">
         <v>1222</v>
       </c>
       <c r="E861" t="s">
-        <v>1223</v>
+        <v>1225</v>
       </c>
       <c r="F861" t="s">
         <v>1182</v>
@@ -21494,13 +21494,13 @@
         <v>7</v>
       </c>
       <c r="C862" t="s">
-        <v>1225</v>
+        <v>1221</v>
       </c>
       <c r="D862" t="s">
         <v>1222</v>
       </c>
       <c r="E862" t="s">
-        <v>1223</v>
+        <v>1225</v>
       </c>
       <c r="F862" t="s">
         <v>713</v>
@@ -21514,13 +21514,13 @@
         <v>7</v>
       </c>
       <c r="C863" t="s">
-        <v>1225</v>
+        <v>1221</v>
       </c>
       <c r="D863" t="s">
         <v>1222</v>
       </c>
       <c r="E863" t="s">
-        <v>1223</v>
+        <v>1225</v>
       </c>
       <c r="F863" t="s">
         <v>1182</v>
@@ -21534,13 +21534,13 @@
         <v>7</v>
       </c>
       <c r="C864" t="s">
-        <v>1225</v>
+        <v>1221</v>
       </c>
       <c r="D864" t="s">
         <v>1222</v>
       </c>
       <c r="E864" t="s">
-        <v>1223</v>
+        <v>1225</v>
       </c>
       <c r="F864" t="s">
         <v>1182</v>
@@ -21554,13 +21554,13 @@
         <v>7</v>
       </c>
       <c r="C865" t="s">
-        <v>1225</v>
+        <v>1221</v>
       </c>
       <c r="D865" t="s">
         <v>1222</v>
       </c>
       <c r="E865" t="s">
-        <v>1223</v>
+        <v>1225</v>
       </c>
       <c r="F865" t="s">
         <v>1182</v>
@@ -21574,13 +21574,13 @@
         <v>7</v>
       </c>
       <c r="C866" t="s">
-        <v>1225</v>
+        <v>1221</v>
       </c>
       <c r="D866" t="s">
         <v>1222</v>
       </c>
       <c r="E866" t="s">
-        <v>1223</v>
+        <v>1225</v>
       </c>
       <c r="F866" t="s">
         <v>713</v>
@@ -22154,13 +22154,13 @@
         <v>7</v>
       </c>
       <c r="C895" t="s">
-        <v>1290</v>
+        <v>1282</v>
       </c>
       <c r="D895" t="s">
         <v>1283</v>
       </c>
       <c r="E895" t="s">
-        <v>1284</v>
+        <v>1290</v>
       </c>
       <c r="F895" t="s">
         <v>1182</v>
@@ -22174,13 +22174,13 @@
         <v>110</v>
       </c>
       <c r="C896" t="s">
-        <v>1290</v>
+        <v>1282</v>
       </c>
       <c r="D896" t="s">
         <v>1283</v>
       </c>
       <c r="E896" t="s">
-        <v>1284</v>
+        <v>1290</v>
       </c>
       <c r="F896" t="s">
         <v>713</v>
@@ -22374,13 +22374,13 @@
         <v>7</v>
       </c>
       <c r="C906" t="s">
-        <v>1304</v>
+        <v>1301</v>
       </c>
       <c r="D906" t="s">
         <v>1283</v>
       </c>
       <c r="E906" t="s">
-        <v>1302</v>
+        <v>1304</v>
       </c>
       <c r="F906" t="s">
         <v>1182</v>

--- a/api/1/clv3/xlsx/fr/HumanitarianPlan.xlsx
+++ b/api/1/clv3/xlsx/fr/HumanitarianPlan.xlsx
@@ -25,15 +25,15 @@
     <t>codeforiati:plan-type</t>
   </si>
   <si>
+    <t>codeforiati:plan-end-date</t>
+  </si>
+  <si>
+    <t>codeforiati:plan-start-date</t>
+  </si>
+  <si>
     <t>codeforiati:plan-year</t>
   </si>
   <si>
-    <t>codeforiati:plan-end-date</t>
-  </si>
-  <si>
-    <t>codeforiati:plan-start-date</t>
-  </si>
-  <si>
     <t>HAFG25</t>
   </si>
   <si>
@@ -43,15 +43,15 @@
     <t>Humanitarian needs and response plan</t>
   </si>
   <si>
+    <t>2025-12-31</t>
+  </si>
+  <si>
+    <t>2025-01-01</t>
+  </si>
+  <si>
     <t>2025</t>
   </si>
   <si>
-    <t>2025-12-31</t>
-  </si>
-  <si>
-    <t>2025-01-01</t>
-  </si>
-  <si>
     <t>RIRNPAK25</t>
   </si>
   <si>
@@ -217,15 +217,15 @@
     <t>HAFG24</t>
   </si>
   <si>
+    <t>2024-12-31</t>
+  </si>
+  <si>
+    <t>2024-01-01</t>
+  </si>
+  <si>
     <t>2024</t>
   </si>
   <si>
-    <t>2024-12-31</t>
-  </si>
-  <si>
-    <t>2024-01-01</t>
-  </si>
-  <si>
     <t>RAFG_RRP24</t>
   </si>
   <si>
@@ -421,15 +421,15 @@
     <t>HAFG23</t>
   </si>
   <si>
+    <t>2023-12-31</t>
+  </si>
+  <si>
+    <t>2023-01-01</t>
+  </si>
+  <si>
     <t>2023</t>
   </si>
   <si>
-    <t>2023-12-31</t>
-  </si>
-  <si>
-    <t>2023-01-01</t>
-  </si>
-  <si>
     <t>RAFG23</t>
   </si>
   <si>
@@ -601,15 +601,15 @@
     <t>HAFG22</t>
   </si>
   <si>
+    <t>2022-12-31</t>
+  </si>
+  <si>
+    <t>2022-01-01</t>
+  </si>
+  <si>
     <t>2022</t>
   </si>
   <si>
-    <t>2022-12-31</t>
-  </si>
-  <si>
-    <t>2022-01-01</t>
-  </si>
-  <si>
     <t>RAFG22</t>
   </si>
   <si>
@@ -805,15 +805,15 @@
     <t>FAFG21</t>
   </si>
   <si>
+    <t>2021-12-31</t>
+  </si>
+  <si>
+    <t>2021-09-01</t>
+  </si>
+  <si>
     <t>2021</t>
   </si>
   <si>
-    <t>2021-12-31</t>
-  </si>
-  <si>
-    <t>2021-09-01</t>
-  </si>
-  <si>
     <t>HAFG21</t>
   </si>
   <si>
@@ -1009,15 +1009,15 @@
     <t>HAFG20</t>
   </si>
   <si>
+    <t>2020-12-31</t>
+  </si>
+  <si>
+    <t>2020-01-01</t>
+  </si>
+  <si>
     <t>2020</t>
   </si>
   <si>
-    <t>2020-12-31</t>
-  </si>
-  <si>
-    <t>2020-01-01</t>
-  </si>
-  <si>
     <t>OBGD20</t>
   </si>
   <si>
@@ -1249,15 +1249,15 @@
     <t>HAFG19</t>
   </si>
   <si>
+    <t>2019-12-31</t>
+  </si>
+  <si>
+    <t>2019-01-01</t>
+  </si>
+  <si>
     <t>2019</t>
   </si>
   <si>
-    <t>2019-12-31</t>
-  </si>
-  <si>
-    <t>2019-01-01</t>
-  </si>
-  <si>
     <t>RBGD19</t>
   </si>
   <si>
@@ -1381,15 +1381,15 @@
     <t>HAFG18</t>
   </si>
   <si>
+    <t>2018-12-31</t>
+  </si>
+  <si>
+    <t>2018-01-01</t>
+  </si>
+  <si>
     <t>2018</t>
   </si>
   <si>
-    <t>2018-12-31</t>
-  </si>
-  <si>
-    <t>2018-01-01</t>
-  </si>
-  <si>
     <t>OBGD18</t>
   </si>
   <si>
@@ -1507,15 +1507,15 @@
     <t>OEUR17</t>
   </si>
   <si>
+    <t>2017-12-31</t>
+  </si>
+  <si>
+    <t>2017-01-01</t>
+  </si>
+  <si>
     <t>2017</t>
   </si>
   <si>
-    <t>2017-12-31</t>
-  </si>
-  <si>
-    <t>2017-01-01</t>
-  </si>
-  <si>
     <t>HAFG17</t>
   </si>
   <si>
@@ -1678,15 +1678,15 @@
     <t>OEUR16</t>
   </si>
   <si>
+    <t>2016-12-31</t>
+  </si>
+  <si>
+    <t>2016-01-01</t>
+  </si>
+  <si>
     <t>2016</t>
   </si>
   <si>
-    <t>2016-12-31</t>
-  </si>
-  <si>
-    <t>2016-01-01</t>
-  </si>
-  <si>
     <t>HAFG16</t>
   </si>
   <si>
@@ -1843,15 +1843,15 @@
     <t>Strategic response plan</t>
   </si>
   <si>
+    <t>2015-12-31</t>
+  </si>
+  <si>
+    <t>2015-01-01</t>
+  </si>
+  <si>
     <t>2015</t>
   </si>
   <si>
-    <t>2015-12-31</t>
-  </si>
-  <si>
-    <t>2015-01-01</t>
-  </si>
-  <si>
     <t>HBFA15</t>
   </si>
   <si>
@@ -1975,15 +1975,15 @@
     <t>HAFG14</t>
   </si>
   <si>
+    <t>2014-12-31</t>
+  </si>
+  <si>
+    <t>2014-01-01</t>
+  </si>
+  <si>
     <t>2014</t>
   </si>
   <si>
-    <t>2014-12-31</t>
-  </si>
-  <si>
-    <t>2014-01-01</t>
-  </si>
-  <si>
     <t>HBFA1314</t>
   </si>
   <si>
@@ -2152,12 +2152,12 @@
     <t>Consolidated appeals process</t>
   </si>
   <si>
+    <t>2013-12-31</t>
+  </si>
+  <si>
     <t>2013</t>
   </si>
   <si>
-    <t>2013-12-31</t>
-  </si>
-  <si>
     <t>CBFA13</t>
   </si>
   <si>
@@ -2242,15 +2242,15 @@
     <t>CKEN12</t>
   </si>
   <si>
+    <t>2012-12-31</t>
+  </si>
+  <si>
+    <t>2012-01-01</t>
+  </si>
+  <si>
     <t>2012</t>
   </si>
   <si>
-    <t>2012-12-31</t>
-  </si>
-  <si>
-    <t>2012-01-01</t>
-  </si>
-  <si>
     <t>CAFG1112</t>
   </si>
   <si>
@@ -2353,12 +2353,12 @@
     <t>CKEN1113</t>
   </si>
   <si>
+    <t>2011-01-01</t>
+  </si>
+  <si>
     <t>2011</t>
   </si>
   <si>
-    <t>2011-01-01</t>
-  </si>
-  <si>
     <t>CAFG11</t>
   </si>
   <si>
@@ -2476,15 +2476,15 @@
     <t>CAFG10</t>
   </si>
   <si>
+    <t>2010-12-31</t>
+  </si>
+  <si>
+    <t>2010-01-01</t>
+  </si>
+  <si>
     <t>2010</t>
   </si>
   <si>
-    <t>2010-12-31</t>
-  </si>
-  <si>
-    <t>2010-01-01</t>
-  </si>
-  <si>
     <t>OBFA1011</t>
   </si>
   <si>
@@ -2608,15 +2608,15 @@
     <t>CAFG09</t>
   </si>
   <si>
+    <t>2009-12-31</t>
+  </si>
+  <si>
+    <t>2009-01-01</t>
+  </si>
+  <si>
     <t>2009</t>
   </si>
   <si>
-    <t>2009-12-31</t>
-  </si>
-  <si>
-    <t>2009-01-01</t>
-  </si>
-  <si>
     <t>FBFA0910</t>
   </si>
   <si>
@@ -2746,15 +2746,15 @@
     <t>OAFG08</t>
   </si>
   <si>
+    <t>2008-06-30</t>
+  </si>
+  <si>
+    <t>2008-02-01</t>
+  </si>
+  <si>
     <t>2008</t>
   </si>
   <si>
-    <t>2008-06-30</t>
-  </si>
-  <si>
-    <t>2008-02-01</t>
-  </si>
-  <si>
     <t>OAFG0809</t>
   </si>
   <si>
@@ -2914,15 +2914,15 @@
     <t>FBOL07</t>
   </si>
   <si>
+    <t>2007-08-21</t>
+  </si>
+  <si>
+    <t>2007-02-22</t>
+  </si>
+  <si>
     <t>2007</t>
   </si>
   <si>
-    <t>2007-08-21</t>
-  </si>
-  <si>
-    <t>2007-02-22</t>
-  </si>
-  <si>
     <t>FBFA0708</t>
   </si>
   <si>
@@ -3112,15 +3112,15 @@
     <t>OAFG06</t>
   </si>
   <si>
+    <t>2006-12-31</t>
+  </si>
+  <si>
+    <t>2006-07-01</t>
+  </si>
+  <si>
     <t>2006</t>
   </si>
   <si>
-    <t>2006-12-31</t>
-  </si>
-  <si>
-    <t>2006-07-01</t>
-  </si>
-  <si>
     <t>CBDI06</t>
   </si>
   <si>
@@ -3271,15 +3271,15 @@
     <t>FAGO05</t>
   </si>
   <si>
+    <t>2005-06-30</t>
+  </si>
+  <si>
+    <t>2005-04-01</t>
+  </si>
+  <si>
     <t>2005</t>
   </si>
   <si>
-    <t>2005-06-30</t>
-  </si>
-  <si>
-    <t>2005-04-01</t>
-  </si>
-  <si>
     <t>FBEN05</t>
   </si>
   <si>
@@ -3400,15 +3400,15 @@
     <t>OAFG04</t>
   </si>
   <si>
+    <t>2004-12-31</t>
+  </si>
+  <si>
+    <t>2004-09-01</t>
+  </si>
+  <si>
     <t>2004</t>
   </si>
   <si>
-    <t>2004-12-31</t>
-  </si>
-  <si>
-    <t>2004-09-01</t>
-  </si>
-  <si>
     <t>CAGO04</t>
   </si>
   <si>
@@ -3550,15 +3550,15 @@
     <t>OAFG03</t>
   </si>
   <si>
+    <t>2003-12-31</t>
+  </si>
+  <si>
+    <t>2003-01-01</t>
+  </si>
+  <si>
     <t>2003</t>
   </si>
   <si>
-    <t>2003-12-31</t>
-  </si>
-  <si>
-    <t>2003-01-01</t>
-  </si>
-  <si>
     <t>CAGO03</t>
   </si>
   <si>
@@ -3679,15 +3679,15 @@
     <t>CAFG0102</t>
   </si>
   <si>
+    <t>2002-12-31</t>
+  </si>
+  <si>
+    <t>2001-10-01</t>
+  </si>
+  <si>
     <t>2002</t>
   </si>
   <si>
-    <t>2002-12-31</t>
-  </si>
-  <si>
-    <t>2001-10-01</t>
-  </si>
-  <si>
     <t>CAGO02</t>
   </si>
   <si>
@@ -3781,15 +3781,15 @@
     <t>CAFG01</t>
   </si>
   <si>
+    <t>2001-09-30</t>
+  </si>
+  <si>
+    <t>2001-01-01</t>
+  </si>
+  <si>
     <t>2001</t>
   </si>
   <si>
-    <t>2001-09-30</t>
-  </si>
-  <si>
-    <t>2001-01-01</t>
-  </si>
-  <si>
     <t>CAGO01</t>
   </si>
   <si>
@@ -3862,15 +3862,15 @@
     <t>CAGO00</t>
   </si>
   <si>
+    <t>2000-12-31</t>
+  </si>
+  <si>
+    <t>2000-01-01</t>
+  </si>
+  <si>
     <t>2000</t>
   </si>
   <si>
-    <t>2000-12-31</t>
-  </si>
-  <si>
-    <t>2000-01-01</t>
-  </si>
-  <si>
     <t>CBDI00</t>
   </si>
   <si>
@@ -3919,10 +3919,10 @@
     <t>CTLS9900</t>
   </si>
   <si>
+    <t>1999-10-01</t>
+  </si>
+  <si>
     <t>1999</t>
-  </si>
-  <si>
-    <t>1999-10-01</t>
   </si>
   <si>
     <t>CRUS9900</t>
@@ -4337,10 +4337,10 @@
         <v>15</v>
       </c>
       <c r="D4" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E4" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F4" t="s">
         <v>11</v>
@@ -4537,10 +4537,10 @@
         <v>24</v>
       </c>
       <c r="D14" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E14" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F14" t="s">
         <v>11</v>
@@ -4557,10 +4557,10 @@
         <v>24</v>
       </c>
       <c r="D15" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="E15" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F15" t="s">
         <v>11</v>
@@ -4597,10 +4597,10 @@
         <v>24</v>
       </c>
       <c r="D17" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="E17" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="F17" t="s">
         <v>11</v>
@@ -4637,10 +4637,10 @@
         <v>24</v>
       </c>
       <c r="D19" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="E19" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="F19" t="s">
         <v>11</v>
@@ -4660,10 +4660,10 @@
         <v>9</v>
       </c>
       <c r="E20" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="F20" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -4737,10 +4737,10 @@
         <v>15</v>
       </c>
       <c r="D24" t="s">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="E24" t="s">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="F24" t="s">
         <v>11</v>
@@ -4940,10 +4940,10 @@
         <v>9</v>
       </c>
       <c r="E34" t="s">
-        <v>10</v>
+        <v>54</v>
       </c>
       <c r="F34" t="s">
-        <v>54</v>
+        <v>11</v>
       </c>
     </row>
     <row r="35" spans="1:6">
@@ -5097,10 +5097,10 @@
         <v>15</v>
       </c>
       <c r="D42" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="E42" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="F42" t="s">
         <v>11</v>
@@ -5137,10 +5137,10 @@
         <v>24</v>
       </c>
       <c r="D44" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="E44" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="F44" t="s">
         <v>11</v>
@@ -5157,10 +5157,10 @@
         <v>24</v>
       </c>
       <c r="D45" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="E45" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F45" t="s">
         <v>11</v>
@@ -5220,10 +5220,10 @@
         <v>67</v>
       </c>
       <c r="E48" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="F48" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="49" spans="1:6">
@@ -5260,10 +5260,10 @@
         <v>67</v>
       </c>
       <c r="E50" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="F50" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
     </row>
     <row r="51" spans="1:6">
@@ -5400,10 +5400,10 @@
         <v>67</v>
       </c>
       <c r="E57" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="F57" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
     </row>
     <row r="58" spans="1:6">
@@ -5480,10 +5480,10 @@
         <v>67</v>
       </c>
       <c r="E61" t="s">
-        <v>68</v>
+        <v>88</v>
       </c>
       <c r="F61" t="s">
-        <v>88</v>
+        <v>69</v>
       </c>
     </row>
     <row r="62" spans="1:6">
@@ -5500,10 +5500,10 @@
         <v>67</v>
       </c>
       <c r="E62" t="s">
-        <v>68</v>
+        <v>88</v>
       </c>
       <c r="F62" t="s">
-        <v>88</v>
+        <v>69</v>
       </c>
     </row>
     <row r="63" spans="1:6">
@@ -5517,10 +5517,10 @@
         <v>24</v>
       </c>
       <c r="D63" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="E63" t="s">
-        <v>91</v>
+        <v>68</v>
       </c>
       <c r="F63" t="s">
         <v>69</v>
@@ -5537,10 +5537,10 @@
         <v>24</v>
       </c>
       <c r="D64" t="s">
-        <v>67</v>
+        <v>93</v>
       </c>
       <c r="E64" t="s">
-        <v>93</v>
+        <v>68</v>
       </c>
       <c r="F64" t="s">
         <v>69</v>
@@ -5560,10 +5560,10 @@
         <v>67</v>
       </c>
       <c r="E65" t="s">
-        <v>68</v>
+        <v>95</v>
       </c>
       <c r="F65" t="s">
-        <v>95</v>
+        <v>69</v>
       </c>
     </row>
     <row r="66" spans="1:6">
@@ -5597,13 +5597,13 @@
         <v>15</v>
       </c>
       <c r="D67" t="s">
-        <v>67</v>
+        <v>93</v>
       </c>
       <c r="E67" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="F67" t="s">
-        <v>98</v>
+        <v>69</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -5620,10 +5620,10 @@
         <v>67</v>
       </c>
       <c r="E68" t="s">
-        <v>68</v>
+        <v>100</v>
       </c>
       <c r="F68" t="s">
-        <v>100</v>
+        <v>69</v>
       </c>
     </row>
     <row r="69" spans="1:6">
@@ -5680,10 +5680,10 @@
         <v>67</v>
       </c>
       <c r="E71" t="s">
-        <v>68</v>
+        <v>104</v>
       </c>
       <c r="F71" t="s">
-        <v>104</v>
+        <v>69</v>
       </c>
     </row>
     <row r="72" spans="1:6">
@@ -5740,10 +5740,10 @@
         <v>67</v>
       </c>
       <c r="E74" t="s">
-        <v>68</v>
+        <v>108</v>
       </c>
       <c r="F74" t="s">
-        <v>108</v>
+        <v>69</v>
       </c>
     </row>
     <row r="75" spans="1:6">
@@ -5860,10 +5860,10 @@
         <v>67</v>
       </c>
       <c r="E80" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="F80" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
     </row>
     <row r="81" spans="1:6">
@@ -6120,10 +6120,10 @@
         <v>67</v>
       </c>
       <c r="E93" t="s">
-        <v>68</v>
+        <v>129</v>
       </c>
       <c r="F93" t="s">
-        <v>129</v>
+        <v>69</v>
       </c>
     </row>
     <row r="94" spans="1:6">
@@ -6160,10 +6160,10 @@
         <v>67</v>
       </c>
       <c r="E95" t="s">
-        <v>68</v>
+        <v>132</v>
       </c>
       <c r="F95" t="s">
-        <v>132</v>
+        <v>69</v>
       </c>
     </row>
     <row r="96" spans="1:6">
@@ -6180,10 +6180,10 @@
         <v>67</v>
       </c>
       <c r="E96" t="s">
-        <v>68</v>
+        <v>132</v>
       </c>
       <c r="F96" t="s">
-        <v>132</v>
+        <v>69</v>
       </c>
     </row>
     <row r="97" spans="1:6">
@@ -6360,10 +6360,10 @@
         <v>135</v>
       </c>
       <c r="E105" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="F105" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
     </row>
     <row r="106" spans="1:6">
@@ -6520,10 +6520,10 @@
         <v>135</v>
       </c>
       <c r="E113" t="s">
-        <v>136</v>
+        <v>155</v>
       </c>
       <c r="F113" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
     </row>
     <row r="114" spans="1:6">
@@ -6577,13 +6577,13 @@
         <v>15</v>
       </c>
       <c r="D116" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="E116" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F116" t="s">
-        <v>160</v>
+        <v>137</v>
       </c>
     </row>
     <row r="117" spans="1:6">
@@ -6597,13 +6597,13 @@
         <v>15</v>
       </c>
       <c r="D117" t="s">
-        <v>135</v>
+        <v>162</v>
       </c>
       <c r="E117" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F117" t="s">
-        <v>163</v>
+        <v>137</v>
       </c>
     </row>
     <row r="118" spans="1:6">
@@ -6697,10 +6697,10 @@
         <v>19</v>
       </c>
       <c r="D122" t="s">
-        <v>135</v>
+        <v>162</v>
       </c>
       <c r="E122" t="s">
-        <v>162</v>
+        <v>136</v>
       </c>
       <c r="F122" t="s">
         <v>137</v>
@@ -6717,10 +6717,10 @@
         <v>15</v>
       </c>
       <c r="D123" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="E123" t="s">
-        <v>159</v>
+        <v>136</v>
       </c>
       <c r="F123" t="s">
         <v>137</v>
@@ -6897,13 +6897,13 @@
         <v>13</v>
       </c>
       <c r="D132" t="s">
-        <v>135</v>
+        <v>179</v>
       </c>
       <c r="E132" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F132" t="s">
-        <v>180</v>
+        <v>137</v>
       </c>
     </row>
     <row r="133" spans="1:6">
@@ -6937,13 +6937,13 @@
         <v>24</v>
       </c>
       <c r="D134" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="E134" t="s">
-        <v>159</v>
+        <v>183</v>
       </c>
       <c r="F134" t="s">
-        <v>183</v>
+        <v>137</v>
       </c>
     </row>
     <row r="135" spans="1:6">
@@ -6977,13 +6977,13 @@
         <v>24</v>
       </c>
       <c r="D136" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="E136" t="s">
-        <v>159</v>
+        <v>186</v>
       </c>
       <c r="F136" t="s">
-        <v>186</v>
+        <v>137</v>
       </c>
     </row>
     <row r="137" spans="1:6">
@@ -7277,13 +7277,13 @@
         <v>15</v>
       </c>
       <c r="D151" t="s">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="E151" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F151" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
     </row>
     <row r="152" spans="1:6">
@@ -7377,13 +7377,13 @@
         <v>24</v>
       </c>
       <c r="D156" t="s">
-        <v>195</v>
+        <v>212</v>
       </c>
       <c r="E156" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F156" t="s">
-        <v>213</v>
+        <v>197</v>
       </c>
     </row>
     <row r="157" spans="1:6">
@@ -7400,10 +7400,10 @@
         <v>195</v>
       </c>
       <c r="E157" t="s">
-        <v>196</v>
+        <v>213</v>
       </c>
       <c r="F157" t="s">
-        <v>213</v>
+        <v>197</v>
       </c>
     </row>
     <row r="158" spans="1:6">
@@ -7477,10 +7477,10 @@
         <v>24</v>
       </c>
       <c r="D161" t="s">
-        <v>195</v>
+        <v>219</v>
       </c>
       <c r="E161" t="s">
-        <v>219</v>
+        <v>196</v>
       </c>
       <c r="F161" t="s">
         <v>197</v>
@@ -7557,13 +7557,13 @@
         <v>24</v>
       </c>
       <c r="D165" t="s">
-        <v>195</v>
+        <v>224</v>
       </c>
       <c r="E165" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F165" t="s">
-        <v>225</v>
+        <v>197</v>
       </c>
     </row>
     <row r="166" spans="1:6">
@@ -7597,13 +7597,13 @@
         <v>24</v>
       </c>
       <c r="D167" t="s">
-        <v>195</v>
+        <v>228</v>
       </c>
       <c r="E167" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F167" t="s">
-        <v>229</v>
+        <v>197</v>
       </c>
     </row>
     <row r="168" spans="1:6">
@@ -7720,10 +7720,10 @@
         <v>195</v>
       </c>
       <c r="E173" t="s">
-        <v>196</v>
+        <v>236</v>
       </c>
       <c r="F173" t="s">
-        <v>236</v>
+        <v>197</v>
       </c>
     </row>
     <row r="174" spans="1:6">
@@ -7737,13 +7737,13 @@
         <v>15</v>
       </c>
       <c r="D174" t="s">
-        <v>195</v>
+        <v>238</v>
       </c>
       <c r="E174" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="F174" t="s">
-        <v>236</v>
+        <v>197</v>
       </c>
     </row>
     <row r="175" spans="1:6">
@@ -7757,13 +7757,13 @@
         <v>15</v>
       </c>
       <c r="D175" t="s">
-        <v>195</v>
+        <v>240</v>
       </c>
       <c r="E175" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F175" t="s">
-        <v>241</v>
+        <v>197</v>
       </c>
     </row>
     <row r="176" spans="1:6">
@@ -7920,10 +7920,10 @@
         <v>195</v>
       </c>
       <c r="E183" t="s">
-        <v>196</v>
+        <v>250</v>
       </c>
       <c r="F183" t="s">
-        <v>250</v>
+        <v>197</v>
       </c>
     </row>
     <row r="184" spans="1:6">
@@ -8020,10 +8020,10 @@
         <v>195</v>
       </c>
       <c r="E188" t="s">
-        <v>196</v>
+        <v>256</v>
       </c>
       <c r="F188" t="s">
-        <v>256</v>
+        <v>197</v>
       </c>
     </row>
     <row r="189" spans="1:6">
@@ -8057,13 +8057,13 @@
         <v>13</v>
       </c>
       <c r="D190" t="s">
-        <v>195</v>
+        <v>259</v>
       </c>
       <c r="E190" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="F190" t="s">
-        <v>256</v>
+        <v>197</v>
       </c>
     </row>
     <row r="191" spans="1:6">
@@ -8140,10 +8140,10 @@
         <v>263</v>
       </c>
       <c r="E194" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="F194" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="195" spans="1:6">
@@ -8160,10 +8160,10 @@
         <v>263</v>
       </c>
       <c r="E195" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="F195" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="196" spans="1:6">
@@ -8180,10 +8180,10 @@
         <v>263</v>
       </c>
       <c r="E196" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="F196" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="197" spans="1:6">
@@ -8200,10 +8200,10 @@
         <v>263</v>
       </c>
       <c r="E197" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="F197" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="198" spans="1:6">
@@ -8220,10 +8220,10 @@
         <v>263</v>
       </c>
       <c r="E198" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="F198" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="199" spans="1:6">
@@ -8240,10 +8240,10 @@
         <v>263</v>
       </c>
       <c r="E199" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="F199" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="200" spans="1:6">
@@ -8260,10 +8260,10 @@
         <v>263</v>
       </c>
       <c r="E200" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="F200" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="201" spans="1:6">
@@ -8280,10 +8280,10 @@
         <v>263</v>
       </c>
       <c r="E201" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="F201" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="202" spans="1:6">
@@ -8300,10 +8300,10 @@
         <v>263</v>
       </c>
       <c r="E202" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="F202" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="203" spans="1:6">
@@ -8320,10 +8320,10 @@
         <v>263</v>
       </c>
       <c r="E203" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="F203" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="204" spans="1:6">
@@ -8340,10 +8340,10 @@
         <v>263</v>
       </c>
       <c r="E204" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="F204" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="205" spans="1:6">
@@ -8360,10 +8360,10 @@
         <v>263</v>
       </c>
       <c r="E205" t="s">
-        <v>264</v>
+        <v>279</v>
       </c>
       <c r="F205" t="s">
-        <v>279</v>
+        <v>265</v>
       </c>
     </row>
     <row r="206" spans="1:6">
@@ -8377,13 +8377,13 @@
         <v>19</v>
       </c>
       <c r="D206" t="s">
-        <v>263</v>
+        <v>195</v>
       </c>
       <c r="E206" t="s">
-        <v>196</v>
+        <v>279</v>
       </c>
       <c r="F206" t="s">
-        <v>279</v>
+        <v>265</v>
       </c>
     </row>
     <row r="207" spans="1:6">
@@ -8397,13 +8397,13 @@
         <v>24</v>
       </c>
       <c r="D207" t="s">
-        <v>263</v>
+        <v>282</v>
       </c>
       <c r="E207" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F207" t="s">
-        <v>283</v>
+        <v>265</v>
       </c>
     </row>
     <row r="208" spans="1:6">
@@ -8420,10 +8420,10 @@
         <v>263</v>
       </c>
       <c r="E208" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="F208" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="209" spans="1:6">
@@ -8440,10 +8440,10 @@
         <v>263</v>
       </c>
       <c r="E209" t="s">
-        <v>264</v>
+        <v>279</v>
       </c>
       <c r="F209" t="s">
-        <v>279</v>
+        <v>265</v>
       </c>
     </row>
     <row r="210" spans="1:6">
@@ -8457,13 +8457,13 @@
         <v>19</v>
       </c>
       <c r="D210" t="s">
-        <v>263</v>
+        <v>195</v>
       </c>
       <c r="E210" t="s">
-        <v>196</v>
+        <v>279</v>
       </c>
       <c r="F210" t="s">
-        <v>279</v>
+        <v>265</v>
       </c>
     </row>
     <row r="211" spans="1:6">
@@ -8477,13 +8477,13 @@
         <v>24</v>
       </c>
       <c r="D211" t="s">
-        <v>263</v>
+        <v>288</v>
       </c>
       <c r="E211" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F211" t="s">
-        <v>289</v>
+        <v>265</v>
       </c>
     </row>
     <row r="212" spans="1:6">
@@ -8500,10 +8500,10 @@
         <v>263</v>
       </c>
       <c r="E212" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="F212" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="213" spans="1:6">
@@ -8517,13 +8517,13 @@
         <v>24</v>
       </c>
       <c r="D213" t="s">
-        <v>263</v>
+        <v>292</v>
       </c>
       <c r="E213" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F213" t="s">
-        <v>293</v>
+        <v>265</v>
       </c>
     </row>
     <row r="214" spans="1:6">
@@ -8540,10 +8540,10 @@
         <v>263</v>
       </c>
       <c r="E214" t="s">
-        <v>264</v>
+        <v>279</v>
       </c>
       <c r="F214" t="s">
-        <v>279</v>
+        <v>265</v>
       </c>
     </row>
     <row r="215" spans="1:6">
@@ -8557,13 +8557,13 @@
         <v>19</v>
       </c>
       <c r="D215" t="s">
-        <v>263</v>
+        <v>195</v>
       </c>
       <c r="E215" t="s">
-        <v>196</v>
+        <v>279</v>
       </c>
       <c r="F215" t="s">
-        <v>279</v>
+        <v>265</v>
       </c>
     </row>
     <row r="216" spans="1:6">
@@ -8580,10 +8580,10 @@
         <v>263</v>
       </c>
       <c r="E216" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="F216" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="217" spans="1:6">
@@ -8600,10 +8600,10 @@
         <v>263</v>
       </c>
       <c r="E217" t="s">
-        <v>264</v>
+        <v>298</v>
       </c>
       <c r="F217" t="s">
-        <v>298</v>
+        <v>265</v>
       </c>
     </row>
     <row r="218" spans="1:6">
@@ -8617,13 +8617,13 @@
         <v>15</v>
       </c>
       <c r="D218" t="s">
-        <v>263</v>
+        <v>300</v>
       </c>
       <c r="E218" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F218" t="s">
-        <v>301</v>
+        <v>265</v>
       </c>
     </row>
     <row r="219" spans="1:6">
@@ -8640,10 +8640,10 @@
         <v>263</v>
       </c>
       <c r="E219" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="F219" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="220" spans="1:6">
@@ -8657,13 +8657,13 @@
         <v>24</v>
       </c>
       <c r="D220" t="s">
-        <v>263</v>
+        <v>224</v>
       </c>
       <c r="E220" t="s">
-        <v>224</v>
+        <v>267</v>
       </c>
       <c r="F220" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="221" spans="1:6">
@@ -8680,10 +8680,10 @@
         <v>263</v>
       </c>
       <c r="E221" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="F221" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="222" spans="1:6">
@@ -8700,10 +8700,10 @@
         <v>263</v>
       </c>
       <c r="E222" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="F222" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="223" spans="1:6">
@@ -8720,10 +8720,10 @@
         <v>263</v>
       </c>
       <c r="E223" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="F223" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="224" spans="1:6">
@@ -8740,10 +8740,10 @@
         <v>263</v>
       </c>
       <c r="E224" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="F224" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="225" spans="1:6">
@@ -8760,10 +8760,10 @@
         <v>263</v>
       </c>
       <c r="E225" t="s">
-        <v>264</v>
+        <v>309</v>
       </c>
       <c r="F225" t="s">
-        <v>309</v>
+        <v>265</v>
       </c>
     </row>
     <row r="226" spans="1:6">
@@ -8780,10 +8780,10 @@
         <v>263</v>
       </c>
       <c r="E226" t="s">
-        <v>264</v>
+        <v>311</v>
       </c>
       <c r="F226" t="s">
-        <v>311</v>
+        <v>265</v>
       </c>
     </row>
     <row r="227" spans="1:6">
@@ -8800,10 +8800,10 @@
         <v>263</v>
       </c>
       <c r="E227" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="F227" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="228" spans="1:6">
@@ -8820,10 +8820,10 @@
         <v>263</v>
       </c>
       <c r="E228" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="F228" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="229" spans="1:6">
@@ -8840,10 +8840,10 @@
         <v>263</v>
       </c>
       <c r="E229" t="s">
-        <v>264</v>
+        <v>311</v>
       </c>
       <c r="F229" t="s">
-        <v>311</v>
+        <v>265</v>
       </c>
     </row>
     <row r="230" spans="1:6">
@@ -8860,10 +8860,10 @@
         <v>263</v>
       </c>
       <c r="E230" t="s">
-        <v>264</v>
+        <v>311</v>
       </c>
       <c r="F230" t="s">
-        <v>311</v>
+        <v>265</v>
       </c>
     </row>
     <row r="231" spans="1:6">
@@ -8880,10 +8880,10 @@
         <v>263</v>
       </c>
       <c r="E231" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="F231" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="232" spans="1:6">
@@ -8900,10 +8900,10 @@
         <v>263</v>
       </c>
       <c r="E232" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="F232" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="233" spans="1:6">
@@ -8920,10 +8920,10 @@
         <v>263</v>
       </c>
       <c r="E233" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="F233" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="234" spans="1:6">
@@ -8940,10 +8940,10 @@
         <v>263</v>
       </c>
       <c r="E234" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="F234" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="235" spans="1:6">
@@ -8960,10 +8960,10 @@
         <v>263</v>
       </c>
       <c r="E235" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="F235" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="236" spans="1:6">
@@ -8980,10 +8980,10 @@
         <v>263</v>
       </c>
       <c r="E236" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="F236" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="237" spans="1:6">
@@ -9000,10 +9000,10 @@
         <v>263</v>
       </c>
       <c r="E237" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="F237" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="238" spans="1:6">
@@ -9020,10 +9020,10 @@
         <v>263</v>
       </c>
       <c r="E238" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="F238" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="239" spans="1:6">
@@ -9040,10 +9040,10 @@
         <v>263</v>
       </c>
       <c r="E239" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="F239" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="240" spans="1:6">
@@ -9060,10 +9060,10 @@
         <v>263</v>
       </c>
       <c r="E240" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="F240" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="241" spans="1:6">
@@ -9080,10 +9080,10 @@
         <v>263</v>
       </c>
       <c r="E241" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="F241" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="242" spans="1:6">
@@ -9100,10 +9100,10 @@
         <v>263</v>
       </c>
       <c r="E242" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="F242" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="243" spans="1:6">
@@ -9120,10 +9120,10 @@
         <v>263</v>
       </c>
       <c r="E243" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="F243" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="244" spans="1:6">
@@ -9140,10 +9140,10 @@
         <v>263</v>
       </c>
       <c r="E244" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="F244" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="245" spans="1:6">
@@ -9180,10 +9180,10 @@
         <v>331</v>
       </c>
       <c r="E246" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="F246" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="247" spans="1:6">
@@ -9220,10 +9220,10 @@
         <v>331</v>
       </c>
       <c r="E248" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="F248" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="249" spans="1:6">
@@ -9300,10 +9300,10 @@
         <v>331</v>
       </c>
       <c r="E252" t="s">
-        <v>332</v>
+        <v>342</v>
       </c>
       <c r="F252" t="s">
-        <v>342</v>
+        <v>333</v>
       </c>
     </row>
     <row r="253" spans="1:6">
@@ -9337,13 +9337,13 @@
         <v>19</v>
       </c>
       <c r="D254" t="s">
-        <v>331</v>
+        <v>267</v>
       </c>
       <c r="E254" t="s">
-        <v>267</v>
+        <v>345</v>
       </c>
       <c r="F254" t="s">
-        <v>345</v>
+        <v>333</v>
       </c>
     </row>
     <row r="255" spans="1:6">
@@ -9400,10 +9400,10 @@
         <v>331</v>
       </c>
       <c r="E257" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="F257" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="258" spans="1:6">
@@ -9420,10 +9420,10 @@
         <v>331</v>
       </c>
       <c r="E258" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="F258" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="259" spans="1:6">
@@ -9440,10 +9440,10 @@
         <v>331</v>
       </c>
       <c r="E259" t="s">
-        <v>332</v>
+        <v>351</v>
       </c>
       <c r="F259" t="s">
-        <v>351</v>
+        <v>333</v>
       </c>
     </row>
     <row r="260" spans="1:6">
@@ -9497,13 +9497,13 @@
         <v>24</v>
       </c>
       <c r="D262" t="s">
-        <v>331</v>
+        <v>355</v>
       </c>
       <c r="E262" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="F262" t="s">
-        <v>356</v>
+        <v>333</v>
       </c>
     </row>
     <row r="263" spans="1:6">
@@ -9520,10 +9520,10 @@
         <v>331</v>
       </c>
       <c r="E263" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="F263" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="264" spans="1:6">
@@ -9540,10 +9540,10 @@
         <v>331</v>
       </c>
       <c r="E264" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="F264" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="265" spans="1:6">
@@ -9580,10 +9580,10 @@
         <v>331</v>
       </c>
       <c r="E266" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="F266" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="267" spans="1:6">
@@ -9620,10 +9620,10 @@
         <v>331</v>
       </c>
       <c r="E268" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="F268" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="269" spans="1:6">
@@ -9640,10 +9640,10 @@
         <v>331</v>
       </c>
       <c r="E269" t="s">
-        <v>332</v>
+        <v>351</v>
       </c>
       <c r="F269" t="s">
-        <v>351</v>
+        <v>333</v>
       </c>
     </row>
     <row r="270" spans="1:6">
@@ -9660,10 +9660,10 @@
         <v>331</v>
       </c>
       <c r="E270" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="F270" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="271" spans="1:6">
@@ -9680,10 +9680,10 @@
         <v>331</v>
       </c>
       <c r="E271" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="F271" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="272" spans="1:6">
@@ -9720,10 +9720,10 @@
         <v>331</v>
       </c>
       <c r="E273" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="F273" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="274" spans="1:6">
@@ -9760,10 +9760,10 @@
         <v>331</v>
       </c>
       <c r="E275" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="F275" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="276" spans="1:6">
@@ -9780,10 +9780,10 @@
         <v>331</v>
       </c>
       <c r="E276" t="s">
-        <v>332</v>
+        <v>371</v>
       </c>
       <c r="F276" t="s">
-        <v>371</v>
+        <v>333</v>
       </c>
     </row>
     <row r="277" spans="1:6">
@@ -9797,13 +9797,13 @@
         <v>24</v>
       </c>
       <c r="D277" t="s">
-        <v>331</v>
+        <v>373</v>
       </c>
       <c r="E277" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="F277" t="s">
-        <v>374</v>
+        <v>333</v>
       </c>
     </row>
     <row r="278" spans="1:6">
@@ -9820,10 +9820,10 @@
         <v>331</v>
       </c>
       <c r="E278" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="F278" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="279" spans="1:6">
@@ -9837,13 +9837,13 @@
         <v>24</v>
       </c>
       <c r="D279" t="s">
-        <v>331</v>
+        <v>377</v>
       </c>
       <c r="E279" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F279" t="s">
-        <v>378</v>
+        <v>333</v>
       </c>
     </row>
     <row r="280" spans="1:6">
@@ -9860,10 +9860,10 @@
         <v>331</v>
       </c>
       <c r="E280" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="F280" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="281" spans="1:6">
@@ -9920,10 +9920,10 @@
         <v>331</v>
       </c>
       <c r="E283" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="F283" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="284" spans="1:6">
@@ -10020,10 +10020,10 @@
         <v>331</v>
       </c>
       <c r="E288" t="s">
-        <v>332</v>
+        <v>371</v>
       </c>
       <c r="F288" t="s">
-        <v>371</v>
+        <v>333</v>
       </c>
     </row>
     <row r="289" spans="1:6">
@@ -10040,10 +10040,10 @@
         <v>331</v>
       </c>
       <c r="E289" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="F289" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="290" spans="1:6">
@@ -10100,10 +10100,10 @@
         <v>331</v>
       </c>
       <c r="E292" t="s">
-        <v>332</v>
+        <v>371</v>
       </c>
       <c r="F292" t="s">
-        <v>371</v>
+        <v>333</v>
       </c>
     </row>
     <row r="293" spans="1:6">
@@ -10120,10 +10120,10 @@
         <v>331</v>
       </c>
       <c r="E293" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="F293" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="294" spans="1:6">
@@ -10260,10 +10260,10 @@
         <v>331</v>
       </c>
       <c r="E300" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="F300" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="301" spans="1:6">
@@ -10280,10 +10280,10 @@
         <v>331</v>
       </c>
       <c r="E301" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="F301" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="302" spans="1:6">
@@ -10300,10 +10300,10 @@
         <v>331</v>
       </c>
       <c r="E302" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="F302" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="303" spans="1:6">
@@ -10340,10 +10340,10 @@
         <v>331</v>
       </c>
       <c r="E304" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="F304" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="305" spans="1:6">
@@ -10397,13 +10397,13 @@
         <v>15</v>
       </c>
       <c r="D307" t="s">
-        <v>331</v>
+        <v>355</v>
       </c>
       <c r="E307" t="s">
-        <v>355</v>
+        <v>407</v>
       </c>
       <c r="F307" t="s">
-        <v>407</v>
+        <v>333</v>
       </c>
     </row>
     <row r="308" spans="1:6">
@@ -10420,10 +10420,10 @@
         <v>331</v>
       </c>
       <c r="E308" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="F308" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="309" spans="1:6">
@@ -10720,10 +10720,10 @@
         <v>411</v>
       </c>
       <c r="E323" t="s">
-        <v>412</v>
+        <v>427</v>
       </c>
       <c r="F323" t="s">
-        <v>427</v>
+        <v>413</v>
       </c>
     </row>
     <row r="324" spans="1:6">
@@ -10757,10 +10757,10 @@
         <v>24</v>
       </c>
       <c r="D325" t="s">
-        <v>411</v>
+        <v>430</v>
       </c>
       <c r="E325" t="s">
-        <v>430</v>
+        <v>412</v>
       </c>
       <c r="F325" t="s">
         <v>413</v>
@@ -10877,10 +10877,10 @@
         <v>19</v>
       </c>
       <c r="D331" t="s">
-        <v>411</v>
+        <v>437</v>
       </c>
       <c r="E331" t="s">
-        <v>437</v>
+        <v>412</v>
       </c>
       <c r="F331" t="s">
         <v>413</v>
@@ -11117,13 +11117,13 @@
         <v>24</v>
       </c>
       <c r="D343" t="s">
-        <v>411</v>
+        <v>450</v>
       </c>
       <c r="E343" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="F343" t="s">
-        <v>451</v>
+        <v>413</v>
       </c>
     </row>
     <row r="344" spans="1:6">
@@ -11137,13 +11137,13 @@
         <v>24</v>
       </c>
       <c r="D344" t="s">
-        <v>411</v>
+        <v>450</v>
       </c>
       <c r="E344" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="F344" t="s">
-        <v>453</v>
+        <v>413</v>
       </c>
     </row>
     <row r="345" spans="1:6">
@@ -11180,10 +11180,10 @@
         <v>455</v>
       </c>
       <c r="E346" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="F346" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
     </row>
     <row r="347" spans="1:6">
@@ -11380,10 +11380,10 @@
         <v>455</v>
       </c>
       <c r="E356" t="s">
-        <v>456</v>
+        <v>470</v>
       </c>
       <c r="F356" t="s">
-        <v>470</v>
+        <v>457</v>
       </c>
     </row>
     <row r="357" spans="1:6">
@@ -11580,10 +11580,10 @@
         <v>455</v>
       </c>
       <c r="E366" t="s">
-        <v>456</v>
+        <v>481</v>
       </c>
       <c r="F366" t="s">
-        <v>481</v>
+        <v>457</v>
       </c>
     </row>
     <row r="367" spans="1:6">
@@ -11600,10 +11600,10 @@
         <v>455</v>
       </c>
       <c r="E367" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="F367" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
     </row>
     <row r="368" spans="1:6">
@@ -11677,10 +11677,10 @@
         <v>19</v>
       </c>
       <c r="D371" t="s">
-        <v>455</v>
+        <v>487</v>
       </c>
       <c r="E371" t="s">
-        <v>487</v>
+        <v>456</v>
       </c>
       <c r="F371" t="s">
         <v>457</v>
@@ -11697,13 +11697,13 @@
         <v>19</v>
       </c>
       <c r="D372" t="s">
-        <v>455</v>
+        <v>489</v>
       </c>
       <c r="E372" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="F372" t="s">
-        <v>490</v>
+        <v>457</v>
       </c>
     </row>
     <row r="373" spans="1:6">
@@ -11737,13 +11737,13 @@
         <v>19</v>
       </c>
       <c r="D374" t="s">
-        <v>455</v>
+        <v>489</v>
       </c>
       <c r="E374" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="F374" t="s">
-        <v>490</v>
+        <v>457</v>
       </c>
     </row>
     <row r="375" spans="1:6">
@@ -11860,10 +11860,10 @@
         <v>497</v>
       </c>
       <c r="E380" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="F380" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
     </row>
     <row r="381" spans="1:6">
@@ -11980,10 +11980,10 @@
         <v>497</v>
       </c>
       <c r="E386" t="s">
-        <v>498</v>
+        <v>509</v>
       </c>
       <c r="F386" t="s">
-        <v>509</v>
+        <v>499</v>
       </c>
     </row>
     <row r="387" spans="1:6">
@@ -12000,10 +12000,10 @@
         <v>497</v>
       </c>
       <c r="E387" t="s">
-        <v>498</v>
+        <v>511</v>
       </c>
       <c r="F387" t="s">
-        <v>511</v>
+        <v>499</v>
       </c>
     </row>
     <row r="388" spans="1:6">
@@ -12037,13 +12037,13 @@
         <v>24</v>
       </c>
       <c r="D389" t="s">
-        <v>497</v>
+        <v>514</v>
       </c>
       <c r="E389" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="F389" t="s">
-        <v>515</v>
+        <v>499</v>
       </c>
     </row>
     <row r="390" spans="1:6">
@@ -12120,10 +12120,10 @@
         <v>497</v>
       </c>
       <c r="E393" t="s">
-        <v>498</v>
+        <v>520</v>
       </c>
       <c r="F393" t="s">
-        <v>520</v>
+        <v>499</v>
       </c>
     </row>
     <row r="394" spans="1:6">
@@ -12157,13 +12157,13 @@
         <v>24</v>
       </c>
       <c r="D395" t="s">
-        <v>497</v>
+        <v>523</v>
       </c>
       <c r="E395" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="F395" t="s">
-        <v>524</v>
+        <v>499</v>
       </c>
     </row>
     <row r="396" spans="1:6">
@@ -12197,13 +12197,13 @@
         <v>24</v>
       </c>
       <c r="D397" t="s">
-        <v>497</v>
+        <v>527</v>
       </c>
       <c r="E397" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="F397" t="s">
-        <v>528</v>
+        <v>499</v>
       </c>
     </row>
     <row r="398" spans="1:6">
@@ -12257,13 +12257,13 @@
         <v>24</v>
       </c>
       <c r="D400" t="s">
-        <v>497</v>
+        <v>532</v>
       </c>
       <c r="E400" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="F400" t="s">
-        <v>533</v>
+        <v>499</v>
       </c>
     </row>
     <row r="401" spans="1:6">
@@ -12377,13 +12377,13 @@
         <v>24</v>
       </c>
       <c r="D406" t="s">
-        <v>497</v>
+        <v>540</v>
       </c>
       <c r="E406" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="F406" t="s">
-        <v>541</v>
+        <v>499</v>
       </c>
     </row>
     <row r="407" spans="1:6">
@@ -12400,10 +12400,10 @@
         <v>497</v>
       </c>
       <c r="E407" t="s">
-        <v>498</v>
+        <v>543</v>
       </c>
       <c r="F407" t="s">
-        <v>543</v>
+        <v>499</v>
       </c>
     </row>
     <row r="408" spans="1:6">
@@ -12640,10 +12640,10 @@
         <v>554</v>
       </c>
       <c r="E419" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="F419" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
     </row>
     <row r="420" spans="1:6">
@@ -12680,10 +12680,10 @@
         <v>554</v>
       </c>
       <c r="E421" t="s">
-        <v>555</v>
+        <v>562</v>
       </c>
       <c r="F421" t="s">
-        <v>562</v>
+        <v>556</v>
       </c>
     </row>
     <row r="422" spans="1:6">
@@ -12817,13 +12817,13 @@
         <v>24</v>
       </c>
       <c r="D428" t="s">
-        <v>554</v>
+        <v>570</v>
       </c>
       <c r="E428" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="F428" t="s">
-        <v>571</v>
+        <v>556</v>
       </c>
     </row>
     <row r="429" spans="1:6">
@@ -12837,13 +12837,13 @@
         <v>24</v>
       </c>
       <c r="D429" t="s">
-        <v>554</v>
+        <v>573</v>
       </c>
       <c r="E429" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F429" t="s">
-        <v>574</v>
+        <v>556</v>
       </c>
     </row>
     <row r="430" spans="1:6">
@@ -12920,10 +12920,10 @@
         <v>554</v>
       </c>
       <c r="E433" t="s">
-        <v>555</v>
+        <v>579</v>
       </c>
       <c r="F433" t="s">
-        <v>579</v>
+        <v>556</v>
       </c>
     </row>
     <row r="434" spans="1:6">
@@ -12980,10 +12980,10 @@
         <v>554</v>
       </c>
       <c r="E436" t="s">
-        <v>555</v>
+        <v>583</v>
       </c>
       <c r="F436" t="s">
-        <v>583</v>
+        <v>556</v>
       </c>
     </row>
     <row r="437" spans="1:6">
@@ -13000,10 +13000,10 @@
         <v>554</v>
       </c>
       <c r="E437" t="s">
-        <v>555</v>
+        <v>585</v>
       </c>
       <c r="F437" t="s">
-        <v>585</v>
+        <v>556</v>
       </c>
     </row>
     <row r="438" spans="1:6">
@@ -13057,13 +13057,13 @@
         <v>24</v>
       </c>
       <c r="D440" t="s">
-        <v>554</v>
+        <v>589</v>
       </c>
       <c r="E440" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="F440" t="s">
-        <v>590</v>
+        <v>556</v>
       </c>
     </row>
     <row r="441" spans="1:6">
@@ -13337,13 +13337,13 @@
         <v>19</v>
       </c>
       <c r="D454" t="s">
-        <v>554</v>
+        <v>605</v>
       </c>
       <c r="E454" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="F454" t="s">
-        <v>606</v>
+        <v>556</v>
       </c>
     </row>
     <row r="455" spans="1:6">
@@ -13537,13 +13537,13 @@
         <v>24</v>
       </c>
       <c r="D464" t="s">
-        <v>609</v>
+        <v>621</v>
       </c>
       <c r="E464" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="F464" t="s">
-        <v>622</v>
+        <v>611</v>
       </c>
     </row>
     <row r="465" spans="1:6">
@@ -13560,10 +13560,10 @@
         <v>609</v>
       </c>
       <c r="E465" t="s">
-        <v>610</v>
+        <v>624</v>
       </c>
       <c r="F465" t="s">
-        <v>624</v>
+        <v>611</v>
       </c>
     </row>
     <row r="466" spans="1:6">
@@ -13577,13 +13577,13 @@
         <v>24</v>
       </c>
       <c r="D466" t="s">
-        <v>609</v>
+        <v>621</v>
       </c>
       <c r="E466" t="s">
-        <v>621</v>
+        <v>626</v>
       </c>
       <c r="F466" t="s">
-        <v>626</v>
+        <v>611</v>
       </c>
     </row>
     <row r="467" spans="1:6">
@@ -13597,13 +13597,13 @@
         <v>24</v>
       </c>
       <c r="D467" t="s">
-        <v>609</v>
+        <v>628</v>
       </c>
       <c r="E467" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="F467" t="s">
-        <v>629</v>
+        <v>611</v>
       </c>
     </row>
     <row r="468" spans="1:6">
@@ -13637,13 +13637,13 @@
         <v>24</v>
       </c>
       <c r="D469" t="s">
-        <v>609</v>
+        <v>632</v>
       </c>
       <c r="E469" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="F469" t="s">
-        <v>633</v>
+        <v>611</v>
       </c>
     </row>
     <row r="470" spans="1:6">
@@ -13717,13 +13717,13 @@
         <v>24</v>
       </c>
       <c r="D473" t="s">
-        <v>609</v>
+        <v>621</v>
       </c>
       <c r="E473" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="F473" t="s">
-        <v>638</v>
+        <v>611</v>
       </c>
     </row>
     <row r="474" spans="1:6">
@@ -14020,10 +14020,10 @@
         <v>653</v>
       </c>
       <c r="E488" t="s">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="F488" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
     </row>
     <row r="489" spans="1:6">
@@ -14097,10 +14097,10 @@
         <v>19</v>
       </c>
       <c r="D492" t="s">
-        <v>653</v>
+        <v>662</v>
       </c>
       <c r="E492" t="s">
-        <v>662</v>
+        <v>654</v>
       </c>
       <c r="F492" t="s">
         <v>655</v>
@@ -14137,13 +14137,13 @@
         <v>13</v>
       </c>
       <c r="D494" t="s">
-        <v>653</v>
+        <v>665</v>
       </c>
       <c r="E494" t="s">
-        <v>665</v>
+        <v>633</v>
       </c>
       <c r="F494" t="s">
-        <v>633</v>
+        <v>655</v>
       </c>
     </row>
     <row r="495" spans="1:6">
@@ -14157,13 +14157,13 @@
         <v>15</v>
       </c>
       <c r="D495" t="s">
-        <v>653</v>
+        <v>665</v>
       </c>
       <c r="E495" t="s">
-        <v>665</v>
+        <v>633</v>
       </c>
       <c r="F495" t="s">
-        <v>633</v>
+        <v>655</v>
       </c>
     </row>
     <row r="496" spans="1:6">
@@ -14220,10 +14220,10 @@
         <v>653</v>
       </c>
       <c r="E498" t="s">
-        <v>654</v>
+        <v>670</v>
       </c>
       <c r="F498" t="s">
-        <v>670</v>
+        <v>655</v>
       </c>
     </row>
     <row r="499" spans="1:6">
@@ -14300,10 +14300,10 @@
         <v>653</v>
       </c>
       <c r="E502" t="s">
-        <v>654</v>
+        <v>675</v>
       </c>
       <c r="F502" t="s">
-        <v>675</v>
+        <v>655</v>
       </c>
     </row>
     <row r="503" spans="1:6">
@@ -14397,13 +14397,13 @@
         <v>24</v>
       </c>
       <c r="D507" t="s">
-        <v>653</v>
+        <v>681</v>
       </c>
       <c r="E507" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="F507" t="s">
-        <v>682</v>
+        <v>655</v>
       </c>
     </row>
     <row r="508" spans="1:6">
@@ -14417,13 +14417,13 @@
         <v>608</v>
       </c>
       <c r="D508" t="s">
-        <v>653</v>
+        <v>684</v>
       </c>
       <c r="E508" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="F508" t="s">
-        <v>685</v>
+        <v>655</v>
       </c>
     </row>
     <row r="509" spans="1:6">
@@ -14437,13 +14437,13 @@
         <v>19</v>
       </c>
       <c r="D509" t="s">
-        <v>653</v>
+        <v>687</v>
       </c>
       <c r="E509" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="F509" t="s">
-        <v>685</v>
+        <v>655</v>
       </c>
     </row>
     <row r="510" spans="1:6">
@@ -14457,13 +14457,13 @@
         <v>24</v>
       </c>
       <c r="D510" t="s">
-        <v>653</v>
+        <v>689</v>
       </c>
       <c r="E510" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="F510" t="s">
-        <v>690</v>
+        <v>655</v>
       </c>
     </row>
     <row r="511" spans="1:6">
@@ -14500,10 +14500,10 @@
         <v>653</v>
       </c>
       <c r="E512" t="s">
-        <v>654</v>
+        <v>693</v>
       </c>
       <c r="F512" t="s">
-        <v>693</v>
+        <v>655</v>
       </c>
     </row>
     <row r="513" spans="1:6">
@@ -14517,10 +14517,10 @@
         <v>19</v>
       </c>
       <c r="D513" t="s">
-        <v>653</v>
+        <v>695</v>
       </c>
       <c r="E513" t="s">
-        <v>695</v>
+        <v>654</v>
       </c>
       <c r="F513" t="s">
         <v>655</v>
@@ -14680,10 +14680,10 @@
         <v>653</v>
       </c>
       <c r="E521" t="s">
-        <v>654</v>
+        <v>704</v>
       </c>
       <c r="F521" t="s">
-        <v>704</v>
+        <v>655</v>
       </c>
     </row>
     <row r="522" spans="1:6">
@@ -14700,10 +14700,10 @@
         <v>653</v>
       </c>
       <c r="E522" t="s">
-        <v>654</v>
+        <v>706</v>
       </c>
       <c r="F522" t="s">
-        <v>706</v>
+        <v>655</v>
       </c>
     </row>
     <row r="523" spans="1:6">
@@ -14720,10 +14720,10 @@
         <v>653</v>
       </c>
       <c r="E523" t="s">
-        <v>654</v>
+        <v>708</v>
       </c>
       <c r="F523" t="s">
-        <v>708</v>
+        <v>655</v>
       </c>
     </row>
     <row r="524" spans="1:6">
@@ -14760,10 +14760,10 @@
         <v>712</v>
       </c>
       <c r="E525" t="s">
+        <v>657</v>
+      </c>
+      <c r="F525" t="s">
         <v>713</v>
-      </c>
-      <c r="F525" t="s">
-        <v>657</v>
       </c>
     </row>
     <row r="526" spans="1:6">
@@ -14780,10 +14780,10 @@
         <v>712</v>
       </c>
       <c r="E526" t="s">
+        <v>657</v>
+      </c>
+      <c r="F526" t="s">
         <v>713</v>
-      </c>
-      <c r="F526" t="s">
-        <v>657</v>
       </c>
     </row>
     <row r="527" spans="1:6">
@@ -14800,10 +14800,10 @@
         <v>712</v>
       </c>
       <c r="E527" t="s">
+        <v>657</v>
+      </c>
+      <c r="F527" t="s">
         <v>713</v>
-      </c>
-      <c r="F527" t="s">
-        <v>657</v>
       </c>
     </row>
     <row r="528" spans="1:6">
@@ -14820,10 +14820,10 @@
         <v>712</v>
       </c>
       <c r="E528" t="s">
+        <v>657</v>
+      </c>
+      <c r="F528" t="s">
         <v>713</v>
-      </c>
-      <c r="F528" t="s">
-        <v>657</v>
       </c>
     </row>
     <row r="529" spans="1:6">
@@ -14840,10 +14840,10 @@
         <v>712</v>
       </c>
       <c r="E529" t="s">
+        <v>718</v>
+      </c>
+      <c r="F529" t="s">
         <v>713</v>
-      </c>
-      <c r="F529" t="s">
-        <v>718</v>
       </c>
     </row>
     <row r="530" spans="1:6">
@@ -14857,13 +14857,13 @@
         <v>711</v>
       </c>
       <c r="D530" t="s">
-        <v>712</v>
+        <v>720</v>
       </c>
       <c r="E530" t="s">
-        <v>720</v>
+        <v>657</v>
       </c>
       <c r="F530" t="s">
-        <v>657</v>
+        <v>713</v>
       </c>
     </row>
     <row r="531" spans="1:6">
@@ -14880,10 +14880,10 @@
         <v>712</v>
       </c>
       <c r="E531" t="s">
+        <v>657</v>
+      </c>
+      <c r="F531" t="s">
         <v>713</v>
-      </c>
-      <c r="F531" t="s">
-        <v>657</v>
       </c>
     </row>
     <row r="532" spans="1:6">
@@ -14900,10 +14900,10 @@
         <v>712</v>
       </c>
       <c r="E532" t="s">
+        <v>657</v>
+      </c>
+      <c r="F532" t="s">
         <v>713</v>
-      </c>
-      <c r="F532" t="s">
-        <v>657</v>
       </c>
     </row>
     <row r="533" spans="1:6">
@@ -14920,10 +14920,10 @@
         <v>712</v>
       </c>
       <c r="E533" t="s">
+        <v>657</v>
+      </c>
+      <c r="F533" t="s">
         <v>713</v>
-      </c>
-      <c r="F533" t="s">
-        <v>657</v>
       </c>
     </row>
     <row r="534" spans="1:6">
@@ -14940,10 +14940,10 @@
         <v>712</v>
       </c>
       <c r="E534" t="s">
+        <v>657</v>
+      </c>
+      <c r="F534" t="s">
         <v>713</v>
-      </c>
-      <c r="F534" t="s">
-        <v>657</v>
       </c>
     </row>
     <row r="535" spans="1:6">
@@ -14960,10 +14960,10 @@
         <v>712</v>
       </c>
       <c r="E535" t="s">
+        <v>657</v>
+      </c>
+      <c r="F535" t="s">
         <v>713</v>
-      </c>
-      <c r="F535" t="s">
-        <v>657</v>
       </c>
     </row>
     <row r="536" spans="1:6">
@@ -14980,10 +14980,10 @@
         <v>712</v>
       </c>
       <c r="E536" t="s">
+        <v>727</v>
+      </c>
+      <c r="F536" t="s">
         <v>713</v>
-      </c>
-      <c r="F536" t="s">
-        <v>727</v>
       </c>
     </row>
     <row r="537" spans="1:6">
@@ -15000,10 +15000,10 @@
         <v>712</v>
       </c>
       <c r="E537" t="s">
+        <v>729</v>
+      </c>
+      <c r="F537" t="s">
         <v>713</v>
-      </c>
-      <c r="F537" t="s">
-        <v>729</v>
       </c>
     </row>
     <row r="538" spans="1:6">
@@ -15020,10 +15020,10 @@
         <v>712</v>
       </c>
       <c r="E538" t="s">
+        <v>657</v>
+      </c>
+      <c r="F538" t="s">
         <v>713</v>
-      </c>
-      <c r="F538" t="s">
-        <v>657</v>
       </c>
     </row>
     <row r="539" spans="1:6">
@@ -15040,10 +15040,10 @@
         <v>712</v>
       </c>
       <c r="E539" t="s">
+        <v>657</v>
+      </c>
+      <c r="F539" t="s">
         <v>713</v>
-      </c>
-      <c r="F539" t="s">
-        <v>657</v>
       </c>
     </row>
     <row r="540" spans="1:6">
@@ -15057,13 +15057,13 @@
         <v>711</v>
       </c>
       <c r="D540" t="s">
-        <v>712</v>
+        <v>689</v>
       </c>
       <c r="E540" t="s">
-        <v>689</v>
+        <v>657</v>
       </c>
       <c r="F540" t="s">
-        <v>657</v>
+        <v>713</v>
       </c>
     </row>
     <row r="541" spans="1:6">
@@ -15080,10 +15080,10 @@
         <v>712</v>
       </c>
       <c r="E541" t="s">
+        <v>657</v>
+      </c>
+      <c r="F541" t="s">
         <v>713</v>
-      </c>
-      <c r="F541" t="s">
-        <v>657</v>
       </c>
     </row>
     <row r="542" spans="1:6">
@@ -15100,10 +15100,10 @@
         <v>712</v>
       </c>
       <c r="E542" t="s">
+        <v>657</v>
+      </c>
+      <c r="F542" t="s">
         <v>713</v>
-      </c>
-      <c r="F542" t="s">
-        <v>657</v>
       </c>
     </row>
     <row r="543" spans="1:6">
@@ -15120,10 +15120,10 @@
         <v>712</v>
       </c>
       <c r="E543" t="s">
+        <v>657</v>
+      </c>
+      <c r="F543" t="s">
         <v>713</v>
-      </c>
-      <c r="F543" t="s">
-        <v>657</v>
       </c>
     </row>
     <row r="544" spans="1:6">
@@ -15140,10 +15140,10 @@
         <v>712</v>
       </c>
       <c r="E544" t="s">
+        <v>657</v>
+      </c>
+      <c r="F544" t="s">
         <v>713</v>
-      </c>
-      <c r="F544" t="s">
-        <v>657</v>
       </c>
     </row>
     <row r="545" spans="1:6">
@@ -15157,13 +15157,13 @@
         <v>13</v>
       </c>
       <c r="D545" t="s">
-        <v>712</v>
+        <v>738</v>
       </c>
       <c r="E545" t="s">
-        <v>738</v>
+        <v>657</v>
       </c>
       <c r="F545" t="s">
-        <v>657</v>
+        <v>713</v>
       </c>
     </row>
     <row r="546" spans="1:6">
@@ -15180,10 +15180,10 @@
         <v>712</v>
       </c>
       <c r="E546" t="s">
+        <v>657</v>
+      </c>
+      <c r="F546" t="s">
         <v>713</v>
-      </c>
-      <c r="F546" t="s">
-        <v>657</v>
       </c>
     </row>
     <row r="547" spans="1:6">
@@ -15200,10 +15200,10 @@
         <v>712</v>
       </c>
       <c r="E547" t="s">
+        <v>657</v>
+      </c>
+      <c r="F547" t="s">
         <v>713</v>
-      </c>
-      <c r="F547" t="s">
-        <v>657</v>
       </c>
     </row>
     <row r="548" spans="1:6">
@@ -15240,10 +15240,10 @@
         <v>742</v>
       </c>
       <c r="E549" t="s">
-        <v>743</v>
+        <v>746</v>
       </c>
       <c r="F549" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
     </row>
     <row r="550" spans="1:6">
@@ -15260,10 +15260,10 @@
         <v>742</v>
       </c>
       <c r="E550" t="s">
-        <v>743</v>
+        <v>748</v>
       </c>
       <c r="F550" t="s">
-        <v>748</v>
+        <v>744</v>
       </c>
     </row>
     <row r="551" spans="1:6">
@@ -15337,10 +15337,10 @@
         <v>711</v>
       </c>
       <c r="D554" t="s">
-        <v>742</v>
+        <v>753</v>
       </c>
       <c r="E554" t="s">
-        <v>753</v>
+        <v>743</v>
       </c>
       <c r="F554" t="s">
         <v>744</v>
@@ -15417,13 +15417,13 @@
         <v>24</v>
       </c>
       <c r="D558" t="s">
-        <v>742</v>
+        <v>758</v>
       </c>
       <c r="E558" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="F558" t="s">
-        <v>759</v>
+        <v>744</v>
       </c>
     </row>
     <row r="559" spans="1:6">
@@ -15460,10 +15460,10 @@
         <v>742</v>
       </c>
       <c r="E560" t="s">
-        <v>743</v>
+        <v>762</v>
       </c>
       <c r="F560" t="s">
-        <v>762</v>
+        <v>744</v>
       </c>
     </row>
     <row r="561" spans="1:6">
@@ -15480,10 +15480,10 @@
         <v>742</v>
       </c>
       <c r="E561" t="s">
-        <v>743</v>
+        <v>762</v>
       </c>
       <c r="F561" t="s">
-        <v>762</v>
+        <v>744</v>
       </c>
     </row>
     <row r="562" spans="1:6">
@@ -15517,10 +15517,10 @@
         <v>15</v>
       </c>
       <c r="D563" t="s">
-        <v>742</v>
+        <v>766</v>
       </c>
       <c r="E563" t="s">
-        <v>766</v>
+        <v>743</v>
       </c>
       <c r="F563" t="s">
         <v>744</v>
@@ -15637,13 +15637,13 @@
         <v>711</v>
       </c>
       <c r="D569" t="s">
-        <v>742</v>
+        <v>773</v>
       </c>
       <c r="E569" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="F569" t="s">
-        <v>774</v>
+        <v>744</v>
       </c>
     </row>
     <row r="570" spans="1:6">
@@ -15717,10 +15717,10 @@
         <v>711</v>
       </c>
       <c r="D573" t="s">
+        <v>712</v>
+      </c>
+      <c r="E573" t="s">
         <v>779</v>
-      </c>
-      <c r="E573" t="s">
-        <v>713</v>
       </c>
       <c r="F573" t="s">
         <v>780</v>
@@ -15737,10 +15737,10 @@
         <v>711</v>
       </c>
       <c r="D574" t="s">
+        <v>782</v>
+      </c>
+      <c r="E574" t="s">
         <v>779</v>
-      </c>
-      <c r="E574" t="s">
-        <v>782</v>
       </c>
       <c r="F574" t="s">
         <v>780</v>
@@ -15757,10 +15757,10 @@
         <v>711</v>
       </c>
       <c r="D575" t="s">
+        <v>782</v>
+      </c>
+      <c r="E575" t="s">
         <v>779</v>
-      </c>
-      <c r="E575" t="s">
-        <v>782</v>
       </c>
       <c r="F575" t="s">
         <v>780</v>
@@ -15777,10 +15777,10 @@
         <v>711</v>
       </c>
       <c r="D576" t="s">
+        <v>782</v>
+      </c>
+      <c r="E576" t="s">
         <v>779</v>
-      </c>
-      <c r="E576" t="s">
-        <v>782</v>
       </c>
       <c r="F576" t="s">
         <v>780</v>
@@ -15797,10 +15797,10 @@
         <v>711</v>
       </c>
       <c r="D577" t="s">
+        <v>742</v>
+      </c>
+      <c r="E577" t="s">
         <v>779</v>
-      </c>
-      <c r="E577" t="s">
-        <v>743</v>
       </c>
       <c r="F577" t="s">
         <v>780</v>
@@ -15817,13 +15817,13 @@
         <v>711</v>
       </c>
       <c r="D578" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="E578" t="s">
-        <v>782</v>
+        <v>787</v>
       </c>
       <c r="F578" t="s">
-        <v>787</v>
+        <v>780</v>
       </c>
     </row>
     <row r="579" spans="1:6">
@@ -15837,13 +15837,13 @@
         <v>24</v>
       </c>
       <c r="D579" t="s">
-        <v>779</v>
+        <v>789</v>
       </c>
       <c r="E579" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="F579" t="s">
-        <v>790</v>
+        <v>780</v>
       </c>
     </row>
     <row r="580" spans="1:6">
@@ -15857,13 +15857,13 @@
         <v>711</v>
       </c>
       <c r="D580" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="E580" t="s">
-        <v>782</v>
+        <v>792</v>
       </c>
       <c r="F580" t="s">
-        <v>792</v>
+        <v>780</v>
       </c>
     </row>
     <row r="581" spans="1:6">
@@ -15877,13 +15877,13 @@
         <v>15</v>
       </c>
       <c r="D581" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="E581" t="s">
-        <v>782</v>
+        <v>794</v>
       </c>
       <c r="F581" t="s">
-        <v>794</v>
+        <v>780</v>
       </c>
     </row>
     <row r="582" spans="1:6">
@@ -15897,10 +15897,10 @@
         <v>15</v>
       </c>
       <c r="D582" t="s">
+        <v>782</v>
+      </c>
+      <c r="E582" t="s">
         <v>779</v>
-      </c>
-      <c r="E582" t="s">
-        <v>782</v>
       </c>
       <c r="F582" t="s">
         <v>780</v>
@@ -15917,13 +15917,13 @@
         <v>24</v>
       </c>
       <c r="D583" t="s">
-        <v>779</v>
+        <v>797</v>
       </c>
       <c r="E583" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="F583" t="s">
-        <v>798</v>
+        <v>780</v>
       </c>
     </row>
     <row r="584" spans="1:6">
@@ -15937,13 +15937,13 @@
         <v>24</v>
       </c>
       <c r="D584" t="s">
-        <v>779</v>
+        <v>800</v>
       </c>
       <c r="E584" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="F584" t="s">
-        <v>801</v>
+        <v>780</v>
       </c>
     </row>
     <row r="585" spans="1:6">
@@ -15957,10 +15957,10 @@
         <v>711</v>
       </c>
       <c r="D585" t="s">
+        <v>782</v>
+      </c>
+      <c r="E585" t="s">
         <v>779</v>
-      </c>
-      <c r="E585" t="s">
-        <v>782</v>
       </c>
       <c r="F585" t="s">
         <v>780</v>
@@ -15977,13 +15977,13 @@
         <v>24</v>
       </c>
       <c r="D586" t="s">
-        <v>779</v>
+        <v>804</v>
       </c>
       <c r="E586" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="F586" t="s">
-        <v>805</v>
+        <v>780</v>
       </c>
     </row>
     <row r="587" spans="1:6">
@@ -15997,13 +15997,13 @@
         <v>13</v>
       </c>
       <c r="D587" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="E587" t="s">
-        <v>782</v>
+        <v>807</v>
       </c>
       <c r="F587" t="s">
-        <v>807</v>
+        <v>780</v>
       </c>
     </row>
     <row r="588" spans="1:6">
@@ -16017,13 +16017,13 @@
         <v>711</v>
       </c>
       <c r="D588" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="E588" t="s">
-        <v>782</v>
+        <v>809</v>
       </c>
       <c r="F588" t="s">
-        <v>809</v>
+        <v>780</v>
       </c>
     </row>
     <row r="589" spans="1:6">
@@ -16037,10 +16037,10 @@
         <v>711</v>
       </c>
       <c r="D589" t="s">
+        <v>782</v>
+      </c>
+      <c r="E589" t="s">
         <v>779</v>
-      </c>
-      <c r="E589" t="s">
-        <v>782</v>
       </c>
       <c r="F589" t="s">
         <v>780</v>
@@ -16057,10 +16057,10 @@
         <v>24</v>
       </c>
       <c r="D590" t="s">
+        <v>782</v>
+      </c>
+      <c r="E590" t="s">
         <v>779</v>
-      </c>
-      <c r="E590" t="s">
-        <v>782</v>
       </c>
       <c r="F590" t="s">
         <v>780</v>
@@ -16077,10 +16077,10 @@
         <v>15</v>
       </c>
       <c r="D591" t="s">
+        <v>782</v>
+      </c>
+      <c r="E591" t="s">
         <v>779</v>
-      </c>
-      <c r="E591" t="s">
-        <v>782</v>
       </c>
       <c r="F591" t="s">
         <v>780</v>
@@ -16097,10 +16097,10 @@
         <v>711</v>
       </c>
       <c r="D592" t="s">
+        <v>814</v>
+      </c>
+      <c r="E592" t="s">
         <v>779</v>
-      </c>
-      <c r="E592" t="s">
-        <v>814</v>
       </c>
       <c r="F592" t="s">
         <v>780</v>
@@ -16117,10 +16117,10 @@
         <v>13</v>
       </c>
       <c r="D593" t="s">
+        <v>782</v>
+      </c>
+      <c r="E593" t="s">
         <v>779</v>
-      </c>
-      <c r="E593" t="s">
-        <v>782</v>
       </c>
       <c r="F593" t="s">
         <v>780</v>
@@ -16137,10 +16137,10 @@
         <v>711</v>
       </c>
       <c r="D594" t="s">
+        <v>782</v>
+      </c>
+      <c r="E594" t="s">
         <v>779</v>
-      </c>
-      <c r="E594" t="s">
-        <v>782</v>
       </c>
       <c r="F594" t="s">
         <v>780</v>
@@ -16157,10 +16157,10 @@
         <v>711</v>
       </c>
       <c r="D595" t="s">
+        <v>782</v>
+      </c>
+      <c r="E595" t="s">
         <v>779</v>
-      </c>
-      <c r="E595" t="s">
-        <v>782</v>
       </c>
       <c r="F595" t="s">
         <v>780</v>
@@ -16177,10 +16177,10 @@
         <v>711</v>
       </c>
       <c r="D596" t="s">
+        <v>782</v>
+      </c>
+      <c r="E596" t="s">
         <v>779</v>
-      </c>
-      <c r="E596" t="s">
-        <v>782</v>
       </c>
       <c r="F596" t="s">
         <v>780</v>
@@ -16217,13 +16217,13 @@
         <v>15</v>
       </c>
       <c r="D598" t="s">
-        <v>820</v>
+        <v>824</v>
       </c>
       <c r="E598" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="F598" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
     </row>
     <row r="599" spans="1:6">
@@ -16297,13 +16297,13 @@
         <v>24</v>
       </c>
       <c r="D602" t="s">
-        <v>820</v>
+        <v>830</v>
       </c>
       <c r="E602" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="F602" t="s">
-        <v>831</v>
+        <v>822</v>
       </c>
     </row>
     <row r="603" spans="1:6">
@@ -16317,13 +16317,13 @@
         <v>24</v>
       </c>
       <c r="D603" t="s">
-        <v>820</v>
+        <v>833</v>
       </c>
       <c r="E603" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="F603" t="s">
-        <v>834</v>
+        <v>822</v>
       </c>
     </row>
     <row r="604" spans="1:6">
@@ -16337,13 +16337,13 @@
         <v>711</v>
       </c>
       <c r="D604" t="s">
-        <v>820</v>
+        <v>836</v>
       </c>
       <c r="E604" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="F604" t="s">
-        <v>837</v>
+        <v>822</v>
       </c>
     </row>
     <row r="605" spans="1:6">
@@ -16360,10 +16360,10 @@
         <v>820</v>
       </c>
       <c r="E605" t="s">
-        <v>821</v>
+        <v>839</v>
       </c>
       <c r="F605" t="s">
-        <v>839</v>
+        <v>822</v>
       </c>
     </row>
     <row r="606" spans="1:6">
@@ -16417,13 +16417,13 @@
         <v>24</v>
       </c>
       <c r="D608" t="s">
-        <v>820</v>
+        <v>843</v>
       </c>
       <c r="E608" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="F608" t="s">
-        <v>844</v>
+        <v>822</v>
       </c>
     </row>
     <row r="609" spans="1:6">
@@ -16437,13 +16437,13 @@
         <v>711</v>
       </c>
       <c r="D609" t="s">
-        <v>820</v>
+        <v>807</v>
       </c>
       <c r="E609" t="s">
-        <v>807</v>
+        <v>846</v>
       </c>
       <c r="F609" t="s">
-        <v>846</v>
+        <v>822</v>
       </c>
     </row>
     <row r="610" spans="1:6">
@@ -16477,13 +16477,13 @@
         <v>24</v>
       </c>
       <c r="D611" t="s">
-        <v>820</v>
+        <v>849</v>
       </c>
       <c r="E611" t="s">
-        <v>849</v>
+        <v>825</v>
       </c>
       <c r="F611" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
     </row>
     <row r="612" spans="1:6">
@@ -16500,10 +16500,10 @@
         <v>820</v>
       </c>
       <c r="E612" t="s">
-        <v>821</v>
+        <v>851</v>
       </c>
       <c r="F612" t="s">
-        <v>851</v>
+        <v>822</v>
       </c>
     </row>
     <row r="613" spans="1:6">
@@ -16540,10 +16540,10 @@
         <v>820</v>
       </c>
       <c r="E614" t="s">
-        <v>821</v>
+        <v>854</v>
       </c>
       <c r="F614" t="s">
-        <v>854</v>
+        <v>822</v>
       </c>
     </row>
     <row r="615" spans="1:6">
@@ -16737,13 +16737,13 @@
         <v>24</v>
       </c>
       <c r="D624" t="s">
-        <v>864</v>
+        <v>868</v>
       </c>
       <c r="E624" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="F624" t="s">
-        <v>869</v>
+        <v>866</v>
       </c>
     </row>
     <row r="625" spans="1:6">
@@ -16817,10 +16817,10 @@
         <v>711</v>
       </c>
       <c r="D628" t="s">
-        <v>864</v>
+        <v>874</v>
       </c>
       <c r="E628" t="s">
-        <v>874</v>
+        <v>865</v>
       </c>
       <c r="F628" t="s">
         <v>866</v>
@@ -16840,10 +16840,10 @@
         <v>864</v>
       </c>
       <c r="E629" t="s">
-        <v>865</v>
+        <v>876</v>
       </c>
       <c r="F629" t="s">
-        <v>876</v>
+        <v>866</v>
       </c>
     </row>
     <row r="630" spans="1:6">
@@ -16897,13 +16897,13 @@
         <v>24</v>
       </c>
       <c r="D632" t="s">
-        <v>864</v>
+        <v>880</v>
       </c>
       <c r="E632" t="s">
-        <v>880</v>
+        <v>876</v>
       </c>
       <c r="F632" t="s">
-        <v>876</v>
+        <v>866</v>
       </c>
     </row>
     <row r="633" spans="1:6">
@@ -16917,13 +16917,13 @@
         <v>24</v>
       </c>
       <c r="D633" t="s">
-        <v>864</v>
+        <v>882</v>
       </c>
       <c r="E633" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="F633" t="s">
-        <v>883</v>
+        <v>866</v>
       </c>
     </row>
     <row r="634" spans="1:6">
@@ -16937,13 +16937,13 @@
         <v>24</v>
       </c>
       <c r="D634" t="s">
-        <v>864</v>
+        <v>885</v>
       </c>
       <c r="E634" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="F634" t="s">
-        <v>886</v>
+        <v>866</v>
       </c>
     </row>
     <row r="635" spans="1:6">
@@ -16980,10 +16980,10 @@
         <v>864</v>
       </c>
       <c r="E636" t="s">
-        <v>865</v>
+        <v>889</v>
       </c>
       <c r="F636" t="s">
-        <v>889</v>
+        <v>866</v>
       </c>
     </row>
     <row r="637" spans="1:6">
@@ -16997,13 +16997,13 @@
         <v>24</v>
       </c>
       <c r="D637" t="s">
-        <v>864</v>
+        <v>891</v>
       </c>
       <c r="E637" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="F637" t="s">
-        <v>892</v>
+        <v>866</v>
       </c>
     </row>
     <row r="638" spans="1:6">
@@ -17077,13 +17077,13 @@
         <v>15</v>
       </c>
       <c r="D641" t="s">
-        <v>864</v>
+        <v>897</v>
       </c>
       <c r="E641" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="F641" t="s">
-        <v>898</v>
+        <v>866</v>
       </c>
     </row>
     <row r="642" spans="1:6">
@@ -17100,10 +17100,10 @@
         <v>864</v>
       </c>
       <c r="E642" t="s">
-        <v>865</v>
+        <v>900</v>
       </c>
       <c r="F642" t="s">
-        <v>900</v>
+        <v>866</v>
       </c>
     </row>
     <row r="643" spans="1:6">
@@ -17120,10 +17120,10 @@
         <v>864</v>
       </c>
       <c r="E643" t="s">
-        <v>865</v>
+        <v>902</v>
       </c>
       <c r="F643" t="s">
-        <v>902</v>
+        <v>866</v>
       </c>
     </row>
     <row r="644" spans="1:6">
@@ -17180,10 +17180,10 @@
         <v>864</v>
       </c>
       <c r="E646" t="s">
-        <v>865</v>
+        <v>906</v>
       </c>
       <c r="F646" t="s">
-        <v>906</v>
+        <v>866</v>
       </c>
     </row>
     <row r="647" spans="1:6">
@@ -17257,13 +17257,13 @@
         <v>15</v>
       </c>
       <c r="D650" t="s">
-        <v>910</v>
+        <v>914</v>
       </c>
       <c r="E650" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="F650" t="s">
-        <v>915</v>
+        <v>912</v>
       </c>
     </row>
     <row r="651" spans="1:6">
@@ -17277,10 +17277,10 @@
         <v>24</v>
       </c>
       <c r="D651" t="s">
-        <v>910</v>
+        <v>917</v>
       </c>
       <c r="E651" t="s">
-        <v>917</v>
+        <v>911</v>
       </c>
       <c r="F651" t="s">
         <v>912</v>
@@ -17297,13 +17297,13 @@
         <v>711</v>
       </c>
       <c r="D652" t="s">
-        <v>910</v>
+        <v>919</v>
       </c>
       <c r="E652" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="F652" t="s">
-        <v>920</v>
+        <v>912</v>
       </c>
     </row>
     <row r="653" spans="1:6">
@@ -17317,13 +17317,13 @@
         <v>711</v>
       </c>
       <c r="D653" t="s">
-        <v>910</v>
+        <v>919</v>
       </c>
       <c r="E653" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="F653" t="s">
-        <v>920</v>
+        <v>912</v>
       </c>
     </row>
     <row r="654" spans="1:6">
@@ -17337,13 +17337,13 @@
         <v>15</v>
       </c>
       <c r="D654" t="s">
-        <v>910</v>
+        <v>864</v>
       </c>
       <c r="E654" t="s">
-        <v>865</v>
+        <v>902</v>
       </c>
       <c r="F654" t="s">
-        <v>902</v>
+        <v>912</v>
       </c>
     </row>
     <row r="655" spans="1:6">
@@ -17357,13 +17357,13 @@
         <v>711</v>
       </c>
       <c r="D655" t="s">
-        <v>910</v>
+        <v>919</v>
       </c>
       <c r="E655" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="F655" t="s">
-        <v>920</v>
+        <v>912</v>
       </c>
     </row>
     <row r="656" spans="1:6">
@@ -17377,13 +17377,13 @@
         <v>711</v>
       </c>
       <c r="D656" t="s">
-        <v>910</v>
+        <v>919</v>
       </c>
       <c r="E656" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="F656" t="s">
-        <v>920</v>
+        <v>912</v>
       </c>
     </row>
     <row r="657" spans="1:6">
@@ -17397,13 +17397,13 @@
         <v>15</v>
       </c>
       <c r="D657" t="s">
-        <v>910</v>
+        <v>926</v>
       </c>
       <c r="E657" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="F657" t="s">
-        <v>927</v>
+        <v>912</v>
       </c>
     </row>
     <row r="658" spans="1:6">
@@ -17417,13 +17417,13 @@
         <v>24</v>
       </c>
       <c r="D658" t="s">
-        <v>910</v>
+        <v>929</v>
       </c>
       <c r="E658" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="F658" t="s">
-        <v>930</v>
+        <v>912</v>
       </c>
     </row>
     <row r="659" spans="1:6">
@@ -17437,13 +17437,13 @@
         <v>24</v>
       </c>
       <c r="D659" t="s">
-        <v>910</v>
+        <v>932</v>
       </c>
       <c r="E659" t="s">
-        <v>932</v>
+        <v>889</v>
       </c>
       <c r="F659" t="s">
-        <v>889</v>
+        <v>912</v>
       </c>
     </row>
     <row r="660" spans="1:6">
@@ -17457,13 +17457,13 @@
         <v>24</v>
       </c>
       <c r="D660" t="s">
-        <v>910</v>
+        <v>934</v>
       </c>
       <c r="E660" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="F660" t="s">
-        <v>935</v>
+        <v>912</v>
       </c>
     </row>
     <row r="661" spans="1:6">
@@ -17477,13 +17477,13 @@
         <v>711</v>
       </c>
       <c r="D661" t="s">
-        <v>910</v>
+        <v>919</v>
       </c>
       <c r="E661" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="F661" t="s">
-        <v>920</v>
+        <v>912</v>
       </c>
     </row>
     <row r="662" spans="1:6">
@@ -17497,13 +17497,13 @@
         <v>24</v>
       </c>
       <c r="D662" t="s">
-        <v>910</v>
+        <v>915</v>
       </c>
       <c r="E662" t="s">
-        <v>915</v>
+        <v>920</v>
       </c>
       <c r="F662" t="s">
-        <v>920</v>
+        <v>912</v>
       </c>
     </row>
     <row r="663" spans="1:6">
@@ -17517,13 +17517,13 @@
         <v>24</v>
       </c>
       <c r="D663" t="s">
-        <v>910</v>
+        <v>939</v>
       </c>
       <c r="E663" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="F663" t="s">
-        <v>940</v>
+        <v>912</v>
       </c>
     </row>
     <row r="664" spans="1:6">
@@ -17537,13 +17537,13 @@
         <v>15</v>
       </c>
       <c r="D664" t="s">
-        <v>910</v>
+        <v>942</v>
       </c>
       <c r="E664" t="s">
-        <v>942</v>
+        <v>902</v>
       </c>
       <c r="F664" t="s">
-        <v>902</v>
+        <v>912</v>
       </c>
     </row>
     <row r="665" spans="1:6">
@@ -17557,13 +17557,13 @@
         <v>711</v>
       </c>
       <c r="D665" t="s">
-        <v>910</v>
+        <v>919</v>
       </c>
       <c r="E665" t="s">
-        <v>919</v>
+        <v>944</v>
       </c>
       <c r="F665" t="s">
-        <v>944</v>
+        <v>912</v>
       </c>
     </row>
     <row r="666" spans="1:6">
@@ -17580,10 +17580,10 @@
         <v>910</v>
       </c>
       <c r="E666" t="s">
-        <v>911</v>
+        <v>944</v>
       </c>
       <c r="F666" t="s">
-        <v>944</v>
+        <v>912</v>
       </c>
     </row>
     <row r="667" spans="1:6">
@@ -17597,13 +17597,13 @@
         <v>24</v>
       </c>
       <c r="D667" t="s">
-        <v>910</v>
+        <v>947</v>
       </c>
       <c r="E667" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="F667" t="s">
-        <v>948</v>
+        <v>912</v>
       </c>
     </row>
     <row r="668" spans="1:6">
@@ -17617,13 +17617,13 @@
         <v>15</v>
       </c>
       <c r="D668" t="s">
-        <v>910</v>
+        <v>919</v>
       </c>
       <c r="E668" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="F668" t="s">
-        <v>920</v>
+        <v>912</v>
       </c>
     </row>
     <row r="669" spans="1:6">
@@ -17637,13 +17637,13 @@
         <v>15</v>
       </c>
       <c r="D669" t="s">
-        <v>910</v>
+        <v>932</v>
       </c>
       <c r="E669" t="s">
-        <v>932</v>
+        <v>902</v>
       </c>
       <c r="F669" t="s">
-        <v>902</v>
+        <v>912</v>
       </c>
     </row>
     <row r="670" spans="1:6">
@@ -17657,13 +17657,13 @@
         <v>711</v>
       </c>
       <c r="D670" t="s">
-        <v>910</v>
+        <v>919</v>
       </c>
       <c r="E670" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="F670" t="s">
-        <v>920</v>
+        <v>912</v>
       </c>
     </row>
     <row r="671" spans="1:6">
@@ -17677,10 +17677,10 @@
         <v>24</v>
       </c>
       <c r="D671" t="s">
-        <v>910</v>
+        <v>953</v>
       </c>
       <c r="E671" t="s">
-        <v>953</v>
+        <v>911</v>
       </c>
       <c r="F671" t="s">
         <v>912</v>
@@ -17697,13 +17697,13 @@
         <v>15</v>
       </c>
       <c r="D672" t="s">
-        <v>910</v>
+        <v>919</v>
       </c>
       <c r="E672" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="F672" t="s">
-        <v>920</v>
+        <v>912</v>
       </c>
     </row>
     <row r="673" spans="1:6">
@@ -17717,13 +17717,13 @@
         <v>711</v>
       </c>
       <c r="D673" t="s">
-        <v>910</v>
+        <v>919</v>
       </c>
       <c r="E673" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="F673" t="s">
-        <v>920</v>
+        <v>912</v>
       </c>
     </row>
     <row r="674" spans="1:6">
@@ -17737,13 +17737,13 @@
         <v>15</v>
       </c>
       <c r="D674" t="s">
-        <v>910</v>
+        <v>934</v>
       </c>
       <c r="E674" t="s">
-        <v>934</v>
+        <v>902</v>
       </c>
       <c r="F674" t="s">
-        <v>902</v>
+        <v>912</v>
       </c>
     </row>
     <row r="675" spans="1:6">
@@ -17757,10 +17757,10 @@
         <v>24</v>
       </c>
       <c r="D675" t="s">
-        <v>910</v>
+        <v>917</v>
       </c>
       <c r="E675" t="s">
-        <v>917</v>
+        <v>911</v>
       </c>
       <c r="F675" t="s">
         <v>912</v>
@@ -17777,13 +17777,13 @@
         <v>15</v>
       </c>
       <c r="D676" t="s">
-        <v>910</v>
+        <v>919</v>
       </c>
       <c r="E676" t="s">
-        <v>919</v>
+        <v>959</v>
       </c>
       <c r="F676" t="s">
-        <v>959</v>
+        <v>912</v>
       </c>
     </row>
     <row r="677" spans="1:6">
@@ -17797,13 +17797,13 @@
         <v>711</v>
       </c>
       <c r="D677" t="s">
-        <v>910</v>
+        <v>919</v>
       </c>
       <c r="E677" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="F677" t="s">
-        <v>920</v>
+        <v>912</v>
       </c>
     </row>
     <row r="678" spans="1:6">
@@ -17817,13 +17817,13 @@
         <v>711</v>
       </c>
       <c r="D678" t="s">
-        <v>910</v>
+        <v>919</v>
       </c>
       <c r="E678" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="F678" t="s">
-        <v>920</v>
+        <v>912</v>
       </c>
     </row>
     <row r="679" spans="1:6">
@@ -17837,13 +17837,13 @@
         <v>24</v>
       </c>
       <c r="D679" t="s">
-        <v>910</v>
+        <v>934</v>
       </c>
       <c r="E679" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="F679" t="s">
-        <v>935</v>
+        <v>912</v>
       </c>
     </row>
     <row r="680" spans="1:6">
@@ -17857,13 +17857,13 @@
         <v>711</v>
       </c>
       <c r="D680" t="s">
-        <v>910</v>
+        <v>919</v>
       </c>
       <c r="E680" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="F680" t="s">
-        <v>920</v>
+        <v>912</v>
       </c>
     </row>
     <row r="681" spans="1:6">
@@ -17877,13 +17877,13 @@
         <v>711</v>
       </c>
       <c r="D681" t="s">
-        <v>910</v>
+        <v>919</v>
       </c>
       <c r="E681" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="F681" t="s">
-        <v>920</v>
+        <v>912</v>
       </c>
     </row>
     <row r="682" spans="1:6">
@@ -17917,13 +17917,13 @@
         <v>24</v>
       </c>
       <c r="D683" t="s">
-        <v>966</v>
+        <v>970</v>
       </c>
       <c r="E683" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="F683" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
     </row>
     <row r="684" spans="1:6">
@@ -17937,13 +17937,13 @@
         <v>711</v>
       </c>
       <c r="D684" t="s">
-        <v>966</v>
+        <v>973</v>
       </c>
       <c r="E684" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="F684" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
     </row>
     <row r="685" spans="1:6">
@@ -17957,13 +17957,13 @@
         <v>711</v>
       </c>
       <c r="D685" t="s">
-        <v>966</v>
+        <v>973</v>
       </c>
       <c r="E685" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="F685" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
     </row>
     <row r="686" spans="1:6">
@@ -17977,13 +17977,13 @@
         <v>711</v>
       </c>
       <c r="D686" t="s">
-        <v>966</v>
+        <v>973</v>
       </c>
       <c r="E686" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="F686" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
     </row>
     <row r="687" spans="1:6">
@@ -17997,13 +17997,13 @@
         <v>711</v>
       </c>
       <c r="D687" t="s">
-        <v>966</v>
+        <v>973</v>
       </c>
       <c r="E687" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="F687" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
     </row>
     <row r="688" spans="1:6">
@@ -18017,13 +18017,13 @@
         <v>711</v>
       </c>
       <c r="D688" t="s">
-        <v>966</v>
+        <v>973</v>
       </c>
       <c r="E688" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="F688" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
     </row>
     <row r="689" spans="1:6">
@@ -18037,13 +18037,13 @@
         <v>24</v>
       </c>
       <c r="D689" t="s">
-        <v>966</v>
+        <v>980</v>
       </c>
       <c r="E689" t="s">
-        <v>980</v>
+        <v>971</v>
       </c>
       <c r="F689" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
     </row>
     <row r="690" spans="1:6">
@@ -18057,13 +18057,13 @@
         <v>24</v>
       </c>
       <c r="D690" t="s">
-        <v>966</v>
+        <v>982</v>
       </c>
       <c r="E690" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="F690" t="s">
-        <v>983</v>
+        <v>968</v>
       </c>
     </row>
     <row r="691" spans="1:6">
@@ -18077,13 +18077,13 @@
         <v>13</v>
       </c>
       <c r="D691" t="s">
-        <v>966</v>
+        <v>973</v>
       </c>
       <c r="E691" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="F691" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
     </row>
     <row r="692" spans="1:6">
@@ -18097,13 +18097,13 @@
         <v>15</v>
       </c>
       <c r="D692" t="s">
-        <v>966</v>
+        <v>919</v>
       </c>
       <c r="E692" t="s">
-        <v>919</v>
+        <v>986</v>
       </c>
       <c r="F692" t="s">
-        <v>986</v>
+        <v>968</v>
       </c>
     </row>
     <row r="693" spans="1:6">
@@ -18117,13 +18117,13 @@
         <v>24</v>
       </c>
       <c r="D693" t="s">
-        <v>966</v>
+        <v>988</v>
       </c>
       <c r="E693" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="F693" t="s">
-        <v>989</v>
+        <v>968</v>
       </c>
     </row>
     <row r="694" spans="1:6">
@@ -18137,13 +18137,13 @@
         <v>15</v>
       </c>
       <c r="D694" t="s">
-        <v>966</v>
+        <v>991</v>
       </c>
       <c r="E694" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="F694" t="s">
-        <v>992</v>
+        <v>968</v>
       </c>
     </row>
     <row r="695" spans="1:6">
@@ -18157,13 +18157,13 @@
         <v>24</v>
       </c>
       <c r="D695" t="s">
-        <v>966</v>
+        <v>994</v>
       </c>
       <c r="E695" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="F695" t="s">
-        <v>995</v>
+        <v>968</v>
       </c>
     </row>
     <row r="696" spans="1:6">
@@ -18177,13 +18177,13 @@
         <v>711</v>
       </c>
       <c r="D696" t="s">
-        <v>966</v>
+        <v>973</v>
       </c>
       <c r="E696" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="F696" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
     </row>
     <row r="697" spans="1:6">
@@ -18197,13 +18197,13 @@
         <v>24</v>
       </c>
       <c r="D697" t="s">
-        <v>966</v>
+        <v>998</v>
       </c>
       <c r="E697" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="F697" t="s">
-        <v>999</v>
+        <v>968</v>
       </c>
     </row>
     <row r="698" spans="1:6">
@@ -18217,13 +18217,13 @@
         <v>24</v>
       </c>
       <c r="D698" t="s">
-        <v>966</v>
+        <v>1001</v>
       </c>
       <c r="E698" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="F698" t="s">
-        <v>1002</v>
+        <v>968</v>
       </c>
     </row>
     <row r="699" spans="1:6">
@@ -18237,13 +18237,13 @@
         <v>15</v>
       </c>
       <c r="D699" t="s">
-        <v>966</v>
+        <v>973</v>
       </c>
       <c r="E699" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="F699" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
     </row>
     <row r="700" spans="1:6">
@@ -18257,13 +18257,13 @@
         <v>24</v>
       </c>
       <c r="D700" t="s">
-        <v>966</v>
+        <v>1005</v>
       </c>
       <c r="E700" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="F700" t="s">
-        <v>1006</v>
+        <v>968</v>
       </c>
     </row>
     <row r="701" spans="1:6">
@@ -18277,13 +18277,13 @@
         <v>15</v>
       </c>
       <c r="D701" t="s">
-        <v>966</v>
+        <v>973</v>
       </c>
       <c r="E701" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="F701" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
     </row>
     <row r="702" spans="1:6">
@@ -18297,13 +18297,13 @@
         <v>24</v>
       </c>
       <c r="D702" t="s">
-        <v>966</v>
+        <v>1009</v>
       </c>
       <c r="E702" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="F702" t="s">
-        <v>1010</v>
+        <v>968</v>
       </c>
     </row>
     <row r="703" spans="1:6">
@@ -18317,13 +18317,13 @@
         <v>24</v>
       </c>
       <c r="D703" t="s">
-        <v>966</v>
+        <v>1005</v>
       </c>
       <c r="E703" t="s">
-        <v>1005</v>
+        <v>1012</v>
       </c>
       <c r="F703" t="s">
-        <v>1012</v>
+        <v>968</v>
       </c>
     </row>
     <row r="704" spans="1:6">
@@ -18337,13 +18337,13 @@
         <v>711</v>
       </c>
       <c r="D704" t="s">
-        <v>966</v>
+        <v>973</v>
       </c>
       <c r="E704" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="F704" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
     </row>
     <row r="705" spans="1:6">
@@ -18357,13 +18357,13 @@
         <v>15</v>
       </c>
       <c r="D705" t="s">
-        <v>966</v>
+        <v>1001</v>
       </c>
       <c r="E705" t="s">
-        <v>1001</v>
+        <v>1015</v>
       </c>
       <c r="F705" t="s">
-        <v>1015</v>
+        <v>968</v>
       </c>
     </row>
     <row r="706" spans="1:6">
@@ -18377,13 +18377,13 @@
         <v>711</v>
       </c>
       <c r="D706" t="s">
-        <v>966</v>
+        <v>973</v>
       </c>
       <c r="E706" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="F706" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
     </row>
     <row r="707" spans="1:6">
@@ -18397,13 +18397,13 @@
         <v>15</v>
       </c>
       <c r="D707" t="s">
-        <v>966</v>
+        <v>1001</v>
       </c>
       <c r="E707" t="s">
-        <v>1001</v>
+        <v>974</v>
       </c>
       <c r="F707" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
     </row>
     <row r="708" spans="1:6">
@@ -18417,13 +18417,13 @@
         <v>24</v>
       </c>
       <c r="D708" t="s">
-        <v>966</v>
+        <v>970</v>
       </c>
       <c r="E708" t="s">
-        <v>970</v>
+        <v>1019</v>
       </c>
       <c r="F708" t="s">
-        <v>1019</v>
+        <v>968</v>
       </c>
     </row>
     <row r="709" spans="1:6">
@@ -18437,13 +18437,13 @@
         <v>711</v>
       </c>
       <c r="D709" t="s">
-        <v>966</v>
+        <v>973</v>
       </c>
       <c r="E709" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="F709" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
     </row>
     <row r="710" spans="1:6">
@@ -18457,13 +18457,13 @@
         <v>24</v>
       </c>
       <c r="D710" t="s">
-        <v>966</v>
+        <v>1022</v>
       </c>
       <c r="E710" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="F710" t="s">
-        <v>1023</v>
+        <v>968</v>
       </c>
     </row>
     <row r="711" spans="1:6">
@@ -18477,13 +18477,13 @@
         <v>711</v>
       </c>
       <c r="D711" t="s">
-        <v>966</v>
+        <v>1001</v>
       </c>
       <c r="E711" t="s">
-        <v>1001</v>
+        <v>974</v>
       </c>
       <c r="F711" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
     </row>
     <row r="712" spans="1:6">
@@ -18497,13 +18497,13 @@
         <v>711</v>
       </c>
       <c r="D712" t="s">
-        <v>966</v>
+        <v>973</v>
       </c>
       <c r="E712" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="F712" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
     </row>
     <row r="713" spans="1:6">
@@ -18517,13 +18517,13 @@
         <v>24</v>
       </c>
       <c r="D713" t="s">
-        <v>966</v>
+        <v>982</v>
       </c>
       <c r="E713" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="F713" t="s">
-        <v>983</v>
+        <v>968</v>
       </c>
     </row>
     <row r="714" spans="1:6">
@@ -18537,13 +18537,13 @@
         <v>711</v>
       </c>
       <c r="D714" t="s">
-        <v>966</v>
+        <v>973</v>
       </c>
       <c r="E714" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="F714" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
     </row>
     <row r="715" spans="1:6">
@@ -18557,13 +18557,13 @@
         <v>24</v>
       </c>
       <c r="D715" t="s">
-        <v>966</v>
+        <v>1001</v>
       </c>
       <c r="E715" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="F715" t="s">
-        <v>999</v>
+        <v>968</v>
       </c>
     </row>
     <row r="716" spans="1:6">
@@ -18577,13 +18577,13 @@
         <v>711</v>
       </c>
       <c r="D716" t="s">
-        <v>966</v>
+        <v>973</v>
       </c>
       <c r="E716" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="F716" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
     </row>
     <row r="717" spans="1:6">
@@ -18597,13 +18597,13 @@
         <v>711</v>
       </c>
       <c r="D717" t="s">
-        <v>966</v>
+        <v>973</v>
       </c>
       <c r="E717" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="F717" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
     </row>
     <row r="718" spans="1:6">
@@ -18640,10 +18640,10 @@
         <v>1032</v>
       </c>
       <c r="E719" t="s">
-        <v>1033</v>
+        <v>1036</v>
       </c>
       <c r="F719" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="720" spans="1:6">
@@ -18660,10 +18660,10 @@
         <v>1032</v>
       </c>
       <c r="E720" t="s">
-        <v>1033</v>
+        <v>1036</v>
       </c>
       <c r="F720" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="721" spans="1:6">
@@ -18680,10 +18680,10 @@
         <v>1032</v>
       </c>
       <c r="E721" t="s">
-        <v>1033</v>
+        <v>1036</v>
       </c>
       <c r="F721" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="722" spans="1:6">
@@ -18700,10 +18700,10 @@
         <v>1032</v>
       </c>
       <c r="E722" t="s">
-        <v>1033</v>
+        <v>1036</v>
       </c>
       <c r="F722" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="723" spans="1:6">
@@ -18720,10 +18720,10 @@
         <v>1032</v>
       </c>
       <c r="E723" t="s">
-        <v>1033</v>
+        <v>1036</v>
       </c>
       <c r="F723" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="724" spans="1:6">
@@ -18740,10 +18740,10 @@
         <v>1032</v>
       </c>
       <c r="E724" t="s">
-        <v>1033</v>
+        <v>1036</v>
       </c>
       <c r="F724" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="725" spans="1:6">
@@ -18757,13 +18757,13 @@
         <v>15</v>
       </c>
       <c r="D725" t="s">
-        <v>1032</v>
+        <v>1043</v>
       </c>
       <c r="E725" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="F725" t="s">
-        <v>1044</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="726" spans="1:6">
@@ -18777,13 +18777,13 @@
         <v>15</v>
       </c>
       <c r="D726" t="s">
-        <v>1032</v>
+        <v>1046</v>
       </c>
       <c r="E726" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="F726" t="s">
-        <v>1047</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="727" spans="1:6">
@@ -18800,10 +18800,10 @@
         <v>1032</v>
       </c>
       <c r="E727" t="s">
-        <v>1033</v>
+        <v>1036</v>
       </c>
       <c r="F727" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="728" spans="1:6">
@@ -18820,10 +18820,10 @@
         <v>1032</v>
       </c>
       <c r="E728" t="s">
-        <v>1033</v>
+        <v>1036</v>
       </c>
       <c r="F728" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="729" spans="1:6">
@@ -18837,13 +18837,13 @@
         <v>24</v>
       </c>
       <c r="D729" t="s">
-        <v>1032</v>
+        <v>1051</v>
       </c>
       <c r="E729" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="F729" t="s">
-        <v>1052</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="730" spans="1:6">
@@ -18860,10 +18860,10 @@
         <v>1032</v>
       </c>
       <c r="E730" t="s">
-        <v>1033</v>
+        <v>1036</v>
       </c>
       <c r="F730" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="731" spans="1:6">
@@ -18877,13 +18877,13 @@
         <v>24</v>
       </c>
       <c r="D731" t="s">
-        <v>1032</v>
+        <v>1051</v>
       </c>
       <c r="E731" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="F731" t="s">
-        <v>1052</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="732" spans="1:6">
@@ -18897,13 +18897,13 @@
         <v>24</v>
       </c>
       <c r="D732" t="s">
-        <v>1032</v>
+        <v>1056</v>
       </c>
       <c r="E732" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="F732" t="s">
-        <v>1057</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="733" spans="1:6">
@@ -18920,10 +18920,10 @@
         <v>1032</v>
       </c>
       <c r="E733" t="s">
-        <v>1033</v>
+        <v>1059</v>
       </c>
       <c r="F733" t="s">
-        <v>1059</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="734" spans="1:6">
@@ -18937,13 +18937,13 @@
         <v>24</v>
       </c>
       <c r="D734" t="s">
-        <v>1032</v>
+        <v>1061</v>
       </c>
       <c r="E734" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="F734" t="s">
-        <v>1062</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="735" spans="1:6">
@@ -18960,10 +18960,10 @@
         <v>1032</v>
       </c>
       <c r="E735" t="s">
-        <v>1033</v>
+        <v>1036</v>
       </c>
       <c r="F735" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="736" spans="1:6">
@@ -18980,10 +18980,10 @@
         <v>1032</v>
       </c>
       <c r="E736" t="s">
-        <v>1033</v>
+        <v>1065</v>
       </c>
       <c r="F736" t="s">
-        <v>1065</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="737" spans="1:6">
@@ -19000,10 +19000,10 @@
         <v>1032</v>
       </c>
       <c r="E737" t="s">
-        <v>1033</v>
+        <v>1036</v>
       </c>
       <c r="F737" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="738" spans="1:6">
@@ -19017,13 +19017,13 @@
         <v>15</v>
       </c>
       <c r="D738" t="s">
-        <v>1032</v>
+        <v>973</v>
       </c>
       <c r="E738" t="s">
-        <v>973</v>
+        <v>1068</v>
       </c>
       <c r="F738" t="s">
-        <v>1068</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="739" spans="1:6">
@@ -19040,10 +19040,10 @@
         <v>1032</v>
       </c>
       <c r="E739" t="s">
-        <v>1033</v>
+        <v>1036</v>
       </c>
       <c r="F739" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="740" spans="1:6">
@@ -19060,10 +19060,10 @@
         <v>1032</v>
       </c>
       <c r="E740" t="s">
-        <v>1033</v>
+        <v>1036</v>
       </c>
       <c r="F740" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="741" spans="1:6">
@@ -19077,13 +19077,13 @@
         <v>24</v>
       </c>
       <c r="D741" t="s">
-        <v>1032</v>
+        <v>1072</v>
       </c>
       <c r="E741" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="F741" t="s">
-        <v>1073</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="742" spans="1:6">
@@ -19100,10 +19100,10 @@
         <v>1032</v>
       </c>
       <c r="E742" t="s">
-        <v>1033</v>
+        <v>1075</v>
       </c>
       <c r="F742" t="s">
-        <v>1075</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="743" spans="1:6">
@@ -19120,10 +19120,10 @@
         <v>1032</v>
       </c>
       <c r="E743" t="s">
-        <v>1033</v>
+        <v>1036</v>
       </c>
       <c r="F743" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="744" spans="1:6">
@@ -19160,10 +19160,10 @@
         <v>1032</v>
       </c>
       <c r="E745" t="s">
-        <v>1033</v>
+        <v>1079</v>
       </c>
       <c r="F745" t="s">
-        <v>1079</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="746" spans="1:6">
@@ -19180,10 +19180,10 @@
         <v>1032</v>
       </c>
       <c r="E746" t="s">
-        <v>1033</v>
+        <v>1036</v>
       </c>
       <c r="F746" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="747" spans="1:6">
@@ -19200,10 +19200,10 @@
         <v>1032</v>
       </c>
       <c r="E747" t="s">
-        <v>1033</v>
+        <v>1036</v>
       </c>
       <c r="F747" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="748" spans="1:6">
@@ -19220,10 +19220,10 @@
         <v>1032</v>
       </c>
       <c r="E748" t="s">
-        <v>1033</v>
+        <v>1036</v>
       </c>
       <c r="F748" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="749" spans="1:6">
@@ -19240,10 +19240,10 @@
         <v>1032</v>
       </c>
       <c r="E749" t="s">
-        <v>1033</v>
+        <v>1036</v>
       </c>
       <c r="F749" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="750" spans="1:6">
@@ -19277,13 +19277,13 @@
         <v>24</v>
       </c>
       <c r="D751" t="s">
-        <v>1085</v>
+        <v>1089</v>
       </c>
       <c r="E751" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="F751" t="s">
-        <v>1090</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="752" spans="1:6">
@@ -19297,13 +19297,13 @@
         <v>711</v>
       </c>
       <c r="D752" t="s">
-        <v>1085</v>
+        <v>1092</v>
       </c>
       <c r="E752" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="F752" t="s">
-        <v>1093</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="753" spans="1:6">
@@ -19317,13 +19317,13 @@
         <v>711</v>
       </c>
       <c r="D753" t="s">
-        <v>1085</v>
+        <v>1092</v>
       </c>
       <c r="E753" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="F753" t="s">
-        <v>1093</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="754" spans="1:6">
@@ -19337,13 +19337,13 @@
         <v>711</v>
       </c>
       <c r="D754" t="s">
-        <v>1085</v>
+        <v>1092</v>
       </c>
       <c r="E754" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="F754" t="s">
-        <v>1093</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="755" spans="1:6">
@@ -19357,13 +19357,13 @@
         <v>711</v>
       </c>
       <c r="D755" t="s">
-        <v>1085</v>
+        <v>1092</v>
       </c>
       <c r="E755" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="F755" t="s">
-        <v>1093</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="756" spans="1:6">
@@ -19377,13 +19377,13 @@
         <v>711</v>
       </c>
       <c r="D756" t="s">
-        <v>1085</v>
+        <v>1092</v>
       </c>
       <c r="E756" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="F756" t="s">
-        <v>1093</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="757" spans="1:6">
@@ -19397,13 +19397,13 @@
         <v>711</v>
       </c>
       <c r="D757" t="s">
-        <v>1085</v>
+        <v>1092</v>
       </c>
       <c r="E757" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="F757" t="s">
-        <v>1093</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="758" spans="1:6">
@@ -19417,10 +19417,10 @@
         <v>24</v>
       </c>
       <c r="D758" t="s">
-        <v>1085</v>
+        <v>1089</v>
       </c>
       <c r="E758" t="s">
-        <v>1089</v>
+        <v>1086</v>
       </c>
       <c r="F758" t="s">
         <v>1087</v>
@@ -19437,13 +19437,13 @@
         <v>15</v>
       </c>
       <c r="D759" t="s">
-        <v>1085</v>
+        <v>1092</v>
       </c>
       <c r="E759" t="s">
-        <v>1092</v>
+        <v>1065</v>
       </c>
       <c r="F759" t="s">
-        <v>1065</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="760" spans="1:6">
@@ -19457,13 +19457,13 @@
         <v>711</v>
       </c>
       <c r="D760" t="s">
-        <v>1085</v>
+        <v>1092</v>
       </c>
       <c r="E760" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="F760" t="s">
-        <v>1093</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="761" spans="1:6">
@@ -19477,13 +19477,13 @@
         <v>711</v>
       </c>
       <c r="D761" t="s">
-        <v>1085</v>
+        <v>1092</v>
       </c>
       <c r="E761" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="F761" t="s">
-        <v>1093</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="762" spans="1:6">
@@ -19497,13 +19497,13 @@
         <v>24</v>
       </c>
       <c r="D762" t="s">
-        <v>1085</v>
+        <v>1104</v>
       </c>
       <c r="E762" t="s">
-        <v>1104</v>
+        <v>1065</v>
       </c>
       <c r="F762" t="s">
-        <v>1065</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="763" spans="1:6">
@@ -19517,13 +19517,13 @@
         <v>711</v>
       </c>
       <c r="D763" t="s">
-        <v>1085</v>
+        <v>1092</v>
       </c>
       <c r="E763" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="F763" t="s">
-        <v>1093</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="764" spans="1:6">
@@ -19537,13 +19537,13 @@
         <v>24</v>
       </c>
       <c r="D764" t="s">
-        <v>1085</v>
+        <v>1107</v>
       </c>
       <c r="E764" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="F764" t="s">
-        <v>1108</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="765" spans="1:6">
@@ -19560,10 +19560,10 @@
         <v>1085</v>
       </c>
       <c r="E765" t="s">
-        <v>1086</v>
+        <v>1093</v>
       </c>
       <c r="F765" t="s">
-        <v>1093</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="766" spans="1:6">
@@ -19577,13 +19577,13 @@
         <v>24</v>
       </c>
       <c r="D766" t="s">
-        <v>1085</v>
+        <v>1104</v>
       </c>
       <c r="E766" t="s">
-        <v>1104</v>
+        <v>1111</v>
       </c>
       <c r="F766" t="s">
-        <v>1111</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="767" spans="1:6">
@@ -19597,13 +19597,13 @@
         <v>24</v>
       </c>
       <c r="D767" t="s">
-        <v>1085</v>
+        <v>1113</v>
       </c>
       <c r="E767" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="F767" t="s">
-        <v>1114</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="768" spans="1:6">
@@ -19617,13 +19617,13 @@
         <v>711</v>
       </c>
       <c r="D768" t="s">
-        <v>1085</v>
+        <v>1092</v>
       </c>
       <c r="E768" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="F768" t="s">
-        <v>1093</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="769" spans="1:6">
@@ -19637,13 +19637,13 @@
         <v>711</v>
       </c>
       <c r="D769" t="s">
-        <v>1085</v>
+        <v>1092</v>
       </c>
       <c r="E769" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="F769" t="s">
-        <v>1093</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="770" spans="1:6">
@@ -19657,13 +19657,13 @@
         <v>24</v>
       </c>
       <c r="D770" t="s">
-        <v>1085</v>
+        <v>1118</v>
       </c>
       <c r="E770" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="F770" t="s">
-        <v>1119</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="771" spans="1:6">
@@ -19677,13 +19677,13 @@
         <v>711</v>
       </c>
       <c r="D771" t="s">
-        <v>1085</v>
+        <v>1092</v>
       </c>
       <c r="E771" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="F771" t="s">
-        <v>1093</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="772" spans="1:6">
@@ -19697,13 +19697,13 @@
         <v>711</v>
       </c>
       <c r="D772" t="s">
-        <v>1085</v>
+        <v>1092</v>
       </c>
       <c r="E772" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="F772" t="s">
-        <v>1093</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="773" spans="1:6">
@@ -19717,13 +19717,13 @@
         <v>711</v>
       </c>
       <c r="D773" t="s">
-        <v>1085</v>
+        <v>1092</v>
       </c>
       <c r="E773" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="F773" t="s">
-        <v>1093</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="774" spans="1:6">
@@ -19737,13 +19737,13 @@
         <v>24</v>
       </c>
       <c r="D774" t="s">
-        <v>1085</v>
+        <v>1124</v>
       </c>
       <c r="E774" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="F774" t="s">
-        <v>1125</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="775" spans="1:6">
@@ -19757,13 +19757,13 @@
         <v>711</v>
       </c>
       <c r="D775" t="s">
-        <v>1085</v>
+        <v>1092</v>
       </c>
       <c r="E775" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="F775" t="s">
-        <v>1093</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="776" spans="1:6">
@@ -19800,10 +19800,10 @@
         <v>1128</v>
       </c>
       <c r="E777" t="s">
-        <v>1129</v>
+        <v>1132</v>
       </c>
       <c r="F777" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="778" spans="1:6">
@@ -19817,13 +19817,13 @@
         <v>24</v>
       </c>
       <c r="D778" t="s">
-        <v>1128</v>
+        <v>1134</v>
       </c>
       <c r="E778" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="F778" t="s">
-        <v>1135</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="779" spans="1:6">
@@ -19837,13 +19837,13 @@
         <v>24</v>
       </c>
       <c r="D779" t="s">
-        <v>1128</v>
+        <v>1137</v>
       </c>
       <c r="E779" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="F779" t="s">
-        <v>1138</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="780" spans="1:6">
@@ -19860,10 +19860,10 @@
         <v>1128</v>
       </c>
       <c r="E780" t="s">
-        <v>1129</v>
+        <v>1132</v>
       </c>
       <c r="F780" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="781" spans="1:6">
@@ -19880,10 +19880,10 @@
         <v>1128</v>
       </c>
       <c r="E781" t="s">
-        <v>1129</v>
+        <v>1132</v>
       </c>
       <c r="F781" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="782" spans="1:6">
@@ -19900,10 +19900,10 @@
         <v>1128</v>
       </c>
       <c r="E782" t="s">
-        <v>1129</v>
+        <v>1142</v>
       </c>
       <c r="F782" t="s">
-        <v>1142</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="783" spans="1:6">
@@ -19920,10 +19920,10 @@
         <v>1128</v>
       </c>
       <c r="E783" t="s">
-        <v>1129</v>
+        <v>1132</v>
       </c>
       <c r="F783" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="784" spans="1:6">
@@ -19940,10 +19940,10 @@
         <v>1128</v>
       </c>
       <c r="E784" t="s">
-        <v>1129</v>
+        <v>1132</v>
       </c>
       <c r="F784" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="785" spans="1:6">
@@ -19960,10 +19960,10 @@
         <v>1128</v>
       </c>
       <c r="E785" t="s">
-        <v>1129</v>
+        <v>1132</v>
       </c>
       <c r="F785" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="786" spans="1:6">
@@ -19980,10 +19980,10 @@
         <v>1128</v>
       </c>
       <c r="E786" t="s">
-        <v>1129</v>
+        <v>1132</v>
       </c>
       <c r="F786" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="787" spans="1:6">
@@ -20000,10 +20000,10 @@
         <v>1128</v>
       </c>
       <c r="E787" t="s">
-        <v>1129</v>
+        <v>1132</v>
       </c>
       <c r="F787" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="788" spans="1:6">
@@ -20020,10 +20020,10 @@
         <v>1128</v>
       </c>
       <c r="E788" t="s">
-        <v>1129</v>
+        <v>1132</v>
       </c>
       <c r="F788" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="789" spans="1:6">
@@ -20037,10 +20037,10 @@
         <v>24</v>
       </c>
       <c r="D789" t="s">
-        <v>1128</v>
+        <v>1150</v>
       </c>
       <c r="E789" t="s">
-        <v>1150</v>
+        <v>1129</v>
       </c>
       <c r="F789" t="s">
         <v>1130</v>
@@ -20060,10 +20060,10 @@
         <v>1128</v>
       </c>
       <c r="E790" t="s">
-        <v>1129</v>
+        <v>1132</v>
       </c>
       <c r="F790" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="791" spans="1:6">
@@ -20077,13 +20077,13 @@
         <v>24</v>
       </c>
       <c r="D791" t="s">
-        <v>1128</v>
+        <v>1153</v>
       </c>
       <c r="E791" t="s">
-        <v>1153</v>
+        <v>1142</v>
       </c>
       <c r="F791" t="s">
-        <v>1142</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="792" spans="1:6">
@@ -20097,13 +20097,13 @@
         <v>24</v>
       </c>
       <c r="D792" t="s">
-        <v>1128</v>
+        <v>1150</v>
       </c>
       <c r="E792" t="s">
-        <v>1150</v>
+        <v>1155</v>
       </c>
       <c r="F792" t="s">
-        <v>1155</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="793" spans="1:6">
@@ -20120,10 +20120,10 @@
         <v>1128</v>
       </c>
       <c r="E793" t="s">
-        <v>1129</v>
+        <v>1132</v>
       </c>
       <c r="F793" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="794" spans="1:6">
@@ -20137,13 +20137,13 @@
         <v>24</v>
       </c>
       <c r="D794" t="s">
-        <v>1128</v>
+        <v>1158</v>
       </c>
       <c r="E794" t="s">
-        <v>1158</v>
+        <v>1132</v>
       </c>
       <c r="F794" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="795" spans="1:6">
@@ -20160,10 +20160,10 @@
         <v>1128</v>
       </c>
       <c r="E795" t="s">
-        <v>1129</v>
+        <v>1160</v>
       </c>
       <c r="F795" t="s">
-        <v>1160</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="796" spans="1:6">
@@ -20180,10 +20180,10 @@
         <v>1128</v>
       </c>
       <c r="E796" t="s">
-        <v>1129</v>
+        <v>1132</v>
       </c>
       <c r="F796" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="797" spans="1:6">
@@ -20197,13 +20197,13 @@
         <v>24</v>
       </c>
       <c r="D797" t="s">
-        <v>1128</v>
+        <v>1163</v>
       </c>
       <c r="E797" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="F797" t="s">
-        <v>1164</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="798" spans="1:6">
@@ -20217,13 +20217,13 @@
         <v>24</v>
       </c>
       <c r="D798" t="s">
-        <v>1128</v>
+        <v>1166</v>
       </c>
       <c r="E798" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="F798" t="s">
-        <v>1167</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="799" spans="1:6">
@@ -20240,10 +20240,10 @@
         <v>1128</v>
       </c>
       <c r="E799" t="s">
-        <v>1129</v>
+        <v>1132</v>
       </c>
       <c r="F799" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="800" spans="1:6">
@@ -20260,10 +20260,10 @@
         <v>1128</v>
       </c>
       <c r="E800" t="s">
-        <v>1129</v>
+        <v>1132</v>
       </c>
       <c r="F800" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="801" spans="1:6">
@@ -20280,10 +20280,10 @@
         <v>1128</v>
       </c>
       <c r="E801" t="s">
-        <v>1129</v>
+        <v>1132</v>
       </c>
       <c r="F801" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="802" spans="1:6">
@@ -20300,10 +20300,10 @@
         <v>1128</v>
       </c>
       <c r="E802" t="s">
-        <v>1129</v>
+        <v>1132</v>
       </c>
       <c r="F802" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="803" spans="1:6">
@@ -20320,10 +20320,10 @@
         <v>1128</v>
       </c>
       <c r="E803" t="s">
-        <v>1129</v>
+        <v>1132</v>
       </c>
       <c r="F803" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="804" spans="1:6">
@@ -20340,10 +20340,10 @@
         <v>1128</v>
       </c>
       <c r="E804" t="s">
-        <v>1129</v>
+        <v>1132</v>
       </c>
       <c r="F804" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="805" spans="1:6">
@@ -20360,10 +20360,10 @@
         <v>1128</v>
       </c>
       <c r="E805" t="s">
-        <v>1129</v>
+        <v>1132</v>
       </c>
       <c r="F805" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="806" spans="1:6">
@@ -20380,10 +20380,10 @@
         <v>1128</v>
       </c>
       <c r="E806" t="s">
-        <v>1129</v>
+        <v>1132</v>
       </c>
       <c r="F806" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="807" spans="1:6">
@@ -20400,10 +20400,10 @@
         <v>1128</v>
       </c>
       <c r="E807" t="s">
-        <v>1129</v>
+        <v>1132</v>
       </c>
       <c r="F807" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="808" spans="1:6">
@@ -20477,13 +20477,13 @@
         <v>24</v>
       </c>
       <c r="D811" t="s">
-        <v>1178</v>
+        <v>1185</v>
       </c>
       <c r="E811" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="F811" t="s">
-        <v>1186</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="812" spans="1:6">
@@ -20540,10 +20540,10 @@
         <v>1178</v>
       </c>
       <c r="E814" t="s">
-        <v>1179</v>
+        <v>1186</v>
       </c>
       <c r="F814" t="s">
-        <v>1186</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="815" spans="1:6">
@@ -20557,13 +20557,13 @@
         <v>24</v>
       </c>
       <c r="D815" t="s">
-        <v>1178</v>
+        <v>1191</v>
       </c>
       <c r="E815" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="F815" t="s">
-        <v>1192</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="816" spans="1:6">
@@ -20677,13 +20677,13 @@
         <v>15</v>
       </c>
       <c r="D821" t="s">
-        <v>1178</v>
+        <v>1199</v>
       </c>
       <c r="E821" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="F821" t="s">
-        <v>1200</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="822" spans="1:6">
@@ -20697,13 +20697,13 @@
         <v>1182</v>
       </c>
       <c r="D822" t="s">
-        <v>1178</v>
+        <v>1202</v>
       </c>
       <c r="E822" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="F822" t="s">
-        <v>1203</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="823" spans="1:6">
@@ -20720,10 +20720,10 @@
         <v>1178</v>
       </c>
       <c r="E823" t="s">
-        <v>1179</v>
+        <v>1203</v>
       </c>
       <c r="F823" t="s">
-        <v>1203</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="824" spans="1:6">
@@ -20737,13 +20737,13 @@
         <v>1182</v>
       </c>
       <c r="D824" t="s">
-        <v>1178</v>
+        <v>1202</v>
       </c>
       <c r="E824" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="F824" t="s">
-        <v>1203</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="825" spans="1:6">
@@ -20757,13 +20757,13 @@
         <v>711</v>
       </c>
       <c r="D825" t="s">
-        <v>1178</v>
+        <v>1202</v>
       </c>
       <c r="E825" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="F825" t="s">
-        <v>1203</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="826" spans="1:6">
@@ -20777,13 +20777,13 @@
         <v>1182</v>
       </c>
       <c r="D826" t="s">
-        <v>1178</v>
+        <v>1202</v>
       </c>
       <c r="E826" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="F826" t="s">
-        <v>1203</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="827" spans="1:6">
@@ -20797,13 +20797,13 @@
         <v>1182</v>
       </c>
       <c r="D827" t="s">
-        <v>1178</v>
+        <v>1202</v>
       </c>
       <c r="E827" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="F827" t="s">
-        <v>1203</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="828" spans="1:6">
@@ -20820,10 +20820,10 @@
         <v>1178</v>
       </c>
       <c r="E828" t="s">
-        <v>1179</v>
+        <v>1203</v>
       </c>
       <c r="F828" t="s">
-        <v>1203</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="829" spans="1:6">
@@ -20860,10 +20860,10 @@
         <v>1178</v>
       </c>
       <c r="E830" t="s">
-        <v>1179</v>
+        <v>1186</v>
       </c>
       <c r="F830" t="s">
-        <v>1186</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="831" spans="1:6">
@@ -21060,10 +21060,10 @@
         <v>1221</v>
       </c>
       <c r="E840" t="s">
-        <v>1222</v>
+        <v>1225</v>
       </c>
       <c r="F840" t="s">
-        <v>1225</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="841" spans="1:6">
@@ -21080,10 +21080,10 @@
         <v>1221</v>
       </c>
       <c r="E841" t="s">
-        <v>1222</v>
+        <v>1225</v>
       </c>
       <c r="F841" t="s">
-        <v>1225</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="842" spans="1:6">
@@ -21100,10 +21100,10 @@
         <v>1221</v>
       </c>
       <c r="E842" t="s">
-        <v>1222</v>
+        <v>1225</v>
       </c>
       <c r="F842" t="s">
-        <v>1225</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="843" spans="1:6">
@@ -21120,10 +21120,10 @@
         <v>1221</v>
       </c>
       <c r="E843" t="s">
-        <v>1222</v>
+        <v>1225</v>
       </c>
       <c r="F843" t="s">
-        <v>1225</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="844" spans="1:6">
@@ -21140,10 +21140,10 @@
         <v>1221</v>
       </c>
       <c r="E844" t="s">
-        <v>1222</v>
+        <v>1225</v>
       </c>
       <c r="F844" t="s">
-        <v>1225</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="845" spans="1:6">
@@ -21160,10 +21160,10 @@
         <v>1221</v>
       </c>
       <c r="E845" t="s">
-        <v>1222</v>
+        <v>1225</v>
       </c>
       <c r="F845" t="s">
-        <v>1225</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="846" spans="1:6">
@@ -21180,10 +21180,10 @@
         <v>1221</v>
       </c>
       <c r="E846" t="s">
-        <v>1222</v>
+        <v>1225</v>
       </c>
       <c r="F846" t="s">
-        <v>1225</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="847" spans="1:6">
@@ -21197,13 +21197,13 @@
         <v>1182</v>
       </c>
       <c r="D847" t="s">
-        <v>1221</v>
+        <v>1185</v>
       </c>
       <c r="E847" t="s">
-        <v>1185</v>
+        <v>1233</v>
       </c>
       <c r="F847" t="s">
-        <v>1233</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="848" spans="1:6">
@@ -21217,13 +21217,13 @@
         <v>1182</v>
       </c>
       <c r="D848" t="s">
-        <v>1221</v>
+        <v>1185</v>
       </c>
       <c r="E848" t="s">
-        <v>1185</v>
+        <v>1233</v>
       </c>
       <c r="F848" t="s">
-        <v>1233</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="849" spans="1:6">
@@ -21237,13 +21237,13 @@
         <v>711</v>
       </c>
       <c r="D849" t="s">
-        <v>1221</v>
+        <v>1185</v>
       </c>
       <c r="E849" t="s">
-        <v>1185</v>
+        <v>1233</v>
       </c>
       <c r="F849" t="s">
-        <v>1233</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="850" spans="1:6">
@@ -21257,13 +21257,13 @@
         <v>1182</v>
       </c>
       <c r="D850" t="s">
-        <v>1221</v>
+        <v>1237</v>
       </c>
       <c r="E850" t="s">
-        <v>1237</v>
+        <v>1233</v>
       </c>
       <c r="F850" t="s">
-        <v>1233</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="851" spans="1:6">
@@ -21277,13 +21277,13 @@
         <v>1182</v>
       </c>
       <c r="D851" t="s">
-        <v>1221</v>
+        <v>1185</v>
       </c>
       <c r="E851" t="s">
-        <v>1185</v>
+        <v>1233</v>
       </c>
       <c r="F851" t="s">
-        <v>1233</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="852" spans="1:6">
@@ -21297,13 +21297,13 @@
         <v>1182</v>
       </c>
       <c r="D852" t="s">
-        <v>1221</v>
+        <v>1185</v>
       </c>
       <c r="E852" t="s">
-        <v>1185</v>
+        <v>1233</v>
       </c>
       <c r="F852" t="s">
-        <v>1233</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="853" spans="1:6">
@@ -21320,10 +21320,10 @@
         <v>1221</v>
       </c>
       <c r="E853" t="s">
-        <v>1222</v>
+        <v>1225</v>
       </c>
       <c r="F853" t="s">
-        <v>1225</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="854" spans="1:6">
@@ -21340,10 +21340,10 @@
         <v>1221</v>
       </c>
       <c r="E854" t="s">
-        <v>1222</v>
+        <v>1225</v>
       </c>
       <c r="F854" t="s">
-        <v>1225</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="855" spans="1:6">
@@ -21360,10 +21360,10 @@
         <v>1221</v>
       </c>
       <c r="E855" t="s">
-        <v>1222</v>
+        <v>1225</v>
       </c>
       <c r="F855" t="s">
-        <v>1225</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="856" spans="1:6">
@@ -21380,10 +21380,10 @@
         <v>1221</v>
       </c>
       <c r="E856" t="s">
-        <v>1222</v>
+        <v>1225</v>
       </c>
       <c r="F856" t="s">
-        <v>1225</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="857" spans="1:6">
@@ -21400,10 +21400,10 @@
         <v>1221</v>
       </c>
       <c r="E857" t="s">
-        <v>1222</v>
+        <v>1225</v>
       </c>
       <c r="F857" t="s">
-        <v>1225</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="858" spans="1:6">
@@ -21420,10 +21420,10 @@
         <v>1221</v>
       </c>
       <c r="E858" t="s">
-        <v>1222</v>
+        <v>1225</v>
       </c>
       <c r="F858" t="s">
-        <v>1225</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="859" spans="1:6">
@@ -21440,10 +21440,10 @@
         <v>1221</v>
       </c>
       <c r="E859" t="s">
-        <v>1222</v>
+        <v>1225</v>
       </c>
       <c r="F859" t="s">
-        <v>1225</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="860" spans="1:6">
@@ -21460,10 +21460,10 @@
         <v>1221</v>
       </c>
       <c r="E860" t="s">
-        <v>1222</v>
+        <v>1225</v>
       </c>
       <c r="F860" t="s">
-        <v>1225</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="861" spans="1:6">
@@ -21480,10 +21480,10 @@
         <v>1221</v>
       </c>
       <c r="E861" t="s">
-        <v>1222</v>
+        <v>1225</v>
       </c>
       <c r="F861" t="s">
-        <v>1225</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="862" spans="1:6">
@@ -21500,10 +21500,10 @@
         <v>1221</v>
       </c>
       <c r="E862" t="s">
-        <v>1222</v>
+        <v>1225</v>
       </c>
       <c r="F862" t="s">
-        <v>1225</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="863" spans="1:6">
@@ -21520,10 +21520,10 @@
         <v>1221</v>
       </c>
       <c r="E863" t="s">
-        <v>1222</v>
+        <v>1225</v>
       </c>
       <c r="F863" t="s">
-        <v>1225</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="864" spans="1:6">
@@ -21540,10 +21540,10 @@
         <v>1221</v>
       </c>
       <c r="E864" t="s">
-        <v>1222</v>
+        <v>1225</v>
       </c>
       <c r="F864" t="s">
-        <v>1225</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="865" spans="1:6">
@@ -21560,10 +21560,10 @@
         <v>1221</v>
       </c>
       <c r="E865" t="s">
-        <v>1222</v>
+        <v>1225</v>
       </c>
       <c r="F865" t="s">
-        <v>1225</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="866" spans="1:6">
@@ -21580,10 +21580,10 @@
         <v>1221</v>
       </c>
       <c r="E866" t="s">
-        <v>1222</v>
+        <v>1225</v>
       </c>
       <c r="F866" t="s">
-        <v>1225</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="867" spans="1:6">
@@ -21617,10 +21617,10 @@
         <v>1182</v>
       </c>
       <c r="D868" t="s">
-        <v>1255</v>
+        <v>1259</v>
       </c>
       <c r="E868" t="s">
-        <v>1259</v>
+        <v>1256</v>
       </c>
       <c r="F868" t="s">
         <v>1257</v>
@@ -21637,10 +21637,10 @@
         <v>1182</v>
       </c>
       <c r="D869" t="s">
-        <v>1255</v>
+        <v>1259</v>
       </c>
       <c r="E869" t="s">
-        <v>1259</v>
+        <v>1256</v>
       </c>
       <c r="F869" t="s">
         <v>1257</v>
@@ -21657,10 +21657,10 @@
         <v>1182</v>
       </c>
       <c r="D870" t="s">
-        <v>1255</v>
+        <v>1259</v>
       </c>
       <c r="E870" t="s">
-        <v>1259</v>
+        <v>1256</v>
       </c>
       <c r="F870" t="s">
         <v>1257</v>
@@ -21677,10 +21677,10 @@
         <v>1182</v>
       </c>
       <c r="D871" t="s">
-        <v>1255</v>
+        <v>1259</v>
       </c>
       <c r="E871" t="s">
-        <v>1259</v>
+        <v>1256</v>
       </c>
       <c r="F871" t="s">
         <v>1257</v>
@@ -21697,10 +21697,10 @@
         <v>15</v>
       </c>
       <c r="D872" t="s">
-        <v>1255</v>
+        <v>1259</v>
       </c>
       <c r="E872" t="s">
-        <v>1259</v>
+        <v>1256</v>
       </c>
       <c r="F872" t="s">
         <v>1257</v>
@@ -21717,10 +21717,10 @@
         <v>15</v>
       </c>
       <c r="D873" t="s">
-        <v>1255</v>
+        <v>1259</v>
       </c>
       <c r="E873" t="s">
-        <v>1259</v>
+        <v>1256</v>
       </c>
       <c r="F873" t="s">
         <v>1257</v>
@@ -21737,10 +21737,10 @@
         <v>1182</v>
       </c>
       <c r="D874" t="s">
-        <v>1255</v>
+        <v>1259</v>
       </c>
       <c r="E874" t="s">
-        <v>1259</v>
+        <v>1256</v>
       </c>
       <c r="F874" t="s">
         <v>1257</v>
@@ -21757,10 +21757,10 @@
         <v>1182</v>
       </c>
       <c r="D875" t="s">
-        <v>1255</v>
+        <v>1259</v>
       </c>
       <c r="E875" t="s">
-        <v>1259</v>
+        <v>1256</v>
       </c>
       <c r="F875" t="s">
         <v>1257</v>
@@ -21777,10 +21777,10 @@
         <v>711</v>
       </c>
       <c r="D876" t="s">
-        <v>1255</v>
+        <v>1259</v>
       </c>
       <c r="E876" t="s">
-        <v>1259</v>
+        <v>1256</v>
       </c>
       <c r="F876" t="s">
         <v>1257</v>
@@ -21797,10 +21797,10 @@
         <v>15</v>
       </c>
       <c r="D877" t="s">
-        <v>1255</v>
+        <v>1259</v>
       </c>
       <c r="E877" t="s">
-        <v>1259</v>
+        <v>1256</v>
       </c>
       <c r="F877" t="s">
         <v>1257</v>
@@ -21817,10 +21817,10 @@
         <v>1182</v>
       </c>
       <c r="D878" t="s">
-        <v>1255</v>
+        <v>1259</v>
       </c>
       <c r="E878" t="s">
-        <v>1259</v>
+        <v>1256</v>
       </c>
       <c r="F878" t="s">
         <v>1257</v>
@@ -21837,10 +21837,10 @@
         <v>1182</v>
       </c>
       <c r="D879" t="s">
-        <v>1255</v>
+        <v>1259</v>
       </c>
       <c r="E879" t="s">
-        <v>1259</v>
+        <v>1256</v>
       </c>
       <c r="F879" t="s">
         <v>1257</v>
@@ -21857,10 +21857,10 @@
         <v>1182</v>
       </c>
       <c r="D880" t="s">
-        <v>1255</v>
+        <v>1259</v>
       </c>
       <c r="E880" t="s">
-        <v>1259</v>
+        <v>1256</v>
       </c>
       <c r="F880" t="s">
         <v>1257</v>
@@ -21877,10 +21877,10 @@
         <v>1182</v>
       </c>
       <c r="D881" t="s">
-        <v>1255</v>
+        <v>1259</v>
       </c>
       <c r="E881" t="s">
-        <v>1259</v>
+        <v>1256</v>
       </c>
       <c r="F881" t="s">
         <v>1257</v>
@@ -21897,10 +21897,10 @@
         <v>1182</v>
       </c>
       <c r="D882" t="s">
-        <v>1255</v>
+        <v>1259</v>
       </c>
       <c r="E882" t="s">
-        <v>1259</v>
+        <v>1256</v>
       </c>
       <c r="F882" t="s">
         <v>1257</v>
@@ -21917,10 +21917,10 @@
         <v>711</v>
       </c>
       <c r="D883" t="s">
-        <v>1255</v>
+        <v>1259</v>
       </c>
       <c r="E883" t="s">
-        <v>1259</v>
+        <v>1256</v>
       </c>
       <c r="F883" t="s">
         <v>1257</v>
@@ -21937,10 +21937,10 @@
         <v>1182</v>
       </c>
       <c r="D884" t="s">
-        <v>1255</v>
+        <v>1259</v>
       </c>
       <c r="E884" t="s">
-        <v>1259</v>
+        <v>1256</v>
       </c>
       <c r="F884" t="s">
         <v>1257</v>
@@ -21957,10 +21957,10 @@
         <v>1182</v>
       </c>
       <c r="D885" t="s">
-        <v>1255</v>
+        <v>1259</v>
       </c>
       <c r="E885" t="s">
-        <v>1259</v>
+        <v>1256</v>
       </c>
       <c r="F885" t="s">
         <v>1257</v>
@@ -21977,10 +21977,10 @@
         <v>1182</v>
       </c>
       <c r="D886" t="s">
-        <v>1255</v>
+        <v>1259</v>
       </c>
       <c r="E886" t="s">
-        <v>1259</v>
+        <v>1256</v>
       </c>
       <c r="F886" t="s">
         <v>1257</v>
@@ -21997,10 +21997,10 @@
         <v>15</v>
       </c>
       <c r="D887" t="s">
-        <v>1255</v>
+        <v>1259</v>
       </c>
       <c r="E887" t="s">
-        <v>1259</v>
+        <v>1256</v>
       </c>
       <c r="F887" t="s">
         <v>1257</v>
@@ -22017,10 +22017,10 @@
         <v>1182</v>
       </c>
       <c r="D888" t="s">
-        <v>1255</v>
+        <v>1259</v>
       </c>
       <c r="E888" t="s">
-        <v>1259</v>
+        <v>1256</v>
       </c>
       <c r="F888" t="s">
         <v>1257</v>
@@ -22037,10 +22037,10 @@
         <v>711</v>
       </c>
       <c r="D889" t="s">
-        <v>1255</v>
+        <v>1259</v>
       </c>
       <c r="E889" t="s">
-        <v>1259</v>
+        <v>1256</v>
       </c>
       <c r="F889" t="s">
         <v>1257</v>
@@ -22160,10 +22160,10 @@
         <v>1282</v>
       </c>
       <c r="E895" t="s">
-        <v>1283</v>
+        <v>1290</v>
       </c>
       <c r="F895" t="s">
-        <v>1290</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="896" spans="1:6">
@@ -22180,10 +22180,10 @@
         <v>1282</v>
       </c>
       <c r="E896" t="s">
-        <v>1283</v>
+        <v>1290</v>
       </c>
       <c r="F896" t="s">
-        <v>1290</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="897" spans="1:6">
@@ -22357,10 +22357,10 @@
         <v>1182</v>
       </c>
       <c r="D905" t="s">
+        <v>1282</v>
+      </c>
+      <c r="E905" t="s">
         <v>1301</v>
-      </c>
-      <c r="E905" t="s">
-        <v>1283</v>
       </c>
       <c r="F905" t="s">
         <v>1302</v>
@@ -22377,13 +22377,13 @@
         <v>1182</v>
       </c>
       <c r="D906" t="s">
-        <v>1301</v>
+        <v>1282</v>
       </c>
       <c r="E906" t="s">
-        <v>1283</v>
+        <v>1304</v>
       </c>
       <c r="F906" t="s">
-        <v>1304</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="907" spans="1:6">
@@ -22397,10 +22397,10 @@
         <v>1182</v>
       </c>
       <c r="D907" t="s">
+        <v>1282</v>
+      </c>
+      <c r="E907" t="s">
         <v>1301</v>
-      </c>
-      <c r="E907" t="s">
-        <v>1283</v>
       </c>
       <c r="F907" t="s">
         <v>1302</v>

--- a/api/1/clv3/xlsx/fr/HumanitarianPlan.xlsx
+++ b/api/1/clv3/xlsx/fr/HumanitarianPlan.xlsx
@@ -25,12 +25,12 @@
     <t>codeforiati:plan-type</t>
   </si>
   <si>
+    <t>codeforiati:plan-start-date</t>
+  </si>
+  <si>
     <t>codeforiati:plan-end-date</t>
   </si>
   <si>
-    <t>codeforiati:plan-start-date</t>
-  </si>
-  <si>
     <t>codeforiati:plan-year</t>
   </si>
   <si>
@@ -43,12 +43,12 @@
     <t>Humanitarian needs and response plan</t>
   </si>
   <si>
+    <t>2025-01-01</t>
+  </si>
+  <si>
     <t>2025-12-31</t>
   </si>
   <si>
-    <t>2025-01-01</t>
-  </si>
-  <si>
     <t>2025</t>
   </si>
   <si>
@@ -217,12 +217,12 @@
     <t>HAFG24</t>
   </si>
   <si>
+    <t>2024-01-01</t>
+  </si>
+  <si>
     <t>2024-12-31</t>
   </si>
   <si>
-    <t>2024-01-01</t>
-  </si>
-  <si>
     <t>2024</t>
   </si>
   <si>
@@ -421,12 +421,12 @@
     <t>HAFG23</t>
   </si>
   <si>
+    <t>2023-01-01</t>
+  </si>
+  <si>
     <t>2023-12-31</t>
   </si>
   <si>
-    <t>2023-01-01</t>
-  </si>
-  <si>
     <t>2023</t>
   </si>
   <si>
@@ -493,21 +493,21 @@
     <t>OMNG2223</t>
   </si>
   <si>
+    <t>2022-12-01</t>
+  </si>
+  <si>
     <t>2023-05-31</t>
   </si>
   <si>
-    <t>2022-12-01</t>
-  </si>
-  <si>
     <t>OMOZ23</t>
   </si>
   <si>
+    <t>2023-03-01</t>
+  </si>
+  <si>
     <t>2023-09-30</t>
   </si>
   <si>
-    <t>2023-03-01</t>
-  </si>
-  <si>
     <t>HMOZ23</t>
   </si>
   <si>
@@ -553,12 +553,12 @@
     <t>RRSDN23</t>
   </si>
   <si>
+    <t>2023-05-01</t>
+  </si>
+  <si>
     <t>2023-10-31</t>
   </si>
   <si>
-    <t>2023-05-01</t>
-  </si>
-  <si>
     <t>HSDN23</t>
   </si>
   <si>
@@ -601,12 +601,12 @@
     <t>HAFG22</t>
   </si>
   <si>
+    <t>2022-01-01</t>
+  </si>
+  <si>
     <t>2022-12-31</t>
   </si>
   <si>
-    <t>2022-01-01</t>
-  </si>
-  <si>
     <t>2022</t>
   </si>
   <si>
@@ -631,12 +631,12 @@
     <t>OCUB2223</t>
   </si>
   <si>
+    <t>2022-10-20</t>
+  </si>
+  <si>
     <t>2023-03-31</t>
   </si>
   <si>
-    <t>2022-10-20</t>
-  </si>
-  <si>
     <t>RDRCRRP22</t>
   </si>
   <si>
@@ -652,12 +652,12 @@
     <t>FHTI2223</t>
   </si>
   <si>
+    <t>2022-10-16</t>
+  </si>
+  <si>
     <t>2023-04-15</t>
   </si>
   <si>
-    <t>2022-10-16</t>
-  </si>
-  <si>
     <t>FHTI22</t>
   </si>
   <si>
@@ -688,24 +688,24 @@
     <t>FMWI22</t>
   </si>
   <si>
+    <t>2022-02-26</t>
+  </si>
+  <si>
     <t>2022-05-31</t>
   </si>
   <si>
-    <t>2022-02-26</t>
-  </si>
-  <si>
     <t>HMLI22</t>
   </si>
   <si>
     <t>FMOZ22</t>
   </si>
   <si>
+    <t>2022-04-01</t>
+  </si>
+  <si>
     <t>2022-09-30</t>
   </si>
   <si>
-    <t>2022-04-01</t>
-  </si>
-  <si>
     <t>HMOZ22</t>
   </si>
   <si>
@@ -736,12 +736,12 @@
     <t>OPHL2122</t>
   </si>
   <si>
+    <t>2021-12-24</t>
+  </si>
+  <si>
     <t>2022-06-30</t>
   </si>
   <si>
-    <t>2021-12-24</t>
-  </si>
-  <si>
     <t>RREG22</t>
   </si>
   <si>
@@ -805,12 +805,12 @@
     <t>FAFG21</t>
   </si>
   <si>
+    <t>2021-09-01</t>
+  </si>
+  <si>
     <t>2021-12-31</t>
   </si>
   <si>
-    <t>2021-09-01</t>
-  </si>
-  <si>
     <t>2021</t>
   </si>
   <si>
@@ -862,12 +862,12 @@
     <t>FPSE21</t>
   </si>
   <si>
+    <t>2021-05-27</t>
+  </si>
+  <si>
     <t>2021-08-27</t>
   </si>
   <si>
-    <t>2021-05-27</t>
-  </si>
-  <si>
     <t>HETH21</t>
   </si>
   <si>
@@ -880,24 +880,24 @@
     <t>FHTI2122</t>
   </si>
   <si>
+    <t>2021-08-16</t>
+  </si>
+  <si>
     <t>2022-02-15</t>
   </si>
   <si>
-    <t>2021-08-16</t>
-  </si>
-  <si>
     <t>HHTI21</t>
   </si>
   <si>
     <t>FHND2021</t>
   </si>
   <si>
+    <t>2020-11-15</t>
+  </si>
+  <si>
     <t>2021-06-30</t>
   </si>
   <si>
-    <t>2020-11-15</t>
-  </si>
-  <si>
     <t>HHND21</t>
   </si>
   <si>
@@ -916,12 +916,12 @@
     <t>OLBN2122</t>
   </si>
   <si>
+    <t>2021-08-03</t>
+  </si>
+  <si>
     <t>2022-07-31</t>
   </si>
   <si>
-    <t>2021-08-03</t>
-  </si>
-  <si>
     <t>HLBY21</t>
   </si>
   <si>
@@ -1009,12 +1009,12 @@
     <t>HAFG20</t>
   </si>
   <si>
+    <t>2020-01-01</t>
+  </si>
+  <si>
     <t>2020-12-31</t>
   </si>
   <si>
-    <t>2020-01-01</t>
-  </si>
-  <si>
     <t>2020</t>
   </si>
   <si>
@@ -1081,12 +1081,12 @@
     <t>FDJI1920</t>
   </si>
   <si>
+    <t>2019-12-17</t>
+  </si>
+  <si>
     <t>2020-03-31</t>
   </si>
   <si>
-    <t>2019-12-17</t>
-  </si>
-  <si>
     <t>ODJI20</t>
   </si>
   <si>
@@ -1135,24 +1135,24 @@
     <t>FLBN20</t>
   </si>
   <si>
+    <t>2020-08-05</t>
+  </si>
+  <si>
     <t>2020-11-13</t>
   </si>
   <si>
-    <t>2020-08-05</t>
-  </si>
-  <si>
     <t>OLBN20</t>
   </si>
   <si>
     <t>FLSO1920</t>
   </si>
   <si>
+    <t>2019-11-01</t>
+  </si>
+  <si>
     <t>2020-04-30</t>
   </si>
   <si>
-    <t>2019-11-01</t>
-  </si>
-  <si>
     <t>OLBR20</t>
   </si>
   <si>
@@ -1249,12 +1249,12 @@
     <t>HAFG19</t>
   </si>
   <si>
+    <t>2019-01-01</t>
+  </si>
+  <si>
     <t>2019-12-31</t>
   </si>
   <si>
-    <t>2019-01-01</t>
-  </si>
-  <si>
     <t>2019</t>
   </si>
   <si>
@@ -1366,12 +1366,12 @@
     <t>FZWE1920</t>
   </si>
   <si>
+    <t>2019-02-01</t>
+  </si>
+  <si>
     <t>2020-04-29</t>
   </si>
   <si>
-    <t>2019-02-01</t>
-  </si>
-  <si>
     <t>FZWE1820</t>
   </si>
   <si>
@@ -1381,12 +1381,12 @@
     <t>HAFG18</t>
   </si>
   <si>
+    <t>2018-01-01</t>
+  </si>
+  <si>
     <t>2018-12-31</t>
   </si>
   <si>
-    <t>2018-01-01</t>
-  </si>
-  <si>
     <t>2018</t>
   </si>
   <si>
@@ -1483,12 +1483,12 @@
     <t>HSYR18</t>
   </si>
   <si>
+    <t>2018-11-30</t>
+  </si>
+  <si>
     <t>2018-12-30</t>
   </si>
   <si>
-    <t>2018-11-30</t>
-  </si>
-  <si>
     <t>RSYR18</t>
   </si>
   <si>
@@ -1507,12 +1507,12 @@
     <t>OEUR17</t>
   </si>
   <si>
+    <t>2017-01-01</t>
+  </si>
+  <si>
     <t>2017-12-31</t>
   </si>
   <si>
-    <t>2017-01-01</t>
-  </si>
-  <si>
     <t>2017</t>
   </si>
   <si>
@@ -1558,12 +1558,12 @@
     <t>FDMA17</t>
   </si>
   <si>
+    <t>2017-09-28</t>
+  </si>
+  <si>
     <t>2017-12-29</t>
   </si>
   <si>
-    <t>2017-09-28</t>
-  </si>
-  <si>
     <t>OPRK17</t>
   </si>
   <si>
@@ -1585,24 +1585,24 @@
     <t>FKEN17</t>
   </si>
   <si>
+    <t>2017-02-10</t>
+  </si>
+  <si>
     <t>2017-11-30</t>
   </si>
   <si>
-    <t>2017-02-10</t>
-  </si>
-  <si>
     <t>HLBY17</t>
   </si>
   <si>
     <t>FMDG17</t>
   </si>
   <si>
+    <t>2017-03-20</t>
+  </si>
+  <si>
     <t>2017-06-20</t>
   </si>
   <si>
-    <t>2017-03-20</t>
-  </si>
-  <si>
     <t>HMLI17</t>
   </si>
   <si>
@@ -1612,12 +1612,12 @@
     <t>FMOZ17</t>
   </si>
   <si>
+    <t>2017-02-28</t>
+  </si>
+  <si>
     <t>2017-05-31</t>
   </si>
   <si>
-    <t>2017-02-28</t>
-  </si>
-  <si>
     <t>HMMR17</t>
   </si>
   <si>
@@ -1636,12 +1636,12 @@
     <t>FPER17</t>
   </si>
   <si>
+    <t>2017-04-01</t>
+  </si>
+  <si>
     <t>2017-10-31</t>
   </si>
   <si>
-    <t>2017-04-01</t>
-  </si>
-  <si>
     <t>HCOG17</t>
   </si>
   <si>
@@ -1678,12 +1678,12 @@
     <t>OEUR16</t>
   </si>
   <si>
+    <t>2016-01-01</t>
+  </si>
+  <si>
     <t>2016-12-31</t>
   </si>
   <si>
-    <t>2016-01-01</t>
-  </si>
-  <si>
     <t>2016</t>
   </si>
   <si>
@@ -1726,21 +1726,21 @@
     <t>FECU16</t>
   </si>
   <si>
+    <t>2016-04-16</t>
+  </si>
+  <si>
     <t>2016-10-31</t>
   </si>
   <si>
-    <t>2016-04-16</t>
-  </si>
-  <si>
     <t>FFJI16</t>
   </si>
   <si>
+    <t>2016-02-20</t>
+  </si>
+  <si>
     <t>2016-05-30</t>
   </si>
   <si>
-    <t>2016-02-20</t>
-  </si>
-  <si>
     <t>HGMB16</t>
   </si>
   <si>
@@ -1783,12 +1783,12 @@
     <t>FIRQ16</t>
   </si>
   <si>
+    <t>2016-07-20</t>
+  </si>
+  <si>
     <t>2016-10-01</t>
   </si>
   <si>
-    <t>2016-07-20</t>
-  </si>
-  <si>
     <t>HMMR16</t>
   </si>
   <si>
@@ -1831,24 +1831,24 @@
     <t>HZWE1617</t>
   </si>
   <si>
+    <t>2016-04-01</t>
+  </si>
+  <si>
     <t>2017-03-31</t>
   </si>
   <si>
-    <t>2016-04-01</t>
-  </si>
-  <si>
     <t>HAFG15</t>
   </si>
   <si>
     <t>Strategic response plan</t>
   </si>
   <si>
+    <t>2015-01-01</t>
+  </si>
+  <si>
     <t>2015-12-31</t>
   </si>
   <si>
-    <t>2015-01-01</t>
-  </si>
-  <si>
     <t>2015</t>
   </si>
   <si>
@@ -1879,12 +1879,12 @@
     <t>FGTM1415</t>
   </si>
   <si>
+    <t>2014-11-03</t>
+  </si>
+  <si>
     <t>2015-09-30</t>
   </si>
   <si>
-    <t>2014-11-03</t>
-  </si>
-  <si>
     <t>FHTI15</t>
   </si>
   <si>
@@ -1900,24 +1900,24 @@
     <t>FVUT15</t>
   </si>
   <si>
+    <t>2015-03-24</t>
+  </si>
+  <si>
     <t>2015-10-31</t>
   </si>
   <si>
-    <t>2015-03-24</t>
-  </si>
-  <si>
     <t>HIRQ15</t>
   </si>
   <si>
     <t>HLBY1415</t>
   </si>
   <si>
+    <t>2014-10-01</t>
+  </si>
+  <si>
     <t>2015-05-31</t>
   </si>
   <si>
-    <t>2014-10-01</t>
-  </si>
-  <si>
     <t>HMLI15</t>
   </si>
   <si>
@@ -1975,12 +1975,12 @@
     <t>HAFG14</t>
   </si>
   <si>
+    <t>2014-01-01</t>
+  </si>
+  <si>
     <t>2014-12-31</t>
   </si>
   <si>
-    <t>2014-01-01</t>
-  </si>
-  <si>
     <t>2014</t>
   </si>
   <si>
@@ -2059,21 +2059,21 @@
     <t>FPHL1314</t>
   </si>
   <si>
+    <t>2013-10-22</t>
+  </si>
+  <si>
     <t>2014-04-22</t>
   </si>
   <si>
-    <t>2013-10-22</t>
-  </si>
-  <si>
     <t>SPHL1314</t>
   </si>
   <si>
+    <t>2013-11-08</t>
+  </si>
+  <si>
     <t>2014-11-07</t>
   </si>
   <si>
-    <t>2013-11-08</t>
-  </si>
-  <si>
     <t>HPHL1314</t>
   </si>
   <si>
@@ -2083,12 +2083,12 @@
     <t>HPHL1314a</t>
   </si>
   <si>
+    <t>2013-10-01</t>
+  </si>
+  <si>
     <t>2014-08-31</t>
   </si>
   <si>
-    <t>2013-10-01</t>
-  </si>
-  <si>
     <t>SCOD14</t>
   </si>
   <si>
@@ -2242,12 +2242,12 @@
     <t>CKEN12</t>
   </si>
   <si>
+    <t>2012-01-01</t>
+  </si>
+  <si>
     <t>2012-12-31</t>
   </si>
   <si>
-    <t>2012-01-01</t>
-  </si>
-  <si>
     <t>2012</t>
   </si>
   <si>
@@ -2290,12 +2290,12 @@
     <t>FLSO1213</t>
   </si>
   <si>
+    <t>2012-09-18</t>
+  </si>
+  <si>
     <t>2013-03-25</t>
   </si>
   <si>
-    <t>2012-09-18</t>
-  </si>
-  <si>
     <t>CLBR12</t>
   </si>
   <si>
@@ -2335,12 +2335,12 @@
     <t>CSYR12</t>
   </si>
   <si>
+    <t>2012-06-05</t>
+  </si>
+  <si>
     <t>2012-12-05</t>
   </si>
   <si>
-    <t>2012-06-05</t>
-  </si>
-  <si>
     <t>CYEM12</t>
   </si>
   <si>
@@ -2383,12 +2383,12 @@
     <t>FSLV1112</t>
   </si>
   <si>
+    <t>2011-10-25</t>
+  </si>
+  <si>
     <t>2012-04-25</t>
   </si>
   <si>
-    <t>2011-10-25</t>
-  </si>
-  <si>
     <t>CHTI1011</t>
   </si>
   <si>
@@ -2407,33 +2407,33 @@
     <t>FNAM11</t>
   </si>
   <si>
+    <t>2011-04-11</t>
+  </si>
+  <si>
     <t>2011-10-11</t>
   </si>
   <si>
-    <t>2011-04-11</t>
-  </si>
-  <si>
     <t>FNIC1112</t>
   </si>
   <si>
+    <t>2011-10-27</t>
+  </si>
+  <si>
     <t>2012-04-26</t>
   </si>
   <si>
-    <t>2011-10-27</t>
-  </si>
-  <si>
     <t>CNER11</t>
   </si>
   <si>
     <t>FPAK1112</t>
   </si>
   <si>
+    <t>2011-09-15</t>
+  </si>
+  <si>
     <t>2012-06-30</t>
   </si>
   <si>
-    <t>2011-09-15</t>
-  </si>
-  <si>
     <t>FXLBYREG11</t>
   </si>
   <si>
@@ -2476,24 +2476,24 @@
     <t>CAFG10</t>
   </si>
   <si>
+    <t>2010-01-01</t>
+  </si>
+  <si>
     <t>2010-12-31</t>
   </si>
   <si>
-    <t>2010-01-01</t>
-  </si>
-  <si>
     <t>2010</t>
   </si>
   <si>
     <t>OBFA1011</t>
   </si>
   <si>
+    <t>2010-08-01</t>
+  </si>
+  <si>
     <t>2011-01-31</t>
   </si>
   <si>
-    <t>2010-08-01</t>
-  </si>
-  <si>
     <t>CCAF10</t>
   </si>
   <si>
@@ -2506,30 +2506,30 @@
     <t>FSLV0910</t>
   </si>
   <si>
+    <t>2009-11-01</t>
+  </si>
+  <si>
     <t>2010-05-31</t>
   </si>
   <si>
-    <t>2009-11-01</t>
-  </si>
-  <si>
     <t>FGTM10</t>
   </si>
   <si>
+    <t>2010-06-10</t>
+  </si>
+  <si>
     <t>2010-12-09</t>
   </si>
   <si>
-    <t>2010-06-10</t>
-  </si>
-  <si>
     <t>CGTM10</t>
   </si>
   <si>
+    <t>2010-02-12</t>
+  </si>
+  <si>
     <t>2010-08-11</t>
   </si>
   <si>
-    <t>2010-02-12</t>
-  </si>
-  <si>
     <t>FHTI10</t>
   </si>
   <si>
@@ -2545,12 +2545,12 @@
     <t>FKGZ1011</t>
   </si>
   <si>
+    <t>2010-06-01</t>
+  </si>
+  <si>
     <t>2011-06-30</t>
   </si>
   <si>
-    <t>2010-06-01</t>
-  </si>
-  <si>
     <t>CMNG1011</t>
   </si>
   <si>
@@ -2608,24 +2608,24 @@
     <t>CAFG09</t>
   </si>
   <si>
+    <t>2009-01-01</t>
+  </si>
+  <si>
     <t>2009-12-31</t>
   </si>
   <si>
-    <t>2009-01-01</t>
-  </si>
-  <si>
     <t>2009</t>
   </si>
   <si>
     <t>FBFA0910</t>
   </si>
   <si>
+    <t>2009-09-10</t>
+  </si>
+  <si>
     <t>2010-03-09</t>
   </si>
   <si>
-    <t>2009-09-10</t>
-  </si>
-  <si>
     <t>CCAF09</t>
   </si>
   <si>
@@ -2662,21 +2662,21 @@
     <t>FMDG09</t>
   </si>
   <si>
+    <t>2009-04-01</t>
+  </si>
+  <si>
     <t>2009-10-31</t>
   </si>
   <si>
-    <t>2009-04-01</t>
-  </si>
-  <si>
     <t>FNAM09</t>
   </si>
   <si>
+    <t>2009-03-20</t>
+  </si>
+  <si>
     <t>2009-09-30</t>
   </si>
   <si>
-    <t>2009-03-20</t>
-  </si>
-  <si>
     <t>ONPL09</t>
   </si>
   <si>
@@ -2689,12 +2689,12 @@
     <t>FPHL0910</t>
   </si>
   <si>
+    <t>2009-10-03</t>
+  </si>
+  <si>
     <t>2010-03-31</t>
   </si>
   <si>
-    <t>2009-10-03</t>
-  </si>
-  <si>
     <t>CSOM09</t>
   </si>
   <si>
@@ -2707,12 +2707,12 @@
     <t>OSYR0910</t>
   </si>
   <si>
+    <t>2009-07-15</t>
+  </si>
+  <si>
     <t>2010-06-14</t>
   </si>
   <si>
-    <t>2009-07-15</t>
-  </si>
-  <si>
     <t>OTJK09</t>
   </si>
   <si>
@@ -2746,24 +2746,24 @@
     <t>OAFG08</t>
   </si>
   <si>
+    <t>2008-02-01</t>
+  </si>
+  <si>
     <t>2008-06-30</t>
   </si>
   <si>
-    <t>2008-02-01</t>
-  </si>
-  <si>
     <t>2008</t>
   </si>
   <si>
     <t>OAFG0809</t>
   </si>
   <si>
+    <t>2008-07-01</t>
+  </si>
+  <si>
     <t>2009-06-30</t>
   </si>
   <si>
-    <t>2008-07-01</t>
-  </si>
-  <si>
     <t>FBOL08</t>
   </si>
   <si>
@@ -2773,12 +2773,12 @@
     <t>CCAF08</t>
   </si>
   <si>
+    <t>2008-01-01</t>
+  </si>
+  <si>
     <t>2008-12-31</t>
   </si>
   <si>
-    <t>2008-01-01</t>
-  </si>
-  <si>
     <t>CTCD08</t>
   </si>
   <si>
@@ -2794,21 +2794,21 @@
     <t>ODJI0809</t>
   </si>
   <si>
+    <t>2008-08-01</t>
+  </si>
+  <si>
     <t>2009-02-28</t>
   </si>
   <si>
-    <t>2008-08-01</t>
-  </si>
-  <si>
     <t>FGEO0809</t>
   </si>
   <si>
+    <t>2008-08-09</t>
+  </si>
+  <si>
     <t>2009-02-09</t>
   </si>
   <si>
-    <t>2008-08-09</t>
-  </si>
-  <si>
     <t>FHTI0809</t>
   </si>
   <si>
@@ -2818,12 +2818,12 @@
     <t>FHND0809</t>
   </si>
   <si>
+    <t>2008-11-01</t>
+  </si>
+  <si>
     <t>2009-04-30</t>
   </si>
   <si>
-    <t>2008-11-01</t>
-  </si>
-  <si>
     <t>CIRQ08</t>
   </si>
   <si>
@@ -2833,12 +2833,12 @@
     <t>FKGZ0809</t>
   </si>
   <si>
+    <t>2008-12-01</t>
+  </si>
+  <si>
     <t>2009-05-31</t>
   </si>
   <si>
-    <t>2008-12-01</t>
-  </si>
-  <si>
     <t>OLAO0809</t>
   </si>
   <si>
@@ -2857,12 +2857,12 @@
     <t>FMMR08</t>
   </si>
   <si>
+    <t>2008-05-01</t>
+  </si>
+  <si>
     <t>2008-11-30</t>
   </si>
   <si>
-    <t>2008-05-01</t>
-  </si>
-  <si>
     <t>ONPL08</t>
   </si>
   <si>
@@ -2914,33 +2914,33 @@
     <t>FBOL07</t>
   </si>
   <si>
+    <t>2007-02-22</t>
+  </si>
+  <si>
     <t>2007-08-21</t>
   </si>
   <si>
-    <t>2007-02-22</t>
-  </si>
-  <si>
     <t>2007</t>
   </si>
   <si>
     <t>FBFA0708</t>
   </si>
   <si>
+    <t>2007-11-01</t>
+  </si>
+  <si>
     <t>2008-01-31</t>
   </si>
   <si>
-    <t>2007-11-01</t>
-  </si>
-  <si>
     <t>CBDI07</t>
   </si>
   <si>
+    <t>2007-01-01</t>
+  </si>
+  <si>
     <t>2007-12-31</t>
   </si>
   <si>
-    <t>2007-01-01</t>
-  </si>
-  <si>
     <t>CCAF07</t>
   </si>
   <si>
@@ -2962,12 +2962,12 @@
     <t>FGHA0708</t>
   </si>
   <si>
+    <t>2007-09-01</t>
+  </si>
+  <si>
     <t>2008-03-31</t>
   </si>
   <si>
-    <t>2007-09-01</t>
-  </si>
-  <si>
     <t>CXGLR07</t>
   </si>
   <si>
@@ -2980,75 +2980,75 @@
     <t>FPRK07</t>
   </si>
   <si>
+    <t>2007-08-28</t>
+  </si>
+  <si>
     <t>2007-11-30</t>
   </si>
   <si>
-    <t>2007-08-28</t>
-  </si>
-  <si>
     <t>OLBN07</t>
   </si>
   <si>
+    <t>2007-06-04</t>
+  </si>
+  <si>
     <t>2007-09-03</t>
   </si>
   <si>
-    <t>2007-06-04</t>
-  </si>
-  <si>
     <t>FLSO0708</t>
   </si>
   <si>
+    <t>2007-07-28</t>
+  </si>
+  <si>
     <t>2008-01-28</t>
   </si>
   <si>
-    <t>2007-07-28</t>
-  </si>
-  <si>
     <t>CLBR07</t>
   </si>
   <si>
     <t>FMDG07</t>
   </si>
   <si>
+    <t>2007-03-15</t>
+  </si>
+  <si>
     <t>2007-09-15</t>
   </si>
   <si>
-    <t>2007-03-15</t>
-  </si>
-  <si>
     <t>FMOZ07</t>
   </si>
   <si>
+    <t>2007-03-01</t>
+  </si>
+  <si>
     <t>2007-06-30</t>
   </si>
   <si>
-    <t>2007-03-01</t>
-  </si>
-  <si>
     <t>ONPL07</t>
   </si>
   <si>
     <t>FNIC0708</t>
   </si>
   <si>
+    <t>2007-09-07</t>
+  </si>
+  <si>
     <t>2008-02-28</t>
   </si>
   <si>
-    <t>2007-09-07</t>
-  </si>
-  <si>
     <t>ORUS07</t>
   </si>
   <si>
     <t>FPAK07</t>
   </si>
   <si>
+    <t>2007-07-15</t>
+  </si>
+  <si>
     <t>2007-10-31</t>
   </si>
   <si>
-    <t>2007-07-15</t>
-  </si>
-  <si>
     <t>FPER0708</t>
   </si>
   <si>
@@ -3082,12 +3082,12 @@
     <t>FSWZ0708</t>
   </si>
   <si>
+    <t>2007-07-20</t>
+  </si>
+  <si>
     <t>2008-01-20</t>
   </si>
   <si>
-    <t>2007-07-20</t>
-  </si>
-  <si>
     <t>CTLS07</t>
   </si>
   <si>
@@ -3112,12 +3112,12 @@
     <t>OAFG06</t>
   </si>
   <si>
+    <t>2006-07-01</t>
+  </si>
+  <si>
     <t>2006-12-31</t>
   </si>
   <si>
-    <t>2006-07-01</t>
-  </si>
-  <si>
     <t>2006</t>
   </si>
   <si>
@@ -3145,21 +3145,21 @@
     <t>OETH06a</t>
   </si>
   <si>
+    <t>2006-08-25</t>
+  </si>
+  <si>
     <t>2006-11-25</t>
   </si>
   <si>
-    <t>2006-08-25</t>
-  </si>
-  <si>
     <t>OETH0607</t>
   </si>
   <si>
+    <t>2006-11-23</t>
+  </si>
+  <si>
     <t>2007-01-22</t>
   </si>
   <si>
-    <t>2006-11-23</t>
-  </si>
-  <si>
     <t>CXGLR06</t>
   </si>
   <si>
@@ -3169,12 +3169,12 @@
     <t>FGNB06</t>
   </si>
   <si>
+    <t>2006-05-01</t>
+  </si>
+  <si>
     <t>2006-11-30</t>
   </si>
   <si>
-    <t>2006-05-01</t>
-  </si>
-  <si>
     <t>CXHAF06</t>
   </si>
   <si>
@@ -3184,12 +3184,12 @@
     <t>FKEN0607</t>
   </si>
   <si>
+    <t>2006-10-16</t>
+  </si>
+  <si>
     <t>2007-04-15</t>
   </si>
   <si>
-    <t>2006-10-16</t>
-  </si>
-  <si>
     <t>FKEN06</t>
   </si>
   <si>
@@ -3199,12 +3199,12 @@
     <t>FLBN06</t>
   </si>
   <si>
+    <t>2006-07-24</t>
+  </si>
+  <si>
     <t>2006-10-23</t>
   </si>
   <si>
-    <t>2006-07-24</t>
-  </si>
-  <si>
     <t>CLBR06</t>
   </si>
   <si>
@@ -3232,12 +3232,12 @@
     <t>FSOM0607</t>
   </si>
   <si>
+    <t>2006-12-05</t>
+  </si>
+  <si>
     <t>2007-03-05</t>
   </si>
   <si>
-    <t>2006-12-05</t>
-  </si>
-  <si>
     <t>OLKA06</t>
   </si>
   <si>
@@ -3271,33 +3271,33 @@
     <t>FAGO05</t>
   </si>
   <si>
+    <t>2005-04-01</t>
+  </si>
+  <si>
     <t>2005-06-30</t>
   </si>
   <si>
-    <t>2005-04-01</t>
-  </si>
-  <si>
     <t>2005</t>
   </si>
   <si>
     <t>FBEN05</t>
   </si>
   <si>
+    <t>2005-05-01</t>
+  </si>
+  <si>
     <t>2005-10-31</t>
   </si>
   <si>
-    <t>2005-05-01</t>
-  </si>
-  <si>
     <t>CBDI05</t>
   </si>
   <si>
+    <t>2005-01-01</t>
+  </si>
+  <si>
     <t>2005-12-31</t>
   </si>
   <si>
-    <t>2005-01-01</t>
-  </si>
-  <si>
     <t>CCAF05</t>
   </si>
   <si>
@@ -3337,12 +3337,12 @@
     <t>FGUY05</t>
   </si>
   <si>
+    <t>2005-02-01</t>
+  </si>
+  <si>
     <t>2005-08-01</t>
   </si>
   <si>
-    <t>2005-02-01</t>
-  </si>
-  <si>
     <t>FXINDTSU05</t>
   </si>
   <si>
@@ -3355,12 +3355,12 @@
     <t>FNER05</t>
   </si>
   <si>
+    <t>2005-06-01</t>
+  </si>
+  <si>
     <t>2005-09-30</t>
   </si>
   <si>
-    <t>2005-06-01</t>
-  </si>
-  <si>
     <t>CCOG05</t>
   </si>
   <si>
@@ -3370,12 +3370,12 @@
     <t>FXSASIA0506</t>
   </si>
   <si>
+    <t>2005-10-11</t>
+  </si>
+  <si>
     <t>2006-04-10</t>
   </si>
   <si>
-    <t>2005-10-11</t>
-  </si>
-  <si>
     <t>CSDN05</t>
   </si>
   <si>
@@ -3388,24 +3388,24 @@
     <t>FXWAF0506</t>
   </si>
   <si>
+    <t>2005-11-01</t>
+  </si>
+  <si>
     <t>2006-05-31</t>
   </si>
   <si>
-    <t>2005-11-01</t>
-  </si>
-  <si>
     <t>CPSE05</t>
   </si>
   <si>
     <t>OAFG04</t>
   </si>
   <si>
+    <t>2004-09-01</t>
+  </si>
+  <si>
     <t>2004-12-31</t>
   </si>
   <si>
-    <t>2004-09-01</t>
-  </si>
-  <si>
     <t>2004</t>
   </si>
   <si>
@@ -3418,21 +3418,21 @@
     <t>FBGD0405</t>
   </si>
   <si>
+    <t>2004-08-01</t>
+  </si>
+  <si>
     <t>2005-01-31</t>
   </si>
   <si>
-    <t>2004-08-01</t>
-  </si>
-  <si>
     <t>FBOL0405</t>
   </si>
   <si>
+    <t>2004-11-01</t>
+  </si>
+  <si>
     <t>2005-05-31</t>
   </si>
   <si>
-    <t>2004-11-01</t>
-  </si>
-  <si>
     <t>CBDI04</t>
   </si>
   <si>
@@ -3505,21 +3505,21 @@
     <t>FMDG04</t>
   </si>
   <si>
+    <t>2004-03-19</t>
+  </si>
+  <si>
     <t>2004-06-19</t>
   </si>
   <si>
-    <t>2004-03-19</t>
-  </si>
-  <si>
     <t>FPHL0405</t>
   </si>
   <si>
+    <t>2004-12-15</t>
+  </si>
+  <si>
     <t>2005-03-15</t>
   </si>
   <si>
-    <t>2004-12-15</t>
-  </si>
-  <si>
     <t>CSLE04</t>
   </si>
   <si>
@@ -3550,12 +3550,12 @@
     <t>OAFG03</t>
   </si>
   <si>
+    <t>2003-01-01</t>
+  </si>
+  <si>
     <t>2003-12-31</t>
   </si>
   <si>
-    <t>2003-01-01</t>
-  </si>
-  <si>
     <t>2003</t>
   </si>
   <si>
@@ -3571,12 +3571,12 @@
     <t>FCAF03</t>
   </si>
   <si>
+    <t>2003-04-01</t>
+  </si>
+  <si>
     <t>2003-06-30</t>
   </si>
   <si>
-    <t>2003-04-01</t>
-  </si>
-  <si>
     <t>CRUS03</t>
   </si>
   <si>
@@ -3589,12 +3589,12 @@
     <t>FCIV0203</t>
   </si>
   <si>
+    <t>2002-11-01</t>
+  </si>
+  <si>
     <t>2003-01-31</t>
   </si>
   <si>
-    <t>2002-11-01</t>
-  </si>
-  <si>
     <t>CPRK03</t>
   </si>
   <si>
@@ -3613,21 +3613,21 @@
     <t>OHTI03</t>
   </si>
   <si>
+    <t>2003-03-01</t>
+  </si>
+  <si>
     <t>2003-08-31</t>
   </si>
   <si>
-    <t>2003-03-01</t>
-  </si>
-  <si>
     <t>CLSO0304</t>
   </si>
   <si>
+    <t>2003-07-01</t>
+  </si>
+  <si>
     <t>2004-06-30</t>
   </si>
   <si>
-    <t>2003-07-01</t>
-  </si>
-  <si>
     <t>CMWI03</t>
   </si>
   <si>
@@ -3679,12 +3679,12 @@
     <t>CAFG0102</t>
   </si>
   <si>
+    <t>2001-10-01</t>
+  </si>
+  <si>
     <t>2002-12-31</t>
   </si>
   <si>
-    <t>2001-10-01</t>
-  </si>
-  <si>
     <t>2002</t>
   </si>
   <si>
@@ -3781,12 +3781,12 @@
     <t>CAFG01</t>
   </si>
   <si>
+    <t>2001-01-01</t>
+  </si>
+  <si>
     <t>2001-09-30</t>
   </si>
   <si>
-    <t>2001-01-01</t>
-  </si>
-  <si>
     <t>2001</t>
   </si>
   <si>
@@ -3862,10 +3862,10 @@
     <t>CAGO00</t>
   </si>
   <si>
+    <t>2000-01-01</t>
+  </si>
+  <si>
     <t>2000-12-31</t>
-  </si>
-  <si>
-    <t>2000-01-01</t>
   </si>
   <si>
     <t>2000</t>
@@ -4337,10 +4337,10 @@
         <v>15</v>
       </c>
       <c r="D4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" t="s">
         <v>16</v>
-      </c>
-      <c r="E4" t="s">
-        <v>10</v>
       </c>
       <c r="F4" t="s">
         <v>11</v>
@@ -4537,10 +4537,10 @@
         <v>24</v>
       </c>
       <c r="D14" t="s">
+        <v>9</v>
+      </c>
+      <c r="E14" t="s">
         <v>16</v>
-      </c>
-      <c r="E14" t="s">
-        <v>10</v>
       </c>
       <c r="F14" t="s">
         <v>11</v>
@@ -4557,10 +4557,10 @@
         <v>24</v>
       </c>
       <c r="D15" t="s">
+        <v>9</v>
+      </c>
+      <c r="E15" t="s">
         <v>30</v>
-      </c>
-      <c r="E15" t="s">
-        <v>10</v>
       </c>
       <c r="F15" t="s">
         <v>11</v>
@@ -4597,10 +4597,10 @@
         <v>24</v>
       </c>
       <c r="D17" t="s">
+        <v>9</v>
+      </c>
+      <c r="E17" t="s">
         <v>33</v>
-      </c>
-      <c r="E17" t="s">
-        <v>10</v>
       </c>
       <c r="F17" t="s">
         <v>11</v>
@@ -4637,10 +4637,10 @@
         <v>24</v>
       </c>
       <c r="D19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E19" t="s">
         <v>36</v>
-      </c>
-      <c r="E19" t="s">
-        <v>10</v>
       </c>
       <c r="F19" t="s">
         <v>11</v>
@@ -4657,10 +4657,10 @@
         <v>8</v>
       </c>
       <c r="D20" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="E20" t="s">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="F20" t="s">
         <v>11</v>
@@ -4737,10 +4737,10 @@
         <v>15</v>
       </c>
       <c r="D24" t="s">
+        <v>9</v>
+      </c>
+      <c r="E24" t="s">
         <v>43</v>
-      </c>
-      <c r="E24" t="s">
-        <v>10</v>
       </c>
       <c r="F24" t="s">
         <v>11</v>
@@ -4937,10 +4937,10 @@
         <v>24</v>
       </c>
       <c r="D34" t="s">
-        <v>9</v>
+        <v>54</v>
       </c>
       <c r="E34" t="s">
-        <v>54</v>
+        <v>10</v>
       </c>
       <c r="F34" t="s">
         <v>11</v>
@@ -5097,10 +5097,10 @@
         <v>15</v>
       </c>
       <c r="D42" t="s">
+        <v>9</v>
+      </c>
+      <c r="E42" t="s">
         <v>36</v>
-      </c>
-      <c r="E42" t="s">
-        <v>10</v>
       </c>
       <c r="F42" t="s">
         <v>11</v>
@@ -5137,10 +5137,10 @@
         <v>24</v>
       </c>
       <c r="D44" t="s">
+        <v>9</v>
+      </c>
+      <c r="E44" t="s">
         <v>36</v>
-      </c>
-      <c r="E44" t="s">
-        <v>10</v>
       </c>
       <c r="F44" t="s">
         <v>11</v>
@@ -5157,10 +5157,10 @@
         <v>24</v>
       </c>
       <c r="D45" t="s">
+        <v>9</v>
+      </c>
+      <c r="E45" t="s">
         <v>30</v>
-      </c>
-      <c r="E45" t="s">
-        <v>10</v>
       </c>
       <c r="F45" t="s">
         <v>11</v>
@@ -5217,10 +5217,10 @@
         <v>15</v>
       </c>
       <c r="D48" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="E48" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="F48" t="s">
         <v>69</v>
@@ -5257,10 +5257,10 @@
         <v>15</v>
       </c>
       <c r="D50" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="E50" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="F50" t="s">
         <v>69</v>
@@ -5397,10 +5397,10 @@
         <v>24</v>
       </c>
       <c r="D57" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="E57" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="F57" t="s">
         <v>69</v>
@@ -5477,10 +5477,10 @@
         <v>15</v>
       </c>
       <c r="D61" t="s">
-        <v>67</v>
+        <v>88</v>
       </c>
       <c r="E61" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
       <c r="F61" t="s">
         <v>69</v>
@@ -5497,10 +5497,10 @@
         <v>24</v>
       </c>
       <c r="D62" t="s">
-        <v>67</v>
+        <v>88</v>
       </c>
       <c r="E62" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
       <c r="F62" t="s">
         <v>69</v>
@@ -5517,10 +5517,10 @@
         <v>24</v>
       </c>
       <c r="D63" t="s">
+        <v>67</v>
+      </c>
+      <c r="E63" t="s">
         <v>91</v>
-      </c>
-      <c r="E63" t="s">
-        <v>68</v>
       </c>
       <c r="F63" t="s">
         <v>69</v>
@@ -5537,10 +5537,10 @@
         <v>24</v>
       </c>
       <c r="D64" t="s">
+        <v>67</v>
+      </c>
+      <c r="E64" t="s">
         <v>93</v>
-      </c>
-      <c r="E64" t="s">
-        <v>68</v>
       </c>
       <c r="F64" t="s">
         <v>69</v>
@@ -5557,10 +5557,10 @@
         <v>24</v>
       </c>
       <c r="D65" t="s">
-        <v>67</v>
+        <v>95</v>
       </c>
       <c r="E65" t="s">
-        <v>95</v>
+        <v>68</v>
       </c>
       <c r="F65" t="s">
         <v>69</v>
@@ -5597,10 +5597,10 @@
         <v>15</v>
       </c>
       <c r="D67" t="s">
+        <v>98</v>
+      </c>
+      <c r="E67" t="s">
         <v>93</v>
-      </c>
-      <c r="E67" t="s">
-        <v>98</v>
       </c>
       <c r="F67" t="s">
         <v>69</v>
@@ -5617,10 +5617,10 @@
         <v>24</v>
       </c>
       <c r="D68" t="s">
-        <v>67</v>
+        <v>100</v>
       </c>
       <c r="E68" t="s">
-        <v>100</v>
+        <v>68</v>
       </c>
       <c r="F68" t="s">
         <v>69</v>
@@ -5677,10 +5677,10 @@
         <v>15</v>
       </c>
       <c r="D71" t="s">
-        <v>67</v>
+        <v>104</v>
       </c>
       <c r="E71" t="s">
-        <v>104</v>
+        <v>68</v>
       </c>
       <c r="F71" t="s">
         <v>69</v>
@@ -5737,10 +5737,10 @@
         <v>15</v>
       </c>
       <c r="D74" t="s">
-        <v>67</v>
+        <v>108</v>
       </c>
       <c r="E74" t="s">
-        <v>108</v>
+        <v>68</v>
       </c>
       <c r="F74" t="s">
         <v>69</v>
@@ -5857,10 +5857,10 @@
         <v>24</v>
       </c>
       <c r="D80" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="E80" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="F80" t="s">
         <v>69</v>
@@ -6117,10 +6117,10 @@
         <v>15</v>
       </c>
       <c r="D93" t="s">
-        <v>67</v>
+        <v>129</v>
       </c>
       <c r="E93" t="s">
-        <v>129</v>
+        <v>68</v>
       </c>
       <c r="F93" t="s">
         <v>69</v>
@@ -6157,10 +6157,10 @@
         <v>24</v>
       </c>
       <c r="D95" t="s">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="E95" t="s">
-        <v>132</v>
+        <v>68</v>
       </c>
       <c r="F95" t="s">
         <v>69</v>
@@ -6177,10 +6177,10 @@
         <v>24</v>
       </c>
       <c r="D96" t="s">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="E96" t="s">
-        <v>132</v>
+        <v>68</v>
       </c>
       <c r="F96" t="s">
         <v>69</v>
@@ -6357,10 +6357,10 @@
         <v>24</v>
       </c>
       <c r="D105" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="E105" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="F105" t="s">
         <v>137</v>
@@ -6517,10 +6517,10 @@
         <v>24</v>
       </c>
       <c r="D113" t="s">
-        <v>135</v>
+        <v>155</v>
       </c>
       <c r="E113" t="s">
-        <v>155</v>
+        <v>136</v>
       </c>
       <c r="F113" t="s">
         <v>137</v>
@@ -6697,10 +6697,10 @@
         <v>19</v>
       </c>
       <c r="D122" t="s">
-        <v>162</v>
+        <v>135</v>
       </c>
       <c r="E122" t="s">
-        <v>136</v>
+        <v>163</v>
       </c>
       <c r="F122" t="s">
         <v>137</v>
@@ -6717,10 +6717,10 @@
         <v>15</v>
       </c>
       <c r="D123" t="s">
-        <v>159</v>
+        <v>135</v>
       </c>
       <c r="E123" t="s">
-        <v>136</v>
+        <v>160</v>
       </c>
       <c r="F123" t="s">
         <v>137</v>
@@ -6937,10 +6937,10 @@
         <v>24</v>
       </c>
       <c r="D134" t="s">
-        <v>159</v>
+        <v>183</v>
       </c>
       <c r="E134" t="s">
-        <v>183</v>
+        <v>160</v>
       </c>
       <c r="F134" t="s">
         <v>137</v>
@@ -6977,10 +6977,10 @@
         <v>24</v>
       </c>
       <c r="D136" t="s">
-        <v>159</v>
+        <v>186</v>
       </c>
       <c r="E136" t="s">
-        <v>186</v>
+        <v>160</v>
       </c>
       <c r="F136" t="s">
         <v>137</v>
@@ -7397,10 +7397,10 @@
         <v>24</v>
       </c>
       <c r="D157" t="s">
-        <v>195</v>
+        <v>212</v>
       </c>
       <c r="E157" t="s">
-        <v>213</v>
+        <v>196</v>
       </c>
       <c r="F157" t="s">
         <v>197</v>
@@ -7477,10 +7477,10 @@
         <v>24</v>
       </c>
       <c r="D161" t="s">
+        <v>195</v>
+      </c>
+      <c r="E161" t="s">
         <v>219</v>
-      </c>
-      <c r="E161" t="s">
-        <v>196</v>
       </c>
       <c r="F161" t="s">
         <v>197</v>
@@ -7717,10 +7717,10 @@
         <v>15</v>
       </c>
       <c r="D173" t="s">
-        <v>195</v>
+        <v>236</v>
       </c>
       <c r="E173" t="s">
-        <v>236</v>
+        <v>196</v>
       </c>
       <c r="F173" t="s">
         <v>197</v>
@@ -7737,10 +7737,10 @@
         <v>15</v>
       </c>
       <c r="D174" t="s">
+        <v>236</v>
+      </c>
+      <c r="E174" t="s">
         <v>238</v>
-      </c>
-      <c r="E174" t="s">
-        <v>236</v>
       </c>
       <c r="F174" t="s">
         <v>197</v>
@@ -7917,10 +7917,10 @@
         <v>15</v>
       </c>
       <c r="D183" t="s">
-        <v>195</v>
+        <v>250</v>
       </c>
       <c r="E183" t="s">
-        <v>250</v>
+        <v>196</v>
       </c>
       <c r="F183" t="s">
         <v>197</v>
@@ -8017,10 +8017,10 @@
         <v>24</v>
       </c>
       <c r="D188" t="s">
-        <v>195</v>
+        <v>256</v>
       </c>
       <c r="E188" t="s">
-        <v>256</v>
+        <v>196</v>
       </c>
       <c r="F188" t="s">
         <v>197</v>
@@ -8057,10 +8057,10 @@
         <v>13</v>
       </c>
       <c r="D190" t="s">
+        <v>256</v>
+      </c>
+      <c r="E190" t="s">
         <v>259</v>
-      </c>
-      <c r="E190" t="s">
-        <v>256</v>
       </c>
       <c r="F190" t="s">
         <v>197</v>
@@ -8137,10 +8137,10 @@
         <v>19</v>
       </c>
       <c r="D194" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="E194" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="F194" t="s">
         <v>265</v>
@@ -8157,10 +8157,10 @@
         <v>13</v>
       </c>
       <c r="D195" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="E195" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="F195" t="s">
         <v>265</v>
@@ -8177,10 +8177,10 @@
         <v>19</v>
       </c>
       <c r="D196" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="E196" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="F196" t="s">
         <v>265</v>
@@ -8197,10 +8197,10 @@
         <v>19</v>
       </c>
       <c r="D197" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="E197" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="F197" t="s">
         <v>265</v>
@@ -8217,10 +8217,10 @@
         <v>13</v>
       </c>
       <c r="D198" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="E198" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="F198" t="s">
         <v>265</v>
@@ -8237,10 +8237,10 @@
         <v>19</v>
       </c>
       <c r="D199" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="E199" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="F199" t="s">
         <v>265</v>
@@ -8257,10 +8257,10 @@
         <v>19</v>
       </c>
       <c r="D200" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="E200" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="F200" t="s">
         <v>265</v>
@@ -8277,10 +8277,10 @@
         <v>19</v>
       </c>
       <c r="D201" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="E201" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="F201" t="s">
         <v>265</v>
@@ -8297,10 +8297,10 @@
         <v>19</v>
       </c>
       <c r="D202" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="E202" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="F202" t="s">
         <v>265</v>
@@ -8317,10 +8317,10 @@
         <v>19</v>
       </c>
       <c r="D203" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="E203" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="F203" t="s">
         <v>265</v>
@@ -8337,10 +8337,10 @@
         <v>13</v>
       </c>
       <c r="D204" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="E204" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="F204" t="s">
         <v>265</v>
@@ -8357,10 +8357,10 @@
         <v>19</v>
       </c>
       <c r="D205" t="s">
-        <v>263</v>
+        <v>279</v>
       </c>
       <c r="E205" t="s">
-        <v>279</v>
+        <v>264</v>
       </c>
       <c r="F205" t="s">
         <v>265</v>
@@ -8377,10 +8377,10 @@
         <v>19</v>
       </c>
       <c r="D206" t="s">
-        <v>195</v>
+        <v>279</v>
       </c>
       <c r="E206" t="s">
-        <v>279</v>
+        <v>196</v>
       </c>
       <c r="F206" t="s">
         <v>265</v>
@@ -8417,10 +8417,10 @@
         <v>19</v>
       </c>
       <c r="D208" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="E208" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="F208" t="s">
         <v>265</v>
@@ -8437,10 +8437,10 @@
         <v>19</v>
       </c>
       <c r="D209" t="s">
-        <v>263</v>
+        <v>279</v>
       </c>
       <c r="E209" t="s">
-        <v>279</v>
+        <v>264</v>
       </c>
       <c r="F209" t="s">
         <v>265</v>
@@ -8457,10 +8457,10 @@
         <v>19</v>
       </c>
       <c r="D210" t="s">
-        <v>195</v>
+        <v>279</v>
       </c>
       <c r="E210" t="s">
-        <v>279</v>
+        <v>196</v>
       </c>
       <c r="F210" t="s">
         <v>265</v>
@@ -8497,10 +8497,10 @@
         <v>19</v>
       </c>
       <c r="D212" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="E212" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="F212" t="s">
         <v>265</v>
@@ -8537,10 +8537,10 @@
         <v>19</v>
       </c>
       <c r="D214" t="s">
-        <v>263</v>
+        <v>279</v>
       </c>
       <c r="E214" t="s">
-        <v>279</v>
+        <v>264</v>
       </c>
       <c r="F214" t="s">
         <v>265</v>
@@ -8557,10 +8557,10 @@
         <v>19</v>
       </c>
       <c r="D215" t="s">
-        <v>195</v>
+        <v>279</v>
       </c>
       <c r="E215" t="s">
-        <v>279</v>
+        <v>196</v>
       </c>
       <c r="F215" t="s">
         <v>265</v>
@@ -8577,10 +8577,10 @@
         <v>19</v>
       </c>
       <c r="D216" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="E216" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="F216" t="s">
         <v>265</v>
@@ -8597,10 +8597,10 @@
         <v>24</v>
       </c>
       <c r="D217" t="s">
-        <v>263</v>
+        <v>298</v>
       </c>
       <c r="E217" t="s">
-        <v>298</v>
+        <v>264</v>
       </c>
       <c r="F217" t="s">
         <v>265</v>
@@ -8637,10 +8637,10 @@
         <v>19</v>
       </c>
       <c r="D219" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="E219" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="F219" t="s">
         <v>265</v>
@@ -8657,10 +8657,10 @@
         <v>24</v>
       </c>
       <c r="D220" t="s">
-        <v>224</v>
+        <v>267</v>
       </c>
       <c r="E220" t="s">
-        <v>267</v>
+        <v>225</v>
       </c>
       <c r="F220" t="s">
         <v>265</v>
@@ -8677,10 +8677,10 @@
         <v>24</v>
       </c>
       <c r="D221" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="E221" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="F221" t="s">
         <v>265</v>
@@ -8697,10 +8697,10 @@
         <v>19</v>
       </c>
       <c r="D222" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="E222" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="F222" t="s">
         <v>265</v>
@@ -8717,10 +8717,10 @@
         <v>19</v>
       </c>
       <c r="D223" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="E223" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="F223" t="s">
         <v>265</v>
@@ -8737,10 +8737,10 @@
         <v>19</v>
       </c>
       <c r="D224" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="E224" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="F224" t="s">
         <v>265</v>
@@ -8757,10 +8757,10 @@
         <v>15</v>
       </c>
       <c r="D225" t="s">
-        <v>263</v>
+        <v>309</v>
       </c>
       <c r="E225" t="s">
-        <v>309</v>
+        <v>264</v>
       </c>
       <c r="F225" t="s">
         <v>265</v>
@@ -8777,10 +8777,10 @@
         <v>15</v>
       </c>
       <c r="D226" t="s">
-        <v>263</v>
+        <v>311</v>
       </c>
       <c r="E226" t="s">
-        <v>311</v>
+        <v>264</v>
       </c>
       <c r="F226" t="s">
         <v>265</v>
@@ -8797,10 +8797,10 @@
         <v>19</v>
       </c>
       <c r="D227" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="E227" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="F227" t="s">
         <v>265</v>
@@ -8817,10 +8817,10 @@
         <v>19</v>
       </c>
       <c r="D228" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="E228" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="F228" t="s">
         <v>265</v>
@@ -8837,10 +8837,10 @@
         <v>24</v>
       </c>
       <c r="D229" t="s">
-        <v>263</v>
+        <v>311</v>
       </c>
       <c r="E229" t="s">
-        <v>311</v>
+        <v>264</v>
       </c>
       <c r="F229" t="s">
         <v>265</v>
@@ -8857,10 +8857,10 @@
         <v>15</v>
       </c>
       <c r="D230" t="s">
-        <v>263</v>
+        <v>311</v>
       </c>
       <c r="E230" t="s">
-        <v>311</v>
+        <v>264</v>
       </c>
       <c r="F230" t="s">
         <v>265</v>
@@ -8877,10 +8877,10 @@
         <v>19</v>
       </c>
       <c r="D231" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="E231" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="F231" t="s">
         <v>265</v>
@@ -8897,10 +8897,10 @@
         <v>19</v>
       </c>
       <c r="D232" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="E232" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="F232" t="s">
         <v>265</v>
@@ -8917,10 +8917,10 @@
         <v>13</v>
       </c>
       <c r="D233" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="E233" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="F233" t="s">
         <v>265</v>
@@ -8937,10 +8937,10 @@
         <v>13</v>
       </c>
       <c r="D234" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="E234" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="F234" t="s">
         <v>265</v>
@@ -8957,10 +8957,10 @@
         <v>19</v>
       </c>
       <c r="D235" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="E235" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="F235" t="s">
         <v>265</v>
@@ -8977,10 +8977,10 @@
         <v>19</v>
       </c>
       <c r="D236" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="E236" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="F236" t="s">
         <v>265</v>
@@ -8997,10 +8997,10 @@
         <v>13</v>
       </c>
       <c r="D237" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="E237" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="F237" t="s">
         <v>265</v>
@@ -9017,10 +9017,10 @@
         <v>19</v>
       </c>
       <c r="D238" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="E238" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="F238" t="s">
         <v>265</v>
@@ -9037,10 +9037,10 @@
         <v>19</v>
       </c>
       <c r="D239" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="E239" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="F239" t="s">
         <v>265</v>
@@ -9057,10 +9057,10 @@
         <v>13</v>
       </c>
       <c r="D240" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="E240" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="F240" t="s">
         <v>265</v>
@@ -9077,10 +9077,10 @@
         <v>19</v>
       </c>
       <c r="D241" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="E241" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="F241" t="s">
         <v>265</v>
@@ -9097,10 +9097,10 @@
         <v>19</v>
       </c>
       <c r="D242" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="E242" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="F242" t="s">
         <v>265</v>
@@ -9117,10 +9117,10 @@
         <v>19</v>
       </c>
       <c r="D243" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="E243" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="F243" t="s">
         <v>265</v>
@@ -9137,10 +9137,10 @@
         <v>19</v>
       </c>
       <c r="D244" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="E244" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="F244" t="s">
         <v>265</v>
@@ -9177,10 +9177,10 @@
         <v>15</v>
       </c>
       <c r="D246" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="E246" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="F246" t="s">
         <v>333</v>
@@ -9217,10 +9217,10 @@
         <v>15</v>
       </c>
       <c r="D248" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="E248" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="F248" t="s">
         <v>333</v>
@@ -9297,10 +9297,10 @@
         <v>15</v>
       </c>
       <c r="D252" t="s">
-        <v>331</v>
+        <v>342</v>
       </c>
       <c r="E252" t="s">
-        <v>342</v>
+        <v>332</v>
       </c>
       <c r="F252" t="s">
         <v>333</v>
@@ -9337,10 +9337,10 @@
         <v>19</v>
       </c>
       <c r="D254" t="s">
+        <v>345</v>
+      </c>
+      <c r="E254" t="s">
         <v>267</v>
-      </c>
-      <c r="E254" t="s">
-        <v>345</v>
       </c>
       <c r="F254" t="s">
         <v>333</v>
@@ -9397,10 +9397,10 @@
         <v>15</v>
       </c>
       <c r="D257" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="E257" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="F257" t="s">
         <v>333</v>
@@ -9417,10 +9417,10 @@
         <v>15</v>
       </c>
       <c r="D258" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="E258" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="F258" t="s">
         <v>333</v>
@@ -9437,10 +9437,10 @@
         <v>19</v>
       </c>
       <c r="D259" t="s">
-        <v>331</v>
+        <v>351</v>
       </c>
       <c r="E259" t="s">
-        <v>351</v>
+        <v>332</v>
       </c>
       <c r="F259" t="s">
         <v>333</v>
@@ -9517,10 +9517,10 @@
         <v>15</v>
       </c>
       <c r="D263" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="E263" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="F263" t="s">
         <v>333</v>
@@ -9537,10 +9537,10 @@
         <v>15</v>
       </c>
       <c r="D264" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="E264" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="F264" t="s">
         <v>333</v>
@@ -9577,10 +9577,10 @@
         <v>15</v>
       </c>
       <c r="D266" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="E266" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="F266" t="s">
         <v>333</v>
@@ -9617,10 +9617,10 @@
         <v>15</v>
       </c>
       <c r="D268" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="E268" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="F268" t="s">
         <v>333</v>
@@ -9637,10 +9637,10 @@
         <v>15</v>
       </c>
       <c r="D269" t="s">
-        <v>331</v>
+        <v>351</v>
       </c>
       <c r="E269" t="s">
-        <v>351</v>
+        <v>332</v>
       </c>
       <c r="F269" t="s">
         <v>333</v>
@@ -9657,10 +9657,10 @@
         <v>15</v>
       </c>
       <c r="D270" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="E270" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="F270" t="s">
         <v>333</v>
@@ -9677,10 +9677,10 @@
         <v>15</v>
       </c>
       <c r="D271" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="E271" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="F271" t="s">
         <v>333</v>
@@ -9717,10 +9717,10 @@
         <v>15</v>
       </c>
       <c r="D273" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="E273" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="F273" t="s">
         <v>333</v>
@@ -9757,10 +9757,10 @@
         <v>15</v>
       </c>
       <c r="D275" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="E275" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="F275" t="s">
         <v>333</v>
@@ -9777,10 +9777,10 @@
         <v>15</v>
       </c>
       <c r="D276" t="s">
-        <v>331</v>
+        <v>371</v>
       </c>
       <c r="E276" t="s">
-        <v>371</v>
+        <v>332</v>
       </c>
       <c r="F276" t="s">
         <v>333</v>
@@ -9817,10 +9817,10 @@
         <v>15</v>
       </c>
       <c r="D278" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="E278" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="F278" t="s">
         <v>333</v>
@@ -9857,10 +9857,10 @@
         <v>15</v>
       </c>
       <c r="D280" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="E280" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="F280" t="s">
         <v>333</v>
@@ -9917,10 +9917,10 @@
         <v>15</v>
       </c>
       <c r="D283" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="E283" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="F283" t="s">
         <v>333</v>
@@ -10017,10 +10017,10 @@
         <v>15</v>
       </c>
       <c r="D288" t="s">
-        <v>331</v>
+        <v>371</v>
       </c>
       <c r="E288" t="s">
-        <v>371</v>
+        <v>332</v>
       </c>
       <c r="F288" t="s">
         <v>333</v>
@@ -10037,10 +10037,10 @@
         <v>15</v>
       </c>
       <c r="D289" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="E289" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="F289" t="s">
         <v>333</v>
@@ -10097,10 +10097,10 @@
         <v>15</v>
       </c>
       <c r="D292" t="s">
-        <v>331</v>
+        <v>371</v>
       </c>
       <c r="E292" t="s">
-        <v>371</v>
+        <v>332</v>
       </c>
       <c r="F292" t="s">
         <v>333</v>
@@ -10117,10 +10117,10 @@
         <v>15</v>
       </c>
       <c r="D293" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="E293" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="F293" t="s">
         <v>333</v>
@@ -10257,10 +10257,10 @@
         <v>15</v>
       </c>
       <c r="D300" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="E300" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="F300" t="s">
         <v>333</v>
@@ -10277,10 +10277,10 @@
         <v>15</v>
       </c>
       <c r="D301" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="E301" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="F301" t="s">
         <v>333</v>
@@ -10297,10 +10297,10 @@
         <v>15</v>
       </c>
       <c r="D302" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="E302" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="F302" t="s">
         <v>333</v>
@@ -10337,10 +10337,10 @@
         <v>15</v>
       </c>
       <c r="D304" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="E304" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="F304" t="s">
         <v>333</v>
@@ -10397,10 +10397,10 @@
         <v>15</v>
       </c>
       <c r="D307" t="s">
-        <v>355</v>
+        <v>407</v>
       </c>
       <c r="E307" t="s">
-        <v>407</v>
+        <v>356</v>
       </c>
       <c r="F307" t="s">
         <v>333</v>
@@ -10417,10 +10417,10 @@
         <v>15</v>
       </c>
       <c r="D308" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="E308" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="F308" t="s">
         <v>333</v>
@@ -10717,10 +10717,10 @@
         <v>15</v>
       </c>
       <c r="D323" t="s">
-        <v>411</v>
+        <v>427</v>
       </c>
       <c r="E323" t="s">
-        <v>427</v>
+        <v>412</v>
       </c>
       <c r="F323" t="s">
         <v>413</v>
@@ -10757,10 +10757,10 @@
         <v>24</v>
       </c>
       <c r="D325" t="s">
+        <v>411</v>
+      </c>
+      <c r="E325" t="s">
         <v>430</v>
-      </c>
-      <c r="E325" t="s">
-        <v>412</v>
       </c>
       <c r="F325" t="s">
         <v>413</v>
@@ -10877,10 +10877,10 @@
         <v>19</v>
       </c>
       <c r="D331" t="s">
+        <v>411</v>
+      </c>
+      <c r="E331" t="s">
         <v>437</v>
-      </c>
-      <c r="E331" t="s">
-        <v>412</v>
       </c>
       <c r="F331" t="s">
         <v>413</v>
@@ -11137,10 +11137,10 @@
         <v>24</v>
       </c>
       <c r="D344" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="E344" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="F344" t="s">
         <v>413</v>
@@ -11177,10 +11177,10 @@
         <v>15</v>
       </c>
       <c r="D346" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="E346" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="F346" t="s">
         <v>457</v>
@@ -11377,10 +11377,10 @@
         <v>15</v>
       </c>
       <c r="D356" t="s">
-        <v>455</v>
+        <v>470</v>
       </c>
       <c r="E356" t="s">
-        <v>470</v>
+        <v>456</v>
       </c>
       <c r="F356" t="s">
         <v>457</v>
@@ -11577,10 +11577,10 @@
         <v>15</v>
       </c>
       <c r="D366" t="s">
-        <v>455</v>
+        <v>481</v>
       </c>
       <c r="E366" t="s">
-        <v>481</v>
+        <v>456</v>
       </c>
       <c r="F366" t="s">
         <v>457</v>
@@ -11597,10 +11597,10 @@
         <v>13</v>
       </c>
       <c r="D367" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="E367" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="F367" t="s">
         <v>457</v>
@@ -11677,10 +11677,10 @@
         <v>19</v>
       </c>
       <c r="D371" t="s">
+        <v>455</v>
+      </c>
+      <c r="E371" t="s">
         <v>487</v>
-      </c>
-      <c r="E371" t="s">
-        <v>456</v>
       </c>
       <c r="F371" t="s">
         <v>457</v>
@@ -11857,10 +11857,10 @@
         <v>13</v>
       </c>
       <c r="D380" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="E380" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="F380" t="s">
         <v>499</v>
@@ -11977,10 +11977,10 @@
         <v>15</v>
       </c>
       <c r="D386" t="s">
-        <v>497</v>
+        <v>509</v>
       </c>
       <c r="E386" t="s">
-        <v>509</v>
+        <v>498</v>
       </c>
       <c r="F386" t="s">
         <v>499</v>
@@ -11997,10 +11997,10 @@
         <v>19</v>
       </c>
       <c r="D387" t="s">
-        <v>497</v>
+        <v>511</v>
       </c>
       <c r="E387" t="s">
-        <v>511</v>
+        <v>498</v>
       </c>
       <c r="F387" t="s">
         <v>499</v>
@@ -12117,10 +12117,10 @@
         <v>15</v>
       </c>
       <c r="D393" t="s">
-        <v>497</v>
+        <v>520</v>
       </c>
       <c r="E393" t="s">
-        <v>520</v>
+        <v>498</v>
       </c>
       <c r="F393" t="s">
         <v>499</v>
@@ -12397,10 +12397,10 @@
         <v>19</v>
       </c>
       <c r="D407" t="s">
-        <v>497</v>
+        <v>543</v>
       </c>
       <c r="E407" t="s">
-        <v>543</v>
+        <v>498</v>
       </c>
       <c r="F407" t="s">
         <v>499</v>
@@ -12637,10 +12637,10 @@
         <v>24</v>
       </c>
       <c r="D419" t="s">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="E419" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="F419" t="s">
         <v>556</v>
@@ -12677,10 +12677,10 @@
         <v>19</v>
       </c>
       <c r="D421" t="s">
-        <v>554</v>
+        <v>562</v>
       </c>
       <c r="E421" t="s">
-        <v>562</v>
+        <v>555</v>
       </c>
       <c r="F421" t="s">
         <v>556</v>
@@ -12917,10 +12917,10 @@
         <v>24</v>
       </c>
       <c r="D433" t="s">
-        <v>554</v>
+        <v>579</v>
       </c>
       <c r="E433" t="s">
-        <v>579</v>
+        <v>555</v>
       </c>
       <c r="F433" t="s">
         <v>556</v>
@@ -12977,10 +12977,10 @@
         <v>24</v>
       </c>
       <c r="D436" t="s">
-        <v>554</v>
+        <v>583</v>
       </c>
       <c r="E436" t="s">
-        <v>583</v>
+        <v>555</v>
       </c>
       <c r="F436" t="s">
         <v>556</v>
@@ -12997,10 +12997,10 @@
         <v>19</v>
       </c>
       <c r="D437" t="s">
-        <v>554</v>
+        <v>585</v>
       </c>
       <c r="E437" t="s">
-        <v>585</v>
+        <v>555</v>
       </c>
       <c r="F437" t="s">
         <v>556</v>
@@ -13557,10 +13557,10 @@
         <v>24</v>
       </c>
       <c r="D465" t="s">
-        <v>609</v>
+        <v>624</v>
       </c>
       <c r="E465" t="s">
-        <v>624</v>
+        <v>610</v>
       </c>
       <c r="F465" t="s">
         <v>611</v>
@@ -13577,10 +13577,10 @@
         <v>24</v>
       </c>
       <c r="D466" t="s">
-        <v>621</v>
+        <v>626</v>
       </c>
       <c r="E466" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="F466" t="s">
         <v>611</v>
@@ -13717,10 +13717,10 @@
         <v>24</v>
       </c>
       <c r="D473" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="E473" t="s">
-        <v>638</v>
+        <v>622</v>
       </c>
       <c r="F473" t="s">
         <v>611</v>
@@ -14017,10 +14017,10 @@
         <v>608</v>
       </c>
       <c r="D488" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="E488" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="F488" t="s">
         <v>655</v>
@@ -14097,10 +14097,10 @@
         <v>19</v>
       </c>
       <c r="D492" t="s">
+        <v>653</v>
+      </c>
+      <c r="E492" t="s">
         <v>662</v>
-      </c>
-      <c r="E492" t="s">
-        <v>654</v>
       </c>
       <c r="F492" t="s">
         <v>655</v>
@@ -14137,10 +14137,10 @@
         <v>13</v>
       </c>
       <c r="D494" t="s">
+        <v>632</v>
+      </c>
+      <c r="E494" t="s">
         <v>665</v>
-      </c>
-      <c r="E494" t="s">
-        <v>633</v>
       </c>
       <c r="F494" t="s">
         <v>655</v>
@@ -14157,10 +14157,10 @@
         <v>15</v>
       </c>
       <c r="D495" t="s">
+        <v>632</v>
+      </c>
+      <c r="E495" t="s">
         <v>665</v>
-      </c>
-      <c r="E495" t="s">
-        <v>633</v>
       </c>
       <c r="F495" t="s">
         <v>655</v>
@@ -14217,10 +14217,10 @@
         <v>608</v>
       </c>
       <c r="D498" t="s">
-        <v>653</v>
+        <v>670</v>
       </c>
       <c r="E498" t="s">
-        <v>670</v>
+        <v>654</v>
       </c>
       <c r="F498" t="s">
         <v>655</v>
@@ -14297,10 +14297,10 @@
         <v>19</v>
       </c>
       <c r="D502" t="s">
-        <v>653</v>
+        <v>675</v>
       </c>
       <c r="E502" t="s">
-        <v>675</v>
+        <v>654</v>
       </c>
       <c r="F502" t="s">
         <v>655</v>
@@ -14437,10 +14437,10 @@
         <v>19</v>
       </c>
       <c r="D509" t="s">
+        <v>684</v>
+      </c>
+      <c r="E509" t="s">
         <v>687</v>
-      </c>
-      <c r="E509" t="s">
-        <v>685</v>
       </c>
       <c r="F509" t="s">
         <v>655</v>
@@ -14497,10 +14497,10 @@
         <v>15</v>
       </c>
       <c r="D512" t="s">
-        <v>653</v>
+        <v>693</v>
       </c>
       <c r="E512" t="s">
-        <v>693</v>
+        <v>654</v>
       </c>
       <c r="F512" t="s">
         <v>655</v>
@@ -14517,10 +14517,10 @@
         <v>19</v>
       </c>
       <c r="D513" t="s">
+        <v>653</v>
+      </c>
+      <c r="E513" t="s">
         <v>695</v>
-      </c>
-      <c r="E513" t="s">
-        <v>654</v>
       </c>
       <c r="F513" t="s">
         <v>655</v>
@@ -14677,10 +14677,10 @@
         <v>19</v>
       </c>
       <c r="D521" t="s">
-        <v>653</v>
+        <v>704</v>
       </c>
       <c r="E521" t="s">
-        <v>704</v>
+        <v>654</v>
       </c>
       <c r="F521" t="s">
         <v>655</v>
@@ -14697,10 +14697,10 @@
         <v>13</v>
       </c>
       <c r="D522" t="s">
-        <v>653</v>
+        <v>706</v>
       </c>
       <c r="E522" t="s">
-        <v>706</v>
+        <v>654</v>
       </c>
       <c r="F522" t="s">
         <v>655</v>
@@ -14717,10 +14717,10 @@
         <v>24</v>
       </c>
       <c r="D523" t="s">
-        <v>653</v>
+        <v>708</v>
       </c>
       <c r="E523" t="s">
-        <v>708</v>
+        <v>654</v>
       </c>
       <c r="F523" t="s">
         <v>655</v>
@@ -14757,10 +14757,10 @@
         <v>711</v>
       </c>
       <c r="D525" t="s">
+        <v>657</v>
+      </c>
+      <c r="E525" t="s">
         <v>712</v>
-      </c>
-      <c r="E525" t="s">
-        <v>657</v>
       </c>
       <c r="F525" t="s">
         <v>713</v>
@@ -14777,10 +14777,10 @@
         <v>711</v>
       </c>
       <c r="D526" t="s">
+        <v>657</v>
+      </c>
+      <c r="E526" t="s">
         <v>712</v>
-      </c>
-      <c r="E526" t="s">
-        <v>657</v>
       </c>
       <c r="F526" t="s">
         <v>713</v>
@@ -14797,10 +14797,10 @@
         <v>711</v>
       </c>
       <c r="D527" t="s">
+        <v>657</v>
+      </c>
+      <c r="E527" t="s">
         <v>712</v>
-      </c>
-      <c r="E527" t="s">
-        <v>657</v>
       </c>
       <c r="F527" t="s">
         <v>713</v>
@@ -14817,10 +14817,10 @@
         <v>711</v>
       </c>
       <c r="D528" t="s">
+        <v>657</v>
+      </c>
+      <c r="E528" t="s">
         <v>712</v>
-      </c>
-      <c r="E528" t="s">
-        <v>657</v>
       </c>
       <c r="F528" t="s">
         <v>713</v>
@@ -14837,10 +14837,10 @@
         <v>15</v>
       </c>
       <c r="D529" t="s">
+        <v>718</v>
+      </c>
+      <c r="E529" t="s">
         <v>712</v>
-      </c>
-      <c r="E529" t="s">
-        <v>718</v>
       </c>
       <c r="F529" t="s">
         <v>713</v>
@@ -14857,10 +14857,10 @@
         <v>711</v>
       </c>
       <c r="D530" t="s">
+        <v>657</v>
+      </c>
+      <c r="E530" t="s">
         <v>720</v>
-      </c>
-      <c r="E530" t="s">
-        <v>657</v>
       </c>
       <c r="F530" t="s">
         <v>713</v>
@@ -14877,10 +14877,10 @@
         <v>711</v>
       </c>
       <c r="D531" t="s">
+        <v>657</v>
+      </c>
+      <c r="E531" t="s">
         <v>712</v>
-      </c>
-      <c r="E531" t="s">
-        <v>657</v>
       </c>
       <c r="F531" t="s">
         <v>713</v>
@@ -14897,10 +14897,10 @@
         <v>711</v>
       </c>
       <c r="D532" t="s">
+        <v>657</v>
+      </c>
+      <c r="E532" t="s">
         <v>712</v>
-      </c>
-      <c r="E532" t="s">
-        <v>657</v>
       </c>
       <c r="F532" t="s">
         <v>713</v>
@@ -14917,10 +14917,10 @@
         <v>711</v>
       </c>
       <c r="D533" t="s">
+        <v>657</v>
+      </c>
+      <c r="E533" t="s">
         <v>712</v>
-      </c>
-      <c r="E533" t="s">
-        <v>657</v>
       </c>
       <c r="F533" t="s">
         <v>713</v>
@@ -14937,10 +14937,10 @@
         <v>711</v>
       </c>
       <c r="D534" t="s">
+        <v>657</v>
+      </c>
+      <c r="E534" t="s">
         <v>712</v>
-      </c>
-      <c r="E534" t="s">
-        <v>657</v>
       </c>
       <c r="F534" t="s">
         <v>713</v>
@@ -14957,10 +14957,10 @@
         <v>711</v>
       </c>
       <c r="D535" t="s">
+        <v>657</v>
+      </c>
+      <c r="E535" t="s">
         <v>712</v>
-      </c>
-      <c r="E535" t="s">
-        <v>657</v>
       </c>
       <c r="F535" t="s">
         <v>713</v>
@@ -14977,10 +14977,10 @@
         <v>15</v>
       </c>
       <c r="D536" t="s">
+        <v>727</v>
+      </c>
+      <c r="E536" t="s">
         <v>712</v>
-      </c>
-      <c r="E536" t="s">
-        <v>727</v>
       </c>
       <c r="F536" t="s">
         <v>713</v>
@@ -14997,10 +14997,10 @@
         <v>15</v>
       </c>
       <c r="D537" t="s">
+        <v>729</v>
+      </c>
+      <c r="E537" t="s">
         <v>712</v>
-      </c>
-      <c r="E537" t="s">
-        <v>729</v>
       </c>
       <c r="F537" t="s">
         <v>713</v>
@@ -15017,10 +15017,10 @@
         <v>711</v>
       </c>
       <c r="D538" t="s">
+        <v>657</v>
+      </c>
+      <c r="E538" t="s">
         <v>712</v>
-      </c>
-      <c r="E538" t="s">
-        <v>657</v>
       </c>
       <c r="F538" t="s">
         <v>713</v>
@@ -15037,10 +15037,10 @@
         <v>711</v>
       </c>
       <c r="D539" t="s">
+        <v>657</v>
+      </c>
+      <c r="E539" t="s">
         <v>712</v>
-      </c>
-      <c r="E539" t="s">
-        <v>657</v>
       </c>
       <c r="F539" t="s">
         <v>713</v>
@@ -15057,10 +15057,10 @@
         <v>711</v>
       </c>
       <c r="D540" t="s">
-        <v>689</v>
+        <v>657</v>
       </c>
       <c r="E540" t="s">
-        <v>657</v>
+        <v>690</v>
       </c>
       <c r="F540" t="s">
         <v>713</v>
@@ -15077,10 +15077,10 @@
         <v>711</v>
       </c>
       <c r="D541" t="s">
+        <v>657</v>
+      </c>
+      <c r="E541" t="s">
         <v>712</v>
-      </c>
-      <c r="E541" t="s">
-        <v>657</v>
       </c>
       <c r="F541" t="s">
         <v>713</v>
@@ -15097,10 +15097,10 @@
         <v>711</v>
       </c>
       <c r="D542" t="s">
+        <v>657</v>
+      </c>
+      <c r="E542" t="s">
         <v>712</v>
-      </c>
-      <c r="E542" t="s">
-        <v>657</v>
       </c>
       <c r="F542" t="s">
         <v>713</v>
@@ -15117,10 +15117,10 @@
         <v>711</v>
       </c>
       <c r="D543" t="s">
+        <v>657</v>
+      </c>
+      <c r="E543" t="s">
         <v>712</v>
-      </c>
-      <c r="E543" t="s">
-        <v>657</v>
       </c>
       <c r="F543" t="s">
         <v>713</v>
@@ -15137,10 +15137,10 @@
         <v>711</v>
       </c>
       <c r="D544" t="s">
+        <v>657</v>
+      </c>
+      <c r="E544" t="s">
         <v>712</v>
-      </c>
-      <c r="E544" t="s">
-        <v>657</v>
       </c>
       <c r="F544" t="s">
         <v>713</v>
@@ -15157,10 +15157,10 @@
         <v>13</v>
       </c>
       <c r="D545" t="s">
+        <v>657</v>
+      </c>
+      <c r="E545" t="s">
         <v>738</v>
-      </c>
-      <c r="E545" t="s">
-        <v>657</v>
       </c>
       <c r="F545" t="s">
         <v>713</v>
@@ -15177,10 +15177,10 @@
         <v>711</v>
       </c>
       <c r="D546" t="s">
+        <v>657</v>
+      </c>
+      <c r="E546" t="s">
         <v>712</v>
-      </c>
-      <c r="E546" t="s">
-        <v>657</v>
       </c>
       <c r="F546" t="s">
         <v>713</v>
@@ -15197,10 +15197,10 @@
         <v>15</v>
       </c>
       <c r="D547" t="s">
+        <v>657</v>
+      </c>
+      <c r="E547" t="s">
         <v>712</v>
-      </c>
-      <c r="E547" t="s">
-        <v>657</v>
       </c>
       <c r="F547" t="s">
         <v>713</v>
@@ -15237,10 +15237,10 @@
         <v>711</v>
       </c>
       <c r="D549" t="s">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="E549" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
       <c r="F549" t="s">
         <v>744</v>
@@ -15257,10 +15257,10 @@
         <v>711</v>
       </c>
       <c r="D550" t="s">
-        <v>742</v>
+        <v>748</v>
       </c>
       <c r="E550" t="s">
-        <v>748</v>
+        <v>743</v>
       </c>
       <c r="F550" t="s">
         <v>744</v>
@@ -15337,10 +15337,10 @@
         <v>711</v>
       </c>
       <c r="D554" t="s">
+        <v>742</v>
+      </c>
+      <c r="E554" t="s">
         <v>753</v>
-      </c>
-      <c r="E554" t="s">
-        <v>743</v>
       </c>
       <c r="F554" t="s">
         <v>744</v>
@@ -15457,10 +15457,10 @@
         <v>711</v>
       </c>
       <c r="D560" t="s">
-        <v>742</v>
+        <v>762</v>
       </c>
       <c r="E560" t="s">
-        <v>762</v>
+        <v>743</v>
       </c>
       <c r="F560" t="s">
         <v>744</v>
@@ -15477,10 +15477,10 @@
         <v>711</v>
       </c>
       <c r="D561" t="s">
-        <v>742</v>
+        <v>762</v>
       </c>
       <c r="E561" t="s">
-        <v>762</v>
+        <v>743</v>
       </c>
       <c r="F561" t="s">
         <v>744</v>
@@ -15517,10 +15517,10 @@
         <v>15</v>
       </c>
       <c r="D563" t="s">
+        <v>742</v>
+      </c>
+      <c r="E563" t="s">
         <v>766</v>
-      </c>
-      <c r="E563" t="s">
-        <v>743</v>
       </c>
       <c r="F563" t="s">
         <v>744</v>
@@ -15717,10 +15717,10 @@
         <v>711</v>
       </c>
       <c r="D573" t="s">
+        <v>779</v>
+      </c>
+      <c r="E573" t="s">
         <v>712</v>
-      </c>
-      <c r="E573" t="s">
-        <v>779</v>
       </c>
       <c r="F573" t="s">
         <v>780</v>
@@ -15737,10 +15737,10 @@
         <v>711</v>
       </c>
       <c r="D574" t="s">
+        <v>779</v>
+      </c>
+      <c r="E574" t="s">
         <v>782</v>
-      </c>
-      <c r="E574" t="s">
-        <v>779</v>
       </c>
       <c r="F574" t="s">
         <v>780</v>
@@ -15757,10 +15757,10 @@
         <v>711</v>
       </c>
       <c r="D575" t="s">
+        <v>779</v>
+      </c>
+      <c r="E575" t="s">
         <v>782</v>
-      </c>
-      <c r="E575" t="s">
-        <v>779</v>
       </c>
       <c r="F575" t="s">
         <v>780</v>
@@ -15777,10 +15777,10 @@
         <v>711</v>
       </c>
       <c r="D576" t="s">
+        <v>779</v>
+      </c>
+      <c r="E576" t="s">
         <v>782</v>
-      </c>
-      <c r="E576" t="s">
-        <v>779</v>
       </c>
       <c r="F576" t="s">
         <v>780</v>
@@ -15797,10 +15797,10 @@
         <v>711</v>
       </c>
       <c r="D577" t="s">
-        <v>742</v>
+        <v>779</v>
       </c>
       <c r="E577" t="s">
-        <v>779</v>
+        <v>743</v>
       </c>
       <c r="F577" t="s">
         <v>780</v>
@@ -15817,10 +15817,10 @@
         <v>711</v>
       </c>
       <c r="D578" t="s">
+        <v>787</v>
+      </c>
+      <c r="E578" t="s">
         <v>782</v>
-      </c>
-      <c r="E578" t="s">
-        <v>787</v>
       </c>
       <c r="F578" t="s">
         <v>780</v>
@@ -15857,10 +15857,10 @@
         <v>711</v>
       </c>
       <c r="D580" t="s">
+        <v>792</v>
+      </c>
+      <c r="E580" t="s">
         <v>782</v>
-      </c>
-      <c r="E580" t="s">
-        <v>792</v>
       </c>
       <c r="F580" t="s">
         <v>780</v>
@@ -15877,10 +15877,10 @@
         <v>15</v>
       </c>
       <c r="D581" t="s">
+        <v>794</v>
+      </c>
+      <c r="E581" t="s">
         <v>782</v>
-      </c>
-      <c r="E581" t="s">
-        <v>794</v>
       </c>
       <c r="F581" t="s">
         <v>780</v>
@@ -15897,10 +15897,10 @@
         <v>15</v>
       </c>
       <c r="D582" t="s">
+        <v>779</v>
+      </c>
+      <c r="E582" t="s">
         <v>782</v>
-      </c>
-      <c r="E582" t="s">
-        <v>779</v>
       </c>
       <c r="F582" t="s">
         <v>780</v>
@@ -15957,10 +15957,10 @@
         <v>711</v>
       </c>
       <c r="D585" t="s">
+        <v>779</v>
+      </c>
+      <c r="E585" t="s">
         <v>782</v>
-      </c>
-      <c r="E585" t="s">
-        <v>779</v>
       </c>
       <c r="F585" t="s">
         <v>780</v>
@@ -15997,10 +15997,10 @@
         <v>13</v>
       </c>
       <c r="D587" t="s">
+        <v>807</v>
+      </c>
+      <c r="E587" t="s">
         <v>782</v>
-      </c>
-      <c r="E587" t="s">
-        <v>807</v>
       </c>
       <c r="F587" t="s">
         <v>780</v>
@@ -16017,10 +16017,10 @@
         <v>711</v>
       </c>
       <c r="D588" t="s">
+        <v>809</v>
+      </c>
+      <c r="E588" t="s">
         <v>782</v>
-      </c>
-      <c r="E588" t="s">
-        <v>809</v>
       </c>
       <c r="F588" t="s">
         <v>780</v>
@@ -16037,10 +16037,10 @@
         <v>711</v>
       </c>
       <c r="D589" t="s">
+        <v>779</v>
+      </c>
+      <c r="E589" t="s">
         <v>782</v>
-      </c>
-      <c r="E589" t="s">
-        <v>779</v>
       </c>
       <c r="F589" t="s">
         <v>780</v>
@@ -16057,10 +16057,10 @@
         <v>24</v>
       </c>
       <c r="D590" t="s">
+        <v>779</v>
+      </c>
+      <c r="E590" t="s">
         <v>782</v>
-      </c>
-      <c r="E590" t="s">
-        <v>779</v>
       </c>
       <c r="F590" t="s">
         <v>780</v>
@@ -16077,10 +16077,10 @@
         <v>15</v>
       </c>
       <c r="D591" t="s">
+        <v>779</v>
+      </c>
+      <c r="E591" t="s">
         <v>782</v>
-      </c>
-      <c r="E591" t="s">
-        <v>779</v>
       </c>
       <c r="F591" t="s">
         <v>780</v>
@@ -16097,10 +16097,10 @@
         <v>711</v>
       </c>
       <c r="D592" t="s">
+        <v>779</v>
+      </c>
+      <c r="E592" t="s">
         <v>814</v>
-      </c>
-      <c r="E592" t="s">
-        <v>779</v>
       </c>
       <c r="F592" t="s">
         <v>780</v>
@@ -16117,10 +16117,10 @@
         <v>13</v>
       </c>
       <c r="D593" t="s">
+        <v>779</v>
+      </c>
+      <c r="E593" t="s">
         <v>782</v>
-      </c>
-      <c r="E593" t="s">
-        <v>779</v>
       </c>
       <c r="F593" t="s">
         <v>780</v>
@@ -16137,10 +16137,10 @@
         <v>711</v>
       </c>
       <c r="D594" t="s">
+        <v>779</v>
+      </c>
+      <c r="E594" t="s">
         <v>782</v>
-      </c>
-      <c r="E594" t="s">
-        <v>779</v>
       </c>
       <c r="F594" t="s">
         <v>780</v>
@@ -16157,10 +16157,10 @@
         <v>711</v>
       </c>
       <c r="D595" t="s">
+        <v>779</v>
+      </c>
+      <c r="E595" t="s">
         <v>782</v>
-      </c>
-      <c r="E595" t="s">
-        <v>779</v>
       </c>
       <c r="F595" t="s">
         <v>780</v>
@@ -16177,10 +16177,10 @@
         <v>711</v>
       </c>
       <c r="D596" t="s">
+        <v>779</v>
+      </c>
+      <c r="E596" t="s">
         <v>782</v>
-      </c>
-      <c r="E596" t="s">
-        <v>779</v>
       </c>
       <c r="F596" t="s">
         <v>780</v>
@@ -16357,10 +16357,10 @@
         <v>24</v>
       </c>
       <c r="D605" t="s">
-        <v>820</v>
+        <v>839</v>
       </c>
       <c r="E605" t="s">
-        <v>839</v>
+        <v>821</v>
       </c>
       <c r="F605" t="s">
         <v>822</v>
@@ -16437,10 +16437,10 @@
         <v>711</v>
       </c>
       <c r="D609" t="s">
+        <v>846</v>
+      </c>
+      <c r="E609" t="s">
         <v>807</v>
-      </c>
-      <c r="E609" t="s">
-        <v>846</v>
       </c>
       <c r="F609" t="s">
         <v>822</v>
@@ -16477,10 +16477,10 @@
         <v>24</v>
       </c>
       <c r="D611" t="s">
+        <v>824</v>
+      </c>
+      <c r="E611" t="s">
         <v>849</v>
-      </c>
-      <c r="E611" t="s">
-        <v>825</v>
       </c>
       <c r="F611" t="s">
         <v>822</v>
@@ -16497,10 +16497,10 @@
         <v>15</v>
       </c>
       <c r="D612" t="s">
-        <v>820</v>
+        <v>851</v>
       </c>
       <c r="E612" t="s">
-        <v>851</v>
+        <v>821</v>
       </c>
       <c r="F612" t="s">
         <v>822</v>
@@ -16537,10 +16537,10 @@
         <v>711</v>
       </c>
       <c r="D614" t="s">
-        <v>820</v>
+        <v>854</v>
       </c>
       <c r="E614" t="s">
-        <v>854</v>
+        <v>821</v>
       </c>
       <c r="F614" t="s">
         <v>822</v>
@@ -16817,10 +16817,10 @@
         <v>711</v>
       </c>
       <c r="D628" t="s">
+        <v>864</v>
+      </c>
+      <c r="E628" t="s">
         <v>874</v>
-      </c>
-      <c r="E628" t="s">
-        <v>865</v>
       </c>
       <c r="F628" t="s">
         <v>866</v>
@@ -16837,10 +16837,10 @@
         <v>24</v>
       </c>
       <c r="D629" t="s">
-        <v>864</v>
+        <v>876</v>
       </c>
       <c r="E629" t="s">
-        <v>876</v>
+        <v>865</v>
       </c>
       <c r="F629" t="s">
         <v>866</v>
@@ -16897,10 +16897,10 @@
         <v>24</v>
       </c>
       <c r="D632" t="s">
+        <v>876</v>
+      </c>
+      <c r="E632" t="s">
         <v>880</v>
-      </c>
-      <c r="E632" t="s">
-        <v>876</v>
       </c>
       <c r="F632" t="s">
         <v>866</v>
@@ -16977,10 +16977,10 @@
         <v>711</v>
       </c>
       <c r="D636" t="s">
-        <v>864</v>
+        <v>889</v>
       </c>
       <c r="E636" t="s">
-        <v>889</v>
+        <v>865</v>
       </c>
       <c r="F636" t="s">
         <v>866</v>
@@ -17097,10 +17097,10 @@
         <v>15</v>
       </c>
       <c r="D642" t="s">
-        <v>864</v>
+        <v>900</v>
       </c>
       <c r="E642" t="s">
-        <v>900</v>
+        <v>865</v>
       </c>
       <c r="F642" t="s">
         <v>866</v>
@@ -17117,10 +17117,10 @@
         <v>15</v>
       </c>
       <c r="D643" t="s">
-        <v>864</v>
+        <v>902</v>
       </c>
       <c r="E643" t="s">
-        <v>902</v>
+        <v>865</v>
       </c>
       <c r="F643" t="s">
         <v>866</v>
@@ -17177,10 +17177,10 @@
         <v>24</v>
       </c>
       <c r="D646" t="s">
-        <v>864</v>
+        <v>906</v>
       </c>
       <c r="E646" t="s">
-        <v>906</v>
+        <v>865</v>
       </c>
       <c r="F646" t="s">
         <v>866</v>
@@ -17277,10 +17277,10 @@
         <v>24</v>
       </c>
       <c r="D651" t="s">
+        <v>910</v>
+      </c>
+      <c r="E651" t="s">
         <v>917</v>
-      </c>
-      <c r="E651" t="s">
-        <v>911</v>
       </c>
       <c r="F651" t="s">
         <v>912</v>
@@ -17337,10 +17337,10 @@
         <v>15</v>
       </c>
       <c r="D654" t="s">
-        <v>864</v>
+        <v>902</v>
       </c>
       <c r="E654" t="s">
-        <v>902</v>
+        <v>865</v>
       </c>
       <c r="F654" t="s">
         <v>912</v>
@@ -17437,10 +17437,10 @@
         <v>24</v>
       </c>
       <c r="D659" t="s">
+        <v>889</v>
+      </c>
+      <c r="E659" t="s">
         <v>932</v>
-      </c>
-      <c r="E659" t="s">
-        <v>889</v>
       </c>
       <c r="F659" t="s">
         <v>912</v>
@@ -17497,10 +17497,10 @@
         <v>24</v>
       </c>
       <c r="D662" t="s">
-        <v>915</v>
+        <v>919</v>
       </c>
       <c r="E662" t="s">
-        <v>920</v>
+        <v>914</v>
       </c>
       <c r="F662" t="s">
         <v>912</v>
@@ -17537,10 +17537,10 @@
         <v>15</v>
       </c>
       <c r="D664" t="s">
+        <v>902</v>
+      </c>
+      <c r="E664" t="s">
         <v>942</v>
-      </c>
-      <c r="E664" t="s">
-        <v>902</v>
       </c>
       <c r="F664" t="s">
         <v>912</v>
@@ -17557,10 +17557,10 @@
         <v>711</v>
       </c>
       <c r="D665" t="s">
-        <v>919</v>
+        <v>944</v>
       </c>
       <c r="E665" t="s">
-        <v>944</v>
+        <v>920</v>
       </c>
       <c r="F665" t="s">
         <v>912</v>
@@ -17577,10 +17577,10 @@
         <v>24</v>
       </c>
       <c r="D666" t="s">
-        <v>910</v>
+        <v>944</v>
       </c>
       <c r="E666" t="s">
-        <v>944</v>
+        <v>911</v>
       </c>
       <c r="F666" t="s">
         <v>912</v>
@@ -17637,10 +17637,10 @@
         <v>15</v>
       </c>
       <c r="D669" t="s">
+        <v>902</v>
+      </c>
+      <c r="E669" t="s">
         <v>932</v>
-      </c>
-      <c r="E669" t="s">
-        <v>902</v>
       </c>
       <c r="F669" t="s">
         <v>912</v>
@@ -17677,10 +17677,10 @@
         <v>24</v>
       </c>
       <c r="D671" t="s">
+        <v>910</v>
+      </c>
+      <c r="E671" t="s">
         <v>953</v>
-      </c>
-      <c r="E671" t="s">
-        <v>911</v>
       </c>
       <c r="F671" t="s">
         <v>912</v>
@@ -17737,10 +17737,10 @@
         <v>15</v>
       </c>
       <c r="D674" t="s">
-        <v>934</v>
+        <v>902</v>
       </c>
       <c r="E674" t="s">
-        <v>902</v>
+        <v>935</v>
       </c>
       <c r="F674" t="s">
         <v>912</v>
@@ -17757,10 +17757,10 @@
         <v>24</v>
       </c>
       <c r="D675" t="s">
+        <v>910</v>
+      </c>
+      <c r="E675" t="s">
         <v>917</v>
-      </c>
-      <c r="E675" t="s">
-        <v>911</v>
       </c>
       <c r="F675" t="s">
         <v>912</v>
@@ -17777,10 +17777,10 @@
         <v>15</v>
       </c>
       <c r="D676" t="s">
-        <v>919</v>
+        <v>959</v>
       </c>
       <c r="E676" t="s">
-        <v>959</v>
+        <v>920</v>
       </c>
       <c r="F676" t="s">
         <v>912</v>
@@ -18037,10 +18037,10 @@
         <v>24</v>
       </c>
       <c r="D689" t="s">
+        <v>970</v>
+      </c>
+      <c r="E689" t="s">
         <v>980</v>
-      </c>
-      <c r="E689" t="s">
-        <v>971</v>
       </c>
       <c r="F689" t="s">
         <v>968</v>
@@ -18097,10 +18097,10 @@
         <v>15</v>
       </c>
       <c r="D692" t="s">
-        <v>919</v>
+        <v>986</v>
       </c>
       <c r="E692" t="s">
-        <v>986</v>
+        <v>920</v>
       </c>
       <c r="F692" t="s">
         <v>968</v>
@@ -18317,10 +18317,10 @@
         <v>24</v>
       </c>
       <c r="D703" t="s">
-        <v>1005</v>
+        <v>1012</v>
       </c>
       <c r="E703" t="s">
-        <v>1012</v>
+        <v>1006</v>
       </c>
       <c r="F703" t="s">
         <v>968</v>
@@ -18357,10 +18357,10 @@
         <v>15</v>
       </c>
       <c r="D705" t="s">
-        <v>1001</v>
+        <v>1015</v>
       </c>
       <c r="E705" t="s">
-        <v>1015</v>
+        <v>1002</v>
       </c>
       <c r="F705" t="s">
         <v>968</v>
@@ -18397,10 +18397,10 @@
         <v>15</v>
       </c>
       <c r="D707" t="s">
-        <v>1001</v>
+        <v>973</v>
       </c>
       <c r="E707" t="s">
-        <v>974</v>
+        <v>1002</v>
       </c>
       <c r="F707" t="s">
         <v>968</v>
@@ -18417,10 +18417,10 @@
         <v>24</v>
       </c>
       <c r="D708" t="s">
-        <v>970</v>
+        <v>1019</v>
       </c>
       <c r="E708" t="s">
-        <v>1019</v>
+        <v>971</v>
       </c>
       <c r="F708" t="s">
         <v>968</v>
@@ -18477,10 +18477,10 @@
         <v>711</v>
       </c>
       <c r="D711" t="s">
-        <v>1001</v>
+        <v>973</v>
       </c>
       <c r="E711" t="s">
-        <v>974</v>
+        <v>1002</v>
       </c>
       <c r="F711" t="s">
         <v>968</v>
@@ -18557,10 +18557,10 @@
         <v>24</v>
       </c>
       <c r="D715" t="s">
-        <v>1001</v>
+        <v>998</v>
       </c>
       <c r="E715" t="s">
-        <v>999</v>
+        <v>1002</v>
       </c>
       <c r="F715" t="s">
         <v>968</v>
@@ -18637,10 +18637,10 @@
         <v>711</v>
       </c>
       <c r="D719" t="s">
-        <v>1032</v>
+        <v>1036</v>
       </c>
       <c r="E719" t="s">
-        <v>1036</v>
+        <v>1033</v>
       </c>
       <c r="F719" t="s">
         <v>1034</v>
@@ -18657,10 +18657,10 @@
         <v>711</v>
       </c>
       <c r="D720" t="s">
-        <v>1032</v>
+        <v>1036</v>
       </c>
       <c r="E720" t="s">
-        <v>1036</v>
+        <v>1033</v>
       </c>
       <c r="F720" t="s">
         <v>1034</v>
@@ -18677,10 +18677,10 @@
         <v>711</v>
       </c>
       <c r="D721" t="s">
-        <v>1032</v>
+        <v>1036</v>
       </c>
       <c r="E721" t="s">
-        <v>1036</v>
+        <v>1033</v>
       </c>
       <c r="F721" t="s">
         <v>1034</v>
@@ -18697,10 +18697,10 @@
         <v>711</v>
       </c>
       <c r="D722" t="s">
-        <v>1032</v>
+        <v>1036</v>
       </c>
       <c r="E722" t="s">
-        <v>1036</v>
+        <v>1033</v>
       </c>
       <c r="F722" t="s">
         <v>1034</v>
@@ -18717,10 +18717,10 @@
         <v>711</v>
       </c>
       <c r="D723" t="s">
-        <v>1032</v>
+        <v>1036</v>
       </c>
       <c r="E723" t="s">
-        <v>1036</v>
+        <v>1033</v>
       </c>
       <c r="F723" t="s">
         <v>1034</v>
@@ -18737,10 +18737,10 @@
         <v>15</v>
       </c>
       <c r="D724" t="s">
-        <v>1032</v>
+        <v>1036</v>
       </c>
       <c r="E724" t="s">
-        <v>1036</v>
+        <v>1033</v>
       </c>
       <c r="F724" t="s">
         <v>1034</v>
@@ -18797,10 +18797,10 @@
         <v>711</v>
       </c>
       <c r="D727" t="s">
-        <v>1032</v>
+        <v>1036</v>
       </c>
       <c r="E727" t="s">
-        <v>1036</v>
+        <v>1033</v>
       </c>
       <c r="F727" t="s">
         <v>1034</v>
@@ -18817,10 +18817,10 @@
         <v>711</v>
       </c>
       <c r="D728" t="s">
-        <v>1032</v>
+        <v>1036</v>
       </c>
       <c r="E728" t="s">
-        <v>1036</v>
+        <v>1033</v>
       </c>
       <c r="F728" t="s">
         <v>1034</v>
@@ -18857,10 +18857,10 @@
         <v>13</v>
       </c>
       <c r="D730" t="s">
-        <v>1032</v>
+        <v>1036</v>
       </c>
       <c r="E730" t="s">
-        <v>1036</v>
+        <v>1033</v>
       </c>
       <c r="F730" t="s">
         <v>1034</v>
@@ -18917,10 +18917,10 @@
         <v>24</v>
       </c>
       <c r="D733" t="s">
-        <v>1032</v>
+        <v>1059</v>
       </c>
       <c r="E733" t="s">
-        <v>1059</v>
+        <v>1033</v>
       </c>
       <c r="F733" t="s">
         <v>1034</v>
@@ -18957,10 +18957,10 @@
         <v>711</v>
       </c>
       <c r="D735" t="s">
-        <v>1032</v>
+        <v>1036</v>
       </c>
       <c r="E735" t="s">
-        <v>1036</v>
+        <v>1033</v>
       </c>
       <c r="F735" t="s">
         <v>1034</v>
@@ -18977,10 +18977,10 @@
         <v>711</v>
       </c>
       <c r="D736" t="s">
-        <v>1032</v>
+        <v>1065</v>
       </c>
       <c r="E736" t="s">
-        <v>1065</v>
+        <v>1033</v>
       </c>
       <c r="F736" t="s">
         <v>1034</v>
@@ -18997,10 +18997,10 @@
         <v>15</v>
       </c>
       <c r="D737" t="s">
-        <v>1032</v>
+        <v>1036</v>
       </c>
       <c r="E737" t="s">
-        <v>1036</v>
+        <v>1033</v>
       </c>
       <c r="F737" t="s">
         <v>1034</v>
@@ -19017,10 +19017,10 @@
         <v>15</v>
       </c>
       <c r="D738" t="s">
-        <v>973</v>
+        <v>1068</v>
       </c>
       <c r="E738" t="s">
-        <v>1068</v>
+        <v>974</v>
       </c>
       <c r="F738" t="s">
         <v>1034</v>
@@ -19037,10 +19037,10 @@
         <v>711</v>
       </c>
       <c r="D739" t="s">
-        <v>1032</v>
+        <v>1036</v>
       </c>
       <c r="E739" t="s">
-        <v>1036</v>
+        <v>1033</v>
       </c>
       <c r="F739" t="s">
         <v>1034</v>
@@ -19057,10 +19057,10 @@
         <v>711</v>
       </c>
       <c r="D740" t="s">
-        <v>1032</v>
+        <v>1036</v>
       </c>
       <c r="E740" t="s">
-        <v>1036</v>
+        <v>1033</v>
       </c>
       <c r="F740" t="s">
         <v>1034</v>
@@ -19097,10 +19097,10 @@
         <v>15</v>
       </c>
       <c r="D742" t="s">
-        <v>1032</v>
+        <v>1075</v>
       </c>
       <c r="E742" t="s">
-        <v>1075</v>
+        <v>1033</v>
       </c>
       <c r="F742" t="s">
         <v>1034</v>
@@ -19117,10 +19117,10 @@
         <v>711</v>
       </c>
       <c r="D743" t="s">
-        <v>1032</v>
+        <v>1036</v>
       </c>
       <c r="E743" t="s">
-        <v>1036</v>
+        <v>1033</v>
       </c>
       <c r="F743" t="s">
         <v>1034</v>
@@ -19157,10 +19157,10 @@
         <v>24</v>
       </c>
       <c r="D745" t="s">
-        <v>1032</v>
+        <v>1079</v>
       </c>
       <c r="E745" t="s">
-        <v>1079</v>
+        <v>1033</v>
       </c>
       <c r="F745" t="s">
         <v>1034</v>
@@ -19177,10 +19177,10 @@
         <v>711</v>
       </c>
       <c r="D746" t="s">
-        <v>1032</v>
+        <v>1036</v>
       </c>
       <c r="E746" t="s">
-        <v>1036</v>
+        <v>1033</v>
       </c>
       <c r="F746" t="s">
         <v>1034</v>
@@ -19197,10 +19197,10 @@
         <v>711</v>
       </c>
       <c r="D747" t="s">
-        <v>1032</v>
+        <v>1036</v>
       </c>
       <c r="E747" t="s">
-        <v>1036</v>
+        <v>1033</v>
       </c>
       <c r="F747" t="s">
         <v>1034</v>
@@ -19217,10 +19217,10 @@
         <v>711</v>
       </c>
       <c r="D748" t="s">
-        <v>1032</v>
+        <v>1036</v>
       </c>
       <c r="E748" t="s">
-        <v>1036</v>
+        <v>1033</v>
       </c>
       <c r="F748" t="s">
         <v>1034</v>
@@ -19237,10 +19237,10 @@
         <v>711</v>
       </c>
       <c r="D749" t="s">
-        <v>1032</v>
+        <v>1036</v>
       </c>
       <c r="E749" t="s">
-        <v>1036</v>
+        <v>1033</v>
       </c>
       <c r="F749" t="s">
         <v>1034</v>
@@ -19417,10 +19417,10 @@
         <v>24</v>
       </c>
       <c r="D758" t="s">
-        <v>1089</v>
+        <v>1085</v>
       </c>
       <c r="E758" t="s">
-        <v>1086</v>
+        <v>1090</v>
       </c>
       <c r="F758" t="s">
         <v>1087</v>
@@ -19437,10 +19437,10 @@
         <v>15</v>
       </c>
       <c r="D759" t="s">
-        <v>1092</v>
+        <v>1065</v>
       </c>
       <c r="E759" t="s">
-        <v>1065</v>
+        <v>1093</v>
       </c>
       <c r="F759" t="s">
         <v>1087</v>
@@ -19497,10 +19497,10 @@
         <v>24</v>
       </c>
       <c r="D762" t="s">
+        <v>1065</v>
+      </c>
+      <c r="E762" t="s">
         <v>1104</v>
-      </c>
-      <c r="E762" t="s">
-        <v>1065</v>
       </c>
       <c r="F762" t="s">
         <v>1087</v>
@@ -19557,10 +19557,10 @@
         <v>24</v>
       </c>
       <c r="D765" t="s">
-        <v>1085</v>
+        <v>1092</v>
       </c>
       <c r="E765" t="s">
-        <v>1093</v>
+        <v>1086</v>
       </c>
       <c r="F765" t="s">
         <v>1087</v>
@@ -19577,10 +19577,10 @@
         <v>24</v>
       </c>
       <c r="D766" t="s">
+        <v>1111</v>
+      </c>
+      <c r="E766" t="s">
         <v>1104</v>
-      </c>
-      <c r="E766" t="s">
-        <v>1111</v>
       </c>
       <c r="F766" t="s">
         <v>1087</v>
@@ -19797,10 +19797,10 @@
         <v>711</v>
       </c>
       <c r="D777" t="s">
-        <v>1128</v>
+        <v>1132</v>
       </c>
       <c r="E777" t="s">
-        <v>1132</v>
+        <v>1129</v>
       </c>
       <c r="F777" t="s">
         <v>1130</v>
@@ -19857,10 +19857,10 @@
         <v>711</v>
       </c>
       <c r="D780" t="s">
-        <v>1128</v>
+        <v>1132</v>
       </c>
       <c r="E780" t="s">
-        <v>1132</v>
+        <v>1129</v>
       </c>
       <c r="F780" t="s">
         <v>1130</v>
@@ -19877,10 +19877,10 @@
         <v>711</v>
       </c>
       <c r="D781" t="s">
-        <v>1128</v>
+        <v>1132</v>
       </c>
       <c r="E781" t="s">
-        <v>1132</v>
+        <v>1129</v>
       </c>
       <c r="F781" t="s">
         <v>1130</v>
@@ -19897,10 +19897,10 @@
         <v>711</v>
       </c>
       <c r="D782" t="s">
-        <v>1128</v>
+        <v>1142</v>
       </c>
       <c r="E782" t="s">
-        <v>1142</v>
+        <v>1129</v>
       </c>
       <c r="F782" t="s">
         <v>1130</v>
@@ -19917,10 +19917,10 @@
         <v>711</v>
       </c>
       <c r="D783" t="s">
-        <v>1128</v>
+        <v>1132</v>
       </c>
       <c r="E783" t="s">
-        <v>1132</v>
+        <v>1129</v>
       </c>
       <c r="F783" t="s">
         <v>1130</v>
@@ -19937,10 +19937,10 @@
         <v>711</v>
       </c>
       <c r="D784" t="s">
-        <v>1128</v>
+        <v>1132</v>
       </c>
       <c r="E784" t="s">
-        <v>1132</v>
+        <v>1129</v>
       </c>
       <c r="F784" t="s">
         <v>1130</v>
@@ -19957,10 +19957,10 @@
         <v>711</v>
       </c>
       <c r="D785" t="s">
-        <v>1128</v>
+        <v>1132</v>
       </c>
       <c r="E785" t="s">
-        <v>1132</v>
+        <v>1129</v>
       </c>
       <c r="F785" t="s">
         <v>1130</v>
@@ -19977,10 +19977,10 @@
         <v>711</v>
       </c>
       <c r="D786" t="s">
-        <v>1128</v>
+        <v>1132</v>
       </c>
       <c r="E786" t="s">
-        <v>1132</v>
+        <v>1129</v>
       </c>
       <c r="F786" t="s">
         <v>1130</v>
@@ -19997,10 +19997,10 @@
         <v>711</v>
       </c>
       <c r="D787" t="s">
-        <v>1128</v>
+        <v>1132</v>
       </c>
       <c r="E787" t="s">
-        <v>1132</v>
+        <v>1129</v>
       </c>
       <c r="F787" t="s">
         <v>1130</v>
@@ -20017,10 +20017,10 @@
         <v>711</v>
       </c>
       <c r="D788" t="s">
-        <v>1128</v>
+        <v>1132</v>
       </c>
       <c r="E788" t="s">
-        <v>1132</v>
+        <v>1129</v>
       </c>
       <c r="F788" t="s">
         <v>1130</v>
@@ -20037,10 +20037,10 @@
         <v>24</v>
       </c>
       <c r="D789" t="s">
+        <v>1128</v>
+      </c>
+      <c r="E789" t="s">
         <v>1150</v>
-      </c>
-      <c r="E789" t="s">
-        <v>1129</v>
       </c>
       <c r="F789" t="s">
         <v>1130</v>
@@ -20057,10 +20057,10 @@
         <v>711</v>
       </c>
       <c r="D790" t="s">
-        <v>1128</v>
+        <v>1132</v>
       </c>
       <c r="E790" t="s">
-        <v>1132</v>
+        <v>1129</v>
       </c>
       <c r="F790" t="s">
         <v>1130</v>
@@ -20077,10 +20077,10 @@
         <v>24</v>
       </c>
       <c r="D791" t="s">
+        <v>1142</v>
+      </c>
+      <c r="E791" t="s">
         <v>1153</v>
-      </c>
-      <c r="E791" t="s">
-        <v>1142</v>
       </c>
       <c r="F791" t="s">
         <v>1130</v>
@@ -20097,10 +20097,10 @@
         <v>24</v>
       </c>
       <c r="D792" t="s">
+        <v>1155</v>
+      </c>
+      <c r="E792" t="s">
         <v>1150</v>
-      </c>
-      <c r="E792" t="s">
-        <v>1155</v>
       </c>
       <c r="F792" t="s">
         <v>1130</v>
@@ -20117,10 +20117,10 @@
         <v>711</v>
       </c>
       <c r="D793" t="s">
-        <v>1128</v>
+        <v>1132</v>
       </c>
       <c r="E793" t="s">
-        <v>1132</v>
+        <v>1129</v>
       </c>
       <c r="F793" t="s">
         <v>1130</v>
@@ -20137,10 +20137,10 @@
         <v>24</v>
       </c>
       <c r="D794" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E794" t="s">
         <v>1158</v>
-      </c>
-      <c r="E794" t="s">
-        <v>1132</v>
       </c>
       <c r="F794" t="s">
         <v>1130</v>
@@ -20157,10 +20157,10 @@
         <v>24</v>
       </c>
       <c r="D795" t="s">
-        <v>1128</v>
+        <v>1160</v>
       </c>
       <c r="E795" t="s">
-        <v>1160</v>
+        <v>1129</v>
       </c>
       <c r="F795" t="s">
         <v>1130</v>
@@ -20177,10 +20177,10 @@
         <v>711</v>
       </c>
       <c r="D796" t="s">
-        <v>1128</v>
+        <v>1132</v>
       </c>
       <c r="E796" t="s">
-        <v>1132</v>
+        <v>1129</v>
       </c>
       <c r="F796" t="s">
         <v>1130</v>
@@ -20237,10 +20237,10 @@
         <v>711</v>
       </c>
       <c r="D799" t="s">
-        <v>1128</v>
+        <v>1132</v>
       </c>
       <c r="E799" t="s">
-        <v>1132</v>
+        <v>1129</v>
       </c>
       <c r="F799" t="s">
         <v>1130</v>
@@ -20257,10 +20257,10 @@
         <v>711</v>
       </c>
       <c r="D800" t="s">
-        <v>1128</v>
+        <v>1132</v>
       </c>
       <c r="E800" t="s">
-        <v>1132</v>
+        <v>1129</v>
       </c>
       <c r="F800" t="s">
         <v>1130</v>
@@ -20277,10 +20277,10 @@
         <v>711</v>
       </c>
       <c r="D801" t="s">
-        <v>1128</v>
+        <v>1132</v>
       </c>
       <c r="E801" t="s">
-        <v>1132</v>
+        <v>1129</v>
       </c>
       <c r="F801" t="s">
         <v>1130</v>
@@ -20297,10 +20297,10 @@
         <v>711</v>
       </c>
       <c r="D802" t="s">
-        <v>1128</v>
+        <v>1132</v>
       </c>
       <c r="E802" t="s">
-        <v>1132</v>
+        <v>1129</v>
       </c>
       <c r="F802" t="s">
         <v>1130</v>
@@ -20317,10 +20317,10 @@
         <v>711</v>
       </c>
       <c r="D803" t="s">
-        <v>1128</v>
+        <v>1132</v>
       </c>
       <c r="E803" t="s">
-        <v>1132</v>
+        <v>1129</v>
       </c>
       <c r="F803" t="s">
         <v>1130</v>
@@ -20337,10 +20337,10 @@
         <v>711</v>
       </c>
       <c r="D804" t="s">
-        <v>1128</v>
+        <v>1132</v>
       </c>
       <c r="E804" t="s">
-        <v>1132</v>
+        <v>1129</v>
       </c>
       <c r="F804" t="s">
         <v>1130</v>
@@ -20357,10 +20357,10 @@
         <v>711</v>
       </c>
       <c r="D805" t="s">
-        <v>1128</v>
+        <v>1132</v>
       </c>
       <c r="E805" t="s">
-        <v>1132</v>
+        <v>1129</v>
       </c>
       <c r="F805" t="s">
         <v>1130</v>
@@ -20377,10 +20377,10 @@
         <v>711</v>
       </c>
       <c r="D806" t="s">
-        <v>1128</v>
+        <v>1132</v>
       </c>
       <c r="E806" t="s">
-        <v>1132</v>
+        <v>1129</v>
       </c>
       <c r="F806" t="s">
         <v>1130</v>
@@ -20397,10 +20397,10 @@
         <v>711</v>
       </c>
       <c r="D807" t="s">
-        <v>1128</v>
+        <v>1132</v>
       </c>
       <c r="E807" t="s">
-        <v>1132</v>
+        <v>1129</v>
       </c>
       <c r="F807" t="s">
         <v>1130</v>
@@ -20537,10 +20537,10 @@
         <v>711</v>
       </c>
       <c r="D814" t="s">
-        <v>1178</v>
+        <v>1185</v>
       </c>
       <c r="E814" t="s">
-        <v>1186</v>
+        <v>1179</v>
       </c>
       <c r="F814" t="s">
         <v>1180</v>
@@ -20717,10 +20717,10 @@
         <v>1182</v>
       </c>
       <c r="D823" t="s">
-        <v>1178</v>
+        <v>1202</v>
       </c>
       <c r="E823" t="s">
-        <v>1203</v>
+        <v>1179</v>
       </c>
       <c r="F823" t="s">
         <v>1180</v>
@@ -20817,10 +20817,10 @@
         <v>1182</v>
       </c>
       <c r="D828" t="s">
-        <v>1178</v>
+        <v>1202</v>
       </c>
       <c r="E828" t="s">
-        <v>1203</v>
+        <v>1179</v>
       </c>
       <c r="F828" t="s">
         <v>1180</v>
@@ -20857,10 +20857,10 @@
         <v>1182</v>
       </c>
       <c r="D830" t="s">
-        <v>1178</v>
+        <v>1185</v>
       </c>
       <c r="E830" t="s">
-        <v>1186</v>
+        <v>1179</v>
       </c>
       <c r="F830" t="s">
         <v>1180</v>
@@ -21057,10 +21057,10 @@
         <v>1182</v>
       </c>
       <c r="D840" t="s">
-        <v>1221</v>
+        <v>1225</v>
       </c>
       <c r="E840" t="s">
-        <v>1225</v>
+        <v>1222</v>
       </c>
       <c r="F840" t="s">
         <v>1223</v>
@@ -21077,10 +21077,10 @@
         <v>1182</v>
       </c>
       <c r="D841" t="s">
-        <v>1221</v>
+        <v>1225</v>
       </c>
       <c r="E841" t="s">
-        <v>1225</v>
+        <v>1222</v>
       </c>
       <c r="F841" t="s">
         <v>1223</v>
@@ -21097,10 +21097,10 @@
         <v>1182</v>
       </c>
       <c r="D842" t="s">
-        <v>1221</v>
+        <v>1225</v>
       </c>
       <c r="E842" t="s">
-        <v>1225</v>
+        <v>1222</v>
       </c>
       <c r="F842" t="s">
         <v>1223</v>
@@ -21117,10 +21117,10 @@
         <v>1182</v>
       </c>
       <c r="D843" t="s">
-        <v>1221</v>
+        <v>1225</v>
       </c>
       <c r="E843" t="s">
-        <v>1225</v>
+        <v>1222</v>
       </c>
       <c r="F843" t="s">
         <v>1223</v>
@@ -21137,10 +21137,10 @@
         <v>1182</v>
       </c>
       <c r="D844" t="s">
-        <v>1221</v>
+        <v>1225</v>
       </c>
       <c r="E844" t="s">
-        <v>1225</v>
+        <v>1222</v>
       </c>
       <c r="F844" t="s">
         <v>1223</v>
@@ -21157,10 +21157,10 @@
         <v>711</v>
       </c>
       <c r="D845" t="s">
-        <v>1221</v>
+        <v>1225</v>
       </c>
       <c r="E845" t="s">
-        <v>1225</v>
+        <v>1222</v>
       </c>
       <c r="F845" t="s">
         <v>1223</v>
@@ -21177,10 +21177,10 @@
         <v>1182</v>
       </c>
       <c r="D846" t="s">
-        <v>1221</v>
+        <v>1225</v>
       </c>
       <c r="E846" t="s">
-        <v>1225</v>
+        <v>1222</v>
       </c>
       <c r="F846" t="s">
         <v>1223</v>
@@ -21197,10 +21197,10 @@
         <v>1182</v>
       </c>
       <c r="D847" t="s">
-        <v>1185</v>
+        <v>1233</v>
       </c>
       <c r="E847" t="s">
-        <v>1233</v>
+        <v>1186</v>
       </c>
       <c r="F847" t="s">
         <v>1223</v>
@@ -21217,10 +21217,10 @@
         <v>1182</v>
       </c>
       <c r="D848" t="s">
-        <v>1185</v>
+        <v>1233</v>
       </c>
       <c r="E848" t="s">
-        <v>1233</v>
+        <v>1186</v>
       </c>
       <c r="F848" t="s">
         <v>1223</v>
@@ -21237,10 +21237,10 @@
         <v>711</v>
       </c>
       <c r="D849" t="s">
-        <v>1185</v>
+        <v>1233</v>
       </c>
       <c r="E849" t="s">
-        <v>1233</v>
+        <v>1186</v>
       </c>
       <c r="F849" t="s">
         <v>1223</v>
@@ -21257,10 +21257,10 @@
         <v>1182</v>
       </c>
       <c r="D850" t="s">
+        <v>1233</v>
+      </c>
+      <c r="E850" t="s">
         <v>1237</v>
-      </c>
-      <c r="E850" t="s">
-        <v>1233</v>
       </c>
       <c r="F850" t="s">
         <v>1223</v>
@@ -21277,10 +21277,10 @@
         <v>1182</v>
       </c>
       <c r="D851" t="s">
-        <v>1185</v>
+        <v>1233</v>
       </c>
       <c r="E851" t="s">
-        <v>1233</v>
+        <v>1186</v>
       </c>
       <c r="F851" t="s">
         <v>1223</v>
@@ -21297,10 +21297,10 @@
         <v>1182</v>
       </c>
       <c r="D852" t="s">
-        <v>1185</v>
+        <v>1233</v>
       </c>
       <c r="E852" t="s">
-        <v>1233</v>
+        <v>1186</v>
       </c>
       <c r="F852" t="s">
         <v>1223</v>
@@ -21317,10 +21317,10 @@
         <v>1182</v>
       </c>
       <c r="D853" t="s">
-        <v>1221</v>
+        <v>1225</v>
       </c>
       <c r="E853" t="s">
-        <v>1225</v>
+        <v>1222</v>
       </c>
       <c r="F853" t="s">
         <v>1223</v>
@@ -21337,10 +21337,10 @@
         <v>15</v>
       </c>
       <c r="D854" t="s">
-        <v>1221</v>
+        <v>1225</v>
       </c>
       <c r="E854" t="s">
-        <v>1225</v>
+        <v>1222</v>
       </c>
       <c r="F854" t="s">
         <v>1223</v>
@@ -21357,10 +21357,10 @@
         <v>15</v>
       </c>
       <c r="D855" t="s">
-        <v>1221</v>
+        <v>1225</v>
       </c>
       <c r="E855" t="s">
-        <v>1225</v>
+        <v>1222</v>
       </c>
       <c r="F855" t="s">
         <v>1223</v>
@@ -21377,10 +21377,10 @@
         <v>15</v>
       </c>
       <c r="D856" t="s">
-        <v>1221</v>
+        <v>1225</v>
       </c>
       <c r="E856" t="s">
-        <v>1225</v>
+        <v>1222</v>
       </c>
       <c r="F856" t="s">
         <v>1223</v>
@@ -21397,10 +21397,10 @@
         <v>1182</v>
       </c>
       <c r="D857" t="s">
-        <v>1221</v>
+        <v>1225</v>
       </c>
       <c r="E857" t="s">
-        <v>1225</v>
+        <v>1222</v>
       </c>
       <c r="F857" t="s">
         <v>1223</v>
@@ -21417,10 +21417,10 @@
         <v>1182</v>
       </c>
       <c r="D858" t="s">
-        <v>1221</v>
+        <v>1225</v>
       </c>
       <c r="E858" t="s">
-        <v>1225</v>
+        <v>1222</v>
       </c>
       <c r="F858" t="s">
         <v>1223</v>
@@ -21437,10 +21437,10 @@
         <v>15</v>
       </c>
       <c r="D859" t="s">
-        <v>1221</v>
+        <v>1225</v>
       </c>
       <c r="E859" t="s">
-        <v>1225</v>
+        <v>1222</v>
       </c>
       <c r="F859" t="s">
         <v>1223</v>
@@ -21457,10 +21457,10 @@
         <v>1182</v>
       </c>
       <c r="D860" t="s">
-        <v>1221</v>
+        <v>1225</v>
       </c>
       <c r="E860" t="s">
-        <v>1225</v>
+        <v>1222</v>
       </c>
       <c r="F860" t="s">
         <v>1223</v>
@@ -21477,10 +21477,10 @@
         <v>1182</v>
       </c>
       <c r="D861" t="s">
-        <v>1221</v>
+        <v>1225</v>
       </c>
       <c r="E861" t="s">
-        <v>1225</v>
+        <v>1222</v>
       </c>
       <c r="F861" t="s">
         <v>1223</v>
@@ -21497,10 +21497,10 @@
         <v>711</v>
       </c>
       <c r="D862" t="s">
-        <v>1221</v>
+        <v>1225</v>
       </c>
       <c r="E862" t="s">
-        <v>1225</v>
+        <v>1222</v>
       </c>
       <c r="F862" t="s">
         <v>1223</v>
@@ -21517,10 +21517,10 @@
         <v>1182</v>
       </c>
       <c r="D863" t="s">
-        <v>1221</v>
+        <v>1225</v>
       </c>
       <c r="E863" t="s">
-        <v>1225</v>
+        <v>1222</v>
       </c>
       <c r="F863" t="s">
         <v>1223</v>
@@ -21537,10 +21537,10 @@
         <v>1182</v>
       </c>
       <c r="D864" t="s">
-        <v>1221</v>
+        <v>1225</v>
       </c>
       <c r="E864" t="s">
-        <v>1225</v>
+        <v>1222</v>
       </c>
       <c r="F864" t="s">
         <v>1223</v>
@@ -21557,10 +21557,10 @@
         <v>1182</v>
       </c>
       <c r="D865" t="s">
-        <v>1221</v>
+        <v>1225</v>
       </c>
       <c r="E865" t="s">
-        <v>1225</v>
+        <v>1222</v>
       </c>
       <c r="F865" t="s">
         <v>1223</v>
@@ -21577,10 +21577,10 @@
         <v>711</v>
       </c>
       <c r="D866" t="s">
-        <v>1221</v>
+        <v>1225</v>
       </c>
       <c r="E866" t="s">
-        <v>1225</v>
+        <v>1222</v>
       </c>
       <c r="F866" t="s">
         <v>1223</v>
@@ -21617,10 +21617,10 @@
         <v>1182</v>
       </c>
       <c r="D868" t="s">
+        <v>1255</v>
+      </c>
+      <c r="E868" t="s">
         <v>1259</v>
-      </c>
-      <c r="E868" t="s">
-        <v>1256</v>
       </c>
       <c r="F868" t="s">
         <v>1257</v>
@@ -21637,10 +21637,10 @@
         <v>1182</v>
       </c>
       <c r="D869" t="s">
+        <v>1255</v>
+      </c>
+      <c r="E869" t="s">
         <v>1259</v>
-      </c>
-      <c r="E869" t="s">
-        <v>1256</v>
       </c>
       <c r="F869" t="s">
         <v>1257</v>
@@ -21657,10 +21657,10 @@
         <v>1182</v>
       </c>
       <c r="D870" t="s">
+        <v>1255</v>
+      </c>
+      <c r="E870" t="s">
         <v>1259</v>
-      </c>
-      <c r="E870" t="s">
-        <v>1256</v>
       </c>
       <c r="F870" t="s">
         <v>1257</v>
@@ -21677,10 +21677,10 @@
         <v>1182</v>
       </c>
       <c r="D871" t="s">
+        <v>1255</v>
+      </c>
+      <c r="E871" t="s">
         <v>1259</v>
-      </c>
-      <c r="E871" t="s">
-        <v>1256</v>
       </c>
       <c r="F871" t="s">
         <v>1257</v>
@@ -21697,10 +21697,10 @@
         <v>15</v>
       </c>
       <c r="D872" t="s">
+        <v>1255</v>
+      </c>
+      <c r="E872" t="s">
         <v>1259</v>
-      </c>
-      <c r="E872" t="s">
-        <v>1256</v>
       </c>
       <c r="F872" t="s">
         <v>1257</v>
@@ -21717,10 +21717,10 @@
         <v>15</v>
       </c>
       <c r="D873" t="s">
+        <v>1255</v>
+      </c>
+      <c r="E873" t="s">
         <v>1259</v>
-      </c>
-      <c r="E873" t="s">
-        <v>1256</v>
       </c>
       <c r="F873" t="s">
         <v>1257</v>
@@ -21737,10 +21737,10 @@
         <v>1182</v>
       </c>
       <c r="D874" t="s">
+        <v>1255</v>
+      </c>
+      <c r="E874" t="s">
         <v>1259</v>
-      </c>
-      <c r="E874" t="s">
-        <v>1256</v>
       </c>
       <c r="F874" t="s">
         <v>1257</v>
@@ -21757,10 +21757,10 @@
         <v>1182</v>
       </c>
       <c r="D875" t="s">
+        <v>1255</v>
+      </c>
+      <c r="E875" t="s">
         <v>1259</v>
-      </c>
-      <c r="E875" t="s">
-        <v>1256</v>
       </c>
       <c r="F875" t="s">
         <v>1257</v>
@@ -21777,10 +21777,10 @@
         <v>711</v>
       </c>
       <c r="D876" t="s">
+        <v>1255</v>
+      </c>
+      <c r="E876" t="s">
         <v>1259</v>
-      </c>
-      <c r="E876" t="s">
-        <v>1256</v>
       </c>
       <c r="F876" t="s">
         <v>1257</v>
@@ -21797,10 +21797,10 @@
         <v>15</v>
       </c>
       <c r="D877" t="s">
+        <v>1255</v>
+      </c>
+      <c r="E877" t="s">
         <v>1259</v>
-      </c>
-      <c r="E877" t="s">
-        <v>1256</v>
       </c>
       <c r="F877" t="s">
         <v>1257</v>
@@ -21817,10 +21817,10 @@
         <v>1182</v>
       </c>
       <c r="D878" t="s">
+        <v>1255</v>
+      </c>
+      <c r="E878" t="s">
         <v>1259</v>
-      </c>
-      <c r="E878" t="s">
-        <v>1256</v>
       </c>
       <c r="F878" t="s">
         <v>1257</v>
@@ -21837,10 +21837,10 @@
         <v>1182</v>
       </c>
       <c r="D879" t="s">
+        <v>1255</v>
+      </c>
+      <c r="E879" t="s">
         <v>1259</v>
-      </c>
-      <c r="E879" t="s">
-        <v>1256</v>
       </c>
       <c r="F879" t="s">
         <v>1257</v>
@@ -21857,10 +21857,10 @@
         <v>1182</v>
       </c>
       <c r="D880" t="s">
+        <v>1255</v>
+      </c>
+      <c r="E880" t="s">
         <v>1259</v>
-      </c>
-      <c r="E880" t="s">
-        <v>1256</v>
       </c>
       <c r="F880" t="s">
         <v>1257</v>
@@ -21877,10 +21877,10 @@
         <v>1182</v>
       </c>
       <c r="D881" t="s">
+        <v>1255</v>
+      </c>
+      <c r="E881" t="s">
         <v>1259</v>
-      </c>
-      <c r="E881" t="s">
-        <v>1256</v>
       </c>
       <c r="F881" t="s">
         <v>1257</v>
@@ -21897,10 +21897,10 @@
         <v>1182</v>
       </c>
       <c r="D882" t="s">
+        <v>1255</v>
+      </c>
+      <c r="E882" t="s">
         <v>1259</v>
-      </c>
-      <c r="E882" t="s">
-        <v>1256</v>
       </c>
       <c r="F882" t="s">
         <v>1257</v>
@@ -21917,10 +21917,10 @@
         <v>711</v>
       </c>
       <c r="D883" t="s">
+        <v>1255</v>
+      </c>
+      <c r="E883" t="s">
         <v>1259</v>
-      </c>
-      <c r="E883" t="s">
-        <v>1256</v>
       </c>
       <c r="F883" t="s">
         <v>1257</v>
@@ -21937,10 +21937,10 @@
         <v>1182</v>
       </c>
       <c r="D884" t="s">
+        <v>1255</v>
+      </c>
+      <c r="E884" t="s">
         <v>1259</v>
-      </c>
-      <c r="E884" t="s">
-        <v>1256</v>
       </c>
       <c r="F884" t="s">
         <v>1257</v>
@@ -21957,10 +21957,10 @@
         <v>1182</v>
       </c>
       <c r="D885" t="s">
+        <v>1255</v>
+      </c>
+      <c r="E885" t="s">
         <v>1259</v>
-      </c>
-      <c r="E885" t="s">
-        <v>1256</v>
       </c>
       <c r="F885" t="s">
         <v>1257</v>
@@ -21977,10 +21977,10 @@
         <v>1182</v>
       </c>
       <c r="D886" t="s">
+        <v>1255</v>
+      </c>
+      <c r="E886" t="s">
         <v>1259</v>
-      </c>
-      <c r="E886" t="s">
-        <v>1256</v>
       </c>
       <c r="F886" t="s">
         <v>1257</v>
@@ -21997,10 +21997,10 @@
         <v>15</v>
       </c>
       <c r="D887" t="s">
+        <v>1255</v>
+      </c>
+      <c r="E887" t="s">
         <v>1259</v>
-      </c>
-      <c r="E887" t="s">
-        <v>1256</v>
       </c>
       <c r="F887" t="s">
         <v>1257</v>
@@ -22017,10 +22017,10 @@
         <v>1182</v>
       </c>
       <c r="D888" t="s">
+        <v>1255</v>
+      </c>
+      <c r="E888" t="s">
         <v>1259</v>
-      </c>
-      <c r="E888" t="s">
-        <v>1256</v>
       </c>
       <c r="F888" t="s">
         <v>1257</v>
@@ -22037,10 +22037,10 @@
         <v>711</v>
       </c>
       <c r="D889" t="s">
+        <v>1255</v>
+      </c>
+      <c r="E889" t="s">
         <v>1259</v>
-      </c>
-      <c r="E889" t="s">
-        <v>1256</v>
       </c>
       <c r="F889" t="s">
         <v>1257</v>
@@ -22157,10 +22157,10 @@
         <v>1182</v>
       </c>
       <c r="D895" t="s">
-        <v>1282</v>
+        <v>1290</v>
       </c>
       <c r="E895" t="s">
-        <v>1290</v>
+        <v>1283</v>
       </c>
       <c r="F895" t="s">
         <v>1284</v>
@@ -22177,10 +22177,10 @@
         <v>711</v>
       </c>
       <c r="D896" t="s">
-        <v>1282</v>
+        <v>1290</v>
       </c>
       <c r="E896" t="s">
-        <v>1290</v>
+        <v>1283</v>
       </c>
       <c r="F896" t="s">
         <v>1284</v>
@@ -22357,10 +22357,10 @@
         <v>1182</v>
       </c>
       <c r="D905" t="s">
-        <v>1282</v>
+        <v>1301</v>
       </c>
       <c r="E905" t="s">
-        <v>1301</v>
+        <v>1283</v>
       </c>
       <c r="F905" t="s">
         <v>1302</v>
@@ -22377,10 +22377,10 @@
         <v>1182</v>
       </c>
       <c r="D906" t="s">
-        <v>1282</v>
+        <v>1304</v>
       </c>
       <c r="E906" t="s">
-        <v>1304</v>
+        <v>1283</v>
       </c>
       <c r="F906" t="s">
         <v>1302</v>
@@ -22397,10 +22397,10 @@
         <v>1182</v>
       </c>
       <c r="D907" t="s">
-        <v>1282</v>
+        <v>1301</v>
       </c>
       <c r="E907" t="s">
-        <v>1301</v>
+        <v>1283</v>
       </c>
       <c r="F907" t="s">
         <v>1302</v>

--- a/api/1/clv3/xlsx/fr/HumanitarianPlan.xlsx
+++ b/api/1/clv3/xlsx/fr/HumanitarianPlan.xlsx
@@ -28,12 +28,12 @@
     <t>codeforiati:plan-type</t>
   </si>
   <si>
+    <t>codeforiati:plan-end-date</t>
+  </si>
+  <si>
     <t>codeforiati:plan-year</t>
   </si>
   <si>
-    <t>codeforiati:plan-end-date</t>
-  </si>
-  <si>
     <t>HAFG25</t>
   </si>
   <si>
@@ -46,12 +46,12 @@
     <t>Humanitarian needs and response plan</t>
   </si>
   <si>
+    <t>2025-12-31</t>
+  </si>
+  <si>
     <t>2025</t>
   </si>
   <si>
-    <t>2025-12-31</t>
-  </si>
-  <si>
     <t>RIRNPAK25</t>
   </si>
   <si>
@@ -220,12 +220,12 @@
     <t>2024-01-01</t>
   </si>
   <si>
+    <t>2024-12-31</t>
+  </si>
+  <si>
     <t>2024</t>
   </si>
   <si>
-    <t>2024-12-31</t>
-  </si>
-  <si>
     <t>RAFG_RRP24</t>
   </si>
   <si>
@@ -424,12 +424,12 @@
     <t>2023-01-01</t>
   </si>
   <si>
+    <t>2023-12-31</t>
+  </si>
+  <si>
     <t>2023</t>
   </si>
   <si>
-    <t>2023-12-31</t>
-  </si>
-  <si>
     <t>RAFG23</t>
   </si>
   <si>
@@ -604,12 +604,12 @@
     <t>2022-01-01</t>
   </si>
   <si>
+    <t>2022-12-31</t>
+  </si>
+  <si>
     <t>2022</t>
   </si>
   <si>
-    <t>2022-12-31</t>
-  </si>
-  <si>
     <t>RAFG22</t>
   </si>
   <si>
@@ -808,12 +808,12 @@
     <t>2021-09-01</t>
   </si>
   <si>
+    <t>2021-12-31</t>
+  </si>
+  <si>
     <t>2021</t>
   </si>
   <si>
-    <t>2021-12-31</t>
-  </si>
-  <si>
     <t>HAFG21</t>
   </si>
   <si>
@@ -1012,12 +1012,12 @@
     <t>2020-01-01</t>
   </si>
   <si>
+    <t>2020-12-31</t>
+  </si>
+  <si>
     <t>2020</t>
   </si>
   <si>
-    <t>2020-12-31</t>
-  </si>
-  <si>
     <t>OBGD20</t>
   </si>
   <si>
@@ -1252,12 +1252,12 @@
     <t>2019-01-01</t>
   </si>
   <si>
+    <t>2019-12-31</t>
+  </si>
+  <si>
     <t>2019</t>
   </si>
   <si>
-    <t>2019-12-31</t>
-  </si>
-  <si>
     <t>RBGD19</t>
   </si>
   <si>
@@ -1384,12 +1384,12 @@
     <t>2018-01-01</t>
   </si>
   <si>
+    <t>2018-12-31</t>
+  </si>
+  <si>
     <t>2018</t>
   </si>
   <si>
-    <t>2018-12-31</t>
-  </si>
-  <si>
     <t>OBGD18</t>
   </si>
   <si>
@@ -1510,12 +1510,12 @@
     <t>2017-01-01</t>
   </si>
   <si>
+    <t>2017-12-31</t>
+  </si>
+  <si>
     <t>2017</t>
   </si>
   <si>
-    <t>2017-12-31</t>
-  </si>
-  <si>
     <t>HAFG17</t>
   </si>
   <si>
@@ -1687,12 +1687,12 @@
     <t>2016-01-01</t>
   </si>
   <si>
+    <t>2016-12-31</t>
+  </si>
+  <si>
     <t>2016</t>
   </si>
   <si>
-    <t>2016-12-31</t>
-  </si>
-  <si>
     <t>HAFG16</t>
   </si>
   <si>
@@ -1858,12 +1858,12 @@
     <t>Strategic response plan</t>
   </si>
   <si>
+    <t>2015-12-31</t>
+  </si>
+  <si>
     <t>2015</t>
   </si>
   <si>
-    <t>2015-12-31</t>
-  </si>
-  <si>
     <t>HBFA15</t>
   </si>
   <si>
@@ -1993,12 +1993,12 @@
     <t>2014-01-01</t>
   </si>
   <si>
+    <t>2014-12-31</t>
+  </si>
+  <si>
     <t>2014</t>
   </si>
   <si>
-    <t>2014-12-31</t>
-  </si>
-  <si>
     <t>HBFA1314</t>
   </si>
   <si>
@@ -2170,12 +2170,12 @@
     <t>Consolidated appeals process</t>
   </si>
   <si>
+    <t>2013-12-31</t>
+  </si>
+  <si>
     <t>2013</t>
   </si>
   <si>
-    <t>2013-12-31</t>
-  </si>
-  <si>
     <t>CBFA13</t>
   </si>
   <si>
@@ -2263,12 +2263,12 @@
     <t>2012-01-01</t>
   </si>
   <si>
+    <t>2012-12-31</t>
+  </si>
+  <si>
     <t>2012</t>
   </si>
   <si>
-    <t>2012-12-31</t>
-  </si>
-  <si>
     <t>CAFG1112</t>
   </si>
   <si>
@@ -2497,12 +2497,12 @@
     <t>2010-01-01</t>
   </si>
   <si>
+    <t>2010-12-31</t>
+  </si>
+  <si>
     <t>2010</t>
   </si>
   <si>
-    <t>2010-12-31</t>
-  </si>
-  <si>
     <t>OBFA1011</t>
   </si>
   <si>
@@ -2641,12 +2641,12 @@
     <t>2009-01-01</t>
   </si>
   <si>
+    <t>2009-12-31</t>
+  </si>
+  <si>
     <t>2009</t>
   </si>
   <si>
-    <t>2009-12-31</t>
-  </si>
-  <si>
     <t>FBFA0910</t>
   </si>
   <si>
@@ -2785,12 +2785,12 @@
     <t>2008-02-01</t>
   </si>
   <si>
+    <t>2008-06-30</t>
+  </si>
+  <si>
     <t>2008</t>
   </si>
   <si>
-    <t>2008-06-30</t>
-  </si>
-  <si>
     <t>OAFG0809</t>
   </si>
   <si>
@@ -2959,12 +2959,12 @@
     <t>2007-02-22</t>
   </si>
   <si>
+    <t>2007-08-21</t>
+  </si>
+  <si>
     <t>2007</t>
   </si>
   <si>
-    <t>2007-08-21</t>
-  </si>
-  <si>
     <t>FBFA0708</t>
   </si>
   <si>
@@ -3163,12 +3163,12 @@
     <t>2006-07-01</t>
   </si>
   <si>
+    <t>2006-12-31</t>
+  </si>
+  <si>
     <t>2006</t>
   </si>
   <si>
-    <t>2006-12-31</t>
-  </si>
-  <si>
     <t>CBDI06</t>
   </si>
   <si>
@@ -3325,12 +3325,12 @@
     <t>2005-04-01</t>
   </si>
   <si>
+    <t>2005-06-30</t>
+  </si>
+  <si>
     <t>2005</t>
   </si>
   <si>
-    <t>2005-06-30</t>
-  </si>
-  <si>
     <t>FBEN05</t>
   </si>
   <si>
@@ -3463,12 +3463,12 @@
     <t>2004-09-01</t>
   </si>
   <si>
+    <t>2004-12-31</t>
+  </si>
+  <si>
     <t>2004</t>
   </si>
   <si>
-    <t>2004-12-31</t>
-  </si>
-  <si>
     <t>CAGO04</t>
   </si>
   <si>
@@ -3616,12 +3616,12 @@
     <t>2003-01-01</t>
   </si>
   <si>
+    <t>2003-12-31</t>
+  </si>
+  <si>
     <t>2003</t>
   </si>
   <si>
-    <t>2003-12-31</t>
-  </si>
-  <si>
     <t>CAGO03</t>
   </si>
   <si>
@@ -3760,12 +3760,12 @@
     <t>2001-10-01</t>
   </si>
   <si>
+    <t>2002-12-31</t>
+  </si>
+  <si>
     <t>2002</t>
   </si>
   <si>
-    <t>2002-12-31</t>
-  </si>
-  <si>
     <t>CAGO02</t>
   </si>
   <si>
@@ -3868,12 +3868,12 @@
     <t>2001-01-01</t>
   </si>
   <si>
+    <t>2001-09-30</t>
+  </si>
+  <si>
     <t>2001</t>
   </si>
   <si>
-    <t>2001-09-30</t>
-  </si>
-  <si>
     <t>CAGO01</t>
   </si>
   <si>
@@ -3952,10 +3952,10 @@
     <t>2000-01-01</t>
   </si>
   <si>
+    <t>2000-12-31</t>
+  </si>
+  <si>
     <t>2000</t>
-  </si>
-  <si>
-    <t>2000-12-31</t>
   </si>
   <si>
     <t>CBDI00</t>
@@ -4427,10 +4427,10 @@
         <v>15</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F4" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -4627,10 +4627,10 @@
         <v>24</v>
       </c>
       <c r="E14" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F14" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -4647,10 +4647,10 @@
         <v>24</v>
       </c>
       <c r="E15" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F15" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -4687,10 +4687,10 @@
         <v>24</v>
       </c>
       <c r="E17" t="s">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="F17" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -4727,10 +4727,10 @@
         <v>24</v>
       </c>
       <c r="E19" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="F19" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -4827,10 +4827,10 @@
         <v>15</v>
       </c>
       <c r="E24" t="s">
-        <v>10</v>
+        <v>43</v>
       </c>
       <c r="F24" t="s">
-        <v>43</v>
+        <v>11</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -5187,10 +5187,10 @@
         <v>15</v>
       </c>
       <c r="E42" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="F42" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
     </row>
     <row r="43" spans="1:6">
@@ -5227,10 +5227,10 @@
         <v>24</v>
       </c>
       <c r="E44" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="F44" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
     </row>
     <row r="45" spans="1:6">
@@ -5247,10 +5247,10 @@
         <v>24</v>
       </c>
       <c r="E45" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F45" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
     </row>
     <row r="46" spans="1:6">
@@ -5607,10 +5607,10 @@
         <v>24</v>
       </c>
       <c r="E63" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="F63" t="s">
-        <v>91</v>
+        <v>69</v>
       </c>
     </row>
     <row r="64" spans="1:6">
@@ -5627,10 +5627,10 @@
         <v>24</v>
       </c>
       <c r="E64" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="F64" t="s">
-        <v>93</v>
+        <v>69</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -5687,10 +5687,10 @@
         <v>15</v>
       </c>
       <c r="E67" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="F67" t="s">
-        <v>93</v>
+        <v>69</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -6667,10 +6667,10 @@
         <v>15</v>
       </c>
       <c r="E116" t="s">
-        <v>136</v>
+        <v>160</v>
       </c>
       <c r="F116" t="s">
-        <v>160</v>
+        <v>137</v>
       </c>
     </row>
     <row r="117" spans="1:6">
@@ -6687,10 +6687,10 @@
         <v>15</v>
       </c>
       <c r="E117" t="s">
-        <v>136</v>
+        <v>163</v>
       </c>
       <c r="F117" t="s">
-        <v>163</v>
+        <v>137</v>
       </c>
     </row>
     <row r="118" spans="1:6">
@@ -6787,10 +6787,10 @@
         <v>19</v>
       </c>
       <c r="E122" t="s">
-        <v>136</v>
+        <v>163</v>
       </c>
       <c r="F122" t="s">
-        <v>163</v>
+        <v>137</v>
       </c>
     </row>
     <row r="123" spans="1:6">
@@ -6807,10 +6807,10 @@
         <v>15</v>
       </c>
       <c r="E123" t="s">
-        <v>136</v>
+        <v>160</v>
       </c>
       <c r="F123" t="s">
-        <v>160</v>
+        <v>137</v>
       </c>
     </row>
     <row r="124" spans="1:6">
@@ -6987,10 +6987,10 @@
         <v>13</v>
       </c>
       <c r="E132" t="s">
-        <v>136</v>
+        <v>180</v>
       </c>
       <c r="F132" t="s">
-        <v>180</v>
+        <v>137</v>
       </c>
     </row>
     <row r="133" spans="1:6">
@@ -7027,10 +7027,10 @@
         <v>24</v>
       </c>
       <c r="E134" t="s">
-        <v>136</v>
+        <v>160</v>
       </c>
       <c r="F134" t="s">
-        <v>160</v>
+        <v>137</v>
       </c>
     </row>
     <row r="135" spans="1:6">
@@ -7067,10 +7067,10 @@
         <v>24</v>
       </c>
       <c r="E136" t="s">
-        <v>136</v>
+        <v>160</v>
       </c>
       <c r="F136" t="s">
-        <v>160</v>
+        <v>137</v>
       </c>
     </row>
     <row r="137" spans="1:6">
@@ -7367,10 +7367,10 @@
         <v>15</v>
       </c>
       <c r="E151" t="s">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="F151" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
     </row>
     <row r="152" spans="1:6">
@@ -7467,10 +7467,10 @@
         <v>24</v>
       </c>
       <c r="E156" t="s">
-        <v>196</v>
+        <v>213</v>
       </c>
       <c r="F156" t="s">
-        <v>213</v>
+        <v>197</v>
       </c>
     </row>
     <row r="157" spans="1:6">
@@ -7567,10 +7567,10 @@
         <v>24</v>
       </c>
       <c r="E161" t="s">
-        <v>196</v>
+        <v>219</v>
       </c>
       <c r="F161" t="s">
-        <v>219</v>
+        <v>197</v>
       </c>
     </row>
     <row r="162" spans="1:6">
@@ -7647,10 +7647,10 @@
         <v>24</v>
       </c>
       <c r="E165" t="s">
-        <v>196</v>
+        <v>225</v>
       </c>
       <c r="F165" t="s">
-        <v>225</v>
+        <v>197</v>
       </c>
     </row>
     <row r="166" spans="1:6">
@@ -7687,10 +7687,10 @@
         <v>24</v>
       </c>
       <c r="E167" t="s">
-        <v>196</v>
+        <v>229</v>
       </c>
       <c r="F167" t="s">
-        <v>229</v>
+        <v>197</v>
       </c>
     </row>
     <row r="168" spans="1:6">
@@ -7827,10 +7827,10 @@
         <v>15</v>
       </c>
       <c r="E174" t="s">
-        <v>196</v>
+        <v>238</v>
       </c>
       <c r="F174" t="s">
-        <v>238</v>
+        <v>197</v>
       </c>
     </row>
     <row r="175" spans="1:6">
@@ -7847,10 +7847,10 @@
         <v>15</v>
       </c>
       <c r="E175" t="s">
-        <v>196</v>
+        <v>241</v>
       </c>
       <c r="F175" t="s">
-        <v>241</v>
+        <v>197</v>
       </c>
     </row>
     <row r="176" spans="1:6">
@@ -8147,10 +8147,10 @@
         <v>13</v>
       </c>
       <c r="E190" t="s">
-        <v>196</v>
+        <v>259</v>
       </c>
       <c r="F190" t="s">
-        <v>259</v>
+        <v>197</v>
       </c>
     </row>
     <row r="191" spans="1:6">
@@ -8467,10 +8467,10 @@
         <v>19</v>
       </c>
       <c r="E206" t="s">
-        <v>264</v>
+        <v>196</v>
       </c>
       <c r="F206" t="s">
-        <v>197</v>
+        <v>265</v>
       </c>
     </row>
     <row r="207" spans="1:6">
@@ -8487,10 +8487,10 @@
         <v>24</v>
       </c>
       <c r="E207" t="s">
-        <v>264</v>
+        <v>283</v>
       </c>
       <c r="F207" t="s">
-        <v>283</v>
+        <v>265</v>
       </c>
     </row>
     <row r="208" spans="1:6">
@@ -8547,10 +8547,10 @@
         <v>19</v>
       </c>
       <c r="E210" t="s">
-        <v>264</v>
+        <v>196</v>
       </c>
       <c r="F210" t="s">
-        <v>197</v>
+        <v>265</v>
       </c>
     </row>
     <row r="211" spans="1:6">
@@ -8567,10 +8567,10 @@
         <v>24</v>
       </c>
       <c r="E211" t="s">
-        <v>264</v>
+        <v>289</v>
       </c>
       <c r="F211" t="s">
-        <v>289</v>
+        <v>265</v>
       </c>
     </row>
     <row r="212" spans="1:6">
@@ -8607,10 +8607,10 @@
         <v>24</v>
       </c>
       <c r="E213" t="s">
-        <v>264</v>
+        <v>293</v>
       </c>
       <c r="F213" t="s">
-        <v>293</v>
+        <v>265</v>
       </c>
     </row>
     <row r="214" spans="1:6">
@@ -8647,10 +8647,10 @@
         <v>19</v>
       </c>
       <c r="E215" t="s">
-        <v>264</v>
+        <v>196</v>
       </c>
       <c r="F215" t="s">
-        <v>197</v>
+        <v>265</v>
       </c>
     </row>
     <row r="216" spans="1:6">
@@ -8707,10 +8707,10 @@
         <v>15</v>
       </c>
       <c r="E218" t="s">
-        <v>264</v>
+        <v>301</v>
       </c>
       <c r="F218" t="s">
-        <v>301</v>
+        <v>265</v>
       </c>
     </row>
     <row r="219" spans="1:6">
@@ -8747,10 +8747,10 @@
         <v>24</v>
       </c>
       <c r="E220" t="s">
-        <v>264</v>
+        <v>225</v>
       </c>
       <c r="F220" t="s">
-        <v>225</v>
+        <v>265</v>
       </c>
     </row>
     <row r="221" spans="1:6">
@@ -9427,10 +9427,10 @@
         <v>19</v>
       </c>
       <c r="E254" t="s">
-        <v>332</v>
+        <v>267</v>
       </c>
       <c r="F254" t="s">
-        <v>267</v>
+        <v>333</v>
       </c>
     </row>
     <row r="255" spans="1:6">
@@ -9587,10 +9587,10 @@
         <v>24</v>
       </c>
       <c r="E262" t="s">
-        <v>332</v>
+        <v>356</v>
       </c>
       <c r="F262" t="s">
-        <v>356</v>
+        <v>333</v>
       </c>
     </row>
     <row r="263" spans="1:6">
@@ -9887,10 +9887,10 @@
         <v>24</v>
       </c>
       <c r="E277" t="s">
-        <v>332</v>
+        <v>374</v>
       </c>
       <c r="F277" t="s">
-        <v>374</v>
+        <v>333</v>
       </c>
     </row>
     <row r="278" spans="1:6">
@@ -9927,10 +9927,10 @@
         <v>24</v>
       </c>
       <c r="E279" t="s">
-        <v>332</v>
+        <v>378</v>
       </c>
       <c r="F279" t="s">
-        <v>378</v>
+        <v>333</v>
       </c>
     </row>
     <row r="280" spans="1:6">
@@ -10487,10 +10487,10 @@
         <v>15</v>
       </c>
       <c r="E307" t="s">
-        <v>332</v>
+        <v>356</v>
       </c>
       <c r="F307" t="s">
-        <v>356</v>
+        <v>333</v>
       </c>
     </row>
     <row r="308" spans="1:6">
@@ -10847,10 +10847,10 @@
         <v>24</v>
       </c>
       <c r="E325" t="s">
-        <v>412</v>
+        <v>430</v>
       </c>
       <c r="F325" t="s">
-        <v>430</v>
+        <v>413</v>
       </c>
     </row>
     <row r="326" spans="1:6">
@@ -10967,10 +10967,10 @@
         <v>19</v>
       </c>
       <c r="E331" t="s">
-        <v>412</v>
+        <v>437</v>
       </c>
       <c r="F331" t="s">
-        <v>437</v>
+        <v>413</v>
       </c>
     </row>
     <row r="332" spans="1:6">
@@ -11207,10 +11207,10 @@
         <v>24</v>
       </c>
       <c r="E343" t="s">
-        <v>412</v>
+        <v>451</v>
       </c>
       <c r="F343" t="s">
-        <v>451</v>
+        <v>413</v>
       </c>
     </row>
     <row r="344" spans="1:6">
@@ -11227,10 +11227,10 @@
         <v>24</v>
       </c>
       <c r="E344" t="s">
-        <v>412</v>
+        <v>451</v>
       </c>
       <c r="F344" t="s">
-        <v>451</v>
+        <v>413</v>
       </c>
     </row>
     <row r="345" spans="1:6">
@@ -11767,10 +11767,10 @@
         <v>19</v>
       </c>
       <c r="E371" t="s">
-        <v>456</v>
+        <v>487</v>
       </c>
       <c r="F371" t="s">
-        <v>487</v>
+        <v>457</v>
       </c>
     </row>
     <row r="372" spans="1:6">
@@ -11787,10 +11787,10 @@
         <v>19</v>
       </c>
       <c r="E372" t="s">
-        <v>456</v>
+        <v>490</v>
       </c>
       <c r="F372" t="s">
-        <v>490</v>
+        <v>457</v>
       </c>
     </row>
     <row r="373" spans="1:6">
@@ -11827,10 +11827,10 @@
         <v>19</v>
       </c>
       <c r="E374" t="s">
-        <v>456</v>
+        <v>490</v>
       </c>
       <c r="F374" t="s">
-        <v>490</v>
+        <v>457</v>
       </c>
     </row>
     <row r="375" spans="1:6">
@@ -12127,10 +12127,10 @@
         <v>24</v>
       </c>
       <c r="E389" t="s">
-        <v>498</v>
+        <v>515</v>
       </c>
       <c r="F389" t="s">
-        <v>515</v>
+        <v>499</v>
       </c>
     </row>
     <row r="390" spans="1:6">
@@ -12247,10 +12247,10 @@
         <v>24</v>
       </c>
       <c r="E395" t="s">
-        <v>498</v>
+        <v>524</v>
       </c>
       <c r="F395" t="s">
-        <v>524</v>
+        <v>499</v>
       </c>
     </row>
     <row r="396" spans="1:6">
@@ -12287,10 +12287,10 @@
         <v>24</v>
       </c>
       <c r="E397" t="s">
-        <v>498</v>
+        <v>528</v>
       </c>
       <c r="F397" t="s">
-        <v>528</v>
+        <v>499</v>
       </c>
     </row>
     <row r="398" spans="1:6">
@@ -12347,10 +12347,10 @@
         <v>24</v>
       </c>
       <c r="E400" t="s">
-        <v>498</v>
+        <v>533</v>
       </c>
       <c r="F400" t="s">
-        <v>533</v>
+        <v>499</v>
       </c>
     </row>
     <row r="401" spans="1:6">
@@ -12467,10 +12467,10 @@
         <v>24</v>
       </c>
       <c r="E406" t="s">
-        <v>498</v>
+        <v>541</v>
       </c>
       <c r="F406" t="s">
-        <v>541</v>
+        <v>499</v>
       </c>
     </row>
     <row r="407" spans="1:6">
@@ -12947,10 +12947,10 @@
         <v>24</v>
       </c>
       <c r="E430" t="s">
-        <v>557</v>
+        <v>573</v>
       </c>
       <c r="F430" t="s">
-        <v>573</v>
+        <v>558</v>
       </c>
     </row>
     <row r="431" spans="1:6">
@@ -12967,10 +12967,10 @@
         <v>24</v>
       </c>
       <c r="E431" t="s">
-        <v>557</v>
+        <v>576</v>
       </c>
       <c r="F431" t="s">
-        <v>576</v>
+        <v>558</v>
       </c>
     </row>
     <row r="432" spans="1:6">
@@ -13187,10 +13187,10 @@
         <v>24</v>
       </c>
       <c r="E442" t="s">
-        <v>557</v>
+        <v>592</v>
       </c>
       <c r="F442" t="s">
-        <v>592</v>
+        <v>558</v>
       </c>
     </row>
     <row r="443" spans="1:6">
@@ -13507,10 +13507,10 @@
         <v>19</v>
       </c>
       <c r="E458" t="s">
-        <v>557</v>
+        <v>610</v>
       </c>
       <c r="F458" t="s">
-        <v>610</v>
+        <v>558</v>
       </c>
     </row>
     <row r="459" spans="1:6">
@@ -13707,10 +13707,10 @@
         <v>24</v>
       </c>
       <c r="E468" t="s">
-        <v>614</v>
+        <v>626</v>
       </c>
       <c r="F468" t="s">
-        <v>626</v>
+        <v>615</v>
       </c>
     </row>
     <row r="469" spans="1:6">
@@ -13747,10 +13747,10 @@
         <v>24</v>
       </c>
       <c r="E470" t="s">
-        <v>614</v>
+        <v>626</v>
       </c>
       <c r="F470" t="s">
-        <v>626</v>
+        <v>615</v>
       </c>
     </row>
     <row r="471" spans="1:6">
@@ -13767,10 +13767,10 @@
         <v>24</v>
       </c>
       <c r="E471" t="s">
-        <v>614</v>
+        <v>633</v>
       </c>
       <c r="F471" t="s">
-        <v>633</v>
+        <v>615</v>
       </c>
     </row>
     <row r="472" spans="1:6">
@@ -13807,10 +13807,10 @@
         <v>24</v>
       </c>
       <c r="E473" t="s">
-        <v>614</v>
+        <v>637</v>
       </c>
       <c r="F473" t="s">
-        <v>637</v>
+        <v>615</v>
       </c>
     </row>
     <row r="474" spans="1:6">
@@ -13887,10 +13887,10 @@
         <v>24</v>
       </c>
       <c r="E477" t="s">
-        <v>614</v>
+        <v>626</v>
       </c>
       <c r="F477" t="s">
-        <v>626</v>
+        <v>615</v>
       </c>
     </row>
     <row r="478" spans="1:6">
@@ -14287,10 +14287,10 @@
         <v>19</v>
       </c>
       <c r="E497" t="s">
-        <v>659</v>
+        <v>667</v>
       </c>
       <c r="F497" t="s">
-        <v>667</v>
+        <v>660</v>
       </c>
     </row>
     <row r="498" spans="1:6">
@@ -14327,10 +14327,10 @@
         <v>13</v>
       </c>
       <c r="E499" t="s">
-        <v>659</v>
+        <v>670</v>
       </c>
       <c r="F499" t="s">
-        <v>670</v>
+        <v>660</v>
       </c>
     </row>
     <row r="500" spans="1:6">
@@ -14347,10 +14347,10 @@
         <v>15</v>
       </c>
       <c r="E500" t="s">
-        <v>659</v>
+        <v>670</v>
       </c>
       <c r="F500" t="s">
-        <v>670</v>
+        <v>660</v>
       </c>
     </row>
     <row r="501" spans="1:6">
@@ -14587,10 +14587,10 @@
         <v>24</v>
       </c>
       <c r="E512" t="s">
-        <v>659</v>
+        <v>687</v>
       </c>
       <c r="F512" t="s">
-        <v>687</v>
+        <v>660</v>
       </c>
     </row>
     <row r="513" spans="1:6">
@@ -14607,10 +14607,10 @@
         <v>613</v>
       </c>
       <c r="E513" t="s">
-        <v>659</v>
+        <v>690</v>
       </c>
       <c r="F513" t="s">
-        <v>690</v>
+        <v>660</v>
       </c>
     </row>
     <row r="514" spans="1:6">
@@ -14627,10 +14627,10 @@
         <v>19</v>
       </c>
       <c r="E514" t="s">
-        <v>659</v>
+        <v>692</v>
       </c>
       <c r="F514" t="s">
-        <v>692</v>
+        <v>660</v>
       </c>
     </row>
     <row r="515" spans="1:6">
@@ -14647,10 +14647,10 @@
         <v>24</v>
       </c>
       <c r="E515" t="s">
-        <v>659</v>
+        <v>695</v>
       </c>
       <c r="F515" t="s">
-        <v>695</v>
+        <v>660</v>
       </c>
     </row>
     <row r="516" spans="1:6">
@@ -14727,10 +14727,10 @@
         <v>19</v>
       </c>
       <c r="E519" t="s">
-        <v>659</v>
+        <v>701</v>
       </c>
       <c r="F519" t="s">
-        <v>701</v>
+        <v>660</v>
       </c>
     </row>
     <row r="520" spans="1:6">
@@ -15067,10 +15067,10 @@
         <v>717</v>
       </c>
       <c r="E536" t="s">
-        <v>718</v>
+        <v>726</v>
       </c>
       <c r="F536" t="s">
-        <v>726</v>
+        <v>719</v>
       </c>
     </row>
     <row r="537" spans="1:6">
@@ -15267,10 +15267,10 @@
         <v>717</v>
       </c>
       <c r="E546" t="s">
-        <v>718</v>
+        <v>695</v>
       </c>
       <c r="F546" t="s">
-        <v>695</v>
+        <v>719</v>
       </c>
     </row>
     <row r="547" spans="1:6">
@@ -15367,10 +15367,10 @@
         <v>13</v>
       </c>
       <c r="E551" t="s">
-        <v>718</v>
+        <v>744</v>
       </c>
       <c r="F551" t="s">
-        <v>744</v>
+        <v>719</v>
       </c>
     </row>
     <row r="552" spans="1:6">
@@ -15547,10 +15547,10 @@
         <v>717</v>
       </c>
       <c r="E560" t="s">
-        <v>749</v>
+        <v>759</v>
       </c>
       <c r="F560" t="s">
-        <v>759</v>
+        <v>750</v>
       </c>
     </row>
     <row r="561" spans="1:6">
@@ -15627,10 +15627,10 @@
         <v>24</v>
       </c>
       <c r="E564" t="s">
-        <v>749</v>
+        <v>765</v>
       </c>
       <c r="F564" t="s">
-        <v>765</v>
+        <v>750</v>
       </c>
     </row>
     <row r="565" spans="1:6">
@@ -15727,10 +15727,10 @@
         <v>15</v>
       </c>
       <c r="E569" t="s">
-        <v>749</v>
+        <v>772</v>
       </c>
       <c r="F569" t="s">
-        <v>772</v>
+        <v>750</v>
       </c>
     </row>
     <row r="570" spans="1:6">
@@ -15847,10 +15847,10 @@
         <v>717</v>
       </c>
       <c r="E575" t="s">
-        <v>749</v>
+        <v>780</v>
       </c>
       <c r="F575" t="s">
-        <v>780</v>
+        <v>750</v>
       </c>
     </row>
     <row r="576" spans="1:6">
@@ -15927,10 +15927,10 @@
         <v>717</v>
       </c>
       <c r="E579" t="s">
+        <v>718</v>
+      </c>
+      <c r="F579" t="s">
         <v>786</v>
-      </c>
-      <c r="F579" t="s">
-        <v>719</v>
       </c>
     </row>
     <row r="580" spans="1:6">
@@ -15947,10 +15947,10 @@
         <v>717</v>
       </c>
       <c r="E580" t="s">
+        <v>788</v>
+      </c>
+      <c r="F580" t="s">
         <v>786</v>
-      </c>
-      <c r="F580" t="s">
-        <v>788</v>
       </c>
     </row>
     <row r="581" spans="1:6">
@@ -15967,10 +15967,10 @@
         <v>717</v>
       </c>
       <c r="E581" t="s">
+        <v>788</v>
+      </c>
+      <c r="F581" t="s">
         <v>786</v>
-      </c>
-      <c r="F581" t="s">
-        <v>788</v>
       </c>
     </row>
     <row r="582" spans="1:6">
@@ -15987,10 +15987,10 @@
         <v>717</v>
       </c>
       <c r="E582" t="s">
+        <v>788</v>
+      </c>
+      <c r="F582" t="s">
         <v>786</v>
-      </c>
-      <c r="F582" t="s">
-        <v>788</v>
       </c>
     </row>
     <row r="583" spans="1:6">
@@ -16007,10 +16007,10 @@
         <v>717</v>
       </c>
       <c r="E583" t="s">
+        <v>749</v>
+      </c>
+      <c r="F583" t="s">
         <v>786</v>
-      </c>
-      <c r="F583" t="s">
-        <v>750</v>
       </c>
     </row>
     <row r="584" spans="1:6">
@@ -16027,10 +16027,10 @@
         <v>717</v>
       </c>
       <c r="E584" t="s">
+        <v>788</v>
+      </c>
+      <c r="F584" t="s">
         <v>786</v>
-      </c>
-      <c r="F584" t="s">
-        <v>788</v>
       </c>
     </row>
     <row r="585" spans="1:6">
@@ -16047,10 +16047,10 @@
         <v>24</v>
       </c>
       <c r="E585" t="s">
+        <v>796</v>
+      </c>
+      <c r="F585" t="s">
         <v>786</v>
-      </c>
-      <c r="F585" t="s">
-        <v>796</v>
       </c>
     </row>
     <row r="586" spans="1:6">
@@ -16067,10 +16067,10 @@
         <v>717</v>
       </c>
       <c r="E586" t="s">
+        <v>788</v>
+      </c>
+      <c r="F586" t="s">
         <v>786</v>
-      </c>
-      <c r="F586" t="s">
-        <v>788</v>
       </c>
     </row>
     <row r="587" spans="1:6">
@@ -16087,10 +16087,10 @@
         <v>15</v>
       </c>
       <c r="E587" t="s">
+        <v>788</v>
+      </c>
+      <c r="F587" t="s">
         <v>786</v>
-      </c>
-      <c r="F587" t="s">
-        <v>788</v>
       </c>
     </row>
     <row r="588" spans="1:6">
@@ -16107,10 +16107,10 @@
         <v>15</v>
       </c>
       <c r="E588" t="s">
+        <v>788</v>
+      </c>
+      <c r="F588" t="s">
         <v>786</v>
-      </c>
-      <c r="F588" t="s">
-        <v>788</v>
       </c>
     </row>
     <row r="589" spans="1:6">
@@ -16127,10 +16127,10 @@
         <v>24</v>
       </c>
       <c r="E589" t="s">
+        <v>804</v>
+      </c>
+      <c r="F589" t="s">
         <v>786</v>
-      </c>
-      <c r="F589" t="s">
-        <v>804</v>
       </c>
     </row>
     <row r="590" spans="1:6">
@@ -16147,10 +16147,10 @@
         <v>24</v>
       </c>
       <c r="E590" t="s">
+        <v>807</v>
+      </c>
+      <c r="F590" t="s">
         <v>786</v>
-      </c>
-      <c r="F590" t="s">
-        <v>807</v>
       </c>
     </row>
     <row r="591" spans="1:6">
@@ -16167,10 +16167,10 @@
         <v>717</v>
       </c>
       <c r="E591" t="s">
+        <v>788</v>
+      </c>
+      <c r="F591" t="s">
         <v>786</v>
-      </c>
-      <c r="F591" t="s">
-        <v>788</v>
       </c>
     </row>
     <row r="592" spans="1:6">
@@ -16187,10 +16187,10 @@
         <v>24</v>
       </c>
       <c r="E592" t="s">
+        <v>811</v>
+      </c>
+      <c r="F592" t="s">
         <v>786</v>
-      </c>
-      <c r="F592" t="s">
-        <v>811</v>
       </c>
     </row>
     <row r="593" spans="1:6">
@@ -16207,10 +16207,10 @@
         <v>13</v>
       </c>
       <c r="E593" t="s">
+        <v>788</v>
+      </c>
+      <c r="F593" t="s">
         <v>786</v>
-      </c>
-      <c r="F593" t="s">
-        <v>788</v>
       </c>
     </row>
     <row r="594" spans="1:6">
@@ -16227,10 +16227,10 @@
         <v>717</v>
       </c>
       <c r="E594" t="s">
+        <v>788</v>
+      </c>
+      <c r="F594" t="s">
         <v>786</v>
-      </c>
-      <c r="F594" t="s">
-        <v>788</v>
       </c>
     </row>
     <row r="595" spans="1:6">
@@ -16247,10 +16247,10 @@
         <v>717</v>
       </c>
       <c r="E595" t="s">
+        <v>788</v>
+      </c>
+      <c r="F595" t="s">
         <v>786</v>
-      </c>
-      <c r="F595" t="s">
-        <v>788</v>
       </c>
     </row>
     <row r="596" spans="1:6">
@@ -16267,10 +16267,10 @@
         <v>24</v>
       </c>
       <c r="E596" t="s">
+        <v>788</v>
+      </c>
+      <c r="F596" t="s">
         <v>786</v>
-      </c>
-      <c r="F596" t="s">
-        <v>788</v>
       </c>
     </row>
     <row r="597" spans="1:6">
@@ -16287,10 +16287,10 @@
         <v>15</v>
       </c>
       <c r="E597" t="s">
+        <v>788</v>
+      </c>
+      <c r="F597" t="s">
         <v>786</v>
-      </c>
-      <c r="F597" t="s">
-        <v>788</v>
       </c>
     </row>
     <row r="598" spans="1:6">
@@ -16307,10 +16307,10 @@
         <v>717</v>
       </c>
       <c r="E598" t="s">
+        <v>820</v>
+      </c>
+      <c r="F598" t="s">
         <v>786</v>
-      </c>
-      <c r="F598" t="s">
-        <v>820</v>
       </c>
     </row>
     <row r="599" spans="1:6">
@@ -16327,10 +16327,10 @@
         <v>13</v>
       </c>
       <c r="E599" t="s">
+        <v>788</v>
+      </c>
+      <c r="F599" t="s">
         <v>786</v>
-      </c>
-      <c r="F599" t="s">
-        <v>788</v>
       </c>
     </row>
     <row r="600" spans="1:6">
@@ -16347,10 +16347,10 @@
         <v>717</v>
       </c>
       <c r="E600" t="s">
+        <v>788</v>
+      </c>
+      <c r="F600" t="s">
         <v>786</v>
-      </c>
-      <c r="F600" t="s">
-        <v>788</v>
       </c>
     </row>
     <row r="601" spans="1:6">
@@ -16367,10 +16367,10 @@
         <v>717</v>
       </c>
       <c r="E601" t="s">
+        <v>788</v>
+      </c>
+      <c r="F601" t="s">
         <v>786</v>
-      </c>
-      <c r="F601" t="s">
-        <v>788</v>
       </c>
     </row>
     <row r="602" spans="1:6">
@@ -16387,10 +16387,10 @@
         <v>717</v>
       </c>
       <c r="E602" t="s">
+        <v>788</v>
+      </c>
+      <c r="F602" t="s">
         <v>786</v>
-      </c>
-      <c r="F602" t="s">
-        <v>788</v>
       </c>
     </row>
     <row r="603" spans="1:6">
@@ -16427,10 +16427,10 @@
         <v>15</v>
       </c>
       <c r="E604" t="s">
-        <v>827</v>
+        <v>831</v>
       </c>
       <c r="F604" t="s">
-        <v>831</v>
+        <v>828</v>
       </c>
     </row>
     <row r="605" spans="1:6">
@@ -16507,10 +16507,10 @@
         <v>24</v>
       </c>
       <c r="E608" t="s">
-        <v>827</v>
+        <v>837</v>
       </c>
       <c r="F608" t="s">
-        <v>837</v>
+        <v>828</v>
       </c>
     </row>
     <row r="609" spans="1:6">
@@ -16527,10 +16527,10 @@
         <v>24</v>
       </c>
       <c r="E609" t="s">
-        <v>827</v>
+        <v>840</v>
       </c>
       <c r="F609" t="s">
-        <v>840</v>
+        <v>828</v>
       </c>
     </row>
     <row r="610" spans="1:6">
@@ -16547,10 +16547,10 @@
         <v>717</v>
       </c>
       <c r="E610" t="s">
-        <v>827</v>
+        <v>843</v>
       </c>
       <c r="F610" t="s">
-        <v>843</v>
+        <v>828</v>
       </c>
     </row>
     <row r="611" spans="1:6">
@@ -16647,10 +16647,10 @@
         <v>24</v>
       </c>
       <c r="E615" t="s">
-        <v>827</v>
+        <v>851</v>
       </c>
       <c r="F615" t="s">
-        <v>851</v>
+        <v>828</v>
       </c>
     </row>
     <row r="616" spans="1:6">
@@ -16667,10 +16667,10 @@
         <v>717</v>
       </c>
       <c r="E616" t="s">
-        <v>827</v>
+        <v>813</v>
       </c>
       <c r="F616" t="s">
-        <v>813</v>
+        <v>828</v>
       </c>
     </row>
     <row r="617" spans="1:6">
@@ -16707,10 +16707,10 @@
         <v>24</v>
       </c>
       <c r="E618" t="s">
-        <v>827</v>
+        <v>856</v>
       </c>
       <c r="F618" t="s">
-        <v>856</v>
+        <v>828</v>
       </c>
     </row>
     <row r="619" spans="1:6">
@@ -17027,10 +17027,10 @@
         <v>24</v>
       </c>
       <c r="E634" t="s">
-        <v>875</v>
+        <v>879</v>
       </c>
       <c r="F634" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
     </row>
     <row r="635" spans="1:6">
@@ -17107,10 +17107,10 @@
         <v>717</v>
       </c>
       <c r="E638" t="s">
-        <v>875</v>
+        <v>884</v>
       </c>
       <c r="F638" t="s">
-        <v>884</v>
+        <v>876</v>
       </c>
     </row>
     <row r="639" spans="1:6">
@@ -17207,10 +17207,10 @@
         <v>24</v>
       </c>
       <c r="E643" t="s">
-        <v>875</v>
+        <v>891</v>
       </c>
       <c r="F643" t="s">
-        <v>891</v>
+        <v>876</v>
       </c>
     </row>
     <row r="644" spans="1:6">
@@ -17227,10 +17227,10 @@
         <v>24</v>
       </c>
       <c r="E644" t="s">
-        <v>875</v>
+        <v>894</v>
       </c>
       <c r="F644" t="s">
-        <v>894</v>
+        <v>876</v>
       </c>
     </row>
     <row r="645" spans="1:6">
@@ -17247,10 +17247,10 @@
         <v>24</v>
       </c>
       <c r="E645" t="s">
-        <v>875</v>
+        <v>897</v>
       </c>
       <c r="F645" t="s">
-        <v>897</v>
+        <v>876</v>
       </c>
     </row>
     <row r="646" spans="1:6">
@@ -17307,10 +17307,10 @@
         <v>24</v>
       </c>
       <c r="E648" t="s">
-        <v>875</v>
+        <v>903</v>
       </c>
       <c r="F648" t="s">
-        <v>903</v>
+        <v>876</v>
       </c>
     </row>
     <row r="649" spans="1:6">
@@ -17387,10 +17387,10 @@
         <v>15</v>
       </c>
       <c r="E652" t="s">
-        <v>875</v>
+        <v>909</v>
       </c>
       <c r="F652" t="s">
-        <v>909</v>
+        <v>876</v>
       </c>
     </row>
     <row r="653" spans="1:6">
@@ -17587,10 +17587,10 @@
         <v>15</v>
       </c>
       <c r="E662" t="s">
-        <v>923</v>
+        <v>927</v>
       </c>
       <c r="F662" t="s">
-        <v>927</v>
+        <v>924</v>
       </c>
     </row>
     <row r="663" spans="1:6">
@@ -17607,10 +17607,10 @@
         <v>24</v>
       </c>
       <c r="E663" t="s">
-        <v>923</v>
+        <v>929</v>
       </c>
       <c r="F663" t="s">
-        <v>929</v>
+        <v>924</v>
       </c>
     </row>
     <row r="664" spans="1:6">
@@ -17627,10 +17627,10 @@
         <v>717</v>
       </c>
       <c r="E664" t="s">
-        <v>923</v>
+        <v>932</v>
       </c>
       <c r="F664" t="s">
-        <v>932</v>
+        <v>924</v>
       </c>
     </row>
     <row r="665" spans="1:6">
@@ -17647,10 +17647,10 @@
         <v>717</v>
       </c>
       <c r="E665" t="s">
-        <v>923</v>
+        <v>932</v>
       </c>
       <c r="F665" t="s">
-        <v>932</v>
+        <v>924</v>
       </c>
     </row>
     <row r="666" spans="1:6">
@@ -17667,10 +17667,10 @@
         <v>15</v>
       </c>
       <c r="E666" t="s">
-        <v>923</v>
+        <v>875</v>
       </c>
       <c r="F666" t="s">
-        <v>876</v>
+        <v>924</v>
       </c>
     </row>
     <row r="667" spans="1:6">
@@ -17687,10 +17687,10 @@
         <v>717</v>
       </c>
       <c r="E667" t="s">
-        <v>923</v>
+        <v>932</v>
       </c>
       <c r="F667" t="s">
-        <v>932</v>
+        <v>924</v>
       </c>
     </row>
     <row r="668" spans="1:6">
@@ -17707,10 +17707,10 @@
         <v>717</v>
       </c>
       <c r="E668" t="s">
-        <v>923</v>
+        <v>932</v>
       </c>
       <c r="F668" t="s">
-        <v>932</v>
+        <v>924</v>
       </c>
     </row>
     <row r="669" spans="1:6">
@@ -17727,10 +17727,10 @@
         <v>15</v>
       </c>
       <c r="E669" t="s">
-        <v>923</v>
+        <v>939</v>
       </c>
       <c r="F669" t="s">
-        <v>939</v>
+        <v>924</v>
       </c>
     </row>
     <row r="670" spans="1:6">
@@ -17747,10 +17747,10 @@
         <v>24</v>
       </c>
       <c r="E670" t="s">
-        <v>923</v>
+        <v>942</v>
       </c>
       <c r="F670" t="s">
-        <v>942</v>
+        <v>924</v>
       </c>
     </row>
     <row r="671" spans="1:6">
@@ -17767,10 +17767,10 @@
         <v>24</v>
       </c>
       <c r="E671" t="s">
-        <v>923</v>
+        <v>944</v>
       </c>
       <c r="F671" t="s">
-        <v>944</v>
+        <v>924</v>
       </c>
     </row>
     <row r="672" spans="1:6">
@@ -17787,10 +17787,10 @@
         <v>24</v>
       </c>
       <c r="E672" t="s">
-        <v>923</v>
+        <v>947</v>
       </c>
       <c r="F672" t="s">
-        <v>947</v>
+        <v>924</v>
       </c>
     </row>
     <row r="673" spans="1:6">
@@ -17807,10 +17807,10 @@
         <v>717</v>
       </c>
       <c r="E673" t="s">
-        <v>923</v>
+        <v>932</v>
       </c>
       <c r="F673" t="s">
-        <v>932</v>
+        <v>924</v>
       </c>
     </row>
     <row r="674" spans="1:6">
@@ -17827,10 +17827,10 @@
         <v>24</v>
       </c>
       <c r="E674" t="s">
-        <v>923</v>
+        <v>926</v>
       </c>
       <c r="F674" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
     </row>
     <row r="675" spans="1:6">
@@ -17847,10 +17847,10 @@
         <v>24</v>
       </c>
       <c r="E675" t="s">
-        <v>923</v>
+        <v>952</v>
       </c>
       <c r="F675" t="s">
-        <v>952</v>
+        <v>924</v>
       </c>
     </row>
     <row r="676" spans="1:6">
@@ -17867,10 +17867,10 @@
         <v>15</v>
       </c>
       <c r="E676" t="s">
-        <v>923</v>
+        <v>954</v>
       </c>
       <c r="F676" t="s">
-        <v>954</v>
+        <v>924</v>
       </c>
     </row>
     <row r="677" spans="1:6">
@@ -17887,10 +17887,10 @@
         <v>15</v>
       </c>
       <c r="E677" t="s">
-        <v>923</v>
+        <v>932</v>
       </c>
       <c r="F677" t="s">
-        <v>932</v>
+        <v>924</v>
       </c>
     </row>
     <row r="678" spans="1:6">
@@ -17907,10 +17907,10 @@
         <v>717</v>
       </c>
       <c r="E678" t="s">
-        <v>923</v>
+        <v>932</v>
       </c>
       <c r="F678" t="s">
-        <v>932</v>
+        <v>924</v>
       </c>
     </row>
     <row r="679" spans="1:6">
@@ -17947,10 +17947,10 @@
         <v>24</v>
       </c>
       <c r="E680" t="s">
-        <v>923</v>
+        <v>961</v>
       </c>
       <c r="F680" t="s">
-        <v>961</v>
+        <v>924</v>
       </c>
     </row>
     <row r="681" spans="1:6">
@@ -17967,10 +17967,10 @@
         <v>15</v>
       </c>
       <c r="E681" t="s">
-        <v>923</v>
+        <v>932</v>
       </c>
       <c r="F681" t="s">
-        <v>932</v>
+        <v>924</v>
       </c>
     </row>
     <row r="682" spans="1:6">
@@ -17987,10 +17987,10 @@
         <v>15</v>
       </c>
       <c r="E682" t="s">
-        <v>923</v>
+        <v>944</v>
       </c>
       <c r="F682" t="s">
-        <v>944</v>
+        <v>924</v>
       </c>
     </row>
     <row r="683" spans="1:6">
@@ -18007,10 +18007,10 @@
         <v>717</v>
       </c>
       <c r="E683" t="s">
-        <v>923</v>
+        <v>932</v>
       </c>
       <c r="F683" t="s">
-        <v>932</v>
+        <v>924</v>
       </c>
     </row>
     <row r="684" spans="1:6">
@@ -18027,10 +18027,10 @@
         <v>13</v>
       </c>
       <c r="E684" t="s">
-        <v>923</v>
+        <v>966</v>
       </c>
       <c r="F684" t="s">
-        <v>966</v>
+        <v>924</v>
       </c>
     </row>
     <row r="685" spans="1:6">
@@ -18047,10 +18047,10 @@
         <v>15</v>
       </c>
       <c r="E685" t="s">
-        <v>923</v>
+        <v>932</v>
       </c>
       <c r="F685" t="s">
-        <v>932</v>
+        <v>924</v>
       </c>
     </row>
     <row r="686" spans="1:6">
@@ -18067,10 +18067,10 @@
         <v>717</v>
       </c>
       <c r="E686" t="s">
-        <v>923</v>
+        <v>932</v>
       </c>
       <c r="F686" t="s">
-        <v>932</v>
+        <v>924</v>
       </c>
     </row>
     <row r="687" spans="1:6">
@@ -18087,10 +18087,10 @@
         <v>15</v>
       </c>
       <c r="E687" t="s">
-        <v>923</v>
+        <v>947</v>
       </c>
       <c r="F687" t="s">
-        <v>947</v>
+        <v>924</v>
       </c>
     </row>
     <row r="688" spans="1:6">
@@ -18107,10 +18107,10 @@
         <v>24</v>
       </c>
       <c r="E688" t="s">
-        <v>923</v>
+        <v>929</v>
       </c>
       <c r="F688" t="s">
-        <v>929</v>
+        <v>924</v>
       </c>
     </row>
     <row r="689" spans="1:6">
@@ -18127,10 +18127,10 @@
         <v>15</v>
       </c>
       <c r="E689" t="s">
-        <v>923</v>
+        <v>932</v>
       </c>
       <c r="F689" t="s">
-        <v>932</v>
+        <v>924</v>
       </c>
     </row>
     <row r="690" spans="1:6">
@@ -18147,10 +18147,10 @@
         <v>717</v>
       </c>
       <c r="E690" t="s">
-        <v>923</v>
+        <v>932</v>
       </c>
       <c r="F690" t="s">
-        <v>932</v>
+        <v>924</v>
       </c>
     </row>
     <row r="691" spans="1:6">
@@ -18167,10 +18167,10 @@
         <v>13</v>
       </c>
       <c r="E691" t="s">
-        <v>923</v>
+        <v>932</v>
       </c>
       <c r="F691" t="s">
-        <v>932</v>
+        <v>924</v>
       </c>
     </row>
     <row r="692" spans="1:6">
@@ -18187,10 +18187,10 @@
         <v>717</v>
       </c>
       <c r="E692" t="s">
-        <v>923</v>
+        <v>932</v>
       </c>
       <c r="F692" t="s">
-        <v>932</v>
+        <v>924</v>
       </c>
     </row>
     <row r="693" spans="1:6">
@@ -18207,10 +18207,10 @@
         <v>24</v>
       </c>
       <c r="E693" t="s">
-        <v>923</v>
+        <v>947</v>
       </c>
       <c r="F693" t="s">
-        <v>947</v>
+        <v>924</v>
       </c>
     </row>
     <row r="694" spans="1:6">
@@ -18227,10 +18227,10 @@
         <v>717</v>
       </c>
       <c r="E694" t="s">
-        <v>923</v>
+        <v>932</v>
       </c>
       <c r="F694" t="s">
-        <v>932</v>
+        <v>924</v>
       </c>
     </row>
     <row r="695" spans="1:6">
@@ -18247,10 +18247,10 @@
         <v>717</v>
       </c>
       <c r="E695" t="s">
-        <v>923</v>
+        <v>932</v>
       </c>
       <c r="F695" t="s">
-        <v>932</v>
+        <v>924</v>
       </c>
     </row>
     <row r="696" spans="1:6">
@@ -18287,10 +18287,10 @@
         <v>24</v>
       </c>
       <c r="E697" t="s">
-        <v>981</v>
+        <v>985</v>
       </c>
       <c r="F697" t="s">
-        <v>985</v>
+        <v>982</v>
       </c>
     </row>
     <row r="698" spans="1:6">
@@ -18307,10 +18307,10 @@
         <v>717</v>
       </c>
       <c r="E698" t="s">
-        <v>981</v>
+        <v>988</v>
       </c>
       <c r="F698" t="s">
-        <v>988</v>
+        <v>982</v>
       </c>
     </row>
     <row r="699" spans="1:6">
@@ -18327,10 +18327,10 @@
         <v>717</v>
       </c>
       <c r="E699" t="s">
-        <v>981</v>
+        <v>988</v>
       </c>
       <c r="F699" t="s">
-        <v>988</v>
+        <v>982</v>
       </c>
     </row>
     <row r="700" spans="1:6">
@@ -18347,10 +18347,10 @@
         <v>717</v>
       </c>
       <c r="E700" t="s">
-        <v>981</v>
+        <v>988</v>
       </c>
       <c r="F700" t="s">
-        <v>988</v>
+        <v>982</v>
       </c>
     </row>
     <row r="701" spans="1:6">
@@ -18367,10 +18367,10 @@
         <v>717</v>
       </c>
       <c r="E701" t="s">
-        <v>981</v>
+        <v>988</v>
       </c>
       <c r="F701" t="s">
-        <v>988</v>
+        <v>982</v>
       </c>
     </row>
     <row r="702" spans="1:6">
@@ -18387,10 +18387,10 @@
         <v>717</v>
       </c>
       <c r="E702" t="s">
-        <v>981</v>
+        <v>988</v>
       </c>
       <c r="F702" t="s">
-        <v>988</v>
+        <v>982</v>
       </c>
     </row>
     <row r="703" spans="1:6">
@@ -18407,10 +18407,10 @@
         <v>24</v>
       </c>
       <c r="E703" t="s">
-        <v>981</v>
+        <v>994</v>
       </c>
       <c r="F703" t="s">
-        <v>994</v>
+        <v>982</v>
       </c>
     </row>
     <row r="704" spans="1:6">
@@ -18427,10 +18427,10 @@
         <v>24</v>
       </c>
       <c r="E704" t="s">
-        <v>981</v>
+        <v>997</v>
       </c>
       <c r="F704" t="s">
-        <v>997</v>
+        <v>982</v>
       </c>
     </row>
     <row r="705" spans="1:6">
@@ -18447,10 +18447,10 @@
         <v>13</v>
       </c>
       <c r="E705" t="s">
-        <v>981</v>
+        <v>988</v>
       </c>
       <c r="F705" t="s">
-        <v>988</v>
+        <v>982</v>
       </c>
     </row>
     <row r="706" spans="1:6">
@@ -18467,10 +18467,10 @@
         <v>13</v>
       </c>
       <c r="E706" t="s">
-        <v>981</v>
+        <v>932</v>
       </c>
       <c r="F706" t="s">
-        <v>932</v>
+        <v>982</v>
       </c>
     </row>
     <row r="707" spans="1:6">
@@ -18487,10 +18487,10 @@
         <v>24</v>
       </c>
       <c r="E707" t="s">
-        <v>981</v>
+        <v>1003</v>
       </c>
       <c r="F707" t="s">
-        <v>1003</v>
+        <v>982</v>
       </c>
     </row>
     <row r="708" spans="1:6">
@@ -18507,10 +18507,10 @@
         <v>15</v>
       </c>
       <c r="E708" t="s">
-        <v>981</v>
+        <v>1006</v>
       </c>
       <c r="F708" t="s">
-        <v>1006</v>
+        <v>982</v>
       </c>
     </row>
     <row r="709" spans="1:6">
@@ -18527,10 +18527,10 @@
         <v>24</v>
       </c>
       <c r="E709" t="s">
-        <v>981</v>
+        <v>1009</v>
       </c>
       <c r="F709" t="s">
-        <v>1009</v>
+        <v>982</v>
       </c>
     </row>
     <row r="710" spans="1:6">
@@ -18547,10 +18547,10 @@
         <v>717</v>
       </c>
       <c r="E710" t="s">
-        <v>981</v>
+        <v>988</v>
       </c>
       <c r="F710" t="s">
-        <v>988</v>
+        <v>982</v>
       </c>
     </row>
     <row r="711" spans="1:6">
@@ -18567,10 +18567,10 @@
         <v>24</v>
       </c>
       <c r="E711" t="s">
-        <v>981</v>
+        <v>1013</v>
       </c>
       <c r="F711" t="s">
-        <v>1013</v>
+        <v>982</v>
       </c>
     </row>
     <row r="712" spans="1:6">
@@ -18587,10 +18587,10 @@
         <v>24</v>
       </c>
       <c r="E712" t="s">
-        <v>981</v>
+        <v>1016</v>
       </c>
       <c r="F712" t="s">
-        <v>1016</v>
+        <v>982</v>
       </c>
     </row>
     <row r="713" spans="1:6">
@@ -18607,10 +18607,10 @@
         <v>15</v>
       </c>
       <c r="E713" t="s">
-        <v>981</v>
+        <v>988</v>
       </c>
       <c r="F713" t="s">
-        <v>988</v>
+        <v>982</v>
       </c>
     </row>
     <row r="714" spans="1:6">
@@ -18627,10 +18627,10 @@
         <v>24</v>
       </c>
       <c r="E714" t="s">
-        <v>981</v>
+        <v>1020</v>
       </c>
       <c r="F714" t="s">
-        <v>1020</v>
+        <v>982</v>
       </c>
     </row>
     <row r="715" spans="1:6">
@@ -18647,10 +18647,10 @@
         <v>15</v>
       </c>
       <c r="E715" t="s">
-        <v>981</v>
+        <v>988</v>
       </c>
       <c r="F715" t="s">
-        <v>988</v>
+        <v>982</v>
       </c>
     </row>
     <row r="716" spans="1:6">
@@ -18667,10 +18667,10 @@
         <v>24</v>
       </c>
       <c r="E716" t="s">
-        <v>981</v>
+        <v>1024</v>
       </c>
       <c r="F716" t="s">
-        <v>1024</v>
+        <v>982</v>
       </c>
     </row>
     <row r="717" spans="1:6">
@@ -18687,10 +18687,10 @@
         <v>24</v>
       </c>
       <c r="E717" t="s">
-        <v>981</v>
+        <v>1020</v>
       </c>
       <c r="F717" t="s">
-        <v>1020</v>
+        <v>982</v>
       </c>
     </row>
     <row r="718" spans="1:6">
@@ -18707,10 +18707,10 @@
         <v>717</v>
       </c>
       <c r="E718" t="s">
-        <v>981</v>
+        <v>988</v>
       </c>
       <c r="F718" t="s">
-        <v>988</v>
+        <v>982</v>
       </c>
     </row>
     <row r="719" spans="1:6">
@@ -18727,10 +18727,10 @@
         <v>15</v>
       </c>
       <c r="E719" t="s">
-        <v>981</v>
+        <v>1016</v>
       </c>
       <c r="F719" t="s">
-        <v>1016</v>
+        <v>982</v>
       </c>
     </row>
     <row r="720" spans="1:6">
@@ -18747,10 +18747,10 @@
         <v>717</v>
       </c>
       <c r="E720" t="s">
-        <v>981</v>
+        <v>988</v>
       </c>
       <c r="F720" t="s">
-        <v>988</v>
+        <v>982</v>
       </c>
     </row>
     <row r="721" spans="1:6">
@@ -18767,10 +18767,10 @@
         <v>717</v>
       </c>
       <c r="E721" t="s">
-        <v>981</v>
+        <v>1016</v>
       </c>
       <c r="F721" t="s">
-        <v>1016</v>
+        <v>982</v>
       </c>
     </row>
     <row r="722" spans="1:6">
@@ -18787,10 +18787,10 @@
         <v>15</v>
       </c>
       <c r="E722" t="s">
-        <v>981</v>
+        <v>1016</v>
       </c>
       <c r="F722" t="s">
-        <v>1016</v>
+        <v>982</v>
       </c>
     </row>
     <row r="723" spans="1:6">
@@ -18807,10 +18807,10 @@
         <v>24</v>
       </c>
       <c r="E723" t="s">
-        <v>981</v>
+        <v>985</v>
       </c>
       <c r="F723" t="s">
-        <v>985</v>
+        <v>982</v>
       </c>
     </row>
     <row r="724" spans="1:6">
@@ -18827,10 +18827,10 @@
         <v>717</v>
       </c>
       <c r="E724" t="s">
-        <v>981</v>
+        <v>988</v>
       </c>
       <c r="F724" t="s">
-        <v>988</v>
+        <v>982</v>
       </c>
     </row>
     <row r="725" spans="1:6">
@@ -18847,10 +18847,10 @@
         <v>24</v>
       </c>
       <c r="E725" t="s">
-        <v>981</v>
+        <v>1038</v>
       </c>
       <c r="F725" t="s">
-        <v>1038</v>
+        <v>982</v>
       </c>
     </row>
     <row r="726" spans="1:6">
@@ -18867,10 +18867,10 @@
         <v>717</v>
       </c>
       <c r="E726" t="s">
-        <v>981</v>
+        <v>1016</v>
       </c>
       <c r="F726" t="s">
-        <v>1016</v>
+        <v>982</v>
       </c>
     </row>
     <row r="727" spans="1:6">
@@ -18887,10 +18887,10 @@
         <v>717</v>
       </c>
       <c r="E727" t="s">
-        <v>981</v>
+        <v>988</v>
       </c>
       <c r="F727" t="s">
-        <v>988</v>
+        <v>982</v>
       </c>
     </row>
     <row r="728" spans="1:6">
@@ -18907,10 +18907,10 @@
         <v>24</v>
       </c>
       <c r="E728" t="s">
-        <v>981</v>
+        <v>997</v>
       </c>
       <c r="F728" t="s">
-        <v>997</v>
+        <v>982</v>
       </c>
     </row>
     <row r="729" spans="1:6">
@@ -18927,10 +18927,10 @@
         <v>13</v>
       </c>
       <c r="E729" t="s">
-        <v>981</v>
+        <v>988</v>
       </c>
       <c r="F729" t="s">
-        <v>988</v>
+        <v>982</v>
       </c>
     </row>
     <row r="730" spans="1:6">
@@ -18947,10 +18947,10 @@
         <v>717</v>
       </c>
       <c r="E730" t="s">
-        <v>981</v>
+        <v>988</v>
       </c>
       <c r="F730" t="s">
-        <v>988</v>
+        <v>982</v>
       </c>
     </row>
     <row r="731" spans="1:6">
@@ -18967,10 +18967,10 @@
         <v>24</v>
       </c>
       <c r="E731" t="s">
-        <v>981</v>
+        <v>1016</v>
       </c>
       <c r="F731" t="s">
-        <v>1016</v>
+        <v>982</v>
       </c>
     </row>
     <row r="732" spans="1:6">
@@ -18987,10 +18987,10 @@
         <v>717</v>
       </c>
       <c r="E732" t="s">
-        <v>981</v>
+        <v>988</v>
       </c>
       <c r="F732" t="s">
-        <v>988</v>
+        <v>982</v>
       </c>
     </row>
     <row r="733" spans="1:6">
@@ -19007,10 +19007,10 @@
         <v>717</v>
       </c>
       <c r="E733" t="s">
-        <v>981</v>
+        <v>988</v>
       </c>
       <c r="F733" t="s">
-        <v>988</v>
+        <v>982</v>
       </c>
     </row>
     <row r="734" spans="1:6">
@@ -19167,10 +19167,10 @@
         <v>15</v>
       </c>
       <c r="E741" t="s">
-        <v>1049</v>
+        <v>1060</v>
       </c>
       <c r="F741" t="s">
-        <v>1060</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="742" spans="1:6">
@@ -19187,10 +19187,10 @@
         <v>15</v>
       </c>
       <c r="E742" t="s">
-        <v>1049</v>
+        <v>1063</v>
       </c>
       <c r="F742" t="s">
-        <v>1063</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="743" spans="1:6">
@@ -19247,10 +19247,10 @@
         <v>24</v>
       </c>
       <c r="E745" t="s">
-        <v>1049</v>
+        <v>1068</v>
       </c>
       <c r="F745" t="s">
-        <v>1068</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="746" spans="1:6">
@@ -19287,10 +19287,10 @@
         <v>24</v>
       </c>
       <c r="E747" t="s">
-        <v>1049</v>
+        <v>1068</v>
       </c>
       <c r="F747" t="s">
-        <v>1068</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="748" spans="1:6">
@@ -19307,10 +19307,10 @@
         <v>24</v>
       </c>
       <c r="E748" t="s">
-        <v>1049</v>
+        <v>1073</v>
       </c>
       <c r="F748" t="s">
-        <v>1073</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="749" spans="1:6">
@@ -19347,10 +19347,10 @@
         <v>24</v>
       </c>
       <c r="E750" t="s">
-        <v>1049</v>
+        <v>1078</v>
       </c>
       <c r="F750" t="s">
-        <v>1078</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="751" spans="1:6">
@@ -19427,10 +19427,10 @@
         <v>15</v>
       </c>
       <c r="E754" t="s">
-        <v>1049</v>
+        <v>988</v>
       </c>
       <c r="F754" t="s">
-        <v>988</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="755" spans="1:6">
@@ -19487,10 +19487,10 @@
         <v>24</v>
       </c>
       <c r="E757" t="s">
-        <v>1049</v>
+        <v>1089</v>
       </c>
       <c r="F757" t="s">
-        <v>1089</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="758" spans="1:6">
@@ -19707,10 +19707,10 @@
         <v>24</v>
       </c>
       <c r="E768" t="s">
-        <v>1103</v>
+        <v>1107</v>
       </c>
       <c r="F768" t="s">
-        <v>1107</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="769" spans="1:6">
@@ -19727,10 +19727,10 @@
         <v>717</v>
       </c>
       <c r="E769" t="s">
-        <v>1103</v>
+        <v>1110</v>
       </c>
       <c r="F769" t="s">
-        <v>1110</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="770" spans="1:6">
@@ -19747,10 +19747,10 @@
         <v>717</v>
       </c>
       <c r="E770" t="s">
-        <v>1103</v>
+        <v>1110</v>
       </c>
       <c r="F770" t="s">
-        <v>1110</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="771" spans="1:6">
@@ -19767,10 +19767,10 @@
         <v>717</v>
       </c>
       <c r="E771" t="s">
-        <v>1103</v>
+        <v>1110</v>
       </c>
       <c r="F771" t="s">
-        <v>1110</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="772" spans="1:6">
@@ -19787,10 +19787,10 @@
         <v>717</v>
       </c>
       <c r="E772" t="s">
-        <v>1103</v>
+        <v>1110</v>
       </c>
       <c r="F772" t="s">
-        <v>1110</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="773" spans="1:6">
@@ -19807,10 +19807,10 @@
         <v>717</v>
       </c>
       <c r="E773" t="s">
-        <v>1103</v>
+        <v>1110</v>
       </c>
       <c r="F773" t="s">
-        <v>1110</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="774" spans="1:6">
@@ -19827,10 +19827,10 @@
         <v>717</v>
       </c>
       <c r="E774" t="s">
-        <v>1103</v>
+        <v>1110</v>
       </c>
       <c r="F774" t="s">
-        <v>1110</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="775" spans="1:6">
@@ -19847,10 +19847,10 @@
         <v>24</v>
       </c>
       <c r="E775" t="s">
-        <v>1103</v>
+        <v>1107</v>
       </c>
       <c r="F775" t="s">
-        <v>1107</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="776" spans="1:6">
@@ -19867,10 +19867,10 @@
         <v>15</v>
       </c>
       <c r="E776" t="s">
-        <v>1103</v>
+        <v>1110</v>
       </c>
       <c r="F776" t="s">
-        <v>1110</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="777" spans="1:6">
@@ -19887,10 +19887,10 @@
         <v>717</v>
       </c>
       <c r="E777" t="s">
-        <v>1103</v>
+        <v>1110</v>
       </c>
       <c r="F777" t="s">
-        <v>1110</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="778" spans="1:6">
@@ -19927,10 +19927,10 @@
         <v>717</v>
       </c>
       <c r="E779" t="s">
-        <v>1103</v>
+        <v>1110</v>
       </c>
       <c r="F779" t="s">
-        <v>1110</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="780" spans="1:6">
@@ -19947,10 +19947,10 @@
         <v>24</v>
       </c>
       <c r="E780" t="s">
-        <v>1103</v>
+        <v>1122</v>
       </c>
       <c r="F780" t="s">
-        <v>1122</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="781" spans="1:6">
@@ -19967,10 +19967,10 @@
         <v>717</v>
       </c>
       <c r="E781" t="s">
-        <v>1103</v>
+        <v>1110</v>
       </c>
       <c r="F781" t="s">
-        <v>1110</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="782" spans="1:6">
@@ -19987,10 +19987,10 @@
         <v>24</v>
       </c>
       <c r="E782" t="s">
-        <v>1103</v>
+        <v>1126</v>
       </c>
       <c r="F782" t="s">
-        <v>1126</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="783" spans="1:6">
@@ -20027,10 +20027,10 @@
         <v>24</v>
       </c>
       <c r="E784" t="s">
-        <v>1103</v>
+        <v>1122</v>
       </c>
       <c r="F784" t="s">
-        <v>1122</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="785" spans="1:6">
@@ -20047,10 +20047,10 @@
         <v>24</v>
       </c>
       <c r="E785" t="s">
-        <v>1103</v>
+        <v>1132</v>
       </c>
       <c r="F785" t="s">
-        <v>1132</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="786" spans="1:6">
@@ -20067,10 +20067,10 @@
         <v>717</v>
       </c>
       <c r="E786" t="s">
-        <v>1103</v>
+        <v>1110</v>
       </c>
       <c r="F786" t="s">
-        <v>1110</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="787" spans="1:6">
@@ -20087,10 +20087,10 @@
         <v>717</v>
       </c>
       <c r="E787" t="s">
-        <v>1103</v>
+        <v>1110</v>
       </c>
       <c r="F787" t="s">
-        <v>1110</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="788" spans="1:6">
@@ -20107,10 +20107,10 @@
         <v>13</v>
       </c>
       <c r="E788" t="s">
-        <v>1103</v>
+        <v>1137</v>
       </c>
       <c r="F788" t="s">
-        <v>1137</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="789" spans="1:6">
@@ -20127,10 +20127,10 @@
         <v>15</v>
       </c>
       <c r="E789" t="s">
-        <v>1103</v>
+        <v>1110</v>
       </c>
       <c r="F789" t="s">
-        <v>1110</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="790" spans="1:6">
@@ -20147,10 +20147,10 @@
         <v>24</v>
       </c>
       <c r="E790" t="s">
-        <v>1103</v>
+        <v>1141</v>
       </c>
       <c r="F790" t="s">
-        <v>1141</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="791" spans="1:6">
@@ -20167,10 +20167,10 @@
         <v>717</v>
       </c>
       <c r="E791" t="s">
-        <v>1103</v>
+        <v>1110</v>
       </c>
       <c r="F791" t="s">
-        <v>1110</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="792" spans="1:6">
@@ -20187,10 +20187,10 @@
         <v>717</v>
       </c>
       <c r="E792" t="s">
-        <v>1103</v>
+        <v>1110</v>
       </c>
       <c r="F792" t="s">
-        <v>1110</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="793" spans="1:6">
@@ -20207,10 +20207,10 @@
         <v>13</v>
       </c>
       <c r="E793" t="s">
-        <v>1103</v>
+        <v>1110</v>
       </c>
       <c r="F793" t="s">
-        <v>1110</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="794" spans="1:6">
@@ -20227,10 +20227,10 @@
         <v>24</v>
       </c>
       <c r="E794" t="s">
-        <v>1103</v>
+        <v>1137</v>
       </c>
       <c r="F794" t="s">
-        <v>1137</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="795" spans="1:6">
@@ -20247,10 +20247,10 @@
         <v>717</v>
       </c>
       <c r="E795" t="s">
-        <v>1103</v>
+        <v>1110</v>
       </c>
       <c r="F795" t="s">
-        <v>1110</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="796" spans="1:6">
@@ -20307,10 +20307,10 @@
         <v>24</v>
       </c>
       <c r="E798" t="s">
-        <v>1149</v>
+        <v>1155</v>
       </c>
       <c r="F798" t="s">
-        <v>1155</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="799" spans="1:6">
@@ -20327,10 +20327,10 @@
         <v>24</v>
       </c>
       <c r="E799" t="s">
-        <v>1149</v>
+        <v>1158</v>
       </c>
       <c r="F799" t="s">
-        <v>1158</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="800" spans="1:6">
@@ -20547,10 +20547,10 @@
         <v>24</v>
       </c>
       <c r="E810" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="F810" t="s">
-        <v>1171</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="811" spans="1:6">
@@ -20587,10 +20587,10 @@
         <v>24</v>
       </c>
       <c r="E812" t="s">
-        <v>1149</v>
+        <v>1174</v>
       </c>
       <c r="F812" t="s">
-        <v>1174</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="813" spans="1:6">
@@ -20607,10 +20607,10 @@
         <v>24</v>
       </c>
       <c r="E813" t="s">
-        <v>1149</v>
+        <v>1171</v>
       </c>
       <c r="F813" t="s">
-        <v>1171</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="814" spans="1:6">
@@ -20647,10 +20647,10 @@
         <v>24</v>
       </c>
       <c r="E815" t="s">
-        <v>1149</v>
+        <v>1179</v>
       </c>
       <c r="F815" t="s">
-        <v>1179</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="816" spans="1:6">
@@ -20707,10 +20707,10 @@
         <v>24</v>
       </c>
       <c r="E818" t="s">
-        <v>1149</v>
+        <v>1185</v>
       </c>
       <c r="F818" t="s">
-        <v>1185</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="819" spans="1:6">
@@ -20727,10 +20727,10 @@
         <v>24</v>
       </c>
       <c r="E819" t="s">
-        <v>1149</v>
+        <v>1188</v>
       </c>
       <c r="F819" t="s">
-        <v>1188</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="820" spans="1:6">
@@ -20987,10 +20987,10 @@
         <v>24</v>
       </c>
       <c r="E832" t="s">
-        <v>1200</v>
+        <v>1207</v>
       </c>
       <c r="F832" t="s">
-        <v>1207</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="833" spans="1:6">
@@ -21067,10 +21067,10 @@
         <v>13</v>
       </c>
       <c r="E836" t="s">
-        <v>1200</v>
+        <v>1213</v>
       </c>
       <c r="F836" t="s">
-        <v>1213</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="837" spans="1:6">
@@ -21107,10 +21107,10 @@
         <v>24</v>
       </c>
       <c r="E838" t="s">
-        <v>1200</v>
+        <v>1213</v>
       </c>
       <c r="F838" t="s">
-        <v>1213</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="839" spans="1:6">
@@ -21247,10 +21247,10 @@
         <v>15</v>
       </c>
       <c r="E845" t="s">
-        <v>1200</v>
+        <v>1224</v>
       </c>
       <c r="F845" t="s">
-        <v>1224</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="846" spans="1:6">
@@ -21267,10 +21267,10 @@
         <v>1203</v>
       </c>
       <c r="E846" t="s">
-        <v>1200</v>
+        <v>1227</v>
       </c>
       <c r="F846" t="s">
-        <v>1227</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="847" spans="1:6">
@@ -21307,10 +21307,10 @@
         <v>1203</v>
       </c>
       <c r="E848" t="s">
-        <v>1200</v>
+        <v>1227</v>
       </c>
       <c r="F848" t="s">
-        <v>1227</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="849" spans="1:6">
@@ -21327,10 +21327,10 @@
         <v>13</v>
       </c>
       <c r="E849" t="s">
-        <v>1200</v>
+        <v>1227</v>
       </c>
       <c r="F849" t="s">
-        <v>1227</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="850" spans="1:6">
@@ -21347,10 +21347,10 @@
         <v>717</v>
       </c>
       <c r="E850" t="s">
-        <v>1200</v>
+        <v>1227</v>
       </c>
       <c r="F850" t="s">
-        <v>1227</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="851" spans="1:6">
@@ -21367,10 +21367,10 @@
         <v>1203</v>
       </c>
       <c r="E851" t="s">
-        <v>1200</v>
+        <v>1227</v>
       </c>
       <c r="F851" t="s">
-        <v>1227</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="852" spans="1:6">
@@ -21387,10 +21387,10 @@
         <v>1203</v>
       </c>
       <c r="E852" t="s">
-        <v>1200</v>
+        <v>1227</v>
       </c>
       <c r="F852" t="s">
-        <v>1227</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="853" spans="1:6">
@@ -21827,10 +21827,10 @@
         <v>1203</v>
       </c>
       <c r="E874" t="s">
-        <v>1248</v>
+        <v>1207</v>
       </c>
       <c r="F874" t="s">
-        <v>1207</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="875" spans="1:6">
@@ -21847,10 +21847,10 @@
         <v>1203</v>
       </c>
       <c r="E875" t="s">
-        <v>1248</v>
+        <v>1207</v>
       </c>
       <c r="F875" t="s">
-        <v>1207</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="876" spans="1:6">
@@ -21867,10 +21867,10 @@
         <v>13</v>
       </c>
       <c r="E876" t="s">
-        <v>1248</v>
+        <v>1207</v>
       </c>
       <c r="F876" t="s">
-        <v>1207</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="877" spans="1:6">
@@ -21887,10 +21887,10 @@
         <v>717</v>
       </c>
       <c r="E877" t="s">
-        <v>1248</v>
+        <v>1207</v>
       </c>
       <c r="F877" t="s">
-        <v>1207</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="878" spans="1:6">
@@ -21907,10 +21907,10 @@
         <v>1203</v>
       </c>
       <c r="E878" t="s">
-        <v>1248</v>
+        <v>1265</v>
       </c>
       <c r="F878" t="s">
-        <v>1265</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="879" spans="1:6">
@@ -21927,10 +21927,10 @@
         <v>1203</v>
       </c>
       <c r="E879" t="s">
-        <v>1248</v>
+        <v>1207</v>
       </c>
       <c r="F879" t="s">
-        <v>1207</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="880" spans="1:6">
@@ -21947,10 +21947,10 @@
         <v>1203</v>
       </c>
       <c r="E880" t="s">
-        <v>1248</v>
+        <v>1207</v>
       </c>
       <c r="F880" t="s">
-        <v>1207</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="881" spans="1:6">
@@ -22267,10 +22267,10 @@
         <v>1203</v>
       </c>
       <c r="E896" t="s">
-        <v>1284</v>
+        <v>1287</v>
       </c>
       <c r="F896" t="s">
-        <v>1287</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="897" spans="1:6">
@@ -22287,10 +22287,10 @@
         <v>1203</v>
       </c>
       <c r="E897" t="s">
-        <v>1284</v>
+        <v>1287</v>
       </c>
       <c r="F897" t="s">
-        <v>1287</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="898" spans="1:6">
@@ -22307,10 +22307,10 @@
         <v>1203</v>
       </c>
       <c r="E898" t="s">
-        <v>1284</v>
+        <v>1287</v>
       </c>
       <c r="F898" t="s">
-        <v>1287</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="899" spans="1:6">
@@ -22327,10 +22327,10 @@
         <v>1203</v>
       </c>
       <c r="E899" t="s">
-        <v>1284</v>
+        <v>1287</v>
       </c>
       <c r="F899" t="s">
-        <v>1287</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="900" spans="1:6">
@@ -22347,10 +22347,10 @@
         <v>15</v>
       </c>
       <c r="E900" t="s">
-        <v>1284</v>
+        <v>1287</v>
       </c>
       <c r="F900" t="s">
-        <v>1287</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="901" spans="1:6">
@@ -22367,10 +22367,10 @@
         <v>13</v>
       </c>
       <c r="E901" t="s">
-        <v>1284</v>
+        <v>1287</v>
       </c>
       <c r="F901" t="s">
-        <v>1287</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="902" spans="1:6">
@@ -22387,10 +22387,10 @@
         <v>15</v>
       </c>
       <c r="E902" t="s">
-        <v>1284</v>
+        <v>1287</v>
       </c>
       <c r="F902" t="s">
-        <v>1287</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="903" spans="1:6">
@@ -22407,10 +22407,10 @@
         <v>1203</v>
       </c>
       <c r="E903" t="s">
-        <v>1284</v>
+        <v>1287</v>
       </c>
       <c r="F903" t="s">
-        <v>1287</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="904" spans="1:6">
@@ -22427,10 +22427,10 @@
         <v>1203</v>
       </c>
       <c r="E904" t="s">
-        <v>1284</v>
+        <v>1287</v>
       </c>
       <c r="F904" t="s">
-        <v>1287</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="905" spans="1:6">
@@ -22447,10 +22447,10 @@
         <v>717</v>
       </c>
       <c r="E905" t="s">
-        <v>1284</v>
+        <v>1287</v>
       </c>
       <c r="F905" t="s">
-        <v>1287</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="906" spans="1:6">
@@ -22467,10 +22467,10 @@
         <v>15</v>
       </c>
       <c r="E906" t="s">
-        <v>1284</v>
+        <v>1287</v>
       </c>
       <c r="F906" t="s">
-        <v>1287</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="907" spans="1:6">
@@ -22487,10 +22487,10 @@
         <v>1203</v>
       </c>
       <c r="E907" t="s">
-        <v>1284</v>
+        <v>1287</v>
       </c>
       <c r="F907" t="s">
-        <v>1287</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="908" spans="1:6">
@@ -22507,10 +22507,10 @@
         <v>1203</v>
       </c>
       <c r="E908" t="s">
-        <v>1284</v>
+        <v>1287</v>
       </c>
       <c r="F908" t="s">
-        <v>1287</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="909" spans="1:6">
@@ -22527,10 +22527,10 @@
         <v>1203</v>
       </c>
       <c r="E909" t="s">
-        <v>1284</v>
+        <v>1287</v>
       </c>
       <c r="F909" t="s">
-        <v>1287</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="910" spans="1:6">
@@ -22547,10 +22547,10 @@
         <v>1203</v>
       </c>
       <c r="E910" t="s">
-        <v>1284</v>
+        <v>1287</v>
       </c>
       <c r="F910" t="s">
-        <v>1287</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="911" spans="1:6">
@@ -22567,10 +22567,10 @@
         <v>1203</v>
       </c>
       <c r="E911" t="s">
-        <v>1284</v>
+        <v>1287</v>
       </c>
       <c r="F911" t="s">
-        <v>1287</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="912" spans="1:6">
@@ -22587,10 +22587,10 @@
         <v>717</v>
       </c>
       <c r="E912" t="s">
-        <v>1284</v>
+        <v>1287</v>
       </c>
       <c r="F912" t="s">
-        <v>1287</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="913" spans="1:6">
@@ -22607,10 +22607,10 @@
         <v>1203</v>
       </c>
       <c r="E913" t="s">
-        <v>1284</v>
+        <v>1287</v>
       </c>
       <c r="F913" t="s">
-        <v>1287</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="914" spans="1:6">
@@ -22627,10 +22627,10 @@
         <v>1203</v>
       </c>
       <c r="E914" t="s">
-        <v>1284</v>
+        <v>1287</v>
       </c>
       <c r="F914" t="s">
-        <v>1287</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="915" spans="1:6">
@@ -22647,10 +22647,10 @@
         <v>1203</v>
       </c>
       <c r="E915" t="s">
-        <v>1284</v>
+        <v>1287</v>
       </c>
       <c r="F915" t="s">
-        <v>1287</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="916" spans="1:6">
@@ -22667,10 +22667,10 @@
         <v>15</v>
       </c>
       <c r="E916" t="s">
-        <v>1284</v>
+        <v>1287</v>
       </c>
       <c r="F916" t="s">
-        <v>1287</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="917" spans="1:6">
@@ -22687,10 +22687,10 @@
         <v>1203</v>
       </c>
       <c r="E917" t="s">
-        <v>1284</v>
+        <v>1287</v>
       </c>
       <c r="F917" t="s">
-        <v>1287</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="918" spans="1:6">
@@ -22707,10 +22707,10 @@
         <v>717</v>
       </c>
       <c r="E918" t="s">
-        <v>1284</v>
+        <v>1287</v>
       </c>
       <c r="F918" t="s">
-        <v>1287</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="919" spans="1:6">

--- a/api/1/clv3/xlsx/fr/HumanitarianPlan.xlsx
+++ b/api/1/clv3/xlsx/fr/HumanitarianPlan.xlsx
@@ -25,15 +25,15 @@
     <t>codeforiati:plan-type</t>
   </si>
   <si>
+    <t>codeforiati:plan-year</t>
+  </si>
+  <si>
+    <t>codeforiati:plan-start-date</t>
+  </si>
+  <si>
     <t>codeforiati:plan-end-date</t>
   </si>
   <si>
-    <t>codeforiati:plan-start-date</t>
-  </si>
-  <si>
-    <t>codeforiati:plan-year</t>
-  </si>
-  <si>
     <t>HAFG26</t>
   </si>
   <si>
@@ -43,15 +43,15 @@
     <t>Humanitarian needs and response plan</t>
   </si>
   <si>
+    <t>2026</t>
+  </si>
+  <si>
+    <t>2026-01-01</t>
+  </si>
+  <si>
     <t>2026-12-31</t>
   </si>
   <si>
-    <t>2026-01-01</t>
-  </si>
-  <si>
-    <t>2026</t>
-  </si>
-  <si>
     <t>HBFA26</t>
   </si>
   <si>
@@ -85,12 +85,12 @@
     <t>Regional response plan</t>
   </si>
   <si>
+    <t>2026-03-01</t>
+  </si>
+  <si>
     <t>2026-05-31</t>
   </si>
   <si>
-    <t>2026-03-01</t>
-  </si>
-  <si>
     <t>FLBN26</t>
   </si>
   <si>
@@ -190,15 +190,15 @@
     <t>HAFG25</t>
   </si>
   <si>
+    <t>2025</t>
+  </si>
+  <si>
+    <t>2025-01-01</t>
+  </si>
+  <si>
     <t>2025-12-31</t>
   </si>
   <si>
-    <t>2025-01-01</t>
-  </si>
-  <si>
-    <t>2025</t>
-  </si>
-  <si>
     <t>RIRNPAK25</t>
   </si>
   <si>
@@ -376,15 +376,15 @@
     <t>HAFG24</t>
   </si>
   <si>
+    <t>2024</t>
+  </si>
+  <si>
+    <t>2024-01-01</t>
+  </si>
+  <si>
     <t>2024-12-31</t>
   </si>
   <si>
-    <t>2024-01-01</t>
-  </si>
-  <si>
-    <t>2024</t>
-  </si>
-  <si>
     <t>RAFG_RRP24</t>
   </si>
   <si>
@@ -577,15 +577,15 @@
     <t>HAFG23</t>
   </si>
   <si>
+    <t>2023</t>
+  </si>
+  <si>
+    <t>2023-01-01</t>
+  </si>
+  <si>
     <t>2023-12-31</t>
   </si>
   <si>
-    <t>2023-01-01</t>
-  </si>
-  <si>
-    <t>2023</t>
-  </si>
-  <si>
     <t>RAFG23</t>
   </si>
   <si>
@@ -649,21 +649,21 @@
     <t>OMNG2223</t>
   </si>
   <si>
+    <t>2022-12-01</t>
+  </si>
+  <si>
     <t>2023-05-31</t>
   </si>
   <si>
-    <t>2022-12-01</t>
-  </si>
-  <si>
     <t>OMOZ23</t>
   </si>
   <si>
+    <t>2023-03-01</t>
+  </si>
+  <si>
     <t>2023-09-30</t>
   </si>
   <si>
-    <t>2023-03-01</t>
-  </si>
-  <si>
     <t>HMOZ23</t>
   </si>
   <si>
@@ -709,12 +709,12 @@
     <t>RRSDN23</t>
   </si>
   <si>
+    <t>2023-05-01</t>
+  </si>
+  <si>
     <t>2023-10-31</t>
   </si>
   <si>
-    <t>2023-05-01</t>
-  </si>
-  <si>
     <t>HSDN23</t>
   </si>
   <si>
@@ -757,15 +757,15 @@
     <t>HAFG22</t>
   </si>
   <si>
+    <t>2022</t>
+  </si>
+  <si>
+    <t>2022-01-01</t>
+  </si>
+  <si>
     <t>2022-12-31</t>
   </si>
   <si>
-    <t>2022-01-01</t>
-  </si>
-  <si>
-    <t>2022</t>
-  </si>
-  <si>
     <t>RAFG22</t>
   </si>
   <si>
@@ -787,12 +787,12 @@
     <t>OCUB2223</t>
   </si>
   <si>
+    <t>2022-10-20</t>
+  </si>
+  <si>
     <t>2023-03-31</t>
   </si>
   <si>
-    <t>2022-10-20</t>
-  </si>
-  <si>
     <t>RDRCRRP22</t>
   </si>
   <si>
@@ -808,12 +808,12 @@
     <t>FHTI2223</t>
   </si>
   <si>
+    <t>2022-10-16</t>
+  </si>
+  <si>
     <t>2023-04-15</t>
   </si>
   <si>
-    <t>2022-10-16</t>
-  </si>
-  <si>
     <t>FHTI22</t>
   </si>
   <si>
@@ -844,24 +844,24 @@
     <t>FMWI22</t>
   </si>
   <si>
+    <t>2022-02-26</t>
+  </si>
+  <si>
     <t>2022-05-31</t>
   </si>
   <si>
-    <t>2022-02-26</t>
-  </si>
-  <si>
     <t>HMLI22</t>
   </si>
   <si>
     <t>FMOZ22</t>
   </si>
   <si>
+    <t>2022-04-01</t>
+  </si>
+  <si>
     <t>2022-09-30</t>
   </si>
   <si>
-    <t>2022-04-01</t>
-  </si>
-  <si>
     <t>HMOZ22</t>
   </si>
   <si>
@@ -892,12 +892,12 @@
     <t>OPHL2122</t>
   </si>
   <si>
+    <t>2021-12-24</t>
+  </si>
+  <si>
     <t>2022-06-30</t>
   </si>
   <si>
-    <t>2021-12-24</t>
-  </si>
-  <si>
     <t>RREG22</t>
   </si>
   <si>
@@ -961,15 +961,15 @@
     <t>FAFG21</t>
   </si>
   <si>
+    <t>2021</t>
+  </si>
+  <si>
+    <t>2021-09-01</t>
+  </si>
+  <si>
     <t>2021-12-31</t>
   </si>
   <si>
-    <t>2021-09-01</t>
-  </si>
-  <si>
-    <t>2021</t>
-  </si>
-  <si>
     <t>HAFG21</t>
   </si>
   <si>
@@ -1018,12 +1018,12 @@
     <t>FPSE21</t>
   </si>
   <si>
+    <t>2021-05-27</t>
+  </si>
+  <si>
     <t>2021-08-27</t>
   </si>
   <si>
-    <t>2021-05-27</t>
-  </si>
-  <si>
     <t>HETH21</t>
   </si>
   <si>
@@ -1036,24 +1036,24 @@
     <t>FHTI2122</t>
   </si>
   <si>
+    <t>2021-08-16</t>
+  </si>
+  <si>
     <t>2022-02-15</t>
   </si>
   <si>
-    <t>2021-08-16</t>
-  </si>
-  <si>
     <t>HHTI21</t>
   </si>
   <si>
     <t>FHND2021</t>
   </si>
   <si>
+    <t>2020-11-15</t>
+  </si>
+  <si>
     <t>2021-06-30</t>
   </si>
   <si>
-    <t>2020-11-15</t>
-  </si>
-  <si>
     <t>HHND21</t>
   </si>
   <si>
@@ -1072,12 +1072,12 @@
     <t>OLBN2122</t>
   </si>
   <si>
+    <t>2021-08-03</t>
+  </si>
+  <si>
     <t>2022-07-31</t>
   </si>
   <si>
-    <t>2021-08-03</t>
-  </si>
-  <si>
     <t>HLBY21</t>
   </si>
   <si>
@@ -1165,15 +1165,15 @@
     <t>HAFG20</t>
   </si>
   <si>
+    <t>2020</t>
+  </si>
+  <si>
+    <t>2020-01-01</t>
+  </si>
+  <si>
     <t>2020-12-31</t>
   </si>
   <si>
-    <t>2020-01-01</t>
-  </si>
-  <si>
-    <t>2020</t>
-  </si>
-  <si>
     <t>OBGD20</t>
   </si>
   <si>
@@ -1237,12 +1237,12 @@
     <t>FDJI1920</t>
   </si>
   <si>
+    <t>2019-12-17</t>
+  </si>
+  <si>
     <t>2020-03-31</t>
   </si>
   <si>
-    <t>2019-12-17</t>
-  </si>
-  <si>
     <t>ODJI20</t>
   </si>
   <si>
@@ -1291,24 +1291,24 @@
     <t>FLBN20</t>
   </si>
   <si>
+    <t>2020-08-05</t>
+  </si>
+  <si>
     <t>2020-11-13</t>
   </si>
   <si>
-    <t>2020-08-05</t>
-  </si>
-  <si>
     <t>OLBN20</t>
   </si>
   <si>
     <t>FLSO1920</t>
   </si>
   <si>
+    <t>2019-11-01</t>
+  </si>
+  <si>
     <t>2020-04-30</t>
   </si>
   <si>
-    <t>2019-11-01</t>
-  </si>
-  <si>
     <t>OLBR20</t>
   </si>
   <si>
@@ -1405,15 +1405,15 @@
     <t>HAFG19</t>
   </si>
   <si>
+    <t>2019</t>
+  </si>
+  <si>
+    <t>2019-01-01</t>
+  </si>
+  <si>
     <t>2019-12-31</t>
   </si>
   <si>
-    <t>2019-01-01</t>
-  </si>
-  <si>
-    <t>2019</t>
-  </si>
-  <si>
     <t>RBGD19</t>
   </si>
   <si>
@@ -1522,12 +1522,12 @@
     <t>FZWE1920</t>
   </si>
   <si>
+    <t>2019-02-01</t>
+  </si>
+  <si>
     <t>2020-04-29</t>
   </si>
   <si>
-    <t>2019-02-01</t>
-  </si>
-  <si>
     <t>FZWE1820</t>
   </si>
   <si>
@@ -1537,15 +1537,15 @@
     <t>HAFG18</t>
   </si>
   <si>
+    <t>2018</t>
+  </si>
+  <si>
+    <t>2018-01-01</t>
+  </si>
+  <si>
     <t>2018-12-31</t>
   </si>
   <si>
-    <t>2018-01-01</t>
-  </si>
-  <si>
-    <t>2018</t>
-  </si>
-  <si>
     <t>OBGD18</t>
   </si>
   <si>
@@ -1639,12 +1639,12 @@
     <t>HSYR18</t>
   </si>
   <si>
+    <t>2018-11-30</t>
+  </si>
+  <si>
     <t>2018-12-30</t>
   </si>
   <si>
-    <t>2018-11-30</t>
-  </si>
-  <si>
     <t>RSYR18</t>
   </si>
   <si>
@@ -1663,15 +1663,15 @@
     <t>OEUR17</t>
   </si>
   <si>
+    <t>2017</t>
+  </si>
+  <si>
+    <t>2017-01-01</t>
+  </si>
+  <si>
     <t>2017-12-31</t>
   </si>
   <si>
-    <t>2017-01-01</t>
-  </si>
-  <si>
-    <t>2017</t>
-  </si>
-  <si>
     <t>HAFG17</t>
   </si>
   <si>
@@ -1714,12 +1714,12 @@
     <t>FDMA17</t>
   </si>
   <si>
+    <t>2017-09-28</t>
+  </si>
+  <si>
     <t>2017-12-29</t>
   </si>
   <si>
-    <t>2017-09-28</t>
-  </si>
-  <si>
     <t>OPRK17</t>
   </si>
   <si>
@@ -1741,24 +1741,24 @@
     <t>FKEN17</t>
   </si>
   <si>
+    <t>2017-02-10</t>
+  </si>
+  <si>
     <t>2017-11-30</t>
   </si>
   <si>
-    <t>2017-02-10</t>
-  </si>
-  <si>
     <t>HLBY17</t>
   </si>
   <si>
     <t>FMDG17</t>
   </si>
   <si>
+    <t>2017-03-20</t>
+  </si>
+  <si>
     <t>2017-06-20</t>
   </si>
   <si>
-    <t>2017-03-20</t>
-  </si>
-  <si>
     <t>HMLI17</t>
   </si>
   <si>
@@ -1768,12 +1768,12 @@
     <t>FMOZ17</t>
   </si>
   <si>
+    <t>2017-02-28</t>
+  </si>
+  <si>
     <t>2017-05-31</t>
   </si>
   <si>
-    <t>2017-02-28</t>
-  </si>
-  <si>
     <t>HMMR17</t>
   </si>
   <si>
@@ -1792,12 +1792,12 @@
     <t>FPER17</t>
   </si>
   <si>
+    <t>2017-04-01</t>
+  </si>
+  <si>
     <t>2017-10-31</t>
   </si>
   <si>
-    <t>2017-04-01</t>
-  </si>
-  <si>
     <t>HCOG17</t>
   </si>
   <si>
@@ -1840,15 +1840,15 @@
     <t>OEUR16</t>
   </si>
   <si>
+    <t>2016</t>
+  </si>
+  <si>
+    <t>2016-01-01</t>
+  </si>
+  <si>
     <t>2016-12-31</t>
   </si>
   <si>
-    <t>2016-01-01</t>
-  </si>
-  <si>
-    <t>2016</t>
-  </si>
-  <si>
     <t>HAFG16</t>
   </si>
   <si>
@@ -1888,21 +1888,21 @@
     <t>FECU16</t>
   </si>
   <si>
+    <t>2016-04-16</t>
+  </si>
+  <si>
     <t>2016-10-31</t>
   </si>
   <si>
-    <t>2016-04-16</t>
-  </si>
-  <si>
     <t>FFJI16</t>
   </si>
   <si>
+    <t>2016-02-20</t>
+  </si>
+  <si>
     <t>2016-05-30</t>
   </si>
   <si>
-    <t>2016-02-20</t>
-  </si>
-  <si>
     <t>HGMB16</t>
   </si>
   <si>
@@ -1945,12 +1945,12 @@
     <t>FIRQ16</t>
   </si>
   <si>
+    <t>2016-07-20</t>
+  </si>
+  <si>
     <t>2016-10-01</t>
   </si>
   <si>
-    <t>2016-07-20</t>
-  </si>
-  <si>
     <t>HMMR16</t>
   </si>
   <si>
@@ -1999,27 +1999,27 @@
     <t>HZWE1617</t>
   </si>
   <si>
+    <t>2016-04-01</t>
+  </si>
+  <si>
     <t>2017-03-31</t>
   </si>
   <si>
-    <t>2016-04-01</t>
-  </si>
-  <si>
     <t>HAFG15</t>
   </si>
   <si>
     <t>Strategic response plan</t>
   </si>
   <si>
+    <t>2015</t>
+  </si>
+  <si>
+    <t>2015-01-01</t>
+  </si>
+  <si>
     <t>2015-12-31</t>
   </si>
   <si>
-    <t>2015-01-01</t>
-  </si>
-  <si>
-    <t>2015</t>
-  </si>
-  <si>
     <t>HBFA15</t>
   </si>
   <si>
@@ -2047,12 +2047,12 @@
     <t>FGTM1415</t>
   </si>
   <si>
+    <t>2014-11-03</t>
+  </si>
+  <si>
     <t>2015-09-30</t>
   </si>
   <si>
-    <t>2014-11-03</t>
-  </si>
-  <si>
     <t>FHTI15</t>
   </si>
   <si>
@@ -2068,24 +2068,24 @@
     <t>FVUT15</t>
   </si>
   <si>
+    <t>2015-03-24</t>
+  </si>
+  <si>
     <t>2015-10-31</t>
   </si>
   <si>
-    <t>2015-03-24</t>
-  </si>
-  <si>
     <t>HIRQ15</t>
   </si>
   <si>
     <t>HLBY1415</t>
   </si>
   <si>
+    <t>2014-10-01</t>
+  </si>
+  <si>
     <t>2015-05-31</t>
   </si>
   <si>
-    <t>2014-10-01</t>
-  </si>
-  <si>
     <t>HMLI15</t>
   </si>
   <si>
@@ -2146,15 +2146,15 @@
     <t>HAFG14</t>
   </si>
   <si>
+    <t>2014</t>
+  </si>
+  <si>
+    <t>2014-01-01</t>
+  </si>
+  <si>
     <t>2014-12-31</t>
   </si>
   <si>
-    <t>2014-01-01</t>
-  </si>
-  <si>
-    <t>2014</t>
-  </si>
-  <si>
     <t>HBFA1314</t>
   </si>
   <si>
@@ -2230,21 +2230,21 @@
     <t>FPHL1314</t>
   </si>
   <si>
+    <t>2013-10-22</t>
+  </si>
+  <si>
     <t>2014-04-22</t>
   </si>
   <si>
-    <t>2013-10-22</t>
-  </si>
-  <si>
     <t>SPHL1314</t>
   </si>
   <si>
+    <t>2013-11-08</t>
+  </si>
+  <si>
     <t>2014-11-07</t>
   </si>
   <si>
-    <t>2013-11-08</t>
-  </si>
-  <si>
     <t>HPHL1314</t>
   </si>
   <si>
@@ -2254,12 +2254,12 @@
     <t>HPHL1314a</t>
   </si>
   <si>
+    <t>2013-10-01</t>
+  </si>
+  <si>
     <t>2014-08-31</t>
   </si>
   <si>
-    <t>2013-10-01</t>
-  </si>
-  <si>
     <t>SCOD14</t>
   </si>
   <si>
@@ -2326,12 +2326,12 @@
     <t>Consolidated appeals process</t>
   </si>
   <si>
+    <t>2013</t>
+  </si>
+  <si>
     <t>2013-12-31</t>
   </si>
   <si>
-    <t>2013</t>
-  </si>
-  <si>
     <t>CBFA13</t>
   </si>
   <si>
@@ -2416,15 +2416,15 @@
     <t>CKEN12</t>
   </si>
   <si>
+    <t>2012</t>
+  </si>
+  <si>
+    <t>2012-01-01</t>
+  </si>
+  <si>
     <t>2012-12-31</t>
   </si>
   <si>
-    <t>2012-01-01</t>
-  </si>
-  <si>
-    <t>2012</t>
-  </si>
-  <si>
     <t>CAFG1112</t>
   </si>
   <si>
@@ -2464,12 +2464,12 @@
     <t>FLSO1213</t>
   </si>
   <si>
+    <t>2012-09-18</t>
+  </si>
+  <si>
     <t>2013-03-25</t>
   </si>
   <si>
-    <t>2012-09-18</t>
-  </si>
-  <si>
     <t>CLBR12</t>
   </si>
   <si>
@@ -2509,12 +2509,12 @@
     <t>CSYR12</t>
   </si>
   <si>
+    <t>2012-06-05</t>
+  </si>
+  <si>
     <t>2012-12-05</t>
   </si>
   <si>
-    <t>2012-06-05</t>
-  </si>
-  <si>
     <t>CYEM12</t>
   </si>
   <si>
@@ -2527,12 +2527,12 @@
     <t>CKEN1113</t>
   </si>
   <si>
+    <t>2011</t>
+  </si>
+  <si>
     <t>2011-01-01</t>
   </si>
   <si>
-    <t>2011</t>
-  </si>
-  <si>
     <t>CAFG11</t>
   </si>
   <si>
@@ -2557,12 +2557,12 @@
     <t>FSLV1112</t>
   </si>
   <si>
+    <t>2011-10-25</t>
+  </si>
+  <si>
     <t>2012-04-25</t>
   </si>
   <si>
-    <t>2011-10-25</t>
-  </si>
-  <si>
     <t>CHTI1011</t>
   </si>
   <si>
@@ -2581,33 +2581,33 @@
     <t>FNAM11</t>
   </si>
   <si>
+    <t>2011-04-11</t>
+  </si>
+  <si>
     <t>2011-10-11</t>
   </si>
   <si>
-    <t>2011-04-11</t>
-  </si>
-  <si>
     <t>FNIC1112</t>
   </si>
   <si>
+    <t>2011-10-27</t>
+  </si>
+  <si>
     <t>2012-04-26</t>
   </si>
   <si>
-    <t>2011-10-27</t>
-  </si>
-  <si>
     <t>CNER11</t>
   </si>
   <si>
     <t>FPAK1112</t>
   </si>
   <si>
+    <t>2011-09-15</t>
+  </si>
+  <si>
     <t>2012-06-30</t>
   </si>
   <si>
-    <t>2011-09-15</t>
-  </si>
-  <si>
     <t>FXLBYREG11</t>
   </si>
   <si>
@@ -2650,24 +2650,24 @@
     <t>CAFG10</t>
   </si>
   <si>
+    <t>2010</t>
+  </si>
+  <si>
+    <t>2010-01-01</t>
+  </si>
+  <si>
     <t>2010-12-31</t>
   </si>
   <si>
-    <t>2010-01-01</t>
-  </si>
-  <si>
-    <t>2010</t>
-  </si>
-  <si>
     <t>OBFA1011</t>
   </si>
   <si>
+    <t>2010-08-01</t>
+  </si>
+  <si>
     <t>2011-01-31</t>
   </si>
   <si>
-    <t>2010-08-01</t>
-  </si>
-  <si>
     <t>CCAF10</t>
   </si>
   <si>
@@ -2680,30 +2680,30 @@
     <t>FSLV0910</t>
   </si>
   <si>
+    <t>2009-11-01</t>
+  </si>
+  <si>
     <t>2010-05-31</t>
   </si>
   <si>
-    <t>2009-11-01</t>
-  </si>
-  <si>
     <t>FGTM10</t>
   </si>
   <si>
+    <t>2010-06-10</t>
+  </si>
+  <si>
     <t>2010-12-09</t>
   </si>
   <si>
-    <t>2010-06-10</t>
-  </si>
-  <si>
     <t>CGTM10</t>
   </si>
   <si>
+    <t>2010-02-12</t>
+  </si>
+  <si>
     <t>2010-08-11</t>
   </si>
   <si>
-    <t>2010-02-12</t>
-  </si>
-  <si>
     <t>FHTI10</t>
   </si>
   <si>
@@ -2722,12 +2722,12 @@
     <t>FKGZ1011</t>
   </si>
   <si>
+    <t>2010-06-01</t>
+  </si>
+  <si>
     <t>2011-06-30</t>
   </si>
   <si>
-    <t>2010-06-01</t>
-  </si>
-  <si>
     <t>CMNG1011</t>
   </si>
   <si>
@@ -2794,24 +2794,24 @@
     <t>CAFG09</t>
   </si>
   <si>
+    <t>2009</t>
+  </si>
+  <si>
+    <t>2009-01-01</t>
+  </si>
+  <si>
     <t>2009-12-31</t>
   </si>
   <si>
-    <t>2009-01-01</t>
-  </si>
-  <si>
-    <t>2009</t>
-  </si>
-  <si>
     <t>FBFA0910</t>
   </si>
   <si>
+    <t>2009-09-10</t>
+  </si>
+  <si>
     <t>2010-03-09</t>
   </si>
   <si>
-    <t>2009-09-10</t>
-  </si>
-  <si>
     <t>CCAF09</t>
   </si>
   <si>
@@ -2851,21 +2851,21 @@
     <t>FMDG09</t>
   </si>
   <si>
+    <t>2009-04-01</t>
+  </si>
+  <si>
     <t>2009-10-31</t>
   </si>
   <si>
-    <t>2009-04-01</t>
-  </si>
-  <si>
     <t>FNAM09</t>
   </si>
   <si>
+    <t>2009-03-20</t>
+  </si>
+  <si>
     <t>2009-09-30</t>
   </si>
   <si>
-    <t>2009-03-20</t>
-  </si>
-  <si>
     <t>ONPL09</t>
   </si>
   <si>
@@ -2878,12 +2878,12 @@
     <t>FPHL0910</t>
   </si>
   <si>
+    <t>2009-10-03</t>
+  </si>
+  <si>
     <t>2010-03-31</t>
   </si>
   <si>
-    <t>2009-10-03</t>
-  </si>
-  <si>
     <t>CSOM09</t>
   </si>
   <si>
@@ -2896,12 +2896,12 @@
     <t>OSYR0910</t>
   </si>
   <si>
+    <t>2009-07-15</t>
+  </si>
+  <si>
     <t>2010-06-14</t>
   </si>
   <si>
-    <t>2009-07-15</t>
-  </si>
-  <si>
     <t>OTJK09</t>
   </si>
   <si>
@@ -2938,24 +2938,24 @@
     <t>OAFG08</t>
   </si>
   <si>
+    <t>2008</t>
+  </si>
+  <si>
+    <t>2008-02-01</t>
+  </si>
+  <si>
     <t>2008-06-30</t>
   </si>
   <si>
-    <t>2008-02-01</t>
-  </si>
-  <si>
-    <t>2008</t>
-  </si>
-  <si>
     <t>OAFG0809</t>
   </si>
   <si>
+    <t>2008-07-01</t>
+  </si>
+  <si>
     <t>2009-06-30</t>
   </si>
   <si>
-    <t>2008-07-01</t>
-  </si>
-  <si>
     <t>FBOL08</t>
   </si>
   <si>
@@ -2965,12 +2965,12 @@
     <t>CCAF08</t>
   </si>
   <si>
+    <t>2008-01-01</t>
+  </si>
+  <si>
     <t>2008-12-31</t>
   </si>
   <si>
-    <t>2008-01-01</t>
-  </si>
-  <si>
     <t>CTCD08</t>
   </si>
   <si>
@@ -2986,21 +2986,21 @@
     <t>ODJI0809</t>
   </si>
   <si>
+    <t>2008-08-01</t>
+  </si>
+  <si>
     <t>2009-02-28</t>
   </si>
   <si>
-    <t>2008-08-01</t>
-  </si>
-  <si>
     <t>FGEO0809</t>
   </si>
   <si>
+    <t>2008-08-09</t>
+  </si>
+  <si>
     <t>2009-02-09</t>
   </si>
   <si>
-    <t>2008-08-09</t>
-  </si>
-  <si>
     <t>FHTI0809</t>
   </si>
   <si>
@@ -3010,12 +3010,12 @@
     <t>FHND0809</t>
   </si>
   <si>
+    <t>2008-11-01</t>
+  </si>
+  <si>
     <t>2009-04-30</t>
   </si>
   <si>
-    <t>2008-11-01</t>
-  </si>
-  <si>
     <t>CIRQ08</t>
   </si>
   <si>
@@ -3025,12 +3025,12 @@
     <t>FKGZ0809</t>
   </si>
   <si>
+    <t>2008-12-01</t>
+  </si>
+  <si>
     <t>2009-05-31</t>
   </si>
   <si>
-    <t>2008-12-01</t>
-  </si>
-  <si>
     <t>OLAO0809</t>
   </si>
   <si>
@@ -3052,12 +3052,12 @@
     <t>FMMR08</t>
   </si>
   <si>
+    <t>2008-05-01</t>
+  </si>
+  <si>
     <t>2008-11-30</t>
   </si>
   <si>
-    <t>2008-05-01</t>
-  </si>
-  <si>
     <t>ONPL08</t>
   </si>
   <si>
@@ -3112,33 +3112,33 @@
     <t>FBOL07</t>
   </si>
   <si>
+    <t>2007</t>
+  </si>
+  <si>
+    <t>2007-02-22</t>
+  </si>
+  <si>
     <t>2007-08-21</t>
   </si>
   <si>
-    <t>2007-02-22</t>
-  </si>
-  <si>
-    <t>2007</t>
-  </si>
-  <si>
     <t>FBFA0708</t>
   </si>
   <si>
+    <t>2007-11-01</t>
+  </si>
+  <si>
     <t>2008-01-31</t>
   </si>
   <si>
-    <t>2007-11-01</t>
-  </si>
-  <si>
     <t>CBDI07</t>
   </si>
   <si>
+    <t>2007-01-01</t>
+  </si>
+  <si>
     <t>2007-12-31</t>
   </si>
   <si>
-    <t>2007-01-01</t>
-  </si>
-  <si>
     <t>CCAF07</t>
   </si>
   <si>
@@ -3160,12 +3160,12 @@
     <t>FGHA0708</t>
   </si>
   <si>
+    <t>2007-09-01</t>
+  </si>
+  <si>
     <t>2008-03-31</t>
   </si>
   <si>
-    <t>2007-09-01</t>
-  </si>
-  <si>
     <t>CXGLR07</t>
   </si>
   <si>
@@ -3178,75 +3178,75 @@
     <t>FPRK07</t>
   </si>
   <si>
+    <t>2007-08-28</t>
+  </si>
+  <si>
     <t>2007-11-30</t>
   </si>
   <si>
-    <t>2007-08-28</t>
-  </si>
-  <si>
     <t>OLBN07</t>
   </si>
   <si>
+    <t>2007-06-04</t>
+  </si>
+  <si>
     <t>2007-09-03</t>
   </si>
   <si>
-    <t>2007-06-04</t>
-  </si>
-  <si>
     <t>FLSO0708</t>
   </si>
   <si>
+    <t>2007-07-28</t>
+  </si>
+  <si>
     <t>2008-01-28</t>
   </si>
   <si>
-    <t>2007-07-28</t>
-  </si>
-  <si>
     <t>CLBR07</t>
   </si>
   <si>
     <t>FMDG07</t>
   </si>
   <si>
+    <t>2007-03-15</t>
+  </si>
+  <si>
     <t>2007-09-15</t>
   </si>
   <si>
-    <t>2007-03-15</t>
-  </si>
-  <si>
     <t>FMOZ07</t>
   </si>
   <si>
+    <t>2007-03-01</t>
+  </si>
+  <si>
     <t>2007-06-30</t>
   </si>
   <si>
-    <t>2007-03-01</t>
-  </si>
-  <si>
     <t>ONPL07</t>
   </si>
   <si>
     <t>FNIC0708</t>
   </si>
   <si>
+    <t>2007-09-07</t>
+  </si>
+  <si>
     <t>2008-02-28</t>
   </si>
   <si>
-    <t>2007-09-07</t>
-  </si>
-  <si>
     <t>ORUS07</t>
   </si>
   <si>
     <t>FPAK07</t>
   </si>
   <si>
+    <t>2007-07-15</t>
+  </si>
+  <si>
     <t>2007-10-31</t>
   </si>
   <si>
-    <t>2007-07-15</t>
-  </si>
-  <si>
     <t>FPER0708</t>
   </si>
   <si>
@@ -3283,12 +3283,12 @@
     <t>FSWZ0708</t>
   </si>
   <si>
+    <t>2007-07-20</t>
+  </si>
+  <si>
     <t>2008-01-20</t>
   </si>
   <si>
-    <t>2007-07-20</t>
-  </si>
-  <si>
     <t>CTLS07</t>
   </si>
   <si>
@@ -3316,15 +3316,15 @@
     <t>OAFG06</t>
   </si>
   <si>
+    <t>2006</t>
+  </si>
+  <si>
+    <t>2006-07-01</t>
+  </si>
+  <si>
     <t>2006-12-31</t>
   </si>
   <si>
-    <t>2006-07-01</t>
-  </si>
-  <si>
-    <t>2006</t>
-  </si>
-  <si>
     <t>CBDI06</t>
   </si>
   <si>
@@ -3349,21 +3349,21 @@
     <t>OETH06a</t>
   </si>
   <si>
+    <t>2006-08-25</t>
+  </si>
+  <si>
     <t>2006-11-25</t>
   </si>
   <si>
-    <t>2006-08-25</t>
-  </si>
-  <si>
     <t>OETH0607</t>
   </si>
   <si>
+    <t>2006-11-23</t>
+  </si>
+  <si>
     <t>2007-01-22</t>
   </si>
   <si>
-    <t>2006-11-23</t>
-  </si>
-  <si>
     <t>CXGLR06</t>
   </si>
   <si>
@@ -3373,12 +3373,12 @@
     <t>FGNB06</t>
   </si>
   <si>
+    <t>2006-05-01</t>
+  </si>
+  <si>
     <t>2006-11-30</t>
   </si>
   <si>
-    <t>2006-05-01</t>
-  </si>
-  <si>
     <t>CXHAF06</t>
   </si>
   <si>
@@ -3388,12 +3388,12 @@
     <t>FKEN0607</t>
   </si>
   <si>
+    <t>2006-10-16</t>
+  </si>
+  <si>
     <t>2007-04-15</t>
   </si>
   <si>
-    <t>2006-10-16</t>
-  </si>
-  <si>
     <t>FKEN06</t>
   </si>
   <si>
@@ -3403,12 +3403,12 @@
     <t>FLBN06</t>
   </si>
   <si>
+    <t>2006-07-24</t>
+  </si>
+  <si>
     <t>2006-10-23</t>
   </si>
   <si>
-    <t>2006-07-24</t>
-  </si>
-  <si>
     <t>CLBR06</t>
   </si>
   <si>
@@ -3436,12 +3436,12 @@
     <t>FSOM0607</t>
   </si>
   <si>
+    <t>2006-12-05</t>
+  </si>
+  <si>
     <t>2007-03-05</t>
   </si>
   <si>
-    <t>2006-12-05</t>
-  </si>
-  <si>
     <t>OLKA06</t>
   </si>
   <si>
@@ -3478,33 +3478,33 @@
     <t>FAGO05</t>
   </si>
   <si>
+    <t>2005</t>
+  </si>
+  <si>
+    <t>2005-04-01</t>
+  </si>
+  <si>
     <t>2005-06-30</t>
   </si>
   <si>
-    <t>2005-04-01</t>
-  </si>
-  <si>
-    <t>2005</t>
-  </si>
-  <si>
     <t>FBEN05</t>
   </si>
   <si>
+    <t>2005-05-01</t>
+  </si>
+  <si>
     <t>2005-10-31</t>
   </si>
   <si>
-    <t>2005-05-01</t>
-  </si>
-  <si>
     <t>CBDI05</t>
   </si>
   <si>
+    <t>2005-01-01</t>
+  </si>
+  <si>
     <t>2005-12-31</t>
   </si>
   <si>
-    <t>2005-01-01</t>
-  </si>
-  <si>
     <t>CCAF05</t>
   </si>
   <si>
@@ -3547,12 +3547,12 @@
     <t>FGUY05</t>
   </si>
   <si>
+    <t>2005-02-01</t>
+  </si>
+  <si>
     <t>2005-08-01</t>
   </si>
   <si>
-    <t>2005-02-01</t>
-  </si>
-  <si>
     <t>FXINDTSU05</t>
   </si>
   <si>
@@ -3565,12 +3565,12 @@
     <t>FNER05</t>
   </si>
   <si>
+    <t>2005-06-01</t>
+  </si>
+  <si>
     <t>2005-09-30</t>
   </si>
   <si>
-    <t>2005-06-01</t>
-  </si>
-  <si>
     <t>CCOG05</t>
   </si>
   <si>
@@ -3580,24 +3580,24 @@
     <t>R0506</t>
   </si>
   <si>
+    <t>2005-11-01</t>
+  </si>
+  <si>
     <t>2006-05-31</t>
   </si>
   <si>
-    <t>2005-11-01</t>
-  </si>
-  <si>
     <t>OSDN05</t>
   </si>
   <si>
     <t>FXSASIA0506</t>
   </si>
   <si>
+    <t>2005-10-11</t>
+  </si>
+  <si>
     <t>2006-04-10</t>
   </si>
   <si>
-    <t>2005-10-11</t>
-  </si>
-  <si>
     <t>CSDN05</t>
   </si>
   <si>
@@ -3616,15 +3616,15 @@
     <t>OAFG04</t>
   </si>
   <si>
+    <t>2004</t>
+  </si>
+  <si>
+    <t>2004-09-01</t>
+  </si>
+  <si>
     <t>2004-12-31</t>
   </si>
   <si>
-    <t>2004-09-01</t>
-  </si>
-  <si>
-    <t>2004</t>
-  </si>
-  <si>
     <t>CAGO04</t>
   </si>
   <si>
@@ -3634,21 +3634,21 @@
     <t>FBGD0405</t>
   </si>
   <si>
+    <t>2004-08-01</t>
+  </si>
+  <si>
     <t>2005-01-31</t>
   </si>
   <si>
-    <t>2004-08-01</t>
-  </si>
-  <si>
     <t>FBOL0405</t>
   </si>
   <si>
+    <t>2004-11-01</t>
+  </si>
+  <si>
     <t>2005-05-31</t>
   </si>
   <si>
-    <t>2004-11-01</t>
-  </si>
-  <si>
     <t>CBDI04</t>
   </si>
   <si>
@@ -3724,21 +3724,21 @@
     <t>FMDG04</t>
   </si>
   <si>
+    <t>2004-03-19</t>
+  </si>
+  <si>
     <t>2004-06-19</t>
   </si>
   <si>
-    <t>2004-03-19</t>
-  </si>
-  <si>
     <t>FPHL0405</t>
   </si>
   <si>
+    <t>2004-12-15</t>
+  </si>
+  <si>
     <t>2005-03-15</t>
   </si>
   <si>
-    <t>2004-12-15</t>
-  </si>
-  <si>
     <t>CSLE04</t>
   </si>
   <si>
@@ -3769,15 +3769,15 @@
     <t>OAFG03</t>
   </si>
   <si>
+    <t>2003</t>
+  </si>
+  <si>
+    <t>2003-01-01</t>
+  </si>
+  <si>
     <t>2003-12-31</t>
   </si>
   <si>
-    <t>2003-01-01</t>
-  </si>
-  <si>
-    <t>2003</t>
-  </si>
-  <si>
     <t>CAGO03</t>
   </si>
   <si>
@@ -3790,12 +3790,12 @@
     <t>FCAF03</t>
   </si>
   <si>
+    <t>2003-04-01</t>
+  </si>
+  <si>
     <t>2003-06-30</t>
   </si>
   <si>
-    <t>2003-04-01</t>
-  </si>
-  <si>
     <t>CRUS03</t>
   </si>
   <si>
@@ -3808,12 +3808,12 @@
     <t>RCIV0203</t>
   </si>
   <si>
+    <t>2002-11-01</t>
+  </si>
+  <si>
     <t>2003-01-31</t>
   </si>
   <si>
-    <t>2002-11-01</t>
-  </si>
-  <si>
     <t>CCIV03</t>
   </si>
   <si>
@@ -3841,21 +3841,21 @@
     <t>OHTI03</t>
   </si>
   <si>
+    <t>2003-03-01</t>
+  </si>
+  <si>
     <t>2003-08-31</t>
   </si>
   <si>
-    <t>2003-03-01</t>
-  </si>
-  <si>
     <t>CLSO0304</t>
   </si>
   <si>
+    <t>2003-07-01</t>
+  </si>
+  <si>
     <t>2004-06-30</t>
   </si>
   <si>
-    <t>2003-07-01</t>
-  </si>
-  <si>
     <t>CMWI03</t>
   </si>
   <si>
@@ -3913,15 +3913,15 @@
     <t>CAFG0102</t>
   </si>
   <si>
+    <t>2002</t>
+  </si>
+  <si>
+    <t>2001-10-01</t>
+  </si>
+  <si>
     <t>2002-12-31</t>
   </si>
   <si>
-    <t>2001-10-01</t>
-  </si>
-  <si>
-    <t>2002</t>
-  </si>
-  <si>
     <t>CAGO02</t>
   </si>
   <si>
@@ -4021,15 +4021,15 @@
     <t>CAFG01</t>
   </si>
   <si>
+    <t>2001</t>
+  </si>
+  <si>
+    <t>2001-01-01</t>
+  </si>
+  <si>
     <t>2001-09-30</t>
   </si>
   <si>
-    <t>2001-01-01</t>
-  </si>
-  <si>
-    <t>2001</t>
-  </si>
-  <si>
     <t>CAGO01</t>
   </si>
   <si>
@@ -4105,13 +4105,13 @@
     <t>CAGO00</t>
   </si>
   <si>
+    <t>2000</t>
+  </si>
+  <si>
+    <t>2000-01-01</t>
+  </si>
+  <si>
     <t>2000-12-31</t>
-  </si>
-  <si>
-    <t>2000-01-01</t>
-  </si>
-  <si>
-    <t>2000</t>
   </si>
   <si>
     <t>CBDI00</t>
@@ -4700,13 +4700,13 @@
         <v>22</v>
       </c>
       <c r="D10" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" t="s">
         <v>23</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>24</v>
-      </c>
-      <c r="F10" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -4720,13 +4720,13 @@
         <v>18</v>
       </c>
       <c r="D11" t="s">
+        <v>9</v>
+      </c>
+      <c r="E11" t="s">
+        <v>23</v>
+      </c>
+      <c r="F11" t="s">
         <v>26</v>
-      </c>
-      <c r="E11" t="s">
-        <v>24</v>
-      </c>
-      <c r="F11" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -4740,13 +4740,13 @@
         <v>18</v>
       </c>
       <c r="D12" t="s">
+        <v>9</v>
+      </c>
+      <c r="E12" t="s">
         <v>23</v>
       </c>
-      <c r="E12" t="s">
+      <c r="F12" t="s">
         <v>24</v>
-      </c>
-      <c r="F12" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -4860,13 +4860,13 @@
         <v>16</v>
       </c>
       <c r="D18" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="E18" t="s">
         <v>10</v>
       </c>
       <c r="F18" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -5020,13 +5020,13 @@
         <v>16</v>
       </c>
       <c r="D26" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="E26" t="s">
         <v>44</v>
       </c>
       <c r="F26" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -5220,13 +5220,13 @@
         <v>16</v>
       </c>
       <c r="D36" t="s">
-        <v>55</v>
+        <v>9</v>
       </c>
       <c r="E36" t="s">
         <v>10</v>
       </c>
       <c r="F36" t="s">
-        <v>11</v>
+        <v>55</v>
       </c>
     </row>
     <row r="37" spans="1:6">
@@ -5300,13 +5300,13 @@
         <v>16</v>
       </c>
       <c r="D40" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="E40" t="s">
         <v>59</v>
       </c>
       <c r="F40" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="41" spans="1:6">
@@ -5520,13 +5520,13 @@
         <v>18</v>
       </c>
       <c r="D51" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="E51" t="s">
         <v>59</v>
       </c>
       <c r="F51" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="52" spans="1:6">
@@ -5540,13 +5540,13 @@
         <v>18</v>
       </c>
       <c r="D52" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="E52" t="s">
         <v>59</v>
       </c>
       <c r="F52" t="s">
-        <v>60</v>
+        <v>78</v>
       </c>
     </row>
     <row r="53" spans="1:6">
@@ -5580,13 +5580,13 @@
         <v>18</v>
       </c>
       <c r="D54" t="s">
-        <v>81</v>
+        <v>58</v>
       </c>
       <c r="E54" t="s">
         <v>59</v>
       </c>
       <c r="F54" t="s">
-        <v>60</v>
+        <v>81</v>
       </c>
     </row>
     <row r="55" spans="1:6">
@@ -5620,13 +5620,13 @@
         <v>18</v>
       </c>
       <c r="D56" t="s">
-        <v>84</v>
+        <v>58</v>
       </c>
       <c r="E56" t="s">
         <v>59</v>
       </c>
       <c r="F56" t="s">
-        <v>60</v>
+        <v>84</v>
       </c>
     </row>
     <row r="57" spans="1:6">
@@ -5740,13 +5740,13 @@
         <v>16</v>
       </c>
       <c r="D62" t="s">
-        <v>93</v>
+        <v>58</v>
       </c>
       <c r="E62" t="s">
         <v>59</v>
       </c>
       <c r="F62" t="s">
-        <v>60</v>
+        <v>93</v>
       </c>
     </row>
     <row r="63" spans="1:6">
@@ -6100,13 +6100,13 @@
         <v>16</v>
       </c>
       <c r="D80" t="s">
-        <v>84</v>
+        <v>58</v>
       </c>
       <c r="E80" t="s">
         <v>59</v>
       </c>
       <c r="F80" t="s">
-        <v>60</v>
+        <v>84</v>
       </c>
     </row>
     <row r="81" spans="1:6">
@@ -6120,13 +6120,13 @@
         <v>16</v>
       </c>
       <c r="D81" t="s">
-        <v>84</v>
+        <v>58</v>
       </c>
       <c r="E81" t="s">
         <v>59</v>
       </c>
       <c r="F81" t="s">
-        <v>60</v>
+        <v>84</v>
       </c>
     </row>
     <row r="82" spans="1:6">
@@ -6180,13 +6180,13 @@
         <v>18</v>
       </c>
       <c r="D84" t="s">
-        <v>84</v>
+        <v>58</v>
       </c>
       <c r="E84" t="s">
         <v>59</v>
       </c>
       <c r="F84" t="s">
-        <v>60</v>
+        <v>84</v>
       </c>
     </row>
     <row r="85" spans="1:6">
@@ -6200,13 +6200,13 @@
         <v>18</v>
       </c>
       <c r="D85" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="E85" t="s">
         <v>59</v>
       </c>
       <c r="F85" t="s">
-        <v>60</v>
+        <v>78</v>
       </c>
     </row>
     <row r="86" spans="1:6">
@@ -6560,13 +6560,13 @@
         <v>18</v>
       </c>
       <c r="D103" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="E103" t="s">
         <v>121</v>
       </c>
       <c r="F103" t="s">
-        <v>122</v>
+        <v>144</v>
       </c>
     </row>
     <row r="104" spans="1:6">
@@ -6580,13 +6580,13 @@
         <v>18</v>
       </c>
       <c r="D104" t="s">
-        <v>146</v>
+        <v>120</v>
       </c>
       <c r="E104" t="s">
         <v>121</v>
       </c>
       <c r="F104" t="s">
-        <v>122</v>
+        <v>146</v>
       </c>
     </row>
     <row r="105" spans="1:6">
@@ -6640,13 +6640,13 @@
         <v>16</v>
       </c>
       <c r="D107" t="s">
-        <v>146</v>
+        <v>120</v>
       </c>
       <c r="E107" t="s">
         <v>151</v>
       </c>
       <c r="F107" t="s">
-        <v>122</v>
+        <v>146</v>
       </c>
     </row>
     <row r="108" spans="1:6">
@@ -7620,13 +7620,13 @@
         <v>16</v>
       </c>
       <c r="D156" t="s">
+        <v>187</v>
+      </c>
+      <c r="E156" t="s">
         <v>211</v>
       </c>
-      <c r="E156" t="s">
+      <c r="F156" t="s">
         <v>212</v>
-      </c>
-      <c r="F156" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="157" spans="1:6">
@@ -7640,13 +7640,13 @@
         <v>16</v>
       </c>
       <c r="D157" t="s">
+        <v>187</v>
+      </c>
+      <c r="E157" t="s">
         <v>214</v>
       </c>
-      <c r="E157" t="s">
+      <c r="F157" t="s">
         <v>215</v>
-      </c>
-      <c r="F157" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="158" spans="1:6">
@@ -7740,13 +7740,13 @@
         <v>66</v>
       </c>
       <c r="D162" t="s">
-        <v>214</v>
+        <v>187</v>
       </c>
       <c r="E162" t="s">
         <v>188</v>
       </c>
       <c r="F162" t="s">
-        <v>189</v>
+        <v>215</v>
       </c>
     </row>
     <row r="163" spans="1:6">
@@ -7760,13 +7760,13 @@
         <v>16</v>
       </c>
       <c r="D163" t="s">
-        <v>211</v>
+        <v>187</v>
       </c>
       <c r="E163" t="s">
         <v>188</v>
       </c>
       <c r="F163" t="s">
-        <v>189</v>
+        <v>212</v>
       </c>
     </row>
     <row r="164" spans="1:6">
@@ -7940,13 +7940,13 @@
         <v>22</v>
       </c>
       <c r="D172" t="s">
+        <v>187</v>
+      </c>
+      <c r="E172" t="s">
         <v>231</v>
       </c>
-      <c r="E172" t="s">
+      <c r="F172" t="s">
         <v>232</v>
-      </c>
-      <c r="F172" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="173" spans="1:6">
@@ -7980,13 +7980,13 @@
         <v>18</v>
       </c>
       <c r="D174" t="s">
-        <v>211</v>
+        <v>187</v>
       </c>
       <c r="E174" t="s">
         <v>235</v>
       </c>
       <c r="F174" t="s">
-        <v>189</v>
+        <v>212</v>
       </c>
     </row>
     <row r="175" spans="1:6">
@@ -8020,13 +8020,13 @@
         <v>18</v>
       </c>
       <c r="D176" t="s">
-        <v>211</v>
+        <v>187</v>
       </c>
       <c r="E176" t="s">
         <v>238</v>
       </c>
       <c r="F176" t="s">
-        <v>189</v>
+        <v>212</v>
       </c>
     </row>
     <row r="177" spans="1:6">
@@ -8320,13 +8320,13 @@
         <v>16</v>
       </c>
       <c r="D191" t="s">
+        <v>247</v>
+      </c>
+      <c r="E191" t="s">
         <v>257</v>
       </c>
-      <c r="E191" t="s">
+      <c r="F191" t="s">
         <v>258</v>
-      </c>
-      <c r="F191" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="192" spans="1:6">
@@ -8420,13 +8420,13 @@
         <v>18</v>
       </c>
       <c r="D196" t="s">
+        <v>247</v>
+      </c>
+      <c r="E196" t="s">
         <v>264</v>
       </c>
-      <c r="E196" t="s">
+      <c r="F196" t="s">
         <v>265</v>
-      </c>
-      <c r="F196" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="197" spans="1:6">
@@ -8443,7 +8443,7 @@
         <v>247</v>
       </c>
       <c r="E197" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F197" t="s">
         <v>249</v>
@@ -8520,13 +8520,13 @@
         <v>18</v>
       </c>
       <c r="D201" t="s">
-        <v>271</v>
+        <v>247</v>
       </c>
       <c r="E201" t="s">
         <v>248</v>
       </c>
       <c r="F201" t="s">
-        <v>249</v>
+        <v>271</v>
       </c>
     </row>
     <row r="202" spans="1:6">
@@ -8600,13 +8600,13 @@
         <v>18</v>
       </c>
       <c r="D205" t="s">
+        <v>247</v>
+      </c>
+      <c r="E205" t="s">
         <v>276</v>
       </c>
-      <c r="E205" t="s">
+      <c r="F205" t="s">
         <v>277</v>
-      </c>
-      <c r="F205" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="206" spans="1:6">
@@ -8640,13 +8640,13 @@
         <v>18</v>
       </c>
       <c r="D207" t="s">
+        <v>247</v>
+      </c>
+      <c r="E207" t="s">
         <v>280</v>
       </c>
-      <c r="E207" t="s">
+      <c r="F207" t="s">
         <v>281</v>
-      </c>
-      <c r="F207" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="208" spans="1:6">
@@ -8780,13 +8780,13 @@
         <v>16</v>
       </c>
       <c r="D214" t="s">
-        <v>290</v>
+        <v>247</v>
       </c>
       <c r="E214" t="s">
         <v>288</v>
       </c>
       <c r="F214" t="s">
-        <v>249</v>
+        <v>290</v>
       </c>
     </row>
     <row r="215" spans="1:6">
@@ -8800,13 +8800,13 @@
         <v>16</v>
       </c>
       <c r="D215" t="s">
+        <v>247</v>
+      </c>
+      <c r="E215" t="s">
         <v>292</v>
       </c>
-      <c r="E215" t="s">
+      <c r="F215" t="s">
         <v>293</v>
-      </c>
-      <c r="F215" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="216" spans="1:6">
@@ -9100,13 +9100,13 @@
         <v>22</v>
       </c>
       <c r="D230" t="s">
-        <v>311</v>
+        <v>247</v>
       </c>
       <c r="E230" t="s">
         <v>308</v>
       </c>
       <c r="F230" t="s">
-        <v>249</v>
+        <v>311</v>
       </c>
     </row>
     <row r="231" spans="1:6">
@@ -9420,13 +9420,13 @@
         <v>66</v>
       </c>
       <c r="D246" t="s">
-        <v>247</v>
+        <v>315</v>
       </c>
       <c r="E246" t="s">
         <v>331</v>
       </c>
       <c r="F246" t="s">
-        <v>317</v>
+        <v>249</v>
       </c>
     </row>
     <row r="247" spans="1:6">
@@ -9440,13 +9440,13 @@
         <v>18</v>
       </c>
       <c r="D247" t="s">
+        <v>315</v>
+      </c>
+      <c r="E247" t="s">
         <v>334</v>
       </c>
-      <c r="E247" t="s">
+      <c r="F247" t="s">
         <v>335</v>
-      </c>
-      <c r="F247" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="248" spans="1:6">
@@ -9500,13 +9500,13 @@
         <v>66</v>
       </c>
       <c r="D250" t="s">
-        <v>247</v>
+        <v>315</v>
       </c>
       <c r="E250" t="s">
         <v>331</v>
       </c>
       <c r="F250" t="s">
-        <v>317</v>
+        <v>249</v>
       </c>
     </row>
     <row r="251" spans="1:6">
@@ -9520,13 +9520,13 @@
         <v>18</v>
       </c>
       <c r="D251" t="s">
+        <v>315</v>
+      </c>
+      <c r="E251" t="s">
         <v>340</v>
       </c>
-      <c r="E251" t="s">
+      <c r="F251" t="s">
         <v>341</v>
-      </c>
-      <c r="F251" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="252" spans="1:6">
@@ -9560,13 +9560,13 @@
         <v>18</v>
       </c>
       <c r="D253" t="s">
+        <v>315</v>
+      </c>
+      <c r="E253" t="s">
         <v>344</v>
       </c>
-      <c r="E253" t="s">
+      <c r="F253" t="s">
         <v>345</v>
-      </c>
-      <c r="F253" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="254" spans="1:6">
@@ -9600,13 +9600,13 @@
         <v>66</v>
       </c>
       <c r="D255" t="s">
-        <v>247</v>
+        <v>315</v>
       </c>
       <c r="E255" t="s">
         <v>331</v>
       </c>
       <c r="F255" t="s">
-        <v>317</v>
+        <v>249</v>
       </c>
     </row>
     <row r="256" spans="1:6">
@@ -9660,13 +9660,13 @@
         <v>16</v>
       </c>
       <c r="D258" t="s">
+        <v>315</v>
+      </c>
+      <c r="E258" t="s">
         <v>352</v>
       </c>
-      <c r="E258" t="s">
+      <c r="F258" t="s">
         <v>353</v>
-      </c>
-      <c r="F258" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="259" spans="1:6">
@@ -9700,13 +9700,13 @@
         <v>18</v>
       </c>
       <c r="D260" t="s">
-        <v>276</v>
+        <v>315</v>
       </c>
       <c r="E260" t="s">
         <v>319</v>
       </c>
       <c r="F260" t="s">
-        <v>317</v>
+        <v>277</v>
       </c>
     </row>
     <row r="261" spans="1:6">
@@ -10380,13 +10380,13 @@
         <v>66</v>
       </c>
       <c r="D294" t="s">
-        <v>319</v>
+        <v>383</v>
       </c>
       <c r="E294" t="s">
         <v>397</v>
       </c>
       <c r="F294" t="s">
-        <v>385</v>
+        <v>319</v>
       </c>
     </row>
     <row r="295" spans="1:6">
@@ -10540,13 +10540,13 @@
         <v>18</v>
       </c>
       <c r="D302" t="s">
+        <v>383</v>
+      </c>
+      <c r="E302" t="s">
         <v>407</v>
       </c>
-      <c r="E302" t="s">
+      <c r="F302" t="s">
         <v>408</v>
-      </c>
-      <c r="F302" t="s">
-        <v>385</v>
       </c>
     </row>
     <row r="303" spans="1:6">
@@ -10840,13 +10840,13 @@
         <v>18</v>
       </c>
       <c r="D317" t="s">
+        <v>383</v>
+      </c>
+      <c r="E317" t="s">
         <v>425</v>
       </c>
-      <c r="E317" t="s">
+      <c r="F317" t="s">
         <v>426</v>
-      </c>
-      <c r="F317" t="s">
-        <v>385</v>
       </c>
     </row>
     <row r="318" spans="1:6">
@@ -10880,13 +10880,13 @@
         <v>18</v>
       </c>
       <c r="D319" t="s">
+        <v>383</v>
+      </c>
+      <c r="E319" t="s">
         <v>429</v>
       </c>
-      <c r="E319" t="s">
+      <c r="F319" t="s">
         <v>430</v>
-      </c>
-      <c r="F319" t="s">
-        <v>385</v>
       </c>
     </row>
     <row r="320" spans="1:6">
@@ -11440,13 +11440,13 @@
         <v>16</v>
       </c>
       <c r="D347" t="s">
-        <v>407</v>
+        <v>383</v>
       </c>
       <c r="E347" t="s">
         <v>459</v>
       </c>
       <c r="F347" t="s">
-        <v>385</v>
+        <v>408</v>
       </c>
     </row>
     <row r="348" spans="1:6">
@@ -11800,13 +11800,13 @@
         <v>18</v>
       </c>
       <c r="D365" t="s">
-        <v>482</v>
+        <v>463</v>
       </c>
       <c r="E365" t="s">
         <v>464</v>
       </c>
       <c r="F365" t="s">
-        <v>465</v>
+        <v>482</v>
       </c>
     </row>
     <row r="366" spans="1:6">
@@ -11920,13 +11920,13 @@
         <v>66</v>
       </c>
       <c r="D371" t="s">
-        <v>489</v>
+        <v>463</v>
       </c>
       <c r="E371" t="s">
         <v>464</v>
       </c>
       <c r="F371" t="s">
-        <v>465</v>
+        <v>489</v>
       </c>
     </row>
     <row r="372" spans="1:6">
@@ -12160,13 +12160,13 @@
         <v>18</v>
       </c>
       <c r="D383" t="s">
+        <v>463</v>
+      </c>
+      <c r="E383" t="s">
         <v>502</v>
       </c>
-      <c r="E383" t="s">
+      <c r="F383" t="s">
         <v>503</v>
-      </c>
-      <c r="F383" t="s">
-        <v>465</v>
       </c>
     </row>
     <row r="384" spans="1:6">
@@ -12180,13 +12180,13 @@
         <v>18</v>
       </c>
       <c r="D384" t="s">
-        <v>502</v>
+        <v>463</v>
       </c>
       <c r="E384" t="s">
         <v>505</v>
       </c>
       <c r="F384" t="s">
-        <v>465</v>
+        <v>503</v>
       </c>
     </row>
     <row r="385" spans="1:6">
@@ -12720,13 +12720,13 @@
         <v>66</v>
       </c>
       <c r="D411" t="s">
-        <v>539</v>
+        <v>507</v>
       </c>
       <c r="E411" t="s">
         <v>508</v>
       </c>
       <c r="F411" t="s">
-        <v>509</v>
+        <v>539</v>
       </c>
     </row>
     <row r="412" spans="1:6">
@@ -12740,13 +12740,13 @@
         <v>66</v>
       </c>
       <c r="D412" t="s">
+        <v>507</v>
+      </c>
+      <c r="E412" t="s">
         <v>541</v>
       </c>
-      <c r="E412" t="s">
+      <c r="F412" t="s">
         <v>542</v>
-      </c>
-      <c r="F412" t="s">
-        <v>509</v>
       </c>
     </row>
     <row r="413" spans="1:6">
@@ -12780,13 +12780,13 @@
         <v>66</v>
       </c>
       <c r="D414" t="s">
+        <v>507</v>
+      </c>
+      <c r="E414" t="s">
         <v>541</v>
       </c>
-      <c r="E414" t="s">
+      <c r="F414" t="s">
         <v>542</v>
-      </c>
-      <c r="F414" t="s">
-        <v>509</v>
       </c>
     </row>
     <row r="415" spans="1:6">
@@ -13080,13 +13080,13 @@
         <v>18</v>
       </c>
       <c r="D429" t="s">
+        <v>549</v>
+      </c>
+      <c r="E429" t="s">
         <v>566</v>
       </c>
-      <c r="E429" t="s">
+      <c r="F429" t="s">
         <v>567</v>
-      </c>
-      <c r="F429" t="s">
-        <v>551</v>
       </c>
     </row>
     <row r="430" spans="1:6">
@@ -13200,13 +13200,13 @@
         <v>18</v>
       </c>
       <c r="D435" t="s">
+        <v>549</v>
+      </c>
+      <c r="E435" t="s">
         <v>575</v>
       </c>
-      <c r="E435" t="s">
+      <c r="F435" t="s">
         <v>576</v>
-      </c>
-      <c r="F435" t="s">
-        <v>551</v>
       </c>
     </row>
     <row r="436" spans="1:6">
@@ -13240,13 +13240,13 @@
         <v>18</v>
       </c>
       <c r="D437" t="s">
+        <v>549</v>
+      </c>
+      <c r="E437" t="s">
         <v>579</v>
       </c>
-      <c r="E437" t="s">
+      <c r="F437" t="s">
         <v>580</v>
-      </c>
-      <c r="F437" t="s">
-        <v>551</v>
       </c>
     </row>
     <row r="438" spans="1:6">
@@ -13300,13 +13300,13 @@
         <v>18</v>
       </c>
       <c r="D440" t="s">
+        <v>549</v>
+      </c>
+      <c r="E440" t="s">
         <v>584</v>
       </c>
-      <c r="E440" t="s">
+      <c r="F440" t="s">
         <v>585</v>
-      </c>
-      <c r="F440" t="s">
-        <v>551</v>
       </c>
     </row>
     <row r="441" spans="1:6">
@@ -13420,13 +13420,13 @@
         <v>18</v>
       </c>
       <c r="D446" t="s">
+        <v>549</v>
+      </c>
+      <c r="E446" t="s">
         <v>592</v>
       </c>
-      <c r="E446" t="s">
+      <c r="F446" t="s">
         <v>593</v>
-      </c>
-      <c r="F446" t="s">
-        <v>551</v>
       </c>
     </row>
     <row r="447" spans="1:6">
@@ -13900,13 +13900,13 @@
         <v>18</v>
       </c>
       <c r="D470" t="s">
+        <v>608</v>
+      </c>
+      <c r="E470" t="s">
         <v>624</v>
       </c>
-      <c r="E470" t="s">
+      <c r="F470" t="s">
         <v>625</v>
-      </c>
-      <c r="F470" t="s">
-        <v>610</v>
       </c>
     </row>
     <row r="471" spans="1:6">
@@ -13920,13 +13920,13 @@
         <v>18</v>
       </c>
       <c r="D471" t="s">
+        <v>608</v>
+      </c>
+      <c r="E471" t="s">
         <v>627</v>
       </c>
-      <c r="E471" t="s">
+      <c r="F471" t="s">
         <v>628</v>
-      </c>
-      <c r="F471" t="s">
-        <v>610</v>
       </c>
     </row>
     <row r="472" spans="1:6">
@@ -14140,13 +14140,13 @@
         <v>18</v>
       </c>
       <c r="D482" t="s">
+        <v>608</v>
+      </c>
+      <c r="E482" t="s">
         <v>643</v>
       </c>
-      <c r="E482" t="s">
+      <c r="F482" t="s">
         <v>644</v>
-      </c>
-      <c r="F482" t="s">
-        <v>610</v>
       </c>
     </row>
     <row r="483" spans="1:6">
@@ -14460,13 +14460,13 @@
         <v>66</v>
       </c>
       <c r="D498" t="s">
+        <v>608</v>
+      </c>
+      <c r="E498" t="s">
         <v>661</v>
       </c>
-      <c r="E498" t="s">
+      <c r="F498" t="s">
         <v>662</v>
-      </c>
-      <c r="F498" t="s">
-        <v>610</v>
       </c>
     </row>
     <row r="499" spans="1:6">
@@ -14660,13 +14660,13 @@
         <v>18</v>
       </c>
       <c r="D508" t="s">
+        <v>665</v>
+      </c>
+      <c r="E508" t="s">
         <v>677</v>
       </c>
-      <c r="E508" t="s">
+      <c r="F508" t="s">
         <v>678</v>
-      </c>
-      <c r="F508" t="s">
-        <v>667</v>
       </c>
     </row>
     <row r="509" spans="1:6">
@@ -14700,13 +14700,13 @@
         <v>18</v>
       </c>
       <c r="D510" t="s">
-        <v>677</v>
+        <v>665</v>
       </c>
       <c r="E510" t="s">
         <v>682</v>
       </c>
       <c r="F510" t="s">
-        <v>667</v>
+        <v>678</v>
       </c>
     </row>
     <row r="511" spans="1:6">
@@ -14720,13 +14720,13 @@
         <v>18</v>
       </c>
       <c r="D511" t="s">
+        <v>665</v>
+      </c>
+      <c r="E511" t="s">
         <v>684</v>
       </c>
-      <c r="E511" t="s">
+      <c r="F511" t="s">
         <v>685</v>
-      </c>
-      <c r="F511" t="s">
-        <v>667</v>
       </c>
     </row>
     <row r="512" spans="1:6">
@@ -14760,13 +14760,13 @@
         <v>18</v>
       </c>
       <c r="D513" t="s">
+        <v>665</v>
+      </c>
+      <c r="E513" t="s">
         <v>688</v>
       </c>
-      <c r="E513" t="s">
+      <c r="F513" t="s">
         <v>689</v>
-      </c>
-      <c r="F513" t="s">
-        <v>667</v>
       </c>
     </row>
     <row r="514" spans="1:6">
@@ -14840,13 +14840,13 @@
         <v>18</v>
       </c>
       <c r="D517" t="s">
-        <v>677</v>
+        <v>665</v>
       </c>
       <c r="E517" t="s">
         <v>694</v>
       </c>
       <c r="F517" t="s">
-        <v>667</v>
+        <v>678</v>
       </c>
     </row>
     <row r="518" spans="1:6">
@@ -15240,13 +15240,13 @@
         <v>66</v>
       </c>
       <c r="D537" t="s">
-        <v>719</v>
+        <v>710</v>
       </c>
       <c r="E537" t="s">
         <v>711</v>
       </c>
       <c r="F537" t="s">
-        <v>712</v>
+        <v>719</v>
       </c>
     </row>
     <row r="538" spans="1:6">
@@ -15280,13 +15280,13 @@
         <v>22</v>
       </c>
       <c r="D539" t="s">
+        <v>710</v>
+      </c>
+      <c r="E539" t="s">
+        <v>688</v>
+      </c>
+      <c r="F539" t="s">
         <v>722</v>
-      </c>
-      <c r="E539" t="s">
-        <v>689</v>
-      </c>
-      <c r="F539" t="s">
-        <v>712</v>
       </c>
     </row>
     <row r="540" spans="1:6">
@@ -15300,13 +15300,13 @@
         <v>16</v>
       </c>
       <c r="D540" t="s">
+        <v>710</v>
+      </c>
+      <c r="E540" t="s">
+        <v>688</v>
+      </c>
+      <c r="F540" t="s">
         <v>722</v>
-      </c>
-      <c r="E540" t="s">
-        <v>689</v>
-      </c>
-      <c r="F540" t="s">
-        <v>712</v>
       </c>
     </row>
     <row r="541" spans="1:6">
@@ -15540,13 +15540,13 @@
         <v>18</v>
       </c>
       <c r="D552" t="s">
+        <v>710</v>
+      </c>
+      <c r="E552" t="s">
         <v>738</v>
       </c>
-      <c r="E552" t="s">
+      <c r="F552" t="s">
         <v>739</v>
-      </c>
-      <c r="F552" t="s">
-        <v>712</v>
       </c>
     </row>
     <row r="553" spans="1:6">
@@ -15560,13 +15560,13 @@
         <v>664</v>
       </c>
       <c r="D553" t="s">
+        <v>710</v>
+      </c>
+      <c r="E553" t="s">
         <v>741</v>
       </c>
-      <c r="E553" t="s">
+      <c r="F553" t="s">
         <v>742</v>
-      </c>
-      <c r="F553" t="s">
-        <v>712</v>
       </c>
     </row>
     <row r="554" spans="1:6">
@@ -15580,13 +15580,13 @@
         <v>66</v>
       </c>
       <c r="D554" t="s">
+        <v>710</v>
+      </c>
+      <c r="E554" t="s">
+        <v>741</v>
+      </c>
+      <c r="F554" t="s">
         <v>744</v>
-      </c>
-      <c r="E554" t="s">
-        <v>742</v>
-      </c>
-      <c r="F554" t="s">
-        <v>712</v>
       </c>
     </row>
     <row r="555" spans="1:6">
@@ -15600,13 +15600,13 @@
         <v>18</v>
       </c>
       <c r="D555" t="s">
+        <v>710</v>
+      </c>
+      <c r="E555" t="s">
         <v>746</v>
       </c>
-      <c r="E555" t="s">
+      <c r="F555" t="s">
         <v>747</v>
-      </c>
-      <c r="F555" t="s">
-        <v>712</v>
       </c>
     </row>
     <row r="556" spans="1:6">
@@ -15680,13 +15680,13 @@
         <v>66</v>
       </c>
       <c r="D559" t="s">
-        <v>753</v>
+        <v>710</v>
       </c>
       <c r="E559" t="s">
         <v>711</v>
       </c>
       <c r="F559" t="s">
-        <v>712</v>
+        <v>753</v>
       </c>
     </row>
     <row r="560" spans="1:6">
@@ -16020,13 +16020,13 @@
         <v>769</v>
       </c>
       <c r="D576" t="s">
-        <v>778</v>
+        <v>770</v>
       </c>
       <c r="E576" t="s">
         <v>714</v>
       </c>
       <c r="F576" t="s">
-        <v>771</v>
+        <v>778</v>
       </c>
     </row>
     <row r="577" spans="1:6">
@@ -16220,13 +16220,13 @@
         <v>769</v>
       </c>
       <c r="D586" t="s">
-        <v>746</v>
+        <v>770</v>
       </c>
       <c r="E586" t="s">
         <v>714</v>
       </c>
       <c r="F586" t="s">
-        <v>771</v>
+        <v>747</v>
       </c>
     </row>
     <row r="587" spans="1:6">
@@ -16320,13 +16320,13 @@
         <v>22</v>
       </c>
       <c r="D591" t="s">
-        <v>796</v>
+        <v>770</v>
       </c>
       <c r="E591" t="s">
         <v>714</v>
       </c>
       <c r="F591" t="s">
-        <v>771</v>
+        <v>796</v>
       </c>
     </row>
     <row r="592" spans="1:6">
@@ -16500,13 +16500,13 @@
         <v>769</v>
       </c>
       <c r="D600" t="s">
-        <v>811</v>
+        <v>800</v>
       </c>
       <c r="E600" t="s">
         <v>801</v>
       </c>
       <c r="F600" t="s">
-        <v>802</v>
+        <v>811</v>
       </c>
     </row>
     <row r="601" spans="1:6">
@@ -16580,13 +16580,13 @@
         <v>18</v>
       </c>
       <c r="D604" t="s">
+        <v>800</v>
+      </c>
+      <c r="E604" t="s">
         <v>816</v>
       </c>
-      <c r="E604" t="s">
+      <c r="F604" t="s">
         <v>817</v>
-      </c>
-      <c r="F604" t="s">
-        <v>802</v>
       </c>
     </row>
     <row r="605" spans="1:6">
@@ -16680,13 +16680,13 @@
         <v>16</v>
       </c>
       <c r="D609" t="s">
-        <v>824</v>
+        <v>800</v>
       </c>
       <c r="E609" t="s">
         <v>801</v>
       </c>
       <c r="F609" t="s">
-        <v>802</v>
+        <v>824</v>
       </c>
     </row>
     <row r="610" spans="1:6">
@@ -16800,13 +16800,13 @@
         <v>769</v>
       </c>
       <c r="D615" t="s">
+        <v>800</v>
+      </c>
+      <c r="E615" t="s">
         <v>831</v>
       </c>
-      <c r="E615" t="s">
+      <c r="F615" t="s">
         <v>832</v>
-      </c>
-      <c r="F615" t="s">
-        <v>802</v>
       </c>
     </row>
     <row r="616" spans="1:6">
@@ -16880,13 +16880,13 @@
         <v>769</v>
       </c>
       <c r="D619" t="s">
-        <v>770</v>
+        <v>837</v>
       </c>
       <c r="E619" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="F619" t="s">
-        <v>838</v>
+        <v>771</v>
       </c>
     </row>
     <row r="620" spans="1:6">
@@ -16900,13 +16900,13 @@
         <v>769</v>
       </c>
       <c r="D620" t="s">
+        <v>837</v>
+      </c>
+      <c r="E620" t="s">
+        <v>838</v>
+      </c>
+      <c r="F620" t="s">
         <v>840</v>
-      </c>
-      <c r="E620" t="s">
-        <v>837</v>
-      </c>
-      <c r="F620" t="s">
-        <v>838</v>
       </c>
     </row>
     <row r="621" spans="1:6">
@@ -16920,13 +16920,13 @@
         <v>769</v>
       </c>
       <c r="D621" t="s">
+        <v>837</v>
+      </c>
+      <c r="E621" t="s">
+        <v>838</v>
+      </c>
+      <c r="F621" t="s">
         <v>840</v>
-      </c>
-      <c r="E621" t="s">
-        <v>837</v>
-      </c>
-      <c r="F621" t="s">
-        <v>838</v>
       </c>
     </row>
     <row r="622" spans="1:6">
@@ -16940,13 +16940,13 @@
         <v>769</v>
       </c>
       <c r="D622" t="s">
+        <v>837</v>
+      </c>
+      <c r="E622" t="s">
+        <v>838</v>
+      </c>
+      <c r="F622" t="s">
         <v>840</v>
-      </c>
-      <c r="E622" t="s">
-        <v>837</v>
-      </c>
-      <c r="F622" t="s">
-        <v>838</v>
       </c>
     </row>
     <row r="623" spans="1:6">
@@ -16960,13 +16960,13 @@
         <v>769</v>
       </c>
       <c r="D623" t="s">
-        <v>800</v>
+        <v>837</v>
       </c>
       <c r="E623" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="F623" t="s">
-        <v>838</v>
+        <v>802</v>
       </c>
     </row>
     <row r="624" spans="1:6">
@@ -16980,13 +16980,13 @@
         <v>769</v>
       </c>
       <c r="D624" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="E624" t="s">
         <v>845</v>
       </c>
       <c r="F624" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
     </row>
     <row r="625" spans="1:6">
@@ -17000,13 +17000,13 @@
         <v>18</v>
       </c>
       <c r="D625" t="s">
+        <v>837</v>
+      </c>
+      <c r="E625" t="s">
         <v>847</v>
       </c>
-      <c r="E625" t="s">
+      <c r="F625" t="s">
         <v>848</v>
-      </c>
-      <c r="F625" t="s">
-        <v>838</v>
       </c>
     </row>
     <row r="626" spans="1:6">
@@ -17020,13 +17020,13 @@
         <v>769</v>
       </c>
       <c r="D626" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="E626" t="s">
         <v>850</v>
       </c>
       <c r="F626" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
     </row>
     <row r="627" spans="1:6">
@@ -17040,13 +17040,13 @@
         <v>16</v>
       </c>
       <c r="D627" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="E627" t="s">
         <v>852</v>
       </c>
       <c r="F627" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
     </row>
     <row r="628" spans="1:6">
@@ -17060,13 +17060,13 @@
         <v>16</v>
       </c>
       <c r="D628" t="s">
+        <v>837</v>
+      </c>
+      <c r="E628" t="s">
+        <v>838</v>
+      </c>
+      <c r="F628" t="s">
         <v>840</v>
-      </c>
-      <c r="E628" t="s">
-        <v>837</v>
-      </c>
-      <c r="F628" t="s">
-        <v>838</v>
       </c>
     </row>
     <row r="629" spans="1:6">
@@ -17080,13 +17080,13 @@
         <v>18</v>
       </c>
       <c r="D629" t="s">
+        <v>837</v>
+      </c>
+      <c r="E629" t="s">
         <v>855</v>
       </c>
-      <c r="E629" t="s">
+      <c r="F629" t="s">
         <v>856</v>
-      </c>
-      <c r="F629" t="s">
-        <v>838</v>
       </c>
     </row>
     <row r="630" spans="1:6">
@@ -17100,13 +17100,13 @@
         <v>18</v>
       </c>
       <c r="D630" t="s">
+        <v>837</v>
+      </c>
+      <c r="E630" t="s">
         <v>858</v>
       </c>
-      <c r="E630" t="s">
+      <c r="F630" t="s">
         <v>859</v>
-      </c>
-      <c r="F630" t="s">
-        <v>838</v>
       </c>
     </row>
     <row r="631" spans="1:6">
@@ -17120,13 +17120,13 @@
         <v>769</v>
       </c>
       <c r="D631" t="s">
+        <v>837</v>
+      </c>
+      <c r="E631" t="s">
+        <v>838</v>
+      </c>
+      <c r="F631" t="s">
         <v>840</v>
-      </c>
-      <c r="E631" t="s">
-        <v>837</v>
-      </c>
-      <c r="F631" t="s">
-        <v>838</v>
       </c>
     </row>
     <row r="632" spans="1:6">
@@ -17140,13 +17140,13 @@
         <v>18</v>
       </c>
       <c r="D632" t="s">
+        <v>837</v>
+      </c>
+      <c r="E632" t="s">
         <v>862</v>
       </c>
-      <c r="E632" t="s">
+      <c r="F632" t="s">
         <v>863</v>
-      </c>
-      <c r="F632" t="s">
-        <v>838</v>
       </c>
     </row>
     <row r="633" spans="1:6">
@@ -17160,13 +17160,13 @@
         <v>22</v>
       </c>
       <c r="D633" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="E633" t="s">
         <v>865</v>
       </c>
       <c r="F633" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
     </row>
     <row r="634" spans="1:6">
@@ -17180,13 +17180,13 @@
         <v>769</v>
       </c>
       <c r="D634" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="E634" t="s">
         <v>867</v>
       </c>
       <c r="F634" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
     </row>
     <row r="635" spans="1:6">
@@ -17200,13 +17200,13 @@
         <v>769</v>
       </c>
       <c r="D635" t="s">
+        <v>837</v>
+      </c>
+      <c r="E635" t="s">
+        <v>838</v>
+      </c>
+      <c r="F635" t="s">
         <v>840</v>
-      </c>
-      <c r="E635" t="s">
-        <v>837</v>
-      </c>
-      <c r="F635" t="s">
-        <v>838</v>
       </c>
     </row>
     <row r="636" spans="1:6">
@@ -17220,13 +17220,13 @@
         <v>18</v>
       </c>
       <c r="D636" t="s">
+        <v>837</v>
+      </c>
+      <c r="E636" t="s">
+        <v>838</v>
+      </c>
+      <c r="F636" t="s">
         <v>840</v>
-      </c>
-      <c r="E636" t="s">
-        <v>837</v>
-      </c>
-      <c r="F636" t="s">
-        <v>838</v>
       </c>
     </row>
     <row r="637" spans="1:6">
@@ -17240,13 +17240,13 @@
         <v>16</v>
       </c>
       <c r="D637" t="s">
+        <v>837</v>
+      </c>
+      <c r="E637" t="s">
+        <v>838</v>
+      </c>
+      <c r="F637" t="s">
         <v>840</v>
-      </c>
-      <c r="E637" t="s">
-        <v>837</v>
-      </c>
-      <c r="F637" t="s">
-        <v>838</v>
       </c>
     </row>
     <row r="638" spans="1:6">
@@ -17260,13 +17260,13 @@
         <v>769</v>
       </c>
       <c r="D638" t="s">
+        <v>837</v>
+      </c>
+      <c r="E638" t="s">
+        <v>838</v>
+      </c>
+      <c r="F638" t="s">
         <v>872</v>
-      </c>
-      <c r="E638" t="s">
-        <v>837</v>
-      </c>
-      <c r="F638" t="s">
-        <v>838</v>
       </c>
     </row>
     <row r="639" spans="1:6">
@@ -17280,13 +17280,13 @@
         <v>22</v>
       </c>
       <c r="D639" t="s">
+        <v>837</v>
+      </c>
+      <c r="E639" t="s">
+        <v>838</v>
+      </c>
+      <c r="F639" t="s">
         <v>840</v>
-      </c>
-      <c r="E639" t="s">
-        <v>837</v>
-      </c>
-      <c r="F639" t="s">
-        <v>838</v>
       </c>
     </row>
     <row r="640" spans="1:6">
@@ -17300,13 +17300,13 @@
         <v>769</v>
       </c>
       <c r="D640" t="s">
+        <v>837</v>
+      </c>
+      <c r="E640" t="s">
+        <v>838</v>
+      </c>
+      <c r="F640" t="s">
         <v>840</v>
-      </c>
-      <c r="E640" t="s">
-        <v>837</v>
-      </c>
-      <c r="F640" t="s">
-        <v>838</v>
       </c>
     </row>
     <row r="641" spans="1:6">
@@ -17320,13 +17320,13 @@
         <v>769</v>
       </c>
       <c r="D641" t="s">
+        <v>837</v>
+      </c>
+      <c r="E641" t="s">
+        <v>838</v>
+      </c>
+      <c r="F641" t="s">
         <v>840</v>
-      </c>
-      <c r="E641" t="s">
-        <v>837</v>
-      </c>
-      <c r="F641" t="s">
-        <v>838</v>
       </c>
     </row>
     <row r="642" spans="1:6">
@@ -17340,13 +17340,13 @@
         <v>769</v>
       </c>
       <c r="D642" t="s">
+        <v>837</v>
+      </c>
+      <c r="E642" t="s">
+        <v>838</v>
+      </c>
+      <c r="F642" t="s">
         <v>840</v>
-      </c>
-      <c r="E642" t="s">
-        <v>837</v>
-      </c>
-      <c r="F642" t="s">
-        <v>838</v>
       </c>
     </row>
     <row r="643" spans="1:6">
@@ -17380,13 +17380,13 @@
         <v>16</v>
       </c>
       <c r="D644" t="s">
+        <v>878</v>
+      </c>
+      <c r="E644" t="s">
         <v>882</v>
       </c>
-      <c r="E644" t="s">
+      <c r="F644" t="s">
         <v>883</v>
-      </c>
-      <c r="F644" t="s">
-        <v>880</v>
       </c>
     </row>
     <row r="645" spans="1:6">
@@ -17460,13 +17460,13 @@
         <v>18</v>
       </c>
       <c r="D648" t="s">
+        <v>878</v>
+      </c>
+      <c r="E648" t="s">
         <v>888</v>
       </c>
-      <c r="E648" t="s">
+      <c r="F648" t="s">
         <v>889</v>
-      </c>
-      <c r="F648" t="s">
-        <v>880</v>
       </c>
     </row>
     <row r="649" spans="1:6">
@@ -17480,13 +17480,13 @@
         <v>18</v>
       </c>
       <c r="D649" t="s">
+        <v>878</v>
+      </c>
+      <c r="E649" t="s">
         <v>891</v>
       </c>
-      <c r="E649" t="s">
+      <c r="F649" t="s">
         <v>892</v>
-      </c>
-      <c r="F649" t="s">
-        <v>880</v>
       </c>
     </row>
     <row r="650" spans="1:6">
@@ -17500,13 +17500,13 @@
         <v>769</v>
       </c>
       <c r="D650" t="s">
+        <v>878</v>
+      </c>
+      <c r="E650" t="s">
         <v>894</v>
       </c>
-      <c r="E650" t="s">
+      <c r="F650" t="s">
         <v>895</v>
-      </c>
-      <c r="F650" t="s">
-        <v>880</v>
       </c>
     </row>
     <row r="651" spans="1:6">
@@ -17600,13 +17600,13 @@
         <v>18</v>
       </c>
       <c r="D655" t="s">
+        <v>878</v>
+      </c>
+      <c r="E655" t="s">
         <v>902</v>
       </c>
-      <c r="E655" t="s">
+      <c r="F655" t="s">
         <v>903</v>
-      </c>
-      <c r="F655" t="s">
-        <v>880</v>
       </c>
     </row>
     <row r="656" spans="1:6">
@@ -17620,13 +17620,13 @@
         <v>769</v>
       </c>
       <c r="D656" t="s">
-        <v>865</v>
+        <v>878</v>
       </c>
       <c r="E656" t="s">
         <v>905</v>
       </c>
       <c r="F656" t="s">
-        <v>880</v>
+        <v>865</v>
       </c>
     </row>
     <row r="657" spans="1:6">
@@ -17660,13 +17660,13 @@
         <v>18</v>
       </c>
       <c r="D658" t="s">
+        <v>878</v>
+      </c>
+      <c r="E658" t="s">
+        <v>882</v>
+      </c>
+      <c r="F658" t="s">
         <v>908</v>
-      </c>
-      <c r="E658" t="s">
-        <v>883</v>
-      </c>
-      <c r="F658" t="s">
-        <v>880</v>
       </c>
     </row>
     <row r="659" spans="1:6">
@@ -17980,13 +17980,13 @@
         <v>18</v>
       </c>
       <c r="D674" t="s">
+        <v>926</v>
+      </c>
+      <c r="E674" t="s">
         <v>930</v>
       </c>
-      <c r="E674" t="s">
+      <c r="F674" t="s">
         <v>931</v>
-      </c>
-      <c r="F674" t="s">
-        <v>928</v>
       </c>
     </row>
     <row r="675" spans="1:6">
@@ -18060,13 +18060,13 @@
         <v>769</v>
       </c>
       <c r="D678" t="s">
-        <v>936</v>
+        <v>926</v>
       </c>
       <c r="E678" t="s">
         <v>927</v>
       </c>
       <c r="F678" t="s">
-        <v>928</v>
+        <v>936</v>
       </c>
     </row>
     <row r="679" spans="1:6">
@@ -18160,13 +18160,13 @@
         <v>18</v>
       </c>
       <c r="D683" t="s">
-        <v>943</v>
+        <v>926</v>
       </c>
       <c r="E683" t="s">
         <v>938</v>
       </c>
       <c r="F683" t="s">
-        <v>928</v>
+        <v>943</v>
       </c>
     </row>
     <row r="684" spans="1:6">
@@ -18180,13 +18180,13 @@
         <v>18</v>
       </c>
       <c r="D684" t="s">
+        <v>926</v>
+      </c>
+      <c r="E684" t="s">
         <v>945</v>
       </c>
-      <c r="E684" t="s">
+      <c r="F684" t="s">
         <v>946</v>
-      </c>
-      <c r="F684" t="s">
-        <v>928</v>
       </c>
     </row>
     <row r="685" spans="1:6">
@@ -18200,13 +18200,13 @@
         <v>18</v>
       </c>
       <c r="D685" t="s">
+        <v>926</v>
+      </c>
+      <c r="E685" t="s">
         <v>948</v>
       </c>
-      <c r="E685" t="s">
+      <c r="F685" t="s">
         <v>949</v>
-      </c>
-      <c r="F685" t="s">
-        <v>928</v>
       </c>
     </row>
     <row r="686" spans="1:6">
@@ -18260,13 +18260,13 @@
         <v>18</v>
       </c>
       <c r="D688" t="s">
+        <v>926</v>
+      </c>
+      <c r="E688" t="s">
         <v>954</v>
       </c>
-      <c r="E688" t="s">
+      <c r="F688" t="s">
         <v>955</v>
-      </c>
-      <c r="F688" t="s">
-        <v>928</v>
       </c>
     </row>
     <row r="689" spans="1:6">
@@ -18340,13 +18340,13 @@
         <v>16</v>
       </c>
       <c r="D692" t="s">
+        <v>926</v>
+      </c>
+      <c r="E692" t="s">
         <v>960</v>
       </c>
-      <c r="E692" t="s">
+      <c r="F692" t="s">
         <v>961</v>
-      </c>
-      <c r="F692" t="s">
-        <v>928</v>
       </c>
     </row>
     <row r="693" spans="1:6">
@@ -18540,13 +18540,13 @@
         <v>16</v>
       </c>
       <c r="D702" t="s">
+        <v>974</v>
+      </c>
+      <c r="E702" t="s">
         <v>978</v>
       </c>
-      <c r="E702" t="s">
+      <c r="F702" t="s">
         <v>979</v>
-      </c>
-      <c r="F702" t="s">
-        <v>976</v>
       </c>
     </row>
     <row r="703" spans="1:6">
@@ -18560,13 +18560,13 @@
         <v>18</v>
       </c>
       <c r="D703" t="s">
-        <v>981</v>
+        <v>974</v>
       </c>
       <c r="E703" t="s">
         <v>975</v>
       </c>
       <c r="F703" t="s">
-        <v>976</v>
+        <v>981</v>
       </c>
     </row>
     <row r="704" spans="1:6">
@@ -18580,13 +18580,13 @@
         <v>769</v>
       </c>
       <c r="D704" t="s">
+        <v>974</v>
+      </c>
+      <c r="E704" t="s">
         <v>983</v>
       </c>
-      <c r="E704" t="s">
+      <c r="F704" t="s">
         <v>984</v>
-      </c>
-      <c r="F704" t="s">
-        <v>976</v>
       </c>
     </row>
     <row r="705" spans="1:6">
@@ -18600,13 +18600,13 @@
         <v>769</v>
       </c>
       <c r="D705" t="s">
+        <v>974</v>
+      </c>
+      <c r="E705" t="s">
         <v>983</v>
       </c>
-      <c r="E705" t="s">
+      <c r="F705" t="s">
         <v>984</v>
-      </c>
-      <c r="F705" t="s">
-        <v>976</v>
       </c>
     </row>
     <row r="706" spans="1:6">
@@ -18620,13 +18620,13 @@
         <v>16</v>
       </c>
       <c r="D706" t="s">
-        <v>926</v>
+        <v>974</v>
       </c>
       <c r="E706" t="s">
         <v>965</v>
       </c>
       <c r="F706" t="s">
-        <v>976</v>
+        <v>928</v>
       </c>
     </row>
     <row r="707" spans="1:6">
@@ -18640,13 +18640,13 @@
         <v>769</v>
       </c>
       <c r="D707" t="s">
+        <v>974</v>
+      </c>
+      <c r="E707" t="s">
         <v>983</v>
       </c>
-      <c r="E707" t="s">
+      <c r="F707" t="s">
         <v>984</v>
-      </c>
-      <c r="F707" t="s">
-        <v>976</v>
       </c>
     </row>
     <row r="708" spans="1:6">
@@ -18660,13 +18660,13 @@
         <v>769</v>
       </c>
       <c r="D708" t="s">
+        <v>974</v>
+      </c>
+      <c r="E708" t="s">
         <v>983</v>
       </c>
-      <c r="E708" t="s">
+      <c r="F708" t="s">
         <v>984</v>
-      </c>
-      <c r="F708" t="s">
-        <v>976</v>
       </c>
     </row>
     <row r="709" spans="1:6">
@@ -18680,13 +18680,13 @@
         <v>16</v>
       </c>
       <c r="D709" t="s">
+        <v>974</v>
+      </c>
+      <c r="E709" t="s">
         <v>990</v>
       </c>
-      <c r="E709" t="s">
+      <c r="F709" t="s">
         <v>991</v>
-      </c>
-      <c r="F709" t="s">
-        <v>976</v>
       </c>
     </row>
     <row r="710" spans="1:6">
@@ -18700,13 +18700,13 @@
         <v>18</v>
       </c>
       <c r="D710" t="s">
+        <v>974</v>
+      </c>
+      <c r="E710" t="s">
         <v>993</v>
       </c>
-      <c r="E710" t="s">
+      <c r="F710" t="s">
         <v>994</v>
-      </c>
-      <c r="F710" t="s">
-        <v>976</v>
       </c>
     </row>
     <row r="711" spans="1:6">
@@ -18720,13 +18720,13 @@
         <v>18</v>
       </c>
       <c r="D711" t="s">
-        <v>996</v>
+        <v>974</v>
       </c>
       <c r="E711" t="s">
         <v>952</v>
       </c>
       <c r="F711" t="s">
-        <v>976</v>
+        <v>996</v>
       </c>
     </row>
     <row r="712" spans="1:6">
@@ -18740,13 +18740,13 @@
         <v>18</v>
       </c>
       <c r="D712" t="s">
+        <v>974</v>
+      </c>
+      <c r="E712" t="s">
         <v>998</v>
       </c>
-      <c r="E712" t="s">
+      <c r="F712" t="s">
         <v>999</v>
-      </c>
-      <c r="F712" t="s">
-        <v>976</v>
       </c>
     </row>
     <row r="713" spans="1:6">
@@ -18760,13 +18760,13 @@
         <v>769</v>
       </c>
       <c r="D713" t="s">
+        <v>974</v>
+      </c>
+      <c r="E713" t="s">
         <v>983</v>
       </c>
-      <c r="E713" t="s">
+      <c r="F713" t="s">
         <v>984</v>
-      </c>
-      <c r="F713" t="s">
-        <v>976</v>
       </c>
     </row>
     <row r="714" spans="1:6">
@@ -18780,13 +18780,13 @@
         <v>18</v>
       </c>
       <c r="D714" t="s">
-        <v>979</v>
+        <v>974</v>
       </c>
       <c r="E714" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="F714" t="s">
-        <v>976</v>
+        <v>978</v>
       </c>
     </row>
     <row r="715" spans="1:6">
@@ -18800,13 +18800,13 @@
         <v>18</v>
       </c>
       <c r="D715" t="s">
+        <v>974</v>
+      </c>
+      <c r="E715" t="s">
         <v>1003</v>
       </c>
-      <c r="E715" t="s">
+      <c r="F715" t="s">
         <v>1004</v>
-      </c>
-      <c r="F715" t="s">
-        <v>976</v>
       </c>
     </row>
     <row r="716" spans="1:6">
@@ -18820,13 +18820,13 @@
         <v>16</v>
       </c>
       <c r="D716" t="s">
-        <v>1006</v>
+        <v>974</v>
       </c>
       <c r="E716" t="s">
         <v>965</v>
       </c>
       <c r="F716" t="s">
-        <v>976</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="717" spans="1:6">
@@ -18840,13 +18840,13 @@
         <v>16</v>
       </c>
       <c r="D717" t="s">
-        <v>983</v>
+        <v>974</v>
       </c>
       <c r="E717" t="s">
         <v>1008</v>
       </c>
       <c r="F717" t="s">
-        <v>976</v>
+        <v>984</v>
       </c>
     </row>
     <row r="718" spans="1:6">
@@ -18860,13 +18860,13 @@
         <v>769</v>
       </c>
       <c r="D718" t="s">
-        <v>983</v>
+        <v>974</v>
       </c>
       <c r="E718" t="s">
         <v>1008</v>
       </c>
       <c r="F718" t="s">
-        <v>976</v>
+        <v>984</v>
       </c>
     </row>
     <row r="719" spans="1:6">
@@ -18900,13 +18900,13 @@
         <v>18</v>
       </c>
       <c r="D720" t="s">
+        <v>974</v>
+      </c>
+      <c r="E720" t="s">
         <v>1012</v>
       </c>
-      <c r="E720" t="s">
+      <c r="F720" t="s">
         <v>1013</v>
-      </c>
-      <c r="F720" t="s">
-        <v>976</v>
       </c>
     </row>
     <row r="721" spans="1:6">
@@ -18920,13 +18920,13 @@
         <v>16</v>
       </c>
       <c r="D721" t="s">
+        <v>974</v>
+      </c>
+      <c r="E721" t="s">
         <v>983</v>
       </c>
-      <c r="E721" t="s">
+      <c r="F721" t="s">
         <v>984</v>
-      </c>
-      <c r="F721" t="s">
-        <v>976</v>
       </c>
     </row>
     <row r="722" spans="1:6">
@@ -18940,13 +18940,13 @@
         <v>16</v>
       </c>
       <c r="D722" t="s">
-        <v>996</v>
+        <v>974</v>
       </c>
       <c r="E722" t="s">
         <v>965</v>
       </c>
       <c r="F722" t="s">
-        <v>976</v>
+        <v>996</v>
       </c>
     </row>
     <row r="723" spans="1:6">
@@ -18960,13 +18960,13 @@
         <v>769</v>
       </c>
       <c r="D723" t="s">
+        <v>974</v>
+      </c>
+      <c r="E723" t="s">
         <v>983</v>
       </c>
-      <c r="E723" t="s">
+      <c r="F723" t="s">
         <v>984</v>
-      </c>
-      <c r="F723" t="s">
-        <v>976</v>
       </c>
     </row>
     <row r="724" spans="1:6">
@@ -18980,13 +18980,13 @@
         <v>22</v>
       </c>
       <c r="D724" t="s">
-        <v>1018</v>
+        <v>974</v>
       </c>
       <c r="E724" t="s">
         <v>975</v>
       </c>
       <c r="F724" t="s">
-        <v>976</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="725" spans="1:6">
@@ -19000,13 +19000,13 @@
         <v>16</v>
       </c>
       <c r="D725" t="s">
+        <v>974</v>
+      </c>
+      <c r="E725" t="s">
         <v>983</v>
       </c>
-      <c r="E725" t="s">
+      <c r="F725" t="s">
         <v>984</v>
-      </c>
-      <c r="F725" t="s">
-        <v>976</v>
       </c>
     </row>
     <row r="726" spans="1:6">
@@ -19020,13 +19020,13 @@
         <v>769</v>
       </c>
       <c r="D726" t="s">
+        <v>974</v>
+      </c>
+      <c r="E726" t="s">
         <v>983</v>
       </c>
-      <c r="E726" t="s">
+      <c r="F726" t="s">
         <v>984</v>
-      </c>
-      <c r="F726" t="s">
-        <v>976</v>
       </c>
     </row>
     <row r="727" spans="1:6">
@@ -19040,13 +19040,13 @@
         <v>16</v>
       </c>
       <c r="D727" t="s">
-        <v>998</v>
+        <v>974</v>
       </c>
       <c r="E727" t="s">
         <v>965</v>
       </c>
       <c r="F727" t="s">
-        <v>976</v>
+        <v>999</v>
       </c>
     </row>
     <row r="728" spans="1:6">
@@ -19060,13 +19060,13 @@
         <v>18</v>
       </c>
       <c r="D728" t="s">
-        <v>981</v>
+        <v>974</v>
       </c>
       <c r="E728" t="s">
         <v>975</v>
       </c>
       <c r="F728" t="s">
-        <v>976</v>
+        <v>981</v>
       </c>
     </row>
     <row r="729" spans="1:6">
@@ -19080,13 +19080,13 @@
         <v>16</v>
       </c>
       <c r="D729" t="s">
-        <v>983</v>
+        <v>974</v>
       </c>
       <c r="E729" t="s">
         <v>1024</v>
       </c>
       <c r="F729" t="s">
-        <v>976</v>
+        <v>984</v>
       </c>
     </row>
     <row r="730" spans="1:6">
@@ -19100,13 +19100,13 @@
         <v>769</v>
       </c>
       <c r="D730" t="s">
+        <v>974</v>
+      </c>
+      <c r="E730" t="s">
         <v>983</v>
       </c>
-      <c r="E730" t="s">
+      <c r="F730" t="s">
         <v>984</v>
-      </c>
-      <c r="F730" t="s">
-        <v>976</v>
       </c>
     </row>
     <row r="731" spans="1:6">
@@ -19120,13 +19120,13 @@
         <v>22</v>
       </c>
       <c r="D731" t="s">
+        <v>974</v>
+      </c>
+      <c r="E731" t="s">
         <v>983</v>
       </c>
-      <c r="E731" t="s">
+      <c r="F731" t="s">
         <v>984</v>
-      </c>
-      <c r="F731" t="s">
-        <v>976</v>
       </c>
     </row>
     <row r="732" spans="1:6">
@@ -19140,13 +19140,13 @@
         <v>769</v>
       </c>
       <c r="D732" t="s">
+        <v>974</v>
+      </c>
+      <c r="E732" t="s">
         <v>983</v>
       </c>
-      <c r="E732" t="s">
+      <c r="F732" t="s">
         <v>984</v>
-      </c>
-      <c r="F732" t="s">
-        <v>976</v>
       </c>
     </row>
     <row r="733" spans="1:6">
@@ -19160,13 +19160,13 @@
         <v>18</v>
       </c>
       <c r="D733" t="s">
+        <v>974</v>
+      </c>
+      <c r="E733" t="s">
         <v>998</v>
       </c>
-      <c r="E733" t="s">
+      <c r="F733" t="s">
         <v>999</v>
-      </c>
-      <c r="F733" t="s">
-        <v>976</v>
       </c>
     </row>
     <row r="734" spans="1:6">
@@ -19180,13 +19180,13 @@
         <v>769</v>
       </c>
       <c r="D734" t="s">
+        <v>974</v>
+      </c>
+      <c r="E734" t="s">
         <v>983</v>
       </c>
-      <c r="E734" t="s">
+      <c r="F734" t="s">
         <v>984</v>
-      </c>
-      <c r="F734" t="s">
-        <v>976</v>
       </c>
     </row>
     <row r="735" spans="1:6">
@@ -19200,13 +19200,13 @@
         <v>769</v>
       </c>
       <c r="D735" t="s">
+        <v>974</v>
+      </c>
+      <c r="E735" t="s">
         <v>983</v>
       </c>
-      <c r="E735" t="s">
+      <c r="F735" t="s">
         <v>984</v>
-      </c>
-      <c r="F735" t="s">
-        <v>976</v>
       </c>
     </row>
     <row r="736" spans="1:6">
@@ -19240,13 +19240,13 @@
         <v>18</v>
       </c>
       <c r="D737" t="s">
+        <v>1032</v>
+      </c>
+      <c r="E737" t="s">
         <v>1036</v>
       </c>
-      <c r="E737" t="s">
+      <c r="F737" t="s">
         <v>1037</v>
-      </c>
-      <c r="F737" t="s">
-        <v>1034</v>
       </c>
     </row>
     <row r="738" spans="1:6">
@@ -19260,13 +19260,13 @@
         <v>769</v>
       </c>
       <c r="D738" t="s">
+        <v>1032</v>
+      </c>
+      <c r="E738" t="s">
         <v>1039</v>
       </c>
-      <c r="E738" t="s">
+      <c r="F738" t="s">
         <v>1040</v>
-      </c>
-      <c r="F738" t="s">
-        <v>1034</v>
       </c>
     </row>
     <row r="739" spans="1:6">
@@ -19280,13 +19280,13 @@
         <v>769</v>
       </c>
       <c r="D739" t="s">
+        <v>1032</v>
+      </c>
+      <c r="E739" t="s">
         <v>1039</v>
       </c>
-      <c r="E739" t="s">
+      <c r="F739" t="s">
         <v>1040</v>
-      </c>
-      <c r="F739" t="s">
-        <v>1034</v>
       </c>
     </row>
     <row r="740" spans="1:6">
@@ -19300,13 +19300,13 @@
         <v>769</v>
       </c>
       <c r="D740" t="s">
+        <v>1032</v>
+      </c>
+      <c r="E740" t="s">
         <v>1039</v>
       </c>
-      <c r="E740" t="s">
+      <c r="F740" t="s">
         <v>1040</v>
-      </c>
-      <c r="F740" t="s">
-        <v>1034</v>
       </c>
     </row>
     <row r="741" spans="1:6">
@@ -19320,13 +19320,13 @@
         <v>769</v>
       </c>
       <c r="D741" t="s">
+        <v>1032</v>
+      </c>
+      <c r="E741" t="s">
         <v>1039</v>
       </c>
-      <c r="E741" t="s">
+      <c r="F741" t="s">
         <v>1040</v>
-      </c>
-      <c r="F741" t="s">
-        <v>1034</v>
       </c>
     </row>
     <row r="742" spans="1:6">
@@ -19340,13 +19340,13 @@
         <v>769</v>
       </c>
       <c r="D742" t="s">
+        <v>1032</v>
+      </c>
+      <c r="E742" t="s">
         <v>1039</v>
       </c>
-      <c r="E742" t="s">
+      <c r="F742" t="s">
         <v>1040</v>
-      </c>
-      <c r="F742" t="s">
-        <v>1034</v>
       </c>
     </row>
     <row r="743" spans="1:6">
@@ -19360,13 +19360,13 @@
         <v>18</v>
       </c>
       <c r="D743" t="s">
+        <v>1032</v>
+      </c>
+      <c r="E743" t="s">
+        <v>1036</v>
+      </c>
+      <c r="F743" t="s">
         <v>1046</v>
-      </c>
-      <c r="E743" t="s">
-        <v>1037</v>
-      </c>
-      <c r="F743" t="s">
-        <v>1034</v>
       </c>
     </row>
     <row r="744" spans="1:6">
@@ -19380,13 +19380,13 @@
         <v>18</v>
       </c>
       <c r="D744" t="s">
+        <v>1032</v>
+      </c>
+      <c r="E744" t="s">
         <v>1048</v>
       </c>
-      <c r="E744" t="s">
+      <c r="F744" t="s">
         <v>1049</v>
-      </c>
-      <c r="F744" t="s">
-        <v>1034</v>
       </c>
     </row>
     <row r="745" spans="1:6">
@@ -19400,13 +19400,13 @@
         <v>22</v>
       </c>
       <c r="D745" t="s">
+        <v>1032</v>
+      </c>
+      <c r="E745" t="s">
         <v>1039</v>
       </c>
-      <c r="E745" t="s">
+      <c r="F745" t="s">
         <v>1040</v>
-      </c>
-      <c r="F745" t="s">
-        <v>1034</v>
       </c>
     </row>
     <row r="746" spans="1:6">
@@ -19420,13 +19420,13 @@
         <v>22</v>
       </c>
       <c r="D746" t="s">
-        <v>983</v>
+        <v>1032</v>
       </c>
       <c r="E746" t="s">
         <v>1052</v>
       </c>
       <c r="F746" t="s">
-        <v>1034</v>
+        <v>984</v>
       </c>
     </row>
     <row r="747" spans="1:6">
@@ -19440,13 +19440,13 @@
         <v>18</v>
       </c>
       <c r="D747" t="s">
+        <v>1032</v>
+      </c>
+      <c r="E747" t="s">
         <v>1054</v>
       </c>
-      <c r="E747" t="s">
+      <c r="F747" t="s">
         <v>1055</v>
-      </c>
-      <c r="F747" t="s">
-        <v>1034</v>
       </c>
     </row>
     <row r="748" spans="1:6">
@@ -19460,13 +19460,13 @@
         <v>16</v>
       </c>
       <c r="D748" t="s">
+        <v>1032</v>
+      </c>
+      <c r="E748" t="s">
         <v>1057</v>
       </c>
-      <c r="E748" t="s">
+      <c r="F748" t="s">
         <v>1058</v>
-      </c>
-      <c r="F748" t="s">
-        <v>1034</v>
       </c>
     </row>
     <row r="749" spans="1:6">
@@ -19480,13 +19480,13 @@
         <v>18</v>
       </c>
       <c r="D749" t="s">
+        <v>1032</v>
+      </c>
+      <c r="E749" t="s">
         <v>1060</v>
       </c>
-      <c r="E749" t="s">
+      <c r="F749" t="s">
         <v>1061</v>
-      </c>
-      <c r="F749" t="s">
-        <v>1034</v>
       </c>
     </row>
     <row r="750" spans="1:6">
@@ -19500,13 +19500,13 @@
         <v>769</v>
       </c>
       <c r="D750" t="s">
+        <v>1032</v>
+      </c>
+      <c r="E750" t="s">
         <v>1039</v>
       </c>
-      <c r="E750" t="s">
+      <c r="F750" t="s">
         <v>1040</v>
-      </c>
-      <c r="F750" t="s">
-        <v>1034</v>
       </c>
     </row>
     <row r="751" spans="1:6">
@@ -19520,13 +19520,13 @@
         <v>18</v>
       </c>
       <c r="D751" t="s">
+        <v>1032</v>
+      </c>
+      <c r="E751" t="s">
         <v>1064</v>
       </c>
-      <c r="E751" t="s">
+      <c r="F751" t="s">
         <v>1065</v>
-      </c>
-      <c r="F751" t="s">
-        <v>1034</v>
       </c>
     </row>
     <row r="752" spans="1:6">
@@ -19540,13 +19540,13 @@
         <v>18</v>
       </c>
       <c r="D752" t="s">
+        <v>1032</v>
+      </c>
+      <c r="E752" t="s">
         <v>1067</v>
       </c>
-      <c r="E752" t="s">
+      <c r="F752" t="s">
         <v>1068</v>
-      </c>
-      <c r="F752" t="s">
-        <v>1034</v>
       </c>
     </row>
     <row r="753" spans="1:6">
@@ -19560,13 +19560,13 @@
         <v>16</v>
       </c>
       <c r="D753" t="s">
+        <v>1032</v>
+      </c>
+      <c r="E753" t="s">
         <v>1039</v>
       </c>
-      <c r="E753" t="s">
+      <c r="F753" t="s">
         <v>1040</v>
-      </c>
-      <c r="F753" t="s">
-        <v>1034</v>
       </c>
     </row>
     <row r="754" spans="1:6">
@@ -19580,13 +19580,13 @@
         <v>18</v>
       </c>
       <c r="D754" t="s">
+        <v>1032</v>
+      </c>
+      <c r="E754" t="s">
         <v>1071</v>
       </c>
-      <c r="E754" t="s">
+      <c r="F754" t="s">
         <v>1072</v>
-      </c>
-      <c r="F754" t="s">
-        <v>1034</v>
       </c>
     </row>
     <row r="755" spans="1:6">
@@ -19600,13 +19600,13 @@
         <v>16</v>
       </c>
       <c r="D755" t="s">
+        <v>1032</v>
+      </c>
+      <c r="E755" t="s">
         <v>1039</v>
       </c>
-      <c r="E755" t="s">
+      <c r="F755" t="s">
         <v>1040</v>
-      </c>
-      <c r="F755" t="s">
-        <v>1034</v>
       </c>
     </row>
     <row r="756" spans="1:6">
@@ -19620,13 +19620,13 @@
         <v>18</v>
       </c>
       <c r="D756" t="s">
+        <v>1032</v>
+      </c>
+      <c r="E756" t="s">
         <v>1075</v>
       </c>
-      <c r="E756" t="s">
+      <c r="F756" t="s">
         <v>1076</v>
-      </c>
-      <c r="F756" t="s">
-        <v>1034</v>
       </c>
     </row>
     <row r="757" spans="1:6">
@@ -19640,13 +19640,13 @@
         <v>18</v>
       </c>
       <c r="D757" t="s">
-        <v>1071</v>
+        <v>1032</v>
       </c>
       <c r="E757" t="s">
         <v>1078</v>
       </c>
       <c r="F757" t="s">
-        <v>1034</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="758" spans="1:6">
@@ -19660,13 +19660,13 @@
         <v>769</v>
       </c>
       <c r="D758" t="s">
+        <v>1032</v>
+      </c>
+      <c r="E758" t="s">
         <v>1039</v>
       </c>
-      <c r="E758" t="s">
+      <c r="F758" t="s">
         <v>1040</v>
-      </c>
-      <c r="F758" t="s">
-        <v>1034</v>
       </c>
     </row>
     <row r="759" spans="1:6">
@@ -19680,13 +19680,13 @@
         <v>16</v>
       </c>
       <c r="D759" t="s">
-        <v>1067</v>
+        <v>1032</v>
       </c>
       <c r="E759" t="s">
         <v>1081</v>
       </c>
       <c r="F759" t="s">
-        <v>1034</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="760" spans="1:6">
@@ -19700,13 +19700,13 @@
         <v>769</v>
       </c>
       <c r="D760" t="s">
+        <v>1032</v>
+      </c>
+      <c r="E760" t="s">
         <v>1039</v>
       </c>
-      <c r="E760" t="s">
+      <c r="F760" t="s">
         <v>1040</v>
-      </c>
-      <c r="F760" t="s">
-        <v>1034</v>
       </c>
     </row>
     <row r="761" spans="1:6">
@@ -19720,13 +19720,13 @@
         <v>769</v>
       </c>
       <c r="D761" t="s">
-        <v>1067</v>
+        <v>1032</v>
       </c>
       <c r="E761" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="F761" t="s">
-        <v>1034</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="762" spans="1:6">
@@ -19740,13 +19740,13 @@
         <v>16</v>
       </c>
       <c r="D762" t="s">
-        <v>1067</v>
+        <v>1032</v>
       </c>
       <c r="E762" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="F762" t="s">
-        <v>1034</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="763" spans="1:6">
@@ -19760,13 +19760,13 @@
         <v>18</v>
       </c>
       <c r="D763" t="s">
-        <v>1036</v>
+        <v>1032</v>
       </c>
       <c r="E763" t="s">
         <v>1086</v>
       </c>
       <c r="F763" t="s">
-        <v>1034</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="764" spans="1:6">
@@ -19780,13 +19780,13 @@
         <v>769</v>
       </c>
       <c r="D764" t="s">
+        <v>1032</v>
+      </c>
+      <c r="E764" t="s">
         <v>1039</v>
       </c>
-      <c r="E764" t="s">
+      <c r="F764" t="s">
         <v>1040</v>
-      </c>
-      <c r="F764" t="s">
-        <v>1034</v>
       </c>
     </row>
     <row r="765" spans="1:6">
@@ -19800,13 +19800,13 @@
         <v>18</v>
       </c>
       <c r="D765" t="s">
+        <v>1032</v>
+      </c>
+      <c r="E765" t="s">
         <v>1089</v>
       </c>
-      <c r="E765" t="s">
+      <c r="F765" t="s">
         <v>1090</v>
-      </c>
-      <c r="F765" t="s">
-        <v>1034</v>
       </c>
     </row>
     <row r="766" spans="1:6">
@@ -19820,13 +19820,13 @@
         <v>769</v>
       </c>
       <c r="D766" t="s">
-        <v>1067</v>
+        <v>1032</v>
       </c>
       <c r="E766" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="F766" t="s">
-        <v>1034</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="767" spans="1:6">
@@ -19840,13 +19840,13 @@
         <v>769</v>
       </c>
       <c r="D767" t="s">
+        <v>1032</v>
+      </c>
+      <c r="E767" t="s">
         <v>1039</v>
       </c>
-      <c r="E767" t="s">
+      <c r="F767" t="s">
         <v>1040</v>
-      </c>
-      <c r="F767" t="s">
-        <v>1034</v>
       </c>
     </row>
     <row r="768" spans="1:6">
@@ -19860,13 +19860,13 @@
         <v>18</v>
       </c>
       <c r="D768" t="s">
+        <v>1032</v>
+      </c>
+      <c r="E768" t="s">
         <v>1048</v>
       </c>
-      <c r="E768" t="s">
+      <c r="F768" t="s">
         <v>1049</v>
-      </c>
-      <c r="F768" t="s">
-        <v>1034</v>
       </c>
     </row>
     <row r="769" spans="1:6">
@@ -19880,13 +19880,13 @@
         <v>22</v>
       </c>
       <c r="D769" t="s">
+        <v>1032</v>
+      </c>
+      <c r="E769" t="s">
         <v>1039</v>
       </c>
-      <c r="E769" t="s">
+      <c r="F769" t="s">
         <v>1040</v>
-      </c>
-      <c r="F769" t="s">
-        <v>1034</v>
       </c>
     </row>
     <row r="770" spans="1:6">
@@ -19900,13 +19900,13 @@
         <v>769</v>
       </c>
       <c r="D770" t="s">
+        <v>1032</v>
+      </c>
+      <c r="E770" t="s">
         <v>1039</v>
       </c>
-      <c r="E770" t="s">
+      <c r="F770" t="s">
         <v>1040</v>
-      </c>
-      <c r="F770" t="s">
-        <v>1034</v>
       </c>
     </row>
     <row r="771" spans="1:6">
@@ -19920,13 +19920,13 @@
         <v>18</v>
       </c>
       <c r="D771" t="s">
-        <v>1067</v>
+        <v>1032</v>
       </c>
       <c r="E771" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="F771" t="s">
-        <v>1034</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="772" spans="1:6">
@@ -19940,13 +19940,13 @@
         <v>769</v>
       </c>
       <c r="D772" t="s">
+        <v>1032</v>
+      </c>
+      <c r="E772" t="s">
         <v>1039</v>
       </c>
-      <c r="E772" t="s">
+      <c r="F772" t="s">
         <v>1040</v>
-      </c>
-      <c r="F772" t="s">
-        <v>1034</v>
       </c>
     </row>
     <row r="773" spans="1:6">
@@ -19960,13 +19960,13 @@
         <v>769</v>
       </c>
       <c r="D773" t="s">
+        <v>1032</v>
+      </c>
+      <c r="E773" t="s">
         <v>1039</v>
       </c>
-      <c r="E773" t="s">
+      <c r="F773" t="s">
         <v>1040</v>
-      </c>
-      <c r="F773" t="s">
-        <v>1034</v>
       </c>
     </row>
     <row r="774" spans="1:6">
@@ -20120,13 +20120,13 @@
         <v>16</v>
       </c>
       <c r="D781" t="s">
+        <v>1100</v>
+      </c>
+      <c r="E781" t="s">
         <v>1111</v>
       </c>
-      <c r="E781" t="s">
+      <c r="F781" t="s">
         <v>1112</v>
-      </c>
-      <c r="F781" t="s">
-        <v>1102</v>
       </c>
     </row>
     <row r="782" spans="1:6">
@@ -20140,13 +20140,13 @@
         <v>16</v>
       </c>
       <c r="D782" t="s">
+        <v>1100</v>
+      </c>
+      <c r="E782" t="s">
         <v>1114</v>
       </c>
-      <c r="E782" t="s">
+      <c r="F782" t="s">
         <v>1115</v>
-      </c>
-      <c r="F782" t="s">
-        <v>1102</v>
       </c>
     </row>
     <row r="783" spans="1:6">
@@ -20200,13 +20200,13 @@
         <v>18</v>
       </c>
       <c r="D785" t="s">
+        <v>1100</v>
+      </c>
+      <c r="E785" t="s">
         <v>1119</v>
       </c>
-      <c r="E785" t="s">
+      <c r="F785" t="s">
         <v>1120</v>
-      </c>
-      <c r="F785" t="s">
-        <v>1102</v>
       </c>
     </row>
     <row r="786" spans="1:6">
@@ -20240,13 +20240,13 @@
         <v>18</v>
       </c>
       <c r="D787" t="s">
+        <v>1100</v>
+      </c>
+      <c r="E787" t="s">
         <v>1119</v>
       </c>
-      <c r="E787" t="s">
+      <c r="F787" t="s">
         <v>1120</v>
-      </c>
-      <c r="F787" t="s">
-        <v>1102</v>
       </c>
     </row>
     <row r="788" spans="1:6">
@@ -20260,13 +20260,13 @@
         <v>18</v>
       </c>
       <c r="D788" t="s">
+        <v>1100</v>
+      </c>
+      <c r="E788" t="s">
         <v>1124</v>
       </c>
-      <c r="E788" t="s">
+      <c r="F788" t="s">
         <v>1125</v>
-      </c>
-      <c r="F788" t="s">
-        <v>1102</v>
       </c>
     </row>
     <row r="789" spans="1:6">
@@ -20300,13 +20300,13 @@
         <v>18</v>
       </c>
       <c r="D790" t="s">
+        <v>1100</v>
+      </c>
+      <c r="E790" t="s">
         <v>1129</v>
       </c>
-      <c r="E790" t="s">
+      <c r="F790" t="s">
         <v>1130</v>
-      </c>
-      <c r="F790" t="s">
-        <v>1102</v>
       </c>
     </row>
     <row r="791" spans="1:6">
@@ -20380,13 +20380,13 @@
         <v>16</v>
       </c>
       <c r="D794" t="s">
-        <v>1039</v>
+        <v>1100</v>
       </c>
       <c r="E794" t="s">
         <v>1136</v>
       </c>
       <c r="F794" t="s">
-        <v>1102</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="795" spans="1:6">
@@ -20440,13 +20440,13 @@
         <v>18</v>
       </c>
       <c r="D797" t="s">
+        <v>1100</v>
+      </c>
+      <c r="E797" t="s">
         <v>1140</v>
       </c>
-      <c r="E797" t="s">
+      <c r="F797" t="s">
         <v>1141</v>
-      </c>
-      <c r="F797" t="s">
-        <v>1102</v>
       </c>
     </row>
     <row r="798" spans="1:6">
@@ -20660,13 +20660,13 @@
         <v>18</v>
       </c>
       <c r="D808" t="s">
+        <v>1154</v>
+      </c>
+      <c r="E808" t="s">
         <v>1158</v>
       </c>
-      <c r="E808" t="s">
+      <c r="F808" t="s">
         <v>1159</v>
-      </c>
-      <c r="F808" t="s">
-        <v>1156</v>
       </c>
     </row>
     <row r="809" spans="1:6">
@@ -20680,13 +20680,13 @@
         <v>769</v>
       </c>
       <c r="D809" t="s">
+        <v>1154</v>
+      </c>
+      <c r="E809" t="s">
         <v>1161</v>
       </c>
-      <c r="E809" t="s">
+      <c r="F809" t="s">
         <v>1162</v>
-      </c>
-      <c r="F809" t="s">
-        <v>1156</v>
       </c>
     </row>
     <row r="810" spans="1:6">
@@ -20700,13 +20700,13 @@
         <v>769</v>
       </c>
       <c r="D810" t="s">
+        <v>1154</v>
+      </c>
+      <c r="E810" t="s">
         <v>1161</v>
       </c>
-      <c r="E810" t="s">
+      <c r="F810" t="s">
         <v>1162</v>
-      </c>
-      <c r="F810" t="s">
-        <v>1156</v>
       </c>
     </row>
     <row r="811" spans="1:6">
@@ -20720,13 +20720,13 @@
         <v>769</v>
       </c>
       <c r="D811" t="s">
+        <v>1154</v>
+      </c>
+      <c r="E811" t="s">
         <v>1161</v>
       </c>
-      <c r="E811" t="s">
+      <c r="F811" t="s">
         <v>1162</v>
-      </c>
-      <c r="F811" t="s">
-        <v>1156</v>
       </c>
     </row>
     <row r="812" spans="1:6">
@@ -20740,13 +20740,13 @@
         <v>769</v>
       </c>
       <c r="D812" t="s">
+        <v>1154</v>
+      </c>
+      <c r="E812" t="s">
         <v>1161</v>
       </c>
-      <c r="E812" t="s">
+      <c r="F812" t="s">
         <v>1162</v>
-      </c>
-      <c r="F812" t="s">
-        <v>1156</v>
       </c>
     </row>
     <row r="813" spans="1:6">
@@ -20760,13 +20760,13 @@
         <v>769</v>
       </c>
       <c r="D813" t="s">
+        <v>1154</v>
+      </c>
+      <c r="E813" t="s">
         <v>1161</v>
       </c>
-      <c r="E813" t="s">
+      <c r="F813" t="s">
         <v>1162</v>
-      </c>
-      <c r="F813" t="s">
-        <v>1156</v>
       </c>
     </row>
     <row r="814" spans="1:6">
@@ -20780,13 +20780,13 @@
         <v>769</v>
       </c>
       <c r="D814" t="s">
+        <v>1154</v>
+      </c>
+      <c r="E814" t="s">
         <v>1161</v>
       </c>
-      <c r="E814" t="s">
+      <c r="F814" t="s">
         <v>1162</v>
-      </c>
-      <c r="F814" t="s">
-        <v>1156</v>
       </c>
     </row>
     <row r="815" spans="1:6">
@@ -20800,13 +20800,13 @@
         <v>18</v>
       </c>
       <c r="D815" t="s">
-        <v>1158</v>
+        <v>1154</v>
       </c>
       <c r="E815" t="s">
         <v>1155</v>
       </c>
       <c r="F815" t="s">
-        <v>1156</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="816" spans="1:6">
@@ -20820,13 +20820,13 @@
         <v>16</v>
       </c>
       <c r="D816" t="s">
-        <v>1161</v>
+        <v>1154</v>
       </c>
       <c r="E816" t="s">
         <v>1133</v>
       </c>
       <c r="F816" t="s">
-        <v>1156</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="817" spans="1:6">
@@ -20840,13 +20840,13 @@
         <v>769</v>
       </c>
       <c r="D817" t="s">
+        <v>1154</v>
+      </c>
+      <c r="E817" t="s">
         <v>1161</v>
       </c>
-      <c r="E817" t="s">
+      <c r="F817" t="s">
         <v>1162</v>
-      </c>
-      <c r="F817" t="s">
-        <v>1156</v>
       </c>
     </row>
     <row r="818" spans="1:6">
@@ -20863,7 +20863,7 @@
         <v>1154</v>
       </c>
       <c r="E818" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="F818" t="s">
         <v>1156</v>
@@ -20880,13 +20880,13 @@
         <v>769</v>
       </c>
       <c r="D819" t="s">
+        <v>1154</v>
+      </c>
+      <c r="E819" t="s">
         <v>1161</v>
       </c>
-      <c r="E819" t="s">
+      <c r="F819" t="s">
         <v>1162</v>
-      </c>
-      <c r="F819" t="s">
-        <v>1156</v>
       </c>
     </row>
     <row r="820" spans="1:6">
@@ -20900,13 +20900,13 @@
         <v>18</v>
       </c>
       <c r="D820" t="s">
-        <v>1174</v>
+        <v>1154</v>
       </c>
       <c r="E820" t="s">
         <v>1133</v>
       </c>
       <c r="F820" t="s">
-        <v>1156</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="821" spans="1:6">
@@ -20920,13 +20920,13 @@
         <v>769</v>
       </c>
       <c r="D821" t="s">
+        <v>1154</v>
+      </c>
+      <c r="E821" t="s">
         <v>1161</v>
       </c>
-      <c r="E821" t="s">
+      <c r="F821" t="s">
         <v>1162</v>
-      </c>
-      <c r="F821" t="s">
-        <v>1156</v>
       </c>
     </row>
     <row r="822" spans="1:6">
@@ -20940,13 +20940,13 @@
         <v>18</v>
       </c>
       <c r="D822" t="s">
+        <v>1154</v>
+      </c>
+      <c r="E822" t="s">
         <v>1177</v>
       </c>
-      <c r="E822" t="s">
+      <c r="F822" t="s">
         <v>1178</v>
-      </c>
-      <c r="F822" t="s">
-        <v>1156</v>
       </c>
     </row>
     <row r="823" spans="1:6">
@@ -20963,7 +20963,7 @@
         <v>1154</v>
       </c>
       <c r="E823" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="F823" t="s">
         <v>1156</v>
@@ -20980,13 +20980,13 @@
         <v>18</v>
       </c>
       <c r="D824" t="s">
-        <v>1174</v>
+        <v>1154</v>
       </c>
       <c r="E824" t="s">
         <v>1181</v>
       </c>
       <c r="F824" t="s">
-        <v>1156</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="825" spans="1:6">
@@ -21000,13 +21000,13 @@
         <v>18</v>
       </c>
       <c r="D825" t="s">
+        <v>1154</v>
+      </c>
+      <c r="E825" t="s">
         <v>1183</v>
       </c>
-      <c r="E825" t="s">
+      <c r="F825" t="s">
         <v>1184</v>
-      </c>
-      <c r="F825" t="s">
-        <v>1156</v>
       </c>
     </row>
     <row r="826" spans="1:6">
@@ -21020,13 +21020,13 @@
         <v>769</v>
       </c>
       <c r="D826" t="s">
+        <v>1154</v>
+      </c>
+      <c r="E826" t="s">
         <v>1161</v>
       </c>
-      <c r="E826" t="s">
+      <c r="F826" t="s">
         <v>1162</v>
-      </c>
-      <c r="F826" t="s">
-        <v>1156</v>
       </c>
     </row>
     <row r="827" spans="1:6">
@@ -21040,13 +21040,13 @@
         <v>769</v>
       </c>
       <c r="D827" t="s">
+        <v>1154</v>
+      </c>
+      <c r="E827" t="s">
         <v>1161</v>
       </c>
-      <c r="E827" t="s">
+      <c r="F827" t="s">
         <v>1162</v>
-      </c>
-      <c r="F827" t="s">
-        <v>1156</v>
       </c>
     </row>
     <row r="828" spans="1:6">
@@ -21060,13 +21060,13 @@
         <v>22</v>
       </c>
       <c r="D828" t="s">
+        <v>1154</v>
+      </c>
+      <c r="E828" t="s">
         <v>1188</v>
       </c>
-      <c r="E828" t="s">
+      <c r="F828" t="s">
         <v>1189</v>
-      </c>
-      <c r="F828" t="s">
-        <v>1156</v>
       </c>
     </row>
     <row r="829" spans="1:6">
@@ -21080,13 +21080,13 @@
         <v>16</v>
       </c>
       <c r="D829" t="s">
+        <v>1154</v>
+      </c>
+      <c r="E829" t="s">
         <v>1161</v>
       </c>
-      <c r="E829" t="s">
+      <c r="F829" t="s">
         <v>1162</v>
-      </c>
-      <c r="F829" t="s">
-        <v>1156</v>
       </c>
     </row>
     <row r="830" spans="1:6">
@@ -21100,13 +21100,13 @@
         <v>18</v>
       </c>
       <c r="D830" t="s">
+        <v>1154</v>
+      </c>
+      <c r="E830" t="s">
         <v>1192</v>
       </c>
-      <c r="E830" t="s">
+      <c r="F830" t="s">
         <v>1193</v>
-      </c>
-      <c r="F830" t="s">
-        <v>1156</v>
       </c>
     </row>
     <row r="831" spans="1:6">
@@ -21120,13 +21120,13 @@
         <v>769</v>
       </c>
       <c r="D831" t="s">
+        <v>1154</v>
+      </c>
+      <c r="E831" t="s">
         <v>1161</v>
       </c>
-      <c r="E831" t="s">
+      <c r="F831" t="s">
         <v>1162</v>
-      </c>
-      <c r="F831" t="s">
-        <v>1156</v>
       </c>
     </row>
     <row r="832" spans="1:6">
@@ -21140,13 +21140,13 @@
         <v>769</v>
       </c>
       <c r="D832" t="s">
+        <v>1154</v>
+      </c>
+      <c r="E832" t="s">
         <v>1161</v>
       </c>
-      <c r="E832" t="s">
+      <c r="F832" t="s">
         <v>1162</v>
-      </c>
-      <c r="F832" t="s">
-        <v>1156</v>
       </c>
     </row>
     <row r="833" spans="1:6">
@@ -21160,13 +21160,13 @@
         <v>22</v>
       </c>
       <c r="D833" t="s">
+        <v>1154</v>
+      </c>
+      <c r="E833" t="s">
         <v>1161</v>
       </c>
-      <c r="E833" t="s">
+      <c r="F833" t="s">
         <v>1162</v>
-      </c>
-      <c r="F833" t="s">
-        <v>1156</v>
       </c>
     </row>
     <row r="834" spans="1:6">
@@ -21180,13 +21180,13 @@
         <v>18</v>
       </c>
       <c r="D834" t="s">
+        <v>1154</v>
+      </c>
+      <c r="E834" t="s">
         <v>1188</v>
       </c>
-      <c r="E834" t="s">
+      <c r="F834" t="s">
         <v>1189</v>
-      </c>
-      <c r="F834" t="s">
-        <v>1156</v>
       </c>
     </row>
     <row r="835" spans="1:6">
@@ -21200,13 +21200,13 @@
         <v>769</v>
       </c>
       <c r="D835" t="s">
+        <v>1154</v>
+      </c>
+      <c r="E835" t="s">
         <v>1161</v>
       </c>
-      <c r="E835" t="s">
+      <c r="F835" t="s">
         <v>1162</v>
-      </c>
-      <c r="F835" t="s">
-        <v>1156</v>
       </c>
     </row>
     <row r="836" spans="1:6">
@@ -21260,13 +21260,13 @@
         <v>18</v>
       </c>
       <c r="D838" t="s">
+        <v>1200</v>
+      </c>
+      <c r="E838" t="s">
         <v>1206</v>
       </c>
-      <c r="E838" t="s">
+      <c r="F838" t="s">
         <v>1207</v>
-      </c>
-      <c r="F838" t="s">
-        <v>1202</v>
       </c>
     </row>
     <row r="839" spans="1:6">
@@ -21280,13 +21280,13 @@
         <v>18</v>
       </c>
       <c r="D839" t="s">
+        <v>1200</v>
+      </c>
+      <c r="E839" t="s">
         <v>1209</v>
       </c>
-      <c r="E839" t="s">
+      <c r="F839" t="s">
         <v>1210</v>
-      </c>
-      <c r="F839" t="s">
-        <v>1202</v>
       </c>
     </row>
     <row r="840" spans="1:6">
@@ -21500,13 +21500,13 @@
         <v>18</v>
       </c>
       <c r="D850" t="s">
-        <v>1223</v>
+        <v>1200</v>
       </c>
       <c r="E850" t="s">
         <v>1201</v>
       </c>
       <c r="F850" t="s">
-        <v>1202</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="851" spans="1:6">
@@ -21540,13 +21540,13 @@
         <v>18</v>
       </c>
       <c r="D852" t="s">
-        <v>1226</v>
+        <v>1200</v>
       </c>
       <c r="E852" t="s">
         <v>1214</v>
       </c>
       <c r="F852" t="s">
-        <v>1202</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="853" spans="1:6">
@@ -21560,13 +21560,13 @@
         <v>18</v>
       </c>
       <c r="D853" t="s">
-        <v>1223</v>
+        <v>1200</v>
       </c>
       <c r="E853" t="s">
         <v>1228</v>
       </c>
       <c r="F853" t="s">
-        <v>1202</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="854" spans="1:6">
@@ -21600,13 +21600,13 @@
         <v>18</v>
       </c>
       <c r="D855" t="s">
-        <v>1231</v>
+        <v>1200</v>
       </c>
       <c r="E855" t="s">
         <v>1204</v>
       </c>
       <c r="F855" t="s">
-        <v>1202</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="856" spans="1:6">
@@ -21660,13 +21660,13 @@
         <v>18</v>
       </c>
       <c r="D858" t="s">
+        <v>1200</v>
+      </c>
+      <c r="E858" t="s">
         <v>1236</v>
       </c>
-      <c r="E858" t="s">
+      <c r="F858" t="s">
         <v>1237</v>
-      </c>
-      <c r="F858" t="s">
-        <v>1202</v>
       </c>
     </row>
     <row r="859" spans="1:6">
@@ -21680,13 +21680,13 @@
         <v>18</v>
       </c>
       <c r="D859" t="s">
+        <v>1200</v>
+      </c>
+      <c r="E859" t="s">
         <v>1239</v>
       </c>
-      <c r="E859" t="s">
+      <c r="F859" t="s">
         <v>1240</v>
-      </c>
-      <c r="F859" t="s">
-        <v>1202</v>
       </c>
     </row>
     <row r="860" spans="1:6">
@@ -21940,13 +21940,13 @@
         <v>18</v>
       </c>
       <c r="D872" t="s">
+        <v>1251</v>
+      </c>
+      <c r="E872" t="s">
         <v>1258</v>
       </c>
-      <c r="E872" t="s">
+      <c r="F872" t="s">
         <v>1259</v>
-      </c>
-      <c r="F872" t="s">
-        <v>1253</v>
       </c>
     </row>
     <row r="873" spans="1:6">
@@ -22003,7 +22003,7 @@
         <v>1251</v>
       </c>
       <c r="E875" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="F875" t="s">
         <v>1253</v>
@@ -22020,13 +22020,13 @@
         <v>22</v>
       </c>
       <c r="D876" t="s">
+        <v>1251</v>
+      </c>
+      <c r="E876" t="s">
         <v>1264</v>
       </c>
-      <c r="E876" t="s">
+      <c r="F876" t="s">
         <v>1265</v>
-      </c>
-      <c r="F876" t="s">
-        <v>1253</v>
       </c>
     </row>
     <row r="877" spans="1:6">
@@ -22043,7 +22043,7 @@
         <v>1251</v>
       </c>
       <c r="E877" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="F877" t="s">
         <v>1253</v>
@@ -22060,13 +22060,13 @@
         <v>18</v>
       </c>
       <c r="D878" t="s">
+        <v>1251</v>
+      </c>
+      <c r="E878" t="s">
         <v>1264</v>
       </c>
-      <c r="E878" t="s">
+      <c r="F878" t="s">
         <v>1265</v>
-      </c>
-      <c r="F878" t="s">
-        <v>1253</v>
       </c>
     </row>
     <row r="879" spans="1:6">
@@ -22200,13 +22200,13 @@
         <v>16</v>
       </c>
       <c r="D885" t="s">
+        <v>1251</v>
+      </c>
+      <c r="E885" t="s">
         <v>1275</v>
       </c>
-      <c r="E885" t="s">
+      <c r="F885" t="s">
         <v>1276</v>
-      </c>
-      <c r="F885" t="s">
-        <v>1253</v>
       </c>
     </row>
     <row r="886" spans="1:6">
@@ -22220,13 +22220,13 @@
         <v>1255</v>
       </c>
       <c r="D886" t="s">
+        <v>1251</v>
+      </c>
+      <c r="E886" t="s">
         <v>1278</v>
       </c>
-      <c r="E886" t="s">
+      <c r="F886" t="s">
         <v>1279</v>
-      </c>
-      <c r="F886" t="s">
-        <v>1253</v>
       </c>
     </row>
     <row r="887" spans="1:6">
@@ -22243,7 +22243,7 @@
         <v>1251</v>
       </c>
       <c r="E887" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="F887" t="s">
         <v>1253</v>
@@ -22260,13 +22260,13 @@
         <v>1255</v>
       </c>
       <c r="D888" t="s">
+        <v>1251</v>
+      </c>
+      <c r="E888" t="s">
         <v>1278</v>
       </c>
-      <c r="E888" t="s">
+      <c r="F888" t="s">
         <v>1279</v>
-      </c>
-      <c r="F888" t="s">
-        <v>1253</v>
       </c>
     </row>
     <row r="889" spans="1:6">
@@ -22280,13 +22280,13 @@
         <v>22</v>
       </c>
       <c r="D889" t="s">
+        <v>1251</v>
+      </c>
+      <c r="E889" t="s">
         <v>1278</v>
       </c>
-      <c r="E889" t="s">
+      <c r="F889" t="s">
         <v>1279</v>
-      </c>
-      <c r="F889" t="s">
-        <v>1253</v>
       </c>
     </row>
     <row r="890" spans="1:6">
@@ -22300,13 +22300,13 @@
         <v>769</v>
       </c>
       <c r="D890" t="s">
+        <v>1251</v>
+      </c>
+      <c r="E890" t="s">
         <v>1278</v>
       </c>
-      <c r="E890" t="s">
+      <c r="F890" t="s">
         <v>1279</v>
-      </c>
-      <c r="F890" t="s">
-        <v>1253</v>
       </c>
     </row>
     <row r="891" spans="1:6">
@@ -22320,13 +22320,13 @@
         <v>1255</v>
       </c>
       <c r="D891" t="s">
+        <v>1251</v>
+      </c>
+      <c r="E891" t="s">
         <v>1278</v>
       </c>
-      <c r="E891" t="s">
+      <c r="F891" t="s">
         <v>1279</v>
-      </c>
-      <c r="F891" t="s">
-        <v>1253</v>
       </c>
     </row>
     <row r="892" spans="1:6">
@@ -22340,13 +22340,13 @@
         <v>1255</v>
       </c>
       <c r="D892" t="s">
+        <v>1251</v>
+      </c>
+      <c r="E892" t="s">
         <v>1278</v>
       </c>
-      <c r="E892" t="s">
+      <c r="F892" t="s">
         <v>1279</v>
-      </c>
-      <c r="F892" t="s">
-        <v>1253</v>
       </c>
     </row>
     <row r="893" spans="1:6">
@@ -22363,7 +22363,7 @@
         <v>1251</v>
       </c>
       <c r="E893" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="F893" t="s">
         <v>1253</v>
@@ -22403,7 +22403,7 @@
         <v>1251</v>
       </c>
       <c r="E895" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="F895" t="s">
         <v>1253</v>
@@ -22423,7 +22423,7 @@
         <v>1251</v>
       </c>
       <c r="E896" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="F896" t="s">
         <v>1253</v>
@@ -22780,13 +22780,13 @@
         <v>1255</v>
       </c>
       <c r="D914" t="s">
-        <v>1258</v>
+        <v>1299</v>
       </c>
       <c r="E914" t="s">
         <v>1312</v>
       </c>
       <c r="F914" t="s">
-        <v>1301</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="915" spans="1:6">
@@ -22800,13 +22800,13 @@
         <v>1255</v>
       </c>
       <c r="D915" t="s">
-        <v>1258</v>
+        <v>1299</v>
       </c>
       <c r="E915" t="s">
         <v>1312</v>
       </c>
       <c r="F915" t="s">
-        <v>1301</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="916" spans="1:6">
@@ -22820,13 +22820,13 @@
         <v>22</v>
       </c>
       <c r="D916" t="s">
-        <v>1258</v>
+        <v>1299</v>
       </c>
       <c r="E916" t="s">
         <v>1312</v>
       </c>
       <c r="F916" t="s">
-        <v>1301</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="917" spans="1:6">
@@ -22840,13 +22840,13 @@
         <v>769</v>
       </c>
       <c r="D917" t="s">
-        <v>1258</v>
+        <v>1299</v>
       </c>
       <c r="E917" t="s">
         <v>1312</v>
       </c>
       <c r="F917" t="s">
-        <v>1301</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="918" spans="1:6">
@@ -22860,13 +22860,13 @@
         <v>1255</v>
       </c>
       <c r="D918" t="s">
-        <v>1317</v>
+        <v>1299</v>
       </c>
       <c r="E918" t="s">
         <v>1312</v>
       </c>
       <c r="F918" t="s">
-        <v>1301</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="919" spans="1:6">
@@ -22880,13 +22880,13 @@
         <v>1255</v>
       </c>
       <c r="D919" t="s">
-        <v>1258</v>
+        <v>1299</v>
       </c>
       <c r="E919" t="s">
         <v>1312</v>
       </c>
       <c r="F919" t="s">
-        <v>1301</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="920" spans="1:6">
@@ -22900,13 +22900,13 @@
         <v>1255</v>
       </c>
       <c r="D920" t="s">
-        <v>1258</v>
+        <v>1299</v>
       </c>
       <c r="E920" t="s">
         <v>1312</v>
       </c>
       <c r="F920" t="s">
-        <v>1301</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="921" spans="1:6">
@@ -23220,13 +23220,13 @@
         <v>1255</v>
       </c>
       <c r="D936" t="s">
-        <v>1339</v>
+        <v>1335</v>
       </c>
       <c r="E936" t="s">
         <v>1336</v>
       </c>
       <c r="F936" t="s">
-        <v>1337</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="937" spans="1:6">
@@ -23240,13 +23240,13 @@
         <v>1255</v>
       </c>
       <c r="D937" t="s">
-        <v>1339</v>
+        <v>1335</v>
       </c>
       <c r="E937" t="s">
         <v>1336</v>
       </c>
       <c r="F937" t="s">
-        <v>1337</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="938" spans="1:6">
@@ -23260,13 +23260,13 @@
         <v>1255</v>
       </c>
       <c r="D938" t="s">
-        <v>1339</v>
+        <v>1335</v>
       </c>
       <c r="E938" t="s">
         <v>1336</v>
       </c>
       <c r="F938" t="s">
-        <v>1337</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="939" spans="1:6">
@@ -23280,13 +23280,13 @@
         <v>1255</v>
       </c>
       <c r="D939" t="s">
-        <v>1339</v>
+        <v>1335</v>
       </c>
       <c r="E939" t="s">
         <v>1336</v>
       </c>
       <c r="F939" t="s">
-        <v>1337</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="940" spans="1:6">
@@ -23300,13 +23300,13 @@
         <v>16</v>
       </c>
       <c r="D940" t="s">
-        <v>1339</v>
+        <v>1335</v>
       </c>
       <c r="E940" t="s">
         <v>1336</v>
       </c>
       <c r="F940" t="s">
-        <v>1337</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="941" spans="1:6">
@@ -23320,13 +23320,13 @@
         <v>22</v>
       </c>
       <c r="D941" t="s">
-        <v>1339</v>
+        <v>1335</v>
       </c>
       <c r="E941" t="s">
         <v>1336</v>
       </c>
       <c r="F941" t="s">
-        <v>1337</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="942" spans="1:6">
@@ -23340,13 +23340,13 @@
         <v>16</v>
       </c>
       <c r="D942" t="s">
-        <v>1339</v>
+        <v>1335</v>
       </c>
       <c r="E942" t="s">
         <v>1336</v>
       </c>
       <c r="F942" t="s">
-        <v>1337</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="943" spans="1:6">
@@ -23360,13 +23360,13 @@
         <v>1255</v>
       </c>
       <c r="D943" t="s">
-        <v>1339</v>
+        <v>1335</v>
       </c>
       <c r="E943" t="s">
         <v>1336</v>
       </c>
       <c r="F943" t="s">
-        <v>1337</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="944" spans="1:6">
@@ -23380,13 +23380,13 @@
         <v>1255</v>
       </c>
       <c r="D944" t="s">
-        <v>1339</v>
+        <v>1335</v>
       </c>
       <c r="E944" t="s">
         <v>1336</v>
       </c>
       <c r="F944" t="s">
-        <v>1337</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="945" spans="1:6">
@@ -23400,13 +23400,13 @@
         <v>769</v>
       </c>
       <c r="D945" t="s">
-        <v>1339</v>
+        <v>1335</v>
       </c>
       <c r="E945" t="s">
         <v>1336</v>
       </c>
       <c r="F945" t="s">
-        <v>1337</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="946" spans="1:6">
@@ -23420,13 +23420,13 @@
         <v>16</v>
       </c>
       <c r="D946" t="s">
-        <v>1339</v>
+        <v>1335</v>
       </c>
       <c r="E946" t="s">
         <v>1336</v>
       </c>
       <c r="F946" t="s">
-        <v>1337</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="947" spans="1:6">
@@ -23440,13 +23440,13 @@
         <v>1255</v>
       </c>
       <c r="D947" t="s">
-        <v>1339</v>
+        <v>1335</v>
       </c>
       <c r="E947" t="s">
         <v>1336</v>
       </c>
       <c r="F947" t="s">
-        <v>1337</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="948" spans="1:6">
@@ -23460,13 +23460,13 @@
         <v>1255</v>
       </c>
       <c r="D948" t="s">
-        <v>1339</v>
+        <v>1335</v>
       </c>
       <c r="E948" t="s">
         <v>1336</v>
       </c>
       <c r="F948" t="s">
-        <v>1337</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="949" spans="1:6">
@@ -23480,13 +23480,13 @@
         <v>1255</v>
       </c>
       <c r="D949" t="s">
-        <v>1339</v>
+        <v>1335</v>
       </c>
       <c r="E949" t="s">
         <v>1336</v>
       </c>
       <c r="F949" t="s">
-        <v>1337</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="950" spans="1:6">
@@ -23500,13 +23500,13 @@
         <v>1255</v>
       </c>
       <c r="D950" t="s">
-        <v>1339</v>
+        <v>1335</v>
       </c>
       <c r="E950" t="s">
         <v>1336</v>
       </c>
       <c r="F950" t="s">
-        <v>1337</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="951" spans="1:6">
@@ -23520,13 +23520,13 @@
         <v>1255</v>
       </c>
       <c r="D951" t="s">
-        <v>1339</v>
+        <v>1335</v>
       </c>
       <c r="E951" t="s">
         <v>1336</v>
       </c>
       <c r="F951" t="s">
-        <v>1337</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="952" spans="1:6">
@@ -23540,13 +23540,13 @@
         <v>769</v>
       </c>
       <c r="D952" t="s">
-        <v>1339</v>
+        <v>1335</v>
       </c>
       <c r="E952" t="s">
         <v>1336</v>
       </c>
       <c r="F952" t="s">
-        <v>1337</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="953" spans="1:6">
@@ -23560,13 +23560,13 @@
         <v>1255</v>
       </c>
       <c r="D953" t="s">
-        <v>1339</v>
+        <v>1335</v>
       </c>
       <c r="E953" t="s">
         <v>1336</v>
       </c>
       <c r="F953" t="s">
-        <v>1337</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="954" spans="1:6">
@@ -23580,13 +23580,13 @@
         <v>1255</v>
       </c>
       <c r="D954" t="s">
-        <v>1339</v>
+        <v>1335</v>
       </c>
       <c r="E954" t="s">
         <v>1336</v>
       </c>
       <c r="F954" t="s">
-        <v>1337</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="955" spans="1:6">
@@ -23600,13 +23600,13 @@
         <v>1255</v>
       </c>
       <c r="D955" t="s">
-        <v>1339</v>
+        <v>1335</v>
       </c>
       <c r="E955" t="s">
         <v>1336</v>
       </c>
       <c r="F955" t="s">
-        <v>1337</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="956" spans="1:6">
@@ -23620,13 +23620,13 @@
         <v>16</v>
       </c>
       <c r="D956" t="s">
-        <v>1339</v>
+        <v>1335</v>
       </c>
       <c r="E956" t="s">
         <v>1336</v>
       </c>
       <c r="F956" t="s">
-        <v>1337</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="957" spans="1:6">
@@ -23640,13 +23640,13 @@
         <v>1255</v>
       </c>
       <c r="D957" t="s">
-        <v>1339</v>
+        <v>1335</v>
       </c>
       <c r="E957" t="s">
         <v>1336</v>
       </c>
       <c r="F957" t="s">
-        <v>1337</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="958" spans="1:6">
@@ -23660,13 +23660,13 @@
         <v>769</v>
       </c>
       <c r="D958" t="s">
-        <v>1339</v>
+        <v>1335</v>
       </c>
       <c r="E958" t="s">
         <v>1336</v>
       </c>
       <c r="F958" t="s">
-        <v>1337</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="959" spans="1:6">

--- a/api/1/clv3/xlsx/fr/HumanitarianPlan.xlsx
+++ b/api/1/clv3/xlsx/fr/HumanitarianPlan.xlsx
@@ -28,12 +28,12 @@
     <t>codeforiati:plan-year</t>
   </si>
   <si>
+    <t>codeforiati:plan-end-date</t>
+  </si>
+  <si>
     <t>codeforiati:plan-start-date</t>
   </si>
   <si>
-    <t>codeforiati:plan-end-date</t>
-  </si>
-  <si>
     <t>HAFG26</t>
   </si>
   <si>
@@ -46,12 +46,12 @@
     <t>2026</t>
   </si>
   <si>
+    <t>2026-12-31</t>
+  </si>
+  <si>
     <t>2026-01-01</t>
   </si>
   <si>
-    <t>2026-12-31</t>
-  </si>
-  <si>
     <t>HBFA26</t>
   </si>
   <si>
@@ -85,12 +85,12 @@
     <t>Regional response plan</t>
   </si>
   <si>
+    <t>2026-05-31</t>
+  </si>
+  <si>
     <t>2026-03-01</t>
   </si>
   <si>
-    <t>2026-05-31</t>
-  </si>
-  <si>
     <t>FLBN26</t>
   </si>
   <si>
@@ -193,12 +193,12 @@
     <t>2025</t>
   </si>
   <si>
+    <t>2025-12-31</t>
+  </si>
+  <si>
     <t>2025-01-01</t>
   </si>
   <si>
-    <t>2025-12-31</t>
-  </si>
-  <si>
     <t>RIRNPAK25</t>
   </si>
   <si>
@@ -379,12 +379,12 @@
     <t>2024</t>
   </si>
   <si>
+    <t>2024-12-31</t>
+  </si>
+  <si>
     <t>2024-01-01</t>
   </si>
   <si>
-    <t>2024-12-31</t>
-  </si>
-  <si>
     <t>RAFG_RRP24</t>
   </si>
   <si>
@@ -580,12 +580,12 @@
     <t>2023</t>
   </si>
   <si>
+    <t>2023-12-31</t>
+  </si>
+  <si>
     <t>2023-01-01</t>
   </si>
   <si>
-    <t>2023-12-31</t>
-  </si>
-  <si>
     <t>RAFG23</t>
   </si>
   <si>
@@ -649,21 +649,21 @@
     <t>OMNG2223</t>
   </si>
   <si>
+    <t>2023-05-31</t>
+  </si>
+  <si>
     <t>2022-12-01</t>
   </si>
   <si>
-    <t>2023-05-31</t>
-  </si>
-  <si>
     <t>OMOZ23</t>
   </si>
   <si>
+    <t>2023-09-30</t>
+  </si>
+  <si>
     <t>2023-03-01</t>
   </si>
   <si>
-    <t>2023-09-30</t>
-  </si>
-  <si>
     <t>HMOZ23</t>
   </si>
   <si>
@@ -709,12 +709,12 @@
     <t>RRSDN23</t>
   </si>
   <si>
+    <t>2023-10-31</t>
+  </si>
+  <si>
     <t>2023-05-01</t>
   </si>
   <si>
-    <t>2023-10-31</t>
-  </si>
-  <si>
     <t>HSDN23</t>
   </si>
   <si>
@@ -760,12 +760,12 @@
     <t>2022</t>
   </si>
   <si>
+    <t>2022-12-31</t>
+  </si>
+  <si>
     <t>2022-01-01</t>
   </si>
   <si>
-    <t>2022-12-31</t>
-  </si>
-  <si>
     <t>RAFG22</t>
   </si>
   <si>
@@ -787,12 +787,12 @@
     <t>OCUB2223</t>
   </si>
   <si>
+    <t>2023-03-31</t>
+  </si>
+  <si>
     <t>2022-10-20</t>
   </si>
   <si>
-    <t>2023-03-31</t>
-  </si>
-  <si>
     <t>RDRCRRP22</t>
   </si>
   <si>
@@ -808,12 +808,12 @@
     <t>FHTI2223</t>
   </si>
   <si>
+    <t>2023-04-15</t>
+  </si>
+  <si>
     <t>2022-10-16</t>
   </si>
   <si>
-    <t>2023-04-15</t>
-  </si>
-  <si>
     <t>FHTI22</t>
   </si>
   <si>
@@ -844,24 +844,24 @@
     <t>FMWI22</t>
   </si>
   <si>
+    <t>2022-05-31</t>
+  </si>
+  <si>
     <t>2022-02-26</t>
   </si>
   <si>
-    <t>2022-05-31</t>
-  </si>
-  <si>
     <t>HMLI22</t>
   </si>
   <si>
     <t>FMOZ22</t>
   </si>
   <si>
+    <t>2022-09-30</t>
+  </si>
+  <si>
     <t>2022-04-01</t>
   </si>
   <si>
-    <t>2022-09-30</t>
-  </si>
-  <si>
     <t>HMOZ22</t>
   </si>
   <si>
@@ -892,12 +892,12 @@
     <t>OPHL2122</t>
   </si>
   <si>
+    <t>2022-06-30</t>
+  </si>
+  <si>
     <t>2021-12-24</t>
   </si>
   <si>
-    <t>2022-06-30</t>
-  </si>
-  <si>
     <t>RREG22</t>
   </si>
   <si>
@@ -964,12 +964,12 @@
     <t>2021</t>
   </si>
   <si>
+    <t>2021-12-31</t>
+  </si>
+  <si>
     <t>2021-09-01</t>
   </si>
   <si>
-    <t>2021-12-31</t>
-  </si>
-  <si>
     <t>HAFG21</t>
   </si>
   <si>
@@ -1018,12 +1018,12 @@
     <t>FPSE21</t>
   </si>
   <si>
+    <t>2021-08-27</t>
+  </si>
+  <si>
     <t>2021-05-27</t>
   </si>
   <si>
-    <t>2021-08-27</t>
-  </si>
-  <si>
     <t>HETH21</t>
   </si>
   <si>
@@ -1036,24 +1036,24 @@
     <t>FHTI2122</t>
   </si>
   <si>
+    <t>2022-02-15</t>
+  </si>
+  <si>
     <t>2021-08-16</t>
   </si>
   <si>
-    <t>2022-02-15</t>
-  </si>
-  <si>
     <t>HHTI21</t>
   </si>
   <si>
     <t>FHND2021</t>
   </si>
   <si>
+    <t>2021-06-30</t>
+  </si>
+  <si>
     <t>2020-11-15</t>
   </si>
   <si>
-    <t>2021-06-30</t>
-  </si>
-  <si>
     <t>HHND21</t>
   </si>
   <si>
@@ -1072,12 +1072,12 @@
     <t>OLBN2122</t>
   </si>
   <si>
+    <t>2022-07-31</t>
+  </si>
+  <si>
     <t>2021-08-03</t>
   </si>
   <si>
-    <t>2022-07-31</t>
-  </si>
-  <si>
     <t>HLBY21</t>
   </si>
   <si>
@@ -1168,12 +1168,12 @@
     <t>2020</t>
   </si>
   <si>
+    <t>2020-12-31</t>
+  </si>
+  <si>
     <t>2020-01-01</t>
   </si>
   <si>
-    <t>2020-12-31</t>
-  </si>
-  <si>
     <t>OBGD20</t>
   </si>
   <si>
@@ -1237,12 +1237,12 @@
     <t>FDJI1920</t>
   </si>
   <si>
+    <t>2020-03-31</t>
+  </si>
+  <si>
     <t>2019-12-17</t>
   </si>
   <si>
-    <t>2020-03-31</t>
-  </si>
-  <si>
     <t>ODJI20</t>
   </si>
   <si>
@@ -1291,24 +1291,24 @@
     <t>FLBN20</t>
   </si>
   <si>
+    <t>2020-11-13</t>
+  </si>
+  <si>
     <t>2020-08-05</t>
   </si>
   <si>
-    <t>2020-11-13</t>
-  </si>
-  <si>
     <t>OLBN20</t>
   </si>
   <si>
     <t>FLSO1920</t>
   </si>
   <si>
+    <t>2020-04-30</t>
+  </si>
+  <si>
     <t>2019-11-01</t>
   </si>
   <si>
-    <t>2020-04-30</t>
-  </si>
-  <si>
     <t>OLBR20</t>
   </si>
   <si>
@@ -1408,12 +1408,12 @@
     <t>2019</t>
   </si>
   <si>
+    <t>2019-12-31</t>
+  </si>
+  <si>
     <t>2019-01-01</t>
   </si>
   <si>
-    <t>2019-12-31</t>
-  </si>
-  <si>
     <t>RBGD19</t>
   </si>
   <si>
@@ -1522,12 +1522,12 @@
     <t>FZWE1920</t>
   </si>
   <si>
+    <t>2020-04-29</t>
+  </si>
+  <si>
     <t>2019-02-01</t>
   </si>
   <si>
-    <t>2020-04-29</t>
-  </si>
-  <si>
     <t>FZWE1820</t>
   </si>
   <si>
@@ -1540,12 +1540,12 @@
     <t>2018</t>
   </si>
   <si>
+    <t>2018-12-31</t>
+  </si>
+  <si>
     <t>2018-01-01</t>
   </si>
   <si>
-    <t>2018-12-31</t>
-  </si>
-  <si>
     <t>OBGD18</t>
   </si>
   <si>
@@ -1639,12 +1639,12 @@
     <t>HSYR18</t>
   </si>
   <si>
+    <t>2018-12-30</t>
+  </si>
+  <si>
     <t>2018-11-30</t>
   </si>
   <si>
-    <t>2018-12-30</t>
-  </si>
-  <si>
     <t>RSYR18</t>
   </si>
   <si>
@@ -1666,12 +1666,12 @@
     <t>2017</t>
   </si>
   <si>
+    <t>2017-12-31</t>
+  </si>
+  <si>
     <t>2017-01-01</t>
   </si>
   <si>
-    <t>2017-12-31</t>
-  </si>
-  <si>
     <t>HAFG17</t>
   </si>
   <si>
@@ -1714,12 +1714,12 @@
     <t>FDMA17</t>
   </si>
   <si>
+    <t>2017-12-29</t>
+  </si>
+  <si>
     <t>2017-09-28</t>
   </si>
   <si>
-    <t>2017-12-29</t>
-  </si>
-  <si>
     <t>OPRK17</t>
   </si>
   <si>
@@ -1741,24 +1741,24 @@
     <t>FKEN17</t>
   </si>
   <si>
+    <t>2017-11-30</t>
+  </si>
+  <si>
     <t>2017-02-10</t>
   </si>
   <si>
-    <t>2017-11-30</t>
-  </si>
-  <si>
     <t>HLBY17</t>
   </si>
   <si>
     <t>FMDG17</t>
   </si>
   <si>
+    <t>2017-06-20</t>
+  </si>
+  <si>
     <t>2017-03-20</t>
   </si>
   <si>
-    <t>2017-06-20</t>
-  </si>
-  <si>
     <t>HMLI17</t>
   </si>
   <si>
@@ -1768,12 +1768,12 @@
     <t>FMOZ17</t>
   </si>
   <si>
+    <t>2017-05-31</t>
+  </si>
+  <si>
     <t>2017-02-28</t>
   </si>
   <si>
-    <t>2017-05-31</t>
-  </si>
-  <si>
     <t>HMMR17</t>
   </si>
   <si>
@@ -1792,12 +1792,12 @@
     <t>FPER17</t>
   </si>
   <si>
+    <t>2017-10-31</t>
+  </si>
+  <si>
     <t>2017-04-01</t>
   </si>
   <si>
-    <t>2017-10-31</t>
-  </si>
-  <si>
     <t>HCOG17</t>
   </si>
   <si>
@@ -1843,12 +1843,12 @@
     <t>2016</t>
   </si>
   <si>
+    <t>2016-12-31</t>
+  </si>
+  <si>
     <t>2016-01-01</t>
   </si>
   <si>
-    <t>2016-12-31</t>
-  </si>
-  <si>
     <t>HAFG16</t>
   </si>
   <si>
@@ -1888,21 +1888,21 @@
     <t>FECU16</t>
   </si>
   <si>
+    <t>2016-10-31</t>
+  </si>
+  <si>
     <t>2016-04-16</t>
   </si>
   <si>
-    <t>2016-10-31</t>
-  </si>
-  <si>
     <t>FFJI16</t>
   </si>
   <si>
+    <t>2016-05-30</t>
+  </si>
+  <si>
     <t>2016-02-20</t>
   </si>
   <si>
-    <t>2016-05-30</t>
-  </si>
-  <si>
     <t>HGMB16</t>
   </si>
   <si>
@@ -1945,12 +1945,12 @@
     <t>FIRQ16</t>
   </si>
   <si>
+    <t>2016-10-01</t>
+  </si>
+  <si>
     <t>2016-07-20</t>
   </si>
   <si>
-    <t>2016-10-01</t>
-  </si>
-  <si>
     <t>HMMR16</t>
   </si>
   <si>
@@ -1999,12 +1999,12 @@
     <t>HZWE1617</t>
   </si>
   <si>
+    <t>2017-03-31</t>
+  </si>
+  <si>
     <t>2016-04-01</t>
   </si>
   <si>
-    <t>2017-03-31</t>
-  </si>
-  <si>
     <t>HAFG15</t>
   </si>
   <si>
@@ -2014,12 +2014,12 @@
     <t>2015</t>
   </si>
   <si>
+    <t>2015-12-31</t>
+  </si>
+  <si>
     <t>2015-01-01</t>
   </si>
   <si>
-    <t>2015-12-31</t>
-  </si>
-  <si>
     <t>HBFA15</t>
   </si>
   <si>
@@ -2047,12 +2047,12 @@
     <t>FGTM1415</t>
   </si>
   <si>
+    <t>2015-09-30</t>
+  </si>
+  <si>
     <t>2014-11-03</t>
   </si>
   <si>
-    <t>2015-09-30</t>
-  </si>
-  <si>
     <t>FHTI15</t>
   </si>
   <si>
@@ -2068,24 +2068,24 @@
     <t>FVUT15</t>
   </si>
   <si>
+    <t>2015-10-31</t>
+  </si>
+  <si>
     <t>2015-03-24</t>
   </si>
   <si>
-    <t>2015-10-31</t>
-  </si>
-  <si>
     <t>HIRQ15</t>
   </si>
   <si>
     <t>HLBY1415</t>
   </si>
   <si>
+    <t>2015-05-31</t>
+  </si>
+  <si>
     <t>2014-10-01</t>
   </si>
   <si>
-    <t>2015-05-31</t>
-  </si>
-  <si>
     <t>HMLI15</t>
   </si>
   <si>
@@ -2149,12 +2149,12 @@
     <t>2014</t>
   </si>
   <si>
+    <t>2014-12-31</t>
+  </si>
+  <si>
     <t>2014-01-01</t>
   </si>
   <si>
-    <t>2014-12-31</t>
-  </si>
-  <si>
     <t>HBFA1314</t>
   </si>
   <si>
@@ -2230,21 +2230,21 @@
     <t>FPHL1314</t>
   </si>
   <si>
+    <t>2014-04-22</t>
+  </si>
+  <si>
     <t>2013-10-22</t>
   </si>
   <si>
-    <t>2014-04-22</t>
-  </si>
-  <si>
     <t>SPHL1314</t>
   </si>
   <si>
+    <t>2014-11-07</t>
+  </si>
+  <si>
     <t>2013-11-08</t>
   </si>
   <si>
-    <t>2014-11-07</t>
-  </si>
-  <si>
     <t>HPHL1314</t>
   </si>
   <si>
@@ -2254,12 +2254,12 @@
     <t>HPHL1314a</t>
   </si>
   <si>
+    <t>2014-08-31</t>
+  </si>
+  <si>
     <t>2013-10-01</t>
   </si>
   <si>
-    <t>2014-08-31</t>
-  </si>
-  <si>
     <t>SCOD14</t>
   </si>
   <si>
@@ -2419,12 +2419,12 @@
     <t>2012</t>
   </si>
   <si>
+    <t>2012-12-31</t>
+  </si>
+  <si>
     <t>2012-01-01</t>
   </si>
   <si>
-    <t>2012-12-31</t>
-  </si>
-  <si>
     <t>CAFG1112</t>
   </si>
   <si>
@@ -2464,12 +2464,12 @@
     <t>FLSO1213</t>
   </si>
   <si>
+    <t>2013-03-25</t>
+  </si>
+  <si>
     <t>2012-09-18</t>
   </si>
   <si>
-    <t>2013-03-25</t>
-  </si>
-  <si>
     <t>CLBR12</t>
   </si>
   <si>
@@ -2509,12 +2509,12 @@
     <t>CSYR12</t>
   </si>
   <si>
+    <t>2012-12-05</t>
+  </si>
+  <si>
     <t>2012-06-05</t>
   </si>
   <si>
-    <t>2012-12-05</t>
-  </si>
-  <si>
     <t>CYEM12</t>
   </si>
   <si>
@@ -2557,12 +2557,12 @@
     <t>FSLV1112</t>
   </si>
   <si>
+    <t>2012-04-25</t>
+  </si>
+  <si>
     <t>2011-10-25</t>
   </si>
   <si>
-    <t>2012-04-25</t>
-  </si>
-  <si>
     <t>CHTI1011</t>
   </si>
   <si>
@@ -2581,33 +2581,33 @@
     <t>FNAM11</t>
   </si>
   <si>
+    <t>2011-10-11</t>
+  </si>
+  <si>
     <t>2011-04-11</t>
   </si>
   <si>
-    <t>2011-10-11</t>
-  </si>
-  <si>
     <t>FNIC1112</t>
   </si>
   <si>
+    <t>2012-04-26</t>
+  </si>
+  <si>
     <t>2011-10-27</t>
   </si>
   <si>
-    <t>2012-04-26</t>
-  </si>
-  <si>
     <t>CNER11</t>
   </si>
   <si>
     <t>FPAK1112</t>
   </si>
   <si>
+    <t>2012-06-30</t>
+  </si>
+  <si>
     <t>2011-09-15</t>
   </si>
   <si>
-    <t>2012-06-30</t>
-  </si>
-  <si>
     <t>FXLBYREG11</t>
   </si>
   <si>
@@ -2653,21 +2653,21 @@
     <t>2010</t>
   </si>
   <si>
+    <t>2010-12-31</t>
+  </si>
+  <si>
     <t>2010-01-01</t>
   </si>
   <si>
-    <t>2010-12-31</t>
-  </si>
-  <si>
     <t>OBFA1011</t>
   </si>
   <si>
+    <t>2011-01-31</t>
+  </si>
+  <si>
     <t>2010-08-01</t>
   </si>
   <si>
-    <t>2011-01-31</t>
-  </si>
-  <si>
     <t>CCAF10</t>
   </si>
   <si>
@@ -2680,30 +2680,30 @@
     <t>FSLV0910</t>
   </si>
   <si>
+    <t>2010-05-31</t>
+  </si>
+  <si>
     <t>2009-11-01</t>
   </si>
   <si>
-    <t>2010-05-31</t>
-  </si>
-  <si>
     <t>FGTM10</t>
   </si>
   <si>
+    <t>2010-12-09</t>
+  </si>
+  <si>
     <t>2010-06-10</t>
   </si>
   <si>
-    <t>2010-12-09</t>
-  </si>
-  <si>
     <t>CGTM10</t>
   </si>
   <si>
+    <t>2010-08-11</t>
+  </si>
+  <si>
     <t>2010-02-12</t>
   </si>
   <si>
-    <t>2010-08-11</t>
-  </si>
-  <si>
     <t>FHTI10</t>
   </si>
   <si>
@@ -2722,12 +2722,12 @@
     <t>FKGZ1011</t>
   </si>
   <si>
+    <t>2011-06-30</t>
+  </si>
+  <si>
     <t>2010-06-01</t>
   </si>
   <si>
-    <t>2011-06-30</t>
-  </si>
-  <si>
     <t>CMNG1011</t>
   </si>
   <si>
@@ -2797,21 +2797,21 @@
     <t>2009</t>
   </si>
   <si>
+    <t>2009-12-31</t>
+  </si>
+  <si>
     <t>2009-01-01</t>
   </si>
   <si>
-    <t>2009-12-31</t>
-  </si>
-  <si>
     <t>FBFA0910</t>
   </si>
   <si>
+    <t>2010-03-09</t>
+  </si>
+  <si>
     <t>2009-09-10</t>
   </si>
   <si>
-    <t>2010-03-09</t>
-  </si>
-  <si>
     <t>CCAF09</t>
   </si>
   <si>
@@ -2851,21 +2851,21 @@
     <t>FMDG09</t>
   </si>
   <si>
+    <t>2009-10-31</t>
+  </si>
+  <si>
     <t>2009-04-01</t>
   </si>
   <si>
-    <t>2009-10-31</t>
-  </si>
-  <si>
     <t>FNAM09</t>
   </si>
   <si>
+    <t>2009-09-30</t>
+  </si>
+  <si>
     <t>2009-03-20</t>
   </si>
   <si>
-    <t>2009-09-30</t>
-  </si>
-  <si>
     <t>ONPL09</t>
   </si>
   <si>
@@ -2878,12 +2878,12 @@
     <t>FPHL0910</t>
   </si>
   <si>
+    <t>2010-03-31</t>
+  </si>
+  <si>
     <t>2009-10-03</t>
   </si>
   <si>
-    <t>2010-03-31</t>
-  </si>
-  <si>
     <t>CSOM09</t>
   </si>
   <si>
@@ -2896,12 +2896,12 @@
     <t>OSYR0910</t>
   </si>
   <si>
+    <t>2010-06-14</t>
+  </si>
+  <si>
     <t>2009-07-15</t>
   </si>
   <si>
-    <t>2010-06-14</t>
-  </si>
-  <si>
     <t>OTJK09</t>
   </si>
   <si>
@@ -2941,21 +2941,21 @@
     <t>2008</t>
   </si>
   <si>
+    <t>2008-06-30</t>
+  </si>
+  <si>
     <t>2008-02-01</t>
   </si>
   <si>
-    <t>2008-06-30</t>
-  </si>
-  <si>
     <t>OAFG0809</t>
   </si>
   <si>
+    <t>2009-06-30</t>
+  </si>
+  <si>
     <t>2008-07-01</t>
   </si>
   <si>
-    <t>2009-06-30</t>
-  </si>
-  <si>
     <t>FBOL08</t>
   </si>
   <si>
@@ -2965,12 +2965,12 @@
     <t>CCAF08</t>
   </si>
   <si>
+    <t>2008-12-31</t>
+  </si>
+  <si>
     <t>2008-01-01</t>
   </si>
   <si>
-    <t>2008-12-31</t>
-  </si>
-  <si>
     <t>CTCD08</t>
   </si>
   <si>
@@ -2986,21 +2986,21 @@
     <t>ODJI0809</t>
   </si>
   <si>
+    <t>2009-02-28</t>
+  </si>
+  <si>
     <t>2008-08-01</t>
   </si>
   <si>
-    <t>2009-02-28</t>
-  </si>
-  <si>
     <t>FGEO0809</t>
   </si>
   <si>
+    <t>2009-02-09</t>
+  </si>
+  <si>
     <t>2008-08-09</t>
   </si>
   <si>
-    <t>2009-02-09</t>
-  </si>
-  <si>
     <t>FHTI0809</t>
   </si>
   <si>
@@ -3010,12 +3010,12 @@
     <t>FHND0809</t>
   </si>
   <si>
+    <t>2009-04-30</t>
+  </si>
+  <si>
     <t>2008-11-01</t>
   </si>
   <si>
-    <t>2009-04-30</t>
-  </si>
-  <si>
     <t>CIRQ08</t>
   </si>
   <si>
@@ -3025,12 +3025,12 @@
     <t>FKGZ0809</t>
   </si>
   <si>
+    <t>2009-05-31</t>
+  </si>
+  <si>
     <t>2008-12-01</t>
   </si>
   <si>
-    <t>2009-05-31</t>
-  </si>
-  <si>
     <t>OLAO0809</t>
   </si>
   <si>
@@ -3052,12 +3052,12 @@
     <t>FMMR08</t>
   </si>
   <si>
+    <t>2008-11-30</t>
+  </si>
+  <si>
     <t>2008-05-01</t>
   </si>
   <si>
-    <t>2008-11-30</t>
-  </si>
-  <si>
     <t>ONPL08</t>
   </si>
   <si>
@@ -3115,30 +3115,30 @@
     <t>2007</t>
   </si>
   <si>
+    <t>2007-08-21</t>
+  </si>
+  <si>
     <t>2007-02-22</t>
   </si>
   <si>
-    <t>2007-08-21</t>
-  </si>
-  <si>
     <t>FBFA0708</t>
   </si>
   <si>
+    <t>2008-01-31</t>
+  </si>
+  <si>
     <t>2007-11-01</t>
   </si>
   <si>
-    <t>2008-01-31</t>
-  </si>
-  <si>
     <t>CBDI07</t>
   </si>
   <si>
+    <t>2007-12-31</t>
+  </si>
+  <si>
     <t>2007-01-01</t>
   </si>
   <si>
-    <t>2007-12-31</t>
-  </si>
-  <si>
     <t>CCAF07</t>
   </si>
   <si>
@@ -3160,12 +3160,12 @@
     <t>FGHA0708</t>
   </si>
   <si>
+    <t>2008-03-31</t>
+  </si>
+  <si>
     <t>2007-09-01</t>
   </si>
   <si>
-    <t>2008-03-31</t>
-  </si>
-  <si>
     <t>CXGLR07</t>
   </si>
   <si>
@@ -3178,75 +3178,75 @@
     <t>FPRK07</t>
   </si>
   <si>
+    <t>2007-11-30</t>
+  </si>
+  <si>
     <t>2007-08-28</t>
   </si>
   <si>
-    <t>2007-11-30</t>
-  </si>
-  <si>
     <t>OLBN07</t>
   </si>
   <si>
+    <t>2007-09-03</t>
+  </si>
+  <si>
     <t>2007-06-04</t>
   </si>
   <si>
-    <t>2007-09-03</t>
-  </si>
-  <si>
     <t>FLSO0708</t>
   </si>
   <si>
+    <t>2008-01-28</t>
+  </si>
+  <si>
     <t>2007-07-28</t>
   </si>
   <si>
-    <t>2008-01-28</t>
-  </si>
-  <si>
     <t>CLBR07</t>
   </si>
   <si>
     <t>FMDG07</t>
   </si>
   <si>
+    <t>2007-09-15</t>
+  </si>
+  <si>
     <t>2007-03-15</t>
   </si>
   <si>
-    <t>2007-09-15</t>
-  </si>
-  <si>
     <t>FMOZ07</t>
   </si>
   <si>
+    <t>2007-06-30</t>
+  </si>
+  <si>
     <t>2007-03-01</t>
   </si>
   <si>
-    <t>2007-06-30</t>
-  </si>
-  <si>
     <t>ONPL07</t>
   </si>
   <si>
     <t>FNIC0708</t>
   </si>
   <si>
+    <t>2008-02-28</t>
+  </si>
+  <si>
     <t>2007-09-07</t>
   </si>
   <si>
-    <t>2008-02-28</t>
-  </si>
-  <si>
     <t>ORUS07</t>
   </si>
   <si>
     <t>FPAK07</t>
   </si>
   <si>
+    <t>2007-10-31</t>
+  </si>
+  <si>
     <t>2007-07-15</t>
   </si>
   <si>
-    <t>2007-10-31</t>
-  </si>
-  <si>
     <t>FPER0708</t>
   </si>
   <si>
@@ -3283,12 +3283,12 @@
     <t>FSWZ0708</t>
   </si>
   <si>
+    <t>2008-01-20</t>
+  </si>
+  <si>
     <t>2007-07-20</t>
   </si>
   <si>
-    <t>2008-01-20</t>
-  </si>
-  <si>
     <t>CTLS07</t>
   </si>
   <si>
@@ -3319,12 +3319,12 @@
     <t>2006</t>
   </si>
   <si>
+    <t>2006-12-31</t>
+  </si>
+  <si>
     <t>2006-07-01</t>
   </si>
   <si>
-    <t>2006-12-31</t>
-  </si>
-  <si>
     <t>CBDI06</t>
   </si>
   <si>
@@ -3349,21 +3349,21 @@
     <t>OETH06a</t>
   </si>
   <si>
+    <t>2006-11-25</t>
+  </si>
+  <si>
     <t>2006-08-25</t>
   </si>
   <si>
-    <t>2006-11-25</t>
-  </si>
-  <si>
     <t>OETH0607</t>
   </si>
   <si>
+    <t>2007-01-22</t>
+  </si>
+  <si>
     <t>2006-11-23</t>
   </si>
   <si>
-    <t>2007-01-22</t>
-  </si>
-  <si>
     <t>CXGLR06</t>
   </si>
   <si>
@@ -3373,12 +3373,12 @@
     <t>FGNB06</t>
   </si>
   <si>
+    <t>2006-11-30</t>
+  </si>
+  <si>
     <t>2006-05-01</t>
   </si>
   <si>
-    <t>2006-11-30</t>
-  </si>
-  <si>
     <t>CXHAF06</t>
   </si>
   <si>
@@ -3388,12 +3388,12 @@
     <t>FKEN0607</t>
   </si>
   <si>
+    <t>2007-04-15</t>
+  </si>
+  <si>
     <t>2006-10-16</t>
   </si>
   <si>
-    <t>2007-04-15</t>
-  </si>
-  <si>
     <t>FKEN06</t>
   </si>
   <si>
@@ -3403,12 +3403,12 @@
     <t>FLBN06</t>
   </si>
   <si>
+    <t>2006-10-23</t>
+  </si>
+  <si>
     <t>2006-07-24</t>
   </si>
   <si>
-    <t>2006-10-23</t>
-  </si>
-  <si>
     <t>CLBR06</t>
   </si>
   <si>
@@ -3436,12 +3436,12 @@
     <t>FSOM0607</t>
   </si>
   <si>
+    <t>2007-03-05</t>
+  </si>
+  <si>
     <t>2006-12-05</t>
   </si>
   <si>
-    <t>2007-03-05</t>
-  </si>
-  <si>
     <t>OLKA06</t>
   </si>
   <si>
@@ -3481,30 +3481,30 @@
     <t>2005</t>
   </si>
   <si>
+    <t>2005-06-30</t>
+  </si>
+  <si>
     <t>2005-04-01</t>
   </si>
   <si>
-    <t>2005-06-30</t>
-  </si>
-  <si>
     <t>FBEN05</t>
   </si>
   <si>
+    <t>2005-10-31</t>
+  </si>
+  <si>
     <t>2005-05-01</t>
   </si>
   <si>
-    <t>2005-10-31</t>
-  </si>
-  <si>
     <t>CBDI05</t>
   </si>
   <si>
+    <t>2005-12-31</t>
+  </si>
+  <si>
     <t>2005-01-01</t>
   </si>
   <si>
-    <t>2005-12-31</t>
-  </si>
-  <si>
     <t>CCAF05</t>
   </si>
   <si>
@@ -3547,12 +3547,12 @@
     <t>FGUY05</t>
   </si>
   <si>
+    <t>2005-08-01</t>
+  </si>
+  <si>
     <t>2005-02-01</t>
   </si>
   <si>
-    <t>2005-08-01</t>
-  </si>
-  <si>
     <t>FXINDTSU05</t>
   </si>
   <si>
@@ -3565,12 +3565,12 @@
     <t>FNER05</t>
   </si>
   <si>
+    <t>2005-09-30</t>
+  </si>
+  <si>
     <t>2005-06-01</t>
   </si>
   <si>
-    <t>2005-09-30</t>
-  </si>
-  <si>
     <t>CCOG05</t>
   </si>
   <si>
@@ -3580,24 +3580,24 @@
     <t>R0506</t>
   </si>
   <si>
+    <t>2006-05-31</t>
+  </si>
+  <si>
     <t>2005-11-01</t>
   </si>
   <si>
-    <t>2006-05-31</t>
-  </si>
-  <si>
     <t>OSDN05</t>
   </si>
   <si>
     <t>FXSASIA0506</t>
   </si>
   <si>
+    <t>2006-04-10</t>
+  </si>
+  <si>
     <t>2005-10-11</t>
   </si>
   <si>
-    <t>2006-04-10</t>
-  </si>
-  <si>
     <t>CSDN05</t>
   </si>
   <si>
@@ -3619,12 +3619,12 @@
     <t>2004</t>
   </si>
   <si>
+    <t>2004-12-31</t>
+  </si>
+  <si>
     <t>2004-09-01</t>
   </si>
   <si>
-    <t>2004-12-31</t>
-  </si>
-  <si>
     <t>CAGO04</t>
   </si>
   <si>
@@ -3634,21 +3634,21 @@
     <t>FBGD0405</t>
   </si>
   <si>
+    <t>2005-01-31</t>
+  </si>
+  <si>
     <t>2004-08-01</t>
   </si>
   <si>
-    <t>2005-01-31</t>
-  </si>
-  <si>
     <t>FBOL0405</t>
   </si>
   <si>
+    <t>2005-05-31</t>
+  </si>
+  <si>
     <t>2004-11-01</t>
   </si>
   <si>
-    <t>2005-05-31</t>
-  </si>
-  <si>
     <t>CBDI04</t>
   </si>
   <si>
@@ -3724,21 +3724,21 @@
     <t>FMDG04</t>
   </si>
   <si>
+    <t>2004-06-19</t>
+  </si>
+  <si>
     <t>2004-03-19</t>
   </si>
   <si>
-    <t>2004-06-19</t>
-  </si>
-  <si>
     <t>FPHL0405</t>
   </si>
   <si>
+    <t>2005-03-15</t>
+  </si>
+  <si>
     <t>2004-12-15</t>
   </si>
   <si>
-    <t>2005-03-15</t>
-  </si>
-  <si>
     <t>CSLE04</t>
   </si>
   <si>
@@ -3772,12 +3772,12 @@
     <t>2003</t>
   </si>
   <si>
+    <t>2003-12-31</t>
+  </si>
+  <si>
     <t>2003-01-01</t>
   </si>
   <si>
-    <t>2003-12-31</t>
-  </si>
-  <si>
     <t>CAGO03</t>
   </si>
   <si>
@@ -3790,12 +3790,12 @@
     <t>FCAF03</t>
   </si>
   <si>
+    <t>2003-06-30</t>
+  </si>
+  <si>
     <t>2003-04-01</t>
   </si>
   <si>
-    <t>2003-06-30</t>
-  </si>
-  <si>
     <t>CRUS03</t>
   </si>
   <si>
@@ -3808,12 +3808,12 @@
     <t>RCIV0203</t>
   </si>
   <si>
+    <t>2003-01-31</t>
+  </si>
+  <si>
     <t>2002-11-01</t>
   </si>
   <si>
-    <t>2003-01-31</t>
-  </si>
-  <si>
     <t>CCIV03</t>
   </si>
   <si>
@@ -3841,21 +3841,21 @@
     <t>OHTI03</t>
   </si>
   <si>
+    <t>2003-08-31</t>
+  </si>
+  <si>
     <t>2003-03-01</t>
   </si>
   <si>
-    <t>2003-08-31</t>
-  </si>
-  <si>
     <t>CLSO0304</t>
   </si>
   <si>
+    <t>2004-06-30</t>
+  </si>
+  <si>
     <t>2003-07-01</t>
   </si>
   <si>
-    <t>2004-06-30</t>
-  </si>
-  <si>
     <t>CMWI03</t>
   </si>
   <si>
@@ -3916,12 +3916,12 @@
     <t>2002</t>
   </si>
   <si>
+    <t>2002-12-31</t>
+  </si>
+  <si>
     <t>2001-10-01</t>
   </si>
   <si>
-    <t>2002-12-31</t>
-  </si>
-  <si>
     <t>CAGO02</t>
   </si>
   <si>
@@ -4024,12 +4024,12 @@
     <t>2001</t>
   </si>
   <si>
+    <t>2001-09-30</t>
+  </si>
+  <si>
     <t>2001-01-01</t>
   </si>
   <si>
-    <t>2001-09-30</t>
-  </si>
-  <si>
     <t>CAGO01</t>
   </si>
   <si>
@@ -4108,10 +4108,10 @@
     <t>2000</t>
   </si>
   <si>
+    <t>2000-12-31</t>
+  </si>
+  <si>
     <t>2000-01-01</t>
-  </si>
-  <si>
-    <t>2000-12-31</t>
   </si>
   <si>
     <t>CBDI00</t>
@@ -4723,10 +4723,10 @@
         <v>9</v>
       </c>
       <c r="E11" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F11" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -4863,10 +4863,10 @@
         <v>9</v>
       </c>
       <c r="E18" t="s">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="F18" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -5023,10 +5023,10 @@
         <v>9</v>
       </c>
       <c r="E26" t="s">
+        <v>34</v>
+      </c>
+      <c r="F26" t="s">
         <v>44</v>
-      </c>
-      <c r="F26" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -5223,10 +5223,10 @@
         <v>9</v>
       </c>
       <c r="E36" t="s">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="F36" t="s">
-        <v>55</v>
+        <v>11</v>
       </c>
     </row>
     <row r="37" spans="1:6">
@@ -5303,10 +5303,10 @@
         <v>58</v>
       </c>
       <c r="E40" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="F40" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="41" spans="1:6">
@@ -5383,10 +5383,10 @@
         <v>58</v>
       </c>
       <c r="E44" t="s">
+        <v>59</v>
+      </c>
+      <c r="F44" t="s">
         <v>69</v>
-      </c>
-      <c r="F44" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="45" spans="1:6">
@@ -5523,10 +5523,10 @@
         <v>58</v>
       </c>
       <c r="E51" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="F51" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="52" spans="1:6">
@@ -5543,10 +5543,10 @@
         <v>58</v>
       </c>
       <c r="E52" t="s">
-        <v>59</v>
+        <v>78</v>
       </c>
       <c r="F52" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
     </row>
     <row r="53" spans="1:6">
@@ -5583,10 +5583,10 @@
         <v>58</v>
       </c>
       <c r="E54" t="s">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="F54" t="s">
-        <v>81</v>
+        <v>60</v>
       </c>
     </row>
     <row r="55" spans="1:6">
@@ -5623,10 +5623,10 @@
         <v>58</v>
       </c>
       <c r="E56" t="s">
-        <v>59</v>
+        <v>84</v>
       </c>
       <c r="F56" t="s">
-        <v>84</v>
+        <v>60</v>
       </c>
     </row>
     <row r="57" spans="1:6">
@@ -5643,10 +5643,10 @@
         <v>58</v>
       </c>
       <c r="E57" t="s">
+        <v>59</v>
+      </c>
+      <c r="F57" t="s">
         <v>86</v>
-      </c>
-      <c r="F57" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="58" spans="1:6">
@@ -5723,10 +5723,10 @@
         <v>58</v>
       </c>
       <c r="E61" t="s">
+        <v>59</v>
+      </c>
+      <c r="F61" t="s">
         <v>91</v>
-      </c>
-      <c r="F61" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="62" spans="1:6">
@@ -5743,10 +5743,10 @@
         <v>58</v>
       </c>
       <c r="E62" t="s">
-        <v>59</v>
+        <v>93</v>
       </c>
       <c r="F62" t="s">
-        <v>93</v>
+        <v>60</v>
       </c>
     </row>
     <row r="63" spans="1:6">
@@ -5943,10 +5943,10 @@
         <v>58</v>
       </c>
       <c r="E72" t="s">
+        <v>59</v>
+      </c>
+      <c r="F72" t="s">
         <v>104</v>
-      </c>
-      <c r="F72" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="73" spans="1:6">
@@ -6103,10 +6103,10 @@
         <v>58</v>
       </c>
       <c r="E80" t="s">
-        <v>59</v>
+        <v>84</v>
       </c>
       <c r="F80" t="s">
-        <v>84</v>
+        <v>60</v>
       </c>
     </row>
     <row r="81" spans="1:6">
@@ -6123,10 +6123,10 @@
         <v>58</v>
       </c>
       <c r="E81" t="s">
-        <v>59</v>
+        <v>84</v>
       </c>
       <c r="F81" t="s">
-        <v>84</v>
+        <v>60</v>
       </c>
     </row>
     <row r="82" spans="1:6">
@@ -6143,10 +6143,10 @@
         <v>58</v>
       </c>
       <c r="E82" t="s">
+        <v>59</v>
+      </c>
+      <c r="F82" t="s">
         <v>115</v>
-      </c>
-      <c r="F82" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="83" spans="1:6">
@@ -6183,10 +6183,10 @@
         <v>58</v>
       </c>
       <c r="E84" t="s">
-        <v>59</v>
+        <v>84</v>
       </c>
       <c r="F84" t="s">
-        <v>84</v>
+        <v>60</v>
       </c>
     </row>
     <row r="85" spans="1:6">
@@ -6203,10 +6203,10 @@
         <v>58</v>
       </c>
       <c r="E85" t="s">
-        <v>59</v>
+        <v>78</v>
       </c>
       <c r="F85" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
     </row>
     <row r="86" spans="1:6">
@@ -6263,10 +6263,10 @@
         <v>120</v>
       </c>
       <c r="E88" t="s">
+        <v>121</v>
+      </c>
+      <c r="F88" t="s">
         <v>125</v>
-      </c>
-      <c r="F88" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="89" spans="1:6">
@@ -6303,10 +6303,10 @@
         <v>120</v>
       </c>
       <c r="E90" t="s">
+        <v>121</v>
+      </c>
+      <c r="F90" t="s">
         <v>128</v>
-      </c>
-      <c r="F90" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="91" spans="1:6">
@@ -6443,10 +6443,10 @@
         <v>120</v>
       </c>
       <c r="E97" t="s">
+        <v>121</v>
+      </c>
+      <c r="F97" t="s">
         <v>136</v>
-      </c>
-      <c r="F97" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="98" spans="1:6">
@@ -6523,10 +6523,10 @@
         <v>120</v>
       </c>
       <c r="E101" t="s">
+        <v>121</v>
+      </c>
+      <c r="F101" t="s">
         <v>141</v>
-      </c>
-      <c r="F101" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="102" spans="1:6">
@@ -6543,10 +6543,10 @@
         <v>120</v>
       </c>
       <c r="E102" t="s">
+        <v>121</v>
+      </c>
+      <c r="F102" t="s">
         <v>141</v>
-      </c>
-      <c r="F102" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="103" spans="1:6">
@@ -6563,10 +6563,10 @@
         <v>120</v>
       </c>
       <c r="E103" t="s">
-        <v>121</v>
+        <v>144</v>
       </c>
       <c r="F103" t="s">
-        <v>144</v>
+        <v>122</v>
       </c>
     </row>
     <row r="104" spans="1:6">
@@ -6583,10 +6583,10 @@
         <v>120</v>
       </c>
       <c r="E104" t="s">
-        <v>121</v>
+        <v>146</v>
       </c>
       <c r="F104" t="s">
-        <v>146</v>
+        <v>122</v>
       </c>
     </row>
     <row r="105" spans="1:6">
@@ -6603,10 +6603,10 @@
         <v>120</v>
       </c>
       <c r="E105" t="s">
+        <v>121</v>
+      </c>
+      <c r="F105" t="s">
         <v>148</v>
-      </c>
-      <c r="F105" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="106" spans="1:6">
@@ -6643,10 +6643,10 @@
         <v>120</v>
       </c>
       <c r="E107" t="s">
+        <v>146</v>
+      </c>
+      <c r="F107" t="s">
         <v>151</v>
-      </c>
-      <c r="F107" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="108" spans="1:6">
@@ -6663,10 +6663,10 @@
         <v>120</v>
       </c>
       <c r="E108" t="s">
+        <v>121</v>
+      </c>
+      <c r="F108" t="s">
         <v>153</v>
-      </c>
-      <c r="F108" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="109" spans="1:6">
@@ -6723,10 +6723,10 @@
         <v>120</v>
       </c>
       <c r="E111" t="s">
+        <v>121</v>
+      </c>
+      <c r="F111" t="s">
         <v>157</v>
-      </c>
-      <c r="F111" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="112" spans="1:6">
@@ -6783,10 +6783,10 @@
         <v>120</v>
       </c>
       <c r="E114" t="s">
+        <v>121</v>
+      </c>
+      <c r="F114" t="s">
         <v>161</v>
-      </c>
-      <c r="F114" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="115" spans="1:6">
@@ -6903,10 +6903,10 @@
         <v>120</v>
       </c>
       <c r="E120" t="s">
+        <v>121</v>
+      </c>
+      <c r="F120" t="s">
         <v>136</v>
-      </c>
-      <c r="F120" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="121" spans="1:6">
@@ -7163,10 +7163,10 @@
         <v>120</v>
       </c>
       <c r="E133" t="s">
+        <v>121</v>
+      </c>
+      <c r="F133" t="s">
         <v>181</v>
-      </c>
-      <c r="F133" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="134" spans="1:6">
@@ -7203,10 +7203,10 @@
         <v>120</v>
       </c>
       <c r="E135" t="s">
+        <v>121</v>
+      </c>
+      <c r="F135" t="s">
         <v>184</v>
-      </c>
-      <c r="F135" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="136" spans="1:6">
@@ -7223,10 +7223,10 @@
         <v>120</v>
       </c>
       <c r="E136" t="s">
+        <v>121</v>
+      </c>
+      <c r="F136" t="s">
         <v>184</v>
-      </c>
-      <c r="F136" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="137" spans="1:6">
@@ -7403,10 +7403,10 @@
         <v>187</v>
       </c>
       <c r="E145" t="s">
+        <v>188</v>
+      </c>
+      <c r="F145" t="s">
         <v>198</v>
-      </c>
-      <c r="F145" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="146" spans="1:6">
@@ -7563,10 +7563,10 @@
         <v>187</v>
       </c>
       <c r="E153" t="s">
+        <v>188</v>
+      </c>
+      <c r="F153" t="s">
         <v>207</v>
-      </c>
-      <c r="F153" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="154" spans="1:6">
@@ -7743,10 +7743,10 @@
         <v>187</v>
       </c>
       <c r="E162" t="s">
-        <v>188</v>
+        <v>214</v>
       </c>
       <c r="F162" t="s">
-        <v>215</v>
+        <v>189</v>
       </c>
     </row>
     <row r="163" spans="1:6">
@@ -7763,10 +7763,10 @@
         <v>187</v>
       </c>
       <c r="E163" t="s">
-        <v>188</v>
+        <v>211</v>
       </c>
       <c r="F163" t="s">
-        <v>212</v>
+        <v>189</v>
       </c>
     </row>
     <row r="164" spans="1:6">
@@ -7983,10 +7983,10 @@
         <v>187</v>
       </c>
       <c r="E174" t="s">
+        <v>211</v>
+      </c>
+      <c r="F174" t="s">
         <v>235</v>
-      </c>
-      <c r="F174" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="175" spans="1:6">
@@ -8023,10 +8023,10 @@
         <v>187</v>
       </c>
       <c r="E176" t="s">
+        <v>211</v>
+      </c>
+      <c r="F176" t="s">
         <v>238</v>
-      </c>
-      <c r="F176" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="177" spans="1:6">
@@ -8443,10 +8443,10 @@
         <v>247</v>
       </c>
       <c r="E197" t="s">
-        <v>264</v>
+        <v>248</v>
       </c>
       <c r="F197" t="s">
-        <v>249</v>
+        <v>265</v>
       </c>
     </row>
     <row r="198" spans="1:6">
@@ -8523,10 +8523,10 @@
         <v>247</v>
       </c>
       <c r="E201" t="s">
-        <v>248</v>
+        <v>271</v>
       </c>
       <c r="F201" t="s">
-        <v>271</v>
+        <v>249</v>
       </c>
     </row>
     <row r="202" spans="1:6">
@@ -8763,10 +8763,10 @@
         <v>247</v>
       </c>
       <c r="E213" t="s">
+        <v>248</v>
+      </c>
+      <c r="F213" t="s">
         <v>288</v>
-      </c>
-      <c r="F213" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="214" spans="1:6">
@@ -8783,10 +8783,10 @@
         <v>247</v>
       </c>
       <c r="E214" t="s">
+        <v>290</v>
+      </c>
+      <c r="F214" t="s">
         <v>288</v>
-      </c>
-      <c r="F214" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="215" spans="1:6">
@@ -8963,10 +8963,10 @@
         <v>247</v>
       </c>
       <c r="E223" t="s">
+        <v>248</v>
+      </c>
+      <c r="F223" t="s">
         <v>302</v>
-      </c>
-      <c r="F223" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="224" spans="1:6">
@@ -9063,10 +9063,10 @@
         <v>247</v>
       </c>
       <c r="E228" t="s">
+        <v>248</v>
+      </c>
+      <c r="F228" t="s">
         <v>308</v>
-      </c>
-      <c r="F228" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="229" spans="1:6">
@@ -9103,10 +9103,10 @@
         <v>247</v>
       </c>
       <c r="E230" t="s">
+        <v>311</v>
+      </c>
+      <c r="F230" t="s">
         <v>308</v>
-      </c>
-      <c r="F230" t="s">
-        <v>311</v>
       </c>
     </row>
     <row r="231" spans="1:6">
@@ -9183,10 +9183,10 @@
         <v>315</v>
       </c>
       <c r="E234" t="s">
+        <v>316</v>
+      </c>
+      <c r="F234" t="s">
         <v>319</v>
-      </c>
-      <c r="F234" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="235" spans="1:6">
@@ -9203,10 +9203,10 @@
         <v>315</v>
       </c>
       <c r="E235" t="s">
+        <v>316</v>
+      </c>
+      <c r="F235" t="s">
         <v>319</v>
-      </c>
-      <c r="F235" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="236" spans="1:6">
@@ -9223,10 +9223,10 @@
         <v>315</v>
       </c>
       <c r="E236" t="s">
+        <v>316</v>
+      </c>
+      <c r="F236" t="s">
         <v>319</v>
-      </c>
-      <c r="F236" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="237" spans="1:6">
@@ -9243,10 +9243,10 @@
         <v>315</v>
       </c>
       <c r="E237" t="s">
+        <v>316</v>
+      </c>
+      <c r="F237" t="s">
         <v>319</v>
-      </c>
-      <c r="F237" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="238" spans="1:6">
@@ -9263,10 +9263,10 @@
         <v>315</v>
       </c>
       <c r="E238" t="s">
+        <v>316</v>
+      </c>
+      <c r="F238" t="s">
         <v>319</v>
-      </c>
-      <c r="F238" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="239" spans="1:6">
@@ -9283,10 +9283,10 @@
         <v>315</v>
       </c>
       <c r="E239" t="s">
+        <v>316</v>
+      </c>
+      <c r="F239" t="s">
         <v>319</v>
-      </c>
-      <c r="F239" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="240" spans="1:6">
@@ -9303,10 +9303,10 @@
         <v>315</v>
       </c>
       <c r="E240" t="s">
+        <v>316</v>
+      </c>
+      <c r="F240" t="s">
         <v>319</v>
-      </c>
-      <c r="F240" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="241" spans="1:6">
@@ -9323,10 +9323,10 @@
         <v>315</v>
       </c>
       <c r="E241" t="s">
+        <v>316</v>
+      </c>
+      <c r="F241" t="s">
         <v>319</v>
-      </c>
-      <c r="F241" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="242" spans="1:6">
@@ -9343,10 +9343,10 @@
         <v>315</v>
       </c>
       <c r="E242" t="s">
+        <v>316</v>
+      </c>
+      <c r="F242" t="s">
         <v>319</v>
-      </c>
-      <c r="F242" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="243" spans="1:6">
@@ -9363,10 +9363,10 @@
         <v>315</v>
       </c>
       <c r="E243" t="s">
+        <v>316</v>
+      </c>
+      <c r="F243" t="s">
         <v>319</v>
-      </c>
-      <c r="F243" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="244" spans="1:6">
@@ -9383,10 +9383,10 @@
         <v>315</v>
       </c>
       <c r="E244" t="s">
+        <v>316</v>
+      </c>
+      <c r="F244" t="s">
         <v>319</v>
-      </c>
-      <c r="F244" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="245" spans="1:6">
@@ -9403,10 +9403,10 @@
         <v>315</v>
       </c>
       <c r="E245" t="s">
+        <v>316</v>
+      </c>
+      <c r="F245" t="s">
         <v>331</v>
-      </c>
-      <c r="F245" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="246" spans="1:6">
@@ -9423,10 +9423,10 @@
         <v>315</v>
       </c>
       <c r="E246" t="s">
+        <v>248</v>
+      </c>
+      <c r="F246" t="s">
         <v>331</v>
-      </c>
-      <c r="F246" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="247" spans="1:6">
@@ -9463,10 +9463,10 @@
         <v>315</v>
       </c>
       <c r="E248" t="s">
+        <v>316</v>
+      </c>
+      <c r="F248" t="s">
         <v>319</v>
-      </c>
-      <c r="F248" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="249" spans="1:6">
@@ -9483,10 +9483,10 @@
         <v>315</v>
       </c>
       <c r="E249" t="s">
+        <v>316</v>
+      </c>
+      <c r="F249" t="s">
         <v>331</v>
-      </c>
-      <c r="F249" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="250" spans="1:6">
@@ -9503,10 +9503,10 @@
         <v>315</v>
       </c>
       <c r="E250" t="s">
+        <v>248</v>
+      </c>
+      <c r="F250" t="s">
         <v>331</v>
-      </c>
-      <c r="F250" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="251" spans="1:6">
@@ -9543,10 +9543,10 @@
         <v>315</v>
       </c>
       <c r="E252" t="s">
+        <v>316</v>
+      </c>
+      <c r="F252" t="s">
         <v>319</v>
-      </c>
-      <c r="F252" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="253" spans="1:6">
@@ -9583,10 +9583,10 @@
         <v>315</v>
       </c>
       <c r="E254" t="s">
+        <v>316</v>
+      </c>
+      <c r="F254" t="s">
         <v>331</v>
-      </c>
-      <c r="F254" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="255" spans="1:6">
@@ -9603,10 +9603,10 @@
         <v>315</v>
       </c>
       <c r="E255" t="s">
+        <v>248</v>
+      </c>
+      <c r="F255" t="s">
         <v>331</v>
-      </c>
-      <c r="F255" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="256" spans="1:6">
@@ -9623,10 +9623,10 @@
         <v>315</v>
       </c>
       <c r="E256" t="s">
+        <v>316</v>
+      </c>
+      <c r="F256" t="s">
         <v>319</v>
-      </c>
-      <c r="F256" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="257" spans="1:6">
@@ -9643,10 +9643,10 @@
         <v>315</v>
       </c>
       <c r="E257" t="s">
+        <v>316</v>
+      </c>
+      <c r="F257" t="s">
         <v>350</v>
-      </c>
-      <c r="F257" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="258" spans="1:6">
@@ -9683,10 +9683,10 @@
         <v>315</v>
       </c>
       <c r="E259" t="s">
+        <v>316</v>
+      </c>
+      <c r="F259" t="s">
         <v>319</v>
-      </c>
-      <c r="F259" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="260" spans="1:6">
@@ -9703,10 +9703,10 @@
         <v>315</v>
       </c>
       <c r="E260" t="s">
+        <v>276</v>
+      </c>
+      <c r="F260" t="s">
         <v>319</v>
-      </c>
-      <c r="F260" t="s">
-        <v>277</v>
       </c>
     </row>
     <row r="261" spans="1:6">
@@ -9723,10 +9723,10 @@
         <v>315</v>
       </c>
       <c r="E261" t="s">
+        <v>316</v>
+      </c>
+      <c r="F261" t="s">
         <v>319</v>
-      </c>
-      <c r="F261" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="262" spans="1:6">
@@ -9743,10 +9743,10 @@
         <v>315</v>
       </c>
       <c r="E262" t="s">
+        <v>316</v>
+      </c>
+      <c r="F262" t="s">
         <v>319</v>
-      </c>
-      <c r="F262" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="263" spans="1:6">
@@ -9763,10 +9763,10 @@
         <v>315</v>
       </c>
       <c r="E263" t="s">
+        <v>316</v>
+      </c>
+      <c r="F263" t="s">
         <v>319</v>
-      </c>
-      <c r="F263" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="264" spans="1:6">
@@ -9783,10 +9783,10 @@
         <v>315</v>
       </c>
       <c r="E264" t="s">
+        <v>316</v>
+      </c>
+      <c r="F264" t="s">
         <v>319</v>
-      </c>
-      <c r="F264" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="265" spans="1:6">
@@ -9803,10 +9803,10 @@
         <v>315</v>
       </c>
       <c r="E265" t="s">
+        <v>316</v>
+      </c>
+      <c r="F265" t="s">
         <v>361</v>
-      </c>
-      <c r="F265" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="266" spans="1:6">
@@ -9823,10 +9823,10 @@
         <v>315</v>
       </c>
       <c r="E266" t="s">
+        <v>316</v>
+      </c>
+      <c r="F266" t="s">
         <v>363</v>
-      </c>
-      <c r="F266" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="267" spans="1:6">
@@ -9843,10 +9843,10 @@
         <v>315</v>
       </c>
       <c r="E267" t="s">
+        <v>316</v>
+      </c>
+      <c r="F267" t="s">
         <v>319</v>
-      </c>
-      <c r="F267" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="268" spans="1:6">
@@ -9863,10 +9863,10 @@
         <v>315</v>
       </c>
       <c r="E268" t="s">
+        <v>316</v>
+      </c>
+      <c r="F268" t="s">
         <v>319</v>
-      </c>
-      <c r="F268" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="269" spans="1:6">
@@ -9883,10 +9883,10 @@
         <v>315</v>
       </c>
       <c r="E269" t="s">
+        <v>316</v>
+      </c>
+      <c r="F269" t="s">
         <v>363</v>
-      </c>
-      <c r="F269" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="270" spans="1:6">
@@ -9903,10 +9903,10 @@
         <v>315</v>
       </c>
       <c r="E270" t="s">
+        <v>316</v>
+      </c>
+      <c r="F270" t="s">
         <v>363</v>
-      </c>
-      <c r="F270" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="271" spans="1:6">
@@ -9923,10 +9923,10 @@
         <v>315</v>
       </c>
       <c r="E271" t="s">
+        <v>316</v>
+      </c>
+      <c r="F271" t="s">
         <v>319</v>
-      </c>
-      <c r="F271" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="272" spans="1:6">
@@ -9943,10 +9943,10 @@
         <v>315</v>
       </c>
       <c r="E272" t="s">
+        <v>316</v>
+      </c>
+      <c r="F272" t="s">
         <v>319</v>
-      </c>
-      <c r="F272" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="273" spans="1:6">
@@ -9963,10 +9963,10 @@
         <v>315</v>
       </c>
       <c r="E273" t="s">
+        <v>316</v>
+      </c>
+      <c r="F273" t="s">
         <v>319</v>
-      </c>
-      <c r="F273" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="274" spans="1:6">
@@ -9983,10 +9983,10 @@
         <v>315</v>
       </c>
       <c r="E274" t="s">
+        <v>316</v>
+      </c>
+      <c r="F274" t="s">
         <v>319</v>
-      </c>
-      <c r="F274" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="275" spans="1:6">
@@ -10003,10 +10003,10 @@
         <v>315</v>
       </c>
       <c r="E275" t="s">
+        <v>316</v>
+      </c>
+      <c r="F275" t="s">
         <v>319</v>
-      </c>
-      <c r="F275" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="276" spans="1:6">
@@ -10023,10 +10023,10 @@
         <v>315</v>
       </c>
       <c r="E276" t="s">
+        <v>316</v>
+      </c>
+      <c r="F276" t="s">
         <v>319</v>
-      </c>
-      <c r="F276" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="277" spans="1:6">
@@ -10043,10 +10043,10 @@
         <v>315</v>
       </c>
       <c r="E277" t="s">
+        <v>316</v>
+      </c>
+      <c r="F277" t="s">
         <v>319</v>
-      </c>
-      <c r="F277" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="278" spans="1:6">
@@ -10063,10 +10063,10 @@
         <v>315</v>
       </c>
       <c r="E278" t="s">
+        <v>316</v>
+      </c>
+      <c r="F278" t="s">
         <v>319</v>
-      </c>
-      <c r="F278" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="279" spans="1:6">
@@ -10083,10 +10083,10 @@
         <v>315</v>
       </c>
       <c r="E279" t="s">
+        <v>316</v>
+      </c>
+      <c r="F279" t="s">
         <v>319</v>
-      </c>
-      <c r="F279" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="280" spans="1:6">
@@ -10103,10 +10103,10 @@
         <v>315</v>
       </c>
       <c r="E280" t="s">
+        <v>316</v>
+      </c>
+      <c r="F280" t="s">
         <v>319</v>
-      </c>
-      <c r="F280" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="281" spans="1:6">
@@ -10123,10 +10123,10 @@
         <v>315</v>
       </c>
       <c r="E281" t="s">
+        <v>316</v>
+      </c>
+      <c r="F281" t="s">
         <v>319</v>
-      </c>
-      <c r="F281" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="282" spans="1:6">
@@ -10143,10 +10143,10 @@
         <v>315</v>
       </c>
       <c r="E282" t="s">
+        <v>316</v>
+      </c>
+      <c r="F282" t="s">
         <v>319</v>
-      </c>
-      <c r="F282" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="283" spans="1:6">
@@ -10163,10 +10163,10 @@
         <v>315</v>
       </c>
       <c r="E283" t="s">
+        <v>316</v>
+      </c>
+      <c r="F283" t="s">
         <v>319</v>
-      </c>
-      <c r="F283" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="284" spans="1:6">
@@ -10183,10 +10183,10 @@
         <v>315</v>
       </c>
       <c r="E284" t="s">
+        <v>316</v>
+      </c>
+      <c r="F284" t="s">
         <v>319</v>
-      </c>
-      <c r="F284" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="285" spans="1:6">
@@ -10223,10 +10223,10 @@
         <v>383</v>
       </c>
       <c r="E286" t="s">
+        <v>384</v>
+      </c>
+      <c r="F286" t="s">
         <v>387</v>
-      </c>
-      <c r="F286" t="s">
-        <v>385</v>
       </c>
     </row>
     <row r="287" spans="1:6">
@@ -10263,10 +10263,10 @@
         <v>383</v>
       </c>
       <c r="E288" t="s">
+        <v>384</v>
+      </c>
+      <c r="F288" t="s">
         <v>387</v>
-      </c>
-      <c r="F288" t="s">
-        <v>385</v>
       </c>
     </row>
     <row r="289" spans="1:6">
@@ -10343,10 +10343,10 @@
         <v>383</v>
       </c>
       <c r="E292" t="s">
+        <v>384</v>
+      </c>
+      <c r="F292" t="s">
         <v>394</v>
-      </c>
-      <c r="F292" t="s">
-        <v>385</v>
       </c>
     </row>
     <row r="293" spans="1:6">
@@ -10383,10 +10383,10 @@
         <v>383</v>
       </c>
       <c r="E294" t="s">
+        <v>319</v>
+      </c>
+      <c r="F294" t="s">
         <v>397</v>
-      </c>
-      <c r="F294" t="s">
-        <v>319</v>
       </c>
     </row>
     <row r="295" spans="1:6">
@@ -10443,10 +10443,10 @@
         <v>383</v>
       </c>
       <c r="E297" t="s">
+        <v>384</v>
+      </c>
+      <c r="F297" t="s">
         <v>387</v>
-      </c>
-      <c r="F297" t="s">
-        <v>385</v>
       </c>
     </row>
     <row r="298" spans="1:6">
@@ -10463,10 +10463,10 @@
         <v>383</v>
       </c>
       <c r="E298" t="s">
+        <v>384</v>
+      </c>
+      <c r="F298" t="s">
         <v>387</v>
-      </c>
-      <c r="F298" t="s">
-        <v>385</v>
       </c>
     </row>
     <row r="299" spans="1:6">
@@ -10483,10 +10483,10 @@
         <v>383</v>
       </c>
       <c r="E299" t="s">
+        <v>384</v>
+      </c>
+      <c r="F299" t="s">
         <v>403</v>
-      </c>
-      <c r="F299" t="s">
-        <v>385</v>
       </c>
     </row>
     <row r="300" spans="1:6">
@@ -10563,10 +10563,10 @@
         <v>383</v>
       </c>
       <c r="E303" t="s">
+        <v>384</v>
+      </c>
+      <c r="F303" t="s">
         <v>387</v>
-      </c>
-      <c r="F303" t="s">
-        <v>385</v>
       </c>
     </row>
     <row r="304" spans="1:6">
@@ -10583,10 +10583,10 @@
         <v>383</v>
       </c>
       <c r="E304" t="s">
+        <v>384</v>
+      </c>
+      <c r="F304" t="s">
         <v>387</v>
-      </c>
-      <c r="F304" t="s">
-        <v>385</v>
       </c>
     </row>
     <row r="305" spans="1:6">
@@ -10623,10 +10623,10 @@
         <v>383</v>
       </c>
       <c r="E306" t="s">
+        <v>384</v>
+      </c>
+      <c r="F306" t="s">
         <v>387</v>
-      </c>
-      <c r="F306" t="s">
-        <v>385</v>
       </c>
     </row>
     <row r="307" spans="1:6">
@@ -10663,10 +10663,10 @@
         <v>383</v>
       </c>
       <c r="E308" t="s">
+        <v>384</v>
+      </c>
+      <c r="F308" t="s">
         <v>387</v>
-      </c>
-      <c r="F308" t="s">
-        <v>385</v>
       </c>
     </row>
     <row r="309" spans="1:6">
@@ -10683,10 +10683,10 @@
         <v>383</v>
       </c>
       <c r="E309" t="s">
+        <v>384</v>
+      </c>
+      <c r="F309" t="s">
         <v>403</v>
-      </c>
-      <c r="F309" t="s">
-        <v>385</v>
       </c>
     </row>
     <row r="310" spans="1:6">
@@ -10703,10 +10703,10 @@
         <v>383</v>
       </c>
       <c r="E310" t="s">
+        <v>384</v>
+      </c>
+      <c r="F310" t="s">
         <v>387</v>
-      </c>
-      <c r="F310" t="s">
-        <v>385</v>
       </c>
     </row>
     <row r="311" spans="1:6">
@@ -10723,10 +10723,10 @@
         <v>383</v>
       </c>
       <c r="E311" t="s">
+        <v>384</v>
+      </c>
+      <c r="F311" t="s">
         <v>387</v>
-      </c>
-      <c r="F311" t="s">
-        <v>385</v>
       </c>
     </row>
     <row r="312" spans="1:6">
@@ -10763,10 +10763,10 @@
         <v>383</v>
       </c>
       <c r="E313" t="s">
+        <v>384</v>
+      </c>
+      <c r="F313" t="s">
         <v>387</v>
-      </c>
-      <c r="F313" t="s">
-        <v>385</v>
       </c>
     </row>
     <row r="314" spans="1:6">
@@ -10803,10 +10803,10 @@
         <v>383</v>
       </c>
       <c r="E315" t="s">
+        <v>384</v>
+      </c>
+      <c r="F315" t="s">
         <v>387</v>
-      </c>
-      <c r="F315" t="s">
-        <v>385</v>
       </c>
     </row>
     <row r="316" spans="1:6">
@@ -10823,10 +10823,10 @@
         <v>383</v>
       </c>
       <c r="E316" t="s">
+        <v>384</v>
+      </c>
+      <c r="F316" t="s">
         <v>423</v>
-      </c>
-      <c r="F316" t="s">
-        <v>385</v>
       </c>
     </row>
     <row r="317" spans="1:6">
@@ -10863,10 +10863,10 @@
         <v>383</v>
       </c>
       <c r="E318" t="s">
+        <v>384</v>
+      </c>
+      <c r="F318" t="s">
         <v>387</v>
-      </c>
-      <c r="F318" t="s">
-        <v>385</v>
       </c>
     </row>
     <row r="319" spans="1:6">
@@ -10903,10 +10903,10 @@
         <v>383</v>
       </c>
       <c r="E320" t="s">
+        <v>384</v>
+      </c>
+      <c r="F320" t="s">
         <v>387</v>
-      </c>
-      <c r="F320" t="s">
-        <v>385</v>
       </c>
     </row>
     <row r="321" spans="1:6">
@@ -10963,10 +10963,10 @@
         <v>383</v>
       </c>
       <c r="E323" t="s">
+        <v>384</v>
+      </c>
+      <c r="F323" t="s">
         <v>387</v>
-      </c>
-      <c r="F323" t="s">
-        <v>385</v>
       </c>
     </row>
     <row r="324" spans="1:6">
@@ -11063,10 +11063,10 @@
         <v>383</v>
       </c>
       <c r="E328" t="s">
+        <v>384</v>
+      </c>
+      <c r="F328" t="s">
         <v>423</v>
-      </c>
-      <c r="F328" t="s">
-        <v>385</v>
       </c>
     </row>
     <row r="329" spans="1:6">
@@ -11083,10 +11083,10 @@
         <v>383</v>
       </c>
       <c r="E329" t="s">
+        <v>384</v>
+      </c>
+      <c r="F329" t="s">
         <v>387</v>
-      </c>
-      <c r="F329" t="s">
-        <v>385</v>
       </c>
     </row>
     <row r="330" spans="1:6">
@@ -11143,10 +11143,10 @@
         <v>383</v>
       </c>
       <c r="E332" t="s">
+        <v>384</v>
+      </c>
+      <c r="F332" t="s">
         <v>423</v>
-      </c>
-      <c r="F332" t="s">
-        <v>385</v>
       </c>
     </row>
     <row r="333" spans="1:6">
@@ -11163,10 +11163,10 @@
         <v>383</v>
       </c>
       <c r="E333" t="s">
+        <v>384</v>
+      </c>
+      <c r="F333" t="s">
         <v>387</v>
-      </c>
-      <c r="F333" t="s">
-        <v>385</v>
       </c>
     </row>
     <row r="334" spans="1:6">
@@ -11303,10 +11303,10 @@
         <v>383</v>
       </c>
       <c r="E340" t="s">
+        <v>384</v>
+      </c>
+      <c r="F340" t="s">
         <v>387</v>
-      </c>
-      <c r="F340" t="s">
-        <v>385</v>
       </c>
     </row>
     <row r="341" spans="1:6">
@@ -11323,10 +11323,10 @@
         <v>383</v>
       </c>
       <c r="E341" t="s">
+        <v>384</v>
+      </c>
+      <c r="F341" t="s">
         <v>387</v>
-      </c>
-      <c r="F341" t="s">
-        <v>385</v>
       </c>
     </row>
     <row r="342" spans="1:6">
@@ -11343,10 +11343,10 @@
         <v>383</v>
       </c>
       <c r="E342" t="s">
+        <v>384</v>
+      </c>
+      <c r="F342" t="s">
         <v>387</v>
-      </c>
-      <c r="F342" t="s">
-        <v>385</v>
       </c>
     </row>
     <row r="343" spans="1:6">
@@ -11383,10 +11383,10 @@
         <v>383</v>
       </c>
       <c r="E344" t="s">
+        <v>384</v>
+      </c>
+      <c r="F344" t="s">
         <v>387</v>
-      </c>
-      <c r="F344" t="s">
-        <v>385</v>
       </c>
     </row>
     <row r="345" spans="1:6">
@@ -11443,10 +11443,10 @@
         <v>383</v>
       </c>
       <c r="E347" t="s">
+        <v>407</v>
+      </c>
+      <c r="F347" t="s">
         <v>459</v>
-      </c>
-      <c r="F347" t="s">
-        <v>408</v>
       </c>
     </row>
     <row r="348" spans="1:6">
@@ -11463,10 +11463,10 @@
         <v>383</v>
       </c>
       <c r="E348" t="s">
+        <v>384</v>
+      </c>
+      <c r="F348" t="s">
         <v>387</v>
-      </c>
-      <c r="F348" t="s">
-        <v>385</v>
       </c>
     </row>
     <row r="349" spans="1:6">
@@ -11763,10 +11763,10 @@
         <v>463</v>
       </c>
       <c r="E363" t="s">
+        <v>464</v>
+      </c>
+      <c r="F363" t="s">
         <v>479</v>
-      </c>
-      <c r="F363" t="s">
-        <v>465</v>
       </c>
     </row>
     <row r="364" spans="1:6">
@@ -11803,10 +11803,10 @@
         <v>463</v>
       </c>
       <c r="E365" t="s">
-        <v>464</v>
+        <v>482</v>
       </c>
       <c r="F365" t="s">
-        <v>482</v>
+        <v>465</v>
       </c>
     </row>
     <row r="366" spans="1:6">
@@ -11923,10 +11923,10 @@
         <v>463</v>
       </c>
       <c r="E371" t="s">
-        <v>464</v>
+        <v>489</v>
       </c>
       <c r="F371" t="s">
-        <v>489</v>
+        <v>465</v>
       </c>
     </row>
     <row r="372" spans="1:6">
@@ -12183,10 +12183,10 @@
         <v>463</v>
       </c>
       <c r="E384" t="s">
+        <v>502</v>
+      </c>
+      <c r="F384" t="s">
         <v>505</v>
-      </c>
-      <c r="F384" t="s">
-        <v>503</v>
       </c>
     </row>
     <row r="385" spans="1:6">
@@ -12223,10 +12223,10 @@
         <v>507</v>
       </c>
       <c r="E386" t="s">
+        <v>508</v>
+      </c>
+      <c r="F386" t="s">
         <v>511</v>
-      </c>
-      <c r="F386" t="s">
-        <v>509</v>
       </c>
     </row>
     <row r="387" spans="1:6">
@@ -12423,10 +12423,10 @@
         <v>507</v>
       </c>
       <c r="E396" t="s">
+        <v>508</v>
+      </c>
+      <c r="F396" t="s">
         <v>522</v>
-      </c>
-      <c r="F396" t="s">
-        <v>509</v>
       </c>
     </row>
     <row r="397" spans="1:6">
@@ -12623,10 +12623,10 @@
         <v>507</v>
       </c>
       <c r="E406" t="s">
+        <v>508</v>
+      </c>
+      <c r="F406" t="s">
         <v>533</v>
-      </c>
-      <c r="F406" t="s">
-        <v>509</v>
       </c>
     </row>
     <row r="407" spans="1:6">
@@ -12643,10 +12643,10 @@
         <v>507</v>
       </c>
       <c r="E407" t="s">
+        <v>508</v>
+      </c>
+      <c r="F407" t="s">
         <v>511</v>
-      </c>
-      <c r="F407" t="s">
-        <v>509</v>
       </c>
     </row>
     <row r="408" spans="1:6">
@@ -12723,10 +12723,10 @@
         <v>507</v>
       </c>
       <c r="E411" t="s">
-        <v>508</v>
+        <v>539</v>
       </c>
       <c r="F411" t="s">
-        <v>539</v>
+        <v>509</v>
       </c>
     </row>
     <row r="412" spans="1:6">
@@ -12903,10 +12903,10 @@
         <v>549</v>
       </c>
       <c r="E420" t="s">
+        <v>550</v>
+      </c>
+      <c r="F420" t="s">
         <v>554</v>
-      </c>
-      <c r="F420" t="s">
-        <v>551</v>
       </c>
     </row>
     <row r="421" spans="1:6">
@@ -13023,10 +13023,10 @@
         <v>549</v>
       </c>
       <c r="E426" t="s">
+        <v>550</v>
+      </c>
+      <c r="F426" t="s">
         <v>561</v>
-      </c>
-      <c r="F426" t="s">
-        <v>551</v>
       </c>
     </row>
     <row r="427" spans="1:6">
@@ -13043,10 +13043,10 @@
         <v>549</v>
       </c>
       <c r="E427" t="s">
+        <v>550</v>
+      </c>
+      <c r="F427" t="s">
         <v>563</v>
-      </c>
-      <c r="F427" t="s">
-        <v>551</v>
       </c>
     </row>
     <row r="428" spans="1:6">
@@ -13163,10 +13163,10 @@
         <v>549</v>
       </c>
       <c r="E433" t="s">
+        <v>550</v>
+      </c>
+      <c r="F433" t="s">
         <v>572</v>
-      </c>
-      <c r="F433" t="s">
-        <v>551</v>
       </c>
     </row>
     <row r="434" spans="1:6">
@@ -13443,10 +13443,10 @@
         <v>549</v>
       </c>
       <c r="E447" t="s">
+        <v>550</v>
+      </c>
+      <c r="F447" t="s">
         <v>595</v>
-      </c>
-      <c r="F447" t="s">
-        <v>551</v>
       </c>
     </row>
     <row r="448" spans="1:6">
@@ -13463,10 +13463,10 @@
         <v>549</v>
       </c>
       <c r="E448" t="s">
+        <v>550</v>
+      </c>
+      <c r="F448" t="s">
         <v>572</v>
-      </c>
-      <c r="F448" t="s">
-        <v>551</v>
       </c>
     </row>
     <row r="449" spans="1:6">
@@ -13483,10 +13483,10 @@
         <v>549</v>
       </c>
       <c r="E449" t="s">
+        <v>550</v>
+      </c>
+      <c r="F449" t="s">
         <v>554</v>
-      </c>
-      <c r="F449" t="s">
-        <v>551</v>
       </c>
     </row>
     <row r="450" spans="1:6">
@@ -13723,10 +13723,10 @@
         <v>608</v>
       </c>
       <c r="E461" t="s">
+        <v>609</v>
+      </c>
+      <c r="F461" t="s">
         <v>613</v>
-      </c>
-      <c r="F461" t="s">
-        <v>610</v>
       </c>
     </row>
     <row r="462" spans="1:6">
@@ -13763,10 +13763,10 @@
         <v>608</v>
       </c>
       <c r="E463" t="s">
+        <v>609</v>
+      </c>
+      <c r="F463" t="s">
         <v>616</v>
-      </c>
-      <c r="F463" t="s">
-        <v>610</v>
       </c>
     </row>
     <row r="464" spans="1:6">
@@ -14003,10 +14003,10 @@
         <v>608</v>
       </c>
       <c r="E475" t="s">
+        <v>609</v>
+      </c>
+      <c r="F475" t="s">
         <v>633</v>
-      </c>
-      <c r="F475" t="s">
-        <v>610</v>
       </c>
     </row>
     <row r="476" spans="1:6">
@@ -14063,10 +14063,10 @@
         <v>608</v>
       </c>
       <c r="E478" t="s">
+        <v>609</v>
+      </c>
+      <c r="F478" t="s">
         <v>637</v>
-      </c>
-      <c r="F478" t="s">
-        <v>610</v>
       </c>
     </row>
     <row r="479" spans="1:6">
@@ -14083,10 +14083,10 @@
         <v>608</v>
       </c>
       <c r="E479" t="s">
+        <v>609</v>
+      </c>
+      <c r="F479" t="s">
         <v>639</v>
-      </c>
-      <c r="F479" t="s">
-        <v>610</v>
       </c>
     </row>
     <row r="480" spans="1:6">
@@ -14683,10 +14683,10 @@
         <v>665</v>
       </c>
       <c r="E509" t="s">
+        <v>666</v>
+      </c>
+      <c r="F509" t="s">
         <v>680</v>
-      </c>
-      <c r="F509" t="s">
-        <v>667</v>
       </c>
     </row>
     <row r="510" spans="1:6">
@@ -14703,10 +14703,10 @@
         <v>665</v>
       </c>
       <c r="E510" t="s">
+        <v>677</v>
+      </c>
+      <c r="F510" t="s">
         <v>682</v>
-      </c>
-      <c r="F510" t="s">
-        <v>678</v>
       </c>
     </row>
     <row r="511" spans="1:6">
@@ -14843,10 +14843,10 @@
         <v>665</v>
       </c>
       <c r="E517" t="s">
+        <v>677</v>
+      </c>
+      <c r="F517" t="s">
         <v>694</v>
-      </c>
-      <c r="F517" t="s">
-        <v>678</v>
       </c>
     </row>
     <row r="518" spans="1:6">
@@ -15163,10 +15163,10 @@
         <v>710</v>
       </c>
       <c r="E533" t="s">
+        <v>711</v>
+      </c>
+      <c r="F533" t="s">
         <v>714</v>
-      </c>
-      <c r="F533" t="s">
-        <v>712</v>
       </c>
     </row>
     <row r="534" spans="1:6">
@@ -15243,10 +15243,10 @@
         <v>710</v>
       </c>
       <c r="E537" t="s">
-        <v>711</v>
+        <v>719</v>
       </c>
       <c r="F537" t="s">
-        <v>719</v>
+        <v>712</v>
       </c>
     </row>
     <row r="538" spans="1:6">
@@ -15283,10 +15283,10 @@
         <v>710</v>
       </c>
       <c r="E539" t="s">
-        <v>688</v>
+        <v>722</v>
       </c>
       <c r="F539" t="s">
-        <v>722</v>
+        <v>689</v>
       </c>
     </row>
     <row r="540" spans="1:6">
@@ -15303,10 +15303,10 @@
         <v>710</v>
       </c>
       <c r="E540" t="s">
-        <v>688</v>
+        <v>722</v>
       </c>
       <c r="F540" t="s">
-        <v>722</v>
+        <v>689</v>
       </c>
     </row>
     <row r="541" spans="1:6">
@@ -15363,10 +15363,10 @@
         <v>710</v>
       </c>
       <c r="E543" t="s">
+        <v>711</v>
+      </c>
+      <c r="F543" t="s">
         <v>727</v>
-      </c>
-      <c r="F543" t="s">
-        <v>712</v>
       </c>
     </row>
     <row r="544" spans="1:6">
@@ -15443,10 +15443,10 @@
         <v>710</v>
       </c>
       <c r="E547" t="s">
+        <v>711</v>
+      </c>
+      <c r="F547" t="s">
         <v>732</v>
-      </c>
-      <c r="F547" t="s">
-        <v>712</v>
       </c>
     </row>
     <row r="548" spans="1:6">
@@ -15583,10 +15583,10 @@
         <v>710</v>
       </c>
       <c r="E554" t="s">
-        <v>741</v>
+        <v>744</v>
       </c>
       <c r="F554" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
     </row>
     <row r="555" spans="1:6">
@@ -15643,10 +15643,10 @@
         <v>710</v>
       </c>
       <c r="E557" t="s">
+        <v>711</v>
+      </c>
+      <c r="F557" t="s">
         <v>750</v>
-      </c>
-      <c r="F557" t="s">
-        <v>712</v>
       </c>
     </row>
     <row r="558" spans="1:6">
@@ -15683,10 +15683,10 @@
         <v>710</v>
       </c>
       <c r="E559" t="s">
-        <v>711</v>
+        <v>753</v>
       </c>
       <c r="F559" t="s">
-        <v>753</v>
+        <v>712</v>
       </c>
     </row>
     <row r="560" spans="1:6">
@@ -15843,10 +15843,10 @@
         <v>710</v>
       </c>
       <c r="E567" t="s">
+        <v>711</v>
+      </c>
+      <c r="F567" t="s">
         <v>762</v>
-      </c>
-      <c r="F567" t="s">
-        <v>712</v>
       </c>
     </row>
     <row r="568" spans="1:6">
@@ -15863,10 +15863,10 @@
         <v>710</v>
       </c>
       <c r="E568" t="s">
+        <v>711</v>
+      </c>
+      <c r="F568" t="s">
         <v>764</v>
-      </c>
-      <c r="F568" t="s">
-        <v>712</v>
       </c>
     </row>
     <row r="569" spans="1:6">
@@ -15883,10 +15883,10 @@
         <v>710</v>
       </c>
       <c r="E569" t="s">
+        <v>711</v>
+      </c>
+      <c r="F569" t="s">
         <v>766</v>
-      </c>
-      <c r="F569" t="s">
-        <v>712</v>
       </c>
     </row>
     <row r="570" spans="1:6">
@@ -15923,10 +15923,10 @@
         <v>770</v>
       </c>
       <c r="E571" t="s">
+        <v>771</v>
+      </c>
+      <c r="F571" t="s">
         <v>714</v>
-      </c>
-      <c r="F571" t="s">
-        <v>771</v>
       </c>
     </row>
     <row r="572" spans="1:6">
@@ -15943,10 +15943,10 @@
         <v>770</v>
       </c>
       <c r="E572" t="s">
+        <v>771</v>
+      </c>
+      <c r="F572" t="s">
         <v>714</v>
-      </c>
-      <c r="F572" t="s">
-        <v>771</v>
       </c>
     </row>
     <row r="573" spans="1:6">
@@ -15963,10 +15963,10 @@
         <v>770</v>
       </c>
       <c r="E573" t="s">
+        <v>771</v>
+      </c>
+      <c r="F573" t="s">
         <v>714</v>
-      </c>
-      <c r="F573" t="s">
-        <v>771</v>
       </c>
     </row>
     <row r="574" spans="1:6">
@@ -15983,10 +15983,10 @@
         <v>770</v>
       </c>
       <c r="E574" t="s">
+        <v>771</v>
+      </c>
+      <c r="F574" t="s">
         <v>714</v>
-      </c>
-      <c r="F574" t="s">
-        <v>771</v>
       </c>
     </row>
     <row r="575" spans="1:6">
@@ -16003,10 +16003,10 @@
         <v>770</v>
       </c>
       <c r="E575" t="s">
+        <v>771</v>
+      </c>
+      <c r="F575" t="s">
         <v>776</v>
-      </c>
-      <c r="F575" t="s">
-        <v>771</v>
       </c>
     </row>
     <row r="576" spans="1:6">
@@ -16023,10 +16023,10 @@
         <v>770</v>
       </c>
       <c r="E576" t="s">
+        <v>778</v>
+      </c>
+      <c r="F576" t="s">
         <v>714</v>
-      </c>
-      <c r="F576" t="s">
-        <v>778</v>
       </c>
     </row>
     <row r="577" spans="1:6">
@@ -16043,10 +16043,10 @@
         <v>770</v>
       </c>
       <c r="E577" t="s">
+        <v>771</v>
+      </c>
+      <c r="F577" t="s">
         <v>714</v>
-      </c>
-      <c r="F577" t="s">
-        <v>771</v>
       </c>
     </row>
     <row r="578" spans="1:6">
@@ -16063,10 +16063,10 @@
         <v>770</v>
       </c>
       <c r="E578" t="s">
+        <v>771</v>
+      </c>
+      <c r="F578" t="s">
         <v>714</v>
-      </c>
-      <c r="F578" t="s">
-        <v>771</v>
       </c>
     </row>
     <row r="579" spans="1:6">
@@ -16083,10 +16083,10 @@
         <v>770</v>
       </c>
       <c r="E579" t="s">
+        <v>771</v>
+      </c>
+      <c r="F579" t="s">
         <v>714</v>
-      </c>
-      <c r="F579" t="s">
-        <v>771</v>
       </c>
     </row>
     <row r="580" spans="1:6">
@@ -16103,10 +16103,10 @@
         <v>770</v>
       </c>
       <c r="E580" t="s">
+        <v>771</v>
+      </c>
+      <c r="F580" t="s">
         <v>714</v>
-      </c>
-      <c r="F580" t="s">
-        <v>771</v>
       </c>
     </row>
     <row r="581" spans="1:6">
@@ -16123,10 +16123,10 @@
         <v>770</v>
       </c>
       <c r="E581" t="s">
+        <v>771</v>
+      </c>
+      <c r="F581" t="s">
         <v>714</v>
-      </c>
-      <c r="F581" t="s">
-        <v>771</v>
       </c>
     </row>
     <row r="582" spans="1:6">
@@ -16143,10 +16143,10 @@
         <v>770</v>
       </c>
       <c r="E582" t="s">
+        <v>771</v>
+      </c>
+      <c r="F582" t="s">
         <v>785</v>
-      </c>
-      <c r="F582" t="s">
-        <v>771</v>
       </c>
     </row>
     <row r="583" spans="1:6">
@@ -16163,10 +16163,10 @@
         <v>770</v>
       </c>
       <c r="E583" t="s">
+        <v>771</v>
+      </c>
+      <c r="F583" t="s">
         <v>787</v>
-      </c>
-      <c r="F583" t="s">
-        <v>771</v>
       </c>
     </row>
     <row r="584" spans="1:6">
@@ -16183,10 +16183,10 @@
         <v>770</v>
       </c>
       <c r="E584" t="s">
+        <v>771</v>
+      </c>
+      <c r="F584" t="s">
         <v>714</v>
-      </c>
-      <c r="F584" t="s">
-        <v>771</v>
       </c>
     </row>
     <row r="585" spans="1:6">
@@ -16203,10 +16203,10 @@
         <v>770</v>
       </c>
       <c r="E585" t="s">
+        <v>771</v>
+      </c>
+      <c r="F585" t="s">
         <v>714</v>
-      </c>
-      <c r="F585" t="s">
-        <v>771</v>
       </c>
     </row>
     <row r="586" spans="1:6">
@@ -16223,10 +16223,10 @@
         <v>770</v>
       </c>
       <c r="E586" t="s">
+        <v>746</v>
+      </c>
+      <c r="F586" t="s">
         <v>714</v>
-      </c>
-      <c r="F586" t="s">
-        <v>747</v>
       </c>
     </row>
     <row r="587" spans="1:6">
@@ -16243,10 +16243,10 @@
         <v>770</v>
       </c>
       <c r="E587" t="s">
+        <v>771</v>
+      </c>
+      <c r="F587" t="s">
         <v>714</v>
-      </c>
-      <c r="F587" t="s">
-        <v>771</v>
       </c>
     </row>
     <row r="588" spans="1:6">
@@ -16263,10 +16263,10 @@
         <v>770</v>
       </c>
       <c r="E588" t="s">
+        <v>771</v>
+      </c>
+      <c r="F588" t="s">
         <v>714</v>
-      </c>
-      <c r="F588" t="s">
-        <v>771</v>
       </c>
     </row>
     <row r="589" spans="1:6">
@@ -16283,10 +16283,10 @@
         <v>770</v>
       </c>
       <c r="E589" t="s">
+        <v>771</v>
+      </c>
+      <c r="F589" t="s">
         <v>714</v>
-      </c>
-      <c r="F589" t="s">
-        <v>771</v>
       </c>
     </row>
     <row r="590" spans="1:6">
@@ -16303,10 +16303,10 @@
         <v>770</v>
       </c>
       <c r="E590" t="s">
+        <v>771</v>
+      </c>
+      <c r="F590" t="s">
         <v>714</v>
-      </c>
-      <c r="F590" t="s">
-        <v>771</v>
       </c>
     </row>
     <row r="591" spans="1:6">
@@ -16323,10 +16323,10 @@
         <v>770</v>
       </c>
       <c r="E591" t="s">
+        <v>796</v>
+      </c>
+      <c r="F591" t="s">
         <v>714</v>
-      </c>
-      <c r="F591" t="s">
-        <v>796</v>
       </c>
     </row>
     <row r="592" spans="1:6">
@@ -16343,10 +16343,10 @@
         <v>770</v>
       </c>
       <c r="E592" t="s">
+        <v>771</v>
+      </c>
+      <c r="F592" t="s">
         <v>714</v>
-      </c>
-      <c r="F592" t="s">
-        <v>771</v>
       </c>
     </row>
     <row r="593" spans="1:6">
@@ -16363,10 +16363,10 @@
         <v>770</v>
       </c>
       <c r="E593" t="s">
+        <v>771</v>
+      </c>
+      <c r="F593" t="s">
         <v>714</v>
-      </c>
-      <c r="F593" t="s">
-        <v>771</v>
       </c>
     </row>
     <row r="594" spans="1:6">
@@ -16403,10 +16403,10 @@
         <v>800</v>
       </c>
       <c r="E595" t="s">
+        <v>801</v>
+      </c>
+      <c r="F595" t="s">
         <v>804</v>
-      </c>
-      <c r="F595" t="s">
-        <v>802</v>
       </c>
     </row>
     <row r="596" spans="1:6">
@@ -16423,10 +16423,10 @@
         <v>800</v>
       </c>
       <c r="E596" t="s">
+        <v>801</v>
+      </c>
+      <c r="F596" t="s">
         <v>806</v>
-      </c>
-      <c r="F596" t="s">
-        <v>802</v>
       </c>
     </row>
     <row r="597" spans="1:6">
@@ -16503,10 +16503,10 @@
         <v>800</v>
       </c>
       <c r="E600" t="s">
-        <v>801</v>
+        <v>811</v>
       </c>
       <c r="F600" t="s">
-        <v>811</v>
+        <v>802</v>
       </c>
     </row>
     <row r="601" spans="1:6">
@@ -16623,10 +16623,10 @@
         <v>800</v>
       </c>
       <c r="E606" t="s">
+        <v>801</v>
+      </c>
+      <c r="F606" t="s">
         <v>820</v>
-      </c>
-      <c r="F606" t="s">
-        <v>802</v>
       </c>
     </row>
     <row r="607" spans="1:6">
@@ -16643,10 +16643,10 @@
         <v>800</v>
       </c>
       <c r="E607" t="s">
+        <v>801</v>
+      </c>
+      <c r="F607" t="s">
         <v>820</v>
-      </c>
-      <c r="F607" t="s">
-        <v>802</v>
       </c>
     </row>
     <row r="608" spans="1:6">
@@ -16683,10 +16683,10 @@
         <v>800</v>
       </c>
       <c r="E609" t="s">
-        <v>801</v>
+        <v>824</v>
       </c>
       <c r="F609" t="s">
-        <v>824</v>
+        <v>802</v>
       </c>
     </row>
     <row r="610" spans="1:6">
@@ -16883,10 +16883,10 @@
         <v>837</v>
       </c>
       <c r="E619" t="s">
+        <v>771</v>
+      </c>
+      <c r="F619" t="s">
         <v>838</v>
-      </c>
-      <c r="F619" t="s">
-        <v>771</v>
       </c>
     </row>
     <row r="620" spans="1:6">
@@ -16903,10 +16903,10 @@
         <v>837</v>
       </c>
       <c r="E620" t="s">
+        <v>840</v>
+      </c>
+      <c r="F620" t="s">
         <v>838</v>
-      </c>
-      <c r="F620" t="s">
-        <v>840</v>
       </c>
     </row>
     <row r="621" spans="1:6">
@@ -16923,10 +16923,10 @@
         <v>837</v>
       </c>
       <c r="E621" t="s">
+        <v>840</v>
+      </c>
+      <c r="F621" t="s">
         <v>838</v>
-      </c>
-      <c r="F621" t="s">
-        <v>840</v>
       </c>
     </row>
     <row r="622" spans="1:6">
@@ -16943,10 +16943,10 @@
         <v>837</v>
       </c>
       <c r="E622" t="s">
+        <v>840</v>
+      </c>
+      <c r="F622" t="s">
         <v>838</v>
-      </c>
-      <c r="F622" t="s">
-        <v>840</v>
       </c>
     </row>
     <row r="623" spans="1:6">
@@ -16963,10 +16963,10 @@
         <v>837</v>
       </c>
       <c r="E623" t="s">
+        <v>801</v>
+      </c>
+      <c r="F623" t="s">
         <v>838</v>
-      </c>
-      <c r="F623" t="s">
-        <v>802</v>
       </c>
     </row>
     <row r="624" spans="1:6">
@@ -16983,10 +16983,10 @@
         <v>837</v>
       </c>
       <c r="E624" t="s">
+        <v>840</v>
+      </c>
+      <c r="F624" t="s">
         <v>845</v>
-      </c>
-      <c r="F624" t="s">
-        <v>840</v>
       </c>
     </row>
     <row r="625" spans="1:6">
@@ -17023,10 +17023,10 @@
         <v>837</v>
       </c>
       <c r="E626" t="s">
+        <v>840</v>
+      </c>
+      <c r="F626" t="s">
         <v>850</v>
-      </c>
-      <c r="F626" t="s">
-        <v>840</v>
       </c>
     </row>
     <row r="627" spans="1:6">
@@ -17043,10 +17043,10 @@
         <v>837</v>
       </c>
       <c r="E627" t="s">
+        <v>840</v>
+      </c>
+      <c r="F627" t="s">
         <v>852</v>
-      </c>
-      <c r="F627" t="s">
-        <v>840</v>
       </c>
     </row>
     <row r="628" spans="1:6">
@@ -17063,10 +17063,10 @@
         <v>837</v>
       </c>
       <c r="E628" t="s">
+        <v>840</v>
+      </c>
+      <c r="F628" t="s">
         <v>838</v>
-      </c>
-      <c r="F628" t="s">
-        <v>840</v>
       </c>
     </row>
     <row r="629" spans="1:6">
@@ -17123,10 +17123,10 @@
         <v>837</v>
       </c>
       <c r="E631" t="s">
+        <v>840</v>
+      </c>
+      <c r="F631" t="s">
         <v>838</v>
-      </c>
-      <c r="F631" t="s">
-        <v>840</v>
       </c>
     </row>
     <row r="632" spans="1:6">
@@ -17163,10 +17163,10 @@
         <v>837</v>
       </c>
       <c r="E633" t="s">
+        <v>840</v>
+      </c>
+      <c r="F633" t="s">
         <v>865</v>
-      </c>
-      <c r="F633" t="s">
-        <v>840</v>
       </c>
     </row>
     <row r="634" spans="1:6">
@@ -17183,10 +17183,10 @@
         <v>837</v>
       </c>
       <c r="E634" t="s">
+        <v>840</v>
+      </c>
+      <c r="F634" t="s">
         <v>867</v>
-      </c>
-      <c r="F634" t="s">
-        <v>840</v>
       </c>
     </row>
     <row r="635" spans="1:6">
@@ -17203,10 +17203,10 @@
         <v>837</v>
       </c>
       <c r="E635" t="s">
+        <v>840</v>
+      </c>
+      <c r="F635" t="s">
         <v>838</v>
-      </c>
-      <c r="F635" t="s">
-        <v>840</v>
       </c>
     </row>
     <row r="636" spans="1:6">
@@ -17223,10 +17223,10 @@
         <v>837</v>
       </c>
       <c r="E636" t="s">
+        <v>840</v>
+      </c>
+      <c r="F636" t="s">
         <v>838</v>
-      </c>
-      <c r="F636" t="s">
-        <v>840</v>
       </c>
     </row>
     <row r="637" spans="1:6">
@@ -17243,10 +17243,10 @@
         <v>837</v>
       </c>
       <c r="E637" t="s">
+        <v>840</v>
+      </c>
+      <c r="F637" t="s">
         <v>838</v>
-      </c>
-      <c r="F637" t="s">
-        <v>840</v>
       </c>
     </row>
     <row r="638" spans="1:6">
@@ -17263,10 +17263,10 @@
         <v>837</v>
       </c>
       <c r="E638" t="s">
+        <v>872</v>
+      </c>
+      <c r="F638" t="s">
         <v>838</v>
-      </c>
-      <c r="F638" t="s">
-        <v>872</v>
       </c>
     </row>
     <row r="639" spans="1:6">
@@ -17283,10 +17283,10 @@
         <v>837</v>
       </c>
       <c r="E639" t="s">
+        <v>840</v>
+      </c>
+      <c r="F639" t="s">
         <v>838</v>
-      </c>
-      <c r="F639" t="s">
-        <v>840</v>
       </c>
     </row>
     <row r="640" spans="1:6">
@@ -17303,10 +17303,10 @@
         <v>837</v>
       </c>
       <c r="E640" t="s">
+        <v>840</v>
+      </c>
+      <c r="F640" t="s">
         <v>838</v>
-      </c>
-      <c r="F640" t="s">
-        <v>840</v>
       </c>
     </row>
     <row r="641" spans="1:6">
@@ -17323,10 +17323,10 @@
         <v>837</v>
       </c>
       <c r="E641" t="s">
+        <v>840</v>
+      </c>
+      <c r="F641" t="s">
         <v>838</v>
-      </c>
-      <c r="F641" t="s">
-        <v>840</v>
       </c>
     </row>
     <row r="642" spans="1:6">
@@ -17343,10 +17343,10 @@
         <v>837</v>
       </c>
       <c r="E642" t="s">
+        <v>840</v>
+      </c>
+      <c r="F642" t="s">
         <v>838</v>
-      </c>
-      <c r="F642" t="s">
-        <v>840</v>
       </c>
     </row>
     <row r="643" spans="1:6">
@@ -17523,10 +17523,10 @@
         <v>878</v>
       </c>
       <c r="E651" t="s">
+        <v>879</v>
+      </c>
+      <c r="F651" t="s">
         <v>897</v>
-      </c>
-      <c r="F651" t="s">
-        <v>880</v>
       </c>
     </row>
     <row r="652" spans="1:6">
@@ -17623,10 +17623,10 @@
         <v>878</v>
       </c>
       <c r="E656" t="s">
+        <v>865</v>
+      </c>
+      <c r="F656" t="s">
         <v>905</v>
-      </c>
-      <c r="F656" t="s">
-        <v>865</v>
       </c>
     </row>
     <row r="657" spans="1:6">
@@ -17663,10 +17663,10 @@
         <v>878</v>
       </c>
       <c r="E658" t="s">
-        <v>882</v>
+        <v>908</v>
       </c>
       <c r="F658" t="s">
-        <v>908</v>
+        <v>883</v>
       </c>
     </row>
     <row r="659" spans="1:6">
@@ -17683,10 +17683,10 @@
         <v>878</v>
       </c>
       <c r="E659" t="s">
+        <v>879</v>
+      </c>
+      <c r="F659" t="s">
         <v>910</v>
-      </c>
-      <c r="F659" t="s">
-        <v>880</v>
       </c>
     </row>
     <row r="660" spans="1:6">
@@ -17703,10 +17703,10 @@
         <v>878</v>
       </c>
       <c r="E660" t="s">
+        <v>879</v>
+      </c>
+      <c r="F660" t="s">
         <v>910</v>
-      </c>
-      <c r="F660" t="s">
-        <v>880</v>
       </c>
     </row>
     <row r="661" spans="1:6">
@@ -17743,10 +17743,10 @@
         <v>878</v>
       </c>
       <c r="E662" t="s">
+        <v>879</v>
+      </c>
+      <c r="F662" t="s">
         <v>914</v>
-      </c>
-      <c r="F662" t="s">
-        <v>880</v>
       </c>
     </row>
     <row r="663" spans="1:6">
@@ -18063,10 +18063,10 @@
         <v>926</v>
       </c>
       <c r="E678" t="s">
-        <v>927</v>
+        <v>936</v>
       </c>
       <c r="F678" t="s">
-        <v>936</v>
+        <v>928</v>
       </c>
     </row>
     <row r="679" spans="1:6">
@@ -18083,10 +18083,10 @@
         <v>926</v>
       </c>
       <c r="E679" t="s">
+        <v>927</v>
+      </c>
+      <c r="F679" t="s">
         <v>938</v>
-      </c>
-      <c r="F679" t="s">
-        <v>928</v>
       </c>
     </row>
     <row r="680" spans="1:6">
@@ -18163,10 +18163,10 @@
         <v>926</v>
       </c>
       <c r="E683" t="s">
+        <v>943</v>
+      </c>
+      <c r="F683" t="s">
         <v>938</v>
-      </c>
-      <c r="F683" t="s">
-        <v>943</v>
       </c>
     </row>
     <row r="684" spans="1:6">
@@ -18243,10 +18243,10 @@
         <v>926</v>
       </c>
       <c r="E687" t="s">
+        <v>927</v>
+      </c>
+      <c r="F687" t="s">
         <v>952</v>
-      </c>
-      <c r="F687" t="s">
-        <v>928</v>
       </c>
     </row>
     <row r="688" spans="1:6">
@@ -18363,10 +18363,10 @@
         <v>926</v>
       </c>
       <c r="E693" t="s">
+        <v>927</v>
+      </c>
+      <c r="F693" t="s">
         <v>963</v>
-      </c>
-      <c r="F693" t="s">
-        <v>928</v>
       </c>
     </row>
     <row r="694" spans="1:6">
@@ -18383,10 +18383,10 @@
         <v>926</v>
       </c>
       <c r="E694" t="s">
+        <v>927</v>
+      </c>
+      <c r="F694" t="s">
         <v>965</v>
-      </c>
-      <c r="F694" t="s">
-        <v>928</v>
       </c>
     </row>
     <row r="695" spans="1:6">
@@ -18463,10 +18463,10 @@
         <v>926</v>
       </c>
       <c r="E698" t="s">
+        <v>927</v>
+      </c>
+      <c r="F698" t="s">
         <v>970</v>
-      </c>
-      <c r="F698" t="s">
-        <v>928</v>
       </c>
     </row>
     <row r="699" spans="1:6">
@@ -18563,10 +18563,10 @@
         <v>974</v>
       </c>
       <c r="E703" t="s">
-        <v>975</v>
+        <v>981</v>
       </c>
       <c r="F703" t="s">
-        <v>981</v>
+        <v>976</v>
       </c>
     </row>
     <row r="704" spans="1:6">
@@ -18623,10 +18623,10 @@
         <v>974</v>
       </c>
       <c r="E706" t="s">
+        <v>927</v>
+      </c>
+      <c r="F706" t="s">
         <v>965</v>
-      </c>
-      <c r="F706" t="s">
-        <v>928</v>
       </c>
     </row>
     <row r="707" spans="1:6">
@@ -18723,10 +18723,10 @@
         <v>974</v>
       </c>
       <c r="E711" t="s">
+        <v>996</v>
+      </c>
+      <c r="F711" t="s">
         <v>952</v>
-      </c>
-      <c r="F711" t="s">
-        <v>996</v>
       </c>
     </row>
     <row r="712" spans="1:6">
@@ -18783,10 +18783,10 @@
         <v>974</v>
       </c>
       <c r="E714" t="s">
-        <v>983</v>
+        <v>979</v>
       </c>
       <c r="F714" t="s">
-        <v>978</v>
+        <v>984</v>
       </c>
     </row>
     <row r="715" spans="1:6">
@@ -18823,10 +18823,10 @@
         <v>974</v>
       </c>
       <c r="E716" t="s">
+        <v>1006</v>
+      </c>
+      <c r="F716" t="s">
         <v>965</v>
-      </c>
-      <c r="F716" t="s">
-        <v>1006</v>
       </c>
     </row>
     <row r="717" spans="1:6">
@@ -18843,10 +18843,10 @@
         <v>974</v>
       </c>
       <c r="E717" t="s">
+        <v>983</v>
+      </c>
+      <c r="F717" t="s">
         <v>1008</v>
-      </c>
-      <c r="F717" t="s">
-        <v>984</v>
       </c>
     </row>
     <row r="718" spans="1:6">
@@ -18863,10 +18863,10 @@
         <v>974</v>
       </c>
       <c r="E718" t="s">
+        <v>983</v>
+      </c>
+      <c r="F718" t="s">
         <v>1008</v>
-      </c>
-      <c r="F718" t="s">
-        <v>984</v>
       </c>
     </row>
     <row r="719" spans="1:6">
@@ -18883,10 +18883,10 @@
         <v>974</v>
       </c>
       <c r="E719" t="s">
+        <v>975</v>
+      </c>
+      <c r="F719" t="s">
         <v>1008</v>
-      </c>
-      <c r="F719" t="s">
-        <v>976</v>
       </c>
     </row>
     <row r="720" spans="1:6">
@@ -18943,10 +18943,10 @@
         <v>974</v>
       </c>
       <c r="E722" t="s">
+        <v>996</v>
+      </c>
+      <c r="F722" t="s">
         <v>965</v>
-      </c>
-      <c r="F722" t="s">
-        <v>996</v>
       </c>
     </row>
     <row r="723" spans="1:6">
@@ -18983,10 +18983,10 @@
         <v>974</v>
       </c>
       <c r="E724" t="s">
-        <v>975</v>
+        <v>1018</v>
       </c>
       <c r="F724" t="s">
-        <v>1018</v>
+        <v>976</v>
       </c>
     </row>
     <row r="725" spans="1:6">
@@ -19043,10 +19043,10 @@
         <v>974</v>
       </c>
       <c r="E727" t="s">
+        <v>998</v>
+      </c>
+      <c r="F727" t="s">
         <v>965</v>
-      </c>
-      <c r="F727" t="s">
-        <v>999</v>
       </c>
     </row>
     <row r="728" spans="1:6">
@@ -19063,10 +19063,10 @@
         <v>974</v>
       </c>
       <c r="E728" t="s">
-        <v>975</v>
+        <v>981</v>
       </c>
       <c r="F728" t="s">
-        <v>981</v>
+        <v>976</v>
       </c>
     </row>
     <row r="729" spans="1:6">
@@ -19083,10 +19083,10 @@
         <v>974</v>
       </c>
       <c r="E729" t="s">
+        <v>983</v>
+      </c>
+      <c r="F729" t="s">
         <v>1024</v>
-      </c>
-      <c r="F729" t="s">
-        <v>984</v>
       </c>
     </row>
     <row r="730" spans="1:6">
@@ -19363,10 +19363,10 @@
         <v>1032</v>
       </c>
       <c r="E743" t="s">
-        <v>1036</v>
+        <v>1046</v>
       </c>
       <c r="F743" t="s">
-        <v>1046</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="744" spans="1:6">
@@ -19423,10 +19423,10 @@
         <v>1032</v>
       </c>
       <c r="E746" t="s">
+        <v>983</v>
+      </c>
+      <c r="F746" t="s">
         <v>1052</v>
-      </c>
-      <c r="F746" t="s">
-        <v>984</v>
       </c>
     </row>
     <row r="747" spans="1:6">
@@ -19643,10 +19643,10 @@
         <v>1032</v>
       </c>
       <c r="E757" t="s">
+        <v>1071</v>
+      </c>
+      <c r="F757" t="s">
         <v>1078</v>
-      </c>
-      <c r="F757" t="s">
-        <v>1072</v>
       </c>
     </row>
     <row r="758" spans="1:6">
@@ -19683,10 +19683,10 @@
         <v>1032</v>
       </c>
       <c r="E759" t="s">
+        <v>1067</v>
+      </c>
+      <c r="F759" t="s">
         <v>1081</v>
-      </c>
-      <c r="F759" t="s">
-        <v>1068</v>
       </c>
     </row>
     <row r="760" spans="1:6">
@@ -19723,10 +19723,10 @@
         <v>1032</v>
       </c>
       <c r="E761" t="s">
-        <v>1039</v>
+        <v>1067</v>
       </c>
       <c r="F761" t="s">
-        <v>1068</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="762" spans="1:6">
@@ -19743,10 +19743,10 @@
         <v>1032</v>
       </c>
       <c r="E762" t="s">
-        <v>1039</v>
+        <v>1067</v>
       </c>
       <c r="F762" t="s">
-        <v>1068</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="763" spans="1:6">
@@ -19763,10 +19763,10 @@
         <v>1032</v>
       </c>
       <c r="E763" t="s">
+        <v>1036</v>
+      </c>
+      <c r="F763" t="s">
         <v>1086</v>
-      </c>
-      <c r="F763" t="s">
-        <v>1037</v>
       </c>
     </row>
     <row r="764" spans="1:6">
@@ -19823,10 +19823,10 @@
         <v>1032</v>
       </c>
       <c r="E766" t="s">
-        <v>1039</v>
+        <v>1067</v>
       </c>
       <c r="F766" t="s">
-        <v>1068</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="767" spans="1:6">
@@ -19923,10 +19923,10 @@
         <v>1032</v>
       </c>
       <c r="E771" t="s">
-        <v>1064</v>
+        <v>1067</v>
       </c>
       <c r="F771" t="s">
-        <v>1068</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="772" spans="1:6">
@@ -20003,10 +20003,10 @@
         <v>1100</v>
       </c>
       <c r="E775" t="s">
+        <v>1101</v>
+      </c>
+      <c r="F775" t="s">
         <v>1104</v>
-      </c>
-      <c r="F775" t="s">
-        <v>1102</v>
       </c>
     </row>
     <row r="776" spans="1:6">
@@ -20023,10 +20023,10 @@
         <v>1100</v>
       </c>
       <c r="E776" t="s">
+        <v>1101</v>
+      </c>
+      <c r="F776" t="s">
         <v>1104</v>
-      </c>
-      <c r="F776" t="s">
-        <v>1102</v>
       </c>
     </row>
     <row r="777" spans="1:6">
@@ -20043,10 +20043,10 @@
         <v>1100</v>
       </c>
       <c r="E777" t="s">
+        <v>1101</v>
+      </c>
+      <c r="F777" t="s">
         <v>1104</v>
-      </c>
-      <c r="F777" t="s">
-        <v>1102</v>
       </c>
     </row>
     <row r="778" spans="1:6">
@@ -20063,10 +20063,10 @@
         <v>1100</v>
       </c>
       <c r="E778" t="s">
+        <v>1101</v>
+      </c>
+      <c r="F778" t="s">
         <v>1104</v>
-      </c>
-      <c r="F778" t="s">
-        <v>1102</v>
       </c>
     </row>
     <row r="779" spans="1:6">
@@ -20083,10 +20083,10 @@
         <v>1100</v>
       </c>
       <c r="E779" t="s">
+        <v>1101</v>
+      </c>
+      <c r="F779" t="s">
         <v>1104</v>
-      </c>
-      <c r="F779" t="s">
-        <v>1102</v>
       </c>
     </row>
     <row r="780" spans="1:6">
@@ -20103,10 +20103,10 @@
         <v>1100</v>
       </c>
       <c r="E780" t="s">
+        <v>1101</v>
+      </c>
+      <c r="F780" t="s">
         <v>1104</v>
-      </c>
-      <c r="F780" t="s">
-        <v>1102</v>
       </c>
     </row>
     <row r="781" spans="1:6">
@@ -20163,10 +20163,10 @@
         <v>1100</v>
       </c>
       <c r="E783" t="s">
+        <v>1101</v>
+      </c>
+      <c r="F783" t="s">
         <v>1104</v>
-      </c>
-      <c r="F783" t="s">
-        <v>1102</v>
       </c>
     </row>
     <row r="784" spans="1:6">
@@ -20183,10 +20183,10 @@
         <v>1100</v>
       </c>
       <c r="E784" t="s">
+        <v>1101</v>
+      </c>
+      <c r="F784" t="s">
         <v>1104</v>
-      </c>
-      <c r="F784" t="s">
-        <v>1102</v>
       </c>
     </row>
     <row r="785" spans="1:6">
@@ -20223,10 +20223,10 @@
         <v>1100</v>
       </c>
       <c r="E786" t="s">
+        <v>1101</v>
+      </c>
+      <c r="F786" t="s">
         <v>1104</v>
-      </c>
-      <c r="F786" t="s">
-        <v>1102</v>
       </c>
     </row>
     <row r="787" spans="1:6">
@@ -20283,10 +20283,10 @@
         <v>1100</v>
       </c>
       <c r="E789" t="s">
+        <v>1101</v>
+      </c>
+      <c r="F789" t="s">
         <v>1127</v>
-      </c>
-      <c r="F789" t="s">
-        <v>1102</v>
       </c>
     </row>
     <row r="790" spans="1:6">
@@ -20323,10 +20323,10 @@
         <v>1100</v>
       </c>
       <c r="E791" t="s">
+        <v>1101</v>
+      </c>
+      <c r="F791" t="s">
         <v>1104</v>
-      </c>
-      <c r="F791" t="s">
-        <v>1102</v>
       </c>
     </row>
     <row r="792" spans="1:6">
@@ -20343,10 +20343,10 @@
         <v>1100</v>
       </c>
       <c r="E792" t="s">
+        <v>1101</v>
+      </c>
+      <c r="F792" t="s">
         <v>1133</v>
-      </c>
-      <c r="F792" t="s">
-        <v>1102</v>
       </c>
     </row>
     <row r="793" spans="1:6">
@@ -20363,10 +20363,10 @@
         <v>1100</v>
       </c>
       <c r="E793" t="s">
+        <v>1101</v>
+      </c>
+      <c r="F793" t="s">
         <v>1104</v>
-      </c>
-      <c r="F793" t="s">
-        <v>1102</v>
       </c>
     </row>
     <row r="794" spans="1:6">
@@ -20383,10 +20383,10 @@
         <v>1100</v>
       </c>
       <c r="E794" t="s">
+        <v>1039</v>
+      </c>
+      <c r="F794" t="s">
         <v>1136</v>
-      </c>
-      <c r="F794" t="s">
-        <v>1040</v>
       </c>
     </row>
     <row r="795" spans="1:6">
@@ -20403,10 +20403,10 @@
         <v>1100</v>
       </c>
       <c r="E795" t="s">
+        <v>1101</v>
+      </c>
+      <c r="F795" t="s">
         <v>1104</v>
-      </c>
-      <c r="F795" t="s">
-        <v>1102</v>
       </c>
     </row>
     <row r="796" spans="1:6">
@@ -20423,10 +20423,10 @@
         <v>1100</v>
       </c>
       <c r="E796" t="s">
+        <v>1101</v>
+      </c>
+      <c r="F796" t="s">
         <v>1104</v>
-      </c>
-      <c r="F796" t="s">
-        <v>1102</v>
       </c>
     </row>
     <row r="797" spans="1:6">
@@ -20463,10 +20463,10 @@
         <v>1100</v>
       </c>
       <c r="E798" t="s">
+        <v>1101</v>
+      </c>
+      <c r="F798" t="s">
         <v>1143</v>
-      </c>
-      <c r="F798" t="s">
-        <v>1102</v>
       </c>
     </row>
     <row r="799" spans="1:6">
@@ -20483,10 +20483,10 @@
         <v>1100</v>
       </c>
       <c r="E799" t="s">
+        <v>1101</v>
+      </c>
+      <c r="F799" t="s">
         <v>1104</v>
-      </c>
-      <c r="F799" t="s">
-        <v>1102</v>
       </c>
     </row>
     <row r="800" spans="1:6">
@@ -20523,10 +20523,10 @@
         <v>1100</v>
       </c>
       <c r="E801" t="s">
+        <v>1101</v>
+      </c>
+      <c r="F801" t="s">
         <v>1147</v>
-      </c>
-      <c r="F801" t="s">
-        <v>1102</v>
       </c>
     </row>
     <row r="802" spans="1:6">
@@ -20543,10 +20543,10 @@
         <v>1100</v>
       </c>
       <c r="E802" t="s">
+        <v>1101</v>
+      </c>
+      <c r="F802" t="s">
         <v>1104</v>
-      </c>
-      <c r="F802" t="s">
-        <v>1102</v>
       </c>
     </row>
     <row r="803" spans="1:6">
@@ -20563,10 +20563,10 @@
         <v>1100</v>
       </c>
       <c r="E803" t="s">
+        <v>1101</v>
+      </c>
+      <c r="F803" t="s">
         <v>1104</v>
-      </c>
-      <c r="F803" t="s">
-        <v>1102</v>
       </c>
     </row>
     <row r="804" spans="1:6">
@@ -20583,10 +20583,10 @@
         <v>1100</v>
       </c>
       <c r="E804" t="s">
+        <v>1101</v>
+      </c>
+      <c r="F804" t="s">
         <v>1104</v>
-      </c>
-      <c r="F804" t="s">
-        <v>1102</v>
       </c>
     </row>
     <row r="805" spans="1:6">
@@ -20603,10 +20603,10 @@
         <v>1100</v>
       </c>
       <c r="E805" t="s">
+        <v>1101</v>
+      </c>
+      <c r="F805" t="s">
         <v>1104</v>
-      </c>
-      <c r="F805" t="s">
-        <v>1102</v>
       </c>
     </row>
     <row r="806" spans="1:6">
@@ -20623,10 +20623,10 @@
         <v>1100</v>
       </c>
       <c r="E806" t="s">
+        <v>1101</v>
+      </c>
+      <c r="F806" t="s">
         <v>1104</v>
-      </c>
-      <c r="F806" t="s">
-        <v>1102</v>
       </c>
     </row>
     <row r="807" spans="1:6">
@@ -20803,10 +20803,10 @@
         <v>1154</v>
       </c>
       <c r="E815" t="s">
-        <v>1155</v>
+        <v>1158</v>
       </c>
       <c r="F815" t="s">
-        <v>1159</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="816" spans="1:6">
@@ -20823,10 +20823,10 @@
         <v>1154</v>
       </c>
       <c r="E816" t="s">
+        <v>1161</v>
+      </c>
+      <c r="F816" t="s">
         <v>1133</v>
-      </c>
-      <c r="F816" t="s">
-        <v>1162</v>
       </c>
     </row>
     <row r="817" spans="1:6">
@@ -20863,10 +20863,10 @@
         <v>1154</v>
       </c>
       <c r="E818" t="s">
-        <v>1161</v>
+        <v>1155</v>
       </c>
       <c r="F818" t="s">
-        <v>1156</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="819" spans="1:6">
@@ -20903,10 +20903,10 @@
         <v>1154</v>
       </c>
       <c r="E820" t="s">
+        <v>1174</v>
+      </c>
+      <c r="F820" t="s">
         <v>1133</v>
-      </c>
-      <c r="F820" t="s">
-        <v>1174</v>
       </c>
     </row>
     <row r="821" spans="1:6">
@@ -20963,10 +20963,10 @@
         <v>1154</v>
       </c>
       <c r="E823" t="s">
-        <v>1161</v>
+        <v>1155</v>
       </c>
       <c r="F823" t="s">
-        <v>1156</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="824" spans="1:6">
@@ -20983,10 +20983,10 @@
         <v>1154</v>
       </c>
       <c r="E824" t="s">
+        <v>1174</v>
+      </c>
+      <c r="F824" t="s">
         <v>1181</v>
-      </c>
-      <c r="F824" t="s">
-        <v>1174</v>
       </c>
     </row>
     <row r="825" spans="1:6">
@@ -21243,10 +21243,10 @@
         <v>1200</v>
       </c>
       <c r="E837" t="s">
+        <v>1201</v>
+      </c>
+      <c r="F837" t="s">
         <v>1204</v>
-      </c>
-      <c r="F837" t="s">
-        <v>1202</v>
       </c>
     </row>
     <row r="838" spans="1:6">
@@ -21303,10 +21303,10 @@
         <v>1200</v>
       </c>
       <c r="E840" t="s">
+        <v>1201</v>
+      </c>
+      <c r="F840" t="s">
         <v>1204</v>
-      </c>
-      <c r="F840" t="s">
-        <v>1202</v>
       </c>
     </row>
     <row r="841" spans="1:6">
@@ -21323,10 +21323,10 @@
         <v>1200</v>
       </c>
       <c r="E841" t="s">
+        <v>1201</v>
+      </c>
+      <c r="F841" t="s">
         <v>1204</v>
-      </c>
-      <c r="F841" t="s">
-        <v>1202</v>
       </c>
     </row>
     <row r="842" spans="1:6">
@@ -21343,10 +21343,10 @@
         <v>1200</v>
       </c>
       <c r="E842" t="s">
+        <v>1201</v>
+      </c>
+      <c r="F842" t="s">
         <v>1214</v>
-      </c>
-      <c r="F842" t="s">
-        <v>1202</v>
       </c>
     </row>
     <row r="843" spans="1:6">
@@ -21363,10 +21363,10 @@
         <v>1200</v>
       </c>
       <c r="E843" t="s">
+        <v>1201</v>
+      </c>
+      <c r="F843" t="s">
         <v>1204</v>
-      </c>
-      <c r="F843" t="s">
-        <v>1202</v>
       </c>
     </row>
     <row r="844" spans="1:6">
@@ -21383,10 +21383,10 @@
         <v>1200</v>
       </c>
       <c r="E844" t="s">
+        <v>1201</v>
+      </c>
+      <c r="F844" t="s">
         <v>1204</v>
-      </c>
-      <c r="F844" t="s">
-        <v>1202</v>
       </c>
     </row>
     <row r="845" spans="1:6">
@@ -21403,10 +21403,10 @@
         <v>1200</v>
       </c>
       <c r="E845" t="s">
+        <v>1201</v>
+      </c>
+      <c r="F845" t="s">
         <v>1204</v>
-      </c>
-      <c r="F845" t="s">
-        <v>1202</v>
       </c>
     </row>
     <row r="846" spans="1:6">
@@ -21423,10 +21423,10 @@
         <v>1200</v>
       </c>
       <c r="E846" t="s">
+        <v>1201</v>
+      </c>
+      <c r="F846" t="s">
         <v>1204</v>
-      </c>
-      <c r="F846" t="s">
-        <v>1202</v>
       </c>
     </row>
     <row r="847" spans="1:6">
@@ -21443,10 +21443,10 @@
         <v>1200</v>
       </c>
       <c r="E847" t="s">
+        <v>1201</v>
+      </c>
+      <c r="F847" t="s">
         <v>1204</v>
-      </c>
-      <c r="F847" t="s">
-        <v>1202</v>
       </c>
     </row>
     <row r="848" spans="1:6">
@@ -21463,10 +21463,10 @@
         <v>1200</v>
       </c>
       <c r="E848" t="s">
+        <v>1201</v>
+      </c>
+      <c r="F848" t="s">
         <v>1204</v>
-      </c>
-      <c r="F848" t="s">
-        <v>1202</v>
       </c>
     </row>
     <row r="849" spans="1:6">
@@ -21483,10 +21483,10 @@
         <v>1200</v>
       </c>
       <c r="E849" t="s">
+        <v>1201</v>
+      </c>
+      <c r="F849" t="s">
         <v>1204</v>
-      </c>
-      <c r="F849" t="s">
-        <v>1202</v>
       </c>
     </row>
     <row r="850" spans="1:6">
@@ -21503,10 +21503,10 @@
         <v>1200</v>
       </c>
       <c r="E850" t="s">
-        <v>1201</v>
+        <v>1223</v>
       </c>
       <c r="F850" t="s">
-        <v>1223</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="851" spans="1:6">
@@ -21523,10 +21523,10 @@
         <v>1200</v>
       </c>
       <c r="E851" t="s">
+        <v>1201</v>
+      </c>
+      <c r="F851" t="s">
         <v>1204</v>
-      </c>
-      <c r="F851" t="s">
-        <v>1202</v>
       </c>
     </row>
     <row r="852" spans="1:6">
@@ -21543,10 +21543,10 @@
         <v>1200</v>
       </c>
       <c r="E852" t="s">
+        <v>1226</v>
+      </c>
+      <c r="F852" t="s">
         <v>1214</v>
-      </c>
-      <c r="F852" t="s">
-        <v>1226</v>
       </c>
     </row>
     <row r="853" spans="1:6">
@@ -21563,10 +21563,10 @@
         <v>1200</v>
       </c>
       <c r="E853" t="s">
+        <v>1223</v>
+      </c>
+      <c r="F853" t="s">
         <v>1228</v>
-      </c>
-      <c r="F853" t="s">
-        <v>1223</v>
       </c>
     </row>
     <row r="854" spans="1:6">
@@ -21583,10 +21583,10 @@
         <v>1200</v>
       </c>
       <c r="E854" t="s">
+        <v>1201</v>
+      </c>
+      <c r="F854" t="s">
         <v>1204</v>
-      </c>
-      <c r="F854" t="s">
-        <v>1202</v>
       </c>
     </row>
     <row r="855" spans="1:6">
@@ -21603,10 +21603,10 @@
         <v>1200</v>
       </c>
       <c r="E855" t="s">
+        <v>1231</v>
+      </c>
+      <c r="F855" t="s">
         <v>1204</v>
-      </c>
-      <c r="F855" t="s">
-        <v>1231</v>
       </c>
     </row>
     <row r="856" spans="1:6">
@@ -21623,10 +21623,10 @@
         <v>1200</v>
       </c>
       <c r="E856" t="s">
+        <v>1201</v>
+      </c>
+      <c r="F856" t="s">
         <v>1233</v>
-      </c>
-      <c r="F856" t="s">
-        <v>1202</v>
       </c>
     </row>
     <row r="857" spans="1:6">
@@ -21643,10 +21643,10 @@
         <v>1200</v>
       </c>
       <c r="E857" t="s">
+        <v>1201</v>
+      </c>
+      <c r="F857" t="s">
         <v>1204</v>
-      </c>
-      <c r="F857" t="s">
-        <v>1202</v>
       </c>
     </row>
     <row r="858" spans="1:6">
@@ -21703,10 +21703,10 @@
         <v>1200</v>
       </c>
       <c r="E860" t="s">
+        <v>1201</v>
+      </c>
+      <c r="F860" t="s">
         <v>1204</v>
-      </c>
-      <c r="F860" t="s">
-        <v>1202</v>
       </c>
     </row>
     <row r="861" spans="1:6">
@@ -21723,10 +21723,10 @@
         <v>1200</v>
       </c>
       <c r="E861" t="s">
+        <v>1201</v>
+      </c>
+      <c r="F861" t="s">
         <v>1204</v>
-      </c>
-      <c r="F861" t="s">
-        <v>1202</v>
       </c>
     </row>
     <row r="862" spans="1:6">
@@ -21743,10 +21743,10 @@
         <v>1200</v>
       </c>
       <c r="E862" t="s">
+        <v>1201</v>
+      </c>
+      <c r="F862" t="s">
         <v>1204</v>
-      </c>
-      <c r="F862" t="s">
-        <v>1202</v>
       </c>
     </row>
     <row r="863" spans="1:6">
@@ -21763,10 +21763,10 @@
         <v>1200</v>
       </c>
       <c r="E863" t="s">
+        <v>1201</v>
+      </c>
+      <c r="F863" t="s">
         <v>1204</v>
-      </c>
-      <c r="F863" t="s">
-        <v>1202</v>
       </c>
     </row>
     <row r="864" spans="1:6">
@@ -21783,10 +21783,10 @@
         <v>1200</v>
       </c>
       <c r="E864" t="s">
+        <v>1201</v>
+      </c>
+      <c r="F864" t="s">
         <v>1204</v>
-      </c>
-      <c r="F864" t="s">
-        <v>1202</v>
       </c>
     </row>
     <row r="865" spans="1:6">
@@ -21803,10 +21803,10 @@
         <v>1200</v>
       </c>
       <c r="E865" t="s">
+        <v>1201</v>
+      </c>
+      <c r="F865" t="s">
         <v>1204</v>
-      </c>
-      <c r="F865" t="s">
-        <v>1202</v>
       </c>
     </row>
     <row r="866" spans="1:6">
@@ -21823,10 +21823,10 @@
         <v>1200</v>
       </c>
       <c r="E866" t="s">
+        <v>1201</v>
+      </c>
+      <c r="F866" t="s">
         <v>1204</v>
-      </c>
-      <c r="F866" t="s">
-        <v>1202</v>
       </c>
     </row>
     <row r="867" spans="1:6">
@@ -21843,10 +21843,10 @@
         <v>1200</v>
       </c>
       <c r="E867" t="s">
+        <v>1201</v>
+      </c>
+      <c r="F867" t="s">
         <v>1204</v>
-      </c>
-      <c r="F867" t="s">
-        <v>1202</v>
       </c>
     </row>
     <row r="868" spans="1:6">
@@ -21863,10 +21863,10 @@
         <v>1200</v>
       </c>
       <c r="E868" t="s">
+        <v>1201</v>
+      </c>
+      <c r="F868" t="s">
         <v>1204</v>
-      </c>
-      <c r="F868" t="s">
-        <v>1202</v>
       </c>
     </row>
     <row r="869" spans="1:6">
@@ -22003,10 +22003,10 @@
         <v>1251</v>
       </c>
       <c r="E875" t="s">
-        <v>1258</v>
+        <v>1252</v>
       </c>
       <c r="F875" t="s">
-        <v>1253</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="876" spans="1:6">
@@ -22043,10 +22043,10 @@
         <v>1251</v>
       </c>
       <c r="E877" t="s">
-        <v>1258</v>
+        <v>1252</v>
       </c>
       <c r="F877" t="s">
-        <v>1253</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="878" spans="1:6">
@@ -22243,10 +22243,10 @@
         <v>1251</v>
       </c>
       <c r="E887" t="s">
-        <v>1278</v>
+        <v>1252</v>
       </c>
       <c r="F887" t="s">
-        <v>1253</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="888" spans="1:6">
@@ -22363,10 +22363,10 @@
         <v>1251</v>
       </c>
       <c r="E893" t="s">
-        <v>1278</v>
+        <v>1252</v>
       </c>
       <c r="F893" t="s">
-        <v>1253</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="894" spans="1:6">
@@ -22403,10 +22403,10 @@
         <v>1251</v>
       </c>
       <c r="E895" t="s">
-        <v>1258</v>
+        <v>1252</v>
       </c>
       <c r="F895" t="s">
-        <v>1253</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="896" spans="1:6">
@@ -22423,10 +22423,10 @@
         <v>1251</v>
       </c>
       <c r="E896" t="s">
-        <v>1258</v>
+        <v>1252</v>
       </c>
       <c r="F896" t="s">
-        <v>1253</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="897" spans="1:6">
@@ -22623,10 +22623,10 @@
         <v>1299</v>
       </c>
       <c r="E906" t="s">
+        <v>1300</v>
+      </c>
+      <c r="F906" t="s">
         <v>1303</v>
-      </c>
-      <c r="F906" t="s">
-        <v>1301</v>
       </c>
     </row>
     <row r="907" spans="1:6">
@@ -22643,10 +22643,10 @@
         <v>1299</v>
       </c>
       <c r="E907" t="s">
+        <v>1300</v>
+      </c>
+      <c r="F907" t="s">
         <v>1303</v>
-      </c>
-      <c r="F907" t="s">
-        <v>1301</v>
       </c>
     </row>
     <row r="908" spans="1:6">
@@ -22663,10 +22663,10 @@
         <v>1299</v>
       </c>
       <c r="E908" t="s">
+        <v>1300</v>
+      </c>
+      <c r="F908" t="s">
         <v>1303</v>
-      </c>
-      <c r="F908" t="s">
-        <v>1301</v>
       </c>
     </row>
     <row r="909" spans="1:6">
@@ -22683,10 +22683,10 @@
         <v>1299</v>
       </c>
       <c r="E909" t="s">
+        <v>1300</v>
+      </c>
+      <c r="F909" t="s">
         <v>1303</v>
-      </c>
-      <c r="F909" t="s">
-        <v>1301</v>
       </c>
     </row>
     <row r="910" spans="1:6">
@@ -22703,10 +22703,10 @@
         <v>1299</v>
       </c>
       <c r="E910" t="s">
+        <v>1300</v>
+      </c>
+      <c r="F910" t="s">
         <v>1303</v>
-      </c>
-      <c r="F910" t="s">
-        <v>1301</v>
       </c>
     </row>
     <row r="911" spans="1:6">
@@ -22723,10 +22723,10 @@
         <v>1299</v>
       </c>
       <c r="E911" t="s">
+        <v>1300</v>
+      </c>
+      <c r="F911" t="s">
         <v>1303</v>
-      </c>
-      <c r="F911" t="s">
-        <v>1301</v>
       </c>
     </row>
     <row r="912" spans="1:6">
@@ -22743,10 +22743,10 @@
         <v>1299</v>
       </c>
       <c r="E912" t="s">
+        <v>1300</v>
+      </c>
+      <c r="F912" t="s">
         <v>1303</v>
-      </c>
-      <c r="F912" t="s">
-        <v>1301</v>
       </c>
     </row>
     <row r="913" spans="1:6">
@@ -22763,10 +22763,10 @@
         <v>1299</v>
       </c>
       <c r="E913" t="s">
+        <v>1300</v>
+      </c>
+      <c r="F913" t="s">
         <v>1303</v>
-      </c>
-      <c r="F913" t="s">
-        <v>1301</v>
       </c>
     </row>
     <row r="914" spans="1:6">
@@ -22783,10 +22783,10 @@
         <v>1299</v>
       </c>
       <c r="E914" t="s">
+        <v>1258</v>
+      </c>
+      <c r="F914" t="s">
         <v>1312</v>
-      </c>
-      <c r="F914" t="s">
-        <v>1259</v>
       </c>
     </row>
     <row r="915" spans="1:6">
@@ -22803,10 +22803,10 @@
         <v>1299</v>
       </c>
       <c r="E915" t="s">
+        <v>1258</v>
+      </c>
+      <c r="F915" t="s">
         <v>1312</v>
-      </c>
-      <c r="F915" t="s">
-        <v>1259</v>
       </c>
     </row>
     <row r="916" spans="1:6">
@@ -22823,10 +22823,10 @@
         <v>1299</v>
       </c>
       <c r="E916" t="s">
+        <v>1258</v>
+      </c>
+      <c r="F916" t="s">
         <v>1312</v>
-      </c>
-      <c r="F916" t="s">
-        <v>1259</v>
       </c>
     </row>
     <row r="917" spans="1:6">
@@ -22843,10 +22843,10 @@
         <v>1299</v>
       </c>
       <c r="E917" t="s">
+        <v>1258</v>
+      </c>
+      <c r="F917" t="s">
         <v>1312</v>
-      </c>
-      <c r="F917" t="s">
-        <v>1259</v>
       </c>
     </row>
     <row r="918" spans="1:6">
@@ -22863,10 +22863,10 @@
         <v>1299</v>
       </c>
       <c r="E918" t="s">
+        <v>1317</v>
+      </c>
+      <c r="F918" t="s">
         <v>1312</v>
-      </c>
-      <c r="F918" t="s">
-        <v>1317</v>
       </c>
     </row>
     <row r="919" spans="1:6">
@@ -22883,10 +22883,10 @@
         <v>1299</v>
       </c>
       <c r="E919" t="s">
+        <v>1258</v>
+      </c>
+      <c r="F919" t="s">
         <v>1312</v>
-      </c>
-      <c r="F919" t="s">
-        <v>1259</v>
       </c>
     </row>
     <row r="920" spans="1:6">
@@ -22903,10 +22903,10 @@
         <v>1299</v>
       </c>
       <c r="E920" t="s">
+        <v>1258</v>
+      </c>
+      <c r="F920" t="s">
         <v>1312</v>
-      </c>
-      <c r="F920" t="s">
-        <v>1259</v>
       </c>
     </row>
     <row r="921" spans="1:6">
@@ -22923,10 +22923,10 @@
         <v>1299</v>
       </c>
       <c r="E921" t="s">
+        <v>1300</v>
+      </c>
+      <c r="F921" t="s">
         <v>1303</v>
-      </c>
-      <c r="F921" t="s">
-        <v>1301</v>
       </c>
     </row>
     <row r="922" spans="1:6">
@@ -22943,10 +22943,10 @@
         <v>1299</v>
       </c>
       <c r="E922" t="s">
+        <v>1300</v>
+      </c>
+      <c r="F922" t="s">
         <v>1303</v>
-      </c>
-      <c r="F922" t="s">
-        <v>1301</v>
       </c>
     </row>
     <row r="923" spans="1:6">
@@ -22963,10 +22963,10 @@
         <v>1299</v>
       </c>
       <c r="E923" t="s">
+        <v>1300</v>
+      </c>
+      <c r="F923" t="s">
         <v>1303</v>
-      </c>
-      <c r="F923" t="s">
-        <v>1301</v>
       </c>
     </row>
     <row r="924" spans="1:6">
@@ -22983,10 +22983,10 @@
         <v>1299</v>
       </c>
       <c r="E924" t="s">
+        <v>1300</v>
+      </c>
+      <c r="F924" t="s">
         <v>1303</v>
-      </c>
-      <c r="F924" t="s">
-        <v>1301</v>
       </c>
     </row>
     <row r="925" spans="1:6">
@@ -23003,10 +23003,10 @@
         <v>1299</v>
       </c>
       <c r="E925" t="s">
+        <v>1300</v>
+      </c>
+      <c r="F925" t="s">
         <v>1303</v>
-      </c>
-      <c r="F925" t="s">
-        <v>1301</v>
       </c>
     </row>
     <row r="926" spans="1:6">
@@ -23023,10 +23023,10 @@
         <v>1299</v>
       </c>
       <c r="E926" t="s">
+        <v>1300</v>
+      </c>
+      <c r="F926" t="s">
         <v>1303</v>
-      </c>
-      <c r="F926" t="s">
-        <v>1301</v>
       </c>
     </row>
     <row r="927" spans="1:6">
@@ -23043,10 +23043,10 @@
         <v>1299</v>
       </c>
       <c r="E927" t="s">
+        <v>1300</v>
+      </c>
+      <c r="F927" t="s">
         <v>1303</v>
-      </c>
-      <c r="F927" t="s">
-        <v>1301</v>
       </c>
     </row>
     <row r="928" spans="1:6">
@@ -23063,10 +23063,10 @@
         <v>1299</v>
       </c>
       <c r="E928" t="s">
+        <v>1300</v>
+      </c>
+      <c r="F928" t="s">
         <v>1303</v>
-      </c>
-      <c r="F928" t="s">
-        <v>1301</v>
       </c>
     </row>
     <row r="929" spans="1:6">
@@ -23083,10 +23083,10 @@
         <v>1299</v>
       </c>
       <c r="E929" t="s">
+        <v>1300</v>
+      </c>
+      <c r="F929" t="s">
         <v>1303</v>
-      </c>
-      <c r="F929" t="s">
-        <v>1301</v>
       </c>
     </row>
     <row r="930" spans="1:6">
@@ -23103,10 +23103,10 @@
         <v>1299</v>
       </c>
       <c r="E930" t="s">
+        <v>1300</v>
+      </c>
+      <c r="F930" t="s">
         <v>1303</v>
-      </c>
-      <c r="F930" t="s">
-        <v>1301</v>
       </c>
     </row>
     <row r="931" spans="1:6">
@@ -23123,10 +23123,10 @@
         <v>1299</v>
       </c>
       <c r="E931" t="s">
+        <v>1300</v>
+      </c>
+      <c r="F931" t="s">
         <v>1303</v>
-      </c>
-      <c r="F931" t="s">
-        <v>1301</v>
       </c>
     </row>
     <row r="932" spans="1:6">
@@ -23143,10 +23143,10 @@
         <v>1299</v>
       </c>
       <c r="E932" t="s">
+        <v>1300</v>
+      </c>
+      <c r="F932" t="s">
         <v>1303</v>
-      </c>
-      <c r="F932" t="s">
-        <v>1301</v>
       </c>
     </row>
     <row r="933" spans="1:6">
@@ -23163,10 +23163,10 @@
         <v>1299</v>
       </c>
       <c r="E933" t="s">
+        <v>1300</v>
+      </c>
+      <c r="F933" t="s">
         <v>1303</v>
-      </c>
-      <c r="F933" t="s">
-        <v>1301</v>
       </c>
     </row>
     <row r="934" spans="1:6">
@@ -23183,10 +23183,10 @@
         <v>1299</v>
       </c>
       <c r="E934" t="s">
+        <v>1300</v>
+      </c>
+      <c r="F934" t="s">
         <v>1303</v>
-      </c>
-      <c r="F934" t="s">
-        <v>1301</v>
       </c>
     </row>
     <row r="935" spans="1:6">
@@ -23223,10 +23223,10 @@
         <v>1335</v>
       </c>
       <c r="E936" t="s">
-        <v>1336</v>
+        <v>1339</v>
       </c>
       <c r="F936" t="s">
-        <v>1339</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="937" spans="1:6">
@@ -23243,10 +23243,10 @@
         <v>1335</v>
       </c>
       <c r="E937" t="s">
-        <v>1336</v>
+        <v>1339</v>
       </c>
       <c r="F937" t="s">
-        <v>1339</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="938" spans="1:6">
@@ -23263,10 +23263,10 @@
         <v>1335</v>
       </c>
       <c r="E938" t="s">
-        <v>1336</v>
+        <v>1339</v>
       </c>
       <c r="F938" t="s">
-        <v>1339</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="939" spans="1:6">
@@ -23283,10 +23283,10 @@
         <v>1335</v>
       </c>
       <c r="E939" t="s">
-        <v>1336</v>
+        <v>1339</v>
       </c>
       <c r="F939" t="s">
-        <v>1339</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="940" spans="1:6">
@@ -23303,10 +23303,10 @@
         <v>1335</v>
       </c>
       <c r="E940" t="s">
-        <v>1336</v>
+        <v>1339</v>
       </c>
       <c r="F940" t="s">
-        <v>1339</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="941" spans="1:6">
@@ -23323,10 +23323,10 @@
         <v>1335</v>
       </c>
       <c r="E941" t="s">
-        <v>1336</v>
+        <v>1339</v>
       </c>
       <c r="F941" t="s">
-        <v>1339</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="942" spans="1:6">
@@ -23343,10 +23343,10 @@
         <v>1335</v>
       </c>
       <c r="E942" t="s">
-        <v>1336</v>
+        <v>1339</v>
       </c>
       <c r="F942" t="s">
-        <v>1339</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="943" spans="1:6">
@@ -23363,10 +23363,10 @@
         <v>1335</v>
       </c>
       <c r="E943" t="s">
-        <v>1336</v>
+        <v>1339</v>
       </c>
       <c r="F943" t="s">
-        <v>1339</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="944" spans="1:6">
@@ -23383,10 +23383,10 @@
         <v>1335</v>
       </c>
       <c r="E944" t="s">
-        <v>1336</v>
+        <v>1339</v>
       </c>
       <c r="F944" t="s">
-        <v>1339</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="945" spans="1:6">
@@ -23403,10 +23403,10 @@
         <v>1335</v>
       </c>
       <c r="E945" t="s">
-        <v>1336</v>
+        <v>1339</v>
       </c>
       <c r="F945" t="s">
-        <v>1339</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="946" spans="1:6">
@@ -23423,10 +23423,10 @@
         <v>1335</v>
       </c>
       <c r="E946" t="s">
-        <v>1336</v>
+        <v>1339</v>
       </c>
       <c r="F946" t="s">
-        <v>1339</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="947" spans="1:6">
@@ -23443,10 +23443,10 @@
         <v>1335</v>
       </c>
       <c r="E947" t="s">
-        <v>1336</v>
+        <v>1339</v>
       </c>
       <c r="F947" t="s">
-        <v>1339</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="948" spans="1:6">
@@ -23463,10 +23463,10 @@
         <v>1335</v>
       </c>
       <c r="E948" t="s">
-        <v>1336</v>
+        <v>1339</v>
       </c>
       <c r="F948" t="s">
-        <v>1339</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="949" spans="1:6">
@@ -23483,10 +23483,10 @@
         <v>1335</v>
       </c>
       <c r="E949" t="s">
-        <v>1336</v>
+        <v>1339</v>
       </c>
       <c r="F949" t="s">
-        <v>1339</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="950" spans="1:6">
@@ -23503,10 +23503,10 @@
         <v>1335</v>
       </c>
       <c r="E950" t="s">
-        <v>1336</v>
+        <v>1339</v>
       </c>
       <c r="F950" t="s">
-        <v>1339</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="951" spans="1:6">
@@ -23523,10 +23523,10 @@
         <v>1335</v>
       </c>
       <c r="E951" t="s">
-        <v>1336</v>
+        <v>1339</v>
       </c>
       <c r="F951" t="s">
-        <v>1339</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="952" spans="1:6">
@@ -23543,10 +23543,10 @@
         <v>1335</v>
       </c>
       <c r="E952" t="s">
-        <v>1336</v>
+        <v>1339</v>
       </c>
       <c r="F952" t="s">
-        <v>1339</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="953" spans="1:6">
@@ -23563,10 +23563,10 @@
         <v>1335</v>
       </c>
       <c r="E953" t="s">
-        <v>1336</v>
+        <v>1339</v>
       </c>
       <c r="F953" t="s">
-        <v>1339</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="954" spans="1:6">
@@ -23583,10 +23583,10 @@
         <v>1335</v>
       </c>
       <c r="E954" t="s">
-        <v>1336</v>
+        <v>1339</v>
       </c>
       <c r="F954" t="s">
-        <v>1339</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="955" spans="1:6">
@@ -23603,10 +23603,10 @@
         <v>1335</v>
       </c>
       <c r="E955" t="s">
-        <v>1336</v>
+        <v>1339</v>
       </c>
       <c r="F955" t="s">
-        <v>1339</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="956" spans="1:6">
@@ -23623,10 +23623,10 @@
         <v>1335</v>
       </c>
       <c r="E956" t="s">
-        <v>1336</v>
+        <v>1339</v>
       </c>
       <c r="F956" t="s">
-        <v>1339</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="957" spans="1:6">
@@ -23643,10 +23643,10 @@
         <v>1335</v>
       </c>
       <c r="E957" t="s">
-        <v>1336</v>
+        <v>1339</v>
       </c>
       <c r="F957" t="s">
-        <v>1339</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="958" spans="1:6">
@@ -23663,10 +23663,10 @@
         <v>1335</v>
       </c>
       <c r="E958" t="s">
-        <v>1336</v>
+        <v>1339</v>
       </c>
       <c r="F958" t="s">
-        <v>1339</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="959" spans="1:6">
@@ -23783,10 +23783,10 @@
         <v>1363</v>
       </c>
       <c r="E964" t="s">
+        <v>1364</v>
+      </c>
+      <c r="F964" t="s">
         <v>1371</v>
-      </c>
-      <c r="F964" t="s">
-        <v>1365</v>
       </c>
     </row>
     <row r="965" spans="1:6">
@@ -23803,10 +23803,10 @@
         <v>1363</v>
       </c>
       <c r="E965" t="s">
+        <v>1364</v>
+      </c>
+      <c r="F965" t="s">
         <v>1371</v>
-      </c>
-      <c r="F965" t="s">
-        <v>1365</v>
       </c>
     </row>
     <row r="966" spans="1:6">
@@ -23983,10 +23983,10 @@
         <v>1363</v>
       </c>
       <c r="E974" t="s">
+        <v>1364</v>
+      </c>
+      <c r="F974" t="s">
         <v>1382</v>
-      </c>
-      <c r="F974" t="s">
-        <v>1365</v>
       </c>
     </row>
     <row r="975" spans="1:6">
@@ -24023,10 +24023,10 @@
         <v>1363</v>
       </c>
       <c r="E976" t="s">
+        <v>1364</v>
+      </c>
+      <c r="F976" t="s">
         <v>1385</v>
-      </c>
-      <c r="F976" t="s">
-        <v>1365</v>
       </c>
     </row>
     <row r="977" spans="1:6">
@@ -24043,10 +24043,10 @@
         <v>1363</v>
       </c>
       <c r="E977" t="s">
+        <v>1364</v>
+      </c>
+      <c r="F977" t="s">
         <v>1382</v>
-      </c>
-      <c r="F977" t="s">
-        <v>1365</v>
       </c>
     </row>
   </sheetData>

--- a/api/1/clv3/xlsx/fr/HumanitarianPlan.xlsx
+++ b/api/1/clv3/xlsx/fr/HumanitarianPlan.xlsx
@@ -25,15 +25,15 @@
     <t>codeforiati:plan-type</t>
   </si>
   <si>
+    <t>codeforiati:plan-end-date</t>
+  </si>
+  <si>
+    <t>codeforiati:plan-start-date</t>
+  </si>
+  <si>
     <t>codeforiati:plan-year</t>
   </si>
   <si>
-    <t>codeforiati:plan-end-date</t>
-  </si>
-  <si>
-    <t>codeforiati:plan-start-date</t>
-  </si>
-  <si>
     <t>HAFG26</t>
   </si>
   <si>
@@ -43,15 +43,15 @@
     <t>Humanitarian needs and response plan</t>
   </si>
   <si>
+    <t>2026-12-31</t>
+  </si>
+  <si>
+    <t>2026-01-01</t>
+  </si>
+  <si>
     <t>2026</t>
   </si>
   <si>
-    <t>2026-12-31</t>
-  </si>
-  <si>
-    <t>2026-01-01</t>
-  </si>
-  <si>
     <t>HBFA26</t>
   </si>
   <si>
@@ -190,15 +190,15 @@
     <t>HAFG25</t>
   </si>
   <si>
+    <t>2025-12-31</t>
+  </si>
+  <si>
+    <t>2025-01-01</t>
+  </si>
+  <si>
     <t>2025</t>
   </si>
   <si>
-    <t>2025-12-31</t>
-  </si>
-  <si>
-    <t>2025-01-01</t>
-  </si>
-  <si>
     <t>RIRNPAK25</t>
   </si>
   <si>
@@ -376,15 +376,15 @@
     <t>HAFG24</t>
   </si>
   <si>
+    <t>2024-12-31</t>
+  </si>
+  <si>
+    <t>2024-01-01</t>
+  </si>
+  <si>
     <t>2024</t>
   </si>
   <si>
-    <t>2024-12-31</t>
-  </si>
-  <si>
-    <t>2024-01-01</t>
-  </si>
-  <si>
     <t>RAFG_RRP24</t>
   </si>
   <si>
@@ -577,15 +577,15 @@
     <t>HAFG23</t>
   </si>
   <si>
+    <t>2023-12-31</t>
+  </si>
+  <si>
+    <t>2023-01-01</t>
+  </si>
+  <si>
     <t>2023</t>
   </si>
   <si>
-    <t>2023-12-31</t>
-  </si>
-  <si>
-    <t>2023-01-01</t>
-  </si>
-  <si>
     <t>RAFG23</t>
   </si>
   <si>
@@ -757,15 +757,15 @@
     <t>HAFG22</t>
   </si>
   <si>
+    <t>2022-12-31</t>
+  </si>
+  <si>
+    <t>2022-01-01</t>
+  </si>
+  <si>
     <t>2022</t>
   </si>
   <si>
-    <t>2022-12-31</t>
-  </si>
-  <si>
-    <t>2022-01-01</t>
-  </si>
-  <si>
     <t>RAFG22</t>
   </si>
   <si>
@@ -961,15 +961,15 @@
     <t>FAFG21</t>
   </si>
   <si>
+    <t>2021-12-31</t>
+  </si>
+  <si>
+    <t>2021-09-01</t>
+  </si>
+  <si>
     <t>2021</t>
   </si>
   <si>
-    <t>2021-12-31</t>
-  </si>
-  <si>
-    <t>2021-09-01</t>
-  </si>
-  <si>
     <t>HAFG21</t>
   </si>
   <si>
@@ -1165,15 +1165,15 @@
     <t>HAFG20</t>
   </si>
   <si>
+    <t>2020-12-31</t>
+  </si>
+  <si>
+    <t>2020-01-01</t>
+  </si>
+  <si>
     <t>2020</t>
   </si>
   <si>
-    <t>2020-12-31</t>
-  </si>
-  <si>
-    <t>2020-01-01</t>
-  </si>
-  <si>
     <t>OBGD20</t>
   </si>
   <si>
@@ -1405,15 +1405,15 @@
     <t>HAFG19</t>
   </si>
   <si>
+    <t>2019-12-31</t>
+  </si>
+  <si>
+    <t>2019-01-01</t>
+  </si>
+  <si>
     <t>2019</t>
   </si>
   <si>
-    <t>2019-12-31</t>
-  </si>
-  <si>
-    <t>2019-01-01</t>
-  </si>
-  <si>
     <t>RBGD19</t>
   </si>
   <si>
@@ -1537,15 +1537,15 @@
     <t>HAFG18</t>
   </si>
   <si>
+    <t>2018-12-31</t>
+  </si>
+  <si>
+    <t>2018-01-01</t>
+  </si>
+  <si>
     <t>2018</t>
   </si>
   <si>
-    <t>2018-12-31</t>
-  </si>
-  <si>
-    <t>2018-01-01</t>
-  </si>
-  <si>
     <t>OBGD18</t>
   </si>
   <si>
@@ -1663,15 +1663,15 @@
     <t>OEUR17</t>
   </si>
   <si>
+    <t>2017-12-31</t>
+  </si>
+  <si>
+    <t>2017-01-01</t>
+  </si>
+  <si>
     <t>2017</t>
   </si>
   <si>
-    <t>2017-12-31</t>
-  </si>
-  <si>
-    <t>2017-01-01</t>
-  </si>
-  <si>
     <t>HAFG17</t>
   </si>
   <si>
@@ -1840,15 +1840,15 @@
     <t>OEUR16</t>
   </si>
   <si>
+    <t>2016-12-31</t>
+  </si>
+  <si>
+    <t>2016-01-01</t>
+  </si>
+  <si>
     <t>2016</t>
   </si>
   <si>
-    <t>2016-12-31</t>
-  </si>
-  <si>
-    <t>2016-01-01</t>
-  </si>
-  <si>
     <t>HAFG16</t>
   </si>
   <si>
@@ -2011,15 +2011,15 @@
     <t>Strategic response plan</t>
   </si>
   <si>
+    <t>2015-12-31</t>
+  </si>
+  <si>
+    <t>2015-01-01</t>
+  </si>
+  <si>
     <t>2015</t>
   </si>
   <si>
-    <t>2015-12-31</t>
-  </si>
-  <si>
-    <t>2015-01-01</t>
-  </si>
-  <si>
     <t>HBFA15</t>
   </si>
   <si>
@@ -2146,15 +2146,15 @@
     <t>HAFG14</t>
   </si>
   <si>
+    <t>2014-12-31</t>
+  </si>
+  <si>
+    <t>2014-01-01</t>
+  </si>
+  <si>
     <t>2014</t>
   </si>
   <si>
-    <t>2014-12-31</t>
-  </si>
-  <si>
-    <t>2014-01-01</t>
-  </si>
-  <si>
     <t>HBFA1314</t>
   </si>
   <si>
@@ -2326,12 +2326,12 @@
     <t>Consolidated appeals process</t>
   </si>
   <si>
+    <t>2013-12-31</t>
+  </si>
+  <si>
     <t>2013</t>
   </si>
   <si>
-    <t>2013-12-31</t>
-  </si>
-  <si>
     <t>CBFA13</t>
   </si>
   <si>
@@ -2416,15 +2416,15 @@
     <t>CKEN12</t>
   </si>
   <si>
+    <t>2012-12-31</t>
+  </si>
+  <si>
+    <t>2012-01-01</t>
+  </si>
+  <si>
     <t>2012</t>
   </si>
   <si>
-    <t>2012-12-31</t>
-  </si>
-  <si>
-    <t>2012-01-01</t>
-  </si>
-  <si>
     <t>CAFG1112</t>
   </si>
   <si>
@@ -2527,12 +2527,12 @@
     <t>CKEN1113</t>
   </si>
   <si>
+    <t>2011-01-01</t>
+  </si>
+  <si>
     <t>2011</t>
   </si>
   <si>
-    <t>2011-01-01</t>
-  </si>
-  <si>
     <t>CAFG11</t>
   </si>
   <si>
@@ -2650,15 +2650,15 @@
     <t>CAFG10</t>
   </si>
   <si>
+    <t>2010-12-31</t>
+  </si>
+  <si>
+    <t>2010-01-01</t>
+  </si>
+  <si>
     <t>2010</t>
   </si>
   <si>
-    <t>2010-12-31</t>
-  </si>
-  <si>
-    <t>2010-01-01</t>
-  </si>
-  <si>
     <t>OBFA1011</t>
   </si>
   <si>
@@ -2794,15 +2794,15 @@
     <t>CAFG09</t>
   </si>
   <si>
+    <t>2009-12-31</t>
+  </si>
+  <si>
+    <t>2009-01-01</t>
+  </si>
+  <si>
     <t>2009</t>
   </si>
   <si>
-    <t>2009-12-31</t>
-  </si>
-  <si>
-    <t>2009-01-01</t>
-  </si>
-  <si>
     <t>FBFA0910</t>
   </si>
   <si>
@@ -2938,15 +2938,15 @@
     <t>OAFG08</t>
   </si>
   <si>
+    <t>2008-06-30</t>
+  </si>
+  <si>
+    <t>2008-02-01</t>
+  </si>
+  <si>
     <t>2008</t>
   </si>
   <si>
-    <t>2008-06-30</t>
-  </si>
-  <si>
-    <t>2008-02-01</t>
-  </si>
-  <si>
     <t>OAFG0809</t>
   </si>
   <si>
@@ -3112,15 +3112,15 @@
     <t>FBOL07</t>
   </si>
   <si>
+    <t>2007-08-21</t>
+  </si>
+  <si>
+    <t>2007-02-22</t>
+  </si>
+  <si>
     <t>2007</t>
   </si>
   <si>
-    <t>2007-08-21</t>
-  </si>
-  <si>
-    <t>2007-02-22</t>
-  </si>
-  <si>
     <t>FBFA0708</t>
   </si>
   <si>
@@ -3316,15 +3316,15 @@
     <t>OAFG06</t>
   </si>
   <si>
+    <t>2006-12-31</t>
+  </si>
+  <si>
+    <t>2006-07-01</t>
+  </si>
+  <si>
     <t>2006</t>
   </si>
   <si>
-    <t>2006-12-31</t>
-  </si>
-  <si>
-    <t>2006-07-01</t>
-  </si>
-  <si>
     <t>CBDI06</t>
   </si>
   <si>
@@ -3478,15 +3478,15 @@
     <t>FAGO05</t>
   </si>
   <si>
+    <t>2005-06-30</t>
+  </si>
+  <si>
+    <t>2005-04-01</t>
+  </si>
+  <si>
     <t>2005</t>
   </si>
   <si>
-    <t>2005-06-30</t>
-  </si>
-  <si>
-    <t>2005-04-01</t>
-  </si>
-  <si>
     <t>FBEN05</t>
   </si>
   <si>
@@ -3616,15 +3616,15 @@
     <t>OAFG04</t>
   </si>
   <si>
+    <t>2004-12-31</t>
+  </si>
+  <si>
+    <t>2004-09-01</t>
+  </si>
+  <si>
     <t>2004</t>
   </si>
   <si>
-    <t>2004-12-31</t>
-  </si>
-  <si>
-    <t>2004-09-01</t>
-  </si>
-  <si>
     <t>CAGO04</t>
   </si>
   <si>
@@ -3769,15 +3769,15 @@
     <t>OAFG03</t>
   </si>
   <si>
+    <t>2003-12-31</t>
+  </si>
+  <si>
+    <t>2003-01-01</t>
+  </si>
+  <si>
     <t>2003</t>
   </si>
   <si>
-    <t>2003-12-31</t>
-  </si>
-  <si>
-    <t>2003-01-01</t>
-  </si>
-  <si>
     <t>CAGO03</t>
   </si>
   <si>
@@ -3913,15 +3913,15 @@
     <t>CAFG0102</t>
   </si>
   <si>
+    <t>2002-12-31</t>
+  </si>
+  <si>
+    <t>2001-10-01</t>
+  </si>
+  <si>
     <t>2002</t>
   </si>
   <si>
-    <t>2002-12-31</t>
-  </si>
-  <si>
-    <t>2001-10-01</t>
-  </si>
-  <si>
     <t>CAGO02</t>
   </si>
   <si>
@@ -4021,15 +4021,15 @@
     <t>CAFG01</t>
   </si>
   <si>
+    <t>2001-09-30</t>
+  </si>
+  <si>
+    <t>2001-01-01</t>
+  </si>
+  <si>
     <t>2001</t>
   </si>
   <si>
-    <t>2001-09-30</t>
-  </si>
-  <si>
-    <t>2001-01-01</t>
-  </si>
-  <si>
     <t>CAGO01</t>
   </si>
   <si>
@@ -4105,13 +4105,13 @@
     <t>CAGO00</t>
   </si>
   <si>
+    <t>2000-12-31</t>
+  </si>
+  <si>
+    <t>2000-01-01</t>
+  </si>
+  <si>
     <t>2000</t>
-  </si>
-  <si>
-    <t>2000-12-31</t>
-  </si>
-  <si>
-    <t>2000-01-01</t>
   </si>
   <si>
     <t>CBDI00</t>
@@ -4700,13 +4700,13 @@
         <v>22</v>
       </c>
       <c r="D10" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="E10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F10" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -4720,13 +4720,13 @@
         <v>18</v>
       </c>
       <c r="D11" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E11" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F11" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -4740,13 +4740,13 @@
         <v>18</v>
       </c>
       <c r="D12" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="E12" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F12" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -4860,10 +4860,10 @@
         <v>16</v>
       </c>
       <c r="D18" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="E18" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="F18" t="s">
         <v>11</v>
@@ -5020,13 +5020,13 @@
         <v>16</v>
       </c>
       <c r="D26" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="E26" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="F26" t="s">
-        <v>44</v>
+        <v>11</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -5220,10 +5220,10 @@
         <v>16</v>
       </c>
       <c r="D36" t="s">
-        <v>9</v>
+        <v>55</v>
       </c>
       <c r="E36" t="s">
-        <v>55</v>
+        <v>10</v>
       </c>
       <c r="F36" t="s">
         <v>11</v>
@@ -5300,10 +5300,10 @@
         <v>16</v>
       </c>
       <c r="D40" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E40" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="F40" t="s">
         <v>60</v>
@@ -5383,10 +5383,10 @@
         <v>58</v>
       </c>
       <c r="E44" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="F44" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
     </row>
     <row r="45" spans="1:6">
@@ -5520,10 +5520,10 @@
         <v>18</v>
       </c>
       <c r="D51" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E51" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="F51" t="s">
         <v>60</v>
@@ -5540,10 +5540,10 @@
         <v>18</v>
       </c>
       <c r="D52" t="s">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="E52" t="s">
-        <v>78</v>
+        <v>59</v>
       </c>
       <c r="F52" t="s">
         <v>60</v>
@@ -5580,10 +5580,10 @@
         <v>18</v>
       </c>
       <c r="D54" t="s">
-        <v>58</v>
+        <v>81</v>
       </c>
       <c r="E54" t="s">
-        <v>81</v>
+        <v>59</v>
       </c>
       <c r="F54" t="s">
         <v>60</v>
@@ -5620,10 +5620,10 @@
         <v>18</v>
       </c>
       <c r="D56" t="s">
-        <v>58</v>
+        <v>84</v>
       </c>
       <c r="E56" t="s">
-        <v>84</v>
+        <v>59</v>
       </c>
       <c r="F56" t="s">
         <v>60</v>
@@ -5643,10 +5643,10 @@
         <v>58</v>
       </c>
       <c r="E57" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="F57" t="s">
-        <v>86</v>
+        <v>60</v>
       </c>
     </row>
     <row r="58" spans="1:6">
@@ -5723,10 +5723,10 @@
         <v>58</v>
       </c>
       <c r="E61" t="s">
-        <v>59</v>
+        <v>91</v>
       </c>
       <c r="F61" t="s">
-        <v>91</v>
+        <v>60</v>
       </c>
     </row>
     <row r="62" spans="1:6">
@@ -5740,10 +5740,10 @@
         <v>16</v>
       </c>
       <c r="D62" t="s">
-        <v>58</v>
+        <v>93</v>
       </c>
       <c r="E62" t="s">
-        <v>93</v>
+        <v>59</v>
       </c>
       <c r="F62" t="s">
         <v>60</v>
@@ -5943,10 +5943,10 @@
         <v>58</v>
       </c>
       <c r="E72" t="s">
-        <v>59</v>
+        <v>104</v>
       </c>
       <c r="F72" t="s">
-        <v>104</v>
+        <v>60</v>
       </c>
     </row>
     <row r="73" spans="1:6">
@@ -6100,10 +6100,10 @@
         <v>16</v>
       </c>
       <c r="D80" t="s">
-        <v>58</v>
+        <v>84</v>
       </c>
       <c r="E80" t="s">
-        <v>84</v>
+        <v>59</v>
       </c>
       <c r="F80" t="s">
         <v>60</v>
@@ -6120,10 +6120,10 @@
         <v>16</v>
       </c>
       <c r="D81" t="s">
-        <v>58</v>
+        <v>84</v>
       </c>
       <c r="E81" t="s">
-        <v>84</v>
+        <v>59</v>
       </c>
       <c r="F81" t="s">
         <v>60</v>
@@ -6143,10 +6143,10 @@
         <v>58</v>
       </c>
       <c r="E82" t="s">
-        <v>59</v>
+        <v>115</v>
       </c>
       <c r="F82" t="s">
-        <v>115</v>
+        <v>60</v>
       </c>
     </row>
     <row r="83" spans="1:6">
@@ -6180,10 +6180,10 @@
         <v>18</v>
       </c>
       <c r="D84" t="s">
-        <v>58</v>
+        <v>84</v>
       </c>
       <c r="E84" t="s">
-        <v>84</v>
+        <v>59</v>
       </c>
       <c r="F84" t="s">
         <v>60</v>
@@ -6200,10 +6200,10 @@
         <v>18</v>
       </c>
       <c r="D85" t="s">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="E85" t="s">
-        <v>78</v>
+        <v>59</v>
       </c>
       <c r="F85" t="s">
         <v>60</v>
@@ -6263,10 +6263,10 @@
         <v>120</v>
       </c>
       <c r="E88" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="F88" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="89" spans="1:6">
@@ -6303,10 +6303,10 @@
         <v>120</v>
       </c>
       <c r="E90" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="F90" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
     </row>
     <row r="91" spans="1:6">
@@ -6443,10 +6443,10 @@
         <v>120</v>
       </c>
       <c r="E97" t="s">
-        <v>121</v>
+        <v>136</v>
       </c>
       <c r="F97" t="s">
-        <v>136</v>
+        <v>122</v>
       </c>
     </row>
     <row r="98" spans="1:6">
@@ -6523,10 +6523,10 @@
         <v>120</v>
       </c>
       <c r="E101" t="s">
-        <v>121</v>
+        <v>141</v>
       </c>
       <c r="F101" t="s">
-        <v>141</v>
+        <v>122</v>
       </c>
     </row>
     <row r="102" spans="1:6">
@@ -6543,10 +6543,10 @@
         <v>120</v>
       </c>
       <c r="E102" t="s">
-        <v>121</v>
+        <v>141</v>
       </c>
       <c r="F102" t="s">
-        <v>141</v>
+        <v>122</v>
       </c>
     </row>
     <row r="103" spans="1:6">
@@ -6560,10 +6560,10 @@
         <v>18</v>
       </c>
       <c r="D103" t="s">
-        <v>120</v>
+        <v>144</v>
       </c>
       <c r="E103" t="s">
-        <v>144</v>
+        <v>121</v>
       </c>
       <c r="F103" t="s">
         <v>122</v>
@@ -6580,10 +6580,10 @@
         <v>18</v>
       </c>
       <c r="D104" t="s">
-        <v>120</v>
+        <v>146</v>
       </c>
       <c r="E104" t="s">
-        <v>146</v>
+        <v>121</v>
       </c>
       <c r="F104" t="s">
         <v>122</v>
@@ -6603,10 +6603,10 @@
         <v>120</v>
       </c>
       <c r="E105" t="s">
-        <v>121</v>
+        <v>148</v>
       </c>
       <c r="F105" t="s">
-        <v>148</v>
+        <v>122</v>
       </c>
     </row>
     <row r="106" spans="1:6">
@@ -6640,13 +6640,13 @@
         <v>16</v>
       </c>
       <c r="D107" t="s">
-        <v>120</v>
+        <v>146</v>
       </c>
       <c r="E107" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="F107" t="s">
-        <v>151</v>
+        <v>122</v>
       </c>
     </row>
     <row r="108" spans="1:6">
@@ -6663,10 +6663,10 @@
         <v>120</v>
       </c>
       <c r="E108" t="s">
-        <v>121</v>
+        <v>153</v>
       </c>
       <c r="F108" t="s">
-        <v>153</v>
+        <v>122</v>
       </c>
     </row>
     <row r="109" spans="1:6">
@@ -6723,10 +6723,10 @@
         <v>120</v>
       </c>
       <c r="E111" t="s">
-        <v>121</v>
+        <v>157</v>
       </c>
       <c r="F111" t="s">
-        <v>157</v>
+        <v>122</v>
       </c>
     </row>
     <row r="112" spans="1:6">
@@ -6783,10 +6783,10 @@
         <v>120</v>
       </c>
       <c r="E114" t="s">
-        <v>121</v>
+        <v>161</v>
       </c>
       <c r="F114" t="s">
-        <v>161</v>
+        <v>122</v>
       </c>
     </row>
     <row r="115" spans="1:6">
@@ -6903,10 +6903,10 @@
         <v>120</v>
       </c>
       <c r="E120" t="s">
-        <v>121</v>
+        <v>136</v>
       </c>
       <c r="F120" t="s">
-        <v>136</v>
+        <v>122</v>
       </c>
     </row>
     <row r="121" spans="1:6">
@@ -7163,10 +7163,10 @@
         <v>120</v>
       </c>
       <c r="E133" t="s">
-        <v>121</v>
+        <v>181</v>
       </c>
       <c r="F133" t="s">
-        <v>181</v>
+        <v>122</v>
       </c>
     </row>
     <row r="134" spans="1:6">
@@ -7203,10 +7203,10 @@
         <v>120</v>
       </c>
       <c r="E135" t="s">
-        <v>121</v>
+        <v>184</v>
       </c>
       <c r="F135" t="s">
-        <v>184</v>
+        <v>122</v>
       </c>
     </row>
     <row r="136" spans="1:6">
@@ -7223,10 +7223,10 @@
         <v>120</v>
       </c>
       <c r="E136" t="s">
-        <v>121</v>
+        <v>184</v>
       </c>
       <c r="F136" t="s">
-        <v>184</v>
+        <v>122</v>
       </c>
     </row>
     <row r="137" spans="1:6">
@@ -7403,10 +7403,10 @@
         <v>187</v>
       </c>
       <c r="E145" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="F145" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
     </row>
     <row r="146" spans="1:6">
@@ -7563,10 +7563,10 @@
         <v>187</v>
       </c>
       <c r="E153" t="s">
-        <v>188</v>
+        <v>207</v>
       </c>
       <c r="F153" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
     </row>
     <row r="154" spans="1:6">
@@ -7620,13 +7620,13 @@
         <v>16</v>
       </c>
       <c r="D156" t="s">
-        <v>187</v>
+        <v>211</v>
       </c>
       <c r="E156" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F156" t="s">
-        <v>212</v>
+        <v>189</v>
       </c>
     </row>
     <row r="157" spans="1:6">
@@ -7640,13 +7640,13 @@
         <v>16</v>
       </c>
       <c r="D157" t="s">
-        <v>187</v>
+        <v>214</v>
       </c>
       <c r="E157" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F157" t="s">
-        <v>215</v>
+        <v>189</v>
       </c>
     </row>
     <row r="158" spans="1:6">
@@ -7740,10 +7740,10 @@
         <v>66</v>
       </c>
       <c r="D162" t="s">
-        <v>187</v>
+        <v>214</v>
       </c>
       <c r="E162" t="s">
-        <v>214</v>
+        <v>188</v>
       </c>
       <c r="F162" t="s">
         <v>189</v>
@@ -7760,10 +7760,10 @@
         <v>16</v>
       </c>
       <c r="D163" t="s">
-        <v>187</v>
+        <v>211</v>
       </c>
       <c r="E163" t="s">
-        <v>211</v>
+        <v>188</v>
       </c>
       <c r="F163" t="s">
         <v>189</v>
@@ -7940,13 +7940,13 @@
         <v>22</v>
       </c>
       <c r="D172" t="s">
-        <v>187</v>
+        <v>231</v>
       </c>
       <c r="E172" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F172" t="s">
-        <v>232</v>
+        <v>189</v>
       </c>
     </row>
     <row r="173" spans="1:6">
@@ -7980,13 +7980,13 @@
         <v>18</v>
       </c>
       <c r="D174" t="s">
-        <v>187</v>
+        <v>211</v>
       </c>
       <c r="E174" t="s">
-        <v>211</v>
+        <v>235</v>
       </c>
       <c r="F174" t="s">
-        <v>235</v>
+        <v>189</v>
       </c>
     </row>
     <row r="175" spans="1:6">
@@ -8020,13 +8020,13 @@
         <v>18</v>
       </c>
       <c r="D176" t="s">
-        <v>187</v>
+        <v>211</v>
       </c>
       <c r="E176" t="s">
-        <v>211</v>
+        <v>238</v>
       </c>
       <c r="F176" t="s">
-        <v>238</v>
+        <v>189</v>
       </c>
     </row>
     <row r="177" spans="1:6">
@@ -8320,13 +8320,13 @@
         <v>16</v>
       </c>
       <c r="D191" t="s">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="E191" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F191" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
     </row>
     <row r="192" spans="1:6">
@@ -8420,13 +8420,13 @@
         <v>18</v>
       </c>
       <c r="D196" t="s">
-        <v>247</v>
+        <v>264</v>
       </c>
       <c r="E196" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F196" t="s">
-        <v>265</v>
+        <v>249</v>
       </c>
     </row>
     <row r="197" spans="1:6">
@@ -8443,10 +8443,10 @@
         <v>247</v>
       </c>
       <c r="E197" t="s">
-        <v>248</v>
+        <v>265</v>
       </c>
       <c r="F197" t="s">
-        <v>265</v>
+        <v>249</v>
       </c>
     </row>
     <row r="198" spans="1:6">
@@ -8520,10 +8520,10 @@
         <v>18</v>
       </c>
       <c r="D201" t="s">
-        <v>247</v>
+        <v>271</v>
       </c>
       <c r="E201" t="s">
-        <v>271</v>
+        <v>248</v>
       </c>
       <c r="F201" t="s">
         <v>249</v>
@@ -8600,13 +8600,13 @@
         <v>18</v>
       </c>
       <c r="D205" t="s">
-        <v>247</v>
+        <v>276</v>
       </c>
       <c r="E205" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F205" t="s">
-        <v>277</v>
+        <v>249</v>
       </c>
     </row>
     <row r="206" spans="1:6">
@@ -8640,13 +8640,13 @@
         <v>18</v>
       </c>
       <c r="D207" t="s">
-        <v>247</v>
+        <v>280</v>
       </c>
       <c r="E207" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F207" t="s">
-        <v>281</v>
+        <v>249</v>
       </c>
     </row>
     <row r="208" spans="1:6">
@@ -8763,10 +8763,10 @@
         <v>247</v>
       </c>
       <c r="E213" t="s">
-        <v>248</v>
+        <v>288</v>
       </c>
       <c r="F213" t="s">
-        <v>288</v>
+        <v>249</v>
       </c>
     </row>
     <row r="214" spans="1:6">
@@ -8780,13 +8780,13 @@
         <v>16</v>
       </c>
       <c r="D214" t="s">
-        <v>247</v>
+        <v>290</v>
       </c>
       <c r="E214" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="F214" t="s">
-        <v>288</v>
+        <v>249</v>
       </c>
     </row>
     <row r="215" spans="1:6">
@@ -8800,13 +8800,13 @@
         <v>16</v>
       </c>
       <c r="D215" t="s">
-        <v>247</v>
+        <v>292</v>
       </c>
       <c r="E215" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F215" t="s">
-        <v>293</v>
+        <v>249</v>
       </c>
     </row>
     <row r="216" spans="1:6">
@@ -8963,10 +8963,10 @@
         <v>247</v>
       </c>
       <c r="E223" t="s">
-        <v>248</v>
+        <v>302</v>
       </c>
       <c r="F223" t="s">
-        <v>302</v>
+        <v>249</v>
       </c>
     </row>
     <row r="224" spans="1:6">
@@ -9063,10 +9063,10 @@
         <v>247</v>
       </c>
       <c r="E228" t="s">
-        <v>248</v>
+        <v>308</v>
       </c>
       <c r="F228" t="s">
-        <v>308</v>
+        <v>249</v>
       </c>
     </row>
     <row r="229" spans="1:6">
@@ -9100,13 +9100,13 @@
         <v>22</v>
       </c>
       <c r="D230" t="s">
-        <v>247</v>
+        <v>311</v>
       </c>
       <c r="E230" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="F230" t="s">
-        <v>308</v>
+        <v>249</v>
       </c>
     </row>
     <row r="231" spans="1:6">
@@ -9183,10 +9183,10 @@
         <v>315</v>
       </c>
       <c r="E234" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="F234" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="235" spans="1:6">
@@ -9203,10 +9203,10 @@
         <v>315</v>
       </c>
       <c r="E235" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="F235" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="236" spans="1:6">
@@ -9223,10 +9223,10 @@
         <v>315</v>
       </c>
       <c r="E236" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="F236" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="237" spans="1:6">
@@ -9243,10 +9243,10 @@
         <v>315</v>
       </c>
       <c r="E237" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="F237" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="238" spans="1:6">
@@ -9263,10 +9263,10 @@
         <v>315</v>
       </c>
       <c r="E238" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="F238" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="239" spans="1:6">
@@ -9283,10 +9283,10 @@
         <v>315</v>
       </c>
       <c r="E239" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="F239" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="240" spans="1:6">
@@ -9303,10 +9303,10 @@
         <v>315</v>
       </c>
       <c r="E240" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="F240" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="241" spans="1:6">
@@ -9323,10 +9323,10 @@
         <v>315</v>
       </c>
       <c r="E241" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="F241" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="242" spans="1:6">
@@ -9343,10 +9343,10 @@
         <v>315</v>
       </c>
       <c r="E242" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="F242" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="243" spans="1:6">
@@ -9363,10 +9363,10 @@
         <v>315</v>
       </c>
       <c r="E243" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="F243" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="244" spans="1:6">
@@ -9383,10 +9383,10 @@
         <v>315</v>
       </c>
       <c r="E244" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="F244" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="245" spans="1:6">
@@ -9403,10 +9403,10 @@
         <v>315</v>
       </c>
       <c r="E245" t="s">
-        <v>316</v>
+        <v>331</v>
       </c>
       <c r="F245" t="s">
-        <v>331</v>
+        <v>317</v>
       </c>
     </row>
     <row r="246" spans="1:6">
@@ -9420,13 +9420,13 @@
         <v>66</v>
       </c>
       <c r="D246" t="s">
-        <v>315</v>
+        <v>247</v>
       </c>
       <c r="E246" t="s">
-        <v>248</v>
+        <v>331</v>
       </c>
       <c r="F246" t="s">
-        <v>331</v>
+        <v>317</v>
       </c>
     </row>
     <row r="247" spans="1:6">
@@ -9440,13 +9440,13 @@
         <v>18</v>
       </c>
       <c r="D247" t="s">
-        <v>315</v>
+        <v>334</v>
       </c>
       <c r="E247" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F247" t="s">
-        <v>335</v>
+        <v>317</v>
       </c>
     </row>
     <row r="248" spans="1:6">
@@ -9463,10 +9463,10 @@
         <v>315</v>
       </c>
       <c r="E248" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="F248" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="249" spans="1:6">
@@ -9483,10 +9483,10 @@
         <v>315</v>
       </c>
       <c r="E249" t="s">
-        <v>316</v>
+        <v>331</v>
       </c>
       <c r="F249" t="s">
-        <v>331</v>
+        <v>317</v>
       </c>
     </row>
     <row r="250" spans="1:6">
@@ -9500,13 +9500,13 @@
         <v>66</v>
       </c>
       <c r="D250" t="s">
-        <v>315</v>
+        <v>247</v>
       </c>
       <c r="E250" t="s">
-        <v>248</v>
+        <v>331</v>
       </c>
       <c r="F250" t="s">
-        <v>331</v>
+        <v>317</v>
       </c>
     </row>
     <row r="251" spans="1:6">
@@ -9520,13 +9520,13 @@
         <v>18</v>
       </c>
       <c r="D251" t="s">
-        <v>315</v>
+        <v>340</v>
       </c>
       <c r="E251" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F251" t="s">
-        <v>341</v>
+        <v>317</v>
       </c>
     </row>
     <row r="252" spans="1:6">
@@ -9543,10 +9543,10 @@
         <v>315</v>
       </c>
       <c r="E252" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="F252" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="253" spans="1:6">
@@ -9560,13 +9560,13 @@
         <v>18</v>
       </c>
       <c r="D253" t="s">
-        <v>315</v>
+        <v>344</v>
       </c>
       <c r="E253" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F253" t="s">
-        <v>345</v>
+        <v>317</v>
       </c>
     </row>
     <row r="254" spans="1:6">
@@ -9583,10 +9583,10 @@
         <v>315</v>
       </c>
       <c r="E254" t="s">
-        <v>316</v>
+        <v>331</v>
       </c>
       <c r="F254" t="s">
-        <v>331</v>
+        <v>317</v>
       </c>
     </row>
     <row r="255" spans="1:6">
@@ -9600,13 +9600,13 @@
         <v>66</v>
       </c>
       <c r="D255" t="s">
-        <v>315</v>
+        <v>247</v>
       </c>
       <c r="E255" t="s">
-        <v>248</v>
+        <v>331</v>
       </c>
       <c r="F255" t="s">
-        <v>331</v>
+        <v>317</v>
       </c>
     </row>
     <row r="256" spans="1:6">
@@ -9623,10 +9623,10 @@
         <v>315</v>
       </c>
       <c r="E256" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="F256" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="257" spans="1:6">
@@ -9643,10 +9643,10 @@
         <v>315</v>
       </c>
       <c r="E257" t="s">
-        <v>316</v>
+        <v>350</v>
       </c>
       <c r="F257" t="s">
-        <v>350</v>
+        <v>317</v>
       </c>
     </row>
     <row r="258" spans="1:6">
@@ -9660,13 +9660,13 @@
         <v>16</v>
       </c>
       <c r="D258" t="s">
-        <v>315</v>
+        <v>352</v>
       </c>
       <c r="E258" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F258" t="s">
-        <v>353</v>
+        <v>317</v>
       </c>
     </row>
     <row r="259" spans="1:6">
@@ -9683,10 +9683,10 @@
         <v>315</v>
       </c>
       <c r="E259" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="F259" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="260" spans="1:6">
@@ -9700,13 +9700,13 @@
         <v>18</v>
       </c>
       <c r="D260" t="s">
-        <v>315</v>
+        <v>276</v>
       </c>
       <c r="E260" t="s">
-        <v>276</v>
+        <v>319</v>
       </c>
       <c r="F260" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="261" spans="1:6">
@@ -9723,10 +9723,10 @@
         <v>315</v>
       </c>
       <c r="E261" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="F261" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="262" spans="1:6">
@@ -9743,10 +9743,10 @@
         <v>315</v>
       </c>
       <c r="E262" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="F262" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="263" spans="1:6">
@@ -9763,10 +9763,10 @@
         <v>315</v>
       </c>
       <c r="E263" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="F263" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="264" spans="1:6">
@@ -9783,10 +9783,10 @@
         <v>315</v>
       </c>
       <c r="E264" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="F264" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="265" spans="1:6">
@@ -9803,10 +9803,10 @@
         <v>315</v>
       </c>
       <c r="E265" t="s">
-        <v>316</v>
+        <v>361</v>
       </c>
       <c r="F265" t="s">
-        <v>361</v>
+        <v>317</v>
       </c>
     </row>
     <row r="266" spans="1:6">
@@ -9823,10 +9823,10 @@
         <v>315</v>
       </c>
       <c r="E266" t="s">
-        <v>316</v>
+        <v>363</v>
       </c>
       <c r="F266" t="s">
-        <v>363</v>
+        <v>317</v>
       </c>
     </row>
     <row r="267" spans="1:6">
@@ -9843,10 +9843,10 @@
         <v>315</v>
       </c>
       <c r="E267" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="F267" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="268" spans="1:6">
@@ -9863,10 +9863,10 @@
         <v>315</v>
       </c>
       <c r="E268" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="F268" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="269" spans="1:6">
@@ -9883,10 +9883,10 @@
         <v>315</v>
       </c>
       <c r="E269" t="s">
-        <v>316</v>
+        <v>363</v>
       </c>
       <c r="F269" t="s">
-        <v>363</v>
+        <v>317</v>
       </c>
     </row>
     <row r="270" spans="1:6">
@@ -9903,10 +9903,10 @@
         <v>315</v>
       </c>
       <c r="E270" t="s">
-        <v>316</v>
+        <v>363</v>
       </c>
       <c r="F270" t="s">
-        <v>363</v>
+        <v>317</v>
       </c>
     </row>
     <row r="271" spans="1:6">
@@ -9923,10 +9923,10 @@
         <v>315</v>
       </c>
       <c r="E271" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="F271" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="272" spans="1:6">
@@ -9943,10 +9943,10 @@
         <v>315</v>
       </c>
       <c r="E272" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="F272" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="273" spans="1:6">
@@ -9963,10 +9963,10 @@
         <v>315</v>
       </c>
       <c r="E273" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="F273" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="274" spans="1:6">
@@ -9983,10 +9983,10 @@
         <v>315</v>
       </c>
       <c r="E274" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="F274" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="275" spans="1:6">
@@ -10003,10 +10003,10 @@
         <v>315</v>
       </c>
       <c r="E275" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="F275" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="276" spans="1:6">
@@ -10023,10 +10023,10 @@
         <v>315</v>
       </c>
       <c r="E276" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="F276" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="277" spans="1:6">
@@ -10043,10 +10043,10 @@
         <v>315</v>
       </c>
       <c r="E277" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="F277" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="278" spans="1:6">
@@ -10063,10 +10063,10 @@
         <v>315</v>
       </c>
       <c r="E278" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="F278" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="279" spans="1:6">
@@ -10083,10 +10083,10 @@
         <v>315</v>
       </c>
       <c r="E279" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="F279" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="280" spans="1:6">
@@ -10103,10 +10103,10 @@
         <v>315</v>
       </c>
       <c r="E280" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="F280" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="281" spans="1:6">
@@ -10123,10 +10123,10 @@
         <v>315</v>
       </c>
       <c r="E281" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="F281" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="282" spans="1:6">
@@ -10143,10 +10143,10 @@
         <v>315</v>
       </c>
       <c r="E282" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="F282" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="283" spans="1:6">
@@ -10163,10 +10163,10 @@
         <v>315</v>
       </c>
       <c r="E283" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="F283" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="284" spans="1:6">
@@ -10183,10 +10183,10 @@
         <v>315</v>
       </c>
       <c r="E284" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="F284" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="285" spans="1:6">
@@ -10223,10 +10223,10 @@
         <v>383</v>
       </c>
       <c r="E286" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="F286" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="287" spans="1:6">
@@ -10263,10 +10263,10 @@
         <v>383</v>
       </c>
       <c r="E288" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="F288" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="289" spans="1:6">
@@ -10343,10 +10343,10 @@
         <v>383</v>
       </c>
       <c r="E292" t="s">
-        <v>384</v>
+        <v>394</v>
       </c>
       <c r="F292" t="s">
-        <v>394</v>
+        <v>385</v>
       </c>
     </row>
     <row r="293" spans="1:6">
@@ -10380,13 +10380,13 @@
         <v>66</v>
       </c>
       <c r="D294" t="s">
-        <v>383</v>
+        <v>319</v>
       </c>
       <c r="E294" t="s">
-        <v>319</v>
+        <v>397</v>
       </c>
       <c r="F294" t="s">
-        <v>397</v>
+        <v>385</v>
       </c>
     </row>
     <row r="295" spans="1:6">
@@ -10443,10 +10443,10 @@
         <v>383</v>
       </c>
       <c r="E297" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="F297" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="298" spans="1:6">
@@ -10463,10 +10463,10 @@
         <v>383</v>
       </c>
       <c r="E298" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="F298" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="299" spans="1:6">
@@ -10483,10 +10483,10 @@
         <v>383</v>
       </c>
       <c r="E299" t="s">
-        <v>384</v>
+        <v>403</v>
       </c>
       <c r="F299" t="s">
-        <v>403</v>
+        <v>385</v>
       </c>
     </row>
     <row r="300" spans="1:6">
@@ -10540,13 +10540,13 @@
         <v>18</v>
       </c>
       <c r="D302" t="s">
-        <v>383</v>
+        <v>407</v>
       </c>
       <c r="E302" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="F302" t="s">
-        <v>408</v>
+        <v>385</v>
       </c>
     </row>
     <row r="303" spans="1:6">
@@ -10563,10 +10563,10 @@
         <v>383</v>
       </c>
       <c r="E303" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="F303" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="304" spans="1:6">
@@ -10583,10 +10583,10 @@
         <v>383</v>
       </c>
       <c r="E304" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="F304" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="305" spans="1:6">
@@ -10623,10 +10623,10 @@
         <v>383</v>
       </c>
       <c r="E306" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="F306" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="307" spans="1:6">
@@ -10663,10 +10663,10 @@
         <v>383</v>
       </c>
       <c r="E308" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="F308" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="309" spans="1:6">
@@ -10683,10 +10683,10 @@
         <v>383</v>
       </c>
       <c r="E309" t="s">
-        <v>384</v>
+        <v>403</v>
       </c>
       <c r="F309" t="s">
-        <v>403</v>
+        <v>385</v>
       </c>
     </row>
     <row r="310" spans="1:6">
@@ -10703,10 +10703,10 @@
         <v>383</v>
       </c>
       <c r="E310" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="F310" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="311" spans="1:6">
@@ -10723,10 +10723,10 @@
         <v>383</v>
       </c>
       <c r="E311" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="F311" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="312" spans="1:6">
@@ -10763,10 +10763,10 @@
         <v>383</v>
       </c>
       <c r="E313" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="F313" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="314" spans="1:6">
@@ -10803,10 +10803,10 @@
         <v>383</v>
       </c>
       <c r="E315" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="F315" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="316" spans="1:6">
@@ -10823,10 +10823,10 @@
         <v>383</v>
       </c>
       <c r="E316" t="s">
-        <v>384</v>
+        <v>423</v>
       </c>
       <c r="F316" t="s">
-        <v>423</v>
+        <v>385</v>
       </c>
     </row>
     <row r="317" spans="1:6">
@@ -10840,13 +10840,13 @@
         <v>18</v>
       </c>
       <c r="D317" t="s">
-        <v>383</v>
+        <v>425</v>
       </c>
       <c r="E317" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="F317" t="s">
-        <v>426</v>
+        <v>385</v>
       </c>
     </row>
     <row r="318" spans="1:6">
@@ -10863,10 +10863,10 @@
         <v>383</v>
       </c>
       <c r="E318" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="F318" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="319" spans="1:6">
@@ -10880,13 +10880,13 @@
         <v>18</v>
       </c>
       <c r="D319" t="s">
-        <v>383</v>
+        <v>429</v>
       </c>
       <c r="E319" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="F319" t="s">
-        <v>430</v>
+        <v>385</v>
       </c>
     </row>
     <row r="320" spans="1:6">
@@ -10903,10 +10903,10 @@
         <v>383</v>
       </c>
       <c r="E320" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="F320" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="321" spans="1:6">
@@ -10963,10 +10963,10 @@
         <v>383</v>
       </c>
       <c r="E323" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="F323" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="324" spans="1:6">
@@ -11063,10 +11063,10 @@
         <v>383</v>
       </c>
       <c r="E328" t="s">
-        <v>384</v>
+        <v>423</v>
       </c>
       <c r="F328" t="s">
-        <v>423</v>
+        <v>385</v>
       </c>
     </row>
     <row r="329" spans="1:6">
@@ -11083,10 +11083,10 @@
         <v>383</v>
       </c>
       <c r="E329" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="F329" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="330" spans="1:6">
@@ -11143,10 +11143,10 @@
         <v>383</v>
       </c>
       <c r="E332" t="s">
-        <v>384</v>
+        <v>423</v>
       </c>
       <c r="F332" t="s">
-        <v>423</v>
+        <v>385</v>
       </c>
     </row>
     <row r="333" spans="1:6">
@@ -11163,10 +11163,10 @@
         <v>383</v>
       </c>
       <c r="E333" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="F333" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="334" spans="1:6">
@@ -11303,10 +11303,10 @@
         <v>383</v>
       </c>
       <c r="E340" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="F340" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="341" spans="1:6">
@@ -11323,10 +11323,10 @@
         <v>383</v>
       </c>
       <c r="E341" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="F341" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="342" spans="1:6">
@@ -11343,10 +11343,10 @@
         <v>383</v>
       </c>
       <c r="E342" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="F342" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="343" spans="1:6">
@@ -11383,10 +11383,10 @@
         <v>383</v>
       </c>
       <c r="E344" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="F344" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="345" spans="1:6">
@@ -11440,13 +11440,13 @@
         <v>16</v>
       </c>
       <c r="D347" t="s">
-        <v>383</v>
+        <v>407</v>
       </c>
       <c r="E347" t="s">
-        <v>407</v>
+        <v>459</v>
       </c>
       <c r="F347" t="s">
-        <v>459</v>
+        <v>385</v>
       </c>
     </row>
     <row r="348" spans="1:6">
@@ -11463,10 +11463,10 @@
         <v>383</v>
       </c>
       <c r="E348" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="F348" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="349" spans="1:6">
@@ -11763,10 +11763,10 @@
         <v>463</v>
       </c>
       <c r="E363" t="s">
-        <v>464</v>
+        <v>479</v>
       </c>
       <c r="F363" t="s">
-        <v>479</v>
+        <v>465</v>
       </c>
     </row>
     <row r="364" spans="1:6">
@@ -11800,10 +11800,10 @@
         <v>18</v>
       </c>
       <c r="D365" t="s">
-        <v>463</v>
+        <v>482</v>
       </c>
       <c r="E365" t="s">
-        <v>482</v>
+        <v>464</v>
       </c>
       <c r="F365" t="s">
         <v>465</v>
@@ -11920,10 +11920,10 @@
         <v>66</v>
       </c>
       <c r="D371" t="s">
-        <v>463</v>
+        <v>489</v>
       </c>
       <c r="E371" t="s">
-        <v>489</v>
+        <v>464</v>
       </c>
       <c r="F371" t="s">
         <v>465</v>
@@ -12160,13 +12160,13 @@
         <v>18</v>
       </c>
       <c r="D383" t="s">
-        <v>463</v>
+        <v>502</v>
       </c>
       <c r="E383" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="F383" t="s">
-        <v>503</v>
+        <v>465</v>
       </c>
     </row>
     <row r="384" spans="1:6">
@@ -12180,13 +12180,13 @@
         <v>18</v>
       </c>
       <c r="D384" t="s">
-        <v>463</v>
+        <v>502</v>
       </c>
       <c r="E384" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="F384" t="s">
-        <v>505</v>
+        <v>465</v>
       </c>
     </row>
     <row r="385" spans="1:6">
@@ -12223,10 +12223,10 @@
         <v>507</v>
       </c>
       <c r="E386" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="F386" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
     </row>
     <row r="387" spans="1:6">
@@ -12423,10 +12423,10 @@
         <v>507</v>
       </c>
       <c r="E396" t="s">
-        <v>508</v>
+        <v>522</v>
       </c>
       <c r="F396" t="s">
-        <v>522</v>
+        <v>509</v>
       </c>
     </row>
     <row r="397" spans="1:6">
@@ -12623,10 +12623,10 @@
         <v>507</v>
       </c>
       <c r="E406" t="s">
-        <v>508</v>
+        <v>533</v>
       </c>
       <c r="F406" t="s">
-        <v>533</v>
+        <v>509</v>
       </c>
     </row>
     <row r="407" spans="1:6">
@@ -12643,10 +12643,10 @@
         <v>507</v>
       </c>
       <c r="E407" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="F407" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
     </row>
     <row r="408" spans="1:6">
@@ -12720,10 +12720,10 @@
         <v>66</v>
       </c>
       <c r="D411" t="s">
-        <v>507</v>
+        <v>539</v>
       </c>
       <c r="E411" t="s">
-        <v>539</v>
+        <v>508</v>
       </c>
       <c r="F411" t="s">
         <v>509</v>
@@ -12740,13 +12740,13 @@
         <v>66</v>
       </c>
       <c r="D412" t="s">
-        <v>507</v>
+        <v>541</v>
       </c>
       <c r="E412" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="F412" t="s">
-        <v>542</v>
+        <v>509</v>
       </c>
     </row>
     <row r="413" spans="1:6">
@@ -12780,13 +12780,13 @@
         <v>66</v>
       </c>
       <c r="D414" t="s">
-        <v>507</v>
+        <v>541</v>
       </c>
       <c r="E414" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="F414" t="s">
-        <v>542</v>
+        <v>509</v>
       </c>
     </row>
     <row r="415" spans="1:6">
@@ -12903,10 +12903,10 @@
         <v>549</v>
       </c>
       <c r="E420" t="s">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="F420" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
     </row>
     <row r="421" spans="1:6">
@@ -13023,10 +13023,10 @@
         <v>549</v>
       </c>
       <c r="E426" t="s">
-        <v>550</v>
+        <v>561</v>
       </c>
       <c r="F426" t="s">
-        <v>561</v>
+        <v>551</v>
       </c>
     </row>
     <row r="427" spans="1:6">
@@ -13043,10 +13043,10 @@
         <v>549</v>
       </c>
       <c r="E427" t="s">
-        <v>550</v>
+        <v>563</v>
       </c>
       <c r="F427" t="s">
-        <v>563</v>
+        <v>551</v>
       </c>
     </row>
     <row r="428" spans="1:6">
@@ -13080,13 +13080,13 @@
         <v>18</v>
       </c>
       <c r="D429" t="s">
-        <v>549</v>
+        <v>566</v>
       </c>
       <c r="E429" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="F429" t="s">
-        <v>567</v>
+        <v>551</v>
       </c>
     </row>
     <row r="430" spans="1:6">
@@ -13163,10 +13163,10 @@
         <v>549</v>
       </c>
       <c r="E433" t="s">
-        <v>550</v>
+        <v>572</v>
       </c>
       <c r="F433" t="s">
-        <v>572</v>
+        <v>551</v>
       </c>
     </row>
     <row r="434" spans="1:6">
@@ -13200,13 +13200,13 @@
         <v>18</v>
       </c>
       <c r="D435" t="s">
-        <v>549</v>
+        <v>575</v>
       </c>
       <c r="E435" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="F435" t="s">
-        <v>576</v>
+        <v>551</v>
       </c>
     </row>
     <row r="436" spans="1:6">
@@ -13240,13 +13240,13 @@
         <v>18</v>
       </c>
       <c r="D437" t="s">
-        <v>549</v>
+        <v>579</v>
       </c>
       <c r="E437" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="F437" t="s">
-        <v>580</v>
+        <v>551</v>
       </c>
     </row>
     <row r="438" spans="1:6">
@@ -13300,13 +13300,13 @@
         <v>18</v>
       </c>
       <c r="D440" t="s">
-        <v>549</v>
+        <v>584</v>
       </c>
       <c r="E440" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="F440" t="s">
-        <v>585</v>
+        <v>551</v>
       </c>
     </row>
     <row r="441" spans="1:6">
@@ -13420,13 +13420,13 @@
         <v>18</v>
       </c>
       <c r="D446" t="s">
-        <v>549</v>
+        <v>592</v>
       </c>
       <c r="E446" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="F446" t="s">
-        <v>593</v>
+        <v>551</v>
       </c>
     </row>
     <row r="447" spans="1:6">
@@ -13443,10 +13443,10 @@
         <v>549</v>
       </c>
       <c r="E447" t="s">
-        <v>550</v>
+        <v>595</v>
       </c>
       <c r="F447" t="s">
-        <v>595</v>
+        <v>551</v>
       </c>
     </row>
     <row r="448" spans="1:6">
@@ -13463,10 +13463,10 @@
         <v>549</v>
       </c>
       <c r="E448" t="s">
-        <v>550</v>
+        <v>572</v>
       </c>
       <c r="F448" t="s">
-        <v>572</v>
+        <v>551</v>
       </c>
     </row>
     <row r="449" spans="1:6">
@@ -13483,10 +13483,10 @@
         <v>549</v>
       </c>
       <c r="E449" t="s">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="F449" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
     </row>
     <row r="450" spans="1:6">
@@ -13723,10 +13723,10 @@
         <v>608</v>
       </c>
       <c r="E461" t="s">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="F461" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
     </row>
     <row r="462" spans="1:6">
@@ -13763,10 +13763,10 @@
         <v>608</v>
       </c>
       <c r="E463" t="s">
-        <v>609</v>
+        <v>616</v>
       </c>
       <c r="F463" t="s">
-        <v>616</v>
+        <v>610</v>
       </c>
     </row>
     <row r="464" spans="1:6">
@@ -13900,13 +13900,13 @@
         <v>18</v>
       </c>
       <c r="D470" t="s">
-        <v>608</v>
+        <v>624</v>
       </c>
       <c r="E470" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="F470" t="s">
-        <v>625</v>
+        <v>610</v>
       </c>
     </row>
     <row r="471" spans="1:6">
@@ -13920,13 +13920,13 @@
         <v>18</v>
       </c>
       <c r="D471" t="s">
-        <v>608</v>
+        <v>627</v>
       </c>
       <c r="E471" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="F471" t="s">
-        <v>628</v>
+        <v>610</v>
       </c>
     </row>
     <row r="472" spans="1:6">
@@ -14003,10 +14003,10 @@
         <v>608</v>
       </c>
       <c r="E475" t="s">
-        <v>609</v>
+        <v>633</v>
       </c>
       <c r="F475" t="s">
-        <v>633</v>
+        <v>610</v>
       </c>
     </row>
     <row r="476" spans="1:6">
@@ -14063,10 +14063,10 @@
         <v>608</v>
       </c>
       <c r="E478" t="s">
-        <v>609</v>
+        <v>637</v>
       </c>
       <c r="F478" t="s">
-        <v>637</v>
+        <v>610</v>
       </c>
     </row>
     <row r="479" spans="1:6">
@@ -14083,10 +14083,10 @@
         <v>608</v>
       </c>
       <c r="E479" t="s">
-        <v>609</v>
+        <v>639</v>
       </c>
       <c r="F479" t="s">
-        <v>639</v>
+        <v>610</v>
       </c>
     </row>
     <row r="480" spans="1:6">
@@ -14140,13 +14140,13 @@
         <v>18</v>
       </c>
       <c r="D482" t="s">
-        <v>608</v>
+        <v>643</v>
       </c>
       <c r="E482" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="F482" t="s">
-        <v>644</v>
+        <v>610</v>
       </c>
     </row>
     <row r="483" spans="1:6">
@@ -14460,13 +14460,13 @@
         <v>66</v>
       </c>
       <c r="D498" t="s">
-        <v>608</v>
+        <v>661</v>
       </c>
       <c r="E498" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="F498" t="s">
-        <v>662</v>
+        <v>610</v>
       </c>
     </row>
     <row r="499" spans="1:6">
@@ -14660,13 +14660,13 @@
         <v>18</v>
       </c>
       <c r="D508" t="s">
-        <v>665</v>
+        <v>677</v>
       </c>
       <c r="E508" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="F508" t="s">
-        <v>678</v>
+        <v>667</v>
       </c>
     </row>
     <row r="509" spans="1:6">
@@ -14683,10 +14683,10 @@
         <v>665</v>
       </c>
       <c r="E509" t="s">
-        <v>666</v>
+        <v>680</v>
       </c>
       <c r="F509" t="s">
-        <v>680</v>
+        <v>667</v>
       </c>
     </row>
     <row r="510" spans="1:6">
@@ -14700,13 +14700,13 @@
         <v>18</v>
       </c>
       <c r="D510" t="s">
-        <v>665</v>
+        <v>677</v>
       </c>
       <c r="E510" t="s">
-        <v>677</v>
+        <v>682</v>
       </c>
       <c r="F510" t="s">
-        <v>682</v>
+        <v>667</v>
       </c>
     </row>
     <row r="511" spans="1:6">
@@ -14720,13 +14720,13 @@
         <v>18</v>
       </c>
       <c r="D511" t="s">
-        <v>665</v>
+        <v>684</v>
       </c>
       <c r="E511" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="F511" t="s">
-        <v>685</v>
+        <v>667</v>
       </c>
     </row>
     <row r="512" spans="1:6">
@@ -14760,13 +14760,13 @@
         <v>18</v>
       </c>
       <c r="D513" t="s">
-        <v>665</v>
+        <v>688</v>
       </c>
       <c r="E513" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="F513" t="s">
-        <v>689</v>
+        <v>667</v>
       </c>
     </row>
     <row r="514" spans="1:6">
@@ -14840,13 +14840,13 @@
         <v>18</v>
       </c>
       <c r="D517" t="s">
-        <v>665</v>
+        <v>677</v>
       </c>
       <c r="E517" t="s">
-        <v>677</v>
+        <v>694</v>
       </c>
       <c r="F517" t="s">
-        <v>694</v>
+        <v>667</v>
       </c>
     </row>
     <row r="518" spans="1:6">
@@ -15163,10 +15163,10 @@
         <v>710</v>
       </c>
       <c r="E533" t="s">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="F533" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
     </row>
     <row r="534" spans="1:6">
@@ -15240,10 +15240,10 @@
         <v>66</v>
       </c>
       <c r="D537" t="s">
-        <v>710</v>
+        <v>719</v>
       </c>
       <c r="E537" t="s">
-        <v>719</v>
+        <v>711</v>
       </c>
       <c r="F537" t="s">
         <v>712</v>
@@ -15280,13 +15280,13 @@
         <v>22</v>
       </c>
       <c r="D539" t="s">
-        <v>710</v>
+        <v>722</v>
       </c>
       <c r="E539" t="s">
-        <v>722</v>
+        <v>689</v>
       </c>
       <c r="F539" t="s">
-        <v>689</v>
+        <v>712</v>
       </c>
     </row>
     <row r="540" spans="1:6">
@@ -15300,13 +15300,13 @@
         <v>16</v>
       </c>
       <c r="D540" t="s">
-        <v>710</v>
+        <v>722</v>
       </c>
       <c r="E540" t="s">
-        <v>722</v>
+        <v>689</v>
       </c>
       <c r="F540" t="s">
-        <v>689</v>
+        <v>712</v>
       </c>
     </row>
     <row r="541" spans="1:6">
@@ -15363,10 +15363,10 @@
         <v>710</v>
       </c>
       <c r="E543" t="s">
-        <v>711</v>
+        <v>727</v>
       </c>
       <c r="F543" t="s">
-        <v>727</v>
+        <v>712</v>
       </c>
     </row>
     <row r="544" spans="1:6">
@@ -15443,10 +15443,10 @@
         <v>710</v>
       </c>
       <c r="E547" t="s">
-        <v>711</v>
+        <v>732</v>
       </c>
       <c r="F547" t="s">
-        <v>732</v>
+        <v>712</v>
       </c>
     </row>
     <row r="548" spans="1:6">
@@ -15540,13 +15540,13 @@
         <v>18</v>
       </c>
       <c r="D552" t="s">
-        <v>710</v>
+        <v>738</v>
       </c>
       <c r="E552" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="F552" t="s">
-        <v>739</v>
+        <v>712</v>
       </c>
     </row>
     <row r="553" spans="1:6">
@@ -15560,13 +15560,13 @@
         <v>664</v>
       </c>
       <c r="D553" t="s">
-        <v>710</v>
+        <v>741</v>
       </c>
       <c r="E553" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="F553" t="s">
-        <v>742</v>
+        <v>712</v>
       </c>
     </row>
     <row r="554" spans="1:6">
@@ -15580,13 +15580,13 @@
         <v>66</v>
       </c>
       <c r="D554" t="s">
-        <v>710</v>
+        <v>744</v>
       </c>
       <c r="E554" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="F554" t="s">
-        <v>742</v>
+        <v>712</v>
       </c>
     </row>
     <row r="555" spans="1:6">
@@ -15600,13 +15600,13 @@
         <v>18</v>
       </c>
       <c r="D555" t="s">
-        <v>710</v>
+        <v>746</v>
       </c>
       <c r="E555" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="F555" t="s">
-        <v>747</v>
+        <v>712</v>
       </c>
     </row>
     <row r="556" spans="1:6">
@@ -15643,10 +15643,10 @@
         <v>710</v>
       </c>
       <c r="E557" t="s">
-        <v>711</v>
+        <v>750</v>
       </c>
       <c r="F557" t="s">
-        <v>750</v>
+        <v>712</v>
       </c>
     </row>
     <row r="558" spans="1:6">
@@ -15680,10 +15680,10 @@
         <v>66</v>
       </c>
       <c r="D559" t="s">
-        <v>710</v>
+        <v>753</v>
       </c>
       <c r="E559" t="s">
-        <v>753</v>
+        <v>711</v>
       </c>
       <c r="F559" t="s">
         <v>712</v>
@@ -15843,10 +15843,10 @@
         <v>710</v>
       </c>
       <c r="E567" t="s">
-        <v>711</v>
+        <v>762</v>
       </c>
       <c r="F567" t="s">
-        <v>762</v>
+        <v>712</v>
       </c>
     </row>
     <row r="568" spans="1:6">
@@ -15863,10 +15863,10 @@
         <v>710</v>
       </c>
       <c r="E568" t="s">
-        <v>711</v>
+        <v>764</v>
       </c>
       <c r="F568" t="s">
-        <v>764</v>
+        <v>712</v>
       </c>
     </row>
     <row r="569" spans="1:6">
@@ -15883,10 +15883,10 @@
         <v>710</v>
       </c>
       <c r="E569" t="s">
-        <v>711</v>
+        <v>766</v>
       </c>
       <c r="F569" t="s">
-        <v>766</v>
+        <v>712</v>
       </c>
     </row>
     <row r="570" spans="1:6">
@@ -15923,10 +15923,10 @@
         <v>770</v>
       </c>
       <c r="E571" t="s">
+        <v>714</v>
+      </c>
+      <c r="F571" t="s">
         <v>771</v>
-      </c>
-      <c r="F571" t="s">
-        <v>714</v>
       </c>
     </row>
     <row r="572" spans="1:6">
@@ -15943,10 +15943,10 @@
         <v>770</v>
       </c>
       <c r="E572" t="s">
+        <v>714</v>
+      </c>
+      <c r="F572" t="s">
         <v>771</v>
-      </c>
-      <c r="F572" t="s">
-        <v>714</v>
       </c>
     </row>
     <row r="573" spans="1:6">
@@ -15963,10 +15963,10 @@
         <v>770</v>
       </c>
       <c r="E573" t="s">
+        <v>714</v>
+      </c>
+      <c r="F573" t="s">
         <v>771</v>
-      </c>
-      <c r="F573" t="s">
-        <v>714</v>
       </c>
     </row>
     <row r="574" spans="1:6">
@@ -15983,10 +15983,10 @@
         <v>770</v>
       </c>
       <c r="E574" t="s">
+        <v>714</v>
+      </c>
+      <c r="F574" t="s">
         <v>771</v>
-      </c>
-      <c r="F574" t="s">
-        <v>714</v>
       </c>
     </row>
     <row r="575" spans="1:6">
@@ -16003,10 +16003,10 @@
         <v>770</v>
       </c>
       <c r="E575" t="s">
+        <v>776</v>
+      </c>
+      <c r="F575" t="s">
         <v>771</v>
-      </c>
-      <c r="F575" t="s">
-        <v>776</v>
       </c>
     </row>
     <row r="576" spans="1:6">
@@ -16020,13 +16020,13 @@
         <v>769</v>
       </c>
       <c r="D576" t="s">
-        <v>770</v>
+        <v>778</v>
       </c>
       <c r="E576" t="s">
-        <v>778</v>
+        <v>714</v>
       </c>
       <c r="F576" t="s">
-        <v>714</v>
+        <v>771</v>
       </c>
     </row>
     <row r="577" spans="1:6">
@@ -16043,10 +16043,10 @@
         <v>770</v>
       </c>
       <c r="E577" t="s">
+        <v>714</v>
+      </c>
+      <c r="F577" t="s">
         <v>771</v>
-      </c>
-      <c r="F577" t="s">
-        <v>714</v>
       </c>
     </row>
     <row r="578" spans="1:6">
@@ -16063,10 +16063,10 @@
         <v>770</v>
       </c>
       <c r="E578" t="s">
+        <v>714</v>
+      </c>
+      <c r="F578" t="s">
         <v>771</v>
-      </c>
-      <c r="F578" t="s">
-        <v>714</v>
       </c>
     </row>
     <row r="579" spans="1:6">
@@ -16083,10 +16083,10 @@
         <v>770</v>
       </c>
       <c r="E579" t="s">
+        <v>714</v>
+      </c>
+      <c r="F579" t="s">
         <v>771</v>
-      </c>
-      <c r="F579" t="s">
-        <v>714</v>
       </c>
     </row>
     <row r="580" spans="1:6">
@@ -16103,10 +16103,10 @@
         <v>770</v>
       </c>
       <c r="E580" t="s">
+        <v>714</v>
+      </c>
+      <c r="F580" t="s">
         <v>771</v>
-      </c>
-      <c r="F580" t="s">
-        <v>714</v>
       </c>
     </row>
     <row r="581" spans="1:6">
@@ -16123,10 +16123,10 @@
         <v>770</v>
       </c>
       <c r="E581" t="s">
+        <v>714</v>
+      </c>
+      <c r="F581" t="s">
         <v>771</v>
-      </c>
-      <c r="F581" t="s">
-        <v>714</v>
       </c>
     </row>
     <row r="582" spans="1:6">
@@ -16143,10 +16143,10 @@
         <v>770</v>
       </c>
       <c r="E582" t="s">
+        <v>785</v>
+      </c>
+      <c r="F582" t="s">
         <v>771</v>
-      </c>
-      <c r="F582" t="s">
-        <v>785</v>
       </c>
     </row>
     <row r="583" spans="1:6">
@@ -16163,10 +16163,10 @@
         <v>770</v>
       </c>
       <c r="E583" t="s">
+        <v>787</v>
+      </c>
+      <c r="F583" t="s">
         <v>771</v>
-      </c>
-      <c r="F583" t="s">
-        <v>787</v>
       </c>
     </row>
     <row r="584" spans="1:6">
@@ -16183,10 +16183,10 @@
         <v>770</v>
       </c>
       <c r="E584" t="s">
+        <v>714</v>
+      </c>
+      <c r="F584" t="s">
         <v>771</v>
-      </c>
-      <c r="F584" t="s">
-        <v>714</v>
       </c>
     </row>
     <row r="585" spans="1:6">
@@ -16203,10 +16203,10 @@
         <v>770</v>
       </c>
       <c r="E585" t="s">
+        <v>714</v>
+      </c>
+      <c r="F585" t="s">
         <v>771</v>
-      </c>
-      <c r="F585" t="s">
-        <v>714</v>
       </c>
     </row>
     <row r="586" spans="1:6">
@@ -16220,13 +16220,13 @@
         <v>769</v>
       </c>
       <c r="D586" t="s">
-        <v>770</v>
+        <v>746</v>
       </c>
       <c r="E586" t="s">
-        <v>746</v>
+        <v>714</v>
       </c>
       <c r="F586" t="s">
-        <v>714</v>
+        <v>771</v>
       </c>
     </row>
     <row r="587" spans="1:6">
@@ -16243,10 +16243,10 @@
         <v>770</v>
       </c>
       <c r="E587" t="s">
+        <v>714</v>
+      </c>
+      <c r="F587" t="s">
         <v>771</v>
-      </c>
-      <c r="F587" t="s">
-        <v>714</v>
       </c>
     </row>
     <row r="588" spans="1:6">
@@ -16263,10 +16263,10 @@
         <v>770</v>
       </c>
       <c r="E588" t="s">
+        <v>714</v>
+      </c>
+      <c r="F588" t="s">
         <v>771</v>
-      </c>
-      <c r="F588" t="s">
-        <v>714</v>
       </c>
     </row>
     <row r="589" spans="1:6">
@@ -16283,10 +16283,10 @@
         <v>770</v>
       </c>
       <c r="E589" t="s">
+        <v>714</v>
+      </c>
+      <c r="F589" t="s">
         <v>771</v>
-      </c>
-      <c r="F589" t="s">
-        <v>714</v>
       </c>
     </row>
     <row r="590" spans="1:6">
@@ -16303,10 +16303,10 @@
         <v>770</v>
       </c>
       <c r="E590" t="s">
+        <v>714</v>
+      </c>
+      <c r="F590" t="s">
         <v>771</v>
-      </c>
-      <c r="F590" t="s">
-        <v>714</v>
       </c>
     </row>
     <row r="591" spans="1:6">
@@ -16320,13 +16320,13 @@
         <v>22</v>
       </c>
       <c r="D591" t="s">
-        <v>770</v>
+        <v>796</v>
       </c>
       <c r="E591" t="s">
-        <v>796</v>
+        <v>714</v>
       </c>
       <c r="F591" t="s">
-        <v>714</v>
+        <v>771</v>
       </c>
     </row>
     <row r="592" spans="1:6">
@@ -16343,10 +16343,10 @@
         <v>770</v>
       </c>
       <c r="E592" t="s">
+        <v>714</v>
+      </c>
+      <c r="F592" t="s">
         <v>771</v>
-      </c>
-      <c r="F592" t="s">
-        <v>714</v>
       </c>
     </row>
     <row r="593" spans="1:6">
@@ -16363,10 +16363,10 @@
         <v>770</v>
       </c>
       <c r="E593" t="s">
+        <v>714</v>
+      </c>
+      <c r="F593" t="s">
         <v>771</v>
-      </c>
-      <c r="F593" t="s">
-        <v>714</v>
       </c>
     </row>
     <row r="594" spans="1:6">
@@ -16403,10 +16403,10 @@
         <v>800</v>
       </c>
       <c r="E595" t="s">
-        <v>801</v>
+        <v>804</v>
       </c>
       <c r="F595" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
     </row>
     <row r="596" spans="1:6">
@@ -16423,10 +16423,10 @@
         <v>800</v>
       </c>
       <c r="E596" t="s">
-        <v>801</v>
+        <v>806</v>
       </c>
       <c r="F596" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
     </row>
     <row r="597" spans="1:6">
@@ -16500,10 +16500,10 @@
         <v>769</v>
       </c>
       <c r="D600" t="s">
-        <v>800</v>
+        <v>811</v>
       </c>
       <c r="E600" t="s">
-        <v>811</v>
+        <v>801</v>
       </c>
       <c r="F600" t="s">
         <v>802</v>
@@ -16580,13 +16580,13 @@
         <v>18</v>
       </c>
       <c r="D604" t="s">
-        <v>800</v>
+        <v>816</v>
       </c>
       <c r="E604" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="F604" t="s">
-        <v>817</v>
+        <v>802</v>
       </c>
     </row>
     <row r="605" spans="1:6">
@@ -16623,10 +16623,10 @@
         <v>800</v>
       </c>
       <c r="E606" t="s">
-        <v>801</v>
+        <v>820</v>
       </c>
       <c r="F606" t="s">
-        <v>820</v>
+        <v>802</v>
       </c>
     </row>
     <row r="607" spans="1:6">
@@ -16643,10 +16643,10 @@
         <v>800</v>
       </c>
       <c r="E607" t="s">
-        <v>801</v>
+        <v>820</v>
       </c>
       <c r="F607" t="s">
-        <v>820</v>
+        <v>802</v>
       </c>
     </row>
     <row r="608" spans="1:6">
@@ -16680,10 +16680,10 @@
         <v>16</v>
       </c>
       <c r="D609" t="s">
-        <v>800</v>
+        <v>824</v>
       </c>
       <c r="E609" t="s">
-        <v>824</v>
+        <v>801</v>
       </c>
       <c r="F609" t="s">
         <v>802</v>
@@ -16800,13 +16800,13 @@
         <v>769</v>
       </c>
       <c r="D615" t="s">
-        <v>800</v>
+        <v>831</v>
       </c>
       <c r="E615" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="F615" t="s">
-        <v>832</v>
+        <v>802</v>
       </c>
     </row>
     <row r="616" spans="1:6">
@@ -16880,10 +16880,10 @@
         <v>769</v>
       </c>
       <c r="D619" t="s">
+        <v>770</v>
+      </c>
+      <c r="E619" t="s">
         <v>837</v>
-      </c>
-      <c r="E619" t="s">
-        <v>771</v>
       </c>
       <c r="F619" t="s">
         <v>838</v>
@@ -16900,10 +16900,10 @@
         <v>769</v>
       </c>
       <c r="D620" t="s">
+        <v>840</v>
+      </c>
+      <c r="E620" t="s">
         <v>837</v>
-      </c>
-      <c r="E620" t="s">
-        <v>840</v>
       </c>
       <c r="F620" t="s">
         <v>838</v>
@@ -16920,10 +16920,10 @@
         <v>769</v>
       </c>
       <c r="D621" t="s">
+        <v>840</v>
+      </c>
+      <c r="E621" t="s">
         <v>837</v>
-      </c>
-      <c r="E621" t="s">
-        <v>840</v>
       </c>
       <c r="F621" t="s">
         <v>838</v>
@@ -16940,10 +16940,10 @@
         <v>769</v>
       </c>
       <c r="D622" t="s">
+        <v>840</v>
+      </c>
+      <c r="E622" t="s">
         <v>837</v>
-      </c>
-      <c r="E622" t="s">
-        <v>840</v>
       </c>
       <c r="F622" t="s">
         <v>838</v>
@@ -16960,10 +16960,10 @@
         <v>769</v>
       </c>
       <c r="D623" t="s">
+        <v>800</v>
+      </c>
+      <c r="E623" t="s">
         <v>837</v>
-      </c>
-      <c r="E623" t="s">
-        <v>801</v>
       </c>
       <c r="F623" t="s">
         <v>838</v>
@@ -16980,13 +16980,13 @@
         <v>769</v>
       </c>
       <c r="D624" t="s">
-        <v>837</v>
+        <v>840</v>
       </c>
       <c r="E624" t="s">
-        <v>840</v>
+        <v>845</v>
       </c>
       <c r="F624" t="s">
-        <v>845</v>
+        <v>838</v>
       </c>
     </row>
     <row r="625" spans="1:6">
@@ -17000,13 +17000,13 @@
         <v>18</v>
       </c>
       <c r="D625" t="s">
-        <v>837</v>
+        <v>847</v>
       </c>
       <c r="E625" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="F625" t="s">
-        <v>848</v>
+        <v>838</v>
       </c>
     </row>
     <row r="626" spans="1:6">
@@ -17020,13 +17020,13 @@
         <v>769</v>
       </c>
       <c r="D626" t="s">
-        <v>837</v>
+        <v>840</v>
       </c>
       <c r="E626" t="s">
-        <v>840</v>
+        <v>850</v>
       </c>
       <c r="F626" t="s">
-        <v>850</v>
+        <v>838</v>
       </c>
     </row>
     <row r="627" spans="1:6">
@@ -17040,13 +17040,13 @@
         <v>16</v>
       </c>
       <c r="D627" t="s">
-        <v>837</v>
+        <v>840</v>
       </c>
       <c r="E627" t="s">
-        <v>840</v>
+        <v>852</v>
       </c>
       <c r="F627" t="s">
-        <v>852</v>
+        <v>838</v>
       </c>
     </row>
     <row r="628" spans="1:6">
@@ -17060,10 +17060,10 @@
         <v>16</v>
       </c>
       <c r="D628" t="s">
+        <v>840</v>
+      </c>
+      <c r="E628" t="s">
         <v>837</v>
-      </c>
-      <c r="E628" t="s">
-        <v>840</v>
       </c>
       <c r="F628" t="s">
         <v>838</v>
@@ -17080,13 +17080,13 @@
         <v>18</v>
       </c>
       <c r="D629" t="s">
-        <v>837</v>
+        <v>855</v>
       </c>
       <c r="E629" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="F629" t="s">
-        <v>856</v>
+        <v>838</v>
       </c>
     </row>
     <row r="630" spans="1:6">
@@ -17100,13 +17100,13 @@
         <v>18</v>
       </c>
       <c r="D630" t="s">
-        <v>837</v>
+        <v>858</v>
       </c>
       <c r="E630" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="F630" t="s">
-        <v>859</v>
+        <v>838</v>
       </c>
     </row>
     <row r="631" spans="1:6">
@@ -17120,10 +17120,10 @@
         <v>769</v>
       </c>
       <c r="D631" t="s">
+        <v>840</v>
+      </c>
+      <c r="E631" t="s">
         <v>837</v>
-      </c>
-      <c r="E631" t="s">
-        <v>840</v>
       </c>
       <c r="F631" t="s">
         <v>838</v>
@@ -17140,13 +17140,13 @@
         <v>18</v>
       </c>
       <c r="D632" t="s">
-        <v>837</v>
+        <v>862</v>
       </c>
       <c r="E632" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="F632" t="s">
-        <v>863</v>
+        <v>838</v>
       </c>
     </row>
     <row r="633" spans="1:6">
@@ -17160,13 +17160,13 @@
         <v>22</v>
       </c>
       <c r="D633" t="s">
-        <v>837</v>
+        <v>840</v>
       </c>
       <c r="E633" t="s">
-        <v>840</v>
+        <v>865</v>
       </c>
       <c r="F633" t="s">
-        <v>865</v>
+        <v>838</v>
       </c>
     </row>
     <row r="634" spans="1:6">
@@ -17180,13 +17180,13 @@
         <v>769</v>
       </c>
       <c r="D634" t="s">
-        <v>837</v>
+        <v>840</v>
       </c>
       <c r="E634" t="s">
-        <v>840</v>
+        <v>867</v>
       </c>
       <c r="F634" t="s">
-        <v>867</v>
+        <v>838</v>
       </c>
     </row>
     <row r="635" spans="1:6">
@@ -17200,10 +17200,10 @@
         <v>769</v>
       </c>
       <c r="D635" t="s">
+        <v>840</v>
+      </c>
+      <c r="E635" t="s">
         <v>837</v>
-      </c>
-      <c r="E635" t="s">
-        <v>840</v>
       </c>
       <c r="F635" t="s">
         <v>838</v>
@@ -17220,10 +17220,10 @@
         <v>18</v>
       </c>
       <c r="D636" t="s">
+        <v>840</v>
+      </c>
+      <c r="E636" t="s">
         <v>837</v>
-      </c>
-      <c r="E636" t="s">
-        <v>840</v>
       </c>
       <c r="F636" t="s">
         <v>838</v>
@@ -17240,10 +17240,10 @@
         <v>16</v>
       </c>
       <c r="D637" t="s">
+        <v>840</v>
+      </c>
+      <c r="E637" t="s">
         <v>837</v>
-      </c>
-      <c r="E637" t="s">
-        <v>840</v>
       </c>
       <c r="F637" t="s">
         <v>838</v>
@@ -17260,10 +17260,10 @@
         <v>769</v>
       </c>
       <c r="D638" t="s">
+        <v>872</v>
+      </c>
+      <c r="E638" t="s">
         <v>837</v>
-      </c>
-      <c r="E638" t="s">
-        <v>872</v>
       </c>
       <c r="F638" t="s">
         <v>838</v>
@@ -17280,10 +17280,10 @@
         <v>22</v>
       </c>
       <c r="D639" t="s">
+        <v>840</v>
+      </c>
+      <c r="E639" t="s">
         <v>837</v>
-      </c>
-      <c r="E639" t="s">
-        <v>840</v>
       </c>
       <c r="F639" t="s">
         <v>838</v>
@@ -17300,10 +17300,10 @@
         <v>769</v>
       </c>
       <c r="D640" t="s">
+        <v>840</v>
+      </c>
+      <c r="E640" t="s">
         <v>837</v>
-      </c>
-      <c r="E640" t="s">
-        <v>840</v>
       </c>
       <c r="F640" t="s">
         <v>838</v>
@@ -17320,10 +17320,10 @@
         <v>769</v>
       </c>
       <c r="D641" t="s">
+        <v>840</v>
+      </c>
+      <c r="E641" t="s">
         <v>837</v>
-      </c>
-      <c r="E641" t="s">
-        <v>840</v>
       </c>
       <c r="F641" t="s">
         <v>838</v>
@@ -17340,10 +17340,10 @@
         <v>769</v>
       </c>
       <c r="D642" t="s">
+        <v>840</v>
+      </c>
+      <c r="E642" t="s">
         <v>837</v>
-      </c>
-      <c r="E642" t="s">
-        <v>840</v>
       </c>
       <c r="F642" t="s">
         <v>838</v>
@@ -17380,13 +17380,13 @@
         <v>16</v>
       </c>
       <c r="D644" t="s">
-        <v>878</v>
+        <v>882</v>
       </c>
       <c r="E644" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="F644" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
     </row>
     <row r="645" spans="1:6">
@@ -17460,13 +17460,13 @@
         <v>18</v>
       </c>
       <c r="D648" t="s">
-        <v>878</v>
+        <v>888</v>
       </c>
       <c r="E648" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="F648" t="s">
-        <v>889</v>
+        <v>880</v>
       </c>
     </row>
     <row r="649" spans="1:6">
@@ -17480,13 +17480,13 @@
         <v>18</v>
       </c>
       <c r="D649" t="s">
-        <v>878</v>
+        <v>891</v>
       </c>
       <c r="E649" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="F649" t="s">
-        <v>892</v>
+        <v>880</v>
       </c>
     </row>
     <row r="650" spans="1:6">
@@ -17500,13 +17500,13 @@
         <v>769</v>
       </c>
       <c r="D650" t="s">
-        <v>878</v>
+        <v>894</v>
       </c>
       <c r="E650" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="F650" t="s">
-        <v>895</v>
+        <v>880</v>
       </c>
     </row>
     <row r="651" spans="1:6">
@@ -17523,10 +17523,10 @@
         <v>878</v>
       </c>
       <c r="E651" t="s">
-        <v>879</v>
+        <v>897</v>
       </c>
       <c r="F651" t="s">
-        <v>897</v>
+        <v>880</v>
       </c>
     </row>
     <row r="652" spans="1:6">
@@ -17600,13 +17600,13 @@
         <v>18</v>
       </c>
       <c r="D655" t="s">
-        <v>878</v>
+        <v>902</v>
       </c>
       <c r="E655" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="F655" t="s">
-        <v>903</v>
+        <v>880</v>
       </c>
     </row>
     <row r="656" spans="1:6">
@@ -17620,13 +17620,13 @@
         <v>769</v>
       </c>
       <c r="D656" t="s">
-        <v>878</v>
+        <v>865</v>
       </c>
       <c r="E656" t="s">
-        <v>865</v>
+        <v>905</v>
       </c>
       <c r="F656" t="s">
-        <v>905</v>
+        <v>880</v>
       </c>
     </row>
     <row r="657" spans="1:6">
@@ -17660,13 +17660,13 @@
         <v>18</v>
       </c>
       <c r="D658" t="s">
-        <v>878</v>
+        <v>908</v>
       </c>
       <c r="E658" t="s">
-        <v>908</v>
+        <v>883</v>
       </c>
       <c r="F658" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
     </row>
     <row r="659" spans="1:6">
@@ -17683,10 +17683,10 @@
         <v>878</v>
       </c>
       <c r="E659" t="s">
-        <v>879</v>
+        <v>910</v>
       </c>
       <c r="F659" t="s">
-        <v>910</v>
+        <v>880</v>
       </c>
     </row>
     <row r="660" spans="1:6">
@@ -17703,10 +17703,10 @@
         <v>878</v>
       </c>
       <c r="E660" t="s">
-        <v>879</v>
+        <v>910</v>
       </c>
       <c r="F660" t="s">
-        <v>910</v>
+        <v>880</v>
       </c>
     </row>
     <row r="661" spans="1:6">
@@ -17743,10 +17743,10 @@
         <v>878</v>
       </c>
       <c r="E662" t="s">
-        <v>879</v>
+        <v>914</v>
       </c>
       <c r="F662" t="s">
-        <v>914</v>
+        <v>880</v>
       </c>
     </row>
     <row r="663" spans="1:6">
@@ -17980,13 +17980,13 @@
         <v>18</v>
       </c>
       <c r="D674" t="s">
-        <v>926</v>
+        <v>930</v>
       </c>
       <c r="E674" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="F674" t="s">
-        <v>931</v>
+        <v>928</v>
       </c>
     </row>
     <row r="675" spans="1:6">
@@ -18060,10 +18060,10 @@
         <v>769</v>
       </c>
       <c r="D678" t="s">
-        <v>926</v>
+        <v>936</v>
       </c>
       <c r="E678" t="s">
-        <v>936</v>
+        <v>927</v>
       </c>
       <c r="F678" t="s">
         <v>928</v>
@@ -18083,10 +18083,10 @@
         <v>926</v>
       </c>
       <c r="E679" t="s">
-        <v>927</v>
+        <v>938</v>
       </c>
       <c r="F679" t="s">
-        <v>938</v>
+        <v>928</v>
       </c>
     </row>
     <row r="680" spans="1:6">
@@ -18160,13 +18160,13 @@
         <v>18</v>
       </c>
       <c r="D683" t="s">
-        <v>926</v>
+        <v>943</v>
       </c>
       <c r="E683" t="s">
-        <v>943</v>
+        <v>938</v>
       </c>
       <c r="F683" t="s">
-        <v>938</v>
+        <v>928</v>
       </c>
     </row>
     <row r="684" spans="1:6">
@@ -18180,13 +18180,13 @@
         <v>18</v>
       </c>
       <c r="D684" t="s">
-        <v>926</v>
+        <v>945</v>
       </c>
       <c r="E684" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="F684" t="s">
-        <v>946</v>
+        <v>928</v>
       </c>
     </row>
     <row r="685" spans="1:6">
@@ -18200,13 +18200,13 @@
         <v>18</v>
       </c>
       <c r="D685" t="s">
-        <v>926</v>
+        <v>948</v>
       </c>
       <c r="E685" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="F685" t="s">
-        <v>949</v>
+        <v>928</v>
       </c>
     </row>
     <row r="686" spans="1:6">
@@ -18243,10 +18243,10 @@
         <v>926</v>
       </c>
       <c r="E687" t="s">
-        <v>927</v>
+        <v>952</v>
       </c>
       <c r="F687" t="s">
-        <v>952</v>
+        <v>928</v>
       </c>
     </row>
     <row r="688" spans="1:6">
@@ -18260,13 +18260,13 @@
         <v>18</v>
       </c>
       <c r="D688" t="s">
-        <v>926</v>
+        <v>954</v>
       </c>
       <c r="E688" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="F688" t="s">
-        <v>955</v>
+        <v>928</v>
       </c>
     </row>
     <row r="689" spans="1:6">
@@ -18340,13 +18340,13 @@
         <v>16</v>
       </c>
       <c r="D692" t="s">
-        <v>926</v>
+        <v>960</v>
       </c>
       <c r="E692" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="F692" t="s">
-        <v>961</v>
+        <v>928</v>
       </c>
     </row>
     <row r="693" spans="1:6">
@@ -18363,10 +18363,10 @@
         <v>926</v>
       </c>
       <c r="E693" t="s">
-        <v>927</v>
+        <v>963</v>
       </c>
       <c r="F693" t="s">
-        <v>963</v>
+        <v>928</v>
       </c>
     </row>
     <row r="694" spans="1:6">
@@ -18383,10 +18383,10 @@
         <v>926</v>
       </c>
       <c r="E694" t="s">
-        <v>927</v>
+        <v>965</v>
       </c>
       <c r="F694" t="s">
-        <v>965</v>
+        <v>928</v>
       </c>
     </row>
     <row r="695" spans="1:6">
@@ -18463,10 +18463,10 @@
         <v>926</v>
       </c>
       <c r="E698" t="s">
-        <v>927</v>
+        <v>970</v>
       </c>
       <c r="F698" t="s">
-        <v>970</v>
+        <v>928</v>
       </c>
     </row>
     <row r="699" spans="1:6">
@@ -18540,13 +18540,13 @@
         <v>16</v>
       </c>
       <c r="D702" t="s">
-        <v>974</v>
+        <v>978</v>
       </c>
       <c r="E702" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="F702" t="s">
-        <v>979</v>
+        <v>976</v>
       </c>
     </row>
     <row r="703" spans="1:6">
@@ -18560,10 +18560,10 @@
         <v>18</v>
       </c>
       <c r="D703" t="s">
-        <v>974</v>
+        <v>981</v>
       </c>
       <c r="E703" t="s">
-        <v>981</v>
+        <v>975</v>
       </c>
       <c r="F703" t="s">
         <v>976</v>
@@ -18580,13 +18580,13 @@
         <v>769</v>
       </c>
       <c r="D704" t="s">
-        <v>974</v>
+        <v>983</v>
       </c>
       <c r="E704" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="F704" t="s">
-        <v>984</v>
+        <v>976</v>
       </c>
     </row>
     <row r="705" spans="1:6">
@@ -18600,13 +18600,13 @@
         <v>769</v>
       </c>
       <c r="D705" t="s">
-        <v>974</v>
+        <v>983</v>
       </c>
       <c r="E705" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="F705" t="s">
-        <v>984</v>
+        <v>976</v>
       </c>
     </row>
     <row r="706" spans="1:6">
@@ -18620,13 +18620,13 @@
         <v>16</v>
       </c>
       <c r="D706" t="s">
-        <v>974</v>
+        <v>926</v>
       </c>
       <c r="E706" t="s">
-        <v>927</v>
+        <v>965</v>
       </c>
       <c r="F706" t="s">
-        <v>965</v>
+        <v>976</v>
       </c>
     </row>
     <row r="707" spans="1:6">
@@ -18640,13 +18640,13 @@
         <v>769</v>
       </c>
       <c r="D707" t="s">
-        <v>974</v>
+        <v>983</v>
       </c>
       <c r="E707" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="F707" t="s">
-        <v>984</v>
+        <v>976</v>
       </c>
     </row>
     <row r="708" spans="1:6">
@@ -18660,13 +18660,13 @@
         <v>769</v>
       </c>
       <c r="D708" t="s">
-        <v>974</v>
+        <v>983</v>
       </c>
       <c r="E708" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="F708" t="s">
-        <v>984</v>
+        <v>976</v>
       </c>
     </row>
     <row r="709" spans="1:6">
@@ -18680,13 +18680,13 @@
         <v>16</v>
       </c>
       <c r="D709" t="s">
-        <v>974</v>
+        <v>990</v>
       </c>
       <c r="E709" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="F709" t="s">
-        <v>991</v>
+        <v>976</v>
       </c>
     </row>
     <row r="710" spans="1:6">
@@ -18700,13 +18700,13 @@
         <v>18</v>
       </c>
       <c r="D710" t="s">
-        <v>974</v>
+        <v>993</v>
       </c>
       <c r="E710" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="F710" t="s">
-        <v>994</v>
+        <v>976</v>
       </c>
     </row>
     <row r="711" spans="1:6">
@@ -18720,13 +18720,13 @@
         <v>18</v>
       </c>
       <c r="D711" t="s">
-        <v>974</v>
+        <v>996</v>
       </c>
       <c r="E711" t="s">
-        <v>996</v>
+        <v>952</v>
       </c>
       <c r="F711" t="s">
-        <v>952</v>
+        <v>976</v>
       </c>
     </row>
     <row r="712" spans="1:6">
@@ -18740,13 +18740,13 @@
         <v>18</v>
       </c>
       <c r="D712" t="s">
-        <v>974</v>
+        <v>998</v>
       </c>
       <c r="E712" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="F712" t="s">
-        <v>999</v>
+        <v>976</v>
       </c>
     </row>
     <row r="713" spans="1:6">
@@ -18760,13 +18760,13 @@
         <v>769</v>
       </c>
       <c r="D713" t="s">
-        <v>974</v>
+        <v>983</v>
       </c>
       <c r="E713" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="F713" t="s">
-        <v>984</v>
+        <v>976</v>
       </c>
     </row>
     <row r="714" spans="1:6">
@@ -18780,13 +18780,13 @@
         <v>18</v>
       </c>
       <c r="D714" t="s">
-        <v>974</v>
+        <v>979</v>
       </c>
       <c r="E714" t="s">
-        <v>979</v>
+        <v>984</v>
       </c>
       <c r="F714" t="s">
-        <v>984</v>
+        <v>976</v>
       </c>
     </row>
     <row r="715" spans="1:6">
@@ -18800,13 +18800,13 @@
         <v>18</v>
       </c>
       <c r="D715" t="s">
-        <v>974</v>
+        <v>1003</v>
       </c>
       <c r="E715" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="F715" t="s">
-        <v>1004</v>
+        <v>976</v>
       </c>
     </row>
     <row r="716" spans="1:6">
@@ -18820,13 +18820,13 @@
         <v>16</v>
       </c>
       <c r="D716" t="s">
-        <v>974</v>
+        <v>1006</v>
       </c>
       <c r="E716" t="s">
-        <v>1006</v>
+        <v>965</v>
       </c>
       <c r="F716" t="s">
-        <v>965</v>
+        <v>976</v>
       </c>
     </row>
     <row r="717" spans="1:6">
@@ -18840,13 +18840,13 @@
         <v>16</v>
       </c>
       <c r="D717" t="s">
-        <v>974</v>
+        <v>983</v>
       </c>
       <c r="E717" t="s">
-        <v>983</v>
+        <v>1008</v>
       </c>
       <c r="F717" t="s">
-        <v>1008</v>
+        <v>976</v>
       </c>
     </row>
     <row r="718" spans="1:6">
@@ -18860,13 +18860,13 @@
         <v>769</v>
       </c>
       <c r="D718" t="s">
-        <v>974</v>
+        <v>983</v>
       </c>
       <c r="E718" t="s">
-        <v>983</v>
+        <v>1008</v>
       </c>
       <c r="F718" t="s">
-        <v>1008</v>
+        <v>976</v>
       </c>
     </row>
     <row r="719" spans="1:6">
@@ -18883,10 +18883,10 @@
         <v>974</v>
       </c>
       <c r="E719" t="s">
-        <v>975</v>
+        <v>1008</v>
       </c>
       <c r="F719" t="s">
-        <v>1008</v>
+        <v>976</v>
       </c>
     </row>
     <row r="720" spans="1:6">
@@ -18900,13 +18900,13 @@
         <v>18</v>
       </c>
       <c r="D720" t="s">
-        <v>974</v>
+        <v>1012</v>
       </c>
       <c r="E720" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="F720" t="s">
-        <v>1013</v>
+        <v>976</v>
       </c>
     </row>
     <row r="721" spans="1:6">
@@ -18920,13 +18920,13 @@
         <v>16</v>
       </c>
       <c r="D721" t="s">
-        <v>974</v>
+        <v>983</v>
       </c>
       <c r="E721" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="F721" t="s">
-        <v>984</v>
+        <v>976</v>
       </c>
     </row>
     <row r="722" spans="1:6">
@@ -18940,13 +18940,13 @@
         <v>16</v>
       </c>
       <c r="D722" t="s">
-        <v>974</v>
+        <v>996</v>
       </c>
       <c r="E722" t="s">
-        <v>996</v>
+        <v>965</v>
       </c>
       <c r="F722" t="s">
-        <v>965</v>
+        <v>976</v>
       </c>
     </row>
     <row r="723" spans="1:6">
@@ -18960,13 +18960,13 @@
         <v>769</v>
       </c>
       <c r="D723" t="s">
-        <v>974</v>
+        <v>983</v>
       </c>
       <c r="E723" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="F723" t="s">
-        <v>984</v>
+        <v>976</v>
       </c>
     </row>
     <row r="724" spans="1:6">
@@ -18980,10 +18980,10 @@
         <v>22</v>
       </c>
       <c r="D724" t="s">
-        <v>974</v>
+        <v>1018</v>
       </c>
       <c r="E724" t="s">
-        <v>1018</v>
+        <v>975</v>
       </c>
       <c r="F724" t="s">
         <v>976</v>
@@ -19000,13 +19000,13 @@
         <v>16</v>
       </c>
       <c r="D725" t="s">
-        <v>974</v>
+        <v>983</v>
       </c>
       <c r="E725" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="F725" t="s">
-        <v>984</v>
+        <v>976</v>
       </c>
     </row>
     <row r="726" spans="1:6">
@@ -19020,13 +19020,13 @@
         <v>769</v>
       </c>
       <c r="D726" t="s">
-        <v>974</v>
+        <v>983</v>
       </c>
       <c r="E726" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="F726" t="s">
-        <v>984</v>
+        <v>976</v>
       </c>
     </row>
     <row r="727" spans="1:6">
@@ -19040,13 +19040,13 @@
         <v>16</v>
       </c>
       <c r="D727" t="s">
-        <v>974</v>
+        <v>998</v>
       </c>
       <c r="E727" t="s">
-        <v>998</v>
+        <v>965</v>
       </c>
       <c r="F727" t="s">
-        <v>965</v>
+        <v>976</v>
       </c>
     </row>
     <row r="728" spans="1:6">
@@ -19060,10 +19060,10 @@
         <v>18</v>
       </c>
       <c r="D728" t="s">
-        <v>974</v>
+        <v>981</v>
       </c>
       <c r="E728" t="s">
-        <v>981</v>
+        <v>975</v>
       </c>
       <c r="F728" t="s">
         <v>976</v>
@@ -19080,13 +19080,13 @@
         <v>16</v>
       </c>
       <c r="D729" t="s">
-        <v>974</v>
+        <v>983</v>
       </c>
       <c r="E729" t="s">
-        <v>983</v>
+        <v>1024</v>
       </c>
       <c r="F729" t="s">
-        <v>1024</v>
+        <v>976</v>
       </c>
     </row>
     <row r="730" spans="1:6">
@@ -19100,13 +19100,13 @@
         <v>769</v>
       </c>
       <c r="D730" t="s">
-        <v>974</v>
+        <v>983</v>
       </c>
       <c r="E730" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="F730" t="s">
-        <v>984</v>
+        <v>976</v>
       </c>
     </row>
     <row r="731" spans="1:6">
@@ -19120,13 +19120,13 @@
         <v>22</v>
       </c>
       <c r="D731" t="s">
-        <v>974</v>
+        <v>983</v>
       </c>
       <c r="E731" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="F731" t="s">
-        <v>984</v>
+        <v>976</v>
       </c>
     </row>
     <row r="732" spans="1:6">
@@ -19140,13 +19140,13 @@
         <v>769</v>
       </c>
       <c r="D732" t="s">
-        <v>974</v>
+        <v>983</v>
       </c>
       <c r="E732" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="F732" t="s">
-        <v>984</v>
+        <v>976</v>
       </c>
     </row>
     <row r="733" spans="1:6">
@@ -19160,13 +19160,13 @@
         <v>18</v>
       </c>
       <c r="D733" t="s">
-        <v>974</v>
+        <v>998</v>
       </c>
       <c r="E733" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="F733" t="s">
-        <v>999</v>
+        <v>976</v>
       </c>
     </row>
     <row r="734" spans="1:6">
@@ -19180,13 +19180,13 @@
         <v>769</v>
       </c>
       <c r="D734" t="s">
-        <v>974</v>
+        <v>983</v>
       </c>
       <c r="E734" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="F734" t="s">
-        <v>984</v>
+        <v>976</v>
       </c>
     </row>
     <row r="735" spans="1:6">
@@ -19200,13 +19200,13 @@
         <v>769</v>
       </c>
       <c r="D735" t="s">
-        <v>974</v>
+        <v>983</v>
       </c>
       <c r="E735" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="F735" t="s">
-        <v>984</v>
+        <v>976</v>
       </c>
     </row>
     <row r="736" spans="1:6">
@@ -19240,13 +19240,13 @@
         <v>18</v>
       </c>
       <c r="D737" t="s">
-        <v>1032</v>
+        <v>1036</v>
       </c>
       <c r="E737" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="F737" t="s">
-        <v>1037</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="738" spans="1:6">
@@ -19260,13 +19260,13 @@
         <v>769</v>
       </c>
       <c r="D738" t="s">
-        <v>1032</v>
+        <v>1039</v>
       </c>
       <c r="E738" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="F738" t="s">
-        <v>1040</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="739" spans="1:6">
@@ -19280,13 +19280,13 @@
         <v>769</v>
       </c>
       <c r="D739" t="s">
-        <v>1032</v>
+        <v>1039</v>
       </c>
       <c r="E739" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="F739" t="s">
-        <v>1040</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="740" spans="1:6">
@@ -19300,13 +19300,13 @@
         <v>769</v>
       </c>
       <c r="D740" t="s">
-        <v>1032</v>
+        <v>1039</v>
       </c>
       <c r="E740" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="F740" t="s">
-        <v>1040</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="741" spans="1:6">
@@ -19320,13 +19320,13 @@
         <v>769</v>
       </c>
       <c r="D741" t="s">
-        <v>1032</v>
+        <v>1039</v>
       </c>
       <c r="E741" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="F741" t="s">
-        <v>1040</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="742" spans="1:6">
@@ -19340,13 +19340,13 @@
         <v>769</v>
       </c>
       <c r="D742" t="s">
-        <v>1032</v>
+        <v>1039</v>
       </c>
       <c r="E742" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="F742" t="s">
-        <v>1040</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="743" spans="1:6">
@@ -19360,13 +19360,13 @@
         <v>18</v>
       </c>
       <c r="D743" t="s">
-        <v>1032</v>
+        <v>1046</v>
       </c>
       <c r="E743" t="s">
-        <v>1046</v>
+        <v>1037</v>
       </c>
       <c r="F743" t="s">
-        <v>1037</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="744" spans="1:6">
@@ -19380,13 +19380,13 @@
         <v>18</v>
       </c>
       <c r="D744" t="s">
-        <v>1032</v>
+        <v>1048</v>
       </c>
       <c r="E744" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="F744" t="s">
-        <v>1049</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="745" spans="1:6">
@@ -19400,13 +19400,13 @@
         <v>22</v>
       </c>
       <c r="D745" t="s">
-        <v>1032</v>
+        <v>1039</v>
       </c>
       <c r="E745" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="F745" t="s">
-        <v>1040</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="746" spans="1:6">
@@ -19420,13 +19420,13 @@
         <v>22</v>
       </c>
       <c r="D746" t="s">
-        <v>1032</v>
+        <v>983</v>
       </c>
       <c r="E746" t="s">
-        <v>983</v>
+        <v>1052</v>
       </c>
       <c r="F746" t="s">
-        <v>1052</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="747" spans="1:6">
@@ -19440,13 +19440,13 @@
         <v>18</v>
       </c>
       <c r="D747" t="s">
-        <v>1032</v>
+        <v>1054</v>
       </c>
       <c r="E747" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="F747" t="s">
-        <v>1055</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="748" spans="1:6">
@@ -19460,13 +19460,13 @@
         <v>16</v>
       </c>
       <c r="D748" t="s">
-        <v>1032</v>
+        <v>1057</v>
       </c>
       <c r="E748" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="F748" t="s">
-        <v>1058</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="749" spans="1:6">
@@ -19480,13 +19480,13 @@
         <v>18</v>
       </c>
       <c r="D749" t="s">
-        <v>1032</v>
+        <v>1060</v>
       </c>
       <c r="E749" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="F749" t="s">
-        <v>1061</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="750" spans="1:6">
@@ -19500,13 +19500,13 @@
         <v>769</v>
       </c>
       <c r="D750" t="s">
-        <v>1032</v>
+        <v>1039</v>
       </c>
       <c r="E750" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="F750" t="s">
-        <v>1040</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="751" spans="1:6">
@@ -19520,13 +19520,13 @@
         <v>18</v>
       </c>
       <c r="D751" t="s">
-        <v>1032</v>
+        <v>1064</v>
       </c>
       <c r="E751" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="F751" t="s">
-        <v>1065</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="752" spans="1:6">
@@ -19540,13 +19540,13 @@
         <v>18</v>
       </c>
       <c r="D752" t="s">
-        <v>1032</v>
+        <v>1067</v>
       </c>
       <c r="E752" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="F752" t="s">
-        <v>1068</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="753" spans="1:6">
@@ -19560,13 +19560,13 @@
         <v>16</v>
       </c>
       <c r="D753" t="s">
-        <v>1032</v>
+        <v>1039</v>
       </c>
       <c r="E753" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="F753" t="s">
-        <v>1040</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="754" spans="1:6">
@@ -19580,13 +19580,13 @@
         <v>18</v>
       </c>
       <c r="D754" t="s">
-        <v>1032</v>
+        <v>1071</v>
       </c>
       <c r="E754" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="F754" t="s">
-        <v>1072</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="755" spans="1:6">
@@ -19600,13 +19600,13 @@
         <v>16</v>
       </c>
       <c r="D755" t="s">
-        <v>1032</v>
+        <v>1039</v>
       </c>
       <c r="E755" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="F755" t="s">
-        <v>1040</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="756" spans="1:6">
@@ -19620,13 +19620,13 @@
         <v>18</v>
       </c>
       <c r="D756" t="s">
-        <v>1032</v>
+        <v>1075</v>
       </c>
       <c r="E756" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="F756" t="s">
-        <v>1076</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="757" spans="1:6">
@@ -19640,13 +19640,13 @@
         <v>18</v>
       </c>
       <c r="D757" t="s">
-        <v>1032</v>
+        <v>1071</v>
       </c>
       <c r="E757" t="s">
-        <v>1071</v>
+        <v>1078</v>
       </c>
       <c r="F757" t="s">
-        <v>1078</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="758" spans="1:6">
@@ -19660,13 +19660,13 @@
         <v>769</v>
       </c>
       <c r="D758" t="s">
-        <v>1032</v>
+        <v>1039</v>
       </c>
       <c r="E758" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="F758" t="s">
-        <v>1040</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="759" spans="1:6">
@@ -19680,13 +19680,13 @@
         <v>16</v>
       </c>
       <c r="D759" t="s">
-        <v>1032</v>
+        <v>1067</v>
       </c>
       <c r="E759" t="s">
-        <v>1067</v>
+        <v>1081</v>
       </c>
       <c r="F759" t="s">
-        <v>1081</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="760" spans="1:6">
@@ -19700,13 +19700,13 @@
         <v>769</v>
       </c>
       <c r="D760" t="s">
-        <v>1032</v>
+        <v>1039</v>
       </c>
       <c r="E760" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="F760" t="s">
-        <v>1040</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="761" spans="1:6">
@@ -19720,13 +19720,13 @@
         <v>769</v>
       </c>
       <c r="D761" t="s">
-        <v>1032</v>
+        <v>1067</v>
       </c>
       <c r="E761" t="s">
-        <v>1067</v>
+        <v>1040</v>
       </c>
       <c r="F761" t="s">
-        <v>1040</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="762" spans="1:6">
@@ -19740,13 +19740,13 @@
         <v>16</v>
       </c>
       <c r="D762" t="s">
-        <v>1032</v>
+        <v>1067</v>
       </c>
       <c r="E762" t="s">
-        <v>1067</v>
+        <v>1040</v>
       </c>
       <c r="F762" t="s">
-        <v>1040</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="763" spans="1:6">
@@ -19760,13 +19760,13 @@
         <v>18</v>
       </c>
       <c r="D763" t="s">
-        <v>1032</v>
+        <v>1036</v>
       </c>
       <c r="E763" t="s">
-        <v>1036</v>
+        <v>1086</v>
       </c>
       <c r="F763" t="s">
-        <v>1086</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="764" spans="1:6">
@@ -19780,13 +19780,13 @@
         <v>769</v>
       </c>
       <c r="D764" t="s">
-        <v>1032</v>
+        <v>1039</v>
       </c>
       <c r="E764" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="F764" t="s">
-        <v>1040</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="765" spans="1:6">
@@ -19800,13 +19800,13 @@
         <v>18</v>
       </c>
       <c r="D765" t="s">
-        <v>1032</v>
+        <v>1089</v>
       </c>
       <c r="E765" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="F765" t="s">
-        <v>1090</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="766" spans="1:6">
@@ -19820,13 +19820,13 @@
         <v>769</v>
       </c>
       <c r="D766" t="s">
-        <v>1032</v>
+        <v>1067</v>
       </c>
       <c r="E766" t="s">
-        <v>1067</v>
+        <v>1040</v>
       </c>
       <c r="F766" t="s">
-        <v>1040</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="767" spans="1:6">
@@ -19840,13 +19840,13 @@
         <v>769</v>
       </c>
       <c r="D767" t="s">
-        <v>1032</v>
+        <v>1039</v>
       </c>
       <c r="E767" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="F767" t="s">
-        <v>1040</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="768" spans="1:6">
@@ -19860,13 +19860,13 @@
         <v>18</v>
       </c>
       <c r="D768" t="s">
-        <v>1032</v>
+        <v>1048</v>
       </c>
       <c r="E768" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="F768" t="s">
-        <v>1049</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="769" spans="1:6">
@@ -19880,13 +19880,13 @@
         <v>22</v>
       </c>
       <c r="D769" t="s">
-        <v>1032</v>
+        <v>1039</v>
       </c>
       <c r="E769" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="F769" t="s">
-        <v>1040</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="770" spans="1:6">
@@ -19900,13 +19900,13 @@
         <v>769</v>
       </c>
       <c r="D770" t="s">
-        <v>1032</v>
+        <v>1039</v>
       </c>
       <c r="E770" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="F770" t="s">
-        <v>1040</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="771" spans="1:6">
@@ -19920,13 +19920,13 @@
         <v>18</v>
       </c>
       <c r="D771" t="s">
-        <v>1032</v>
+        <v>1067</v>
       </c>
       <c r="E771" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="F771" t="s">
-        <v>1065</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="772" spans="1:6">
@@ -19940,13 +19940,13 @@
         <v>769</v>
       </c>
       <c r="D772" t="s">
-        <v>1032</v>
+        <v>1039</v>
       </c>
       <c r="E772" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="F772" t="s">
-        <v>1040</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="773" spans="1:6">
@@ -19960,13 +19960,13 @@
         <v>769</v>
       </c>
       <c r="D773" t="s">
-        <v>1032</v>
+        <v>1039</v>
       </c>
       <c r="E773" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="F773" t="s">
-        <v>1040</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="774" spans="1:6">
@@ -20003,10 +20003,10 @@
         <v>1100</v>
       </c>
       <c r="E775" t="s">
-        <v>1101</v>
+        <v>1104</v>
       </c>
       <c r="F775" t="s">
-        <v>1104</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="776" spans="1:6">
@@ -20023,10 +20023,10 @@
         <v>1100</v>
       </c>
       <c r="E776" t="s">
-        <v>1101</v>
+        <v>1104</v>
       </c>
       <c r="F776" t="s">
-        <v>1104</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="777" spans="1:6">
@@ -20043,10 +20043,10 @@
         <v>1100</v>
       </c>
       <c r="E777" t="s">
-        <v>1101</v>
+        <v>1104</v>
       </c>
       <c r="F777" t="s">
-        <v>1104</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="778" spans="1:6">
@@ -20063,10 +20063,10 @@
         <v>1100</v>
       </c>
       <c r="E778" t="s">
-        <v>1101</v>
+        <v>1104</v>
       </c>
       <c r="F778" t="s">
-        <v>1104</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="779" spans="1:6">
@@ -20083,10 +20083,10 @@
         <v>1100</v>
       </c>
       <c r="E779" t="s">
-        <v>1101</v>
+        <v>1104</v>
       </c>
       <c r="F779" t="s">
-        <v>1104</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="780" spans="1:6">
@@ -20103,10 +20103,10 @@
         <v>1100</v>
       </c>
       <c r="E780" t="s">
-        <v>1101</v>
+        <v>1104</v>
       </c>
       <c r="F780" t="s">
-        <v>1104</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="781" spans="1:6">
@@ -20120,13 +20120,13 @@
         <v>16</v>
       </c>
       <c r="D781" t="s">
-        <v>1100</v>
+        <v>1111</v>
       </c>
       <c r="E781" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="F781" t="s">
-        <v>1112</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="782" spans="1:6">
@@ -20140,13 +20140,13 @@
         <v>16</v>
       </c>
       <c r="D782" t="s">
-        <v>1100</v>
+        <v>1114</v>
       </c>
       <c r="E782" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="F782" t="s">
-        <v>1115</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="783" spans="1:6">
@@ -20163,10 +20163,10 @@
         <v>1100</v>
       </c>
       <c r="E783" t="s">
-        <v>1101</v>
+        <v>1104</v>
       </c>
       <c r="F783" t="s">
-        <v>1104</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="784" spans="1:6">
@@ -20183,10 +20183,10 @@
         <v>1100</v>
       </c>
       <c r="E784" t="s">
-        <v>1101</v>
+        <v>1104</v>
       </c>
       <c r="F784" t="s">
-        <v>1104</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="785" spans="1:6">
@@ -20200,13 +20200,13 @@
         <v>18</v>
       </c>
       <c r="D785" t="s">
-        <v>1100</v>
+        <v>1119</v>
       </c>
       <c r="E785" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="F785" t="s">
-        <v>1120</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="786" spans="1:6">
@@ -20223,10 +20223,10 @@
         <v>1100</v>
       </c>
       <c r="E786" t="s">
-        <v>1101</v>
+        <v>1104</v>
       </c>
       <c r="F786" t="s">
-        <v>1104</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="787" spans="1:6">
@@ -20240,13 +20240,13 @@
         <v>18</v>
       </c>
       <c r="D787" t="s">
-        <v>1100</v>
+        <v>1119</v>
       </c>
       <c r="E787" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="F787" t="s">
-        <v>1120</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="788" spans="1:6">
@@ -20260,13 +20260,13 @@
         <v>18</v>
       </c>
       <c r="D788" t="s">
-        <v>1100</v>
+        <v>1124</v>
       </c>
       <c r="E788" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="F788" t="s">
-        <v>1125</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="789" spans="1:6">
@@ -20283,10 +20283,10 @@
         <v>1100</v>
       </c>
       <c r="E789" t="s">
-        <v>1101</v>
+        <v>1127</v>
       </c>
       <c r="F789" t="s">
-        <v>1127</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="790" spans="1:6">
@@ -20300,13 +20300,13 @@
         <v>18</v>
       </c>
       <c r="D790" t="s">
-        <v>1100</v>
+        <v>1129</v>
       </c>
       <c r="E790" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="F790" t="s">
-        <v>1130</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="791" spans="1:6">
@@ -20323,10 +20323,10 @@
         <v>1100</v>
       </c>
       <c r="E791" t="s">
-        <v>1101</v>
+        <v>1104</v>
       </c>
       <c r="F791" t="s">
-        <v>1104</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="792" spans="1:6">
@@ -20343,10 +20343,10 @@
         <v>1100</v>
       </c>
       <c r="E792" t="s">
-        <v>1101</v>
+        <v>1133</v>
       </c>
       <c r="F792" t="s">
-        <v>1133</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="793" spans="1:6">
@@ -20363,10 +20363,10 @@
         <v>1100</v>
       </c>
       <c r="E793" t="s">
-        <v>1101</v>
+        <v>1104</v>
       </c>
       <c r="F793" t="s">
-        <v>1104</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="794" spans="1:6">
@@ -20380,13 +20380,13 @@
         <v>16</v>
       </c>
       <c r="D794" t="s">
-        <v>1100</v>
+        <v>1039</v>
       </c>
       <c r="E794" t="s">
-        <v>1039</v>
+        <v>1136</v>
       </c>
       <c r="F794" t="s">
-        <v>1136</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="795" spans="1:6">
@@ -20403,10 +20403,10 @@
         <v>1100</v>
       </c>
       <c r="E795" t="s">
-        <v>1101</v>
+        <v>1104</v>
       </c>
       <c r="F795" t="s">
-        <v>1104</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="796" spans="1:6">
@@ -20423,10 +20423,10 @@
         <v>1100</v>
       </c>
       <c r="E796" t="s">
-        <v>1101</v>
+        <v>1104</v>
       </c>
       <c r="F796" t="s">
-        <v>1104</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="797" spans="1:6">
@@ -20440,13 +20440,13 @@
         <v>18</v>
       </c>
       <c r="D797" t="s">
-        <v>1100</v>
+        <v>1140</v>
       </c>
       <c r="E797" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="F797" t="s">
-        <v>1141</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="798" spans="1:6">
@@ -20463,10 +20463,10 @@
         <v>1100</v>
       </c>
       <c r="E798" t="s">
-        <v>1101</v>
+        <v>1143</v>
       </c>
       <c r="F798" t="s">
-        <v>1143</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="799" spans="1:6">
@@ -20483,10 +20483,10 @@
         <v>1100</v>
       </c>
       <c r="E799" t="s">
-        <v>1101</v>
+        <v>1104</v>
       </c>
       <c r="F799" t="s">
-        <v>1104</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="800" spans="1:6">
@@ -20523,10 +20523,10 @@
         <v>1100</v>
       </c>
       <c r="E801" t="s">
-        <v>1101</v>
+        <v>1147</v>
       </c>
       <c r="F801" t="s">
-        <v>1147</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="802" spans="1:6">
@@ -20543,10 +20543,10 @@
         <v>1100</v>
       </c>
       <c r="E802" t="s">
-        <v>1101</v>
+        <v>1104</v>
       </c>
       <c r="F802" t="s">
-        <v>1104</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="803" spans="1:6">
@@ -20563,10 +20563,10 @@
         <v>1100</v>
       </c>
       <c r="E803" t="s">
-        <v>1101</v>
+        <v>1104</v>
       </c>
       <c r="F803" t="s">
-        <v>1104</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="804" spans="1:6">
@@ -20583,10 +20583,10 @@
         <v>1100</v>
       </c>
       <c r="E804" t="s">
-        <v>1101</v>
+        <v>1104</v>
       </c>
       <c r="F804" t="s">
-        <v>1104</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="805" spans="1:6">
@@ -20603,10 +20603,10 @@
         <v>1100</v>
       </c>
       <c r="E805" t="s">
-        <v>1101</v>
+        <v>1104</v>
       </c>
       <c r="F805" t="s">
-        <v>1104</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="806" spans="1:6">
@@ -20623,10 +20623,10 @@
         <v>1100</v>
       </c>
       <c r="E806" t="s">
-        <v>1101</v>
+        <v>1104</v>
       </c>
       <c r="F806" t="s">
-        <v>1104</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="807" spans="1:6">
@@ -20660,13 +20660,13 @@
         <v>18</v>
       </c>
       <c r="D808" t="s">
-        <v>1154</v>
+        <v>1158</v>
       </c>
       <c r="E808" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="F808" t="s">
-        <v>1159</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="809" spans="1:6">
@@ -20680,13 +20680,13 @@
         <v>769</v>
       </c>
       <c r="D809" t="s">
-        <v>1154</v>
+        <v>1161</v>
       </c>
       <c r="E809" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="F809" t="s">
-        <v>1162</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="810" spans="1:6">
@@ -20700,13 +20700,13 @@
         <v>769</v>
       </c>
       <c r="D810" t="s">
-        <v>1154</v>
+        <v>1161</v>
       </c>
       <c r="E810" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="F810" t="s">
-        <v>1162</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="811" spans="1:6">
@@ -20720,13 +20720,13 @@
         <v>769</v>
       </c>
       <c r="D811" t="s">
-        <v>1154</v>
+        <v>1161</v>
       </c>
       <c r="E811" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="F811" t="s">
-        <v>1162</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="812" spans="1:6">
@@ -20740,13 +20740,13 @@
         <v>769</v>
       </c>
       <c r="D812" t="s">
-        <v>1154</v>
+        <v>1161</v>
       </c>
       <c r="E812" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="F812" t="s">
-        <v>1162</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="813" spans="1:6">
@@ -20760,13 +20760,13 @@
         <v>769</v>
       </c>
       <c r="D813" t="s">
-        <v>1154</v>
+        <v>1161</v>
       </c>
       <c r="E813" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="F813" t="s">
-        <v>1162</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="814" spans="1:6">
@@ -20780,13 +20780,13 @@
         <v>769</v>
       </c>
       <c r="D814" t="s">
-        <v>1154</v>
+        <v>1161</v>
       </c>
       <c r="E814" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="F814" t="s">
-        <v>1162</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="815" spans="1:6">
@@ -20800,10 +20800,10 @@
         <v>18</v>
       </c>
       <c r="D815" t="s">
-        <v>1154</v>
+        <v>1158</v>
       </c>
       <c r="E815" t="s">
-        <v>1158</v>
+        <v>1155</v>
       </c>
       <c r="F815" t="s">
         <v>1156</v>
@@ -20820,13 +20820,13 @@
         <v>16</v>
       </c>
       <c r="D816" t="s">
-        <v>1154</v>
+        <v>1161</v>
       </c>
       <c r="E816" t="s">
-        <v>1161</v>
+        <v>1133</v>
       </c>
       <c r="F816" t="s">
-        <v>1133</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="817" spans="1:6">
@@ -20840,13 +20840,13 @@
         <v>769</v>
       </c>
       <c r="D817" t="s">
-        <v>1154</v>
+        <v>1161</v>
       </c>
       <c r="E817" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="F817" t="s">
-        <v>1162</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="818" spans="1:6">
@@ -20863,10 +20863,10 @@
         <v>1154</v>
       </c>
       <c r="E818" t="s">
-        <v>1155</v>
+        <v>1162</v>
       </c>
       <c r="F818" t="s">
-        <v>1162</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="819" spans="1:6">
@@ -20880,13 +20880,13 @@
         <v>769</v>
       </c>
       <c r="D819" t="s">
-        <v>1154</v>
+        <v>1161</v>
       </c>
       <c r="E819" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="F819" t="s">
-        <v>1162</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="820" spans="1:6">
@@ -20900,13 +20900,13 @@
         <v>18</v>
       </c>
       <c r="D820" t="s">
-        <v>1154</v>
+        <v>1174</v>
       </c>
       <c r="E820" t="s">
-        <v>1174</v>
+        <v>1133</v>
       </c>
       <c r="F820" t="s">
-        <v>1133</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="821" spans="1:6">
@@ -20920,13 +20920,13 @@
         <v>769</v>
       </c>
       <c r="D821" t="s">
-        <v>1154</v>
+        <v>1161</v>
       </c>
       <c r="E821" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="F821" t="s">
-        <v>1162</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="822" spans="1:6">
@@ -20940,13 +20940,13 @@
         <v>18</v>
       </c>
       <c r="D822" t="s">
-        <v>1154</v>
+        <v>1177</v>
       </c>
       <c r="E822" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="F822" t="s">
-        <v>1178</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="823" spans="1:6">
@@ -20963,10 +20963,10 @@
         <v>1154</v>
       </c>
       <c r="E823" t="s">
-        <v>1155</v>
+        <v>1162</v>
       </c>
       <c r="F823" t="s">
-        <v>1162</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="824" spans="1:6">
@@ -20980,13 +20980,13 @@
         <v>18</v>
       </c>
       <c r="D824" t="s">
-        <v>1154</v>
+        <v>1174</v>
       </c>
       <c r="E824" t="s">
-        <v>1174</v>
+        <v>1181</v>
       </c>
       <c r="F824" t="s">
-        <v>1181</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="825" spans="1:6">
@@ -21000,13 +21000,13 @@
         <v>18</v>
       </c>
       <c r="D825" t="s">
-        <v>1154</v>
+        <v>1183</v>
       </c>
       <c r="E825" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="F825" t="s">
-        <v>1184</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="826" spans="1:6">
@@ -21020,13 +21020,13 @@
         <v>769</v>
       </c>
       <c r="D826" t="s">
-        <v>1154</v>
+        <v>1161</v>
       </c>
       <c r="E826" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="F826" t="s">
-        <v>1162</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="827" spans="1:6">
@@ -21040,13 +21040,13 @@
         <v>769</v>
       </c>
       <c r="D827" t="s">
-        <v>1154</v>
+        <v>1161</v>
       </c>
       <c r="E827" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="F827" t="s">
-        <v>1162</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="828" spans="1:6">
@@ -21060,13 +21060,13 @@
         <v>22</v>
       </c>
       <c r="D828" t="s">
-        <v>1154</v>
+        <v>1188</v>
       </c>
       <c r="E828" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="F828" t="s">
-        <v>1189</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="829" spans="1:6">
@@ -21080,13 +21080,13 @@
         <v>16</v>
       </c>
       <c r="D829" t="s">
-        <v>1154</v>
+        <v>1161</v>
       </c>
       <c r="E829" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="F829" t="s">
-        <v>1162</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="830" spans="1:6">
@@ -21100,13 +21100,13 @@
         <v>18</v>
       </c>
       <c r="D830" t="s">
-        <v>1154</v>
+        <v>1192</v>
       </c>
       <c r="E830" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="F830" t="s">
-        <v>1193</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="831" spans="1:6">
@@ -21120,13 +21120,13 @@
         <v>769</v>
       </c>
       <c r="D831" t="s">
-        <v>1154</v>
+        <v>1161</v>
       </c>
       <c r="E831" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="F831" t="s">
-        <v>1162</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="832" spans="1:6">
@@ -21140,13 +21140,13 @@
         <v>769</v>
       </c>
       <c r="D832" t="s">
-        <v>1154</v>
+        <v>1161</v>
       </c>
       <c r="E832" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="F832" t="s">
-        <v>1162</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="833" spans="1:6">
@@ -21160,13 +21160,13 @@
         <v>22</v>
       </c>
       <c r="D833" t="s">
-        <v>1154</v>
+        <v>1161</v>
       </c>
       <c r="E833" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="F833" t="s">
-        <v>1162</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="834" spans="1:6">
@@ -21180,13 +21180,13 @@
         <v>18</v>
       </c>
       <c r="D834" t="s">
-        <v>1154</v>
+        <v>1188</v>
       </c>
       <c r="E834" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="F834" t="s">
-        <v>1189</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="835" spans="1:6">
@@ -21200,13 +21200,13 @@
         <v>769</v>
       </c>
       <c r="D835" t="s">
-        <v>1154</v>
+        <v>1161</v>
       </c>
       <c r="E835" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="F835" t="s">
-        <v>1162</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="836" spans="1:6">
@@ -21243,10 +21243,10 @@
         <v>1200</v>
       </c>
       <c r="E837" t="s">
-        <v>1201</v>
+        <v>1204</v>
       </c>
       <c r="F837" t="s">
-        <v>1204</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="838" spans="1:6">
@@ -21260,13 +21260,13 @@
         <v>18</v>
       </c>
       <c r="D838" t="s">
-        <v>1200</v>
+        <v>1206</v>
       </c>
       <c r="E838" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="F838" t="s">
-        <v>1207</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="839" spans="1:6">
@@ -21280,13 +21280,13 @@
         <v>18</v>
       </c>
       <c r="D839" t="s">
-        <v>1200</v>
+        <v>1209</v>
       </c>
       <c r="E839" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="F839" t="s">
-        <v>1210</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="840" spans="1:6">
@@ -21303,10 +21303,10 @@
         <v>1200</v>
       </c>
       <c r="E840" t="s">
-        <v>1201</v>
+        <v>1204</v>
       </c>
       <c r="F840" t="s">
-        <v>1204</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="841" spans="1:6">
@@ -21323,10 +21323,10 @@
         <v>1200</v>
       </c>
       <c r="E841" t="s">
-        <v>1201</v>
+        <v>1204</v>
       </c>
       <c r="F841" t="s">
-        <v>1204</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="842" spans="1:6">
@@ -21343,10 +21343,10 @@
         <v>1200</v>
       </c>
       <c r="E842" t="s">
-        <v>1201</v>
+        <v>1214</v>
       </c>
       <c r="F842" t="s">
-        <v>1214</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="843" spans="1:6">
@@ -21363,10 +21363,10 @@
         <v>1200</v>
       </c>
       <c r="E843" t="s">
-        <v>1201</v>
+        <v>1204</v>
       </c>
       <c r="F843" t="s">
-        <v>1204</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="844" spans="1:6">
@@ -21383,10 +21383,10 @@
         <v>1200</v>
       </c>
       <c r="E844" t="s">
-        <v>1201</v>
+        <v>1204</v>
       </c>
       <c r="F844" t="s">
-        <v>1204</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="845" spans="1:6">
@@ -21403,10 +21403,10 @@
         <v>1200</v>
       </c>
       <c r="E845" t="s">
-        <v>1201</v>
+        <v>1204</v>
       </c>
       <c r="F845" t="s">
-        <v>1204</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="846" spans="1:6">
@@ -21423,10 +21423,10 @@
         <v>1200</v>
       </c>
       <c r="E846" t="s">
-        <v>1201</v>
+        <v>1204</v>
       </c>
       <c r="F846" t="s">
-        <v>1204</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="847" spans="1:6">
@@ -21443,10 +21443,10 @@
         <v>1200</v>
       </c>
       <c r="E847" t="s">
-        <v>1201</v>
+        <v>1204</v>
       </c>
       <c r="F847" t="s">
-        <v>1204</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="848" spans="1:6">
@@ -21463,10 +21463,10 @@
         <v>1200</v>
       </c>
       <c r="E848" t="s">
-        <v>1201</v>
+        <v>1204</v>
       </c>
       <c r="F848" t="s">
-        <v>1204</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="849" spans="1:6">
@@ -21483,10 +21483,10 @@
         <v>1200</v>
       </c>
       <c r="E849" t="s">
-        <v>1201</v>
+        <v>1204</v>
       </c>
       <c r="F849" t="s">
-        <v>1204</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="850" spans="1:6">
@@ -21500,10 +21500,10 @@
         <v>18</v>
       </c>
       <c r="D850" t="s">
-        <v>1200</v>
+        <v>1223</v>
       </c>
       <c r="E850" t="s">
-        <v>1223</v>
+        <v>1201</v>
       </c>
       <c r="F850" t="s">
         <v>1202</v>
@@ -21523,10 +21523,10 @@
         <v>1200</v>
       </c>
       <c r="E851" t="s">
-        <v>1201</v>
+        <v>1204</v>
       </c>
       <c r="F851" t="s">
-        <v>1204</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="852" spans="1:6">
@@ -21540,13 +21540,13 @@
         <v>18</v>
       </c>
       <c r="D852" t="s">
-        <v>1200</v>
+        <v>1226</v>
       </c>
       <c r="E852" t="s">
-        <v>1226</v>
+        <v>1214</v>
       </c>
       <c r="F852" t="s">
-        <v>1214</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="853" spans="1:6">
@@ -21560,13 +21560,13 @@
         <v>18</v>
       </c>
       <c r="D853" t="s">
-        <v>1200</v>
+        <v>1223</v>
       </c>
       <c r="E853" t="s">
-        <v>1223</v>
+        <v>1228</v>
       </c>
       <c r="F853" t="s">
-        <v>1228</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="854" spans="1:6">
@@ -21583,10 +21583,10 @@
         <v>1200</v>
       </c>
       <c r="E854" t="s">
-        <v>1201</v>
+        <v>1204</v>
       </c>
       <c r="F854" t="s">
-        <v>1204</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="855" spans="1:6">
@@ -21600,13 +21600,13 @@
         <v>18</v>
       </c>
       <c r="D855" t="s">
-        <v>1200</v>
+        <v>1231</v>
       </c>
       <c r="E855" t="s">
-        <v>1231</v>
+        <v>1204</v>
       </c>
       <c r="F855" t="s">
-        <v>1204</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="856" spans="1:6">
@@ -21623,10 +21623,10 @@
         <v>1200</v>
       </c>
       <c r="E856" t="s">
-        <v>1201</v>
+        <v>1233</v>
       </c>
       <c r="F856" t="s">
-        <v>1233</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="857" spans="1:6">
@@ -21643,10 +21643,10 @@
         <v>1200</v>
       </c>
       <c r="E857" t="s">
-        <v>1201</v>
+        <v>1204</v>
       </c>
       <c r="F857" t="s">
-        <v>1204</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="858" spans="1:6">
@@ -21660,13 +21660,13 @@
         <v>18</v>
       </c>
       <c r="D858" t="s">
-        <v>1200</v>
+        <v>1236</v>
       </c>
       <c r="E858" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="F858" t="s">
-        <v>1237</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="859" spans="1:6">
@@ -21680,13 +21680,13 @@
         <v>18</v>
       </c>
       <c r="D859" t="s">
-        <v>1200</v>
+        <v>1239</v>
       </c>
       <c r="E859" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="F859" t="s">
-        <v>1240</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="860" spans="1:6">
@@ -21703,10 +21703,10 @@
         <v>1200</v>
       </c>
       <c r="E860" t="s">
-        <v>1201</v>
+        <v>1204</v>
       </c>
       <c r="F860" t="s">
-        <v>1204</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="861" spans="1:6">
@@ -21723,10 +21723,10 @@
         <v>1200</v>
       </c>
       <c r="E861" t="s">
-        <v>1201</v>
+        <v>1204</v>
       </c>
       <c r="F861" t="s">
-        <v>1204</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="862" spans="1:6">
@@ -21743,10 +21743,10 @@
         <v>1200</v>
       </c>
       <c r="E862" t="s">
-        <v>1201</v>
+        <v>1204</v>
       </c>
       <c r="F862" t="s">
-        <v>1204</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="863" spans="1:6">
@@ -21763,10 +21763,10 @@
         <v>1200</v>
       </c>
       <c r="E863" t="s">
-        <v>1201</v>
+        <v>1204</v>
       </c>
       <c r="F863" t="s">
-        <v>1204</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="864" spans="1:6">
@@ -21783,10 +21783,10 @@
         <v>1200</v>
       </c>
       <c r="E864" t="s">
-        <v>1201</v>
+        <v>1204</v>
       </c>
       <c r="F864" t="s">
-        <v>1204</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="865" spans="1:6">
@@ -21803,10 +21803,10 @@
         <v>1200</v>
       </c>
       <c r="E865" t="s">
-        <v>1201</v>
+        <v>1204</v>
       </c>
       <c r="F865" t="s">
-        <v>1204</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="866" spans="1:6">
@@ -21823,10 +21823,10 @@
         <v>1200</v>
       </c>
       <c r="E866" t="s">
-        <v>1201</v>
+        <v>1204</v>
       </c>
       <c r="F866" t="s">
-        <v>1204</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="867" spans="1:6">
@@ -21843,10 +21843,10 @@
         <v>1200</v>
       </c>
       <c r="E867" t="s">
-        <v>1201</v>
+        <v>1204</v>
       </c>
       <c r="F867" t="s">
-        <v>1204</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="868" spans="1:6">
@@ -21863,10 +21863,10 @@
         <v>1200</v>
       </c>
       <c r="E868" t="s">
-        <v>1201</v>
+        <v>1204</v>
       </c>
       <c r="F868" t="s">
-        <v>1204</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="869" spans="1:6">
@@ -21940,13 +21940,13 @@
         <v>18</v>
       </c>
       <c r="D872" t="s">
-        <v>1251</v>
+        <v>1258</v>
       </c>
       <c r="E872" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="F872" t="s">
-        <v>1259</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="873" spans="1:6">
@@ -22003,10 +22003,10 @@
         <v>1251</v>
       </c>
       <c r="E875" t="s">
-        <v>1252</v>
+        <v>1259</v>
       </c>
       <c r="F875" t="s">
-        <v>1259</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="876" spans="1:6">
@@ -22020,13 +22020,13 @@
         <v>22</v>
       </c>
       <c r="D876" t="s">
-        <v>1251</v>
+        <v>1264</v>
       </c>
       <c r="E876" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="F876" t="s">
-        <v>1265</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="877" spans="1:6">
@@ -22043,10 +22043,10 @@
         <v>1251</v>
       </c>
       <c r="E877" t="s">
-        <v>1252</v>
+        <v>1259</v>
       </c>
       <c r="F877" t="s">
-        <v>1259</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="878" spans="1:6">
@@ -22060,13 +22060,13 @@
         <v>18</v>
       </c>
       <c r="D878" t="s">
-        <v>1251</v>
+        <v>1264</v>
       </c>
       <c r="E878" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="F878" t="s">
-        <v>1265</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="879" spans="1:6">
@@ -22200,13 +22200,13 @@
         <v>16</v>
       </c>
       <c r="D885" t="s">
-        <v>1251</v>
+        <v>1275</v>
       </c>
       <c r="E885" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="F885" t="s">
-        <v>1276</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="886" spans="1:6">
@@ -22220,13 +22220,13 @@
         <v>1255</v>
       </c>
       <c r="D886" t="s">
-        <v>1251</v>
+        <v>1278</v>
       </c>
       <c r="E886" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="F886" t="s">
-        <v>1279</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="887" spans="1:6">
@@ -22243,10 +22243,10 @@
         <v>1251</v>
       </c>
       <c r="E887" t="s">
-        <v>1252</v>
+        <v>1279</v>
       </c>
       <c r="F887" t="s">
-        <v>1279</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="888" spans="1:6">
@@ -22260,13 +22260,13 @@
         <v>1255</v>
       </c>
       <c r="D888" t="s">
-        <v>1251</v>
+        <v>1278</v>
       </c>
       <c r="E888" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="F888" t="s">
-        <v>1279</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="889" spans="1:6">
@@ -22280,13 +22280,13 @@
         <v>22</v>
       </c>
       <c r="D889" t="s">
-        <v>1251</v>
+        <v>1278</v>
       </c>
       <c r="E889" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="F889" t="s">
-        <v>1279</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="890" spans="1:6">
@@ -22300,13 +22300,13 @@
         <v>769</v>
       </c>
       <c r="D890" t="s">
-        <v>1251</v>
+        <v>1278</v>
       </c>
       <c r="E890" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="F890" t="s">
-        <v>1279</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="891" spans="1:6">
@@ -22320,13 +22320,13 @@
         <v>1255</v>
       </c>
       <c r="D891" t="s">
-        <v>1251</v>
+        <v>1278</v>
       </c>
       <c r="E891" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="F891" t="s">
-        <v>1279</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="892" spans="1:6">
@@ -22340,13 +22340,13 @@
         <v>1255</v>
       </c>
       <c r="D892" t="s">
-        <v>1251</v>
+        <v>1278</v>
       </c>
       <c r="E892" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="F892" t="s">
-        <v>1279</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="893" spans="1:6">
@@ -22363,10 +22363,10 @@
         <v>1251</v>
       </c>
       <c r="E893" t="s">
-        <v>1252</v>
+        <v>1279</v>
       </c>
       <c r="F893" t="s">
-        <v>1279</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="894" spans="1:6">
@@ -22403,10 +22403,10 @@
         <v>1251</v>
       </c>
       <c r="E895" t="s">
-        <v>1252</v>
+        <v>1259</v>
       </c>
       <c r="F895" t="s">
-        <v>1259</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="896" spans="1:6">
@@ -22423,10 +22423,10 @@
         <v>1251</v>
       </c>
       <c r="E896" t="s">
-        <v>1252</v>
+        <v>1259</v>
       </c>
       <c r="F896" t="s">
-        <v>1259</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="897" spans="1:6">
@@ -22623,10 +22623,10 @@
         <v>1299</v>
       </c>
       <c r="E906" t="s">
-        <v>1300</v>
+        <v>1303</v>
       </c>
       <c r="F906" t="s">
-        <v>1303</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="907" spans="1:6">
@@ -22643,10 +22643,10 @@
         <v>1299</v>
       </c>
       <c r="E907" t="s">
-        <v>1300</v>
+        <v>1303</v>
       </c>
       <c r="F907" t="s">
-        <v>1303</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="908" spans="1:6">
@@ -22663,10 +22663,10 @@
         <v>1299</v>
       </c>
       <c r="E908" t="s">
-        <v>1300</v>
+        <v>1303</v>
       </c>
       <c r="F908" t="s">
-        <v>1303</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="909" spans="1:6">
@@ -22683,10 +22683,10 @@
         <v>1299</v>
       </c>
       <c r="E909" t="s">
-        <v>1300</v>
+        <v>1303</v>
       </c>
       <c r="F909" t="s">
-        <v>1303</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="910" spans="1:6">
@@ -22703,10 +22703,10 @@
         <v>1299</v>
       </c>
       <c r="E910" t="s">
-        <v>1300</v>
+        <v>1303</v>
       </c>
       <c r="F910" t="s">
-        <v>1303</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="911" spans="1:6">
@@ -22723,10 +22723,10 @@
         <v>1299</v>
       </c>
       <c r="E911" t="s">
-        <v>1300</v>
+        <v>1303</v>
       </c>
       <c r="F911" t="s">
-        <v>1303</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="912" spans="1:6">
@@ -22743,10 +22743,10 @@
         <v>1299</v>
       </c>
       <c r="E912" t="s">
-        <v>1300</v>
+        <v>1303</v>
       </c>
       <c r="F912" t="s">
-        <v>1303</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="913" spans="1:6">
@@ -22763,10 +22763,10 @@
         <v>1299</v>
       </c>
       <c r="E913" t="s">
-        <v>1300</v>
+        <v>1303</v>
       </c>
       <c r="F913" t="s">
-        <v>1303</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="914" spans="1:6">
@@ -22780,13 +22780,13 @@
         <v>1255</v>
       </c>
       <c r="D914" t="s">
-        <v>1299</v>
+        <v>1258</v>
       </c>
       <c r="E914" t="s">
-        <v>1258</v>
+        <v>1312</v>
       </c>
       <c r="F914" t="s">
-        <v>1312</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="915" spans="1:6">
@@ -22800,13 +22800,13 @@
         <v>1255</v>
       </c>
       <c r="D915" t="s">
-        <v>1299</v>
+        <v>1258</v>
       </c>
       <c r="E915" t="s">
-        <v>1258</v>
+        <v>1312</v>
       </c>
       <c r="F915" t="s">
-        <v>1312</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="916" spans="1:6">
@@ -22820,13 +22820,13 @@
         <v>22</v>
       </c>
       <c r="D916" t="s">
-        <v>1299</v>
+        <v>1258</v>
       </c>
       <c r="E916" t="s">
-        <v>1258</v>
+        <v>1312</v>
       </c>
       <c r="F916" t="s">
-        <v>1312</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="917" spans="1:6">
@@ -22840,13 +22840,13 @@
         <v>769</v>
       </c>
       <c r="D917" t="s">
-        <v>1299</v>
+        <v>1258</v>
       </c>
       <c r="E917" t="s">
-        <v>1258</v>
+        <v>1312</v>
       </c>
       <c r="F917" t="s">
-        <v>1312</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="918" spans="1:6">
@@ -22860,13 +22860,13 @@
         <v>1255</v>
       </c>
       <c r="D918" t="s">
-        <v>1299</v>
+        <v>1317</v>
       </c>
       <c r="E918" t="s">
-        <v>1317</v>
+        <v>1312</v>
       </c>
       <c r="F918" t="s">
-        <v>1312</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="919" spans="1:6">
@@ -22880,13 +22880,13 @@
         <v>1255</v>
       </c>
       <c r="D919" t="s">
-        <v>1299</v>
+        <v>1258</v>
       </c>
       <c r="E919" t="s">
-        <v>1258</v>
+        <v>1312</v>
       </c>
       <c r="F919" t="s">
-        <v>1312</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="920" spans="1:6">
@@ -22900,13 +22900,13 @@
         <v>1255</v>
       </c>
       <c r="D920" t="s">
-        <v>1299</v>
+        <v>1258</v>
       </c>
       <c r="E920" t="s">
-        <v>1258</v>
+        <v>1312</v>
       </c>
       <c r="F920" t="s">
-        <v>1312</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="921" spans="1:6">
@@ -22923,10 +22923,10 @@
         <v>1299</v>
       </c>
       <c r="E921" t="s">
-        <v>1300</v>
+        <v>1303</v>
       </c>
       <c r="F921" t="s">
-        <v>1303</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="922" spans="1:6">
@@ -22943,10 +22943,10 @@
         <v>1299</v>
       </c>
       <c r="E922" t="s">
-        <v>1300</v>
+        <v>1303</v>
       </c>
       <c r="F922" t="s">
-        <v>1303</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="923" spans="1:6">
@@ -22963,10 +22963,10 @@
         <v>1299</v>
       </c>
       <c r="E923" t="s">
-        <v>1300</v>
+        <v>1303</v>
       </c>
       <c r="F923" t="s">
-        <v>1303</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="924" spans="1:6">
@@ -22983,10 +22983,10 @@
         <v>1299</v>
       </c>
       <c r="E924" t="s">
-        <v>1300</v>
+        <v>1303</v>
       </c>
       <c r="F924" t="s">
-        <v>1303</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="925" spans="1:6">
@@ -23003,10 +23003,10 @@
         <v>1299</v>
       </c>
       <c r="E925" t="s">
-        <v>1300</v>
+        <v>1303</v>
       </c>
       <c r="F925" t="s">
-        <v>1303</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="926" spans="1:6">
@@ -23023,10 +23023,10 @@
         <v>1299</v>
       </c>
       <c r="E926" t="s">
-        <v>1300</v>
+        <v>1303</v>
       </c>
       <c r="F926" t="s">
-        <v>1303</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="927" spans="1:6">
@@ -23043,10 +23043,10 @@
         <v>1299</v>
       </c>
       <c r="E927" t="s">
-        <v>1300</v>
+        <v>1303</v>
       </c>
       <c r="F927" t="s">
-        <v>1303</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="928" spans="1:6">
@@ -23063,10 +23063,10 @@
         <v>1299</v>
       </c>
       <c r="E928" t="s">
-        <v>1300</v>
+        <v>1303</v>
       </c>
       <c r="F928" t="s">
-        <v>1303</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="929" spans="1:6">
@@ -23083,10 +23083,10 @@
         <v>1299</v>
       </c>
       <c r="E929" t="s">
-        <v>1300</v>
+        <v>1303</v>
       </c>
       <c r="F929" t="s">
-        <v>1303</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="930" spans="1:6">
@@ -23103,10 +23103,10 @@
         <v>1299</v>
       </c>
       <c r="E930" t="s">
-        <v>1300</v>
+        <v>1303</v>
       </c>
       <c r="F930" t="s">
-        <v>1303</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="931" spans="1:6">
@@ -23123,10 +23123,10 @@
         <v>1299</v>
       </c>
       <c r="E931" t="s">
-        <v>1300</v>
+        <v>1303</v>
       </c>
       <c r="F931" t="s">
-        <v>1303</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="932" spans="1:6">
@@ -23143,10 +23143,10 @@
         <v>1299</v>
       </c>
       <c r="E932" t="s">
-        <v>1300</v>
+        <v>1303</v>
       </c>
       <c r="F932" t="s">
-        <v>1303</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="933" spans="1:6">
@@ -23163,10 +23163,10 @@
         <v>1299</v>
       </c>
       <c r="E933" t="s">
-        <v>1300</v>
+        <v>1303</v>
       </c>
       <c r="F933" t="s">
-        <v>1303</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="934" spans="1:6">
@@ -23183,10 +23183,10 @@
         <v>1299</v>
       </c>
       <c r="E934" t="s">
-        <v>1300</v>
+        <v>1303</v>
       </c>
       <c r="F934" t="s">
-        <v>1303</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="935" spans="1:6">
@@ -23220,10 +23220,10 @@
         <v>1255</v>
       </c>
       <c r="D936" t="s">
-        <v>1335</v>
+        <v>1339</v>
       </c>
       <c r="E936" t="s">
-        <v>1339</v>
+        <v>1336</v>
       </c>
       <c r="F936" t="s">
         <v>1337</v>
@@ -23240,10 +23240,10 @@
         <v>1255</v>
       </c>
       <c r="D937" t="s">
-        <v>1335</v>
+        <v>1339</v>
       </c>
       <c r="E937" t="s">
-        <v>1339</v>
+        <v>1336</v>
       </c>
       <c r="F937" t="s">
         <v>1337</v>
@@ -23260,10 +23260,10 @@
         <v>1255</v>
       </c>
       <c r="D938" t="s">
-        <v>1335</v>
+        <v>1339</v>
       </c>
       <c r="E938" t="s">
-        <v>1339</v>
+        <v>1336</v>
       </c>
       <c r="F938" t="s">
         <v>1337</v>
@@ -23280,10 +23280,10 @@
         <v>1255</v>
       </c>
       <c r="D939" t="s">
-        <v>1335</v>
+        <v>1339</v>
       </c>
       <c r="E939" t="s">
-        <v>1339</v>
+        <v>1336</v>
       </c>
       <c r="F939" t="s">
         <v>1337</v>
@@ -23300,10 +23300,10 @@
         <v>16</v>
       </c>
       <c r="D940" t="s">
-        <v>1335</v>
+        <v>1339</v>
       </c>
       <c r="E940" t="s">
-        <v>1339</v>
+        <v>1336</v>
       </c>
       <c r="F940" t="s">
         <v>1337</v>
@@ -23320,10 +23320,10 @@
         <v>22</v>
       </c>
       <c r="D941" t="s">
-        <v>1335</v>
+        <v>1339</v>
       </c>
       <c r="E941" t="s">
-        <v>1339</v>
+        <v>1336</v>
       </c>
       <c r="F941" t="s">
         <v>1337</v>
@@ -23340,10 +23340,10 @@
         <v>16</v>
       </c>
       <c r="D942" t="s">
-        <v>1335</v>
+        <v>1339</v>
       </c>
       <c r="E942" t="s">
-        <v>1339</v>
+        <v>1336</v>
       </c>
       <c r="F942" t="s">
         <v>1337</v>
@@ -23360,10 +23360,10 @@
         <v>1255</v>
       </c>
       <c r="D943" t="s">
-        <v>1335</v>
+        <v>1339</v>
       </c>
       <c r="E943" t="s">
-        <v>1339</v>
+        <v>1336</v>
       </c>
       <c r="F943" t="s">
         <v>1337</v>
@@ -23380,10 +23380,10 @@
         <v>1255</v>
       </c>
       <c r="D944" t="s">
-        <v>1335</v>
+        <v>1339</v>
       </c>
       <c r="E944" t="s">
-        <v>1339</v>
+        <v>1336</v>
       </c>
       <c r="F944" t="s">
         <v>1337</v>
@@ -23400,10 +23400,10 @@
         <v>769</v>
       </c>
       <c r="D945" t="s">
-        <v>1335</v>
+        <v>1339</v>
       </c>
       <c r="E945" t="s">
-        <v>1339</v>
+        <v>1336</v>
       </c>
       <c r="F945" t="s">
         <v>1337</v>
@@ -23420,10 +23420,10 @@
         <v>16</v>
       </c>
       <c r="D946" t="s">
-        <v>1335</v>
+        <v>1339</v>
       </c>
       <c r="E946" t="s">
-        <v>1339</v>
+        <v>1336</v>
       </c>
       <c r="F946" t="s">
         <v>1337</v>
@@ -23440,10 +23440,10 @@
         <v>1255</v>
       </c>
       <c r="D947" t="s">
-        <v>1335</v>
+        <v>1339</v>
       </c>
       <c r="E947" t="s">
-        <v>1339</v>
+        <v>1336</v>
       </c>
       <c r="F947" t="s">
         <v>1337</v>
@@ -23460,10 +23460,10 @@
         <v>1255</v>
       </c>
       <c r="D948" t="s">
-        <v>1335</v>
+        <v>1339</v>
       </c>
       <c r="E948" t="s">
-        <v>1339</v>
+        <v>1336</v>
       </c>
       <c r="F948" t="s">
         <v>1337</v>
@@ -23480,10 +23480,10 @@
         <v>1255</v>
       </c>
       <c r="D949" t="s">
-        <v>1335</v>
+        <v>1339</v>
       </c>
       <c r="E949" t="s">
-        <v>1339</v>
+        <v>1336</v>
       </c>
       <c r="F949" t="s">
         <v>1337</v>
@@ -23500,10 +23500,10 @@
         <v>1255</v>
       </c>
       <c r="D950" t="s">
-        <v>1335</v>
+        <v>1339</v>
       </c>
       <c r="E950" t="s">
-        <v>1339</v>
+        <v>1336</v>
       </c>
       <c r="F950" t="s">
         <v>1337</v>
@@ -23520,10 +23520,10 @@
         <v>1255</v>
       </c>
       <c r="D951" t="s">
-        <v>1335</v>
+        <v>1339</v>
       </c>
       <c r="E951" t="s">
-        <v>1339</v>
+        <v>1336</v>
       </c>
       <c r="F951" t="s">
         <v>1337</v>
@@ -23540,10 +23540,10 @@
         <v>769</v>
       </c>
       <c r="D952" t="s">
-        <v>1335</v>
+        <v>1339</v>
       </c>
       <c r="E952" t="s">
-        <v>1339</v>
+        <v>1336</v>
       </c>
       <c r="F952" t="s">
         <v>1337</v>
@@ -23560,10 +23560,10 @@
         <v>1255</v>
       </c>
       <c r="D953" t="s">
-        <v>1335</v>
+        <v>1339</v>
       </c>
       <c r="E953" t="s">
-        <v>1339</v>
+        <v>1336</v>
       </c>
       <c r="F953" t="s">
         <v>1337</v>
@@ -23580,10 +23580,10 @@
         <v>1255</v>
       </c>
       <c r="D954" t="s">
-        <v>1335</v>
+        <v>1339</v>
       </c>
       <c r="E954" t="s">
-        <v>1339</v>
+        <v>1336</v>
       </c>
       <c r="F954" t="s">
         <v>1337</v>
@@ -23600,10 +23600,10 @@
         <v>1255</v>
       </c>
       <c r="D955" t="s">
-        <v>1335</v>
+        <v>1339</v>
       </c>
       <c r="E955" t="s">
-        <v>1339</v>
+        <v>1336</v>
       </c>
       <c r="F955" t="s">
         <v>1337</v>
@@ -23620,10 +23620,10 @@
         <v>16</v>
       </c>
       <c r="D956" t="s">
-        <v>1335</v>
+        <v>1339</v>
       </c>
       <c r="E956" t="s">
-        <v>1339</v>
+        <v>1336</v>
       </c>
       <c r="F956" t="s">
         <v>1337</v>
@@ -23640,10 +23640,10 @@
         <v>1255</v>
       </c>
       <c r="D957" t="s">
-        <v>1335</v>
+        <v>1339</v>
       </c>
       <c r="E957" t="s">
-        <v>1339</v>
+        <v>1336</v>
       </c>
       <c r="F957" t="s">
         <v>1337</v>
@@ -23660,10 +23660,10 @@
         <v>769</v>
       </c>
       <c r="D958" t="s">
-        <v>1335</v>
+        <v>1339</v>
       </c>
       <c r="E958" t="s">
-        <v>1339</v>
+        <v>1336</v>
       </c>
       <c r="F958" t="s">
         <v>1337</v>
@@ -23783,10 +23783,10 @@
         <v>1363</v>
       </c>
       <c r="E964" t="s">
-        <v>1364</v>
+        <v>1371</v>
       </c>
       <c r="F964" t="s">
-        <v>1371</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="965" spans="1:6">
@@ -23803,10 +23803,10 @@
         <v>1363</v>
       </c>
       <c r="E965" t="s">
-        <v>1364</v>
+        <v>1371</v>
       </c>
       <c r="F965" t="s">
-        <v>1371</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="966" spans="1:6">
@@ -23983,10 +23983,10 @@
         <v>1363</v>
       </c>
       <c r="E974" t="s">
-        <v>1364</v>
+        <v>1382</v>
       </c>
       <c r="F974" t="s">
-        <v>1382</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="975" spans="1:6">
@@ -24023,10 +24023,10 @@
         <v>1363</v>
       </c>
       <c r="E976" t="s">
-        <v>1364</v>
+        <v>1385</v>
       </c>
       <c r="F976" t="s">
-        <v>1385</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="977" spans="1:6">
@@ -24043,10 +24043,10 @@
         <v>1363</v>
       </c>
       <c r="E977" t="s">
-        <v>1364</v>
+        <v>1382</v>
       </c>
       <c r="F977" t="s">
-        <v>1382</v>
+        <v>1365</v>
       </c>
     </row>
   </sheetData>
